--- a/test_openalex_200.xlsx
+++ b/test_openalex_200.xlsx
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>63730</v>
+        <v>63735</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>49334</v>
+        <v>49340</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>23698</v>
+        <v>23702</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>25713</v>
+        <v>25716</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>['Ian H. Witten', 'Eibe Frank', 'Mark A. Hall']</t>
+          <t>['Ian H. Witten', 'Eibe Frank']</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>['Witten, I. H.    (Ian H.)    62970', 'Frank, Eibe    62960', 'Hall, Mark A.    (Mark Andrew)    62962']</t>
+          <t>['Witten, I. H.    (Ian H.)    62970    author', 'Frank, Eibe.    62960    author']</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>17771</v>
+        <v>17773</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>11734</v>
+        <v>11733</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>9566</v>
+        <v>9574</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>9861</v>
+        <v>9862</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>10547</v>
+        <v>10548</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>8216</v>
+        <v>8220</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>8823</v>
+        <v>8824</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>['Mikolov T, 2013, ARXIV (CORNELL UNIVERSITY)', 'Jia Y, 2014, ARXIV (CORNELL UNIVERSITY)', 'Sutskever I, 2014, ARXIV (CORNELL UNIVERSITY)', 'Szegedy C, 2014, ARXIV (CORNELL UNIVERSITY)', 'Niu F, 2011, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>['Russakovsky O, 2015, INTERNATIONAL JOURNAL OF COMPUTER VISION', 'Rumelhart D, 1986, NATURE', 'Mnih V, 2015, NATURE', '淳司 柴, 2017, JOURNAL OF JAPAN SOCIETY FOR FUZZY THEORY AND INTELLIGENT INFORMATICS', 'Dean J, 2008, COMMUNICATIONS OF THE ACM', 'Hinton G, 2012, IEEE SIGNAL PROCESSING MAGAZINE', 'Zaharia M, 2012, ', 'Sutskever I, 2013, ', 'Dean J, 2012, ', ', 2000, APPLIED PHYSICS LETTERS', 'Team T, 2016, ARXIV (CORNELL UNIVERSITY)', 'Le Q, 2013, ', 'Hindman B, 2011, UC BERKELEY', 'Verma A, 2015, ', 'Karpathy A, 2014, ', 'Jordan M, 1997, ADVANCES IN PSYCHOLOGY', 'Chu C, 2007, THE MIT PRESS EBOOKS', 'Larochelle H, 2009, ', 'Li M, 2014, OPERATING SYSTEMS DESIGN AND IMPLEMENTATION', 'Burrows M, 2006, OPERATING SYSTEMS DESIGN AND IMPLEMENTATION', 'Ragan‐Kelley J, 2013, ', 'Jean S, 2015, ', 'Hinton G, 1989, ESCHOLARSHIP (CALIFORNIA DIGITAL LIBRARY)', 'Li M, 2014, ', 'Yu Y, 2008, ', 'Chilimbi T, 2014, OPERATING SYSTEMS DESIGN AND IMPLEMENTATION', 'Collobert R, 2002, INFOSCIENCE (ECOLE POLYTECHNIQUE FÉDÉRALE DE LAUSANNE)', 'Smola A, 2010, PROCEEDINGS OF THE VLDB ENDOWMENT', 'Byrd R, 2012, MATHEMATICAL PROGRAMMING', 'Cui H, 2016, ', 'Heigold G, 2013, ', 'Rossbach C, 2013, ', 'Chung E, 2013, ', 'Ovtcharov K, 2015, ', 'Ioffe S, 2024, ARXIV (CORNELL UNIVERSITY)', 'He K, 2015, ARXIV (CORNELL UNIVERSITY)', 'Chen T, 2015, ARXIV (CORNELL UNIVERSITY)', 'Chetlur S, 2014, ARXIV (CORNELL UNIVERSITY)', 'Krizhevsky A, 2014, ARXIV (CORNELL UNIVERSITY)', 'Józefowicz R, 2016, ARXIV (CORNELL UNIVERSITY)', 'Ba J, 2014, ARXIV (CORNELL UNIVERSITY)', 'Xinghao P, 2017, ARXIV (CORNELL UNIVERSITY)', 'Szegedy C, 2015, ARXIV (CORNELL UNIVERSITY)', 'Nair A, 2015, ARXIV (CORNELL UNIVERSITY)', 'Vinyals O, 2014, ARXIV (CORNELL UNIVERSITY)', 'Dai A, 2015, ARXIV (CORNELL UNIVERSITY)', 'Crankshaw D, 2014, ARXIV (CORNELL UNIVERSITY)', 'Lavin A, 2015, ARXIV (CORNELL UNIVERSITY)', 'Moritz P, 2015, ARXIV (CORNELL UNIVERSITY)', 'Mikolov T, 2013, ARXIV (CORNELL UNIVERSITY)', 'Jia Y, 2014, ARXIV (CORNELL UNIVERSITY)', 'Sutskever I, 2014, ARXIV (CORNELL UNIVERSITY)', 'Szegedy C, 2014, ARXIV (CORNELL UNIVERSITY)', 'Niu F, 2011, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>7892</v>
+        <v>7898</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>['John G, 1994, ELSEVIER EBOOKS', 'Lewis D, 1998, LECTURE NOTES IN COMPUTER SCIENCE', 'Lang K, 1995, ELSEVIER EBOOKS', 'Cavnar W, 1994, ', 'Lewis D, 1994, ELSEVIER EBOOKS', 'Jones K, 1997, MORGAN KAUFMANN PUBLISHERS INC. EBOOKS', 'Koller D, 1997, ', 'McCallum A, 1998, ', 'Klinkenberg R, 2000, ', 'Cohen W, 1996, ', 'Lewis D, 1991, SCHOLARWORKS@UMASSAMHERST (UNIVERSITY OF MASSACHUSETTS AMHERST)', 'Cohen W, 1999, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Yang Y, 2002, JOURNAL OF INTELLIGENT INFORMATION SYSTEMS', 'Scott S, 1999, ', 'Galavotti L, 2000, LECTURE NOTES IN COMPUTER SCIENCE', 'Liere R, 1997, ', 'Caropreso M, 2001, ', 'Mladenić D, 1998, LECTURE NOTES IN COMPUTER SCIENCE', 'Weigend A, 1999, INFORMATION RETRIEVAL', 'Wermter S, 1996, LECTURE NOTES IN COMPUTER SCIENCE', 'Taira H, 1999, ', 'Willett P, 1988, ', 'Roussinov D, 1998, UA CAMPUS REPOSITORY (THE UNIVERSITY OF ARIZONA)', 'Fuhr N, 1991, ', 'Diao Y, 2000, LECTURE NOTES IN COMPUTER SCIENCE', 'Escudero G, 2000, EUROPEAN CONFERENCE ON MACHINE LEARNING', 'Frasconi P, 2002, JOURNAL OF INTELLIGENT INFORMATION SYSTEMS', 'Myers K, 2000, ', 'Joachims T, 2002, JOURNAL OF INTELLIGENT INFORMATION SYSTEMS', 'Forsyth R, 1999, ', 'Cohen W, 1995, ELSEVIER EBOOKS', ', 2002, PROGRAM ELECTRONIC LIBRARY AND INFORMATION SYSTEMS', 'Lam W, 1997, INTERNATIONAL JOINT CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Fuhr N, 1985, ', 'Fuhr N, 1984, INTERNATIONAL ACM SIGIR CONFERENCE ON RESEARCH AND DEVELOPMENT IN INFORMATION RETRIEVAL', 'Attardi G, 1998, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Hull D, 1997, ', 'Sable C, 1999, LECTURE NOTES IN COMPUTER SCIENCE', 'Lim J, 1999, ', 'Manning C, 1999, ', 'McCallum A, 2022, ', 'Roth D, 1998, ARXIV.ORG', 'Dagan I, 1997, ARXIV.ORG', 'Rodríguez M, 1997, ARXIV.ORG', 'Lewis D, 1994, ACM TRANSACTIONS ON OFFICE INFORMATION SYSTEMS', 'Knorz G, 1982, INTERNATIONAL ACM SIGIR CONFERENCE ON RESEARCH AND DEVELOPMENT IN INFORMATION RETRIEVAL', 'Fangmeyer H, 1968, IFIP CONGRESS', 'Díaz A, 1998, ', 'Lewis D, 1999, INTERNATIONAL ACM SIGIR CONFERENCE ON RESEARCH AND DEVELOPMENT IN INFORMATION RETRIEVAL', 'Tong R, 1992, TEXT RETRIEVAL CONFERENCE', 'Salton G, 1988, INFORMATION PROCESSING &amp; MANAGEMENT', 'Yang Y, 1999, ', 'Schapire R, 2000, MACHINE LEARNING', 'Robertson S, 1976, JOURNAL OF THE AMERICAN SOCIETY FOR INFORMATION SCIENCE', 'Chakrabarti S, 1998, COMPUTER NETWORKS AND ISDN SYSTEMS', 'Weikum G, 2002, ACM SIGMOD RECORD', 'Tumer K, 1996, CONNECTION SCIENCE', 'Maron M, 1961, JOURNAL OF THE ACM', 'Gale W, 1992, COMPUTERS AND THE HUMANITIES', 'Schütze H, 1995, ', 'Ng H, 1997, ', 'Larkey L, 1996, ', 'Yang Y, 1994, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Crestani F, 1998, ACM COMPUTING SURVEYS', 'Schapire R, 1998, ', 'Masand B, 1992, ', 'Weiss S, 1999, IEEE INTELLIGENT SYSTEMS AND THEIR APPLICATIONS', 'Fuhr N, 1991, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Singhal A, 1996, INFORMATION PROCESSING &amp; MANAGEMENT', 'Yang Y, 1995, ', 'Lam W, 1998, ', 'Wong S, 1995, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Hull D, 1994, ', 'Dörre J, 1999, ', 'Tzeras K, 1993, ', 'Fürnkranz J, 1999, LECTURE NOTES IN COMPUTER SCIENCE', 'Iwayama M, 1995, ', 'Merkl D, 1998, NEUROCOMPUTING', 'Cooper W, 1995, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Fuhr N, 1989, INFORMATION PROCESSING &amp; MANAGEMENT', 'Singhal A, 1997, ', 'Kim Y, 2000, ', 'Frasconi P, 2001, ', 'Biebricher P, 1988, ', 'Iyer R, 2000, ', 'Knight K, 1999, COMMUNICATIONS OF THE ACM', 'Li P, 1996, CONNECTION SCIENCE', 'Papka R, 1998, ', 'Yu K, 1998, ', 'Cooper W, 1991, ', 'Klingbiel P, 1973, INFORMATION STORAGE AND RETRIEVAL', 'Field B, 1975, JOURNAL OF DOCUMENTATION', 'Guthrie L, 1994, ', 'Sable C, 2000, INTERNATIONAL JOURNAL ON DIGITAL LIBRARIES', 'Liddy E, 1994, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Klingbiel P, 1973, INFORMATION STORAGE AND RETRIEVAL', 'Robertson S, 1984, JOURNAL OF DOCUMENTATION', 'Hoyle W, 1973, INFORMATION STORAGE AND RETRIEVAL', 'Wong J, 1996, ACM SIGIR FORUM', 'Cleverdon C, 1984, INFORMATION SERVICES &amp; USE', 'Domingos P, 1997, MACHINE LEARNING', 'Nigam K, 2000, MACHINE LEARNING', 'Joachims T, 1999, ', 'Yang Y, 1999, INFORMATION RETRIEVAL', 'Lewis D, 1994, ARXIV (CORNELL UNIVERSITY)', 'Belkin N, 1992, COMMUNICATIONS OF THE ACM', 'Schütze H, 1998, ', 'Joachims T, 1997, ', 'Apté C, 1994, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Saračević T, 1975, JOURNAL OF THE AMERICAN SOCIETY FOR INFORMATION SCIENCE', 'Dumais S, 2000, ', 'Chakrabarti S, 1998, ', 'Baker L, 1998, ', 'Lewis D, 1992, ', 'Lewis D, 1996, ', 'Rijsbergen C, 1977, JOURNAL OF DOCUMENTATION', 'Androutsopoulos I, 2000, ', 'Lewis D, 1995, ACM SIGIR FORUM', 'Li Y, 1998, THE COMPUTER JOURNAL', 'Nigam K, 1998, ', 'Larkey L, 1998, ', 'Chakrabarti S, 1998, THE VLDB JOURNAL', 'Larkey L, 1999, ', 'Lam S, 2003, ', 'Borko H, 1963, JOURNAL OF THE ACM', 'Creecy R, 1992, COMMUNICATIONS OF THE ACM', 'Oh H, 2000, ', 'Attardi G, 1999, CINECA IRIS INSTITUTIAL RESEARCH INFORMATION SYSTEM (UNIVERSITY OF PISA)', 'Hayes P, 2002, ', 'Amati G, 1999, INFORMATION PROCESSING &amp; MANAGEMENT', 'Heaps H, 1973, INFORMATION AND CONTROL', 'Riloff E, 1994, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Cohen W, 1998, ', 'Hull D, 1996, ', 'Ruiz M, 1999, ', 'Gövert N, 1999, ', 'Ragas H, 1998, ', 'Li H, 1999, ', 'Clack C, 1997, ', 'Hamill K, 1980, JOURNAL OF THE AMERICAN SOCIETY FOR INFORMATION SCIENCE', 'Fuhr N, 1994, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Moulinier I, 1996, LECTURE NOTES IN COMPUTER SCIENCE', 'Rau L, 1991, ', 'Goodman M, 1990, INNOVATIVE APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Junker M, 1998, INTERNATIONAL JOURNAL ON DOCUMENT ANALYSIS AND RECOGNITION (IJDAR)', 'Gray W, 1971, INFORMATION STORAGE AND RETRIEVAL', 'Brückner T, 1997, TEXT RETRIEVAL CONFERENCE']</t>
+          <t>['John G, 1994, ELSEVIER EBOOKS', 'Lewis D, 1998, LECTURE NOTES IN COMPUTER SCIENCE', 'Lang K, 1995, ELSEVIER EBOOKS', 'Cavnar W, 1994, ', 'Lewis D, 1994, ELSEVIER EBOOKS', 'Jones K, 1997, MORGAN KAUFMANN PUBLISHERS INC. EBOOKS', 'Koller D, 1997, ', 'McCallum A, 1998, ', 'Klinkenberg R, 2000, ', 'Cohen W, 1996, ', 'Lewis D, 1991, SCHOLARWORKS@UMASSAMHERST (UNIVERSITY OF MASSACHUSETTS AMHERST)', 'Cohen W, 1999, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Yang Y, 2002, JOURNAL OF INTELLIGENT INFORMATION SYSTEMS', 'Scott S, 1999, ', 'Galavotti L, 2000, LECTURE NOTES IN COMPUTER SCIENCE', 'Liere R, 1997, ', 'Caropreso M, 2001, ', 'Mladenić D, 1998, LECTURE NOTES IN COMPUTER SCIENCE', 'Weigend A, 1999, INFORMATION RETRIEVAL', 'Wermter S, 1996, LECTURE NOTES IN COMPUTER SCIENCE', 'Taira H, 1999, ', 'Willett P, 1988, ', 'Roussinov D, 1998, UA CAMPUS REPOSITORY (THE UNIVERSITY OF ARIZONA)', 'Fuhr N, 1991, ', 'Diao Y, 2000, LECTURE NOTES IN COMPUTER SCIENCE', 'Escudero G, 2000, EUROPEAN CONFERENCE ON MACHINE LEARNING', 'Frasconi P, 2002, JOURNAL OF INTELLIGENT INFORMATION SYSTEMS', 'Myers K, 2000, ', 'Joachims T, 2002, JOURNAL OF INTELLIGENT INFORMATION SYSTEMS', 'Forsyth R, 1999, ', 'Cohen W, 1995, ELSEVIER EBOOKS', ', 2002, PROGRAM ELECTRONIC LIBRARY AND INFORMATION SYSTEMS', 'Lam W, 1997, INTERNATIONAL JOINT CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Fuhr N, 1985, ', 'Fuhr N, 1984, INTERNATIONAL ACM SIGIR CONFERENCE ON RESEARCH AND DEVELOPMENT IN INFORMATION RETRIEVAL', 'Attardi G, 1998, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Hull D, 1997, ', 'Sable C, 1999, LECTURE NOTES IN COMPUTER SCIENCE', 'Lim J, 1999, ', 'Manning C, 1999, ', 'McCallum A, 2022, ', 'Roth D, 1998, ARXIV.ORG', 'Dagan I, 1997, ARXIV.ORG', 'Rodríguez M, 1997, ARXIV.ORG', 'Lewis D, 1994, ACM TRANSACTIONS ON OFFICE INFORMATION SYSTEMS', 'Knorz G, 1982, INTERNATIONAL ACM SIGIR CONFERENCE ON RESEARCH AND DEVELOPMENT IN INFORMATION RETRIEVAL', 'Fangmeyer H, 1968, IFIP CONGRESS', 'Díaz A, 1998, ', 'Lewis D, 1999, INTERNATIONAL ACM SIGIR CONFERENCE ON RESEARCH AND DEVELOPMENT IN INFORMATION RETRIEVAL', 'Tong R, 1992, TEXT RETRIEVAL CONFERENCE', 'Salton G, 1988, INFORMATION PROCESSING &amp; MANAGEMENT', 'Yang Y, 1999, ', 'Schapire R, 2000, MACHINE LEARNING', 'Robertson S, 1976, JOURNAL OF THE AMERICAN SOCIETY FOR INFORMATION SCIENCE', 'Chakrabarti S, 1998, COMPUTER NETWORKS AND ISDN SYSTEMS', 'Weikum G, 2002, ACM SIGMOD RECORD', 'Tumer K, 1996, CONNECTION SCIENCE', 'Maron M, 1961, JOURNAL OF THE ACM', 'Gale W, 1992, COMPUTERS AND THE HUMANITIES', 'Schütze H, 1995, ', 'Ng H, 1997, ', 'Larkey L, 1996, ', 'Yang Y, 1994, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Crestani F, 1998, ACM COMPUTING SURVEYS', 'Schapire R, 1998, ', 'Masand B, 1992, ', 'Weiss S, 1999, IEEE INTELLIGENT SYSTEMS AND THEIR APPLICATIONS', 'Fuhr N, 1991, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Singhal A, 1996, INFORMATION PROCESSING &amp; MANAGEMENT', 'Yang Y, 1995, ', 'Lam W, 1998, ', 'Wong S, 1995, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Hull D, 1994, ', 'Dörre J, 1999, ', 'Tzeras K, 1993, ', 'Fürnkranz J, 1999, LECTURE NOTES IN COMPUTER SCIENCE', 'Iwayama M, 1995, ', 'Merkl D, 1998, NEUROCOMPUTING', 'Cooper W, 1995, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Fuhr N, 1989, INFORMATION PROCESSING &amp; MANAGEMENT', 'Singhal A, 1997, ', 'Kim Y, 2000, ', 'Frasconi P, 2001, ', 'Biebricher P, 1988, ', 'Iyer R, 2000, ', 'Knight K, 1999, COMMUNICATIONS OF THE ACM', 'Li P, 1996, CONNECTION SCIENCE', 'Papka R, 1998, ', 'Yu K, 1998, ', 'Cooper W, 1991, ', 'Klingbiel P, 1973, INFORMATION STORAGE AND RETRIEVAL', 'Field B, 1975, JOURNAL OF DOCUMENTATION', 'Guthrie L, 1994, ', 'Sable C, 2000, INTERNATIONAL JOURNAL ON DIGITAL LIBRARIES', 'Liddy E, 1994, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Klingbiel P, 1973, INFORMATION STORAGE AND RETRIEVAL', 'Robertson S, 1984, JOURNAL OF DOCUMENTATION', 'Hoyle W, 1973, INFORMATION STORAGE AND RETRIEVAL', 'Wong J, 1996, ACM SIGIR FORUM', 'Cleverdon C, 1984, INFORMATION SERVICES &amp; USE', 'Domingos P, 1997, MACHINE LEARNING', 'Nigam K, 2000, MACHINE LEARNING', 'Joachims T, 1999, ', 'Yang Y, 1999, INFORMATION RETRIEVAL', 'Lewis D, 1994, ARXIV (CORNELL UNIVERSITY)', 'Belkin N, 1992, COMMUNICATIONS OF THE ACM', 'Schütze H, 1998, ', 'Joachims T, 1997, ', 'Apté C, 1994, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Saračević T, 1975, JOURNAL OF THE AMERICAN SOCIETY FOR INFORMATION SCIENCE', 'Dumais S, 2000, ', 'Chakrabarti S, 1998, ', 'Baker L, 1998, ', 'Lewis D, 1992, ', 'Lewis D, 1996, ', 'Rijsbergen C, 1977, JOURNAL OF DOCUMENTATION', 'Androutsopoulos I, 2000, ', 'Lewis D, 1995, ACM SIGIR FORUM', 'Li Y, 1998, THE COMPUTER JOURNAL', 'Nigam K, 1998, ', 'Larkey L, 1998, ', 'Chakrabarti S, 1998, THE VLDB JOURNAL', 'Larkey L, 1999, ', 'Lam S, 2003, ', 'Borko H, 1963, JOURNAL OF THE ACM', 'Creecy R, 1992, COMMUNICATIONS OF THE ACM', 'Oh H, 2000, ', 'Attardi G, 1999, CINECA IRIS INSTITUTIAL RESEARCH INFORMATION SYSTEM (UNIVERSITY OF PISA)', 'Hayes P, 2002, ', 'Amati G, 1999, INFORMATION PROCESSING &amp; MANAGEMENT', 'Heaps H, 1973, INFORMATION AND CONTROL', 'Riloff E, 1994, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Cohen W, 1998, ', 'Hull D, 1996, ', 'Ruiz M, 1999, ', 'Gövert N, 1999, ', 'Ragas H, 1998, ', 'Li H, 1999, ', 'Clack C, 1997, ', 'Hamill K, 1980, JOURNAL OF THE AMERICAN SOCIETY FOR INFORMATION SCIENCE', 'Fuhr N, 1994, ACM TRANSACTIONS ON INFORMATION SYSTEMS', 'Moulinier I, 1996, LECTURE NOTES IN COMPUTER SCIENCE', 'Rau L, 1991, ', 'Goodman M, 1990, INNOVATIVE APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Junker M, 1998, INTERNATIONAL JOURNAL ON DOCUMENT ANALYSIS AND RECOGNITION (IJDAR)', 'Gray W, 1971, INFORMATION STORAGE AND RETRIEVAL', 'Brückner T, 1997, TEXT RETRIEVAL CONFERENCE', ', 1999, INDUSTRIAL ROBOT THE INTERNATIONAL JOURNAL OF ROBOTICS RESEARCH AND APPLICATION', 'Deerwester S, 1990, JOURNAL OF THE AMERICAN SOCIETY FOR INFORMATION SCIENCE', 'Joachims T, 1998, LECTURE NOTES IN COMPUTER SCIENCE', 'Salton G, 1975, COMMUNICATIONS OF THE ACM', 'Yang Y, 1997, ', 'Drucker H, 1999, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Dumais S, 1998, ', 'Subashini D, 1993, JOURNAL OF COMPUTATIONAL AND APPLIED MATHEMATICS', 'Willett P, 1988, INFORMATION PROCESSING &amp; MANAGEMENT', 'Kessler B, 1997, ', 'Lewis D, 1995, ', 'Lam W, 1999, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Escudero G, 2000, LECTURE NOTES IN COMPUTER SCIENCE', 'Raghavan V, 2004, CHAPMAN &amp; HALL/CRC COMPUTER AND INFORMATION SCIENCE SERIES', 'Robertson S, 1988, TAYLOR GRAHAM PUBLISHING EBOOKS', 'Riloff E, 1995, ', 'Ruiz M, 1999, ACM SIGIR FORUM', 'Moulinier I, 1996, ', 'Sebastiani F, 2000, ', 'Denoyer L, 2001, ', 'Tauritz D, 2000, INFORMATION SCIENCES', 'Ignatow G, 2017, ', 'Kessler B, 1997, ARXIV.ORG', 'Dagan I, 1997, ARXIV (CORNELL UNIVERSITY)', 'Institute N, 2020, DEFINITIONS', 'Escudero G, 2000, ARXIV.ORG']</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5804</v>
+        <v>5807</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>6553</v>
+        <v>6571</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>7844</v>
+        <v>7848</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>4435</v>
+        <v>4437</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>5863</v>
+        <v>5867</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>['Pan S, 2009, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Silver D, 2016, NATURE', 'Sweeney L, 2002, INTERNATIONAL JOURNAL OF UNCERTAINTY FUZZINESS AND KNOWLEDGE-BASED SYSTEMS', 'Abadi M, 2016, ', 'Goldreich O, 1987, ', 'Bonawitz K, 2017, ', 'Dwork C, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Agrawal R, 2000, ACM SIGMOD RECORD', 'Yao A, 1982, FOUNDATIONS OF COMPUTER SCIENCE', 'Shokri R, 2015, ', 'Mohassel P, 2017, ', 'Rivest R, 1978, ', 'Dowlin N, 2016, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Hitaj B, 2017, ', 'Acar A, 2018, ACM COMPUTING SURVEYS', 'Vaidya J, 2002, ', 'Clifton C, 2010, ', 'Liu J, 2017, ', 'Bogdanov D, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Vaidya J, 2003, ', 'Ho Q, 2013, PUBMED', 'Song S, 2013, ', 'Nikolaenko V, 2013, ', 'Araki T, 2016, ', 'Du W, 2004, ', 'Du W, 2002, SYRACUSE UNIVERSITY LIBRARIES (SYRACUSE UNIVERSITY)', 'Du W, 2005, ', 'Zhang Q, 2015, IEEE TRANSACTIONS ON COMPUTERS', 'Vaidya J, 2004, ', 'Yuan J, 2013, IEEE TRANSACTIONS ON PARALLEL AND DISTRIBUTED SYSTEMS', 'Yu H, 2006, ', 'Yu H, 2006, LECTURE NOTES IN COMPUTER SCIENCE', 'Scannapieco M, 2007, ', 'Aono Y, 2016, ', 'Sanil A, 2004, ', 'Karr A, 2009, ', 'Hall R, 2011, ', 'Mohassel P, 2015, ', 'Bahmani R, 2017, LECTURE NOTES IN COMPUTER SCIENCE', 'McMahan H, 2017, ', 'Vaidya J, 2005, LECTURE NOTES IN COMPUTER SCIENCE', 'Wan L, 2007, ', 'Liang G, 2004, LECTURE NOTES IN COMPUTER SCIENCE', 'Faltings B, 2017, SYNTHESIS LECTURES ON ARTIFICIAL INTELLIGENCE AND MACHINE LEARNING', 'Konečný J, 2016, ARXIV (CORNELL UNIVERSITY)', 'McMahan H, 2016, ARXIV (CORNELL UNIVERSITY)', 'Hesamifard E, 2017, ARXIV (CORNELL UNIVERSITY)', 'Chabanne H, 2017, IACR CRYPTOLOGY EPRINT ARCHIVE', 'Smith V, 2017, ARXIV (CORNELL UNIVERSITY)', ', 2007, THE MIT PRESS EBOOKS', 'Leen T, 2000, ', 'Agrawal R, 2000, ', 'Phong L, 2017, IEEE TRANSACTIONS ON INFORMATION FORENSICS AND SECURITY', 'Mohassel P, 2018, ', 'Riazi M, 2018, ', 'Bourse F, 2018, LECTURE NOTES IN COMPUTER SCIENCE', 'Kim M, 2018, JMIR MEDICAL INFORMATICS', 'Wang S, 2018, ', 'Rouhani B, 2018, 2018 55TH ACM/ESDA/IEEE DESIGN AUTOMATION CONFERENCE (DAC)', 'Kim H, 2018, ', 'Melis L, 2018, ARXIV (CORNELL UNIVERSITY)', 'Chen F, 2018, ', 'Cheng Y, 2019, ', 'Bourse F, 2018, IACR CRYPTOLOGY EPRINT ARCHIVE', 'Faltings B, 2017, SYNTHESIS LECTURES ON ARTIFICIAL INTELLIGENCE AND MACHINE LEARNING', 'Zhao Y, 2018, ARXIV (CORNELL UNIVERSITY)', 'Dariusz W, 2019, SGEM INTERNATIONAL MULTIDISCIPLINARY SCIENTIFIC CONFERENCES ON SOCIAL SCIENCES AND ARTS', 'Bagdasaryan E, 2018, ARXIV (CORNELL UNIVERSITY)', 'Lin Y, 2017, ARXIV (CORNELL UNIVERSITY)', 'Geyer R, 2017, ARXIV (CORNELL UNIVERSITY)', 'Hardy S, 2017, ARXIV (CORNELL UNIVERSITY)', 'Hitaj B, 2017, ARXIV (CORNELL UNIVERSITY)', 'Gascón A, 2016, IACR CRYPTOLOGY EPRINT ARCHIVE', ', 1999, ', 'Nock R, 2018, ARXIV (CORNELL UNIVERSITY)', 'Kilbertus N, 2025, WARWICK RESEARCH ARCHIVE PORTAL (UNIVERSITY OF WARWICK)', 'Su L, 2018, ARXIV (CORNELL UNIVERSITY)', 'Giacomelli I, 2017, IACR CRYPTOLOGY EPRINT ARCHIVE']</t>
+          <t>['Pan S, 2009, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Silver D, 2016, NATURE', 'Sweeney L, 2002, INTERNATIONAL JOURNAL OF UNCERTAINTY FUZZINESS AND KNOWLEDGE-BASED SYSTEMS', 'Abadi M, 2016, ', 'Goldreich O, 1987, ', 'Bonawitz K, 2017, ', 'Dwork C, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Agrawal R, 2000, ACM SIGMOD RECORD', 'Yao A, 1982, FOUNDATIONS OF COMPUTER SCIENCE', 'Shokri R, 2015, ', 'Mohassel P, 2017, ', 'Rivest R, 1978, ', 'Dowlin N, 2016, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Hitaj B, 2017, ', 'Acar A, 2018, ACM COMPUTING SURVEYS', 'Vaidya J, 2002, ', 'Clifton C, 2010, ', 'Liu J, 2017, ', 'Bogdanov D, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Vaidya J, 2003, ', 'Ho Q, 2013, PUBMED', 'Song S, 2013, ', 'Nikolaenko V, 2013, ', 'Araki T, 2016, ', 'Du W, 2004, ', 'Du W, 2002, SYRACUSE UNIVERSITY LIBRARIES (SYRACUSE UNIVERSITY)', 'Du W, 2005, ', 'Zhang Q, 2015, IEEE TRANSACTIONS ON COMPUTERS', 'Vaidya J, 2004, ', 'Yuan J, 2013, IEEE TRANSACTIONS ON PARALLEL AND DISTRIBUTED SYSTEMS', 'Yu H, 2006, ', 'Yu H, 2006, LECTURE NOTES IN COMPUTER SCIENCE', 'Scannapieco M, 2007, ', 'Aono Y, 2016, ', 'Sanil A, 2004, ', 'Karr A, 2009, ', 'Hall R, 2011, ', 'Mohassel P, 2015, ', 'Bahmani R, 2017, LECTURE NOTES IN COMPUTER SCIENCE', 'McMahan H, 2017, ', 'Vaidya J, 2005, LECTURE NOTES IN COMPUTER SCIENCE', 'Wan L, 2007, ', 'Liang G, 2004, LECTURE NOTES IN COMPUTER SCIENCE', 'Faltings B, 2017, SYNTHESIS LECTURES ON ARTIFICIAL INTELLIGENCE AND MACHINE LEARNING', 'Konečný J, 2016, ARXIV (CORNELL UNIVERSITY)', 'McMahan H, 2016, ARXIV (CORNELL UNIVERSITY)', 'Hesamifard E, 2017, ARXIV (CORNELL UNIVERSITY)', 'Chabanne H, 2017, IACR CRYPTOLOGY EPRINT ARCHIVE', 'Smith V, 2017, ARXIV (CORNELL UNIVERSITY)', ', 2007, THE MIT PRESS EBOOKS', 'Leen T, 2000, ', 'Agrawal R, 2000, ', 'Phong L, 2017, IEEE TRANSACTIONS ON INFORMATION FORENSICS AND SECURITY', 'Mohassel P, 2018, ', 'Riazi M, 2018, ', 'Bourse F, 2018, LECTURE NOTES IN COMPUTER SCIENCE', 'Kim M, 2018, JMIR MEDICAL INFORMATICS', 'Wang S, 2018, ', 'Rouhani B, 2018, 2018 55TH ACM/ESDA/IEEE DESIGN AUTOMATION CONFERENCE (DAC)', 'Kim H, 2018, ', 'Melis L, 2018, ARXIV (CORNELL UNIVERSITY)', 'Chen F, 2018, ', 'Cheng Y, 2019, ', 'Bourse F, 2018, IACR CRYPTOLOGY EPRINT ARCHIVE', 'Faltings B, 2017, SYNTHESIS LECTURES ON ARTIFICIAL INTELLIGENCE AND MACHINE LEARNING', 'Zhao Y, 2018, ARXIV (CORNELL UNIVERSITY)', 'Elke E, 2019, SGEM INTERNATIONAL MULTIDISCIPLINARY SCIENTIFIC CONFERENCES ON SOCIAL SCIENCES AND ARTS', 'Bagdasaryan E, 2018, ARXIV (CORNELL UNIVERSITY)', 'Lin Y, 2017, ARXIV (CORNELL UNIVERSITY)', 'Geyer R, 2017, ARXIV (CORNELL UNIVERSITY)', 'Hardy S, 2017, ARXIV (CORNELL UNIVERSITY)', 'Hitaj B, 2017, ARXIV (CORNELL UNIVERSITY)', 'Gascón A, 2016, IACR CRYPTOLOGY EPRINT ARCHIVE', ', 1999, ', 'Nock R, 2018, ARXIV (CORNELL UNIVERSITY)', 'Kilbertus N, 2025, WARWICK RESEARCH ARCHIVE PORTAL (UNIVERSITY OF WARWICK)', 'Su L, 2018, ARXIV (CORNELL UNIVERSITY)', 'Giacomelli I, 2017, IACR CRYPTOLOGY EPRINT ARCHIVE']</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>7226</v>
+        <v>7227</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4521</v>
+        <v>4527</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>['Kohn W, 1965, PHYSICAL REVIEW', 'Schmidhuber J, 2014, NEURAL NETWORKS', 'Jain A, 2013, APL MATERIALS', 'Shawe‐Taylor J, 2004, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Sterling T, 2015, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Harrow A, 2009, PHYSICAL REVIEW LETTERS', 'Bartók A, 2010, PHYSICAL REVIEW LETTERS', 'Lake B, 2015, SCIENCE', 'Schmidt M, 2009, SCIENCE', 'Drori I, 2022, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Saal J, 2013, JOM', 'Rupp M, 2012, PHYSICAL REVIEW LETTERS', 'Hansch C, 1964, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Curtarolo S, 2013, NATURE MATERIALS', 'Tropsha A, 2010, MOLECULAR INFORMATICS', 'Dirac P, 1929, PROCEEDINGS OF THE ROYAL SOCIETY OF LONDON SERIES A CONTAINING PAPERS OF A MATHEMATICAL AND PHYSICAL CHARACTER', 'Lejaeghere K, 2016, SCIENCE', 'Aspuru‐Guzik A, 2005, SCIENCE', 'Ghiringhelli L, 2015, PHYSICAL REVIEW LETTERS', 'Hand D, 2001, INTERNATIONAL STATISTICAL REVIEW', 'Pilania G, 2013, SCIENTIFIC REPORTS', 'Fourches D, 2010, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Billinge S, 2007, SCIENCE', 'Corey E, 1969, SCIENCE', 'Hachmann J, 2011, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Snyder J, 2012, PHYSICAL REVIEW LETTERS', 'Havu V, 2009, JOURNAL OF COMPUTATIONAL PHYSICS', 'Hautier G, 2010, CHEMISTRY OF MATERIALS', 'Schütt K, 2014, PHYSICAL REVIEW B', 'Calderón C, 2015, COMPUTATIONAL MATERIALS SCIENCE', 'Faber F, 2016, PHYSICAL REVIEW LETTERS', 'Shakhnarovich G, 2005, ', 'Kalinin S, 2015, NATURE MATERIALS', 'Handley C, 2010, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Franceschetti A, 1999, NATURE', 'Christensen R, 2015, CATALYSIS SCIENCE &amp; TECHNOLOGY', 'Fleuren W, 2015, METHODS', 'Kireeva N, 2012, MOLECULAR INFORMATICS', 'Pople J, 1999, ANGEWANDTE CHEMIE INTERNATIONAL EDITION', 'Bonchev D, 1994, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Albuquerque V, 2008, NONDESTRUCTIVE TESTING AND EVALUATION', 'Wicker J, 2014, CRYSTENGCOMM', 'Kühn C, 1996, THE JOURNAL OF PHYSICAL CHEMISTRY', 'Walsh A, 2015, NATURE CHEMISTRY', ', 2013, ', 'Oprea T, 2006, DRUG DISCOVERY TODAY TECHNOLOGIES', 'Kiselyova N, 1998, JOURNAL OF ALLOYS AND COMPOUNDS', 'Duvenaud D, 2015, ARXIV (CORNELL UNIVERSITY)', 'Jastrzȩbski S, 2016, ARXIV (CORNELL UNIVERSITY)', 'Biamonte J, 2017, NATURE', 'Smith J, 2017, CHEMICAL SCIENCE', 'Segler M, 2018, NATURE', 'Raccuglia P, 2016, NATURE', ', 2021, ENCYCLOPEDIA OF THE UN SUSTAINABLE DEVELOPMENT GOALS', 'Rudy S, 2017, SCIENCE ADVANCES', 'Wellendorff J, 2012, PHYSICAL REVIEW B', 'Carrasquilla J, 2017, NATURE PHYSICS', 'Steane A, 1998, REPORTS ON PROGRESS IN PHYSICS', 'Agrawal A, 2016, APL MATERIALS', 'Mardirossian N, 2016, THE JOURNAL OF CHEMICAL PHYSICS', 'Gómez‐Bombarelli R, 2016, NATURE MATERIALS', 'Altae-Tran H, 2017, ACS CENTRAL SCIENCE', 'Reiher M, 2017, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Behler J, 2017, ANGEWANDTE CHEMIE INTERNATIONAL EDITION', 'Faber F, 2017, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Isayev O, 2017, NATURE COMMUNICATIONS', 'Szymkuć S, 2016, ANGEWANDTE CHEMIE INTERNATIONAL EDITION', 'Segler M, 2017, CHEMISTRY - A EUROPEAN JOURNAL', 'Brockherde F, 2017, NATURE COMMUNICATIONS', 'Liu B, 2017, ACS CENTRAL SCIENCE', 'Pulido A, 2017, NATURE', 'Kim E, 2017, CHEMISTRY OF MATERIALS', 'Dunjko V, 2016, PHYSICAL REVIEW LETTERS', 'Ward L, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Oliynyk A, 2016, CHEMISTRY OF MATERIALS', 'Klucznik T, 2018, CHEM', 'Duan Y, 2017, NEURAL INFORMATION PROCESSING SYSTEMS', 'Hill J, 2016, MRS BULLETIN', 'Davies D, 2016, CHEM', 'Pensak D, 1977, ACS SYMPOSIUM SERIES', 'Legrain F, 2017, THE JOURNAL OF PHYSICAL CHEMISTRY B', 'Ziatdinov M, 2017, NPJ COMPUTATIONAL MATERIALS', 'Dragone V, 2017, NATURE COMMUNICATIONS', 'Wilkinson K, 2014, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', '50130; V, 2011, STUDIES IN COMPUTATIONAL INTELLIGENCE', 'Seko A, 2018, ', 'Arita M, 2014, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Coudert F, 2017, CHEMISTRY OF MATERIALS', 'Tetko I, 2016, MOLECULAR INFORMATICS', 'Cole J, 2016, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE CRYSTAL ENGINEERING AND MATERIALS', 'Boyd D, 2013, ACS SYMPOSIUM SERIES', 'Moot T, 2016, MATERIALS DISCOVERY', 'Pillong M, 2017, CRYSTENGCOMM', 'Trabesinger A, 2017, NATURE', 'Hui Y, 2019, ADVANCES IN INTELLIGENT SYSTEMS AND COMPUTING', 'Guimaraes G, 2017, ARXIV (CORNELL UNIVERSITY)', 'Nam J, 2016, ARXIV (CORNELL UNIVERSITY)', 'Calderón C, 2015, ARXIV (CORNELL UNIVERSITY)', 'F B, 2017, MPG.PURE (MAX PLANCK SOCIETY)', 'R.B. M, 1993, JOURNAL OF MOLECULAR STRUCTURE THEOCHEM', 'Rokach L, 2009, ']</t>
+          <t>['Kohn W, 1965, PHYSICAL REVIEW', 'Schmidhuber J, 2014, NEURAL NETWORKS', 'Jain A, 2013, APL MATERIALS', 'Shawe‐Taylor J, 2004, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Sterling T, 2015, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Harrow A, 2009, PHYSICAL REVIEW LETTERS', 'Bartók A, 2010, PHYSICAL REVIEW LETTERS', 'Lake B, 2015, SCIENCE', 'Schmidt M, 2009, SCIENCE', 'Drori I, 2022, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Saal J, 2013, JOM', 'Rupp M, 2012, PHYSICAL REVIEW LETTERS', 'Hansch C, 1964, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Curtarolo S, 2013, NATURE MATERIALS', 'Tropsha A, 2010, MOLECULAR INFORMATICS', 'Dirac P, 1929, PROCEEDINGS OF THE ROYAL SOCIETY OF LONDON SERIES A CONTAINING PAPERS OF A MATHEMATICAL AND PHYSICAL CHARACTER', 'Lejaeghere K, 2016, SCIENCE', 'Aspuru‐Guzik A, 2005, SCIENCE', 'Ghiringhelli L, 2015, PHYSICAL REVIEW LETTERS', 'Hand D, 2001, INTERNATIONAL STATISTICAL REVIEW', 'Pilania G, 2013, SCIENTIFIC REPORTS', 'Fourches D, 2010, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Billinge S, 2007, SCIENCE', 'Corey E, 1969, SCIENCE', 'Hachmann J, 2011, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Snyder J, 2012, PHYSICAL REVIEW LETTERS', 'Havu V, 2009, JOURNAL OF COMPUTATIONAL PHYSICS', 'Hautier G, 2010, CHEMISTRY OF MATERIALS', 'Schütt K, 2014, PHYSICAL REVIEW B', 'Calderón C, 2015, COMPUTATIONAL MATERIALS SCIENCE', 'Faber F, 2016, PHYSICAL REVIEW LETTERS', 'Shakhnarovich G, 2005, ', 'Kalinin S, 2015, NATURE MATERIALS', 'Handley C, 2010, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Franceschetti A, 1999, NATURE', 'Christensen R, 2015, CATALYSIS SCIENCE &amp; TECHNOLOGY', 'Fleuren W, 2015, METHODS', 'Kireeva N, 2012, MOLECULAR INFORMATICS', 'Pople J, 1999, ANGEWANDTE CHEMIE INTERNATIONAL EDITION', 'Bonchev D, 1994, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Albuquerque V, 2008, NONDESTRUCTIVE TESTING AND EVALUATION', 'Wicker J, 2014, CRYSTENGCOMM', 'Kühn C, 1996, THE JOURNAL OF PHYSICAL CHEMISTRY', 'Walsh A, 2015, NATURE CHEMISTRY', ', 2013, ', 'Oprea T, 2006, DRUG DISCOVERY TODAY TECHNOLOGIES', 'Kiselyova N, 1998, JOURNAL OF ALLOYS AND COMPOUNDS', 'Duvenaud D, 2015, ARXIV (CORNELL UNIVERSITY)', 'Jastrzȩbski S, 2016, ARXIV (CORNELL UNIVERSITY)', 'Biamonte J, 2017, NATURE', 'Smith J, 2017, CHEMICAL SCIENCE', 'Segler M, 2018, NATURE', 'Raccuglia P, 2016, NATURE', ', 2021, ENCYCLOPEDIA OF THE UN SUSTAINABLE DEVELOPMENT GOALS', 'Rudy S, 2017, SCIENCE ADVANCES', 'Wellendorff J, 2012, PHYSICAL REVIEW B', 'Carrasquilla J, 2017, NATURE PHYSICS', 'Steane A, 1998, REPORTS ON PROGRESS IN PHYSICS', 'Agrawal A, 2016, APL MATERIALS', 'Mardirossian N, 2016, THE JOURNAL OF CHEMICAL PHYSICS', 'Gómez‐Bombarelli R, 2016, NATURE MATERIALS', 'Altae-Tran H, 2017, ACS CENTRAL SCIENCE', 'Reiher M, 2017, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Behler J, 2017, ANGEWANDTE CHEMIE INTERNATIONAL EDITION', 'Faber F, 2017, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Isayev O, 2017, NATURE COMMUNICATIONS', 'Szymkuć S, 2016, ANGEWANDTE CHEMIE INTERNATIONAL EDITION', 'Segler M, 2017, CHEMISTRY - A EUROPEAN JOURNAL', 'Brockherde F, 2017, NATURE COMMUNICATIONS', 'Liu B, 2017, ACS CENTRAL SCIENCE', 'Pulido A, 2017, NATURE', 'Kim E, 2017, CHEMISTRY OF MATERIALS', 'Dunjko V, 2016, PHYSICAL REVIEW LETTERS', 'Ward L, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Oliynyk A, 2016, CHEMISTRY OF MATERIALS', 'Klucznik T, 2018, CHEM', 'Duan Y, 2017, NEURAL INFORMATION PROCESSING SYSTEMS', 'Hill J, 2016, MRS BULLETIN', 'Davies D, 2016, CHEM', 'Pensak D, 1977, ACS SYMPOSIUM SERIES', 'Legrain F, 2017, THE JOURNAL OF PHYSICAL CHEMISTRY B', 'Ziatdinov M, 2017, NPJ COMPUTATIONAL MATERIALS', 'Dragone V, 2017, NATURE COMMUNICATIONS', 'Wilkinson K, 2014, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Norbert J, 2011, STUDIES IN COMPUTATIONAL INTELLIGENCE', 'Seko A, 2018, ', 'Arita M, 2014, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Coudert F, 2017, CHEMISTRY OF MATERIALS', 'Tetko I, 2016, MOLECULAR INFORMATICS', 'Cole J, 2016, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE CRYSTAL ENGINEERING AND MATERIALS', 'Boyd D, 2013, ACS SYMPOSIUM SERIES', 'Moot T, 2016, MATERIALS DISCOVERY', 'Pillong M, 2017, CRYSTENGCOMM', 'Trabesinger A, 2017, NATURE', 'Hui Y, 2019, ADVANCES IN INTELLIGENT SYSTEMS AND COMPUTING', 'Guimaraes G, 2017, ARXIV (CORNELL UNIVERSITY)', 'Nam J, 2016, ARXIV (CORNELL UNIVERSITY)', 'Calderón C, 2015, ARXIV (CORNELL UNIVERSITY)', 'F B, 2017, MPG.PURE (MAX PLANCK SOCIETY)', 'R.B. M, 1993, JOURNAL OF MOLECULAR STRUCTURE THEOCHEM', 'Rokach L, 2009, ']</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>5549</v>
+        <v>5550</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>3957</v>
+        <v>3966</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>7990</v>
+        <v>7995</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>['Hochreiter S, 1997, NEURAL COMPUTATION', 'Long J, 2015, ', 'Cho K, 2014, ', 'Goodfellow I, 2016, MIT PRESS EBOOKS', 'Donahue J, 2015, ', 'Karpathy A, 2015, ', 'Davide B, 2013, DROPS (SCHLOSS DAGSTUHL – LEIBNIZ CENTER FOR INFORMATICS)', 'Brox T, 2004, LECTURE NOTES IN COMPUTER SCIENCE', 'Sun J, 2013, BULLETIN OF THE AMERICAN METEOROLOGICAL SOCIETY', 'Germann U, 2002, MONTHLY WEATHER REVIEW', 'Bridson R, 2011, ', 'Bridson R, 2015, ', 'Klein B, 2015, ', 'Sakaino H, 2012, IEEE TRANSACTIONS ON GEOSCIENCE AND REMOTE SENSING', 'Woo W, 2014, 27TH CONFERENCE ON SEVERE LOCAL STORMS', 'Douglas R, 1990, AMERICAN METEOROLOGICAL SOCIETY EBOOKS', 'Sutskever I, 2014, ARXIV (CORNELL UNIVERSITY)', 'Xu K, 2015, ARXIV (CORNELL UNIVERSITY)', 'Pascanu R, 2012, ARXIV (CORNELL UNIVERSITY)', 'Cho K, 2014, ARXIV (CORNELL UNIVERSITY)', 'Long J, 2014, ARXIV (CORNELL UNIVERSITY)', 'Srivastava N, 2015, ARXIV (CORNELL UNIVERSITY)', 'Donahue J, 2014, ', 'Bastien F, 2012, ARXIV (CORNELL UNIVERSITY)', 'Ranzato M, 2014, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>['Hochreiter S, 1997, NEURAL COMPUTATION', 'Long J, 2015, ', 'Cho K, 2014, ', 'Goodfellow I, 2016, MIT PRESS EBOOKS', 'Donahue J, 2015, ', 'Karpathy A, 2015, ', 'Elena L, 2013, DROPS (SCHLOSS DAGSTUHL – LEIBNIZ CENTER FOR INFORMATICS)', 'Brox T, 2004, LECTURE NOTES IN COMPUTER SCIENCE', 'Sun J, 2013, BULLETIN OF THE AMERICAN METEOROLOGICAL SOCIETY', 'Germann U, 2002, MONTHLY WEATHER REVIEW', 'Bridson R, 2011, ', 'Bridson R, 2015, ', 'Klein B, 2015, ', 'Sakaino H, 2012, IEEE TRANSACTIONS ON GEOSCIENCE AND REMOTE SENSING', 'Woo W, 2014, 27TH CONFERENCE ON SEVERE LOCAL STORMS', 'Douglas R, 1990, AMERICAN METEOROLOGICAL SOCIETY EBOOKS', 'Sutskever I, 2014, ARXIV (CORNELL UNIVERSITY)', 'Xu K, 2015, ARXIV (CORNELL UNIVERSITY)', 'Pascanu R, 2012, ARXIV (CORNELL UNIVERSITY)', 'Cho K, 2014, ARXIV (CORNELL UNIVERSITY)', 'Long J, 2014, ARXIV (CORNELL UNIVERSITY)', 'Srivastava N, 2015, ARXIV (CORNELL UNIVERSITY)', 'Donahue J, 2014, ', 'Bastien F, 2012, ARXIV (CORNELL UNIVERSITY)', 'Ranzato M, 2014, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>5624</v>
+        <v>5628</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -4434,22 +4434,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://openalex.org/W1680797894</t>
+          <t>https://openalex.org/W2945976633</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10.1007/978-0-387-30164-8</t>
+          <t>10.1038/s42256-019-0048-x</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Encyclopedia of Machine Learning</t>
+          <t>Stop explaining black box machine learning models for high stakes decisions and use interpretable models instead</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4459,52 +4459,76 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>3462</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+        <v>8965</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>NATURE MACHINE INTELLIGENCE</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Nature Machine Intelligence</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>['Claude Sammut']</t>
+          <t>['Cynthia Rudin']</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>['Sammut, Claude 1956-']</t>
+          <t>['Cynthia Rudin']</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['University Of New south Wales']</t>
+          <t>['Duke University', 'Duke University, Durham, NC, USA']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Sammut, Claude 1956- (corresponding author), University Of New south Wales</t>
+          <t>Cynthia Rudin (corresponding author), Duke University; Duke University, Durham, NC, USA</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>['Encyclopedia', 'Computer science', 'Artificial intelligence', 'Data science', 'Library science']</t>
+          <t>['Black box', 'Harm', 'Computer science', 'Key (lock)', 'Criminal justice', 'Artificial intelligence', 'Economic Justice', 'Machine learning', 'Data science', 'Criminology', 'Psychology', 'Computer security', 'Political science', 'Social psychology', 'Law']</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>['AU']</t>
+          <t>['US']</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Ryzin J, 1986, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Miller G, 1956, PSYCHOLOGICAL REVIEW', 'Miller G, 1994, PSYCHOLOGICAL REVIEW', 'Ganin Y, 2017, ADVANCES IN COMPUTER VISION AND PATTERN RECOGNITION', 'Fayyad U, 1996, ', 'Goodman B, 2017, AI MAGAZINE', 'Murdoch W, 2019, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Holte R, 1993, MACHINE LEARNING', 'Zech J, 2018, PLOS MEDICINE', 'Cowan N, 2010, CURRENT DIRECTIONS IN PSYCHOLOGICAL SCIENCE', 'Mittelstadt B, 2019, ', 'Hand D, 2006, STATISTICAL SCIENCE', 'Freitas A, 2014, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Lou Y, 2013, ', 'Lou Y, 2012, ', 'Huysmans J, 2010, DECISION SUPPORT SYSTEMS', 'Li O, 2018, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Ustun B, 2017, JAMA PSYCHIATRY', 'Brennan T, 2008, CRIMINAL JUSTICE AND BEHAVIOR', 'Flores A, 2016, FEDERAL PROBATION', 'Razavian N, 2015, BIG DATA', 'Zeng J, 2016, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES A (STATISTICS IN SOCIETY)', 'Wang F, 2015, INTERNATIONAL CONFERENCE ON ARTIFICIAL INTELLIGENCE AND STATISTICS', 'Rudin C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Goodman B, 2016, ARXIV (CORNELL UNIVERSITY)', 'Tollenaar N, 2012, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES A (STATISTICS IN SOCIETY)', 'Rudin C, 2018, INFORMS JOURNAL ON APPLIED ANALYTICS', 'Gupta M, 2016, JOURNAL OF MACHINE LEARNING RESEARCH', 'Rudin C, 2020, HARVARD DATA SCIENCE REVIEW', 'Rüping S, 2006, ', 'Rudin C, 2010, MACHINE LEARNING', 'Ustun B, 2017, ', 'Auer P, 1995, ELSEVIER EBOOKS', 'Carrizosa E, 2009, INFORMS JOURNAL ON COMPUTING', 'Wang J, 2018, ', 'Gallagher N, 2017, NEURAL INFORMATION PROCESSING SYSTEMS', 'Chang A, 2012, MACHINE LEARNING', 'Goel A, 2017, AI MAGAZINE', 'Wang F, 2018, BIOSTATISTICS', 'Mannshardt E, 2018, SIGNIFICANCE', 'Neri P, 2018, INFORMS JOURNAL ON APPLIED ANALYTICS', ', , VIEW', 'Chen C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Li O, 2017, ARXIV (CORNELL UNIVERSITY)', 'Chen C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Carrière M, 2017, ARXIV (CORNELL UNIVERSITY)', "Sokolovska N, 2018, BASE INSTITUTIONNELLE DE RECHERCHE DE L'UNIVERSITÉ PARIS-DAUPHINE (BIRD) (UNIVERSITY PARIS-DAUPHINE)", ', 2017, AUERBACH PUBLICATIONS EBOOKS']</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4520,34 +4544,34 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sammut C, 2010, </t>
+          <t>Rudin C, 2019, NATURE MACHINE INTELLIGENCE</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sammut C, 2010, </t>
+          <t>Rudin C, 2019, NATURE MACHINE INTELLIGENCE</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2945976633</t>
+          <t>https://openalex.org/W1680797894</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10.1038/s42256-019-0048-x</t>
+          <t>10.1007/978-0-387-30164-8</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Stop explaining black box machine learning models for high stakes decisions and use interpretable models instead</t>
+          <t>Encyclopedia of Machine Learning</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4557,76 +4581,52 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>book</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>8936</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>NATURE MACHINE INTELLIGENCE</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Nature Machine Intelligence</t>
-        </is>
-      </c>
+        <v>3463</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>['Cynthia Rudin']</t>
+          <t>['Claude Sammut']</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>['Cynthia Rudin']</t>
+          <t>['Nijssen, Siegfried']</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['Duke University', 'Duke University, Durham, NC, USA']</t>
+          <t>['University Of New south Wales']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Cynthia Rudin (corresponding author), Duke University; Duke University, Durham, NC, USA</t>
+          <t>Nijssen, Siegfried (corresponding author), University Of New south Wales</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>['Black box', 'Harm', 'Computer science', 'Key (lock)', 'Criminal justice', 'Artificial intelligence', 'Economic Justice', 'Machine learning', 'Data science', 'Criminology', 'Psychology', 'Computer security', 'Political science', 'Social psychology', 'Law']</t>
+          <t>['Encyclopedia', 'Computer science', 'Artificial intelligence', 'Data science', 'Library science']</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>['US']</t>
+          <t>['AU']</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>['Ryzin J, 1986, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Miller G, 1956, PSYCHOLOGICAL REVIEW', 'Miller G, 1994, PSYCHOLOGICAL REVIEW', 'Ganin Y, 2017, ADVANCES IN COMPUTER VISION AND PATTERN RECOGNITION', 'Fayyad U, 1996, ', 'Goodman B, 2017, AI MAGAZINE', 'Murdoch W, 2019, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Holte R, 1993, MACHINE LEARNING', 'Zech J, 2018, PLOS MEDICINE', 'Cowan N, 2010, CURRENT DIRECTIONS IN PSYCHOLOGICAL SCIENCE', 'Mittelstadt B, 2019, ', 'Hand D, 2006, STATISTICAL SCIENCE', 'Freitas A, 2014, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Lou Y, 2013, ', 'Lou Y, 2012, ', 'Huysmans J, 2010, DECISION SUPPORT SYSTEMS', 'Li O, 2018, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Ustun B, 2017, JAMA PSYCHIATRY', 'Brennan T, 2008, CRIMINAL JUSTICE AND BEHAVIOR', 'Flores A, 2016, FEDERAL PROBATION', 'Razavian N, 2015, BIG DATA', 'Zeng J, 2016, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES A (STATISTICS IN SOCIETY)', 'Wang F, 2015, INTERNATIONAL CONFERENCE ON ARTIFICIAL INTELLIGENCE AND STATISTICS', 'Rudin C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Goodman B, 2016, ARXIV (CORNELL UNIVERSITY)', 'Tollenaar N, 2012, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES A (STATISTICS IN SOCIETY)', 'Rudin C, 2018, INFORMS JOURNAL ON APPLIED ANALYTICS', 'Gupta M, 2016, JOURNAL OF MACHINE LEARNING RESEARCH', 'Rudin C, 2020, HARVARD DATA SCIENCE REVIEW', 'Rüping S, 2006, ', 'Rudin C, 2010, MACHINE LEARNING', 'Ustun B, 2017, ', 'Auer P, 1995, ELSEVIER EBOOKS', 'Carrizosa E, 2009, INFORMS JOURNAL ON COMPUTING', 'Wang J, 2018, ', 'Gallagher N, 2017, NEURAL INFORMATION PROCESSING SYSTEMS', 'Chang A, 2012, MACHINE LEARNING', 'Goel A, 2017, AI MAGAZINE', 'Wang F, 2018, BIOSTATISTICS', 'Mannshardt E, 2018, SIGNIFICANCE', 'Neri P, 2018, INFORMS JOURNAL ON APPLIED ANALYTICS', ', , VIEW', 'Chen C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Li O, 2017, ARXIV (CORNELL UNIVERSITY)', 'Chen C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Carrière M, 2017, ARXIV (CORNELL UNIVERSITY)', "Sokolovska N, 2018, BASE INSTITUTIONNELLE DE RECHERCHE DE L'UNIVERSITÉ PARIS-DAUPHINE (BIRD) (UNIVERSITY PARIS-DAUPHINE)", ', 2017, AUERBACH PUBLICATIONS EBOOKS']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4642,34 +4642,34 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>Rudin C, 2019, NATURE MACHINE INTELLIGENCE</t>
+          <t xml:space="preserve">Sammut C, 2010, </t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>Rudin C, 2019, NATURE MACHINE INTELLIGENCE</t>
+          <t xml:space="preserve">Sammut C, 2010, </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2177870565</t>
+          <t>https://openalex.org/W2619383789</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10.1161/circulationaha.115.001593</t>
+          <t>10.1109/tpami.2018.2798607</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Machine Learning in Medicine</t>
+          <t>Multimodal Machine Learning: A Survey and Taxonomy</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4679,80 +4679,76 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>3411</v>
+        <v>4218</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CIRCULATION</t>
+          <t>IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Circulation</t>
+          <t>IEEE Transactions on Pattern Analysis and Machine Intelligence</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>['Rahul C. Deo']</t>
+          <t>['Tadas Baltrušaitis', 'Chaitanya Ahuja', 'Louis‐Philippe Morency']</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>['Rahul C. Deo']</t>
+          <t>['Tadas Baltrusaitis', 'Chaitanya Ahuja', 'Louis-Philippe Morency']</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['From Cardiovascular Research Institute, Department of Medicine and Institute for Human Genetics, University of California, San Francisco, and California Institute for Quantitative Biosciences, San Francisco']</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Rahul C. Deo (corresponding author), From Cardiovascular Research Institute, Department of Medicine and Institute for Human Genetics, University of California, San Francisco, and California Institute for Quantitative Biosciences, San Francisco</t>
-        </is>
-      </c>
+          <t>['Microsoft Corporation, Cambridge, United Kingdom', 'Language Technologies Institute, Carnegie Mellon University, Pittsburgh, PA', 'Language Technologies Institute, Carnegie Mellon University, Pittsburgh, PA']</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Spurred by advances in processing power, memory, storage, and an unprecedented wealth of data, computers are being asked to tackle increasingly complex learning tasks, often with astonishing success. Computers have now mastered a popular variant of poker, learned the laws of physics from experimental data, and become experts in video games - tasks that would have been deemed impossible not too long ago. In parallel, the number of companies centered on applying complex data analysis to varying industries has exploded, and it is thus unsurprising that some analytic companies are turning attention to problems in health care. The purpose of this review is to explore what problems in medicine might benefit from such learning approaches and use examples from the literature to introduce basic concepts in machine learning. It is important to note that seemingly large enough medical data sets and adequate learning algorithms have been available for many decades, and yet, although there are thousands of papers applying machine learning algorithms to medical data, very few have contributed meaningfully to clinical care. This lack of impact stands in stark contrast to the enormous relevance of machine learning to many other industries. Thus, part of my effort will be to identify what obstacles there may be to changing the practice of medicine through statistical learning approaches, and discuss how these might be overcome.</t>
+          <t>Our experience of the world is multimodal - we see objects, hear sounds, feel texture, smell odors, and taste flavors. Modality refers to the way in which something happens or is experienced and a research problem is characterized as multimodal when it includes multiple such modalities. In order for Artificial Intelligence to make progress in understanding the world around us, it needs to be able to interpret such multimodal signals together. Multimodal machine learning aims to build models that can process and relate information from multiple modalities. It is a vibrant multi-disciplinary field of increasing importance and with extraordinary potential. Instead of focusing on specific multimodal applications, this paper surveys the recent advances in multimodal machine learning itself and presents them in a common taxonomy. We go beyond the typical early and late fusion categorization and identify broader challenges that are faced by multimodal machine learning, namely: representation, translation, alignment, fusion, and co-learning. This new taxonomy will enable researchers to better understand the state of the field and identify directions for future research.</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>41</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>423</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>443</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>['Medicine', 'Medical physics', 'Medical education', 'Intensive care medicine']</t>
+          <t>['Multimodal learning', 'Computer science', 'Artificial intelligence', 'Modalities', 'Taxonomy (biology)', 'Categorization', 'Multimodality', 'Field (mathematics)', 'Machine learning', 'Human–computer interaction', 'World Wide Web']</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>['US']</t>
+          <t>['GB', 'US']</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>['Breiman L, 2001, MACHINE LEARNING', 'Tibshirani R, 1996, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Friedman J, 2001, THE ANNALS OF STATISTICS', 'Hastie T, 2001, SPRINGER SERIES IN STATISTICS', 'Hastie T, 2009, SPRINGER SERIES IN STATISTICS', 'Breiman L, 1996, MACHINE LEARNING', 'Burges C, 1998, DATA MINING AND KNOWLEDGE DISCOVERY', 'Breiman L, 1996, MACHINE LEARNING', 'Cover T, 1967, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Lee D, 1999, NATURE', 'GuyonIsabelle, 2003, JOURNAL OF MACHINE LEARNING RESEARCH', 'Bengio Y, 2009, FOUNDATIONS AND TRENDS® IN MACHINE LEARNING', 'Lip G, 2009, CHEST JOURNAL', 'Vapnik V, 1999, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Bengio Y, 2009, NOW PUBLISHERS, INC. EBOOKS', 'Olshausen B, 1997, VISION RESEARCH', 'Pitt B, 2014, NEW ENGLAND JOURNAL OF MEDICINE', 'Ishwaran H, 2008, THE ANNALS OF APPLIED STATISTICS', 'Lee H, 2007, THE MIT PRESS EBOOKS', 'D’Agostino R, 2001, JAMA', 'Woodruff P, 2009, AMERICAN JOURNAL OF RESPIRATORY AND CRITICAL CARE MEDICINE', 'Le Q, 2013, ', 'Corren J, 2011, NEW ENGLAND JOURNAL OF MEDICINE', 'Ishwaran H, 2008, ', 'O’Mahony C, 2013, EUROPEAN HEART JOURNAL', 'James M, 2012, PHYSIOLOGICAL REVIEWS', 'Shah S, 2014, CIRCULATION', 'Beck A, 2011, SCIENCE TRANSLATIONAL MEDICINE', 'Koren Y, 2009, ', 'Peña‐Castillo L, 2008, GENOME BIOLOGY', 'Abu‐Mostafa Y, 2012, ', 'Hsich E, 2010, CIRCULATION CARDIOVASCULAR QUALITY AND OUTCOMES', 'Cheng W, 2013, SCIENCE TRANSLATIONAL MEDICINE', 'Margolin A, 2013, SCIENCE TRANSLATIONAL MEDICINE', 'Udelson J, 2011, CIRCULATION', 'Kannel W, 1975, CIRCULATION', 'Cheng W, 2013, PLOS COMPUTATIONAL BIOLOGY', 'Gorodeski E, 2011, CIRCULATION CARDIOVASCULAR QUALITY AND OUTCOMES', 'Deo R, 2014, GENOME BIOLOGY', 'Yogatama D, 2014, ARXIV (CORNELL UNIVERSITY)', 'Ausiello D, 2014, EUROPE PMC (PUBMED CENTRAL)']</t>
+          <t>['Glorot X, 2010, ', 'Zhu Y, 2015, ', 'Salakhutdinov R, 2009, ', 'Plummer B, 2015, ', 'Kalchbrenner N, 2013, ', 'Hodosh M, 2013, JOURNAL OF ARTIFICIAL INTELLIGENCE RESEARCH', 'Andrew G, 2013, ', 'Ghahramani Z, 1997, MACHINE LEARNING', 'Yao L, 2015, ', 'Sutton C, 2007, THE MIT PRESS EBOOKS', 'Weston J, 2011, ', 'Pan Y, 2016, ', 'Wang W, 2015, ', 'Kumar S, 2012, ', 'Mitchell M, 2012, CONFERENCE OF THE EUROPEAN CHAPTER OF THE ASSOCIATION FOR COMPUTATIONAL LINGUISTICS', 'Louwerse M, 2010, TOPICS IN COGNITIVE SCIENCE', 'Kahou S, 2015, JOURNAL ON MULTIMODAL USER INTERFACES', 'Martin A, 2014, IT UNIVERSITY OF COPENHAGEN (IT UNIVERSITY OF COPENHAGEN)', 'Li S, 2011, ', 'Kojima A, 2002, INTERNATIONAL JOURNAL OF COMPUTER VISION', 'Yang Y, 2011, ', 'Xu R, 2015, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Castellano G, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Mroueh Y, 2015, ', 'Glodek M, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Cour T, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Gupta A, 2021, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Morvant E, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Bojanowski P, 2015, ', 'Feng Y, 2010, EDINBURGH RESEARCH EXPLORER (UNIVERSITY OF EDINBURGH)', 'Wei Y, 2016, ACM TRANSACTIONS ON INTELLIGENT SYSTEMS AND TECHNOLOGY', 'Chen Y, 2004, ', 'Sjölander K, 2003, ', 'Wu Z, 2005, LECTURE NOTES IN COMPUTER SCIENCE', 'Naim I, 2014, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Khapra M, 2010, ', 'Deena S, 2009, LECTURE NOTES IN COMPUTER SCIENCE', 'Kingma D, 2014, UVA-DARE (UNIVERSITY OF AMSTERDAM)', 'Simonyan K, 2014, ARXIV (CORNELL UNIVERSITY)', 'Ioffe S, 2015, ARXIV (CORNELL UNIVERSITY)', 'Xu K, 2015, ARXIV (CORNELL UNIVERSITY)', 'Chorowski J, 2015, ARXIV (CORNELL UNIVERSITY)', 'Chen X, 2015, ARXIV (CORNELL UNIVERSITY)', 'Kiros R, 2014, ARXIV (CORNELL UNIVERSITY)', 'Mao J, 2014, ARXIV (CORNELL UNIVERSITY)', 'Gao H, 2015, ARXIV (CORNELL UNIVERSITY)', 'Torabi A, 2015, ARXIV (CORNELL UNIVERSITY)', 'McFee B, 2010, ARXIV (CORNELL UNIVERSITY)', 'Christoudias C, 2012, ARXIV (CORNELL UNIVERSITY)', 'Lebret R, 2015, ARXIV (CORNELL UNIVERSITY)', 'Vinyals O, 2015, ', 'McGurk H, 1976, NATURE', 'Blum A, 1998, ', 'Hotelling H, 1936, BIOMETRIKA', 'Karpathy A, 2015, ', 'Vedantam R, 2015, ', 'Antol S, 2015, ', 'Brown P, 1993, ', 'Farhadi A, 2010, LECTURE NOTES IN COMPUTER SCIENCE', 'Atrey P, 2010, MULTIMEDIA SYSTEMS', 'Kulkarni G, 2013, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Vogel S, 1996, ', 'Juang B, 1991, TECHNOMETRICS', 'D’Mello S, 2015, ACM COMPUTING SURVEYS', 'Feng F, 2014, ', 'Valstar M, 2013, ', 'Bronstein M, 2010, ', 'Kim Y, 2013, ', 'Lienhart R, 1998, PROCEEDINGS OF SPIE, THE INTERNATIONAL SOCIETY FOR OPTICAL ENGINEERING/PROCEEDINGS OF SPIE', 'Kruskal J, 1983, SIAM REVIEW', 'Yao B, 2010, PROCEEDINGS OF THE IEEE', 'Wöllmer M, 2012, IMAGE AND VISION COMPUTING', 'Ouyang W, 2014, ', 'Evangelopoulos G, 2013, IEEE TRANSACTIONS ON MULTIMEDIA', 'Socher R, 2010, ', 'Li Y, 2014, NEUROCOMPUTING', 'Zitnick C, 2013, ', 'Kong C, 2014, ', 'Huang J, 2013, ', 'Sargin M, 2007, IEEE TRANSACTIONS ON MULTIMEDIA', 'Zhou F, 2012, ', 'Mei H, 2016, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Liu F, 2013, IEEE JOURNAL OF BIOMEDICAL AND HEALTH INFORMATICS', 'Rohrbach A, 2015, LECTURE NOTES IN COMPUTER SCIENCE', 'Chen S, 2015, ', 'Sarah T, 2012, ', 'Baltrušaitis T, 2013, ', 'Chen J, 2014, ', 'Zen H, 2012, IEEE TRANSACTIONS ON AUDIO SPEECH AND LANGUAGE PROCESSING', 'Tapaswi M, 2015, ', 'Arora R, 2013, ', 'Feng F, 2014, NEUROCOMPUTING', 'Bourlard H, 2002, ', 'Yeh Y, 2012, IEEE TRANSACTIONS ON MULTIMEDIA', 'Noulas A, 2011, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Jiang X, 2014, PATTERN RECOGNITION LETTERS', 'Haubold A, 2007, ', 'Tapaswi M, 2014, INTERNATIONAL JOURNAL OF MULTIMEDIA INFORMATION RETRIEVAL', 'Wu D, 2014, ', 'Klein B, 2014, ARXIV (CORNELL UNIVERSITY)', 'Hochreiter S, 1997, NEURAL COMPUTATION', 'Srivastava N, 2014, ', '淳司 柴, 2017, JOURNAL OF JAPAN SOCIETY FOR FUZZY THEORY AND INTELLIGENT INFORMATICS', 'Papineni K, 2001, ', 'Hinton G, 2006, NEURAL COMPUTATION', 'Hardoon D, 2004, NEURAL COMPUTATION', 'Denkowski M, 2014, ', 'Frome A, 2013, ', 'Farhadi A, 2009, 2009 IEEE CONFERENCE ON COMPUTER VISION AND PATTERN RECOGNITION', 'Gönen M, 2011, ', 'Rasiwasia N, 2010, ', 'Zen H, 2009, SPEECH COMMUNICATION', 'Suk H, 2014, NEUROIMAGE', 'Ordóñez V, 2011, ', 'James A, 2014, INFORMATION FUSION', 'Bruni E, 2014, JOURNAL OF ARTIFICIAL INTELLIGENCE RESEARCH', 'Carletta J, 2006, LECTURE NOTES IN COMPUTER SCIENCE', 'Gehler P, 2009, ', 'Pomianos G, 2003, PROCEEDINGS OF THE IEEE', 'Bigham J, 2010, ', 'Lai P, 2000, INTERNATIONAL JOURNAL OF NEURAL SYSTEMS', 'Quattoni A, 2007, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Regneri M, 2013, TRANSACTIONS OF THE ASSOCIATION FOR COMPUTATIONAL LINGUISTICS', 'Snoek C, 2004, MULTIMEDIA TOOLS AND APPLICATIONS', 'Anagnostopoulos C, 2012, ARTIFICIAL INTELLIGENCE REVIEW', 'Weston J, 2010, MACHINE LEARNING', 'Coyne B, 2001, ', 'Bucak S, 2014, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'McKeown G, 2010, ', 'Schuller B, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Devlin J, 2015, ', 'Bojanowski P, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Wu Z, 2014, ', 'Elliott D, 2014, ', 'Mason R, 2014, ', 'Ramírez G, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Anderson R, 2013, ', 'Song Y, 2012, ', 'Slaney M, 2000, NEURAL INFORMATION PROCESSING SYSTEMS', 'Lan Z, 2013, MULTIMEDIA TOOLS AND APPLICATIONS', 'Chang A, 2015, ', 'Gurban M, 2008, ', 'Krogel M, 2004, MACHINE LEARNING', 'Garg A, 2003, PROCEEDINGS OF THE IEEE', 'Christoudias C, 2006, ', 'Cosi P, 2002, ', 'Bahdanau D, 2014, ARXIV (CORNELL UNIVERSITY)', 'Sutskever I, 2014, ARXIV (CORNELL UNIVERSITY)', 'Socher R, 2013, ARXIV (CORNELL UNIVERSITY)', 'Karpathy A, 2014, ARXIV (CORNELL UNIVERSITY)', 'Krizhevsky A, 2017, COMMUNICATIONS OF THE ACM', 'Lowe D, 2004, INTERNATIONAL JOURNAL OF COMPUTER VISION', 'Lafferty J, 2001, SCHOLARLY COMMONS (UNIVERSITY OF PENNSYLVANIA)', 'Bengio Y, 2013, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Hinton G, 2012, IEEE SIGNAL PROCESSING MAGAZINE', 'Graves A, 2013, ', 'Zeng Z, 2008, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Young P, 2014, TRANSACTIONS OF THE ASSOCIATION FOR COMPUTATIONAL LINGUISTICS', 'Ngiam J, 2011, ', 'Hinton G, 2012, ', 'Lin C, 2003, ', 'Hunt A, 2002, ', 'Brand M, 2002, ', 'Socher R, 2014, TRANSACTIONS OF THE ASSOCIATION FOR COMPUTATIONAL LINGUISTICS', 'Palatucci M, 2018, FIGSHARE', 'Soleymani M, 2011, IEEE TRANSACTIONS ON AFFECTIVE COMPUTING', 'Bregler C, 1997, ', 'Zhang D, 2014, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Malinowski M, 2015, ', 'Guadarrama S, 2013, ', 'Nicolaou M, 2011, IEEE TRANSACTIONS ON AFFECTIVE COMPUTING', 'Jia X, 2015, ', 'Harvey D, 2009, ', 'Bruni E, 2012, INSTITUTIONAL RESEARCH INFORMATION SYSTEM (UNIVERSITÀ DEGLI STUDI DI TRENTO)', 'Кузнецова П, 2012, ', 'Hendricks L, 2016, ', 'Elliott D, 2013, ', 'Kiela D, 2014, ', 'Левин, 2003, ', 'Silberer C, 2014, ', 'Nefian A, 2002, IEEE INTERNATIONAL CONFERENCE ON ACOUSTICS SPEECH AND SIGNAL PROCESSING', 'Yuhas B, 1989, IEEE COMMUNICATIONS MAGAZINE', 'Wöllmer M, 2010, ', 'Zhou F, 2009, ', 'Thomason J, 2014, ', 'Sikka K, 2013, ', 'Qin T, 2008, ', 'Yu H, 2013, ', 'Wang D, 2015, INTERNATIONAL CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Sarkar A, 2001, ', 'Song Y, 2012, ', 'Nakov P, 2012, JOURNAL OF ARTIFICIAL INTELLIGENCE RESEARCH', 'Yagcioglu S, 2015, ', 'Shariat S, 2011, ', 'Masuko T, 2002, ', 'Reiter S, 2007, ', 'Mikolov T, 2013, ARXIV (CORNELL UNIVERSITY)', 'Simonyan K, 2014, ARXIV (CORNELL UNIVERSITY)', 'Ratnaparkhi A, 2000, ARXIV.ORG', 'Feichtenhofer C, 2016, ', 'Chan W, 2016, ', 'Fukui A, 2016, ', 'Mao J, 2016, ', 'Yu L, 2016, LECTURE NOTES IN COMPUTER SCIENCE', 'Jiang Q, 2017, ', 'Trigeorgis G, 2016, ', 'Wang L, 2016, ', 'Yu H, 2016, ', 'Poria S, 2015, ', 'Müller M, 2008, ', 'Fan Y, 2014, ', 'Bernardi R, 2016, JOURNAL OF ARTIFICIAL INTELLIGENCE RESEARCH', 'Rohrbach A, 2017, INTERNATIONAL JOURNAL OF COMPUTER VISION', ', 2009, ENCYCLOPEDIA OF BIOMETRICS', 'Cao Y, 2016, ', 'Nojavanasghari B, 2016, ', 'Shutova E, 2016, ', 'Srivastava N, 2012, ', 'Mahasseni B, 2016, ', 'Rajagopalan S, 2016, LECTURE NOTES IN COMPUTER SCIENCE', 'Gebru I, 2017, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Baroni M, 2015, LANGUAGE AND LINGUISTICS COMPASS', 'Lazaridou A, 2014, ', 'Kiela D, 2015, ', 'Silberer C, 2012, EDINBURGH RESEARCH EXPLORER (UNIVERSITY OF EDINBURGH)', 'Gao H, 2015, ARXIV (CORNELL UNIVERSITY)', 'Kiela D, 2015, ', 'Trigeorgis G, 2016, ', 'Jin Q, 2016, ', 'Song Y, 2016, INTERNATIONAL JOINT CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Naim I, 2015, ', 'Anguera X, 2014, ', 'Moon S, 2014, ', 'Oord A, 2016, ARXIV (CORNELL UNIVERSITY)', 'Reed S, 2016, ARXIV (CORNELL UNIVERSITY)', 'Oord A, 2016, ARXIV (CORNELL UNIVERSITY)', 'Xiong C, 2016, ARXIV (CORNELL UNIVERSITY)', 'Oord A, 2016, ARXIV (CORNELL UNIVERSITY)', 'Collobert R, 2016, ARXIV (CORNELL UNIVERSITY)', 'Lu J, 2016, ARXIV (CORNELL UNIVERSITY)', 'Jayanta M, 2021, DROPS (SCHLOSS DAGSTUHL – LEIBNIZ CENTER FOR INFORMATICS)', 'Labaca-Castro R, 2023, ', 'Barsalou L, 2007, ANNUAL REVIEW OF PSYCHOLOGY', 'Yang Z, 2016, ', ', 2007, ', 'Xu H, 2016, LECTURE NOTES IN COMPUTER SCIENCE', 'Juang B, 1991, TECHNOMETRICS', 'Hu R, 2016, ', 'Xiong C, 2016, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Huang T, 2016, ', 'Zeng K, 2017, ', 'Torre F, 2011, ', 'Nefian, 2002, IEEE INTERNATIONAL CONFERENCE ON ACOUSTICS SPEECH AND SIGNAL PROCESSING', 'McFeeBrian, 2011, JOURNAL OF MACHINE LEARNING RESEARCH', 'Bourlard H, 1996, 4TH INTERNATIONAL CONFERENCE ON SPOKEN LANGUAGE PROCESSING (ICSLP 1996)', 'Zhang H, 2016, ', 'Ghahramani Z, 1996, ', 'Mei H, 2015, ARXIV (CORNELL UNIVERSITY)', 'Klein B, 2014, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4768,34 +4764,34 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>Deo R, 2015, CIRCULATION</t>
+          <t>Baltrušaitis T, 2018, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>Deo R, 2015, CIRCULATION</t>
+          <t>Baltrušaitis T, 2018, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2619383789</t>
+          <t>https://openalex.org/W2177870565</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10.1109/tpami.2018.2798607</t>
+          <t>10.1161/circulationaha.115.001593</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Multimodal Machine Learning: A Survey and Taxonomy</t>
+          <t>Machine Learning in Medicine</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4805,76 +4801,80 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>4212</v>
+        <v>3415</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE</t>
+          <t>CIRCULATION</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>IEEE Transactions on Pattern Analysis and Machine Intelligence</t>
+          <t>Circulation</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>['Tadas Baltrušaitis', 'Chaitanya Ahuja', 'Louis‐Philippe Morency']</t>
+          <t>['Rahul C. Deo']</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>['Tadas Baltrusaitis', 'Chaitanya Ahuja', 'Louis-Philippe Morency']</t>
+          <t>['Rahul C. Deo']</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>['Microsoft Corporation, Cambridge, United Kingdom', 'Language Technologies Institute, Carnegie Mellon University, Pittsburgh, PA', 'Language Technologies Institute, Carnegie Mellon University, Pittsburgh, PA']</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
+          <t>['From Cardiovascular Research Institute, Department of Medicine and Institute for Human Genetics, University of California, San Francisco, and California Institute for Quantitative Biosciences, San Francisco']</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Rahul C. Deo (corresponding author), From Cardiovascular Research Institute, Department of Medicine and Institute for Human Genetics, University of California, San Francisco, and California Institute for Quantitative Biosciences, San Francisco</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Our experience of the world is multimodal - we see objects, hear sounds, feel texture, smell odors, and taste flavors. Modality refers to the way in which something happens or is experienced and a research problem is characterized as multimodal when it includes multiple such modalities. In order for Artificial Intelligence to make progress in understanding the world around us, it needs to be able to interpret such multimodal signals together. Multimodal machine learning aims to build models that can process and relate information from multiple modalities. It is a vibrant multi-disciplinary field of increasing importance and with extraordinary potential. Instead of focusing on specific multimodal applications, this paper surveys the recent advances in multimodal machine learning itself and presents them in a common taxonomy. We go beyond the typical early and late fusion categorization and identify broader challenges that are faced by multimodal machine learning, namely: representation, translation, alignment, fusion, and co-learning. This new taxonomy will enable researchers to better understand the state of the field and identify directions for future research.</t>
+          <t>Spurred by advances in processing power, memory, storage, and an unprecedented wealth of data, computers are being asked to tackle increasingly complex learning tasks, often with astonishing success. Computers have now mastered a popular variant of poker, learned the laws of physics from experimental data, and become experts in video games - tasks that would have been deemed impossible not too long ago. In parallel, the number of companies centered on applying complex data analysis to varying industries has exploded, and it is thus unsurprising that some analytic companies are turning attention to problems in health care. The purpose of this review is to explore what problems in medicine might benefit from such learning approaches and use examples from the literature to introduce basic concepts in machine learning. It is important to note that seemingly large enough medical data sets and adequate learning algorithms have been available for many decades, and yet, although there are thousands of papers applying machine learning algorithms to medical data, very few have contributed meaningfully to clinical care. This lack of impact stands in stark contrast to the enormous relevance of machine learning to many other industries. Thus, part of my effort will be to identify what obstacles there may be to changing the practice of medicine through statistical learning approaches, and discuss how these might be overcome.</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>132</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>['Multimodal learning', 'Computer science', 'Artificial intelligence', 'Modalities', 'Taxonomy (biology)', 'Categorization', 'Multimodality', 'Field (mathematics)', 'Machine learning', 'Human–computer interaction', 'World Wide Web']</t>
+          <t>['Medicine', 'Medical physics', 'Medical education', 'Intensive care medicine']</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>['GB', 'US']</t>
+          <t>['US']</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>['Glorot X, 2010, ', 'Zhu Y, 2015, ', 'Salakhutdinov R, 2009, ', 'Plummer B, 2015, ', 'Kalchbrenner N, 2013, ', 'Hodosh M, 2013, JOURNAL OF ARTIFICIAL INTELLIGENCE RESEARCH', 'Andrew G, 2013, ', 'Ghahramani Z, 1997, MACHINE LEARNING', 'Yao L, 2015, ', 'Sutton C, 2007, THE MIT PRESS EBOOKS', 'Weston J, 2011, ', 'Pan Y, 2016, ', 'Wang W, 2015, ', 'Kumar S, 2012, ', 'Mitchell M, 2012, CONFERENCE OF THE EUROPEAN CHAPTER OF THE ASSOCIATION FOR COMPUTATIONAL LINGUISTICS', 'Louwerse M, 2010, TOPICS IN COGNITIVE SCIENCE', 'Kahou S, 2015, JOURNAL ON MULTIMODAL USER INTERFACES', 'Jingdong W, 2014, IT UNIVERSITY OF COPENHAGEN (IT UNIVERSITY OF COPENHAGEN)', 'Li S, 2011, ', 'Kojima A, 2002, INTERNATIONAL JOURNAL OF COMPUTER VISION', 'Yang Y, 2011, ', 'Xu R, 2015, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Castellano G, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Mroueh Y, 2015, ', 'Glodek M, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Cour T, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Gupta A, 2021, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Morvant E, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Bojanowski P, 2015, ', 'Feng Y, 2010, EDINBURGH RESEARCH EXPLORER (UNIVERSITY OF EDINBURGH)', 'Wei Y, 2016, ACM TRANSACTIONS ON INTELLIGENT SYSTEMS AND TECHNOLOGY', 'Chen Y, 2004, ', 'Sjölander K, 2003, ', 'Wu Z, 2005, LECTURE NOTES IN COMPUTER SCIENCE', 'Naim I, 2014, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Khapra M, 2010, ', 'Deena S, 2009, LECTURE NOTES IN COMPUTER SCIENCE', 'Kingma D, 2014, UVA-DARE (UNIVERSITY OF AMSTERDAM)', 'Simonyan K, 2014, ARXIV (CORNELL UNIVERSITY)', 'Ioffe S, 2015, ARXIV (CORNELL UNIVERSITY)', 'Xu K, 2015, ARXIV (CORNELL UNIVERSITY)', 'Chorowski J, 2015, ARXIV (CORNELL UNIVERSITY)', 'Chen X, 2015, ARXIV (CORNELL UNIVERSITY)', 'Kiros R, 2014, ARXIV (CORNELL UNIVERSITY)', 'Mao J, 2014, ARXIV (CORNELL UNIVERSITY)', 'Gao H, 2015, ARXIV (CORNELL UNIVERSITY)', 'Torabi A, 2015, ARXIV (CORNELL UNIVERSITY)', 'McFee B, 2010, ARXIV (CORNELL UNIVERSITY)', 'Christoudias C, 2012, ARXIV (CORNELL UNIVERSITY)', 'Lebret R, 2015, ARXIV (CORNELL UNIVERSITY)', 'Vinyals O, 2015, ', 'McGurk H, 1976, NATURE', 'Blum A, 1998, ', 'Hotelling H, 1936, BIOMETRIKA', 'Karpathy A, 2015, ', 'Vedantam R, 2015, ', 'Antol S, 2015, ', 'Brown P, 1993, ', 'Farhadi A, 2010, LECTURE NOTES IN COMPUTER SCIENCE', 'Atrey P, 2010, MULTIMEDIA SYSTEMS', 'Kulkarni G, 2013, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Vogel S, 1996, ', 'Juang B, 1991, TECHNOMETRICS', 'D’Mello S, 2015, ACM COMPUTING SURVEYS', 'Feng F, 2014, ', 'Valstar M, 2013, ', 'Bronstein M, 2010, ', 'Kim Y, 2013, ', 'Lienhart R, 1998, PROCEEDINGS OF SPIE, THE INTERNATIONAL SOCIETY FOR OPTICAL ENGINEERING/PROCEEDINGS OF SPIE', 'Kruskal J, 1983, SIAM REVIEW', 'Yao B, 2010, PROCEEDINGS OF THE IEEE', 'Wöllmer M, 2012, IMAGE AND VISION COMPUTING', 'Ouyang W, 2014, ', 'Evangelopoulos G, 2013, IEEE TRANSACTIONS ON MULTIMEDIA', 'Socher R, 2010, ', 'Li Y, 2014, NEUROCOMPUTING', 'Zitnick C, 2013, ', 'Kong C, 2014, ', 'Huang J, 2013, ', 'Sargin M, 2007, IEEE TRANSACTIONS ON MULTIMEDIA', 'Zhou F, 2012, ', 'Mei H, 2016, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Liu F, 2013, IEEE JOURNAL OF BIOMEDICAL AND HEALTH INFORMATICS', 'Rohrbach A, 2015, LECTURE NOTES IN COMPUTER SCIENCE', 'Chen S, 2015, ', 'Sarah T, 2012, ', 'Baltrušaitis T, 2013, ', 'Chen J, 2014, ', 'Zen H, 2012, IEEE TRANSACTIONS ON AUDIO SPEECH AND LANGUAGE PROCESSING', 'Tapaswi M, 2015, ', 'Arora R, 2013, ', 'Feng F, 2014, NEUROCOMPUTING', 'Bourlard H, 2002, ', 'Yeh Y, 2012, IEEE TRANSACTIONS ON MULTIMEDIA', 'Noulas A, 2011, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Jiang X, 2014, PATTERN RECOGNITION LETTERS', 'Haubold A, 2007, ', 'Tapaswi M, 2014, INTERNATIONAL JOURNAL OF MULTIMEDIA INFORMATION RETRIEVAL', 'Wu D, 2014, ', 'Klein B, 2014, ARXIV (CORNELL UNIVERSITY)', 'Hochreiter S, 1997, NEURAL COMPUTATION', 'Srivastava N, 2014, ', '淳司 柴, 2017, JOURNAL OF JAPAN SOCIETY FOR FUZZY THEORY AND INTELLIGENT INFORMATICS', 'Papineni K, 2001, ', 'Hinton G, 2006, NEURAL COMPUTATION', 'Hardoon D, 2004, NEURAL COMPUTATION', 'Denkowski M, 2014, ', 'Frome A, 2013, ', 'Farhadi A, 2009, 2009 IEEE CONFERENCE ON COMPUTER VISION AND PATTERN RECOGNITION', 'Gönen M, 2011, ', 'Rasiwasia N, 2010, ', 'Zen H, 2009, SPEECH COMMUNICATION', 'Suk H, 2014, NEUROIMAGE', 'Ordóñez V, 2011, ', 'James A, 2014, INFORMATION FUSION', 'Bruni E, 2014, JOURNAL OF ARTIFICIAL INTELLIGENCE RESEARCH', 'Carletta J, 2006, LECTURE NOTES IN COMPUTER SCIENCE', 'Gehler P, 2009, ', 'Pomianos G, 2003, PROCEEDINGS OF THE IEEE', 'Bigham J, 2010, ', 'Lai P, 2000, INTERNATIONAL JOURNAL OF NEURAL SYSTEMS', 'Quattoni A, 2007, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Regneri M, 2013, TRANSACTIONS OF THE ASSOCIATION FOR COMPUTATIONAL LINGUISTICS', 'Snoek C, 2004, MULTIMEDIA TOOLS AND APPLICATIONS', 'Anagnostopoulos C, 2012, ARTIFICIAL INTELLIGENCE REVIEW', 'Weston J, 2010, MACHINE LEARNING', 'Coyne B, 2001, ', 'Bucak S, 2014, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'McKeown G, 2010, ', 'Schuller B, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Devlin J, 2015, ', 'Bojanowski P, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Wu Z, 2014, ', 'Elliott D, 2014, ', 'Mason R, 2014, ', 'Ramírez G, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Anderson R, 2013, ', 'Song Y, 2012, ', 'Slaney M, 2000, NEURAL INFORMATION PROCESSING SYSTEMS', 'Lan Z, 2013, MULTIMEDIA TOOLS AND APPLICATIONS', 'Chang A, 2015, ', 'Gurban M, 2008, ', 'Krogel M, 2004, MACHINE LEARNING', 'Garg A, 2003, PROCEEDINGS OF THE IEEE', 'Christoudias C, 2006, ', 'Cosi P, 2002, ', 'Bahdanau D, 2014, ARXIV (CORNELL UNIVERSITY)', 'Sutskever I, 2014, ARXIV (CORNELL UNIVERSITY)', 'Socher R, 2013, ARXIV (CORNELL UNIVERSITY)', 'Karpathy A, 2014, ARXIV (CORNELL UNIVERSITY)', 'Krizhevsky A, 2017, COMMUNICATIONS OF THE ACM', 'Lowe D, 2004, INTERNATIONAL JOURNAL OF COMPUTER VISION', 'Lafferty J, 2001, SCHOLARLY COMMONS (UNIVERSITY OF PENNSYLVANIA)', 'Bengio Y, 2013, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Hinton G, 2012, IEEE SIGNAL PROCESSING MAGAZINE', 'Graves A, 2013, ', 'Zeng Z, 2008, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Young P, 2014, TRANSACTIONS OF THE ASSOCIATION FOR COMPUTATIONAL LINGUISTICS', 'Ngiam J, 2011, ', 'Hinton G, 2012, ', 'Lin C, 2003, ', 'Hunt A, 2002, ', 'Brand M, 2002, ', 'Socher R, 2014, TRANSACTIONS OF THE ASSOCIATION FOR COMPUTATIONAL LINGUISTICS', 'Palatucci M, 2018, FIGSHARE', 'Soleymani M, 2011, IEEE TRANSACTIONS ON AFFECTIVE COMPUTING', 'Bregler C, 1997, ', 'Zhang D, 2014, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Malinowski M, 2015, ', 'Guadarrama S, 2013, ', 'Nicolaou M, 2011, IEEE TRANSACTIONS ON AFFECTIVE COMPUTING', 'Jia X, 2015, ', 'Harvey D, 2009, ', 'Bruni E, 2012, INSTITUTIONAL RESEARCH INFORMATION SYSTEM (UNIVERSITÀ DEGLI STUDI DI TRENTO)', 'Кузнецова П, 2012, ', 'Hendricks L, 2016, ', 'Elliott D, 2013, ', 'Kiela D, 2014, ', 'Левин, 2003, ', 'Silberer C, 2014, ', 'Nefian A, 2002, IEEE INTERNATIONAL CONFERENCE ON ACOUSTICS SPEECH AND SIGNAL PROCESSING', 'Yuhas B, 1989, IEEE COMMUNICATIONS MAGAZINE', 'Wöllmer M, 2010, ', 'Zhou F, 2009, ', 'Thomason J, 2014, ', 'Sikka K, 2013, ', 'Qin T, 2008, ', 'Yu H, 2013, ', 'Wang D, 2015, INTERNATIONAL CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Sarkar A, 2001, ', 'Song Y, 2012, ', 'Nakov P, 2012, JOURNAL OF ARTIFICIAL INTELLIGENCE RESEARCH', 'Yagcioglu S, 2015, ', 'Shariat S, 2011, ', 'Masuko T, 2002, ', 'Reiter S, 2007, ', 'Mikolov T, 2013, ARXIV (CORNELL UNIVERSITY)', 'Simonyan K, 2014, ARXIV (CORNELL UNIVERSITY)', 'Ratnaparkhi A, 2000, ARXIV.ORG', 'Feichtenhofer C, 2016, ', 'Chan W, 2016, ', 'Fukui A, 2016, ', 'Mao J, 2016, ', 'Yu L, 2016, LECTURE NOTES IN COMPUTER SCIENCE', 'Jiang Q, 2017, ', 'Trigeorgis G, 2016, ', 'Wang L, 2016, ', 'Yu H, 2016, ', 'Poria S, 2015, ', 'Müller M, 2008, ', 'Fan Y, 2014, ', 'Bernardi R, 2016, JOURNAL OF ARTIFICIAL INTELLIGENCE RESEARCH', 'Rohrbach A, 2017, INTERNATIONAL JOURNAL OF COMPUTER VISION', ', 2009, ENCYCLOPEDIA OF BIOMETRICS', 'Cao Y, 2016, ', 'Nojavanasghari B, 2016, ', 'Shutova E, 2016, ', 'Srivastava N, 2012, ', 'Mahasseni B, 2016, ', 'Rajagopalan S, 2016, LECTURE NOTES IN COMPUTER SCIENCE', 'Gebru I, 2017, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Baroni M, 2015, LANGUAGE AND LINGUISTICS COMPASS', 'Lazaridou A, 2014, ', 'Kiela D, 2015, ', 'Silberer C, 2012, EDINBURGH RESEARCH EXPLORER (UNIVERSITY OF EDINBURGH)', 'Gao H, 2015, ARXIV (CORNELL UNIVERSITY)', 'Kiela D, 2015, ', 'Trigeorgis G, 2016, ', 'Jin Q, 2016, ', 'Song Y, 2016, INTERNATIONAL JOINT CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Naim I, 2015, ', 'Anguera X, 2014, ', 'Moon S, 2014, ', 'Oord A, 2016, ARXIV (CORNELL UNIVERSITY)', 'Reed S, 2016, ARXIV (CORNELL UNIVERSITY)', 'Oord A, 2016, ARXIV (CORNELL UNIVERSITY)', 'Xiong C, 2016, ARXIV (CORNELL UNIVERSITY)', 'Oord A, 2016, ARXIV (CORNELL UNIVERSITY)', 'Collobert R, 2016, ARXIV (CORNELL UNIVERSITY)', 'Lu J, 2016, ARXIV (CORNELL UNIVERSITY)', 'Jayanta M, 2021, DROPS (SCHLOSS DAGSTUHL – LEIBNIZ CENTER FOR INFORMATICS)', 'Labaca-Castro R, 2023, ', 'Barsalou L, 2007, ANNUAL REVIEW OF PSYCHOLOGY', 'Yang Z, 2016, ', ', 2007, ', 'Xu H, 2016, LECTURE NOTES IN COMPUTER SCIENCE', 'Juang B, 1991, TECHNOMETRICS', 'Hu R, 2016, ', 'Xiong C, 2016, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Huang T, 2016, ', 'Zeng K, 2017, ', 'Torre F, 2011, ', 'Nefian, 2002, IEEE INTERNATIONAL CONFERENCE ON ACOUSTICS SPEECH AND SIGNAL PROCESSING', 'McFeeBrian, 2011, JOURNAL OF MACHINE LEARNING RESEARCH', 'Bourlard H, 1996, 4TH INTERNATIONAL CONFERENCE ON SPOKEN LANGUAGE PROCESSING (ICSLP 1996)', 'Zhang H, 2016, ', 'Ghahramani Z, 1996, ', 'Mei H, 2015, ARXIV (CORNELL UNIVERSITY)', 'Klein B, 2014, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>['Breiman L, 2001, MACHINE LEARNING', 'Tibshirani R, 1996, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Friedman J, 2001, THE ANNALS OF STATISTICS', 'Hastie T, 2001, SPRINGER SERIES IN STATISTICS', 'Hastie T, 2009, SPRINGER SERIES IN STATISTICS', 'Breiman L, 1996, MACHINE LEARNING', 'Burges C, 1998, DATA MINING AND KNOWLEDGE DISCOVERY', 'Breiman L, 1996, MACHINE LEARNING', 'Cover T, 1967, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Lee D, 1999, NATURE', 'GuyonIsabelle, 2003, JOURNAL OF MACHINE LEARNING RESEARCH', 'Bengio Y, 2009, FOUNDATIONS AND TRENDS® IN MACHINE LEARNING', 'Lip G, 2009, CHEST JOURNAL', 'Vapnik V, 1999, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Bengio Y, 2009, NOW PUBLISHERS, INC. EBOOKS', 'Olshausen B, 1997, VISION RESEARCH', 'Pitt B, 2014, NEW ENGLAND JOURNAL OF MEDICINE', 'Ishwaran H, 2008, THE ANNALS OF APPLIED STATISTICS', 'Lee H, 2007, THE MIT PRESS EBOOKS', 'D’Agostino R, 2001, JAMA', 'Woodruff P, 2009, AMERICAN JOURNAL OF RESPIRATORY AND CRITICAL CARE MEDICINE', 'Le Q, 2013, ', 'Corren J, 2011, NEW ENGLAND JOURNAL OF MEDICINE', 'Ishwaran H, 2008, ', 'O’Mahony C, 2013, EUROPEAN HEART JOURNAL', 'James M, 2012, PHYSIOLOGICAL REVIEWS', 'Shah S, 2014, CIRCULATION', 'Beck A, 2011, SCIENCE TRANSLATIONAL MEDICINE', 'Koren Y, 2009, ', 'Peña‐Castillo L, 2008, GENOME BIOLOGY', 'Abu‐Mostafa Y, 2012, ', 'Hsich E, 2010, CIRCULATION CARDIOVASCULAR QUALITY AND OUTCOMES', 'Cheng W, 2013, SCIENCE TRANSLATIONAL MEDICINE', 'Margolin A, 2013, SCIENCE TRANSLATIONAL MEDICINE', 'Udelson J, 2011, CIRCULATION', 'Kannel W, 1975, CIRCULATION', 'Cheng W, 2013, PLOS COMPUTATIONAL BIOLOGY', 'Gorodeski E, 2011, CIRCULATION CARDIOVASCULAR QUALITY AND OUTCOMES', 'Deo R, 2014, GENOME BIOLOGY', 'Yogatama D, 2014, ARXIV (CORNELL UNIVERSITY)', 'Ausiello D, 2014, PUBMED']</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>Baltrušaitis T, 2018, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE</t>
+          <t>Deo R, 2015, CIRCULATION</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>Baltrušaitis T, 2018, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE</t>
+          <t>Deo R, 2015, CIRCULATION</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>5111</v>
+        <v>5114</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>['LeCun Y, 1998, PROCEEDINGS OF THE IEEE', 'Szegedy C, 2015, ', 'Witten I, 2011, ELSEVIER EBOOKS', 'Gordon A, 1984, BIOMETRICS', 'Cios K, 1997, NEUROCOMPUTING', 'Ester M, 1996, ', 'He K, 2015, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Agrawal R, 1998, ', 'Hotelling H, 1933, JOURNAL OF EDUCATIONAL PSYCHOLOGY', 'Kaelbling L, 1996, JOURNAL OF ARTIFICIAL INTELLIGENCE RESEARCH', 'Hazeghi K, 1995, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Kohonen T, 1990, PROCEEDINGS OF THE IEEE', 'Freund Y, 1996, ', 'Han J, 2000, ACM SIGMOD RECORD', 'Zanella A, 2014, IEEE INTERNET OF THINGS JOURNAL', 'Dey A, 2001, PERSONAL AND UBIQUITOUS COMPUTING', 'Tavallaee M, 2009, ', 'Hinton G, 2012, LECTURE NOTES IN COMPUTER SCIENCE', 'Agrawal R, 1998, ', 'Park H, 2008, EXPERT SYSTEMS WITH APPLICATIONS', 'Xu D, 2015, ANNALS OF DATA SCIENCE', 'Zaki M, 2000, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Cessie S, 1992, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES C (APPLIED STATISTICS)', 'Amit Y, 1997, NEURAL COMPUTATION', 'Wang W, 1997, ', ', 1993, CHOICE REVIEWS ONLINE', 'Sneath P, 1957, MICROBIOLOGY', 'MTW, 1999, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Witten I, 1999, RESEARCH COMMONS (THE UNIVERSITY OF WAIKATO)', 'Bishop C, 2007, ', 'Houtsma M, 2002, ', 'Agrawal R, 1998, KNOWLEDGE DISCOVERY AND DATA MINING', 'Rokach L, 2009, ', 'Zheng Y, 2015, ', 'Scheffer T, 2001, LECTURE NOTES IN COMPUTER SCIENCE', 'Zhu H, 2014, ACM TRANSACTIONS ON INTELLIGENT SYSTEMS AND TECHNOLOGY', 'Zhao Q, 2003, PALLIATIVE &amp; SUPPORTIVE CARE', 'Flach P, 2001, MACHINE LEARNING', 'Cobuloglu H, 2015, EXPERT SYSTEMS WITH APPLICATIONS', 'McCallum A, 2005, QUEUE', 'Das A, 2001, ', 'Phithakkitnukoon S, 2011, ACM TRANSACTIONS ON AUTONOMOUS AND ADAPTIVE SYSTEMS', 'Zhu H, 2012, ', 'Zulkernain S, 2010, E-PUBLICATIONS@MARQUETTE (MARQUETTE UNIVERSITY)', 'Amorim R, 2012, ', 'Sheng S, 2005, LECTURE NOTES IN COMPUTER SCIENCE', 'Bell A, 2005, QUEUE', 'Zulkernain S, 2010, LECTURE NOTES OF THE INSTITUTE FOR COMPUTER SCIENCES, SOCIAL INFORMATICS AND TELECOMMUNICATIONS ENGINEERING', 'Pedregosa F, 2012, ARXIV (CORNELL UNIVERSITY)', 'John G, 2013, ARXIV (CORNELL UNIVERSITY)', 'He K, 2016, ', 'Breiman L, 2001, MACHINE LEARNING', 'Krizhevsky A, 2017, COMMUNICATIONS OF THE ACM', 'Han J, 2012, CHOICE REVIEWS ONLINE', 'MacQueen J, 1967, DEFENSE TECHNICAL INFORMATION CENTER (DTIC)', 'Chollet F, 2017, ', 'Silver D, 2016, NATURE', 'Quinlan J, 1986, MACHINE LEARNING', 'Agrawal R, 1993, ', 'Pearson K, 1901, THE LONDON EDINBURGH AND DUBLIN PHILOSOPHICAL MAGAZINE AND JOURNAL OF SCIENCE', 'Goodfellow I, 2016, MIT PRESS EBOOKS', 'Weiss K, 2016, JOURNAL OF BIG DATA', 'Wu X, 2007, KNOWLEDGE AND INFORMATION SYSTEMS', 'Aha D, 1991, MACHINE LEARNING', 'Ankerst M, 1999, ACM SIGMOD RECORD', 'Moustafa N, 2015, ', 'Fukunaga K, 1975, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Eagle N, 2005, PERSONAL AND UBIQUITOUS COMPUTING', 'Carpenter G, 1987, COMPUTER VISION GRAPHICS AND IMAGE PROCESSING', 'Wagstaff K, 2001, ', 'Keerthi S, 2001, NEURAL COMPUTATION', 'Holte R, 1993, MACHINE LEARNING', 'Kamble S, 2018, PROCESS SAFETY AND ENVIRONMENTAL PROTECTION', 'Ravi K, 2015, KNOWLEDGE-BASED SYSTEMS', 'Xin Y, 2018, IEEE ACCESS', 'Rasmussen C, 1999, ', 'Mahdavinejad M, 2017, DIGITAL COMMUNICATIONS AND NETWORKS', 'Fatima M, 2017, JOURNAL OF INTELLIGENT LEARNING SYSTEMS AND APPLICATIONS', 'Ibáñez J, 2018, SENSORS', 'Liu H, 1998, ', 'Polydoros A, 2017, JOURNAL OF INTELLIGENT &amp; ROBOTIC SYSTEMS', 'Ślusarczyk B, 2018, POLISH JOURNAL OF MANAGEMENT STUDIES', 'Ismail A, 2019, JOURNAL OF BIG DATA', 'López G, 2017, ADVANCES IN INTELLIGENT SYSTEMS AND COMPUTING', 'Lade P, 2017, IEEE INTELLIGENT SYSTEMS', 'Mohammed M, 2016, ', 'Balducci F, 2018, MACHINES', 'Nilashi M, 2017, COMPUTERS &amp; CHEMICAL ENGINEERING', 'Safdar S, 2017, ARTIFICIAL INTELLIGENCE REVIEW', 'Srinivasan V, 2014, ', 'Mehrotra A, 2016, ', 'Sarker I, 2017, THE COMPUTER JOURNAL', 'Perveen S, 2018, IEEE ACCESS', 'Adnan N, 2017, WORLD JOURNAL OF SCIENCE TECHNOLOGY AND SUSTAINABLE DEVELOPMENT', 'Cai J, 2003, ', 'Essien A, 2019, ', 'Wu C, 2016, APPLIED INTELLIGENCE', 'Sarker I, 2016, ', 'Cao L, 2020, ARXIV (CORNELL UNIVERSITY)', 'Ryzin J, 1986, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Breiman L, 1996, MACHINE LEARNING', 'Breiman L, 1996, MACHINE LEARNING', 'Quinlan J, 1986, MACHINE LEARNING', ', 1991, CHOICE REVIEWS ONLINE', 'Agrawal R, 1993, ACM SIGMOD RECORD', 'Saeid M, 2017, VIEW', 'Kamble S, 2019, INTERNATIONAL JOURNAL OF PRODUCTION ECONOMICS', 'Lalmuanawma S, 2020, CHAOS SOLITONS &amp; FRACTALS', 'Sharma R, 2020, COMPUTERS &amp; OPERATIONS RESEARCH', 'Sarker I, 2020, JOURNAL OF BIG DATA', 'Agrawal R, 1998, ACM SIGMOD RECORD', 'Harmon S, 2020, NATURE COMMUNICATIONS', 'Jamshidi M, 2020, IEEE ACCESS', 'Sarker I, 2021, SN COMPUTER SCIENCE', 'Fujiyoshi H, 2019, IATSS RESEARCH', 'Kalan A, 2020, NATURE COMMUNICATIONS', 'Zheng T, 2016, INTERNATIONAL JOURNAL OF MEDICAL INFORMATICS', 'Ardabili S, 2020, ALGORITHMS', 'Alakuş T, 2020, CHAOS SOLITONS &amp; FRACTALS', 'Mohamadou Y, 2020, APPLIED INTELLIGENCE', 'Shorten C, 2021, JOURNAL OF BIG DATA', 'Sarker I, 2020, SYMMETRY', 'Boukerche A, 2020, COMPUTER NETWORKS', 'Sarker I, 2019, JOURNAL OF BIG DATA', 'Sarker I, 2021, SN COMPUTER SCIENCE', 'Tao J, 2020, JOURNAL OF BIG DATA', 'Sarker I, 2020, MOBILE NETWORKS AND APPLICATIONS', 'Essien A, 2020, WORLD WIDE WEB', 'Kushwaha S, 2020, JOURNAL OF INDUSTRIAL INTEGRATION AND MANAGEMENT', 'Wei P, 2019, IEEE ACCESS', 'Sarker I, 2019, MOBILE NETWORKS AND APPLICATIONS', 'Sarker I, 2019, INTERNET OF THINGS', 'Sarker I, 2019, JOURNAL OF BIG DATA', 'Tsagkias M, 2020, ACM SIGIR FORUM', 'Marchand A, 2020, JOURNAL OF RETAILING', 'Sarker I, 2020, JOURNAL OF NETWORK AND COMPUTER APPLICATIONS', 'Sarker I, 2020, SYMMETRY', 'Scheffer T, 2005, INTELLIGENT DATA ANALYSIS', 'Sarker I, 2019, INTERNET OF THINGS', 'Sarker I, 2020, JOURNAL OF BIG DATA', 'Khadse V, 2018, ', 'Zi-kang H, 2020, ', 'Sarker I, 2021, PREPRINTS.ORG', 'Sarker I, 2021, PREPRINTS.ORG', 'Sarle W, 1991, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Aha D, 1991, MACHINE LEARNING', 'Baxter L, 1995, TECHNOMETRICS', 'Mohammed M, 2016, ']</t>
+          <t>['LeCun Y, 1998, PROCEEDINGS OF THE IEEE', 'Szegedy C, 2015, ', 'Witten I, 2011, ELSEVIER EBOOKS', 'Gordon A, 1984, BIOMETRICS', 'Cios K, 1997, NEUROCOMPUTING', 'Ester M, 1996, ', 'He K, 2015, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Agrawal R, 1998, ', 'Hotelling H, 1933, JOURNAL OF EDUCATIONAL PSYCHOLOGY', 'Kaelbling L, 1996, JOURNAL OF ARTIFICIAL INTELLIGENCE RESEARCH', 'Hazeghi K, 1995, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Kohonen T, 1990, PROCEEDINGS OF THE IEEE', 'Freund Y, 1996, ', 'Han J, 2000, ACM SIGMOD RECORD', 'Zanella A, 2014, IEEE INTERNET OF THINGS JOURNAL', 'Dey A, 2001, PERSONAL AND UBIQUITOUS COMPUTING', 'Tavallaee M, 2009, ', 'Hinton G, 2012, LECTURE NOTES IN COMPUTER SCIENCE', 'Agrawal R, 1998, ', 'Park H, 2008, EXPERT SYSTEMS WITH APPLICATIONS', 'Xu D, 2015, ANNALS OF DATA SCIENCE', 'Zaki M, 2000, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Cessie S, 1992, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES C (APPLIED STATISTICS)', 'Amit Y, 1997, NEURAL COMPUTATION', 'Wang W, 1997, ', ', 1993, CHOICE REVIEWS ONLINE', 'Sneath P, 1957, MICROBIOLOGY', 'MTW, 1999, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Witten I, 1999, RESEARCH COMMONS (THE UNIVERSITY OF WAIKATO)', 'Bishop C, 2007, ', 'Houtsma M, 2002, ', 'Agrawal R, 1998, KNOWLEDGE DISCOVERY AND DATA MINING', 'Rokach L, 2009, ', 'Zheng Y, 2015, ', 'Scheffer T, 2001, LECTURE NOTES IN COMPUTER SCIENCE', 'Zhu H, 2014, ACM TRANSACTIONS ON INTELLIGENT SYSTEMS AND TECHNOLOGY', 'Zhao Q, 2003, PALLIATIVE &amp; SUPPORTIVE CARE', 'Flach P, 2001, MACHINE LEARNING', 'Cobuloglu H, 2015, EXPERT SYSTEMS WITH APPLICATIONS', 'McCallum A, 2005, QUEUE', 'Das A, 2001, ', 'Phithakkitnukoon S, 2011, ACM TRANSACTIONS ON AUTONOMOUS AND ADAPTIVE SYSTEMS', 'Zhu H, 2012, ', 'Zulkernain S, 2010, E-PUBLICATIONS@MARQUETTE (MARQUETTE UNIVERSITY)', 'Amorim R, 2012, ', 'Sheng S, 2005, LECTURE NOTES IN COMPUTER SCIENCE', 'Bell A, 2005, QUEUE', 'Zulkernain S, 2010, LECTURE NOTES OF THE INSTITUTE FOR COMPUTER SCIENCES, SOCIAL INFORMATICS AND TELECOMMUNICATIONS ENGINEERING', 'Pedregosa F, 2012, ARXIV (CORNELL UNIVERSITY)', 'John G, 2013, ARXIV (CORNELL UNIVERSITY)', 'He K, 2016, ', 'Breiman L, 2001, MACHINE LEARNING', 'Krizhevsky A, 2017, COMMUNICATIONS OF THE ACM', 'Han J, 2012, CHOICE REVIEWS ONLINE', 'MacQueen J, 1967, DEFENSE TECHNICAL INFORMATION CENTER (DTIC)', 'Chollet F, 2017, ', 'Silver D, 2016, NATURE', 'Quinlan J, 1986, MACHINE LEARNING', 'Agrawal R, 1993, ', 'Pearson K, 1901, THE LONDON EDINBURGH AND DUBLIN PHILOSOPHICAL MAGAZINE AND JOURNAL OF SCIENCE', 'Goodfellow I, 2016, MIT PRESS EBOOKS', 'Weiss K, 2016, JOURNAL OF BIG DATA', 'Wu X, 2007, KNOWLEDGE AND INFORMATION SYSTEMS', 'Aha D, 1991, MACHINE LEARNING', 'Ankerst M, 1999, ACM SIGMOD RECORD', 'Moustafa N, 2015, ', 'Fukunaga K, 1975, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Eagle N, 2005, PERSONAL AND UBIQUITOUS COMPUTING', 'Carpenter G, 1987, COMPUTER VISION GRAPHICS AND IMAGE PROCESSING', 'Wagstaff K, 2001, ', 'Keerthi S, 2001, NEURAL COMPUTATION', 'Holte R, 1993, MACHINE LEARNING', 'Kamble S, 2018, PROCESS SAFETY AND ENVIRONMENTAL PROTECTION', 'Ravi K, 2015, KNOWLEDGE-BASED SYSTEMS', 'Xin Y, 2018, IEEE ACCESS', 'Rasmussen C, 1999, ', 'Mahdavinejad M, 2017, DIGITAL COMMUNICATIONS AND NETWORKS', 'Fatima M, 2017, JOURNAL OF INTELLIGENT LEARNING SYSTEMS AND APPLICATIONS', 'Ibáñez J, 2018, SENSORS', 'Liu H, 1998, ', 'Polydoros A, 2017, JOURNAL OF INTELLIGENT &amp; ROBOTIC SYSTEMS', 'Ślusarczyk B, 2018, POLISH JOURNAL OF MANAGEMENT STUDIES', 'Ismail A, 2019, JOURNAL OF BIG DATA', 'López G, 2017, ADVANCES IN INTELLIGENT SYSTEMS AND COMPUTING', 'Lade P, 2017, IEEE INTELLIGENT SYSTEMS', 'Mohammed M, 2016, ', 'Balducci F, 2018, MACHINES', 'Nilashi M, 2017, COMPUTERS &amp; CHEMICAL ENGINEERING', 'Safdar S, 2017, ARTIFICIAL INTELLIGENCE REVIEW', 'Srinivasan V, 2014, ', 'Mehrotra A, 2016, ', 'Sarker I, 2017, THE COMPUTER JOURNAL', 'Perveen S, 2018, IEEE ACCESS', 'Adnan N, 2017, WORLD JOURNAL OF SCIENCE TECHNOLOGY AND SUSTAINABLE DEVELOPMENT', 'Cai J, 2003, ', 'Essien A, 2019, ', 'Wu C, 2016, APPLIED INTELLIGENCE', 'Sarker I, 2016, ', 'Cao L, 2020, ARXIV (CORNELL UNIVERSITY)', 'Ryzin J, 1986, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Breiman L, 1996, MACHINE LEARNING', 'Breiman L, 1996, MACHINE LEARNING', 'Quinlan J, 1986, MACHINE LEARNING', ', 1991, CHOICE REVIEWS ONLINE', 'Agrawal R, 1993, ACM SIGMOD RECORD', 'Saeid M, 2017, VIEW', 'Kamble S, 2019, INTERNATIONAL JOURNAL OF PRODUCTION ECONOMICS', 'Oh Y, 2020, PUBMED', 'Lalmuanawma S, 2020, CHAOS SOLITONS &amp; FRACTALS', 'Sharma R, 2020, COMPUTERS &amp; OPERATIONS RESEARCH', 'Sarker I, 2020, JOURNAL OF BIG DATA', 'Agrawal R, 1998, ACM SIGMOD RECORD', 'Harmon S, 2020, NATURE COMMUNICATIONS', 'Jamshidi M, 2020, IEEE ACCESS', 'Sarker I, 2021, SN COMPUTER SCIENCE', 'Fujiyoshi H, 2019, IATSS RESEARCH', 'Kalan A, 2020, NATURE COMMUNICATIONS', 'Zheng T, 2016, INTERNATIONAL JOURNAL OF MEDICAL INFORMATICS', 'Ardabili S, 2020, ALGORITHMS', 'Alakuş T, 2020, CHAOS SOLITONS &amp; FRACTALS', 'Mohamadou Y, 2020, APPLIED INTELLIGENCE', 'Shorten C, 2021, JOURNAL OF BIG DATA', 'Sarker I, 2020, SYMMETRY', 'Boukerche A, 2020, COMPUTER NETWORKS', 'Sarker I, 2019, JOURNAL OF BIG DATA', 'Sarker I, 2021, SN COMPUTER SCIENCE', 'Tao J, 2020, JOURNAL OF BIG DATA', 'Sarker I, 2020, MOBILE NETWORKS AND APPLICATIONS', 'Essien A, 2020, WORLD WIDE WEB', 'Kushwaha S, 2020, JOURNAL OF INDUSTRIAL INTEGRATION AND MANAGEMENT', 'Wei P, 2019, IEEE ACCESS', 'Sarker I, 2019, MOBILE NETWORKS AND APPLICATIONS', 'Sarker I, 2019, INTERNET OF THINGS', 'Sarker I, 2019, JOURNAL OF BIG DATA', 'Tsagkias M, 2020, ACM SIGIR FORUM', 'Marchand A, 2020, JOURNAL OF RETAILING', 'Sarker I, 2020, JOURNAL OF NETWORK AND COMPUTER APPLICATIONS', 'Sarker I, 2020, SYMMETRY', 'Scheffer T, 2005, INTELLIGENT DATA ANALYSIS', 'Sarker I, 2019, INTERNET OF THINGS', 'Sarker I, 2020, JOURNAL OF BIG DATA', 'Khadse V, 2018, ', 'Zi-kang H, 2020, ', 'Sarker I, 2021, PREPRINTS.ORG', 'Sarker I, 2021, PREPRINTS.ORG', 'Sarle W, 1991, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Aha D, 1991, MACHINE LEARNING', 'Baxter L, 1995, TECHNOMETRICS', 'Mohammed M, 2016, ']</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>6087</v>
+        <v>6089</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2920</v>
+        <v>2923</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>4348</v>
+        <v>4352</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -5570,22 +5570,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2535690855</t>
+          <t>https://openalex.org/W2885770726</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10.1109/sp.2017.41</t>
+          <t>10.3390/s18082674</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Membership Inference Attacks Against Machine Learning Models</t>
+          <t>Machine Learning in Agriculture: A Review</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5595,60 +5595,80 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>4215</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+        <v>3036</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>SENSORS</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>['Reza Shokri', 'Marco Stronati', 'Congzheng Song', 'Vitaly Shmatikov']</t>
+          <t>['Κωνσταντίνος Λιάκος', 'Patrizia Busato', 'Dimitrios Moshou', 'Simon Pearson', 'Dionysis Bochtis']</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>['Reza Shokri', 'Marco Stronati', 'Congzheng Song', 'Vitaly Shmatikov']</t>
+          <t>['Konstantinos Liakos', 'Patrizia Busato', 'Dimitrios Moshou', 'Simon Pearson', 'Dionysis Bochtis']</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>['Cornell Tech', 'INRIA', 'Cornell', 'Cornell Tech']</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
+          <t>['Institute for Bio-Economy and Agri-Technology (IBO), Centre of Research and Technology—Hellas (CERTH), 6th km Charilaou-Thermi Rd, GR 57001 Thessaloniki, Greece', 'Department of Agriculture, Forestry and Food Sciences (DISAFA), Faculty of Agriculture, University of Turin, Largo Braccini 2, 10095 Grugliasco, Italy', 'Agricultural Engineering Laboratory, Faculty of Agriculture, Aristotle University of Thessaloniki, 54124 Thessaloniki, Greece', 'Institute for Bio-Economy and Agri-Technology (IBO), Centre of Research and Technology—Hellas (CERTH), 6th km Charilaou-Thermi Rd, GR 57001 Thessaloniki, Greece', 'Lincoln Institute for Agri-food Technology (LIAT), University of Lincoln, Brayford Way, Brayford Pool, Lincoln LN6 7TS, UK', 'Institute for Bio-Economy and Agri-Technology (IBO), Centre of Research and Technology—Hellas (CERTH), 6th km Charilaou-Thermi Rd, GR 57001 Thessaloniki, Greece']</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Dionysis Bochtis (corresponding author), Institute for Bio-Economy and Agri-Technology (IBO), Centre of Research and Technology—Hellas (CERTH), 6th km Charilaou-Thermi Rd, GR 57001 Thessaloniki, Greece</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>We quantitatively investigate how machine learning models leak information about the individual data records on which they were trained. We focus on the basic membership inference attack: given a data record and black-box access to a model, determine if the record was in the model's training dataset. To perform membership inference against a target model, we make adversarial use of machine learning and train our own inference model to recognize differences in the target model's predictions on the inputs that it trained on versus the inputs that it did not train on. We empirically evaluate our inference techniques on classification models trained by commercial "machine learning as a service" providers such as Google and Amazon. Using realistic datasets and classification tasks, including a hospital discharge dataset whose membership is sensitive from the privacy perspective, we show that these models can be vulnerable to membership inference attacks. We then investigate the factors that influence this leakage and evaluate mitigation strategies.</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+          <t>Machine learning has emerged with big data technologies and high-performance computing to create new opportunities for data intensive science in the multi-disciplinary agri-technologies domain. In this paper, we present a comprehensive review of research dedicated to applications of machine learning in agricultural production systems. The works analyzed were categorized in (a) crop management, including applications on yield prediction, disease detection, weed detection crop quality, and species recognition; (b) livestock management, including applications on animal welfare and livestock production; (c) water management; and (d) soil management. The filtering and classification of the presented articles demonstrate how agriculture will benefit from machine learning technologies. By applying machine learning to sensor data, farm management systems are evolving into real time artificial intelligence enabled programs that provide rich recommendations and insights for farmer decision support and action.</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>['Inference', 'Machine learning', 'Computer science', 'Artificial intelligence', 'Perspective (graphical)', 'Focus (optics)', 'Data modeling', 'Data mining', 'Adversarial system', 'Database']</t>
+          <t>['Agriculture', 'Artificial intelligence', 'Precision agriculture', 'Computer science', 'Machine learning', 'Big data', 'Livestock', 'Decision support system', 'Data science', 'Data mining']</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>['US', 'FR']</t>
+          <t>['GR', 'IT', 'GB']</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>['Srivastava N, 2014, ', 'Hastie T, 2013, ', 'Dwork C, 2006, LECTURE NOTES IN COMPUTER SCIENCE', 'Abadi M, 2016, ', 'Fredrikson M, 2015, ', 'Shokri R, 2015, ', 'Franklin J, 2005, THE MATHEMATICAL INTELLIGENCER', 'Homer N, 2008, PLOS GENETICS', 'Lindell Y, 2000, LECTURE NOTES IN COMPUTER SCIENCE', 'Chaudhuri K, 2011, PUBMED', 'Bassily R, 2014, ', 'Fredrikson M, 2014, PUBMED', 'Chaudhuri K, 2008, ', 'Jagannathan G, 2005, ', 'Hardt M, 2016, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Du W, 2004, ', 'Zhang J, 2012, PROCEEDINGS OF THE VLDB ENDOWMENT', 'Dwork C, 2011, ', 'Yang D, 2016, ACM TRANSACTIONS ON INTELLIGENT SYSTEMS AND TECHNOLOGY', 'Calandrino J, 2011, ', 'Bos J, 2014, JOURNAL OF BIOMEDICAL INFORMATICS', 'Rubinstein B, 2012, JOURNAL OF PRIVACY AND CONFIDENTIALITY', 'Sankararaman S, 2009, NATURE GENETICS', 'Vaidya J, 2007, THE VLDB JOURNAL', 'Barni M, 2011, IEEE TRANSACTIONS ON INFORMATION FORENSICS AND SECURITY', 'Duchi J, 2014, JOURNAL OF THE ACM', 'Schneider I, 2005, THE MATHEMATICAL INTELLIGENCER', 'Dwork C, 2015, ', 'Backes M, 2016, ', 'Zhu J, 2001, ', 'Dwork C, 2010, JOURNAL OF PRIVACY AND CONFIDENTIALITY', 'Diakonikolas I, 2015, EDINBURGH RESEARCH EXPLORER (UNIVERSITY OF EDINBURGH)', 'Krizhevsky A, 2024, ', 'Hinton G, 2015, ARXIV (CORNELL UNIVERSITY)', 'Tramèr F, 2016, ARXIV (CORNELL UNIVERSITY)', 'Chaudhuri K, 2009, ARXIV (CORNELL UNIVERSITY)', ', 2016, IRIS RESEARCH PRODUCT CATALOG (SAPIENZA UNIVERSITY OF ROME)', 'Hardt M, 2015, ARXIV (CORNELL UNIVERSITY)', 'Xie P, 2014, ARXIV (CORNELL UNIVERSITY)', 'Duchi J, 2012, ARXIV (CORNELL UNIVERSITY)', 'Jain P, 2015, ARXIV (CORNELL UNIVERSITY)', 'Kusner M, 2015, POLYPUBLIE (ÉCOLE POLYTECHNIQUE DE MONTRÉAL)']</t>
+          <t>['Dempster A, 1977, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Chang C, 2011, ACM TRANSACTIONS ON INTELLIGENT SYSTEMS AND TECHNOLOGY', 'Cortes C, 1995, MACHINE LEARNING', 'Hopfield J, 1982, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'McCulloch W, 1943, BULLETIN OF MATHEMATICAL BIOLOGY', 'Jang J, 1993, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS', 'Lloyd S, 1982, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Fisher R, 1936, ANNALS OF EUGENICS', 'Huang G, 2006, NEUROCOMPUTING', 'Rosenblatt F, 1958, PSYCHOLOGICAL REVIEW', 'Cleveland W, 1979, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Suykens J, 1999, NEURAL PROCESSING LETTERS', 'Kohonen T, 1990, PROCEEDINGS OF THE IEEE', 'Friedman J, 1991, THE ANNALS OF STATISTICS', 'Johnson S, 1967, PSYCHOMETRIKA', 'Specht D, 1991, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Riedmiller M, 2002, IEEE INTERNATIONAL CONFERENCE ON NEURAL NETWORKS', 'Suykens J, 2002, WORLD SCIENTIFIC EBOOKS', 'Broomhead D, 1988, COMPLEX SYSTEMS', 'Kong L, 2007, NUCLEIC ACIDS RESEARCH', 'Kass G, 1980, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES C (APPLIED STATISTICS)', 'Fix E, 1989, INTERNATIONAL STATISTICAL REVIEW', 'Salakhutdinov R, 2009, ', 'Atkeson C, 1997, ARTIFICIAL INTELLIGENCE REVIEW', 'Samuel A, 2000, IBM JOURNAL OF RESEARCH AND DEVELOPMENT', 'Pal S, 1992, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Moshou D, 2004, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Linnainmaa S, 1976, BIT NUMERICAL MATHEMATICS', 'Cao J, 2012, NEURAL PROCESSING LETTERS', 'Galvão R, 2008, CHEMOMETRICS AND INTELLIGENT LABORATORY SYSTEMS', 'Mackowiak S, 2015, GENOME BIOLOGY', 'Moshou D, 2005, REAL-TIME IMAGING', 'Asadi H, 2014, PLOS ONE', 'Melssen W, 2006, CHEMOMETRICS AND INTELLIGENT LABORATORY SYSTEMS', 'Dutta R, 2014, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Sengupta S, 2013, BIOSYSTEMS ENGINEERING', 'Amatya S, 2015, BIOSYSTEMS ENGINEERING', 'Mohammadi K, 2015, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Thomas P, 2002, BRITISH JOURNAL OF EDUCATIONAL TECHNOLOGY', 'Coopersmith E, 2014, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Moshou D, 2006, PRECISION AGRICULTURE', 'Craninx M, 2007, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Moshou D, 2013, BIOSYSTEMS ENGINEERING', 'Alonso J, 2013, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Hossain M, 2011, JOURNAL OF HAND SURGERY (EUROPEAN VOLUME)', 'Alonso J, 2014, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Gastaldo P, 2014, ROBOTICS AND AUTONOMOUS SYSTEMS', 'Tryon R, 1957, PSYCHOMETRIKA', 'Neapolitan R, 1987, APPLIED ARTIFICIAL INTELLIGENCE', 'Smith D, 1978, SOCIETY', 'Breiman L, 2001, MACHINE LEARNING', 'LeCun Y, 2015, NATURE', 'Pearson K, 1901, THE LONDON EDINBURGH AND DUBLIN PHILOSOPHICAL MAGAZINE AND JOURNAL OF SCIENCE', 'Ferentinos K, 2018, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Cox D, 1958, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Barboza F, 2017, EXPERT SYSTEMS WITH APPLICATIONS', 'Grinblat G, 2016, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Pantazi X, 2015, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Ebrahimi M, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Morellos A, 2016, BIOSYSTEMS ENGINEERING', 'Zhao Y, 2017, ENERGY ECONOMICS', 'Hansen M, 2018, COMPUTERS IN INDUSTRY', 'Fang K, 2017, GEOPHYSICAL RESEARCH LETTERS', 'Feng Y, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Zhang B, 2017, CANCER LETTERS', 'Rhee J, 2017, AGRICULTURAL AND FOREST METEOROLOGY', 'Mehdizadeh S, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Kang J, 2015, INTERNATIONAL JOURNAL OF RADIATION ONCOLOGY*BIOLOGY*PHYSICS', 'Cramer S, 2017, EXPERT SYSTEMS WITH APPLICATIONS', 'Chung C, 2016, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Matthews S, 2017, SCIENTIFIC REPORTS', 'Zhou C, 2018, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Pantazi X, 2016, BIOSYSTEMS ENGINEERING', 'Ramos P, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Ali I, 2016, IEEE JOURNAL OF SELECTED TOPICS IN APPLIED EARTH OBSERVATIONS AND REMOTE SENSING', 'Bohanec M, 2016, EXPERT SYSTEMS WITH APPLICATIONS', 'Senthilnath J, 2016, BIOSYSTEMS ENGINEERING', 'Patil A, 2016, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Belson W, 1959, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES C (APPLIED STATISTICS)', 'Nahvi B, 2016, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Maione C, 2015, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Wildenhain J, 2015, CELL SYSTEMS', 'Su Y, 2017, SAUDI JOURNAL OF BIOLOGICAL SCIENCES', 'Aybar-Ruíz A, 2016, SOLAR ENERGY', 'Maione C, 2018, CRITICAL REVIEWS IN FOOD SCIENCE AND NUTRITION', 'Pantazi X, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Binch A, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Pantazi X, 2017, PRECISION AGRICULTURE', 'Ramírez-Morales I, 2016, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Zhang M, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Johann A, 2016, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Pantazi X, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Kung H, 2016, SUSTAINABILITY', 'Pegorini V, 2015, SENSORS', 'Richardson A, 2016, CLINICAL BIOCHEMISTRY', 'López-Cortés X, 2016, AQUACULTURE', 'Takahashi K, 2017, ROBOTICS AND AUTONOMOUS SYSTEMS', 'Fragni R, 2018, FOOD CONTROL', 'Hu H, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Craninx M, 2006, PUBMED', 'Cortes C, 1995, MACHINE LEARNING', 'Breiman L, 1996, MACHINE LEARNING', ', 1988, ELSEVIER EBOOKS', 'Hecht-Nielsen R, 1987, APPLIED OPTICS', ', 1988, NEURAL NETWORKS', 'Strunk K, 2024, ']</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5664,34 +5684,34 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shokri R, 2017, </t>
+          <t>Λιάκος Κ, 2018, SENSORS</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shokri R, 2017, </t>
+          <t>Λιάκος Κ, 2018, SENSORS</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2885770726</t>
+          <t>https://openalex.org/W2535690855</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10.3390/s18082674</t>
+          <t>10.1109/sp.2017.41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Machine Learning in Agriculture: A Review</t>
+          <t>Membership Inference Attacks Against Machine Learning Models</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5701,80 +5721,60 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>3029</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>SENSORS</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Sensors</t>
-        </is>
-      </c>
+        <v>4215</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>['Κωνσταντίνος Λιάκος', 'Patrizia Busato', 'Dimitrios Moshou', 'Simon Pearson', 'Dionysis Bochtis']</t>
+          <t>['Reza Shokri', 'Marco Stronati', 'Congzheng Song', 'Vitaly Shmatikov']</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>['Konstantinos Liakos', 'Patrizia Busato', 'Dimitrios Moshou', 'Simon Pearson', 'Dionysis Bochtis']</t>
+          <t>['Reza Shokri', 'Marco Stronati', 'Congzheng Song', 'Vitaly Shmatikov']</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>['Institute for Bio-Economy and Agri-Technology (IBO), Centre of Research and Technology—Hellas (CERTH), 6th km Charilaou-Thermi Rd, GR 57001 Thessaloniki, Greece', 'Department of Agriculture, Forestry and Food Sciences (DISAFA), Faculty of Agriculture, University of Turin, Largo Braccini 2, 10095 Grugliasco, Italy', 'Agricultural Engineering Laboratory, Faculty of Agriculture, Aristotle University of Thessaloniki, 54124 Thessaloniki, Greece', 'Institute for Bio-Economy and Agri-Technology (IBO), Centre of Research and Technology—Hellas (CERTH), 6th km Charilaou-Thermi Rd, GR 57001 Thessaloniki, Greece', 'Lincoln Institute for Agri-food Technology (LIAT), University of Lincoln, Brayford Way, Brayford Pool, Lincoln LN6 7TS, UK', 'Institute for Bio-Economy and Agri-Technology (IBO), Centre of Research and Technology—Hellas (CERTH), 6th km Charilaou-Thermi Rd, GR 57001 Thessaloniki, Greece']</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Dionysis Bochtis (corresponding author), Institute for Bio-Economy and Agri-Technology (IBO), Centre of Research and Technology—Hellas (CERTH), 6th km Charilaou-Thermi Rd, GR 57001 Thessaloniki, Greece</t>
-        </is>
-      </c>
+          <t>['Cornell Tech', 'INRIA', 'Cornell', 'Cornell Tech']</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Machine learning has emerged with big data technologies and high-performance computing to create new opportunities for data intensive science in the multi-disciplinary agri-technologies domain. In this paper, we present a comprehensive review of research dedicated to applications of machine learning in agricultural production systems. The works analyzed were categorized in (a) crop management, including applications on yield prediction, disease detection, weed detection crop quality, and species recognition; (b) livestock management, including applications on animal welfare and livestock production; (c) water management; and (d) soil management. The filtering and classification of the presented articles demonstrate how agriculture will benefit from machine learning technologies. By applying machine learning to sensor data, farm management systems are evolving into real time artificial intelligence enabled programs that provide rich recommendations and insights for farmer decision support and action.</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
+          <t>We quantitatively investigate how machine learning models leak information about the individual data records on which they were trained. We focus on the basic membership inference attack: given a data record and black-box access to a model, determine if the record was in the model's training dataset. To perform membership inference against a target model, we make adversarial use of machine learning and train our own inference model to recognize differences in the target model's predictions on the inputs that it trained on versus the inputs that it did not train on. We empirically evaluate our inference techniques on classification models trained by commercial "machine learning as a service" providers such as Google and Amazon. Using realistic datasets and classification tasks, including a hospital discharge dataset whose membership is sensitive from the privacy perspective, we show that these models can be vulnerable to membership inference attacks. We then investigate the factors that influence this leakage and evaluate mitigation strategies.</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>2674</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>2674</t>
-        </is>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>['Agriculture', 'Artificial intelligence', 'Precision agriculture', 'Computer science', 'Machine learning', 'Big data', 'Livestock', 'Decision support system', 'Data science', 'Data mining']</t>
+          <t>['Inference', 'Machine learning', 'Computer science', 'Artificial intelligence', 'Perspective (graphical)', 'Focus (optics)', 'Data modeling', 'Data mining', 'Adversarial system', 'Database']</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>['GR', 'IT', 'GB']</t>
+          <t>['US', 'FR']</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>['Dempster A, 1977, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Chang C, 2011, ACM TRANSACTIONS ON INTELLIGENT SYSTEMS AND TECHNOLOGY', 'Cortes C, 1995, MACHINE LEARNING', 'Hopfield J, 1982, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'McCulloch W, 1943, BULLETIN OF MATHEMATICAL BIOLOGY', 'Jang J, 1993, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS', 'Lloyd S, 1982, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Fisher R, 1936, ANNALS OF EUGENICS', 'Huang G, 2006, NEUROCOMPUTING', 'Rosenblatt F, 1958, PSYCHOLOGICAL REVIEW', 'Cleveland W, 1979, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Suykens J, 1999, NEURAL PROCESSING LETTERS', 'Kohonen T, 1990, PROCEEDINGS OF THE IEEE', 'Friedman J, 1991, THE ANNALS OF STATISTICS', 'Johnson S, 1967, PSYCHOMETRIKA', 'Specht D, 1991, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Riedmiller M, 2002, IEEE INTERNATIONAL CONFERENCE ON NEURAL NETWORKS', 'Suykens J, 2002, WORLD SCIENTIFIC EBOOKS', 'Broomhead D, 1988, COMPLEX SYSTEMS', 'Kong L, 2007, NUCLEIC ACIDS RESEARCH', 'Kass G, 1980, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES C (APPLIED STATISTICS)', 'Fix E, 1989, INTERNATIONAL STATISTICAL REVIEW', 'Salakhutdinov R, 2009, ', 'Atkeson C, 1997, ARTIFICIAL INTELLIGENCE REVIEW', 'Samuel A, 2000, IBM JOURNAL OF RESEARCH AND DEVELOPMENT', 'Pal S, 1992, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Moshou D, 2004, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Linnainmaa S, 1976, BIT NUMERICAL MATHEMATICS', 'Cao J, 2012, NEURAL PROCESSING LETTERS', 'Galvão R, 2008, CHEMOMETRICS AND INTELLIGENT LABORATORY SYSTEMS', 'Mackowiak S, 2015, GENOME BIOLOGY', 'Moshou D, 2005, REAL-TIME IMAGING', 'Asadi H, 2014, PLOS ONE', 'Melssen W, 2006, CHEMOMETRICS AND INTELLIGENT LABORATORY SYSTEMS', 'Dutta R, 2014, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Sengupta S, 2013, BIOSYSTEMS ENGINEERING', 'Amatya S, 2015, BIOSYSTEMS ENGINEERING', 'Mohammadi K, 2015, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Thomas P, 2002, BRITISH JOURNAL OF EDUCATIONAL TECHNOLOGY', 'Coopersmith E, 2014, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Moshou D, 2006, PRECISION AGRICULTURE', 'Craninx M, 2007, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Moshou D, 2013, BIOSYSTEMS ENGINEERING', 'Alonso J, 2013, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Hossain M, 2011, JOURNAL OF HAND SURGERY (EUROPEAN VOLUME)', 'Alonso J, 2014, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Gastaldo P, 2014, ROBOTICS AND AUTONOMOUS SYSTEMS', 'Tryon R, 1957, PSYCHOMETRIKA', 'Neapolitan R, 1987, APPLIED ARTIFICIAL INTELLIGENCE', 'Smith D, 1978, SOCIETY', 'Breiman L, 2001, MACHINE LEARNING', 'LeCun Y, 2015, NATURE', 'Pearson K, 1901, THE LONDON EDINBURGH AND DUBLIN PHILOSOPHICAL MAGAZINE AND JOURNAL OF SCIENCE', 'Ferentinos K, 2018, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Cox D, 1958, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Barboza F, 2017, EXPERT SYSTEMS WITH APPLICATIONS', 'Grinblat G, 2016, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Pantazi X, 2015, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Ebrahimi M, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Morellos A, 2016, BIOSYSTEMS ENGINEERING', 'Zhao Y, 2017, ENERGY ECONOMICS', 'Hansen M, 2018, COMPUTERS IN INDUSTRY', 'Fang K, 2017, GEOPHYSICAL RESEARCH LETTERS', 'Feng Y, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Zhang B, 2017, CANCER LETTERS', 'Rhee J, 2017, AGRICULTURAL AND FOREST METEOROLOGY', 'Mehdizadeh S, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Kang J, 2015, INTERNATIONAL JOURNAL OF RADIATION ONCOLOGY*BIOLOGY*PHYSICS', 'Cramer S, 2017, EXPERT SYSTEMS WITH APPLICATIONS', 'Chung C, 2016, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Matthews S, 2017, SCIENTIFIC REPORTS', 'Zhou C, 2018, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Pantazi X, 2016, BIOSYSTEMS ENGINEERING', 'Ramos P, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Ali I, 2016, IEEE JOURNAL OF SELECTED TOPICS IN APPLIED EARTH OBSERVATIONS AND REMOTE SENSING', 'Bohanec M, 2016, EXPERT SYSTEMS WITH APPLICATIONS', 'Senthilnath J, 2016, BIOSYSTEMS ENGINEERING', 'Patil A, 2016, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Belson W, 1959, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES C (APPLIED STATISTICS)', 'Nahvi B, 2016, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Maione C, 2015, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Wildenhain J, 2015, CELL SYSTEMS', 'Su Y, 2017, SAUDI JOURNAL OF BIOLOGICAL SCIENCES', 'Aybar-Ruíz A, 2016, SOLAR ENERGY', 'Maione C, 2018, CRITICAL REVIEWS IN FOOD SCIENCE AND NUTRITION', 'Pantazi X, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Binch A, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Pantazi X, 2017, PRECISION AGRICULTURE', 'Ramírez-Morales I, 2016, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Zhang M, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Johann A, 2016, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Pantazi X, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Kung H, 2016, SUSTAINABILITY', 'Pegorini V, 2015, SENSORS', 'Richardson A, 2016, CLINICAL BIOCHEMISTRY', 'López-Cortés X, 2016, AQUACULTURE', 'Takahashi K, 2017, ROBOTICS AND AUTONOMOUS SYSTEMS', 'Fragni R, 2018, FOOD CONTROL', 'Hu H, 2017, COMPUTERS AND ELECTRONICS IN AGRICULTURE', 'Craninx M, 2006, PUBMED', 'Cortes C, 1995, MACHINE LEARNING', 'Breiman L, 1996, MACHINE LEARNING', ', 1988, ELSEVIER EBOOKS', 'Hecht-Nielsen R, 1987, APPLIED OPTICS', ', 1988, NEURAL NETWORKS', 'Strunk K, 2024, ']</t>
+          <t>['Srivastava N, 2014, ', 'Hastie T, 2013, ', 'Dwork C, 2006, LECTURE NOTES IN COMPUTER SCIENCE', 'Abadi M, 2016, ', 'Fredrikson M, 2015, ', 'Shokri R, 2015, ', 'Franklin J, 2005, THE MATHEMATICAL INTELLIGENCER', 'Homer N, 2008, PLOS GENETICS', 'Lindell Y, 2000, LECTURE NOTES IN COMPUTER SCIENCE', 'Chaudhuri K, 2011, PUBMED', 'Bassily R, 2014, ', 'Fredrikson M, 2014, PUBMED', 'Chaudhuri K, 2008, ', 'Jagannathan G, 2005, ', 'Hardt M, 2016, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Du W, 2004, ', 'Zhang J, 2012, PROCEEDINGS OF THE VLDB ENDOWMENT', 'Dwork C, 2011, ', 'Yang D, 2016, ACM TRANSACTIONS ON INTELLIGENT SYSTEMS AND TECHNOLOGY', 'Calandrino J, 2011, ', 'Bos J, 2014, JOURNAL OF BIOMEDICAL INFORMATICS', 'Rubinstein B, 2012, JOURNAL OF PRIVACY AND CONFIDENTIALITY', 'Sankararaman S, 2009, NATURE GENETICS', 'Vaidya J, 2007, THE VLDB JOURNAL', 'Barni M, 2011, IEEE TRANSACTIONS ON INFORMATION FORENSICS AND SECURITY', 'Duchi J, 2014, JOURNAL OF THE ACM', 'Schneider I, 2005, THE MATHEMATICAL INTELLIGENCER', 'Dwork C, 2015, ', 'Backes M, 2016, ', 'Zhu J, 2001, ', 'Dwork C, 2010, JOURNAL OF PRIVACY AND CONFIDENTIALITY', 'Diakonikolas I, 2015, EDINBURGH RESEARCH EXPLORER (UNIVERSITY OF EDINBURGH)', 'Krizhevsky A, 2024, ', 'Hinton G, 2015, ARXIV (CORNELL UNIVERSITY)', 'Tramèr F, 2016, ARXIV (CORNELL UNIVERSITY)', 'Chaudhuri K, 2009, ARXIV (CORNELL UNIVERSITY)', ', 2016, IRIS RESEARCH PRODUCT CATALOG (SAPIENZA UNIVERSITY OF ROME)', 'Hardt M, 2015, ARXIV (CORNELL UNIVERSITY)', 'Xie P, 2014, ARXIV (CORNELL UNIVERSITY)', 'Duchi J, 2012, ARXIV (CORNELL UNIVERSITY)', 'Jain P, 2015, ARXIV (CORNELL UNIVERSITY)', 'Kusner M, 2015, POLYPUBLIE (ÉCOLE POLYTECHNIQUE DE MONTRÉAL)']</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>Λιάκος Κ, 2018, SENSORS</t>
+          <t xml:space="preserve">Shokri R, 2017, </t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>Λιάκος Κ, 2018, SENSORS</t>
+          <t xml:space="preserve">Shokri R, 2017, </t>
         </is>
       </c>
     </row>
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>4373</v>
+        <v>4374</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>4651</v>
+        <v>4654</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>2475</v>
+        <v>2478</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -6094,7 +6094,11 @@
           <t>['Faculty of Business Management &amp; Economics, University of Würzburg, Sanderring 2, 97070, Würzburg, Germany', 'Institute of Information Systems, Friedrich-Alexander University Erlangen-Nürnberg, Lange Gasse 20, 90403, Nürnberg, Germany', 'Faculty of Economics and Management, Otto-von-Guericke-Universität Magdeburg, Universitätsplatz 2, 39106, Magdeburg, Germany']</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Christian Janiesch (corresponding author), Faculty of Business Management &amp; Economics, University of Würzburg, Sanderring 2, 97070, Würzburg, Germany</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>Abstract Today, intelligent systems that offer artificial intelligence capabilities often rely on machine learning. Machine learning describes the capacity of systems to learn from problem-specific training data to automate the process of analytical model building and solve associated tasks. Deep learning is a machine learning concept based on artificial neural networks. For many applications, deep learning models outperform shallow machine learning models and traditional data analysis approaches. In this article, we summarize the fundamentals of machine learning and deep learning to generate a broader understanding of the methodical underpinning of current intelligent systems. In particular, we provide a conceptual distinction between relevant terms and concepts, explain the process of automated analytical model building through machine learning and deep learning, and discuss the challenges that arise when implementing such intelligent systems in the field of electronic markets and networked business. These naturally go beyond technological aspects and highlight issues in human-machine interaction and artificial intelligence servitization.</t>
@@ -6185,7 +6189,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>3502</v>
+        <v>3503</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -6287,7 +6291,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2944</v>
+        <v>2947</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -6413,7 +6417,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>3294</v>
+        <v>3295</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -6584,7 +6588,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>['Silver D, 2016, NATURE', 'Dwork C, 2012, ', 'Hempel C, 1948, PHILOSOPHY OF SCIENCE', 'Goodman B, 2017, AI MAGAZINE', 'Chang J, 2009, ', 'Kush B, 2016, ARXIV (CORNELL UNIVERSITY)', 'Keil F, 2005, ANNUAL REVIEW OF PSYCHOLOGY', 'Bechtel W, 2005, STUDIES IN HISTORY AND PHILOSOPHY OF SCIENCE PART C STUDIES IN HISTORY AND PHILOSOPHY OF BIOLOGICAL AND BIOMEDICAL SCIENCES', 'Vanschoren J, 2014, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Lazar J, 2010, ', 'Glennan S, 2002, PHILOSOPHY OF SCIENCE', 'Sculley D, 2015, NEURAL INFORMATION PROCESSING SYSTEMS', 'Lakkaraju H, 2016, ', 'Williams J, 2016, ', 'Wang F, 2015, INTERNATIONAL CONFERENCE ON ARTIFICIAL INTELLIGENCE AND STATISTICS', 'Leí T, 2016, ', 'Kim B, 2015, NEURAL INFORMATION PROCESSING SYSTEMS', 'Antunes P, 2008, ACM COMPUTING SURVEYS', 'Doshi‐Velez F, 2015, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Otte C, 2012, STUDIES IN COMPUTATIONAL INTELLIGENCE', 'Kim B, 2015, DSPACE@MIT (MASSACHUSETTS INSTITUTE OF TECHNOLOGY)', 'Varshney K, 2017, BIG DATA', 'Suissa‐Peleg A, 2016, MICROSCOPY AND MICROANALYSIS', 'Mnih V, 2013, ARXIV (CORNELL UNIVERSITY)', 'Ribeiro M, 2016, ARXIV (CORNELL UNIVERSITY)', 'Garg V, 2016, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>['Silver D, 2016, NATURE', 'Dwork C, 2012, ', 'Hempel C, 1948, PHILOSOPHY OF SCIENCE', 'Goodman B, 2017, AI MAGAZINE', 'Chang J, 2009, ', 'A. D, 2016, ARXIV (CORNELL UNIVERSITY)', 'Keil F, 2005, ANNUAL REVIEW OF PSYCHOLOGY', 'Bechtel W, 2005, STUDIES IN HISTORY AND PHILOSOPHY OF SCIENCE PART C STUDIES IN HISTORY AND PHILOSOPHY OF BIOLOGICAL AND BIOMEDICAL SCIENCES', 'Vanschoren J, 2014, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Lazar J, 2010, ', 'Glennan S, 2002, PHILOSOPHY OF SCIENCE', 'Sculley D, 2015, NEURAL INFORMATION PROCESSING SYSTEMS', 'Lakkaraju H, 2016, ', 'Williams J, 2016, ', 'Wang F, 2015, INTERNATIONAL CONFERENCE ON ARTIFICIAL INTELLIGENCE AND STATISTICS', 'Leí T, 2016, ', 'Kim B, 2015, NEURAL INFORMATION PROCESSING SYSTEMS', 'Antunes P, 2008, ACM COMPUTING SURVEYS', 'Doshi‐Velez F, 2015, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Otte C, 2012, STUDIES IN COMPUTATIONAL INTELLIGENCE', 'Kim B, 2015, DSPACE@MIT (MASSACHUSETTS INSTITUTE OF TECHNOLOGY)', 'Varshney K, 2017, BIG DATA', 'Suissa‐Peleg A, 2016, MICROSCOPY AND MICROANALYSIS', 'Mnih V, 2013, ARXIV (CORNELL UNIVERSITY)', 'Ribeiro M, 2016, ARXIV (CORNELL UNIVERSITY)', 'Garg V, 2016, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -6641,7 +6645,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>4610</v>
+        <v>4615</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -6767,7 +6771,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3091</v>
+        <v>3092</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -6808,7 +6812,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>['Hastie T, 2001, SPRINGER SERIES IN STATISTICS', 'Nasrabadi N, 2007, JOURNAL OF ELECTRONIC IMAGING', 'Schölkopf B, 2001, THE MIT PRESS EBOOKS', 'Murphy K, 2012, ', 'Koller D, 2009, ', 'LeCun Y, 1998, HAL (LE CENTRE POUR LA COMMUNICATION SCIENTIFIQUE DIRECTE)', 'Cristianini N, 2000, EPRINTS SOTON (UNIVERSITY OF SOUTHAMPTON)', 'Devroye L, 1996, STOCHASTIC MODELLING AND APPLIED PROBABILITY', 'Cesa‐Bianchi N, 2006, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Dietterich T, 1995, JOURNAL OF ARTIFICIAL INTELLIGENCE RESEARCH', 'Hiriart‐Urruty J, 1993, ', 'Vapnik V, 1995, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Vapnik V, 2006, INFORMATION SCIENCE AND STATISTICS', 'García J, 1966, PSYCHONOMIC SCIENCE', 'Shapiro A, 2009, ', 'Kearns M, 1994, THE MIT PRESS EBOOKS', 'Barber D, 2012, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Schölkopf B, 2001, LECTURE NOTES IN COMPUTER SCIENCE', 'Айзерман М, 1964, AUTOMATION AND REMOTE CONTROL', 'Zaki M, 2020, CAMBRIDGE UNIVERSITY PRESS EBOOKS', ', 1984, MATHEMATICS AND COMPUTERS IN SIMULATION', 'Anthony M, 1999, LONDON SCHOOL OF ECONOMICS AND POLITICAL SCIENCE RESEARCH ONLINE (LONDON SCHOOL OF ECONOMICS AND POLITICAL SCIENCE)', 'Rokach L, 2007, SERIES IN MACHINE PERCEPTION AND ARTIFICIAL INTELLIGENCE', 'Freund Y, 1998, ', 'Hyafil L, 1976, INFORMATION PROCESSING LETTERS', 'Sauer N, 1972, JOURNAL OF COMBINATORIAL THEORY SERIES A', 'Borwein J, 2006, CMS BOOKS IN MATHEMATICS', 'Weston J, 1999, THE EUROPEAN SYMPOSIUM ON ARTIFICIAL NEURAL NETWORKS', 'E S, 2012, CHOICE REVIEWS ONLINE', 'Shakhnarovich G, 2005, ', 'Shalev‐Shwartz S, 2010, JOURNAL OF MACHINE LEARNING RESEARCH', 'Littlestone N, 2003, ', 'Koltchinskii V, 2000, BIRKHÄUSER BOSTON EBOOKS', 'Shalev‐Shwartz S, 2009, CONFERENCE ON LEARNING THEORY', 'McAllester D, 2003, LECTURE NOTES IN COMPUTER SCIENCE', 'Li L, 2015, SPRINGER OPTIMIZATION AND ITS APPLICATIONS', 'Ian P, 1995, CHOICE REVIEWS ONLINE', 'Gentile C, 2003, MACHINE LEARNING', 'Abernethy J, 2008, SCHOLARLYCOMMONS (UNIVERSITY OF PENNSYLVANIA)', 'Ben-David S, 2009, ', 'Haussler D, 1995, JOURNAL OF COMBINATORIAL THEORY SERIES A', "Bousquet O, 2002, OPENGREY (INSTITUT DE L'INFORMATION SCIENTIFIQUE ET TECHNIQUE)", 'Klivans A, 2006, ', 'Warmuth M, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Pisier G, 1981, FRENCH DIGITAL MATHEMATICS LIBRARY (NUMDAM)', 'Agarwal S, 2005, LECTURE NOTES IN COMPUTER SCIENCE', 'Livni R, 2013, CONFERENCE ON LEARNING THEORY', 'Naftali T, 2000, ARXIV.ORG', 'Shamir O, 2012, ARXIV (CORNELL UNIVERSITY)', 'Freund Y, 1997, JOURNAL OF COMPUTER AND SYSTEM SCIENCES', 'Rosenblatt F, 1958, PSYCHOLOGICAL REVIEW', 'Boser B, 1992, ', 'Robbins H, 1951, THE ANNALS OF MATHEMATICAL STATISTICS', 'Rissanen J, 1978, AUTOMATICA', 'Bengio Y, 2009, NOW PUBLISHERS, INC. EBOOKS', 'Valiant L, 1984, ', 'Fisher R, 1922, PHILOSOPHICAL TRANSACTIONS OF THE ROYAL SOCIETY OF LONDON SERIES A CONTAINING PAPERS OF A MATHEMATICAL OR PHYSICAL CHARACTER', 'Candès E, 2008, COMPTES RENDUS MATHÉMATIQUE', 'Schapire R, 1990, MACHINE LEARNING', 'Vapnik V, 2015, ', 'Sipser M, 1996, ACM SIGACT NEWS', 'Natarajan B, 1995, SIAM JOURNAL ON COMPUTING', 'Neumann J, 1928, MATHEMATISCHE ANNALEN', 'Baraniuk R, 2008, CONSTRUCTIVE APPROXIMATION', 'Nemirovski A, 2009, SIAM JOURNAL ON OPTIMIZATION', 'Phillips D, 1962, JOURNAL OF THE ACM', 'Littlestone N, 1994, INFORMATION AND COMPUTATION', 'Collins M, 2002, ', 'Stone C, 1977, THE ANNALS OF STATISTICS', 'Shalev‐Shwartz S, 2011, NOW PUBLISHERS, INC. EBOOKS', 'Zhang T, 2004, ', 'Davis G, 1997, CONSTRUCTIVE APPROXIMATION', 'Blumer A, 1987, INFORMATION PROCESSING LETTERS', 'Blum L, 1989, BULLETIN OF THE AMERICAN MATHEMATICAL SOCIETY', 'Haussler D, 1992, INFORMATION AND COMPUTATION', 'Joachims T, 2005, ', 'Shelah S, 1972, PACIFIC JOURNAL OF MATHEMATICS', 'McAllester D, 1998, ', 'Boucheron S, 2005, ESAIM PROBABILITY AND STATISTICS', 'McAllester D, 1999, ', 'Kearns M, 1992, ', 'Alon N, 1997, JOURNAL OF THE ACM', 'Shalev‐Shwartz S, 2008, ', 'Shalev‐Shwartz S, 2010, SIAM JOURNAL ON OPTIMIZATION', 'Rogers W, 1978, THE ANNALS OF STATISTICS', 'Gordon G, 1999, ', 'Natarajan B, 1989, MACHINE LEARNING', 'Dudley R, 2010, ', 'Warmuth M, 2006, ', 'Bartlett P, 1994, ', 'Kearns M, 1996, ', 'Ben-David S, 1995, JOURNAL OF COMPUTER AND SYSTEM SCIENCES', 'Slud E, 1977, THE ANNALS OF PROBABILITY', 'Shalev‐Shwartz S, 2010, MACHINE LEARNING', 'Dudley R, 1991, JOURNAL OF THEORETICAL PROBABILITY', 'Floyd S, 1989, CONFERENCE ON LEARNING THEORY', 'Horváth M, 1998, DISCRETE APPLIED MATHEMATICS', 'Sankaran J, 1993, OPERATIONS RESEARCH LETTERS', 'Minsky M, 1969, ', 'Tibshirani R, 1996, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Vapnik V, 1995, ', 'Cortes C, 1995, MACHINE LEARNING', 'Wu Y, 1999, TECHNOMETRICS', 'Quinlan J, 1992, ', 'Hinton G, 2006, NEURAL COMPUTATION', 'Cover T, 1967, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Quinlan J, 1986, MACHINE LEARNING', 'Wolpert D, 1997, IEEE TRANSACTIONS ON EVOLUTIONARY COMPUTATION', 'Lafferty J, 2001, SCHOLARLY COMMONS (UNIVERSITY OF PENNSYLVANIA)', 'Luxburg U, 2007, STATISTICS AND COMPUTING', 'Mallat S, 1993, IEEE TRANSACTIONS ON SIGNAL PROCESSING', 'Schölkopf B, 1998, NEURAL COMPUTATION', 'Candès E, 2005, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Collobert R, 2008, ', 'Hsu C, 2008, ', 'Georghiades A, 2001, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Rabiner L, 1986, IEEE ASSP MAGAZINE', ', 2000, APPLIED PHYSICS LETTERS', 'Frank M, 1956, NAVAL RESEARCH LOGISTICS QUARTERLY', 'Rumelhart D, 1988, ELSEVIER EBOOKS', 'Lee H, 2009, ', 'Zhao P, 2006, ', 'Blumer A, 1989, JOURNAL OF THE ACM', 'Zinkevich M, 2003, ', 'Rissanen J, 1983, THE ANNALS OF STATISTICS', 'Littlestone N, 1988, MACHINE LEARNING', 'Taskar B, 2003, ', 'Bottou L, 2011, THE MIT PRESS EBOOKS', 'Ranzato M, 2007, ', 'Shalev‐Shwartz S, 2007, ', 'Hazan E, 2007, MACHINE LEARNING', ', 2000, APPLIED PHYSICS LETTERS', 'Vapnik V, 1991, NEURAL INFORMATION PROCESSING SYSTEMS', 'Kleinberg J, 2002, ', ', 2000, APPLIED PHYSICS LETTERS', 'Kearns M, 1999, NEURAL COMPUTATION', 'Collins M, 2005, COMPUTATIONAL LINGUISTICS', 'Bottou L, 2003, ', 'Shalev‐Shwartz S, 2007, ', 'Floyd S, 1995, MACHINE LEARNING', 'Weston J, 2002, ', 'Langford J, 2002, NEURAL INFORMATION PROCESSING SYSTEMS', 'Ben-David S, 2008, NEURAL INFORMATION PROCESSING SYSTEMS', 'Pitt L, 1988, JOURNAL OF THE ACM', 'Rakhlin A, 2010, SCHOLARLYCOMMONS (UNIVERSITY OF PENNSYLVANIA)', 'Rakhlin A, 2005, ANALYSIS AND APPLICATIONS', 'Ben-David S, 2000, ', 'Bartlett P, 2002, THEORETICAL COMPUTER SCIENCE', 'Rakhlin A, 2011, ARXIV (CORNELL UNIVERSITY)', 'Breiman L, 2001, MACHINE LEARNING', 'Boyd S, 2004, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Ryzin J, 1986, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Donoho D, 2004, ', 'Kuhn H, 1955, NAVAL RESEARCH LOGISTICS QUARTERLY', 'Pearson K, 1901, THE LONDON EDINBURGH AND DUBLIN PHILOSOPHICAL MAGAZINE AND JOURNAL OF SCIENCE', 'Karp R, 1972, ', 'Bertsekas D, 1997, JOURNAL OF THE OPERATIONAL RESEARCH SOCIETY', ', 2004, CHOICE REVIEWS ONLINE', 'Нестеров Ю, 2014, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Bartlett P, 2001, LECTURE NOTES IN COMPUTER SCIENCE', 'Crammer K, 2002, ', 'Rarp K, 2012, ', 'Bruijn d, 1946, DATA ARCHIVING AND NETWORKED SERVICES (DANS)', 'Tsochantaridis I, 2004, ', 'Bengio Y, 2007, ', 'Tikhonov A, 1943, PROCEEDINGS OF THE USSR ACADEMY OF SCIENCES', 'Ranzato M, 2012, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Bartlett P, 2002, ', 'Vovk V, 1990, CONFERENCE ON LEARNING THEORY', 'Agmon S, 1954, CANADIAN JOURNAL OF MATHEMATICS', 'Neumann J, 1953, PRINCETON UNIVERSITY PRESS EBOOKS', 'Collins M, 2000, ', 'Hadamard J, 1902, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Donoho D, 2011, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Langford J, 2005, ', 'Seeger M, 2003, JOURNAL OF MACHINE LEARNING RESEARCH', 'Kakade S, 2008, SCHOLARLYCOMMONS (UNIVERSITY OF PENNSYLVANIA)', 'Mukherjee S, 2006, ADVANCES IN COMPUTATIONAL MATHEMATICS', 'Kearns M, 1988, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Cover T, 1966, ', 'Murata N, 1999, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Livni R, 2013, ARXIV (CORNELL UNIVERSITY)', 'Shalev‐Shwartz S, 2010, ', ', 2012, SPRINGERREFERENCE', 'Poon H, 2012, ARXIV (CORNELL UNIVERSITY)', 'Daniely A, 2012, ARXIV (CORNELL UNIVERSITY)', 'Chang H, 2009, ARXIV.ORG']</t>
+          <t>['Hastie T, 2001, SPRINGER SERIES IN STATISTICS', 'Nasrabadi N, 2007, JOURNAL OF ELECTRONIC IMAGING', 'Schölkopf B, 2001, THE MIT PRESS EBOOKS', 'Murphy K, 2012, ', 'Koller D, 2009, ', 'LeCun Y, 1998, HAL (LE CENTRE POUR LA COMMUNICATION SCIENTIFIQUE DIRECTE)', 'Cristianini N, 2000, EPRINTS SOTON (UNIVERSITY OF SOUTHAMPTON)', 'Devroye L, 1996, STOCHASTIC MODELLING AND APPLIED PROBABILITY', 'Cesa‐Bianchi N, 2006, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Dietterich T, 1995, JOURNAL OF ARTIFICIAL INTELLIGENCE RESEARCH', 'Hiriart‐Urruty J, 1993, ', 'Vapnik V, 1995, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Vapnik V, 2006, INFORMATION SCIENCE AND STATISTICS', 'García J, 1966, PSYCHONOMIC SCIENCE', 'Shapiro A, 2009, ', 'Kearns M, 1994, THE MIT PRESS EBOOKS', 'Barber D, 2012, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Schölkopf B, 2001, LECTURE NOTES IN COMPUTER SCIENCE', 'Айзерман М, 1964, AUTOMATION AND REMOTE CONTROL', 'Zaki M, 2020, CAMBRIDGE UNIVERSITY PRESS EBOOKS', ', 1984, MATHEMATICS AND COMPUTERS IN SIMULATION', 'Anthony M, 1999, LONDON SCHOOL OF ECONOMICS AND POLITICAL SCIENCE RESEARCH ONLINE (LONDON SCHOOL OF ECONOMICS AND POLITICAL SCIENCE)', 'Rokach L, 2007, SERIES IN MACHINE PERCEPTION AND ARTIFICIAL INTELLIGENCE', 'Freund Y, 1998, ', 'Hyafil L, 1976, INFORMATION PROCESSING LETTERS', 'Sauer N, 1972, JOURNAL OF COMBINATORIAL THEORY SERIES A', 'Borwein J, 2006, CMS BOOKS IN MATHEMATICS', 'Weston J, 1999, THE EUROPEAN SYMPOSIUM ON ARTIFICIAL NEURAL NETWORKS', 'E S, 2012, CHOICE REVIEWS ONLINE', 'Shakhnarovich G, 2005, ', 'Shalev‐Shwartz S, 2010, JOURNAL OF MACHINE LEARNING RESEARCH', 'Littlestone N, 2003, ', 'Koltchinskii V, 2000, BIRKHÄUSER BOSTON EBOOKS', 'Shalev‐Shwartz S, 2009, CONFERENCE ON LEARNING THEORY', 'McAllester D, 2003, LECTURE NOTES IN COMPUTER SCIENCE', 'Li L, 2015, SPRINGER OPTIMIZATION AND ITS APPLICATIONS', 'Ian P, 1995, CHOICE REVIEWS ONLINE', 'Gentile C, 2003, MACHINE LEARNING', 'Abernethy J, 2008, SCHOLARLYCOMMONS (UNIVERSITY OF PENNSYLVANIA)', 'Ben-David S, 2009, ', 'Haussler D, 1995, JOURNAL OF COMBINATORIAL THEORY SERIES A', "Bousquet O, 2002, OPENGREY (INSTITUT DE L'INFORMATION SCIENTIFIQUE ET TECHNIQUE)", 'Klivans A, 2006, ', 'Warmuth M, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Pisier G, 1981, FRENCH DIGITAL MATHEMATICS LIBRARY (NUMDAM)', 'Agarwal S, 2005, LECTURE NOTES IN COMPUTER SCIENCE', 'Livni R, 2013, CONFERENCE ON LEARNING THEORY', 'Eugenio P, 2000, ARXIV.ORG', 'Shamir O, 2012, ARXIV (CORNELL UNIVERSITY)', 'Freund Y, 1997, JOURNAL OF COMPUTER AND SYSTEM SCIENCES', 'Rosenblatt F, 1958, PSYCHOLOGICAL REVIEW', 'Boser B, 1992, ', 'Robbins H, 1951, THE ANNALS OF MATHEMATICAL STATISTICS', 'Rissanen J, 1978, AUTOMATICA', 'Bengio Y, 2009, NOW PUBLISHERS, INC. EBOOKS', 'Valiant L, 1984, ', 'Fisher R, 1922, PHILOSOPHICAL TRANSACTIONS OF THE ROYAL SOCIETY OF LONDON SERIES A CONTAINING PAPERS OF A MATHEMATICAL OR PHYSICAL CHARACTER', 'Candès E, 2008, COMPTES RENDUS MATHÉMATIQUE', 'Schapire R, 1990, MACHINE LEARNING', 'Vapnik V, 2015, ', 'Sipser M, 1996, ACM SIGACT NEWS', 'Natarajan B, 1995, SIAM JOURNAL ON COMPUTING', 'Neumann J, 1928, MATHEMATISCHE ANNALEN', 'Baraniuk R, 2008, CONSTRUCTIVE APPROXIMATION', 'Nemirovski A, 2009, SIAM JOURNAL ON OPTIMIZATION', 'Phillips D, 1962, JOURNAL OF THE ACM', 'Littlestone N, 1994, INFORMATION AND COMPUTATION', 'Collins M, 2002, ', 'Stone C, 1977, THE ANNALS OF STATISTICS', 'Shalev‐Shwartz S, 2011, NOW PUBLISHERS, INC. EBOOKS', 'Zhang T, 2004, ', 'Davis G, 1997, CONSTRUCTIVE APPROXIMATION', 'Blumer A, 1987, INFORMATION PROCESSING LETTERS', 'Blum L, 1989, BULLETIN OF THE AMERICAN MATHEMATICAL SOCIETY', 'Haussler D, 1992, INFORMATION AND COMPUTATION', 'Joachims T, 2005, ', 'Shelah S, 1972, PACIFIC JOURNAL OF MATHEMATICS', 'McAllester D, 1998, ', 'Boucheron S, 2005, ESAIM PROBABILITY AND STATISTICS', 'McAllester D, 1999, ', 'Kearns M, 1992, ', 'Alon N, 1997, JOURNAL OF THE ACM', 'Shalev‐Shwartz S, 2008, ', 'Shalev‐Shwartz S, 2010, SIAM JOURNAL ON OPTIMIZATION', 'Rogers W, 1978, THE ANNALS OF STATISTICS', 'Gordon G, 1999, ', 'Natarajan B, 1989, MACHINE LEARNING', 'Dudley R, 2010, ', 'Warmuth M, 2006, ', 'Bartlett P, 1994, ', 'Kearns M, 1996, ', 'Ben-David S, 1995, JOURNAL OF COMPUTER AND SYSTEM SCIENCES', 'Slud E, 1977, THE ANNALS OF PROBABILITY', 'Shalev‐Shwartz S, 2010, MACHINE LEARNING', 'Dudley R, 1991, JOURNAL OF THEORETICAL PROBABILITY', 'Floyd S, 1989, CONFERENCE ON LEARNING THEORY', 'Horváth M, 1998, DISCRETE APPLIED MATHEMATICS', 'Sankaran J, 1993, OPERATIONS RESEARCH LETTERS', 'Minsky M, 1969, ', 'Tibshirani R, 1996, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Vapnik V, 1995, ', 'Cortes C, 1995, MACHINE LEARNING', 'Wu Y, 1999, TECHNOMETRICS', 'Quinlan J, 1992, ', 'Hinton G, 2006, NEURAL COMPUTATION', 'Cover T, 1967, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Quinlan J, 1986, MACHINE LEARNING', 'Wolpert D, 1997, IEEE TRANSACTIONS ON EVOLUTIONARY COMPUTATION', 'Lafferty J, 2001, SCHOLARLY COMMONS (UNIVERSITY OF PENNSYLVANIA)', 'Luxburg U, 2007, STATISTICS AND COMPUTING', 'Mallat S, 1993, IEEE TRANSACTIONS ON SIGNAL PROCESSING', 'Schölkopf B, 1998, NEURAL COMPUTATION', 'Candès E, 2005, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Collobert R, 2008, ', 'Hsu C, 2008, ', 'Georghiades A, 2001, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Rabiner L, 1986, IEEE ASSP MAGAZINE', ', 2000, APPLIED PHYSICS LETTERS', 'Frank M, 1956, NAVAL RESEARCH LOGISTICS QUARTERLY', 'Rumelhart D, 1988, ELSEVIER EBOOKS', 'Lee H, 2009, ', 'Zhao P, 2006, ', 'Blumer A, 1989, JOURNAL OF THE ACM', 'Zinkevich M, 2003, ', 'Rissanen J, 1983, THE ANNALS OF STATISTICS', 'Littlestone N, 1988, MACHINE LEARNING', 'Taskar B, 2003, ', 'Bottou L, 2011, THE MIT PRESS EBOOKS', 'Ranzato M, 2007, ', 'Shalev‐Shwartz S, 2007, ', 'Hazan E, 2007, MACHINE LEARNING', ', 2000, APPLIED PHYSICS LETTERS', 'Vapnik V, 1991, NEURAL INFORMATION PROCESSING SYSTEMS', 'Kleinberg J, 2002, ', ', 2000, APPLIED PHYSICS LETTERS', 'Kearns M, 1999, NEURAL COMPUTATION', 'Collins M, 2005, COMPUTATIONAL LINGUISTICS', 'Bottou L, 2003, ', 'Shalev‐Shwartz S, 2007, ', 'Floyd S, 1995, MACHINE LEARNING', 'Weston J, 2002, ', 'Langford J, 2002, NEURAL INFORMATION PROCESSING SYSTEMS', 'Ben-David S, 2008, NEURAL INFORMATION PROCESSING SYSTEMS', 'Pitt L, 1988, JOURNAL OF THE ACM', 'Rakhlin A, 2010, SCHOLARLYCOMMONS (UNIVERSITY OF PENNSYLVANIA)', 'Rakhlin A, 2005, ANALYSIS AND APPLICATIONS', 'Ben-David S, 2000, ', 'Bartlett P, 2002, THEORETICAL COMPUTER SCIENCE', 'Rakhlin A, 2011, ARXIV (CORNELL UNIVERSITY)', 'Breiman L, 2001, MACHINE LEARNING', 'Boyd S, 2004, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Ryzin J, 1986, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Donoho D, 2004, ', 'Kuhn H, 1955, NAVAL RESEARCH LOGISTICS QUARTERLY', 'Pearson K, 1901, THE LONDON EDINBURGH AND DUBLIN PHILOSOPHICAL MAGAZINE AND JOURNAL OF SCIENCE', 'Karp R, 1972, ', 'Bertsekas D, 1997, JOURNAL OF THE OPERATIONAL RESEARCH SOCIETY', ', 2004, CHOICE REVIEWS ONLINE', 'Нестеров Ю, 2014, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Bartlett P, 2001, LECTURE NOTES IN COMPUTER SCIENCE', 'Crammer K, 2002, ', 'Rarp K, 2012, ', 'Bruijn d, 1946, DATA ARCHIVING AND NETWORKED SERVICES (DANS)', 'Tsochantaridis I, 2004, ', 'Bengio Y, 2007, ', 'Tikhonov A, 1943, PROCEEDINGS OF THE USSR ACADEMY OF SCIENCES', 'Ranzato M, 2012, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Bartlett P, 2002, ', 'Vovk V, 1990, CONFERENCE ON LEARNING THEORY', 'Agmon S, 1954, CANADIAN JOURNAL OF MATHEMATICS', 'Neumann J, 1953, PRINCETON UNIVERSITY PRESS EBOOKS', 'Collins M, 2000, ', 'Hadamard J, 1902, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Donoho D, 2011, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Langford J, 2005, ', 'Seeger M, 2003, JOURNAL OF MACHINE LEARNING RESEARCH', 'Kakade S, 2008, SCHOLARLYCOMMONS (UNIVERSITY OF PENNSYLVANIA)', 'Mukherjee S, 2006, ADVANCES IN COMPUTATIONAL MATHEMATICS', 'Kearns M, 1988, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Cover T, 1966, ', 'Murata N, 1999, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Livni R, 2013, ARXIV (CORNELL UNIVERSITY)', 'Shalev‐Shwartz S, 2010, ', ', 2012, SPRINGERREFERENCE', 'Poon H, 2012, ARXIV (CORNELL UNIVERSITY)', 'Daniely A, 2012, ARXIV (CORNELL UNIVERSITY)', 'Chang H, 2009, ARXIV.ORG']</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -6983,7 +6987,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -7080,17 +7084,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2975634117</t>
+          <t>https://openalex.org/W2973119841</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10.1038/s41592-019-0582-9</t>
+          <t>10.1146/annurev-fluid-010719-060214</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ilastik: interactive machine learning for (bio)image analysis</t>
+          <t>Machine Learning for Fluid Mechanics</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7105,72 +7109,76 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>3605</v>
+        <v>2608</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>NATURE METHODS</t>
+          <t>ANNUAL REVIEW OF FLUID MECHANICS</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Nature Methods</t>
+          <t>Annual Review of Fluid Mechanics</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>['Stuart Berg', 'Dominik Kutra', 'Thorben Kroeger', 'Christoph Straehle', 'Bernhard X. Kausler', 'Carsten Haubold', 'Martin Schiegg', 'Janez Aleš', 'Thorsten Beier', 'Markus Rudy', 'Kemal Eren', 'Jaime I Cervantes', 'Buote Xu', 'Fynn Beuttenmueller', 'Adrian Wolny', 'Chong Zhang', 'Ullrich Koethe', 'Fred A. Hamprecht', 'Anna Kreshuk']</t>
+          <t>['Steven L. Brunton', 'Bernd R. Noack', 'Petros Koumoutsakos']</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>['Stuart Berg', 'Dominik Kutra', 'Thorben Kroeger', 'Christoph N. Straehle', 'Bernhard X. Kausler', 'Carsten Haubold', 'Martin Schiegg', 'Janez Ales', 'Thorsten Beier', 'Markus Rudy', 'Kemal Eren', 'Jaime I Cervantes', 'Buote Xu', 'Fynn Beuttenmueller', 'Adrian Wolny', 'Chong Zhang', 'Ullrich Koethe', 'Fred A. Hamprecht', 'Anna Kreshuk']</t>
+          <t>['Steven L. Brunton', 'Bernd R. Noack', 'Petros Koumoutsakos']</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>['HHMI Janelia Research Campus, Ashburn, Virginia, USA', 'European Molecular Biology Laboratory, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'European Molecular Biology Laboratory, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany. fred.hamprecht@iwr.uni-heidelberg.de', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'European Molecular Biology Laboratory, Heidelberg, Germany. anna.kreshuk@embl.de', 'HCI/IWR, Heidelberg University, Heidelberg, Germany. anna.kreshuk@embl.de', 'European Molecular Biology Laboratory, Heidelberg, Germany']</t>
+          <t>['Department of Mechanical Engineering, University of Washington, Seattle, Washington 98195, USA', 'Institut für Strömungsmechanik und Technische Akustik, Technische Universität Berlin, D-10634 Berlin, Germany', "LIMSI (Laboratoire d'Informatique pour la Mécanique et les Sciences de l'Ingénieur), CNRS UPR 3251, Université Paris-Saclay, F-91403 Orsay, France", 'Computational Science and Engineering Laboratory, ETH Zurich, CH-8092 Zurich, Switzerland;']</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>The field of fluid mechanics is rapidly advancing, driven by unprecedented volumes of data from experiments, field measurements, and large-scale simulations at multiple spatiotemporal scales. Machine learning (ML) offers a wealth of techniques to extract information from data that can be translated into knowledge about the underlying fluid mechanics. Moreover, ML algorithms can augment domain knowledge and automate tasks related to flow control and optimization. This article presents an overview of past history, current developments, and emerging opportunities of ML for fluid mechanics. We outline fundamental ML methodologies and discuss their uses for understanding, modeling, optimizing, and controlling fluid flows. The strengths and limitations of these methods are addressed from the perspective of scientific inquiry that considers data as an inherent part of modeling, experiments, and simulations. ML provides a powerful information-processing framework that can augment, and possibly even transform, current lines of fluid mechanics research and industrial applications.</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>52</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>477</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>508</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>['Computer science', 'Workflow', 'Artificial intelligence', 'Segmentation', 'Machine learning', 'Classifier (UML)', 'Image segmentation', 'Computer vision', 'Pattern recognition (psychology)', 'Database']</t>
+          <t>['Fluid mechanics', 'Current (fluid)', 'Field (mathematics)', 'Perspective (graphical)', 'Fluid dynamics', 'Domain (mathematical analysis)']</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>['US', 'DE']</t>
+          <t>['US', 'FR', 'DE', 'CH']</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>['Breiman L, 2001, MACHINE LEARNING', 'Schindelin J, 2012, NATURE METHODS', 'Carpenter A, 2006, GENOME BIOLOGY', 'Arganda‐Carreras I, 2017, BIOINFORMATICS', 'Loy C, 2012, ', 'Vilariño D, 2017, JOURNAL OF APPLIED REMOTE SENSING', 'Erickson B, 2017, RADIOGRAPHICS', 'Berthold M, 2008, STUDIES IN CLASSIFICATION, DATA ANALYSIS, AND KNOWLEDGE ORGANIZATION', 'Sommer C, 2011, ', 'Linkert M, 2010, THE JOURNAL OF CELL BIOLOGY', 'Neumann B, 2010, NATURE', 'Tarca A, 2007, PLOS COMPUTATIONAL BIOLOGY', 'Tu Z, 2009, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Stalling D, 2005, ELSEVIER EBOOKS', 'Belevich I, 2016, PLOS BIOLOGY', 'Nixon‐Abell J, 2016, SCIENCE', 'Korogod N, 2015, ELIFE', 'Ciliberti S, 2007, PLOS COMPUTATIONAL BIOLOGY', 'Streichan S, 2014, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Simpson R, 2014, ', 'Geurts P, 2009, MOLECULAR BIOSYSTEMS', 'Marée R, 2016, BIOINFORMATICS', 'Wolff C, 2018, ELIFE', 'Beier T, 2017, NATURE METHODS', 'Raote I, 2018, ELIFE', 'Andres B, 2011, ', 'Luengo I, 2017, JOURNAL OF STRUCTURAL BIOLOGY', 'Sommer C, 2017, MOLECULAR BIOLOGY OF THE CELL', 'Maco B, 2013, PLOS ONE', 'Schiegg M, 2013, ', 'Cassani C, 2016, PLOS BIOLOGY', 'Hughes A, 2018, NATURE METHODS', 'Hilsenbeck O, 2017, BIOINFORMATICS', 'González-Tendero A, 2016, EUROPEAN HEART JOURNAL - CARDIOVASCULAR IMAGING', 'Haubold C, 2016, ADVANCES IN ANATOMY, EMBRYOLOGY AND CELL BIOLOGY', 'Beier T, 2015, ', 'Jorstad A, 2018, FRONTIERS IN NEUROANATOMY', 'Straehle C, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Straehle C, 2012, ', 'Haubold C, 2016, LECTURE NOTES IN COMPUTER SCIENCE', 'Pedregosa F, 2012, ARXIV (CORNELL UNIVERSITY)', ', 2013, ', ', 2011, ']</t>
+          <t>['Hochreiter S, 1997, NEURAL COMPUTATION', 'Rumelhart D, 1986, NATURE', 'Rosenblatt F, 1958, PSYCHOLOGICAL REVIEW', 'Germano M, 1991, PHYSICS OF FLUIDS A FLUID DYNAMICS', 'Sirovich L, 1987, QUARTERLY OF APPLIED MATHEMATICS', 'Schmid P, 2010, JOURNAL OF FLUID MECHANICS', 'Dong C, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Schmidt M, 2009, SCIENCE', 'Freeman W, 2002, IEEE COMPUTER GRAPHICS AND APPLICATIONS', 'Willert C, 1991, EXPERIMENTS IN FLUIDS', 'Grossberg S, 1976, BIOLOGICAL CYBERNETICS', 'Barber D, 2012, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Grossberg S, 1988, NEURAL NETWORKS', 'Baldi P, 1989, NEURAL NETWORKS', 'Gardner E, 1988, JOURNAL OF PHYSICS A MATHEMATICAL AND GENERAL', 'Bellman R, 1952, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Tesauro G, 1992, MACHINE LEARNING', 'Schwefel H, 1977, BIRKHÄUSER BASEL EBOOKS', 'Fleming P, 2002, CONTROL ENGINEERING PRACTICE', 'Brunton S, 2015, APPLIED MECHANICS REVIEWS', 'Dissanayake G, 1994, COMMUNICATIONS IN NUMERICAL METHODS IN ENGINEERING', 'Barber R, 2015, THE ANNALS OF STATISTICS', 'Amsallem D, 2012, INTERNATIONAL JOURNAL FOR NUMERICAL METHODS IN ENGINEERING', 'Ouellette N, 2005, EXPERIMENTS IN FLUIDS', 'Bewley T, 2001, JOURNAL OF FLUID MECHANICS', 'Rokhlin V, 2009, SIAM JOURNAL ON MATRIX ANALYSIS AND APPLICATIONS', 'Milano M, 2002, JOURNAL OF COMPUTATIONAL PHYSICS', 'Ling J, 2015, PHYSICS OF FLUIDS', 'Hansen N, 2008, IEEE TRANSACTIONS ON EVOLUTIONARY COMPUTATION', 'Lee C, 1997, PHYSICS OF FLUIDS', 'Graves A, 2007, LECTURE NOTES IN COMPUTER SCIENCE', 'Kern S, 2004, NATURAL COMPUTING', 'González‐García R, 1998, COMPUTERS &amp; CHEMICAL ENGINEERING', 'Bright I, 2013, PHYSICS OF FLUIDS', 'Jambunathan K, 1996, INTERNATIONAL JOURNAL OF HEAT AND MASS TRANSFER', 'Rico-Martı́nez R, 1992, CHEMICAL ENGINEERING COMMUNICATIONS', 'Gazzola M, 2014, SIAM JOURNAL ON SCIENTIFIC COMPUTING', 'Faller W, 1996, PROGRESS IN AEROSPACE SCIENCES', 'Nair A, 2015, JOURNAL OF FLUID MECHANICS', 'Ostermeier A, 1994, LECTURE NOTES IN COMPUTER SCIENCE', 'Bishop C, 1993, NUCLEAR INSTRUMENTS AND METHODS IN PHYSICS RESEARCH SECTION A ACCELERATORS SPECTROMETERS DETECTORS AND ASSOCIATED EQUIPMENT', 'Giannakoglou K, 2006, COMPUTER METHODS IN APPLIED MECHANICS AND ENGINEERING', 'Dracopoulos D, 1997, PERSPECTIVES IN NEURAL COMPUTING', 'Labonté G, 1999, EXPERIMENTS IN FLUIDS', 'Liang D, 2003, EXPERIMENTS IN FLUIDS', 'Grant I, 1995, EXPERIMENTS IN FLUIDS', 'Bourguignon J, 2014, PHYSICS OF FLUIDS', 'Hamdaouı M, 2010, JOURNAL OF AIRCRAFT', 'Pelikán M, 2004, LECTURE NOTES IN COMPUTER SCIENCE', 'Phan M, 1995, SERIES ON STABILITY, VIBRATION AND CONTROL OF SYSTEMS - SERIES B', 'Mnih V, 2015, NATURE', 'Hornik K, 1989, NEURAL NETWORKS', 'Hopfield J, 1982, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Silver D, 2016, NATURE', 'Wright J, 2009, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Yang J, 2010, IEEE TRANSACTIONS ON IMAGE PROCESSING', 'Brunton S, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Halko N, 2011, SIAM REVIEW', 'Adrian R, 1991, ANNUAL REVIEW OF FLUID MECHANICS', 'Hansen N, 2003, EVOLUTIONARY COMPUTATION', 'Sirovich L, 1987, JOURNAL OF THE OPTICAL SOCIETY OF AMERICA A', 'Rowley C, 2009, JOURNAL OF FLUID MECHANICS', 'Lagaris I, 1998, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Richter S, 2016, LECTURE NOTES IN COMPUTER SCIENCE', 'Ling J, 2016, JOURNAL OF FLUID MECHANICS', 'Rudy S, 2017, SCIENCE ADVANCES', 'Meneveau C, 2000, ANNUAL REVIEW OF FLUID MECHANICS', 'Raissi M, 2017, JOURNAL OF COMPUTATIONAL PHYSICS', 'Mezić I, 2012, ANNUAL REVIEW OF FLUID MECHANICS', 'Rowley C, 2016, ANNUAL REVIEW OF FLUID MECHANICS', 'Meijering E, 2002, PROCEEDINGS OF THE IEEE', 'Parish E, 2015, JOURNAL OF COMPUTATIONAL PHYSICS', 'Wang J, 2017, PHYSICAL REVIEW FLUIDS', 'Manohar K, 2018, IEEE CONTROL SYSTEMS', 'Schaeffer H, 2017, PROCEEDINGS OF THE ROYAL SOCIETY A MATHEMATICAL PHYSICAL AND ENGINEERING SCIENCES', 'Li Q, 2017, CHAOS AN INTERDISCIPLINARY JOURNAL OF NONLINEAR SCIENCE', 'Wu X, 2008, JOURNAL OF FLUID MECHANICS', 'Ling J, 2016, JOURNAL OF COMPUTATIONAL PHYSICS', 'Loiseau J, 2018, JOURNAL OF FLUID MECHANICS', 'Williams M, 2015, JOURNAL OF COMPUTATIONAL DYNAMICS', 'Xiao H, 2016, JOURNAL OF COMPUTATIONAL PHYSICS', 'Kaiser E, 2014, JOURNAL OF FLUID MECHANICS', 'Perlman E, 2007, ', 'Colabrese S, 2017, PHYSICAL REVIEW LETTERS', 'Glaz B, 2010, AIAA JOURNAL', 'Pierret S, 1999, JOURNAL OF TURBOMACHINERY', 'Reddy G, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Gazzola M, 2012, JOURNAL OF FLUID MECHANICS', 'Büche D, 2002, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS PART C (APPLICATIONS AND REVIEWS)', 'Gazzola M, 2016, JOURNAL OF FLUID MECHANICS', 'Perdikaris P, 2016, SIAM JOURNAL ON SCIENTIFIC COMPUTING', 'Bai Z, 2014, AIAA JOURNAL', 'Bénard N, 2016, EXPERIMENTS IN FLUIDS', 'Nüske F, 2016, THE JOURNAL OF CHEMICAL PHYSICS', 'Semeraro O, 2017, PHYSICAL REVIEW FLUIDS', 'Rees W, 2015, JOURNAL OF FLUID MECHANICS', 'Guéniat F, 2016, THEORETICAL AND COMPUTATIONAL FLUID DYNAMICS', 'Tsiotras P, 2017, JOURNAL OF GUIDANCE CONTROL AND DYNAMICS', 'Teo C, 2002, ', 'Papadimitriou D, 2015, INTERNATIONAL JOURNAL FOR UNCERTAINTY QUANTIFICATION', 'Breiman L, 2001, MACHINE LEARNING', 'LeCun Y, 2015, NATURE', 'Hastie T, 2009, SPRINGER SERIES IN STATISTICS', 'Donoho D, 2006, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Raissi M, 2018, JOURNAL OF COMPUTATIONAL PHYSICS', 'Taira K, 2017, AIAA JOURNAL', 'Duraisamy K, 2018, ANNUAL REVIEW OF FLUID MECHANICS', 'Lusch B, 2018, NATURE COMMUNICATIONS', 'Pathak J, 2018, PHYSICAL REVIEW LETTERS', 'Kutz J, 2016, SOCIETY FOR INDUSTRIAL AND APPLIED MATHEMATICS EBOOKS', 'Brunton S, 2019, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Fukami K, 2019, JOURNAL OF FLUID MECHANICS', 'Rabault J, 2019, JOURNAL OF FLUID MECHANICS', 'Mardt A, 2017, NATURE COMMUNICATIONS', 'Cherkassky V, 2006, ', 'Verma S, 2018, ARXIV (CORNELL UNIVERSITY)', 'Wehmeyer C, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Vlachas P, 2018, PROCEEDINGS OF THE ROYAL SOCIETY A MATHEMATICAL PHYSICAL AND ENGINEERING SCIENCES', 'Maulik R, 2018, JOURNAL OF FLUID MECHANICS', 'Xie Y, 2018, ACM TRANSACTIONS ON GRAPHICS', 'Kim B, 2019, COMPUTER GRAPHICS FORUM', 'Wan Z, 2018, PLOS ONE', 'Skinner S, 2017, APPLIED SOFT COMPUTING', 'Reddy G, 2018, NATURE', 'Novati G, 2017, BIOINSPIRATION &amp; BIOMIMETICS', 'Lee Y, 2017, EXPERIMENTS IN FLUIDS', 'Colvert B, 2018, BIOINSPIRATION &amp; BIOMIMETICS', 'Novati G, 2019, PHYSICAL REVIEW FLUIDS', 'Colabrese S, 2018, PHYSICAL REVIEW FLUIDS', 'Meena M, 2018, PHYSICAL REVIEW. E', 'Alsalman M, 2018, BIOINSPIRATION &amp; BIOMIMETICS', 'Martin N, 2018, BIOINSPIRATION &amp; BIOMIMETICS', 'Hou W, 2019, AIAA SCITECH 2019 FORUM']</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -7186,29 +7194,29 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>Berg S, 2019, NATURE METHODS</t>
+          <t>Brunton S, 2019, ANNUAL REVIEW OF FLUID MECHANICS</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>Berg S, 2019, NATURE METHODS</t>
+          <t>Brunton S, 2019, ANNUAL REVIEW OF FLUID MECHANICS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2973119841</t>
+          <t>https://openalex.org/W2975634117</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>10.1146/annurev-fluid-010719-060214</t>
+          <t>10.1038/s41592-019-0582-9</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Machine Learning for Fluid Mechanics</t>
+          <t>ilastik: interactive machine learning for (bio)image analysis</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7223,76 +7231,72 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>2604</v>
+        <v>3608</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>ANNUAL REVIEW OF FLUID MECHANICS</t>
+          <t>NATURE METHODS</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Annual Review of Fluid Mechanics</t>
+          <t>Nature Methods</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>['Steven L. Brunton', 'Bernd R. Noack', 'Petros Koumoutsakos']</t>
+          <t>['Stuart Berg', 'Dominik Kutra', 'Thorben Kroeger', 'Christoph Straehle', 'Bernhard X. Kausler', 'Carsten Haubold', 'Martin Schiegg', 'Janez Aleš', 'Thorsten Beier', 'Markus Rudy', 'Kemal Eren', 'Jaime I Cervantes', 'Buote Xu', 'Fynn Beuttenmueller', 'Adrian Wolny', 'Chong Zhang', 'Ullrich Koethe', 'Fred A. Hamprecht', 'Anna Kreshuk']</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>['Steven L. Brunton', 'Bernd R. Noack', 'Petros Koumoutsakos']</t>
+          <t>['Stuart Berg', 'Dominik Kutra', 'Thorben Kroeger', 'Christoph N. Straehle', 'Bernhard X. Kausler', 'Carsten Haubold', 'Martin Schiegg', 'Janez Ales', 'Thorsten Beier', 'Markus Rudy', 'Kemal Eren', 'Jaime I Cervantes', 'Buote Xu', 'Fynn Beuttenmueller', 'Adrian Wolny', 'Chong Zhang', 'Ullrich Koethe', 'Fred A. Hamprecht', 'Anna Kreshuk']</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>['Department of Mechanical Engineering, University of Washington, Seattle, Washington 98195, USA', 'Institut für Strömungsmechanik und Technische Akustik, Technische Universität Berlin, D-10634 Berlin, Germany', "LIMSI (Laboratoire d'Informatique pour la Mécanique et les Sciences de l'Ingénieur), CNRS UPR 3251, Université Paris-Saclay, F-91403 Orsay, France", 'Computational Science and Engineering Laboratory, ETH Zurich, CH-8092 Zurich, Switzerland;']</t>
+          <t>['HHMI Janelia Research Campus, Ashburn, Virginia, USA', 'European Molecular Biology Laboratory, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'European Molecular Biology Laboratory, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'HCI/IWR, Heidelberg University, Heidelberg, Germany. fred.hamprecht@iwr.uni-heidelberg.de', 'HCI/IWR, Heidelberg University, Heidelberg, Germany', 'European Molecular Biology Laboratory, Heidelberg, Germany. anna.kreshuk@embl.de', 'HCI/IWR, Heidelberg University, Heidelberg, Germany. anna.kreshuk@embl.de', 'European Molecular Biology Laboratory, Heidelberg, Germany']</t>
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>The field of fluid mechanics is rapidly advancing, driven by unprecedented volumes of data from experiments, field measurements, and large-scale simulations at multiple spatiotemporal scales. Machine learning (ML) offers a wealth of techniques to extract information from data that can be translated into knowledge about the underlying fluid mechanics. Moreover, ML algorithms can augment domain knowledge and automate tasks related to flow control and optimization. This article presents an overview of past history, current developments, and emerging opportunities of ML for fluid mechanics. We outline fundamental ML methodologies and discuss their uses for understanding, modeling, optimizing, and controlling fluid flows. The strengths and limitations of these methods are addressed from the perspective of scientific inquiry that considers data as an inherent part of modeling, experiments, and simulations. ML provides a powerful information-processing framework that can augment, and possibly even transform, current lines of fluid mechanics research and industrial applications.</t>
-        </is>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>['Fluid mechanics', 'Current (fluid)', 'Field (mathematics)', 'Perspective (graphical)', 'Fluid dynamics', 'Domain (mathematical analysis)']</t>
+          <t>['Computer science', 'Workflow', 'Artificial intelligence', 'Segmentation', 'Machine learning', 'Classifier (UML)', 'Image segmentation', 'Computer vision', 'Pattern recognition (psychology)', 'Database']</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>['US', 'FR', 'DE', 'CH']</t>
+          <t>['US', 'DE']</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>['Hochreiter S, 1997, NEURAL COMPUTATION', 'Rumelhart D, 1986, NATURE', 'Rosenblatt F, 1958, PSYCHOLOGICAL REVIEW', 'Germano M, 1991, PHYSICS OF FLUIDS A FLUID DYNAMICS', 'Sirovich L, 1987, QUARTERLY OF APPLIED MATHEMATICS', 'Schmid P, 2010, JOURNAL OF FLUID MECHANICS', 'Dong C, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Schmidt M, 2009, SCIENCE', 'Freeman W, 2002, IEEE COMPUTER GRAPHICS AND APPLICATIONS', 'Willert C, 1991, EXPERIMENTS IN FLUIDS', 'Grossberg S, 1976, BIOLOGICAL CYBERNETICS', 'Barber D, 2012, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Grossberg S, 1988, NEURAL NETWORKS', 'Baldi P, 1989, NEURAL NETWORKS', 'Gardner E, 1988, JOURNAL OF PHYSICS A MATHEMATICAL AND GENERAL', 'Bellman R, 1952, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Tesauro G, 1992, MACHINE LEARNING', 'Schwefel H, 1977, BIRKHÄUSER BASEL EBOOKS', 'Fleming P, 2002, CONTROL ENGINEERING PRACTICE', 'Brunton S, 2015, APPLIED MECHANICS REVIEWS', 'Dissanayake G, 1994, COMMUNICATIONS IN NUMERICAL METHODS IN ENGINEERING', 'Barber R, 2015, THE ANNALS OF STATISTICS', 'Amsallem D, 2012, INTERNATIONAL JOURNAL FOR NUMERICAL METHODS IN ENGINEERING', 'Ouellette N, 2005, EXPERIMENTS IN FLUIDS', 'Bewley T, 2001, JOURNAL OF FLUID MECHANICS', 'Rokhlin V, 2009, SIAM JOURNAL ON MATRIX ANALYSIS AND APPLICATIONS', 'Milano M, 2002, JOURNAL OF COMPUTATIONAL PHYSICS', 'Ling J, 2015, PHYSICS OF FLUIDS', 'Hansen N, 2008, IEEE TRANSACTIONS ON EVOLUTIONARY COMPUTATION', 'Lee C, 1997, PHYSICS OF FLUIDS', 'Graves A, 2007, LECTURE NOTES IN COMPUTER SCIENCE', 'Kern S, 2004, NATURAL COMPUTING', 'González‐García R, 1998, COMPUTERS &amp; CHEMICAL ENGINEERING', 'Bright I, 2013, PHYSICS OF FLUIDS', 'Jambunathan K, 1996, INTERNATIONAL JOURNAL OF HEAT AND MASS TRANSFER', 'Rico-Martı́nez R, 1992, CHEMICAL ENGINEERING COMMUNICATIONS', 'Gazzola M, 2014, SIAM JOURNAL ON SCIENTIFIC COMPUTING', 'Faller W, 1996, PROGRESS IN AEROSPACE SCIENCES', 'Nair A, 2015, JOURNAL OF FLUID MECHANICS', 'Ostermeier A, 1994, LECTURE NOTES IN COMPUTER SCIENCE', 'Bishop C, 1993, NUCLEAR INSTRUMENTS AND METHODS IN PHYSICS RESEARCH SECTION A ACCELERATORS SPECTROMETERS DETECTORS AND ASSOCIATED EQUIPMENT', 'Giannakoglou K, 2006, COMPUTER METHODS IN APPLIED MECHANICS AND ENGINEERING', 'Dracopoulos D, 1997, PERSPECTIVES IN NEURAL COMPUTING', 'Labonté G, 1999, EXPERIMENTS IN FLUIDS', 'Liang D, 2003, EXPERIMENTS IN FLUIDS', 'Grant I, 1995, EXPERIMENTS IN FLUIDS', 'Bourguignon J, 2014, PHYSICS OF FLUIDS', 'Hamdaouı M, 2010, JOURNAL OF AIRCRAFT', 'Pelikán M, 2004, LECTURE NOTES IN COMPUTER SCIENCE', 'Phan M, 1995, SERIES ON STABILITY, VIBRATION AND CONTROL OF SYSTEMS - SERIES B', 'Mnih V, 2015, NATURE', 'Hornik K, 1989, NEURAL NETWORKS', 'Hopfield J, 1982, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Silver D, 2016, NATURE', 'Wright J, 2009, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Yang J, 2010, IEEE TRANSACTIONS ON IMAGE PROCESSING', 'Brunton S, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Halko N, 2011, SIAM REVIEW', 'Adrian R, 1991, ANNUAL REVIEW OF FLUID MECHANICS', 'Hansen N, 2003, EVOLUTIONARY COMPUTATION', 'Sirovich L, 1987, JOURNAL OF THE OPTICAL SOCIETY OF AMERICA A', 'Rowley C, 2009, JOURNAL OF FLUID MECHANICS', 'Lagaris I, 1998, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Richter S, 2016, LECTURE NOTES IN COMPUTER SCIENCE', 'Ling J, 2016, JOURNAL OF FLUID MECHANICS', 'Rudy S, 2017, SCIENCE ADVANCES', 'Meneveau C, 2000, ANNUAL REVIEW OF FLUID MECHANICS', 'Raissi M, 2017, JOURNAL OF COMPUTATIONAL PHYSICS', 'Mezić I, 2012, ANNUAL REVIEW OF FLUID MECHANICS', 'Rowley C, 2016, ANNUAL REVIEW OF FLUID MECHANICS', 'Meijering E, 2002, PROCEEDINGS OF THE IEEE', 'Parish E, 2015, JOURNAL OF COMPUTATIONAL PHYSICS', 'Wang J, 2017, PHYSICAL REVIEW FLUIDS', 'Manohar K, 2018, IEEE CONTROL SYSTEMS', 'Schaeffer H, 2017, PROCEEDINGS OF THE ROYAL SOCIETY A MATHEMATICAL PHYSICAL AND ENGINEERING SCIENCES', 'Li Q, 2017, CHAOS AN INTERDISCIPLINARY JOURNAL OF NONLINEAR SCIENCE', 'Wu X, 2008, JOURNAL OF FLUID MECHANICS', 'Ling J, 2016, JOURNAL OF COMPUTATIONAL PHYSICS', 'Loiseau J, 2018, JOURNAL OF FLUID MECHANICS', 'Williams M, 2015, JOURNAL OF COMPUTATIONAL DYNAMICS', 'Xiao H, 2016, JOURNAL OF COMPUTATIONAL PHYSICS', 'Kaiser E, 2014, JOURNAL OF FLUID MECHANICS', 'Perlman E, 2007, ', 'Colabrese S, 2017, PHYSICAL REVIEW LETTERS', 'Glaz B, 2010, AIAA JOURNAL', 'Pierret S, 1999, JOURNAL OF TURBOMACHINERY', 'Reddy G, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Gazzola M, 2012, JOURNAL OF FLUID MECHANICS', 'Büche D, 2002, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS PART C (APPLICATIONS AND REVIEWS)', 'Gazzola M, 2016, JOURNAL OF FLUID MECHANICS', 'Perdikaris P, 2016, SIAM JOURNAL ON SCIENTIFIC COMPUTING', 'Bai Z, 2014, AIAA JOURNAL', 'Bénard N, 2016, EXPERIMENTS IN FLUIDS', 'Nüske F, 2016, THE JOURNAL OF CHEMICAL PHYSICS', 'Semeraro O, 2017, PHYSICAL REVIEW FLUIDS', 'Rees W, 2015, JOURNAL OF FLUID MECHANICS', 'Guéniat F, 2016, THEORETICAL AND COMPUTATIONAL FLUID DYNAMICS', 'Tsiotras P, 2017, JOURNAL OF GUIDANCE CONTROL AND DYNAMICS', 'Teo C, 2002, ', 'Papadimitriou D, 2015, INTERNATIONAL JOURNAL FOR UNCERTAINTY QUANTIFICATION', 'Breiman L, 2001, MACHINE LEARNING', 'LeCun Y, 2015, NATURE', 'Hastie T, 2009, SPRINGER SERIES IN STATISTICS', 'Donoho D, 2006, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Raissi M, 2018, JOURNAL OF COMPUTATIONAL PHYSICS', 'Taira K, 2017, AIAA JOURNAL', 'Duraisamy K, 2018, ANNUAL REVIEW OF FLUID MECHANICS', 'Lusch B, 2018, NATURE COMMUNICATIONS', 'Pathak J, 2018, PHYSICAL REVIEW LETTERS', 'Kutz J, 2016, SOCIETY FOR INDUSTRIAL AND APPLIED MATHEMATICS EBOOKS', 'Brunton S, 2019, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Fukami K, 2019, JOURNAL OF FLUID MECHANICS', 'Rabault J, 2019, JOURNAL OF FLUID MECHANICS', 'Mardt A, 2017, NATURE COMMUNICATIONS', 'Cherkassky V, 2006, ', 'Verma S, 2018, ARXIV (CORNELL UNIVERSITY)', 'Wehmeyer C, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Vlachas P, 2018, PROCEEDINGS OF THE ROYAL SOCIETY A MATHEMATICAL PHYSICAL AND ENGINEERING SCIENCES', 'Maulik R, 2018, JOURNAL OF FLUID MECHANICS', 'Xie Y, 2018, ACM TRANSACTIONS ON GRAPHICS', 'Kim B, 2019, COMPUTER GRAPHICS FORUM', 'Wan Z, 2018, PLOS ONE', 'Skinner S, 2017, APPLIED SOFT COMPUTING', 'Reddy G, 2018, NATURE', 'Novati G, 2017, BIOINSPIRATION &amp; BIOMIMETICS', 'Lee Y, 2017, EXPERIMENTS IN FLUIDS', 'Colvert B, 2018, BIOINSPIRATION &amp; BIOMIMETICS', 'Novati G, 2019, PHYSICAL REVIEW FLUIDS', 'Colabrese S, 2018, PHYSICAL REVIEW FLUIDS', 'Meena M, 2018, PHYSICAL REVIEW. E', 'Alsalman M, 2018, BIOINSPIRATION &amp; BIOMIMETICS', 'Martin N, 2018, BIOINSPIRATION &amp; BIOMIMETICS', 'Hou W, 2019, AIAA SCITECH 2019 FORUM']</t>
+          <t>['Breiman L, 2001, MACHINE LEARNING', 'Schindelin J, 2012, NATURE METHODS', 'Carpenter A, 2006, GENOME BIOLOGY', 'Arganda‐Carreras I, 2017, BIOINFORMATICS', 'Loy C, 2012, ', 'Vilariño D, 2017, JOURNAL OF APPLIED REMOTE SENSING', 'Erickson B, 2017, RADIOGRAPHICS', 'Berthold M, 2008, STUDIES IN CLASSIFICATION, DATA ANALYSIS, AND KNOWLEDGE ORGANIZATION', 'Sommer C, 2011, ', 'Linkert M, 2010, THE JOURNAL OF CELL BIOLOGY', 'Neumann B, 2010, NATURE', 'Tarca A, 2007, PLOS COMPUTATIONAL BIOLOGY', 'Tu Z, 2009, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Stalling D, 2005, ELSEVIER EBOOKS', 'Belevich I, 2016, PLOS BIOLOGY', 'Nixon‐Abell J, 2016, SCIENCE', 'Korogod N, 2015, ELIFE', 'Ciliberti S, 2007, PLOS COMPUTATIONAL BIOLOGY', 'Streichan S, 2014, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Simpson R, 2014, ', 'Geurts P, 2009, MOLECULAR BIOSYSTEMS', 'Marée R, 2016, BIOINFORMATICS', 'Wolff C, 2018, ELIFE', 'Beier T, 2017, NATURE METHODS', 'Raote I, 2018, ELIFE', 'Andres B, 2011, ', 'Luengo I, 2017, JOURNAL OF STRUCTURAL BIOLOGY', 'Sommer C, 2017, MOLECULAR BIOLOGY OF THE CELL', 'Maco B, 2013, PLOS ONE', 'Schiegg M, 2013, ', 'Cassani C, 2016, PLOS BIOLOGY', 'Hughes A, 2018, NATURE METHODS', 'Hilsenbeck O, 2017, BIOINFORMATICS', 'González-Tendero A, 2016, EUROPEAN HEART JOURNAL - CARDIOVASCULAR IMAGING', 'Haubold C, 2016, ADVANCES IN ANATOMY, EMBRYOLOGY AND CELL BIOLOGY', 'Beier T, 2015, ', 'Jorstad A, 2018, FRONTIERS IN NEUROANATOMY', 'Straehle C, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Straehle C, 2012, ', 'Haubold C, 2016, LECTURE NOTES IN COMPUTER SCIENCE', 'Pedregosa F, 2012, ARXIV (CORNELL UNIVERSITY)', ', 2013, ', ', 2011, ']</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -7308,12 +7312,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>Brunton S, 2019, ANNUAL REVIEW OF FLUID MECHANICS</t>
+          <t>Berg S, 2019, NATURE METHODS</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>Brunton S, 2019, ANNUAL REVIEW OF FLUID MECHANICS</t>
+          <t>Berg S, 2019, NATURE METHODS</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7353,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>3133</v>
+        <v>3137</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -7438,22 +7442,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://openalex.org/W1541288193</t>
+          <t>https://openalex.org/W2937307539</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>10.1023/a:1022602019183</t>
+          <t>10.1038/s41573-019-0024-5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Genetic Algorithms and Machine Learning</t>
+          <t>Applications of machine learning in drug discovery and development</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7463,72 +7467,76 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>3031</v>
+        <v>2937</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>MACHINE LEARNING</t>
+          <t>NATURE REVIEWS DRUG DISCOVERY</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Nature Reviews Drug Discovery</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>['David E. Goldberg', 'John H. Holland']</t>
+          <t>['Jessica Vamathevan', 'Dominic A. Clark', 'Paul Czodrowski', 'Ian Dunham', 'Edgardo A. Ferrán', 'George Lee', 'Bin Li', 'Anant Madabhushi', 'Parantu K. Shah', 'Michaela Spitzer', 'Shanrong Zhao']</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>['David E. Goldberg', 'John H. Holland']</t>
+          <t>['Jessica Vamathevan', 'Dominic Clark', 'Paul Czodrowski', 'Ian Dunham', 'Edgardo Ferran', 'George Lee', 'Bin Li', 'Anant Madabhushi', 'Parantu Shah', 'Michaela Spitzer', 'Shanrong Zhao']</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>['University of Alabama, Tuscaloosa, USA', 'University of Alabama, Tuscaloosa. DGOLDBER@UA1VM.BITNET#TAB#', 'University of Michigan, Ann Arbor, USA', 'University of Michigan, Ann Arbor. JHH@UM.CC.UMICH.EDU#TAB#']</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
+          <t>['European Molecular Biology Laboratory, European Bioinformatics Institute, Cambridge, UK. jessicav@ebi.ac.uk', 'European Molecular Biology Laboratory, European Bioinformatics Institute, Cambridge, UK', 'European Molecular Biology Laboratory, European Bioinformatics Institute, Cambridge, UK', 'Technical University of Dortmund, Dortmund, Germany', 'Open Targets and European Molecular Biology Laboratory, European Bioinformatics Institute, Cambridge, UK', 'European Molecular Biology Laboratory, European Bioinformatics Institute, Cambridge, UK', 'Bristol-Myers Squibb, Princeton, NJ, USA', 'Takeda Pharmaceuticals International Co., Cambridge, MA, USA', 'Case Western Reserve University, Cleveland, OH, USA', 'Louis Stokes Cleveland Veterans Affair Medical Center, Cleveland, OH, USA', 'EMD Serono R&amp;D Institute, Billerica, MA, USA', 'Open Targets and European Molecular Biology Laboratory, European Bioinformatics Institute, Cambridge, UK', 'Pfizer Worldwide Research and Development, Cambridge, MA, USA']</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Jessica Vamathevan (corresponding author), European Molecular Biology Laboratory, European Bioinformatics Institute, Cambridge, UK. jessicav@ebi.ac.uk; European Molecular Biology Laboratory, European Bioinformatics Institute, Cambridge, UK</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>463</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>477</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>['Mathematics', 'Artificial intelligence', 'Computer science']</t>
+          <t>['Computer science', 'Machine learning', 'Interpretability', 'Drug discovery', 'Artificial intelligence', 'Pipeline (software)', 'Identification (biology)', 'Context (archaeology)', 'Data science', 'Field (mathematics)', 'Drug development', 'Process (computing)', 'Data mining', 'Drug', 'Bioinformatics', 'Medicine']</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>['US']</t>
+          <t>['GB', 'RU', 'DE', 'US']</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>[', 1989, CHOICE REVIEWS ONLINE', 'Holland J, 1992, THE MIT PRESS EBOOKS', 'Goldberg D, 1988, ', 'Foxman D, 1973, THE WESTERN POLITICAL QUARTERLY', 'Seel P, 2012, ', 'Edelman G, 1987, ', 'Holland J, 1986, THE MIT PRESS EBOOKS', 'Holland J, 1962, JOURNAL OF THE ACM', 'Grefenstette J, 2014, PSYCHOLOGY PRESS EBOOKS', ', 2013, PSYCHOLOGY PRESS EBOOKS', 'Fourman M, 1985, INTERNATIONAL CONFERENCE ON GENETIC ALGORITHMS', 'Grefenstette J, 1987, ', 'Davis L, 1987, INTERNATIONAL CONFERENCE ON GENETIC ALGORITHMS']</t>
+          <t>['Srivastava N, 2014, ', 'Hinton G, 2006, SCIENCE', 'Gaulton A, 2016, NUCLEIC ACIDS RESEARCH', 'Keiser M, 2007, NATURE BIOTECHNOLOGY', 'Iorio F, 2016, CELL', 'Nelson M, 2015, NATURE GENETICS', 'Angermueller C, 2016, MOLECULAR SYSTEMS BIOLOGY', 'Janowczyk A, 2016, JOURNAL OF PATHOLOGY INFORMATICS', 'Xiong H, 2014, SCIENCE', 'Sotillo E, 2015, CANCER DISCOVERY', 'Ma J, 2015, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Zhan F, 2006, BLOOD', 'Shaughnessy J, 2006, BLOOD', 'Thorn B, 2010, NATURE BIOTECHNOLOGY', 'Kim E, 2011, CANCER DISCOVERY', 'Community N, 2014, NATURE BIOTECHNOLOGY', 'Mohr D, 2017, ANNUAL REVIEW OF CLINICAL PSYCHOLOGY', 'Beck A, 2011, SCIENCE TRANSLATIONAL MEDICINE', 'Pierson E, 2015, GENOME BIOLOGY', 'Vaquero-Garcia J, 2016, ELIFE', 'Koscielny G, 2016, NUCLEIC ACIDS RESEARCH', 'Leung M, 2014, BIOINFORMATICS', 'Mulligan G, 2006, BLOOD', 'Decaux O, 2008, JOURNAL OF CLINICAL ONCOLOGY', 'Bakheet T, 2009, BIOINFORMATICS', 'Jiao Y, 2016, QUANTITATIVE BIOLOGY', 'Nayal M, 2006, PROTEINS STRUCTURE FUNCTION AND BIOINFORMATICS', 'Bravo Á, 2015, BMC BIOINFORMATICS', 'Jeon J, 2014, GENOME MEDICINE', 'Tan J, 2016, MSYSTEMS', 'Turkki R, 2016, JOURNAL OF PATHOLOGY INFORMATICS', 'Koscielny S, 2010, SCIENCE TRANSLATIONAL MEDICINE', 'Mani N, 2016, BREAST CANCER RESEARCH', 'Romo‐Bucheli D, 2016, SCIENTIFIC REPORTS', 'Riniker S, 2014, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Li Q, 2007, BMC BIOINFORMATICS', 'Costa P, 2010, BMC GENOMICS', 'Kandoi G, 2015, FRONTIERS IN PHYSIOLOGY', 'Lee G, 2016, EUROPEAN UROLOGY FOCUS', 'Zhan F, 2008, BLOOD', 'Kim J, 2017, SCIENTIFIC REPORTS', 'Ли Б, 2015, PLOS ONE', 'Czodrowski P, 2014, JOURNAL OF COMPUTER-AIDED MOLECULAR DESIGN', 'Bunte K, 2016, BIOINFORMATICS', 'Gütlein M, 2016, JOURNAL OF CHEMINFORMATICS', 'Kumar V, 2016, SCIENTIFIC REPORTS', 'Hejase H, 2015, CPT PHARMACOMETRICS &amp; SYSTEMS PHARMACOLOGY', 'Veltri R, 2000, JOURNAL OF CELLULAR BIOCHEMISTRY', 'Ramsundar B, 2015, ARXIV (CORNELL UNIVERSITY)', 'Unterthiner T, 2015, ARXIV (CORNELL UNIVERSITY)', 'Tsherniak A, 2017, CELL', 'Khera A, 2018, NATURE GENETICS', 'Wu Z, 2017, CHEMICAL SCIENCE', 'Coudray N, 2018, NATURE MEDICINE', 'Segler M, 2018, NATURE', 'Chen H, 2017, IEEE TRANSACTIONS ON MEDICAL IMAGING', 'Chen H, 2018, DRUG DISCOVERY TODAY', 'Wong C, 2017, BIOSTATISTICS', 'Olivecrona M, 2017, JOURNAL OF CHEMINFORMATICS', 'Saltz J, 2018, CELL REPORTS', 'Hinton G, 2018, JAMA', 'Bychkov D, 2018, SCIENTIFIC REPORTS', 'Kadurin A, 2017, MOLECULAR PHARMACEUTICS', 'Mayr A, 2018, CHEMICAL SCIENCE', 'Hutson M, 2018, SCIENCE', 'Rifaioğlu A, 2018, BRIEFINGS IN BIOINFORMATICS', 'Cruz-Roa Á, 2017, SCIENTIFIC REPORTS', 'Morgan P, 2018, NATURE REVIEWS DRUG DISCOVERY', 'Korbar B, 2017, JOURNAL OF PATHOLOGY INFORMATICS', 'Preuer K, 2018, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Lenselink E, 2017, JOURNAL OF CHEMINFORMATICS', 'Sharma H, 2017, COMPUTERIZED MEDICAL IMAGING AND GRAPHICS', 'Cohen O, 2018, MAGNETIC RESONANCE IN MEDICINE', 'Ramsundar B, 2017, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Corredor G, 2018, CLINICAL CANCER RESEARCH', 'Tasaki S, 2018, NATURE COMMUNICATIONS', 'Gkotsis G, 2017, SCIENTIFIC REPORTS', 'Mamoshina P, 2018, FRONTIERS IN GENETICS', 'Kraus V, 2018, NATURE REVIEWS RHEUMATOLOGY', 'Boyiadzis M, 2018, JOURNAL FOR IMMUNOTHERAPY OF CANCER', 'Godinez W, 2017, BIOINFORMATICS', 'Lu C, 2018, LABORATORY INVESTIGATION', 'McMillan E, 2018, CELL', 'Nirschl J, 2018, PLOS ONE', 'Ferrero E, 2017, JOURNAL OF TRANSLATIONAL MEDICINE', 'Olsen T, 2018, JOURNAL OF PATHOLOGY INFORMATICS', 'Huang C, 2017, PLOS ONE', 'Lu C, 2017, MODERN PATHOLOGY', 'Paré G, 2017, SCIENTIFIC REPORTS', 'Ament S, 2018, MOLECULAR SYSTEMS BIOLOGY', 'Rahman R, 2016, BIOINFORMATICS', 'Romo‐Bucheli D, 2017, CYTOMETRY PART A', 'Gool A, 2017, NATURE REVIEWS DRUG DISCOVERY', 'Rohacek A, 2017, DEVELOPMENTAL CELL', 'Odell S, 2017, CURRENT PLANT BIOLOGY', 'Wang Q, 2017, PLOS ONE', 'Casanova R, 2017, CANCER RESEARCH', 'Farimani A, 2018, BIOPHYSICAL JOURNAL', 'Giraldo N, 2017, CANCER RESEARCH', 'Rashid S, 2017, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'LeCun Y, 2015, NATURE', 'Esteva A, 2018, NATURE MEDICINE', 'Wang B, 2017, NATURE METHODS', 'Ding J, 2018, NATURE COMMUNICATIONS', 'Norgeot B, 2018, NATURE MEDICINE', 'Way G, 2017, ', 'Steele A, 2018, PLOS ONE', 'Wang D, 2018, GENOMICS PROTEOMICS &amp; BIOINFORMATICS', 'Smith J, 2018, ACS MEDICINAL CHEMISTRY LETTERS', 'Jha A, 2017, BIOINFORMATICS', 'Rashid S, 2019, BIOINFORMATICS', 'Finnegan A, 2017, PLOS COMPUTATIONAL BIOLOGY', 'Rouillard A, 2018, PLOS COMPUTATIONAL BIOLOGY', 'Korbar B, 2017, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -7544,34 +7552,34 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>Goldberg D, 1988, MACHINE LEARNING</t>
+          <t>Vamathevan J, 2019, NATURE REVIEWS DRUG DISCOVERY</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>Goldberg D, 1988, MACHINE LEARNING</t>
+          <t>Vamathevan J, 2019, NATURE REVIEWS DRUG DISCOVERY</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2937307539</t>
+          <t>https://openalex.org/W1541288193</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>10.1038/s41573-019-0024-5</t>
+          <t>10.1023/a:1022602019183</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Applications of machine learning in drug discovery and development</t>
+          <t>Genetic Algorithms and Machine Learning</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7581,76 +7589,72 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>2933</v>
+        <v>3031</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>NATURE REVIEWS DRUG DISCOVERY</t>
+          <t>MACHINE LEARNING</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Nature Reviews Drug Discovery</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>['Jessica Vamathevan', 'Dominic A. Clark', 'Paul Czodrowski', 'Ian Dunham', 'Edgardo A. Ferrán', 'George Lee', 'Bin Li', 'Anant Madabhushi', 'Parantu K. Shah', 'Michaela Spitzer', 'Shanrong Zhao']</t>
+          <t>['David E. Goldberg', 'John H. Holland']</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>['Jessica Vamathevan', 'Dominic Clark', 'Paul Czodrowski', 'Ian Dunham', 'Edgardo Ferran', 'George Lee', 'Bin Li', 'Anant Madabhushi', 'Parantu Shah', 'Michaela Spitzer', 'Shanrong Zhao']</t>
+          <t>['David E. Goldberg', 'John H. Holland']</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['European Molecular Biology Laboratory, European Bioinformatics Institute, Cambridge, UK. jessicav@ebi.ac.uk', 'European Molecular Biology Laboratory, European Bioinformatics Institute, Cambridge, UK', 'European Molecular Biology Laboratory, European Bioinformatics Institute, Cambridge, UK', 'Technical University of Dortmund, Dortmund, Germany', 'Open Targets and European Molecular Biology Laboratory, European Bioinformatics Institute, Cambridge, UK', 'European Molecular Biology Laboratory, European Bioinformatics Institute, Cambridge, UK', 'Bristol-Myers Squibb, Princeton, NJ, USA', 'Takeda Pharmaceuticals International Co., Cambridge, MA, USA', 'Case Western Reserve University, Cleveland, OH, USA', 'Louis Stokes Cleveland Veterans Affair Medical Center, Cleveland, OH, USA', 'EMD Serono R&amp;D Institute, Billerica, MA, USA', 'Open Targets and European Molecular Biology Laboratory, European Bioinformatics Institute, Cambridge, UK', 'Pfizer Worldwide Research and Development, Cambridge, MA, USA']</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>Jessica Vamathevan (corresponding author), European Molecular Biology Laboratory, European Bioinformatics Institute, Cambridge, UK. jessicav@ebi.ac.uk; European Molecular Biology Laboratory, European Bioinformatics Institute, Cambridge, UK</t>
-        </is>
-      </c>
+          <t>['University of Alabama, Tuscaloosa, USA', 'University of Alabama, Tuscaloosa. DGOLDBER@UA1VM.BITNET#TAB#', 'University of Michigan, Ann Arbor, USA', 'University of Michigan, Ann Arbor. JHH@UM.CC.UMICH.EDU#TAB#']</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>95</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>99</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>['Computer science', 'Machine learning', 'Interpretability', 'Drug discovery', 'Artificial intelligence', 'Pipeline (software)', 'Identification (biology)', 'Context (archaeology)', 'Data science', 'Field (mathematics)', 'Drug development', 'Process (computing)', 'Data mining', 'Drug', 'Bioinformatics', 'Medicine']</t>
+          <t>['Mathematics', 'Artificial intelligence', 'Computer science']</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>['GB', 'RU', 'DE', 'US']</t>
+          <t>['US']</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>['Srivastava N, 2014, ', 'Hinton G, 2006, SCIENCE', 'Gaulton A, 2016, NUCLEIC ACIDS RESEARCH', 'Keiser M, 2007, NATURE BIOTECHNOLOGY', 'Iorio F, 2016, CELL', 'Nelson M, 2015, NATURE GENETICS', 'Angermueller C, 2016, MOLECULAR SYSTEMS BIOLOGY', 'Janowczyk A, 2016, JOURNAL OF PATHOLOGY INFORMATICS', 'Xiong H, 2014, SCIENCE', 'Sotillo E, 2015, CANCER DISCOVERY', 'Ma J, 2015, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Zhan F, 2006, BLOOD', 'Shaughnessy J, 2006, BLOOD', 'Thorn B, 2010, NATURE BIOTECHNOLOGY', 'Kim E, 2011, CANCER DISCOVERY', 'Community N, 2014, NATURE BIOTECHNOLOGY', 'Mohr D, 2017, ANNUAL REVIEW OF CLINICAL PSYCHOLOGY', 'Beck A, 2011, SCIENCE TRANSLATIONAL MEDICINE', 'Pierson E, 2015, GENOME BIOLOGY', 'Vaquero-Garcia J, 2016, ELIFE', 'Koscielny G, 2016, NUCLEIC ACIDS RESEARCH', 'Leung M, 2014, BIOINFORMATICS', 'Mulligan G, 2006, BLOOD', 'Decaux O, 2008, JOURNAL OF CLINICAL ONCOLOGY', 'Bakheet T, 2009, BIOINFORMATICS', 'Jiao Y, 2016, QUANTITATIVE BIOLOGY', 'Nayal M, 2006, PROTEINS STRUCTURE FUNCTION AND BIOINFORMATICS', 'Bravo Á, 2015, BMC BIOINFORMATICS', 'Jeon J, 2014, GENOME MEDICINE', 'Tan J, 2016, MSYSTEMS', 'Turkki R, 2016, JOURNAL OF PATHOLOGY INFORMATICS', 'Koscielny S, 2010, SCIENCE TRANSLATIONAL MEDICINE', 'Mani N, 2016, BREAST CANCER RESEARCH', 'Romo‐Bucheli D, 2016, SCIENTIFIC REPORTS', 'Riniker S, 2014, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Li Q, 2007, BMC BIOINFORMATICS', 'Costa P, 2010, BMC GENOMICS', 'Kandoi G, 2015, FRONTIERS IN PHYSIOLOGY', 'Lee G, 2016, EUROPEAN UROLOGY FOCUS', 'Zhan F, 2008, BLOOD', 'Kim J, 2017, SCIENTIFIC REPORTS', 'Ли Б, 2015, PLOS ONE', 'Czodrowski P, 2014, JOURNAL OF COMPUTER-AIDED MOLECULAR DESIGN', 'Bunte K, 2016, BIOINFORMATICS', 'Gütlein M, 2016, JOURNAL OF CHEMINFORMATICS', 'Kumar V, 2016, SCIENTIFIC REPORTS', 'Hejase H, 2015, CPT PHARMACOMETRICS &amp; SYSTEMS PHARMACOLOGY', 'Veltri R, 2000, JOURNAL OF CELLULAR BIOCHEMISTRY', 'Ramsundar B, 2015, ARXIV (CORNELL UNIVERSITY)', 'Unterthiner T, 2015, ARXIV (CORNELL UNIVERSITY)', 'Tsherniak A, 2017, CELL', 'Khera A, 2018, NATURE GENETICS', 'Wu Z, 2017, CHEMICAL SCIENCE', 'Coudray N, 2018, NATURE MEDICINE', 'Segler M, 2018, NATURE', 'Chen H, 2017, IEEE TRANSACTIONS ON MEDICAL IMAGING', 'Chen H, 2018, DRUG DISCOVERY TODAY', 'Wong C, 2017, BIOSTATISTICS', 'Olivecrona M, 2017, JOURNAL OF CHEMINFORMATICS', 'Saltz J, 2018, CELL REPORTS', 'Hinton G, 2018, JAMA', 'Bychkov D, 2018, SCIENTIFIC REPORTS', 'Kadurin A, 2017, MOLECULAR PHARMACEUTICS', 'Mayr A, 2018, CHEMICAL SCIENCE', 'Hutson M, 2018, SCIENCE', 'Rifaioğlu A, 2018, BRIEFINGS IN BIOINFORMATICS', 'Cruz-Roa Á, 2017, SCIENTIFIC REPORTS', 'Morgan P, 2018, NATURE REVIEWS DRUG DISCOVERY', 'Korbar B, 2017, JOURNAL OF PATHOLOGY INFORMATICS', 'Preuer K, 2018, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Lenselink E, 2017, JOURNAL OF CHEMINFORMATICS', 'Sharma H, 2017, COMPUTERIZED MEDICAL IMAGING AND GRAPHICS', 'Cohen O, 2018, MAGNETIC RESONANCE IN MEDICINE', 'Ramsundar B, 2017, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Corredor G, 2018, CLINICAL CANCER RESEARCH', 'Tasaki S, 2018, NATURE COMMUNICATIONS', 'Gkotsis G, 2017, SCIENTIFIC REPORTS', 'Mamoshina P, 2018, FRONTIERS IN GENETICS', 'Kraus V, 2018, NATURE REVIEWS RHEUMATOLOGY', 'Boyiadzis M, 2018, JOURNAL FOR IMMUNOTHERAPY OF CANCER', 'Godinez W, 2017, BIOINFORMATICS', 'Lu C, 2018, LABORATORY INVESTIGATION', 'McMillan E, 2018, CELL', 'Nirschl J, 2018, PLOS ONE', 'Ferrero E, 2017, JOURNAL OF TRANSLATIONAL MEDICINE', 'Olsen T, 2018, JOURNAL OF PATHOLOGY INFORMATICS', 'Huang C, 2017, PLOS ONE', 'Lu C, 2017, MODERN PATHOLOGY', 'Paré G, 2017, SCIENTIFIC REPORTS', 'Ament S, 2018, MOLECULAR SYSTEMS BIOLOGY', 'Rahman R, 2016, BIOINFORMATICS', 'Romo‐Bucheli D, 2017, CYTOMETRY PART A', 'Gool A, 2017, NATURE REVIEWS DRUG DISCOVERY', 'Rohacek A, 2017, DEVELOPMENTAL CELL', 'Odell S, 2017, CURRENT PLANT BIOLOGY', 'Wang Q, 2017, PLOS ONE', 'Casanova R, 2017, CANCER RESEARCH', 'Farimani A, 2018, BIOPHYSICAL JOURNAL', 'Giraldo N, 2017, CANCER RESEARCH', 'Rashid S, 2017, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'LeCun Y, 2015, NATURE', 'Esteva A, 2018, NATURE MEDICINE', 'Wang B, 2017, NATURE METHODS', 'Ding J, 2018, NATURE COMMUNICATIONS', 'Norgeot B, 2018, NATURE MEDICINE', 'Steele A, 2018, PLOS ONE', 'Way G, 2017, ', 'Wang D, 2018, GENOMICS PROTEOMICS &amp; BIOINFORMATICS', 'Smith J, 2018, ACS MEDICINAL CHEMISTRY LETTERS', 'Jha A, 2017, BIOINFORMATICS', 'Rashid S, 2019, BIOINFORMATICS', 'Finnegan A, 2017, PLOS COMPUTATIONAL BIOLOGY', 'Rouillard A, 2018, PLOS COMPUTATIONAL BIOLOGY', 'Korbar B, 2017, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>[', 1989, CHOICE REVIEWS ONLINE', 'Holland J, 1992, THE MIT PRESS EBOOKS', 'Goldberg D, 1988, ', 'Foxman D, 1973, THE WESTERN POLITICAL QUARTERLY', 'Seel P, 2012, ', 'Edelman G, 1987, ', 'Holland J, 1986, THE MIT PRESS EBOOKS', 'Holland J, 1962, JOURNAL OF THE ACM', 'Grefenstette J, 2014, PSYCHOLOGY PRESS EBOOKS', ', 2013, PSYCHOLOGY PRESS EBOOKS', 'Fourman M, 1985, INTERNATIONAL CONFERENCE ON GENETIC ALGORITHMS', 'Grefenstette J, 1987, ', 'Davis L, 1987, INTERNATIONAL CONFERENCE ON GENETIC ALGORITHMS']</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -7666,12 +7670,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>Vamathevan J, 2019, NATURE REVIEWS DRUG DISCOVERY</t>
+          <t>Goldberg D, 1988, MACHINE LEARNING</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>Vamathevan J, 2019, NATURE REVIEWS DRUG DISCOVERY</t>
+          <t>Goldberg D, 1988, MACHINE LEARNING</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7711,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>3243</v>
+        <v>3244</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -7804,17 +7808,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2151591509</t>
+          <t>https://openalex.org/W2111547563</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10.3389/fninf.2014.00014</t>
+          <t>10.1016/j.csbj.2014.11.005</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Machine learning for neuroimaging with scikit-learn</t>
+          <t>Machine learning applications in cancer prognosis and prediction</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7829,76 +7833,76 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>2639</v>
+        <v>3293</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>FRONTIERS IN NEUROINFORMATICS</t>
+          <t>COMPUTATIONAL AND STRUCTURAL BIOTECHNOLOGY JOURNAL</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Frontiers in Neuroinformatics</t>
+          <t>Computational and Structural Biotechnology Journal</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>['Alexandre Abraham', 'Fabian Pedregosa', 'Michael Eickenberg', 'Philippe Gervais', 'Andreas Mueller', 'Jean Kossaifi', 'Alexandre Gramfort', 'Bertrand Thirion', 'Gaël Varoquaux']</t>
+          <t>['Κωνσταντίνα Κούρου', 'Themis P. Exarchos', 'Konstantinos Exarchos', 'Michalis V. Karamouzis', 'Dimitrios I. Fotiadis']</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>['Alexandre Abraham', 'Fabian Pedregosa', 'Michael Eickenberg', 'Philippe Gervais', 'Andreas Mueller', 'Jean Kossaifi', 'Alexandre Gramfort', 'Bertrand Thirion', 'Gaël Varoquaux']</t>
+          <t>['Konstantina Kourou', 'Themis P. Exarchos', 'Konstantinos P. Exarchos', 'Michalis V. Karamouzis', 'Dimitrios I. Fotiadis']</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>['Parietal Team, INRIA Saclay-Île-de-France Saclay, France ; Neurospin, I2 BM, DSV, CEA Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France, Saclay, France', 'Neurospin, I2 BM, DSV, CEA, Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France Saclay, France ; Neurospin, I2 BM, DSV, CEA Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France, Saclay, France', 'Neurospin, I2 BM, DSV, CEA, Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France Saclay, France ; Neurospin, I2 BM, DSV, CEA Gif-Sur-Yvette, France', 'Neurospin, I2 BM, DSV, CEA, Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France, Saclay, France', 'Parietal Team, INRIA Saclay-Île-de-France Saclay, France ; Neurospin, I2 BM, DSV, CEA Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France, Saclay, France', 'Neurospin, I2 BM, DSV, CEA, Gif-Sur-Yvette, France', 'Institute of Computer Science VI, University of Bonn Bonn, Germany', 'Institute of Computer Science VI, University of Bonn, Bonn, Germany', 'Department of Computing, Imperial College London London, UK', 'Department of Computing, Imperial College London, London, UK', 'Parietal Team, INRIA Saclay-Île-de-France Saclay, France ; Neurospin, I2 BM, DSV, CEA Gif-Sur-Yvette, France ; Institut Mines-Telecom, Telecom ParisTech, CNRS LTCI Paris, France', 'Parietal Team, INRIA Saclay-Île-de-France, Saclay, France', 'Neurospin, I2 BM, DSV, CEA, Gif-Sur-Yvette, France', 'Institut Mines-Telecom, Telecom ParisTech, CNRS LTCI, Paris, France', 'Parietal Team, INRIA Saclay-Île-de-France Saclay, France ; Neurospin, I2 BM, DSV, CEA Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France, Saclay, France', 'Neurospin, I2 BM, DSV, CEA, Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France Saclay, France ; Neurospin, I2 BM, DSV, CEA Gif-Sur-Yvette, France', 'Neurospin, I2 BM, DSV, CEA, Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France, Saclay, France']</t>
+          <t>['Unit of Medical Technology and Intelligent Information Systems, Dept. of Materials Science and Engineering, University of Ioannina, Ioannina, Greece', 'IMBB — FORTH, Dept. of Biomedical Research, Ioannina, Greece', 'Unit of Medical Technology and Intelligent Information Systems, Dept. of Materials Science and Engineering, University of Ioannina, Ioannina, Greece', 'Unit of Medical Technology and Intelligent Information Systems, Dept. of Materials Science and Engineering, University of Ioannina, Ioannina, Greece', 'Molecular Oncology Unit, Department of Biological Chemistry, Medical School, University of Athens, Athens, Greece', 'IMBB — FORTH, Dept. of Biomedical Research, Ioannina, Greece', 'Unit of Medical Technology and Intelligent Information Systems, Dept. of Materials Science and Engineering, University of Ioannina, Ioannina, Greece']</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Alexandre Abraham (corresponding author), Parietal Team, INRIA Saclay-Île-de-France Saclay, France ; Neurospin, I2 BM, DSV, CEA Gif-Sur-Yvette, France; Parietal Team, INRIA Saclay-Île-de-France, Saclay, France; Neurospin, I2 BM, DSV, CEA, Gif-Sur-Yvette, France</t>
+          <t>Dimitrios I. Fotiadis (corresponding author), IMBB — FORTH, Dept. of Biomedical Research, Ioannina, Greece; Unit of Medical Technology and Intelligent Information Systems, Dept. of Materials Science and Engineering, University of Ioannina, Ioannina, Greece</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Statistical machine learning methods are increasingly used for neuroimaging data analysis. Their main virtue is their ability to model high-dimensional datasets, e.g., multivariate analysis of activation images or resting-state time series. Supervised learning is typically used in decoding or encoding settings to relate brain images to behavioral or clinical observations, while unsupervised learning can uncover hidden structures in sets of images (e.g., resting state functional MRI) or find sub-populations in large cohorts. By considering different functional neuroimaging applications, we illustrate how scikit-learn, a Python machine learning library, can be used to perform some key analysis steps. Scikit-learn contains a very large set of statistical learning algorithms, both supervised and unsupervised, and its application to neuroimaging data provides a versatile tool to study the brain.</t>
+          <t>Cancer has been characterized as a heterogeneous disease consisting of many different subtypes. The early diagnosis and prognosis of a cancer type have become a necessity in cancer research, as it can facilitate the subsequent clinical management of patients. The importance of classifying cancer patients into high or low risk groups has led many research teams, from the biomedical and the bioinformatics field, to study the application of machine learning (ML) methods. Therefore, these techniques have been utilized as an aim to model the progression and treatment of cancerous conditions. In addition, the ability of ML tools to detect key features from complex datasets reveals their importance. A variety of these techniques, including Artificial Neural Networks (ANNs), Bayesian Networks (BNs), Support Vector Machines (SVMs) and Decision Trees (DTs) have been widely applied in cancer research for the development of predictive models, resulting in effective and accurate decision making. Even though it is evident that the use of ML methods can improve our understanding of cancer progression, an appropriate level of validation is needed in order for these methods to be considered in the everyday clinical practice. In this work, we present a review of recent ML approaches employed in the modeling of cancer progression. The predictive models discussed here are based on various supervised ML techniques as well as on different input features and data samples. Given the growing trend on the application of ML methods in cancer research, we present here the most recent publications that employ these techniques as an aim to model cancer risk or patient outcomes.</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>['Neuroimaging', 'Computer science', 'Artificial intelligence', 'Unsupervised learning', 'Machine learning', 'Python (programming language)', 'Functional neuroimaging', 'Pattern recognition (psychology)', 'Psychology', 'Neuroscience']</t>
+          <t>['Machine learning', 'Artificial intelligence', 'Computer science', 'Support vector machine', 'Cancer', 'Artificial neural network', 'Bayesian network', 'Clinical Practice', 'Variety (cybernetics)', 'Field (mathematics)', 'Predictive modelling', 'Medicine', 'Mathematics']</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>['FR', 'DE', 'GB']</t>
+          <t>['GR']</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>['Tibshirani R, 1996, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Hunter J, 2007, COMPUTING IN SCIENCE &amp; ENGINEERING', 'Hastie T, 2001, SPRINGER SERIES IN STATISTICS', 'Hall M, 2009, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Smith S, 2004, NEUROIMAGE', 'Biswal B, 1995, MAGNETIC RESONANCE IN MEDICINE', 'Efron B, 2004, THE ANNALS OF STATISTICS', 'Hyvärinen A, 2000, NEURAL NETWORKS', 'Aapo H, 2004, THE MIT PRESS EBOOKS', 'Smith S, 2009, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Haxby J, 2001, SCIENCE', 'Penny W, 2007, UCL DISCOVERY (UNIVERSITY COLLEGE LONDON)', 'Destrieux C, 2010, NEUROIMAGE', 'Calhoun V, 2001, HUMAN BRAIN MAPPING', 'Beckmann C, 2004, IEEE TRANSACTIONS ON MEDICAL IMAGING', 'Gorgolewski K, 2011, FRONTIERS IN NEUROINFORMATICS', 'Kriegeskorte N, 2006, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Craddock R, 2011, HUMAN BRAIN MAPPING', 'Turkeltaub P, 2002, NEUROIMAGE', 'Fagin R, 2004, THEORETICAL COMPUTER SCIENCE', 'Naselaris T, 2010, NEUROIMAGE', 'Laird A, 2005, HUMAN BRAIN MAPPING', 'Miyawaki Y, 2008, NEURON', 'Hanke M, 2009, NEUROINFORMATICS', 'Schrouff J, 2013, NEUROINFORMATICS', 'Calı̀ A, 2012, JOURNAL OF WEB SEMANTICS', 'Poldrack R, 2011, FRONTIERS IN NEUROINFORMATICS', 'Poldrack R, 2015, ANNUAL REVIEW OF PSYCHOLOGY', 'Kiviniemi V, 2003, NEUROIMAGE', 'Baget J, 2011, ARTIFICIAL INTELLIGENCE', 'Hanson S, 2004, NEUROIMAGE', 'Beeri C, 1981, LECTURE NOTES IN COMPUTER SCIENCE', 'Sören S, 2010, MAX PLANCK INSTITUTE FOR PLASMA PHYSICS', 'O’Toole A, 2007, JOURNAL OF COGNITIVE NEUROSCIENCE', 'Varoquaux G, 2013, NEUROIMAGE', 'Calı̀ A, 2012, ARTIFICIAL INTELLIGENCE', 'Laird A, 2011, BMC RESEARCH NOTES', 'Varoquaux G, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Thirion B, 2005, HUMAN BRAIN MAPPING', 'Varoquaux G, 2010, NEUROIMAGE', 'Dalvi N, 2012, JOURNAL OF THE ACM', 'Michel V, 2011, PATTERN RECOGNITION', 'Vennekens J, 2009, THEORY AND PRACTICE OF LOGIC PROGRAMMING', 'Gottlob G, 2014, ACM TRANSACTIONS ON DATABASE SYSTEMS', 'Hanson S, 2007, NEURAL COMPUTATION', 'Millman K, 2007, COMPUTING IN SCIENCE &amp; ENGINEERING', 'Gottlob G, 2013, ANNALS OF MATHEMATICS AND ARTIFICIAL INTELLIGENCE', 'Destrieux C, 2009, NEUROIMAGE', 'Vlasselaer J, 2014, LIRIAS (KU LEUVEN)', 'Pedregosa F, 2012, ARXIV (CORNELL UNIVERSITY)', 'Walt S, 2011, COMPUTING IN SCIENCE &amp; ENGINEERING', 'Fischl B, 2003, CEREBRAL CORTEX', 'Mesulam M, 1998, BRAIN', 'Abraham A, 2014, FRONTIERS IN NEUROINFORMATICS', 'Eickhoff S, 2009, HUMAN BRAIN MAPPING', ', 1995, CHOICE REVIEWS ONLINE', 'Pereira F, 2008, NEUROIMAGE', 'Nieuwenhuys R, 2012, PROGRESS IN BRAIN RESEARCH', 'Mur M, 2009, SOCIAL COGNITIVE AND AFFECTIVE NEUROSCIENCE', 'Lieberman M, 2015, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Dantsin E, 2002, ', 'Samartsidis P, 2017, STATISTICAL SCIENCE', 'Jha A, 2012, PROCEEDINGS OF THE VLDB ENDOWMENT', 'Ceylan İ, 2021, ARTIFICIAL INTELLIGENCE', 'Riguzzi F, 2007, MACHINE LEARNING', 'Senellart P, 2017, HAL (LE CENTRE POUR LA COMMUNICATION SCIENTIFIQUE DIRECTE)']</t>
+          <t>['Hanahan D, 2011, CELL', 'Witten I, 2011, ELSEVIER EBOOKS', 'Nasrabadi N, 2007, JOURNAL OF ELECTRONIC IMAGING', 'Kohavi R, 1997, ARTIFICIAL INTELLIGENCE', ', 2008, ', 'Paik S, 2004, NEW ENGLAND JOURNAL OF MEDICINE', 'Kononenko I, 2001, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Delen D, 2004, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Michiels S, 2005, THE LANCET', 'Cruz J, 2007, PUBMED', 'Akay M, 2008, EXPERT SYSTEMS WITH APPLICATIONS', 'Ein‐Dor L, 2006, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Bach P, 2003, JNCI JOURNAL OF THE NATIONAL CANCER INSTITUTE', 'Dupuy A, 2007, JNCI JOURNAL OF THE NATIONAL CANCER INSTITUTE', 'Zen K, 2010, MEDICINAL RESEARCH REVIEWS', 'Heneghan H, 2010, CURRENT OPINION IN PHARMACOLOGY', 'Listgarten J, 2004, CLINICAL CANCER RESEARCH', 'Kim W, 2012, JOURNAL OF BREAST CANCER', 'Chang S, 2013, BMC BIOINFORMATICS', 'Papadopoulos A, 2004, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Chen Y, 2014, COMPUTERS IN BIOLOGY AND MEDICINE', 'Tseng C, 2013, NEURAL COMPUTING AND APPLICATIONS', 'Ayer T, 2010, CANCER', 'Park K, 2013, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Papadopoulos A, 2008, COMPUTERS IN BIOLOGY AND MEDICINE', 'Maclin P, 1991, JOURNAL OF MEDICAL SYSTEMS', 'Koscielny S, 2010, SCIENCE TRANSLATIONAL MEDICINE', 'Exarchos K, 2011, IEEE TRANSACTIONS ON INFORMATION TECHNOLOGY IN BIOMEDICINE', 'Kim J, 2013, JOURNAL OF THE AMERICAN MEDICAL INFORMATICS ASSOCIATION', 'Domchek S, 2003, JOURNAL OF CLINICAL ONCOLOGY', 'Xu X, 2012, ', 'Hall M, 1999, RESEARCH COMMONS (UNIVERSITY OF WAIKATO)', 'Fortunato O, 2014, MOLECULES', 'Cicchetti D, 1992, CLINICAL CHEMISTRY', 'Waddell M, 2005, ', 'Gilmore S, 2010, EXPERIMENTAL DERMATOLOGY', 'Park C, 2014, PLOS ONE', 'Cochran A, 1997, PIGMENT CELL RESEARCH', 'Ren X, 2012, NUCLEIC ACIDS RESEARCH', 'Rosado P, 2013, EXPERT SYSTEMS WITH APPLICATIONS', 'Drier Y, 2011, PLOS ONE', 'Wang Y, 2012, BMC SYSTEMS BIOLOGY', 'Fielding L, 1992, CANCER', 'Exarchos K, 2012, BMC MEDICAL INFORMATICS AND DECISION MAKING', 'Stojadinovic A, 2011, THE AMERICAN SURGEON', 'Ren X, 2013, NUCLEIC ACIDS RESEARCH', '́n F, 2004, EUROPEAN JOURNAL OF CANCER PREVENTION', 'Bochare A, 2014, INTERNATIONAL JOURNAL OF MEDICAL ENGINEERING AND INFORMATICS', 'Bian X, 2009, NATURE PRECEDINGS', 'Parthaláin N, 2010, LECTURE NOTES IN COMPUTER SCIENCE', 'Parker J, 2009, JOURNAL OF CLINICAL ONCOLOGY', 'Platt J, 1999, EXPLORE BRISTOL RESEARCH', 'Barrett T, 2006, NUCLEIC ACIDS RESEARCH', 'Estévez P, 2009, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Cruz J, 2006, CANCER INFORMATICS', ', 2007, APRESS EBOOKS', 'Ein‐Dor L, 2004, BIOINFORMATICS', 'Cuzick J, 2011, JOURNAL OF CLINICAL ONCOLOGY', 'Gevaert O, 2006, BIOINFORMATICS', 'LG A, 2013, JOURNAL OF HEALTH &amp; MEDICAL INFORMATICS', 'Bottaci L, 1997, THE LANCET', 'Sun Y, 2006, BIOINFORMATICS', 'Polley M, 2013, JNCI JOURNAL OF THE NATIONAL CANCER INSTITUTE', 'Madhavan D, 2013, FRONTIERS IN GENETICS', 'Bilal E, 2013, PLOS COMPUTATIONAL BIOLOGY', 'Simes R, 1985, JOURNAL OF CHRONIC DISEASES', 'Niu Y, 2009, BIOINFORMATICS', 'Urbanowicz R, 2013, JOURNAL OF THE AMERICAN MEDICAL INFORMATICS ASSOCIATION', 'Chuang L, 2011, ', 'Niknejad A, 2013, ', 'Agah A, 2013, ', 'Bian X, 2009, NATURE PRECEDINGS']</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -7914,29 +7918,29 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>Abraham A, 2014, FRONTIERS IN NEUROINFORMATICS</t>
+          <t>Κούρου Κ, 2014, COMPUTATIONAL AND STRUCTURAL BIOTECHNOLOGY JOURNAL</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>Abraham A, 2014, FRONTIERS IN NEUROINFORMATICS</t>
+          <t>Κούρου Κ, 2014, COMPUTATIONAL AND STRUCTURAL BIOTECHNOLOGY JOURNAL</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2111547563</t>
+          <t>https://openalex.org/W2151591509</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>10.1016/j.csbj.2014.11.005</t>
+          <t>10.3389/fninf.2014.00014</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Machine learning applications in cancer prognosis and prediction</t>
+          <t>Machine learning for neuroimaging with scikit-learn</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7951,76 +7955,76 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>3292</v>
+        <v>2640</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>COMPUTATIONAL AND STRUCTURAL BIOTECHNOLOGY JOURNAL</t>
+          <t>FRONTIERS IN NEUROINFORMATICS</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Computational and Structural Biotechnology Journal</t>
+          <t>Frontiers in Neuroinformatics</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>['Κωνσταντίνα Κούρου', 'Themis P. Exarchos', 'Konstantinos Exarchos', 'Michalis V. Karamouzis', 'Dimitrios I. Fotiadis']</t>
+          <t>['Alexandre Abraham', 'Fabian Pedregosa', 'Michael Eickenberg', 'Philippe Gervais', 'Andreas Mueller', 'Jean Kossaifi', 'Alexandre Gramfort', 'Bertrand Thirion', 'Gaël Varoquaux']</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>['Konstantina Kourou', 'Themis P. Exarchos', 'Konstantinos P. Exarchos', 'Michalis V. Karamouzis', 'Dimitrios I. Fotiadis']</t>
+          <t>['Alexandre Abraham', 'Fabian Pedregosa', 'Michael Eickenberg', 'Philippe Gervais', 'Andreas Mueller', 'Jean Kossaifi', 'Alexandre Gramfort', 'Bertrand Thirion', 'Gaël Varoquaux']</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>['Unit of Medical Technology and Intelligent Information Systems, Dept. of Materials Science and Engineering, University of Ioannina, Ioannina, Greece', 'IMBB — FORTH, Dept. of Biomedical Research, Ioannina, Greece', 'Unit of Medical Technology and Intelligent Information Systems, Dept. of Materials Science and Engineering, University of Ioannina, Ioannina, Greece', 'Unit of Medical Technology and Intelligent Information Systems, Dept. of Materials Science and Engineering, University of Ioannina, Ioannina, Greece', 'Molecular Oncology Unit, Department of Biological Chemistry, Medical School, University of Athens, Athens, Greece', 'IMBB — FORTH, Dept. of Biomedical Research, Ioannina, Greece', 'Unit of Medical Technology and Intelligent Information Systems, Dept. of Materials Science and Engineering, University of Ioannina, Ioannina, Greece']</t>
+          <t>['Parietal Team, INRIA Saclay-Île-de-France Saclay, France ; Neurospin, I2 BM, DSV, CEA Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France, Saclay, France', 'Neurospin, I2 BM, DSV, CEA, Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France Saclay, France ; Neurospin, I2 BM, DSV, CEA Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France, Saclay, France', 'Neurospin, I2 BM, DSV, CEA, Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France Saclay, France ; Neurospin, I2 BM, DSV, CEA Gif-Sur-Yvette, France', 'Neurospin, I2 BM, DSV, CEA, Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France, Saclay, France', 'Parietal Team, INRIA Saclay-Île-de-France Saclay, France ; Neurospin, I2 BM, DSV, CEA Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France, Saclay, France', 'Neurospin, I2 BM, DSV, CEA, Gif-Sur-Yvette, France', 'Institute of Computer Science VI, University of Bonn Bonn, Germany', 'Institute of Computer Science VI, University of Bonn, Bonn, Germany', 'Department of Computing, Imperial College London London, UK', 'Department of Computing, Imperial College London, London, UK', 'Parietal Team, INRIA Saclay-Île-de-France Saclay, France ; Neurospin, I2 BM, DSV, CEA Gif-Sur-Yvette, France ; Institut Mines-Telecom, Telecom ParisTech, CNRS LTCI Paris, France', 'Parietal Team, INRIA Saclay-Île-de-France, Saclay, France', 'Neurospin, I2 BM, DSV, CEA, Gif-Sur-Yvette, France', 'Institut Mines-Telecom, Telecom ParisTech, CNRS LTCI, Paris, France', 'Parietal Team, INRIA Saclay-Île-de-France Saclay, France ; Neurospin, I2 BM, DSV, CEA Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France, Saclay, France', 'Neurospin, I2 BM, DSV, CEA, Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France Saclay, France ; Neurospin, I2 BM, DSV, CEA Gif-Sur-Yvette, France', 'Neurospin, I2 BM, DSV, CEA, Gif-Sur-Yvette, France', 'Parietal Team, INRIA Saclay-Île-de-France, Saclay, France']</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Dimitrios I. Fotiadis (corresponding author), IMBB — FORTH, Dept. of Biomedical Research, Ioannina, Greece; Unit of Medical Technology and Intelligent Information Systems, Dept. of Materials Science and Engineering, University of Ioannina, Ioannina, Greece</t>
+          <t>Alexandre Abraham (corresponding author), Parietal Team, INRIA Saclay-Île-de-France Saclay, France ; Neurospin, I2 BM, DSV, CEA Gif-Sur-Yvette, France; Parietal Team, INRIA Saclay-Île-de-France, Saclay, France; Neurospin, I2 BM, DSV, CEA, Gif-Sur-Yvette, France</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Cancer has been characterized as a heterogeneous disease consisting of many different subtypes. The early diagnosis and prognosis of a cancer type have become a necessity in cancer research, as it can facilitate the subsequent clinical management of patients. The importance of classifying cancer patients into high or low risk groups has led many research teams, from the biomedical and the bioinformatics field, to study the application of machine learning (ML) methods. Therefore, these techniques have been utilized as an aim to model the progression and treatment of cancerous conditions. In addition, the ability of ML tools to detect key features from complex datasets reveals their importance. A variety of these techniques, including Artificial Neural Networks (ANNs), Bayesian Networks (BNs), Support Vector Machines (SVMs) and Decision Trees (DTs) have been widely applied in cancer research for the development of predictive models, resulting in effective and accurate decision making. Even though it is evident that the use of ML methods can improve our understanding of cancer progression, an appropriate level of validation is needed in order for these methods to be considered in the everyday clinical practice. In this work, we present a review of recent ML approaches employed in the modeling of cancer progression. The predictive models discussed here are based on various supervised ML techniques as well as on different input features and data samples. Given the growing trend on the application of ML methods in cancer research, we present here the most recent publications that employ these techniques as an aim to model cancer risk or patient outcomes.</t>
+          <t>Statistical machine learning methods are increasingly used for neuroimaging data analysis. Their main virtue is their ability to model high-dimensional datasets, e.g., multivariate analysis of activation images or resting-state time series. Supervised learning is typically used in decoding or encoding settings to relate brain images to behavioral or clinical observations, while unsupervised learning can uncover hidden structures in sets of images (e.g., resting state functional MRI) or find sub-populations in large cohorts. By considering different functional neuroimaging applications, we illustrate how scikit-learn, a Python machine learning library, can be used to perform some key analysis steps. Scikit-learn contains a very large set of statistical learning algorithms, both supervised and unsupervised, and its application to neuroimaging data provides a versatile tool to study the brain.</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>['Machine learning', 'Artificial intelligence', 'Computer science', 'Support vector machine', 'Cancer', 'Artificial neural network', 'Bayesian network', 'Clinical Practice', 'Variety (cybernetics)', 'Field (mathematics)', 'Predictive modelling', 'Medicine', 'Mathematics']</t>
+          <t>['Neuroimaging', 'Computer science', 'Artificial intelligence', 'Unsupervised learning', 'Machine learning', 'Python (programming language)', 'Functional neuroimaging', 'Pattern recognition (psychology)', 'Psychology', 'Neuroscience']</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>['GR']</t>
+          <t>['FR', 'DE', 'GB']</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>['Hanahan D, 2011, CELL', 'Witten I, 2011, ELSEVIER EBOOKS', 'Nasrabadi N, 2007, JOURNAL OF ELECTRONIC IMAGING', 'Kohavi R, 1997, ARTIFICIAL INTELLIGENCE', ', 2008, ', 'Paik S, 2004, NEW ENGLAND JOURNAL OF MEDICINE', 'Kononenko I, 2001, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Delen D, 2004, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Michiels S, 2005, THE LANCET', 'Cruz J, 2007, PUBMED', 'Akay M, 2008, EXPERT SYSTEMS WITH APPLICATIONS', 'Ein‐Dor L, 2006, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Bach P, 2003, JNCI JOURNAL OF THE NATIONAL CANCER INSTITUTE', 'Dupuy A, 2007, JNCI JOURNAL OF THE NATIONAL CANCER INSTITUTE', 'Zen K, 2010, MEDICINAL RESEARCH REVIEWS', 'Heneghan H, 2010, CURRENT OPINION IN PHARMACOLOGY', 'Listgarten J, 2004, CLINICAL CANCER RESEARCH', 'Kim W, 2012, JOURNAL OF BREAST CANCER', 'Chang S, 2013, BMC BIOINFORMATICS', 'Papadopoulos A, 2004, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Chen Y, 2014, COMPUTERS IN BIOLOGY AND MEDICINE', 'Tseng C, 2013, NEURAL COMPUTING AND APPLICATIONS', 'Ayer T, 2010, CANCER', 'Park K, 2013, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Papadopoulos A, 2008, COMPUTERS IN BIOLOGY AND MEDICINE', 'Maclin P, 1991, JOURNAL OF MEDICAL SYSTEMS', 'Koscielny S, 2010, SCIENCE TRANSLATIONAL MEDICINE', 'Exarchos K, 2011, IEEE TRANSACTIONS ON INFORMATION TECHNOLOGY IN BIOMEDICINE', 'Kim J, 2013, JOURNAL OF THE AMERICAN MEDICAL INFORMATICS ASSOCIATION', 'Domchek S, 2003, JOURNAL OF CLINICAL ONCOLOGY', 'Xu X, 2012, ', 'Hall M, 1999, RESEARCH COMMONS (UNIVERSITY OF WAIKATO)', 'Fortunato O, 2014, MOLECULES', 'Cicchetti D, 1992, CLINICAL CHEMISTRY', 'Waddell M, 2005, ', 'Gilmore S, 2010, EXPERIMENTAL DERMATOLOGY', 'Park C, 2014, PLOS ONE', 'Cochran A, 1997, PIGMENT CELL RESEARCH', 'Ren X, 2012, NUCLEIC ACIDS RESEARCH', 'Rosado P, 2013, EXPERT SYSTEMS WITH APPLICATIONS', 'Drier Y, 2011, PLOS ONE', 'Wang Y, 2012, BMC SYSTEMS BIOLOGY', 'Fielding L, 1992, CANCER', 'Exarchos K, 2012, BMC MEDICAL INFORMATICS AND DECISION MAKING', 'Stojadinovic A, 2011, THE AMERICAN SURGEON', 'Ren X, 2013, NUCLEIC ACIDS RESEARCH', '́n F, 2004, EUROPEAN JOURNAL OF CANCER PREVENTION', 'Bochare A, 2014, INTERNATIONAL JOURNAL OF MEDICAL ENGINEERING AND INFORMATICS', 'Bian X, 2009, NATURE PRECEDINGS', 'Parthaláin N, 2010, LECTURE NOTES IN COMPUTER SCIENCE', 'Parker J, 2009, JOURNAL OF CLINICAL ONCOLOGY', 'Platt J, 1999, EXPLORE BRISTOL RESEARCH', 'Barrett T, 2006, NUCLEIC ACIDS RESEARCH', 'Estévez P, 2009, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Cruz J, 2006, CANCER INFORMATICS', ', 2007, APRESS EBOOKS', 'Ein‐Dor L, 2004, BIOINFORMATICS', 'Cuzick J, 2011, JOURNAL OF CLINICAL ONCOLOGY', 'Gevaert O, 2006, BIOINFORMATICS', 'LG A, 2013, JOURNAL OF HEALTH &amp; MEDICAL INFORMATICS', 'Bottaci L, 1997, THE LANCET', 'Sun Y, 2006, BIOINFORMATICS', 'Polley M, 2013, JNCI JOURNAL OF THE NATIONAL CANCER INSTITUTE', 'Madhavan D, 2013, FRONTIERS IN GENETICS', 'Bilal E, 2013, PLOS COMPUTATIONAL BIOLOGY', 'Simes R, 1985, JOURNAL OF CHRONIC DISEASES', 'Niu Y, 2009, BIOINFORMATICS', 'Urbanowicz R, 2013, JOURNAL OF THE AMERICAN MEDICAL INFORMATICS ASSOCIATION', 'Chuang L, 2011, ', 'Niknejad A, 2013, ', 'Agah A, 2013, ', 'Bian X, 2009, NATURE PRECEDINGS']</t>
+          <t>['Tibshirani R, 1996, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Hunter J, 2007, COMPUTING IN SCIENCE &amp; ENGINEERING', 'Hastie T, 2001, SPRINGER SERIES IN STATISTICS', 'Hall M, 2009, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Smith S, 2004, NEUROIMAGE', 'Biswal B, 1995, MAGNETIC RESONANCE IN MEDICINE', 'Efron B, 2004, THE ANNALS OF STATISTICS', 'Hyvärinen A, 2000, NEURAL NETWORKS', 'Aapo H, 2004, THE MIT PRESS EBOOKS', 'Smith S, 2009, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Haxby J, 2001, SCIENCE', 'Penny W, 2007, UCL DISCOVERY (UNIVERSITY COLLEGE LONDON)', 'Destrieux C, 2010, NEUROIMAGE', 'Calhoun V, 2001, HUMAN BRAIN MAPPING', 'Beckmann C, 2004, IEEE TRANSACTIONS ON MEDICAL IMAGING', 'Gorgolewski K, 2011, FRONTIERS IN NEUROINFORMATICS', 'Kriegeskorte N, 2006, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Craddock R, 2011, HUMAN BRAIN MAPPING', 'Turkeltaub P, 2002, NEUROIMAGE', 'Fagin R, 2004, THEORETICAL COMPUTER SCIENCE', 'Naselaris T, 2010, NEUROIMAGE', 'Laird A, 2005, HUMAN BRAIN MAPPING', 'Miyawaki Y, 2008, NEURON', 'Hanke M, 2009, NEUROINFORMATICS', 'Schrouff J, 2013, NEUROINFORMATICS', 'Calı̀ A, 2012, JOURNAL OF WEB SEMANTICS', 'Poldrack R, 2011, FRONTIERS IN NEUROINFORMATICS', 'Poldrack R, 2015, ANNUAL REVIEW OF PSYCHOLOGY', 'Kiviniemi V, 2003, NEUROIMAGE', 'Baget J, 2011, ARTIFICIAL INTELLIGENCE', 'Hanson S, 2004, NEUROIMAGE', 'Beeri C, 1981, LECTURE NOTES IN COMPUTER SCIENCE', 'Sören S, 2010, MAX PLANCK INSTITUTE FOR PLASMA PHYSICS', 'O’Toole A, 2007, JOURNAL OF COGNITIVE NEUROSCIENCE', 'Varoquaux G, 2013, NEUROIMAGE', 'Calı̀ A, 2012, ARTIFICIAL INTELLIGENCE', 'Laird A, 2011, BMC RESEARCH NOTES', 'Varoquaux G, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Thirion B, 2005, HUMAN BRAIN MAPPING', 'Varoquaux G, 2010, NEUROIMAGE', 'Dalvi N, 2012, JOURNAL OF THE ACM', 'Michel V, 2011, PATTERN RECOGNITION', 'Vennekens J, 2009, THEORY AND PRACTICE OF LOGIC PROGRAMMING', 'Gottlob G, 2014, ACM TRANSACTIONS ON DATABASE SYSTEMS', 'Hanson S, 2007, NEURAL COMPUTATION', 'Millman K, 2007, COMPUTING IN SCIENCE &amp; ENGINEERING', 'Gottlob G, 2013, ANNALS OF MATHEMATICS AND ARTIFICIAL INTELLIGENCE', 'Destrieux C, 2009, NEUROIMAGE', 'Vlasselaer J, 2014, LIRIAS (KU LEUVEN)', 'Pedregosa F, 2012, ARXIV (CORNELL UNIVERSITY)', 'Walt S, 2011, COMPUTING IN SCIENCE &amp; ENGINEERING', 'Fischl B, 2003, CEREBRAL CORTEX', 'Mesulam M, 1998, BRAIN', 'Abraham A, 2014, FRONTIERS IN NEUROINFORMATICS', 'Eickhoff S, 2009, HUMAN BRAIN MAPPING', ', 1995, CHOICE REVIEWS ONLINE', 'Pereira F, 2008, NEUROIMAGE', 'Nieuwenhuys R, 2012, PROGRESS IN BRAIN RESEARCH', 'Mur M, 2009, SOCIAL COGNITIVE AND AFFECTIVE NEUROSCIENCE', 'Lieberman M, 2015, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Dantsin E, 2002, ', 'Samartsidis P, 2017, STATISTICAL SCIENCE', 'Jha A, 2012, PROCEEDINGS OF THE VLDB ENDOWMENT', 'Ceylan İ, 2021, ARTIFICIAL INTELLIGENCE', 'Riguzzi F, 2007, MACHINE LEARNING', 'Senellart P, 2017, HAL (LE CENTRE POUR LA COMMUNICATION SCIENTIFIQUE DIRECTE)']</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -8036,12 +8040,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>Κούρου Κ, 2014, COMPUTATIONAL AND STRUCTURAL BIOTECHNOLOGY JOURNAL</t>
+          <t>Abraham A, 2014, FRONTIERS IN NEUROINFORMATICS</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>Κούρου Κ, 2014, COMPUTATIONAL AND STRUCTURAL BIOTECHNOLOGY JOURNAL</t>
+          <t>Abraham A, 2014, FRONTIERS IN NEUROINFORMATICS</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8081,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>13166</v>
+        <v>13171</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -8195,7 +8199,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -8222,7 +8226,11 @@
           <t>['Department of Mathematics, Statistics Group, University of Bristol, University Walk, Bristol, BS8 1TW, UK', 'Department of Mathematics, Statistics Group, University of Bristol, University Walk, UK', 'Department of Computer Science, University of British Columbia, 2366 Main Mall, Vancouver, BC, V6T 1Z4, Canada', 'Department of Computer Science,  University of British Columbia,  Vancouver, Canada', 'Department of Electrical and Electronic Engineering, University of Melbourne, Parkville, Victoria, 3052, Australia', '[Department of Electrical and Electronic Engineering, University of Melbourne, Parkville, Australia]', 'Departments of Computer Science and Statistics, University of California at Berkeley, 387 Soda Hall, Berkeley, CA, 94720-1776, USA', 'Departments of Computer Science and Statistics, University of California at Berkeley, Berkeley, USA']</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Michael I. Jordan (corresponding author), Departments of Computer Science and Statistics, University of California at Berkeley, 387 Soda Hall, Berkeley, CA, 94720-1776, USA; Departments of Computer Science and Statistics, University of California at Berkeley, Berkeley, USA</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
@@ -8256,7 +8264,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>['Page L, 1999, ', 'Doucet A, 2001, ', 'Baxter R, 1985, SERIES ON ADVANCES IN STATISTICAL MECHANICS', 'Kim H, 2000, TECHNOMETRICS', 'Meyn S, 1993, ', 'Neal R, 1996, LECTURE NOTES IN STATISTICS', 'Hochba D, 1997, ACM SIGACT NEWS', 'N. K, 1992, ELSEVIER EBOOKS', 'Ghahramani Z, 1997, MACHINE LEARNING', 'Neal R, 2011, ', 'Carlin B, 1995, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Besag J, 1995, STATISTICAL SCIENCE', 'Isard M, 1996, LECTURE NOTES IN COMPUTER SCIENCE', 'Gilks W, 1994, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES D (THE STATISTICIAN)', 'Jong P, 1995, BIOMETRIKA', 'Mengersen K, 1996, THE ANNALS OF STATISTICS', 'Bergman N, 1999, ', 'Jerrum M, 1996, ', "Doucet A, 1998, OPENGREY (INSTITUT DE L'INFORMATION SCIENTIFIQUE ET TECHNIQUE)", 'Fox D, 2001, ', 'Dension D, 1998, BIOMETRIKA', 'Tierney L, 1999, STATISTICS IN MEDICINE', 'McCulloch C, 1994, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Browne W, 2000, COMPUTATIONAL STATISTICS', 'Pasula H, 1999, ', 'Higdon D, 1998, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'MacEachern S, 1999, CANADIAN JOURNAL OF STATISTICS', 'Godsill S, 1998, ', 'Wakefield J, 1991, STATISTICS AND COMPUTING', 'Chenney S, 2000, ', 'Bielza C, 1999, MANAGEMENT SCIENCE', 'Ishwaran H, 1999, JOURNAL OF COMPUTATIONAL AND GRAPHICAL STATISTICS', 'Bar-Yossef Z, 2000, ', 'Andrieu C, 2003, ', 'Propp J, 1998, DIMACS SERIES IN DISCRETE MATHEMATICS AND THEORETICAL COMPUTER SCIENCE', 'Andrieu C, 2001, ', 'Fill J, 1997, ', 'Insua D, 1998, LECTURE NOTES IN STATISTICS', 'Morris R, 2002, ', 'Wilkinson D, 2002, STATISTICS AND COMPUTING', 'Salmond D, 2001, ', 'Pasula H, 2001, INTERNATIONAL JOINT CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Bui H, 2000, OWN YOUR POTENTIAL (DEAKIN)', 'Kanazawa K, 2013, ARXIV (CORNELL UNIVERSITY)', 'Ortiz L, 2013, ARXIV (CORNELL UNIVERSITY)', 'Casella G, 1999, ECOMMONS (CORNELL UNIVERSITY)', 'Ormoneit D, 2013, ARXIV (CORNELL UNIVERSITY)', 'Utsugi A, 2001, NEURAL PROCESSING LETTERS', 'Vermaak J, 1999, CAMBRIDGE UNIVERSITY ENGINEERING DEPARTMENT PUBLICATIONS DATABASE', 'Dempster A, 1977, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Kirkpatrick S, 1983, SCIENCE', 'Metropolis N, 1953, THE JOURNAL OF CHEMICAL PHYSICS', 'Geman S, 1984, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Gordon N, 1993, IEE PROCEEDINGS F RADAR AND SIGNAL PROCESSING', 'Gelfand A, 1990, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Metropolis N, 1949, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Green P, 1995, BIOMETRIKA', 'Baum L, 1970, THE ANNALS OF MATHEMATICAL STATISTICS', 'Duane S, 1987, PHYSICS LETTERS B', 'Albert J, 1993, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Swendsen R, 1987, PHYSICAL REVIEW LETTERS', 'Liu J, 2004, SPRINGER SERIES IN STATISTICS', 'Escobar M, 1995, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Carter C, 1994, BIOMETRIKA', 'Richardson S, 1997, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Geweke J, 1989, ECONOMETRICA', 'Hesterberg T, 2002, TECHNOMETRICS', 'Wei G, 1990, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Richardson S, 1997, ', 'Chen M, 2000, SPRINGER SERIES IN STATISTICS', 'Brooks S, 1998, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES D (THE STATISTICIAN)', 'Dyer M, 1991, JOURNAL OF THE ACM', 'Tu Z, 2002, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Casella G, 1996, BIOMETRIKA', 'Veach E, 1997, ', 'Bucher C, 1988, STRUCTURAL SAFETY', 'Roberts G, 1996, BIOMETRIKA', 'Pearl J, 1987, ARTIFICIAL INTELLIGENCE', 'Gilks W, 1998, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Green P, 2001, SCANDINAVIAN JOURNAL OF STATISTICS', 'Levine R, 2001, JOURNAL OF COMPUTATIONAL AND GRAPHICAL STATISTICS', 'Andrieu C, 1999, IEEE TRANSACTIONS ON SIGNAL PROCESSING', 'Thrun S, 1999, NEURAL INFORMATION PROCESSING SYSTEMS', 'Mykland P, 1995, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Ziegel E, 1999, TECHNOMETRICS', 'Fill J, 1998, THE ANNALS OF APPLIED PROBABILITY', 'Diaconis P, 1998, JOURNAL OF COMPUTER AND SYSTEM SCIENCES', 'Applegate D, 1991, ', 'Jensen C, 1995, INTERNATIONAL JOURNAL OF HUMAN-COMPUTER STUDIES', 'Celeux G, 1992, STOCHASTICS AND STOCHASTICS REPORTS', 'Haario H, 1991, ADVANCES IN APPLIED PROBABILITY', 'Gelfand A, 1994, JOURNAL OF COMPUTATIONAL AND GRAPHICAL STATISTICS', 'Barber D, 1996, ASTON PUBLICATIONS EXPLORER (ASTON UNIVERSITY)', 'Wood S, 1998, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Sherman R, 1999, ECONOMETRICS JOURNAL', 'Al-Qaq W, 1995, IEEE TRANSACTIONS ON COMMUNICATIONS', 'Newton M, 2000, BIOMETRICS', 'Jaumard B, 2006, ', 'Schuurmans D, 2013, ARXIV (CORNELL UNIVERSITY)', 'Hastings W, 1970, BIOMETRIKA', 'Gilks W, 1995, ', 'Moore M, 1983, PHYSICS BULLETIN', 'Doucet A, 2000, STATISTICS AND COMPUTING', 'Tanner M, 1987, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Tierney L, 1994, THE ANNALS OF STATISTICS', 'Rubinstein R, 2016, WILEY SERIES IN PROBABILITY AND STATISTICS', ', 1988, MATHEMATICS AND COMPUTERS IN SIMULATION', 'Pitt M, 1999, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Merwe R, 2000, ', 'Neal R, 2000, ARXIV (CORNELL UNIVERSITY)', 'Murphy K, 2001, ', 'Berners‐Lee T, 1994, COMMUNICATIONS OF THE ACM', 'Kalos M, 1986, ', 'Rota G, 1988, ADVANCES IN MATHEMATICS', 'Peskun P, 1973, BIOMETRIKA', 'Damlen P, 1999, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Escobar M, 1995, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Smith P, 1997, IEEE JOURNAL ON SELECTED AREAS IN COMMUNICATIONS', 'Freitas J, 2000, NEURAL COMPUTATION', 'Cheng J, 2000, ', 'Cheng J, 2000, JOURNAL OF ARTIFICIAL INTELLIGENCE RESEARCH', 'Troughton P, 2002, ', ', 1995, ', 'Neuwald A, 1997, NUCLEIC ACIDS RESEARCH', 'Beichl I, 2000, COMPUTING IN SCIENCE &amp; ENGINEERING', 'Andrieu C, 2001, NEURAL COMPUTATION', 'Tu Z, 2002, ', 'Freitas N, 2001, UNCERTAINTY IN ARTIFICIAL INTELLIGENCE', 'Peskun P, 1973, BIOMETRIKA', 'Müller P, 1998, NEURAL COMPUTATION', 'Holmes C, 1998, NEURAL COMPUTATION', 'Ghahramani Z, 1994, ', 'Remondo D, 2000, IEEE TRANSACTIONS ON COMMUNICATIONS', 'Andrieu C, 2002, THE MIT PRESS EBOOKS', 'Poupart P, 2017, ENCYCLOPEDIA OF MACHINE LEARNING AND DATA MINING', 'Mykland P, 1995, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Andrieu C, 2001, JOURNAL OF APPLIED PROBABILITY', 'Aldous D, 1998, DIMACS SERIES IN DISCRETE MATHEMATICS AND THEORETICAL COMPUTER SCIENCE', 'Kannan R, 2002, ', 'Andrieu C, 1999, OXFORD UNIVERSITY RESEARCH ARCHIVE (ORA) (UNIVERSITY OF OXFORD)', 'Clark E, 1999, ', 'Doucet A, 2013, ARXIV (CORNELL UNIVERSITY)', 'Andrieu C, 2013, ARXIV (CORNELL UNIVERSITY)', 'Forsyth D, 2003, ', 'Ridgeway G, 1999, RESEARCHWORKS AT THE UNIVERSITY OF WASHINGTON (UNIVERSITY OF WASHINGTON)', 'Ortiz L, 2013, ARXIV (CORNELL UNIVERSITY)', 'Rubinstein R, 1981, WILEY SERIES IN PROBABILITY AND STATISTICS', 'Laarhoven P, 1987, ', 'Robert C, 1999, SPRINGER TEXTS IN STATISTICS', 'Gasparini M, 1997, TECHNOMETRICS', 'Meyn S, 2009, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Gelfand A, 1990, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Hastings W, 1970, BIOMETRIKA', 'Wei G, 1990, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Pitt M, 1999, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Geman S, 1987, ELSEVIER EBOOKS', 'Tanner M, 1987, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Green P, 1995, BIOMETRIKA', 'Albert J, 1993, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Doucet A, 2005, ', 'Seila A, 1982, TECHNOMETRICS', 'Carter C, 1994, BIOMETRIKA', 'McLoughlin I, 2016, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'McCulloch C, 1994, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Gilks W, 1998, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Gelfand A, 1994, JOURNAL OF COMPUTATIONAL AND GRAPHICAL STATISTICS', 'Haario H, 1991, ADVANCES IN APPLIED PROBABILITY', 'Andrieu C, 2001, JOURNAL OF APPLIED PROBABILITY', 'Wood S, 1998, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Ghahramani Z, 1996, ', 'Moreau T, 2023, MEDICAL IMAGE ANALYSIS']</t>
+          <t>['Page L, 1999, ', 'Doucet A, 2001, ', 'Baxter R, 1985, SERIES ON ADVANCES IN STATISTICAL MECHANICS', 'Kim H, 2000, TECHNOMETRICS', 'Meyn S, 1993, ', 'Neal R, 1996, LECTURE NOTES IN STATISTICS', 'Hochba D, 1997, ACM SIGACT NEWS', 'N. K, 1992, ELSEVIER EBOOKS', 'Ghahramani Z, 1997, MACHINE LEARNING', 'Neal R, 2011, ', 'Carlin B, 1995, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Besag J, 1995, STATISTICAL SCIENCE', 'Isard M, 1996, LECTURE NOTES IN COMPUTER SCIENCE', 'Gilks W, 1994, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES D (THE STATISTICIAN)', 'Jong P, 1995, BIOMETRIKA', 'Mengersen K, 1996, THE ANNALS OF STATISTICS', 'Bergman N, 1999, ', 'Jerrum M, 1996, ', "Doucet A, 1998, OPENGREY (INSTITUT DE L'INFORMATION SCIENTIFIQUE ET TECHNIQUE)", 'Fox D, 2001, ', 'Dension D, 1998, BIOMETRIKA', 'Tierney L, 1999, STATISTICS IN MEDICINE', 'McCulloch C, 1994, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Browne W, 2000, COMPUTATIONAL STATISTICS', 'Pasula H, 1999, ', 'Higdon D, 1998, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'MacEachern S, 1999, CANADIAN JOURNAL OF STATISTICS', 'Godsill S, 1998, ', 'Wakefield J, 1991, STATISTICS AND COMPUTING', 'Chenney S, 2000, ', 'Bielza C, 1999, MANAGEMENT SCIENCE', 'Ishwaran H, 1999, JOURNAL OF COMPUTATIONAL AND GRAPHICAL STATISTICS', 'Bar-Yossef Z, 2000, ', 'Andrieu C, 2003, ', 'Propp J, 1998, DIMACS SERIES IN DISCRETE MATHEMATICS AND THEORETICAL COMPUTER SCIENCE', 'Andrieu C, 2001, ', 'Fill J, 1997, ', 'Insua D, 1998, LECTURE NOTES IN STATISTICS', 'Morris R, 2002, ', 'Wilkinson D, 2002, STATISTICS AND COMPUTING', 'Salmond D, 2001, ', 'Pasula H, 2001, INTERNATIONAL JOINT CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Bui H, 2000, OWN YOUR POTENTIAL (DEAKIN)', 'Kanazawa K, 2013, ARXIV (CORNELL UNIVERSITY)', 'Ortiz L, 2013, ARXIV (CORNELL UNIVERSITY)', 'Casella G, 1999, ECOMMONS (CORNELL UNIVERSITY)', 'Ormoneit D, 2013, ARXIV (CORNELL UNIVERSITY)', 'Utsugi A, 2001, NEURAL PROCESSING LETTERS', 'Vermaak J, 1999, CAMBRIDGE UNIVERSITY ENGINEERING DEPARTMENT PUBLICATIONS DATABASE', 'Dempster A, 1977, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Kirkpatrick S, 1983, SCIENCE', 'Metropolis N, 1953, THE JOURNAL OF CHEMICAL PHYSICS', 'Geman S, 1984, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Gordon N, 1993, IEE PROCEEDINGS F RADAR AND SIGNAL PROCESSING', 'Gelfand A, 1990, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Metropolis N, 1949, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Green P, 1995, BIOMETRIKA', 'Baum L, 1970, THE ANNALS OF MATHEMATICAL STATISTICS', 'Duane S, 1987, PHYSICS LETTERS B', 'Albert J, 1993, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Swendsen R, 1987, PHYSICAL REVIEW LETTERS', 'Liu J, 2004, SPRINGER SERIES IN STATISTICS', 'Escobar M, 1995, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Carter C, 1994, BIOMETRIKA', 'Richardson S, 1997, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Geweke J, 1989, ECONOMETRICA', 'Hesterberg T, 2002, TECHNOMETRICS', 'Wei G, 1990, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Richardson S, 1997, ', 'Chen M, 2000, SPRINGER SERIES IN STATISTICS', 'Brooks S, 1998, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES D (THE STATISTICIAN)', 'Dyer M, 1991, JOURNAL OF THE ACM', 'Tu Z, 2002, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Casella G, 1996, BIOMETRIKA', 'Veach E, 1997, ', 'Bucher C, 1988, STRUCTURAL SAFETY', 'Roberts G, 1996, BIOMETRIKA', 'Pearl J, 1987, ARTIFICIAL INTELLIGENCE', 'Gilks W, 1998, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Green P, 2001, SCANDINAVIAN JOURNAL OF STATISTICS', 'Levine R, 2001, JOURNAL OF COMPUTATIONAL AND GRAPHICAL STATISTICS', 'Andrieu C, 1999, IEEE TRANSACTIONS ON SIGNAL PROCESSING', 'Thrun S, 1999, NEURAL INFORMATION PROCESSING SYSTEMS', 'Mykland P, 1995, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Ziegel E, 1999, TECHNOMETRICS', 'Fill J, 1998, THE ANNALS OF APPLIED PROBABILITY', 'Diaconis P, 1998, JOURNAL OF COMPUTER AND SYSTEM SCIENCES', 'Applegate D, 1991, ', 'Jensen C, 1995, INTERNATIONAL JOURNAL OF HUMAN-COMPUTER STUDIES', 'Celeux G, 1992, STOCHASTICS AND STOCHASTICS REPORTS', 'Haario H, 1991, ADVANCES IN APPLIED PROBABILITY', 'Gelfand A, 1994, JOURNAL OF COMPUTATIONAL AND GRAPHICAL STATISTICS', 'Barber D, 1996, ASTON PUBLICATIONS EXPLORER (ASTON UNIVERSITY)', 'Wood S, 1998, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Sherman R, 1999, ECONOMETRICS JOURNAL', 'Al-Qaq W, 1995, IEEE TRANSACTIONS ON COMMUNICATIONS', 'Newton M, 2000, BIOMETRICS', 'Jaumard B, 2006, ', 'Schuurmans D, 2013, ARXIV (CORNELL UNIVERSITY)', 'Hastings W, 1970, BIOMETRIKA', 'Gilks W, 1995, ', 'Moore M, 1983, PHYSICS BULLETIN', 'Doucet A, 2000, STATISTICS AND COMPUTING', 'Tanner M, 1987, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Tierney L, 1994, THE ANNALS OF STATISTICS', 'Rubinstein R, 2016, WILEY SERIES IN PROBABILITY AND STATISTICS', ', 1988, MATHEMATICS AND COMPUTERS IN SIMULATION', 'Pitt M, 1999, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Merwe R, 2000, ', 'Neal R, 2000, ARXIV (CORNELL UNIVERSITY)', 'Murphy K, 2001, ', 'Berners‐Lee T, 1994, COMMUNICATIONS OF THE ACM', 'Kalos M, 1986, ', 'Rota G, 1988, ADVANCES IN MATHEMATICS', 'Peskun P, 1973, BIOMETRIKA', 'Damlen P, 1999, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Escobar M, 1995, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Smith P, 1997, IEEE JOURNAL ON SELECTED AREAS IN COMMUNICATIONS', 'Freitas J, 2000, NEURAL COMPUTATION', 'Cheng J, 2000, ', 'Cheng J, 2000, JOURNAL OF ARTIFICIAL INTELLIGENCE RESEARCH', 'Troughton P, 2002, ', ', 1995, ', 'Neuwald A, 1997, NUCLEIC ACIDS RESEARCH', 'Beichl I, 2000, COMPUTING IN SCIENCE &amp; ENGINEERING', 'Andrieu C, 2001, NEURAL COMPUTATION', 'Tu Z, 2002, ', 'Freitas N, 2001, UNCERTAINTY IN ARTIFICIAL INTELLIGENCE', 'Peskun P, 1973, BIOMETRIKA', 'Müller P, 1998, NEURAL COMPUTATION', 'Holmes C, 1998, NEURAL COMPUTATION', 'Ghahramani Z, 1994, ', 'Remondo D, 2000, IEEE TRANSACTIONS ON COMMUNICATIONS', 'Andrieu C, 2002, THE MIT PRESS EBOOKS', 'Poupart P, 2017, ENCYCLOPEDIA OF MACHINE LEARNING AND DATA MINING', 'Mykland P, 1995, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Andrieu C, 2001, JOURNAL OF APPLIED PROBABILITY', 'Aldous D, 1998, DIMACS SERIES IN DISCRETE MATHEMATICS AND THEORETICAL COMPUTER SCIENCE', 'Kannan R, 2002, ', 'Andrieu C, 1999, OXFORD UNIVERSITY RESEARCH ARCHIVE (ORA) (UNIVERSITY OF OXFORD)', 'Clark E, 1999, ', 'Doucet A, 2013, ARXIV (CORNELL UNIVERSITY)', 'Andrieu C, 2013, ARXIV (CORNELL UNIVERSITY)', 'Forsyth D, 2003, ', 'Ridgeway G, 1999, RESEARCHWORKS AT THE UNIVERSITY OF WASHINGTON (UNIVERSITY OF WASHINGTON)', 'Ortiz L, 2013, ARXIV (CORNELL UNIVERSITY)', 'Rubinstein R, 1981, WILEY SERIES IN PROBABILITY AND STATISTICS', 'Laarhoven P, 1987, ', 'Robert C, 1999, SPRINGER TEXTS IN STATISTICS', 'Gasparini M, 1997, TECHNOMETRICS', 'Meyn S, 2009, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Hastings W, 1970, BIOMETRIKA', 'Gelfand A, 1990, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Wei G, 1990, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Pitt M, 1999, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Geman S, 1987, ELSEVIER EBOOKS', 'Tanner M, 1987, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Green P, 1995, BIOMETRIKA', 'Albert J, 1993, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Doucet A, 2005, ', 'Seila A, 1982, TECHNOMETRICS', 'Carter C, 1994, BIOMETRIKA', 'McLoughlin I, 2016, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'McCulloch C, 1994, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Gilks W, 1998, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Gelfand A, 1994, JOURNAL OF COMPUTATIONAL AND GRAPHICAL STATISTICS', 'Haario H, 1991, ADVANCES IN APPLIED PROBABILITY', 'Andrieu C, 2001, JOURNAL OF APPLIED PROBABILITY', 'Wood S, 1998, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Ghahramani Z, 1996, ', 'Moreau T, 2023, MEDICAL IMAGE ANALYSIS']</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -8313,7 +8321,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -8370,7 +8378,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>['Gordon A, 1984, BIOMETRICS', 'Nielsen M, 2002, AMERICAN JOURNAL OF PHYSICS', 'Freund Y, 1997, JOURNAL OF COMPUTER AND SYSTEM SCIENCES', 'Johnson J, 2000, NEUROCOMPUTING', 'Jones D, 1998, JOURNAL OF GLOBAL OPTIMIZATION', 'Ganin Y, 2017, ADVANCES IN COMPUTER VISION AND PATTERN RECOGNITION', 'Амари Ш, 1998, NEURAL COMPUTATION', 'Oseledets I, 2011, SIAM JOURNAL ON SCIENTIFIC COMPUTING', 'Smolensky P, 1986, MIT PRESS EBOOKS', 'Lloyd S, 2014, NATURE PHYSICS', 'Thouless D, 1977, PHILOSOPHICAL MAGAZINE', 'Nishimori H, 2001, ', 'Groß D, 2010, PHYSICAL REVIEW LETTERS', 'Decelle A, 2011, PHYSICAL REVIEW E', 'Engel A, 2001, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Dean D, 1996, JOURNAL OF PHYSICS A MATHEMATICAL AND GENERAL', 'Lakemeyer G, 2003, ', 'Decelle A, 2011, PHYSICAL REVIEW LETTERS', 'Gligorov V, 2013, JOURNAL OF INSTRUMENTATION', 'Collett T, 2015, THE ASTROPHYSICAL JOURNAL', 'Minitti M, 2015, PHYSICAL REVIEW LETTERS', 'Kind M, 2013, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Feldmann R, 2006, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Tóth G, 2010, PHYSICAL REVIEW LETTERS', 'Saad D, 1995, PHYSICAL REVIEW. E, STATISTICAL PHYSICS, PLASMAS, FLUIDS, AND RELATED INTERDISCIPLINARY TOPICS', 'Robin A, 2014, ASTRONOMY AND ASTROPHYSICS', 'Hand D, 2015, STATISTICS AND COMPUTING', 'Bonnett C, 2016, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Kabashima Y, 2016, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Ntampaka M, 2015, THE ASTROPHYSICAL JOURNAL', 'Sompolinsky H, 1990, PHYSICAL REVIEW LETTERS', 'Schuch N, 2008, PHYSICAL REVIEW LETTERS', 'Changlani H, 2009, PHYSICAL REVIEW B', 'Györgyi G, 1990, PHYSICAL REVIEW A', 'Mezzacapo F, 2009, NEW JOURNAL OF PHYSICS', 'University&amp;gt; C, 1984, CONTEMPORARY MATHEMATICS - AMERICAN MATHEMATICAL SOCIETY', 'Ishida É, 2015, ASTRONOMY AND COMPUTING', 'Lorenz U, 2010, NEW JOURNAL OF PHYSICS', 'Estrada J, 2007, THE ASTROPHYSICAL JOURNAL', 'Lorenz U, 2010, PHYSICAL REVIEW A', 'Bang J, 2014, NEW JOURNAL OF PHYSICS', 'Sakata A, 2013, EUROPHYSICS LETTERS (EPL)', 'Hintikka J, 1970, ', 'Levi I, 1967, SYNTHESE', 'Gendiar A, 2002, PHYSICAL REVIEW. E, STATISTICAL PHYSICS, PLASMAS, FLUIDS, AND RELATED INTERDISCIPLINARY TOPICS', 'Mehta P, 2014, ARXIV (CORNELL UNIVERSITY)', 'Cranmer K, 2015, ARXIV (CORNELL UNIVERSITY)', 'Bény C, 2013, ARXIV (CORNELL UNIVERSITY)', 'Hochreiter S, 1997, NEURAL COMPUTATION', 'Schmidhuber J, 2014, NEURAL NETWORKS', 'Cybenko G, 1989, MATHEMATICS OF CONTROL SIGNALS AND SYSTEMS', 'Foreman-Mackey D, 2013, PUBLICATIONS OF THE ASTRONOMICAL SOCIETY OF THE PACIFIC', 'White S, 1992, PHYSICAL REVIEW LETTERS', 'Hinton G, 2002, NEURAL COMPUTATION', 'Behler J, 2007, PHYSICAL REVIEW LETTERS', 'Jaeger H, 2004, SCIENCE', 'Bartók A, 2010, PHYSICAL REVIEW LETTERS', 'Beaumont M, 2002, GENETICS', 'Bartók A, 2013, PHYSICAL REVIEW B', 'Rupp M, 2012, PHYSICAL REVIEW LETTERS', 'Reck M, 1994, PHYSICAL REVIEW LETTERS', 'Ramakrishnan R, 2014, SCIENTIFIC DATA', 'Brammer G, 2008, THE ASTROPHYSICAL JOURNAL', 'Verstraete F, 2008, ADVANCES IN PHYSICS', 'Seung H, 1992, ', 'Marjoram P, 2003, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Amit D, 1985, PHYSICAL REVIEW. A, GENERAL PHYSICS', 'Bershady M, 2004, PUBLICATIONS OF THE ASTRONOMICAL SOCIETY OF THE PACIFIC', 'Benitez N, 2000, THE ASTROPHYSICAL JOURNAL', 'Gardner E, 1988, JOURNAL OF PHYSICS A MATHEMATICAL AND GENERAL', 'Johnstone I, 2009, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Anandkumar A, 2014, CALTECHAUTHORS (CALIFORNIA INSTITUTE OF TECHNOLOGY)', 'Snyder J, 2012, PHYSICAL REVIEW LETTERS', 'Krząkała F, 2013, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Shi Y, 2006, PHYSICAL REVIEW A', 'Seung H, 1992, PHYSICAL REVIEW A', 'Hackbusch W, 2009, JOURNAL OF FOURIER ANALYSIS AND APPLICATIONS', 'Cubuk E, 2015, PHYSICAL REVIEW LETTERS', 'Gardner E, 1987, EUROPHYSICS LETTERS (EPL)', 'Sorella S, 1998, PHYSICAL REVIEW LETTERS', 'Carleo G, 2012, SCIENTIFIC REPORTS', 'Forte S, 2002, JOURNAL OF HIGH ENERGY PHYSICS', 'Gardner E, 1989, JOURNAL OF PHYSICS A MATHEMATICAL AND GENERAL', 'Ambs P, 2010, ADVANCES IN OPTICAL TECHNOLOGIES', 'Cameron E, 2012, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Saad D, 1995, PHYSICAL REVIEW LETTERS', 'Marshall P, 2009, THE ASTROPHYSICAL JOURNAL', 'Ben-Nun M, 1997, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Watkin T, 1994, JOURNAL OF PHYSICS A MATHEMATICAL AND GENERAL', 'Shalashilin D, 2011, FARADAY DISCUSSIONS', 'Schwarze H, 1993, JOURNAL OF PHYSICS A MATHEMATICAL AND GENERAL', 'Lu T, 1989, APPLIED OPTICS', 'Lundberg K, 2005, IEEE CONTROL SYSTEMS', 'Barkai N, 1994, PHYSICAL REVIEW. E, STATISTICAL PHYSICS, PLASMAS, FLUIDS, AND RELATED INTERDISCIPLINARY TOPICS', 'Çakmak B, 2014, ', 'Biehl M, 1993, EUROPHYSICS LETTERS (EPL)', 'Minsky M, 1969, ', 'Adachi S, 2015, ARXIV (CORNELL UNIVERSITY)', 'S S, 2005, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Hopfield J, 1982, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Fortunato S, 2009, PHYSICS REPORTS', 'Luxburg U, 2007, STATISTICS AND COMPUTING', 'Dirac P, 1930, MATHEMATICAL PROCEEDINGS OF THE CAMBRIDGE PHILOSOPHICAL SOCIETY', 'Ball R, 2015, JOURNAL OF HIGH ENERGY PHYSICS', 'McClean J, 2016, NEW JOURNAL OF PHYSICS', 'Carleo G, 2017, SCIENCE', 'Hofmann T, 2008, THE ANNALS OF STATISTICS', 'Carrasquilla J, 2017, NATURE PHYSICS', 'Baldi P, 2014, NATURE COMMUNICATIONS', 'Sisson S, 2007, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Marin J, 2011, STATISTICS AND COMPUTING', 'Nishimori H, 2001, ', 'Wang L, 2016, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Brockherde F, 2017, NATURE COMMUNICATIONS', 'Roe B, 2005, NUCLEAR INSTRUMENTS AND METHODS IN PHYSICS RESEARCH SECTION A ACCELERATORS SPECTROMETERS DETECTORS AND ASSOCIATED EQUIPMENT', 'Collister A, 2004, PUBLICATIONS OF THE ASTRONOMICAL SOCIETY OF THE PACIFIC', 'Acar E, 2008, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Zdeborová L, 2016, ADVANCES IN PHYSICS', 'Broecker P, 2017, SCIENTIFIC REPORTS', 'Oliveira L, 2016, JOURNAL OF HIGH ENERGY PHYSICS', 'Krenn M, 2016, PHYSICAL REVIEW LETTERS', 'Baldi P, 2016, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Aurisano A, 2016, JOURNAL OF INSTRUMENTATION', 'Baldi P, 2016, THE EUROPEAN PHYSICAL JOURNAL C', 'Wigley P, 2016, SCIENTIFIC REPORTS', 'Guest D, 2016, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Lookman T, 2015, SPRINGER SERIES IN MATERIALS SCIENCE', 'Tanaka A, 2017, JOURNAL OF THE PHYSICAL SOCIETY OF JAPAN', 'Reddy G, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Riofrío C, 2017, NATURE COMMUNICATIONS', 'Baldassi C, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Baldassi C, 2015, PHYSICAL REVIEW LETTERS', 'Ohtsuki T, 2016, JOURNAL OF THE PHYSICAL SOCIETY OF JAPAN', 'Schoenholz S, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Barnes D, 2016, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Mézard M, 2017, PHYSICAL REVIEW. E', 'Likhomanenko T, 2015, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Ntampaka M, 2016, THE ASTROPHYSICAL JOURNAL', 'Firth A, 2003, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Mavadia S, 2017, NATURE COMMUNICATIONS', 'Kirrander A, 2015, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Stevens J, 2013, JOURNAL OF INSTRUMENTATION', 'Li N, 2016, THE ASTROPHYSICAL JOURNAL', 'Ravanbakhsh S, 2017, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Novikov A, 2016, ARXIV (CORNELL UNIVERSITY)', 'Sutherland D, 2012, ARXIV (CORNELL UNIVERSITY)', 'Flach P, 2015, ', 'Teymur O, 2016, ', 'Biamonte J, 2017, NATURE', 'Bronstein M, 2017, IEEE SIGNAL PROCESSING MAGAZINE', ', 2007, CHOICE REVIEWS ONLINE', 'Germain M, 2015, ', 'Smith J, 2017, CHEMICAL SCIENCE', 'Mézard M, 2009, ', 'Behler J, 2016, THE JOURNAL OF CHEMICAL PHYSICS', 'Nieuwenburg E, 2017, NATURE PHYSICS', 'Gastegger M, 2017, CHEMICAL SCIENCE', 'Wetzel S, 2017, PHYSICAL REVIEW. E', 'Deng D, 2017, PHYSICAL REVIEW X', 'Kull M, 2017, ', 'Paganini M, 2018, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Gao X, 2017, NATURE COMMUNICATIONS', 'Nguyen H, 2017, ADVANCES IN PHYSICS', 'Lanyon B, 2017, NATURE PHYSICS', 'Chen J, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Liu J, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Schawinski K, 2017, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY LETTERS', 'Huang L, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Cai Z, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Koch-Janusz M, 2018, NATURE PHYSICS', 'Torlai G, 2017, PHYSICAL REVIEW LETTERS', 'Lanusse F, 2017, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Arunachalam S, 2017, ACM SIGACT NEWS', 'Schindler F, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Lelarge M, 2018, PROBABILITY THEORY AND RELATED FIELDS', 'Shimmin C, 2017, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Tubiana J, 2017, PHYSICAL REVIEW LETTERS', 'Zhang Y, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Acciarri R, 2017, JOURNAL OF INSTRUMENTATION', 'Varsamopoulos S, 2017, QUANTUM SCIENCE AND TECHNOLOGY', 'Ballard A, 2017, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Coja‐Oghlan A, 2018, ADVANCES IN MATHEMATICS', 'Bradde S, 2017, JOURNAL OF STATISTICAL PHYSICS', 'Liu J, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Ohtsuki T, 2017, JOURNAL OF THE PHYSICAL SOCIETY OF JAPAN', 'Nagai Y, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Barra A, 2018, PHYSICAL REVIEW. E', 'Huang Y, 2021, PHYSICAL REVIEW LETTERS', 'Ilten P, 2017, JOURNAL OF INSTRUMENTATION', 'Miller R, 2016, FARADAY DISCUSSIONS', 'Bellshaw D, 2017, CHEMICAL PHYSICS LETTERS', 'Tramel E, 2018, PHYSICAL REVIEW X', ', 2015, ', 'Shwartz-Ziv R, 2017, ARXIV (CORNELL UNIVERSITY)', 'Law J, 2001, ACM SIGSOFT SOFTWARE ENGINEERING NOTES', 'Shen Y, 2017, NATURE PHOTONICS', 'Zhang L, 2018, PHYSICAL REVIEW LETTERS', 'Faber F, 2017, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Pathak J, 2017, CHAOS AN INTERDISCIPLINARY JOURNAL OF NONLINEAR SCIENCE', 'Becca F, 2017, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Ciliberto C, 2018, PROCEEDINGS OF THE ROYAL SOCIETY A MATHEMATICAL PHYSICAL AND ENGINEERING SCIENCES', 'Mardt A, 2017, NATURE COMMUNICATIONS', 'Wehmeyer C, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Hu W, 2017, PHYSICAL REVIEW. E', 'Nomura Y, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Melnikov A, 2018, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Lubbers N, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Metodiev E, 2017, JOURNAL OF HIGH ENERGY PHYSICS', 'Bukov M, 2018, PHYSICAL REVIEW X', 'Zhang Y, 2017, PHYSICAL REVIEW LETTERS', 'Zhang P, 2018, PHYSICAL REVIEW LETTERS', 'Hezaveh Y, 2017, NATURE', 'Han Z, 2018, PHYSICAL REVIEW X', 'Glasser I, 2018, PHYSICAL REVIEW X', 'Beach M, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Haah J, 2017, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Bereau T, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Venderley J, 2018, PHYSICAL REVIEW LETTERS', 'Schneider E, 2017, PHYSICAL REVIEW LETTERS', 'Advani M, 2020, NEURAL NETWORKS', 'Wang C, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Baireuther P, 2018, QUANTUM', 'Saito H, 2017, JOURNAL OF THE PHYSICAL SOCIETY OF JAPAN', 'Carifio J, 2017, JOURNAL OF HIGH ENERGY PHYSICS', 'Saito H, 2017, JOURNAL OF THE PHYSICAL SOCIETY OF JAPAN', 'Benedetti M, 2017, PHYSICAL REVIEW X', 'Krastanov S, 2017, SCIENTIFIC REPORTS', 'Kaubruegger R, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Martiniani S, 2019, PHYSICAL REVIEW X', 'Clark S, 2018, JOURNAL OF PHYSICS A MATHEMATICAL AND THEORETICAL', 'Rocchetto A, 2018, NPJ QUANTUM INFORMATION', 'Schmitt M, 2018, SCIPOST PHYSICS', 'Arsenault L, 2017, INVERSE PROBLEMS', 'Teng P, 2018, PHYSICAL REVIEW. E', 'Barbier J, 2017, ', 'Cocco S, 2017, PHYSICA A STATISTICAL MECHANICS AND ITS APPLICATIONS', 'Apollinari G, 2015, ARXIV (CORNELL UNIVERSITY)', 'Putzky P, 2017, ARXIV (CORNELL UNIVERSITY)', 'Broecker P, 2017, ARXIV (CORNELL UNIVERSITY)', 'Louppe G, 2017, ARXIV (CORNELL UNIVERSITY)', 'Cristoforetti M, 2017, ARXIV (CORNELL UNIVERSITY)', 'Frate M, 2017, ARXIV (CORNELL UNIVERSITY)', 'Pang L, 2016, ARXIV (CORNELL UNIVERSITY)', 'Izmailov P, 2017, ARXIV (CORNELL UNIVERSITY)', 'Schütt K, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Schuld M, 2019, PHYSICAL REVIEW LETTERS', 'Pathak J, 2018, PHYSICAL REVIEW LETTERS', 'Dunjko V, 2018, REPORTS ON PROGRESS IN PHYSICS', 'Smith J, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Chmiela S, 2018, NATURE COMMUNICATIONS', 'Alet F, 2018, COMPTES RENDUS PHYSIQUE', 'Yao K, 2018, CHEMICAL SCIENCE', 'Deng D, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Paganini M, 2018, PHYSICAL REVIEW LETTERS', 'Deringer V, 2018, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Kamath A, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Fösel T, 2018, PHYSICAL REVIEW X', 'Pang L, 2018, NATURE COMMUNICATIONS', 'Nguyen T, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Alsing J, 2018, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Li S, 2018, PHYSICAL REVIEW LETTERS', 'Carleo G, 2018, NATURE COMMUNICATIONS', 'Torlai G, 2018, PHYSICAL REVIEW LETTERS', 'Komiske P, 2018, JOURNAL OF HIGH ENERGY PHYSICS', 'Chung S, 2018, PHYSICAL REVIEW X', 'Charnock T, 2018, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Kalantre S, 2019, NPJ QUANTUM INFORMATION', 'Hashimoto K, 2018, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Stoudenmire E, 2018, QUANTUM SCIENCE AND TECHNOLOGY', 'Sosso G, 2018, MOLECULAR SIMULATION', 'Czischek S, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Maskara N, 2019, PHYSICAL REVIEW. A/PHYSICAL REVIEW, A', 'Sidky H, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Rodríguez A, 2018, COMPUTATIONAL ASTROPHYSICS AND COSMOLOGY', 'Nagai R, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Shanahan P, 2018, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Nieuwenburg E, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Iakovlev I, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Chen C, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Decelle A, 2017, EUROPHYSICS LETTERS (EPL)', 'Wang C, 2018, FRONTIERS OF PHYSICS', 'Agresti I, 2019, PHYSICAL REVIEW X', 'Anelli A, 2018, PHYSICAL REVIEW MATERIALS', 'Tubiana J, 2019, ELIFE', 'Schmidt E, 2018, COMPUTATIONAL MATERIALS SCIENCE', 'Charnock T, 2018, ARXIV (CORNELL UNIVERSITY)', 'Aaronson S, 2018, SIAM JOURNAL ON COMPUTING', 'Lee J, 2017, ARXIV (CORNELL UNIVERSITY)', 'Torlai G, 2017, ARXIV (CORNELL UNIVERSITY)', 'Kondor R, 2018, ARXIV (CORNELL UNIVERSITY)', 'Tanaka A, 2017, ARXIV (CORNELL UNIVERSITY)', 'Casado M, 2017, ARXIV (CORNELL UNIVERSITY)', 'Regier J, 2018, ARXIV (CORNELL UNIVERSITY)', 'Jain A, 2018, ARXIV (CORNELL UNIVERSITY)', 'Butler K, 2018, NATURE', 'Lin X, 2018, SCIENCE', 'Havlíček V, 2019, NATURE', 'Ambrogio S, 2018, NATURE', 'Schuld M, 2018, QUANTUM SCIENCE AND TECHNOLOGY', 'Radovic A, 2018, NATURE', 'Bartók A, 2018, PHYSICAL REVIEW X', 'Duarte J, 2018, JOURNAL OF INSTRUMENTATION', 'Guest D, 2018, ANNUAL REVIEW OF NUCLEAR AND PARTICLE SCIENCE', 'Paruzzo F, 2018, NATURE COMMUNICATIONS', 'Choo K, 2018, PHYSICAL REVIEW LETTERS', 'Albertsson K, 2018, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Wu D, 2019, PHYSICAL REVIEW LETTERS', 'Reddy G, 2018, NATURE', 'Brehmer J, 2018, PHYSICAL REVIEW LETTERS', 'Brehmer J, 2018, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Gabrié M, 2019, JOURNAL OF STATISTICAL MECHANICS THEORY AND EXPERIMENT', 'Sifain A, 2018, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Huembeli P, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Komiske P, 2018, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Liang X, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Rupp M, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Fournier R, 2020, PHYSICAL REVIEW LETTERS', 'Hsu Y, 2018, PHYSICAL REVIEW LETTERS', 'Engel E, 2018, NATURE COMMUNICATIONS', 'Eickenberg M, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Sun N, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Greitemann J, 2019, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Yoon H, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Bukov M, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Hashimoto K, 2018, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Lu S, 2019, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Huembeli P, 2019, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Guo C, 2018, PHYSICAL REVIEW. E', 'Banchi L, 2018, NEW JOURNAL OF PHYSICS', 'Seif A, 2018, JOURNAL OF PHYSICS B ATOMIC MOLECULAR AND OPTICAL PHYSICS', 'Zhang W, 2019, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Saito H, 2018, JOURNAL OF THE PHYSICAL SOCIETY OF JAPAN', 'Leistedt B, 2019, THE ASTROPHYSICAL JOURNAL', 'Liu Y, 2018, ARXIV (CORNELL UNIVERSITY)', 'Steinbrecher G, 2019, NPJ QUANTUM INFORMATION', 'Papamakarios G, 2018, ARXIV (CORNELL UNIVERSITY)', 'Jónsson B, 2018, ARXIV (CORNELL UNIVERSITY)', 'Song M, 2018, ARXIV (CORNELL UNIVERSITY)', 'Kondor R, 2018, ARXIV (CORNELL UNIVERSITY)', 'Glasser I, 2018, ARXIV (CORNELL UNIVERSITY)', 'Morningstar W, 2018, ARXIV (CORNELL UNIVERSITY)', 'Wang C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Golkar S, 2018, ARXIV (CORNELL UNIVERSITY)', 'LeCun Y, 2015, NATURE', 'Cong I, 2019, NATURE PHYSICS', 'Zhang L, 2019, PHYSICAL REVIEW MATERIALS', 'Carrasquilla J, 2019, NATURE MACHINE INTELLIGENCE', 'Hartmann M, 2019, PHYSICAL REVIEW LETTERS', 'Sharir O, 2020, PHYSICAL REVIEW LETTERS', 'Rem B, 2019, NATURE PHYSICS', 'Nagy A, 2019, PHYSICAL REVIEW LETTERS', 'Vicentini F, 2019, PHYSICAL REVIEW LETTERS', 'Komiske P, 2019, JOURNAL OF HIGH ENERGY PHYSICS', 'Albergo M, 2019, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'He S, 2019, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Levine Y, 2019, PHYSICAL REVIEW LETTERS', 'Barbier J, 2019, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Doggen E, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Yoshioka N, 2019, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Luo D, 2019, PHYSICAL REVIEW LETTERS', 'Zhang Y, 2019, NATURE', 'Torlai G, 2019, PHYSICAL REVIEW LETTERS', 'Gray J, 2018, PHYSICAL REVIEW LETTERS', 'Cheng S, 2019, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Alsing J, 2019, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Salamani D, 2018, ', 'Peel A, 2019, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Morningstar W, 2019, THE ASTROPHYSICAL JOURNAL', 'Liu K, 2019, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Mills K, 2019, CHEMICAL SCIENCE', 'Armitage T, 2019, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Stokes J, 2019, ENTROPY', 'Kashiwa K, 2019, PROGRESS OF THEORETICAL AND EXPERIMENTAL PHYSICS', 'Borin A, 2020, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Tsaris A, 2018, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Zheng Y, 2019, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Quek Y, 2021, NPJ QUANTUM INFORMATION', 'Cohen T, 2019, ARXIV (CORNELL UNIVERSITY)', ', 2016, ', 'Farrell S, 2018, ARXIV (CORNELL UNIVERSITY)', 'Zhang X, 2019, ARXIV (CORNELL UNIVERSITY)', 'Ntampaka M, 2019, ARXIV (CORNELL UNIVERSITY)', 'Kochkov D, 2018, ARXIV (CORNELL UNIVERSITY)', 'Albertsson K, 2018, ARXIV (CORNELL UNIVERSITY)', 'Xu Q, 2018, ARXIV (CORNELL UNIVERSITY)', 'Cranmer K, 2019, ARXIV (CORNELL UNIVERSITY)', 'Choma N, 2018, ARXIV (CORNELL UNIVERSITY)', 'Bozson A, 2018, ARXIV (CORNELL UNIVERSITY)', ', 2002, THE MIT PRESS EBOOKS', 'Yu B, 2018, FRONTIERS OF INFORMATION TECHNOLOGY &amp; ELECTRONIC ENGINEERING', 'Vidal G, 2007, PHYSICAL REVIEW LETTERS', 'Matteo P, 2004, LECTURE NOTES IN PHYSICS', 'Noé F, 2019, SCIENCE', 'Han J, 2019, JOURNAL OF COMPUTATIONAL PHYSICS', 'Yang J, 2020, SCIENCE', 'Brehmer J, 2020, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Louppe G, 2017, ORBI (UNIVERSITY OF LIÈGE)', 'Stankus B, 2019, NATURE CHEMISTRY', 'Yong H, 2020, NATURE COMMUNICATIONS', 'Lang D, 2016, ASTROPHYSICS SOURCE CODE LIBRARY', 'Ronhovde P, 2011, THE EUROPEAN PHYSICAL JOURNAL E', 'Rocchetto A, 2019, IRIS RESEARCH PRODUCT CATALOG (SAPIENZA UNIVERSITY OF ROME)', 'Fabiani G, 2019, SCIPOST PHYSICS', 'Morningstar A, 2018, ARXIV (CORNELL UNIVERSITY)', 'Schoenholz S, 2019, ARXIV (CORNELL UNIVERSITY)', 'Cranmer K, 2016, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Mardt A, 2018, REPEC: RESEARCH PAPERS IN ECONOMICS', ', , PORTSMOUTH RESEARCH PORTAL (UNIVERSITY OF PORTSMOUTH)', 'A. C, 2003, ', 'Gao X, , REPEC: RESEARCH PAPERS IN ECONOMICS', 'Ritzmann U, 2018, ARXIV (CORNELL UNIVERSITY)', 'Zhang Y, , REPEC: RESEARCH PAPERS IN ECONOMICS', 'Justin S, 2013, DSPACE@MIT (MASSACHUSETTS INSTITUTE OF TECHNOLOGY)', 'Aubin B, 2018, HAL (LE CENTRE POUR LA COMMUNICATION SCIENTIFIQUE DIRECTE)', 'Hermans J, 2019, ARXIV (CORNELL UNIVERSITY)', 'Lanusse F, 2019, ARXIV (CORNELL UNIVERSITY)', 'T. H, 2008, ', 'F B, 2017, MPG.PURE (MAX PLANCK SOCIETY)', 'I. G, 2018, MAX PLANCK DIGITAL LIBRARY', 'T. F, 2018, MPG.PURE (MAX PLANCK SOCIETY)', 'Nguyen T, 2018, OPEN MIND', 'Robin A, 2014, SPRINGER LINK (CHIBA INSTITUTE OF TECHNOLOGY)', 'Ntampaka M, 2019, DSPACE@MIT (MASSACHUSETTS INSTITUTE OF TECHNOLOGY)', 'Rocchetto A, 2018, UCL DISCOVERY (UNIVERSITY COLLEGE LONDON)', 'F. M, 2009, MPG.PURE (MAX PLANCK SOCIETY)', 'Sarao M, 2020, HAL (LE CENTRE POUR LA COMMUNICATION SCIENTIFIQUE DIRECTE)', 'vloncar, 2021, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', ', , ANET (UNIVERSITY OF ANTWERP)', 'Komiske P, 2019, DSPACE@MIT (MASSACHUSETTS INSTITUTE OF TECHNOLOGY)', 'Komiske P, 2018, OSTI OAI (U.S. DEPARTMENT OF ENERGY OFFICE OF SCIENTIFIC AND TECHNICAL INFORMATION)', 'Donoho D, 2006, IEEE TRANSACTIONS ON INFORMATION THEORY', ', 1996, COMPUTERS &amp; MATHEMATICS WITH APPLICATIONS', 'Valiant L, 1984, COMMUNICATIONS OF THE ACM', 'Ziegel E, 1989, TECHNOMETRICS', 'Frenkelʹ I, 1934, CLARENDON PRESS EBOOKS', 'Wu Z, 2015, ', 'Dean D, 1996, ', 'Carleo G, 2018, REPEC: RESEARCH PAPERS IN ECONOMICS', 'Rodríguez A, 2018, REPOSITORY FOR PUBLICATIONS AND RESEARCH DATA (ETH ZURICH)', 'Wecker D, 2016, PHYSICAL REVIEW. A/PHYSICAL REVIEW, A', 'L B, 2018, UCL DISCOVERY (UNIVERSITY COLLEGE LONDON)', 'E F, 2002, ', 'M. S, 2018, MAX PLANCK DIGITAL LIBRARY', 'Tiersch M, 2015, SCIENTIFIC REPORTS', ', 2005, IEEE TRANSACTIONS ON INFORMATION THEORY', ', 1992, ', 'Nathan K, 2018, DSPACE@MIT (MASSACHUSETTS INSTITUTE OF TECHNOLOGY)', 'Oliveira L, 2022, OSTI OAI (U.S. DEPARTMENT OF ENERGY OFFICE OF SCIENTIFIC AND TECHNICAL INFORMATION)', ', 2013, PROBABILITY THEORY AND RELATED FIELDS', ', 2018, ', 'Ilten P, 2015, CERN DOCUMENT SERVER (EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', ', 1990, ', ', 2017, ', ', 2008, ADVANCES IN OPTICAL TECHNOLOGIES', 'Mannelli S, 2019, ARXIV (CORNELL UNIVERSITY)', ', 2014, ', 'Kagan M, 2016, OPEN REPOSITORY AND BIBLIOGRAPHY (UNIVERSITY OF LIÈGE)', 'Kondor R, 2018, ARXIV (CORNELL UNIVERSITY)', 'Cohen T, 2018, ARXIV (CORNELL UNIVERSITY)', 'Louppe G, 2020, OPEN REPOSITORY AND BIBLIOGRAPHY (UNIVERSITY OF LIÈGE)', 'Kondor R, 2018, ARXIV (CORNELL UNIVERSITY)', ', 2018, ', 'Levine Y, 2017, ARXIV (CORNELL UNIVERSITY)', 'Frate M, 2017, ARXIV (CORNELL UNIVERSITY)', 'Glasser I, 2018, ARXIV (CORNELL UNIVERSITY)', 'Baydin A, 2018, ARXIV (CORNELL UNIVERSITY)', 'Goldt S, 2019, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>['Gordon A, 1984, BIOMETRICS', 'Nielsen M, 2002, AMERICAN JOURNAL OF PHYSICS', 'Freund Y, 1997, JOURNAL OF COMPUTER AND SYSTEM SCIENCES', 'Johnson J, 2000, NEUROCOMPUTING', 'Jones D, 1998, JOURNAL OF GLOBAL OPTIMIZATION', 'Ganin Y, 2017, ADVANCES IN COMPUTER VISION AND PATTERN RECOGNITION', 'Nielsen M, 2011, ', 'Амари Ш, 1998, NEURAL COMPUTATION', 'Oseledets I, 2011, SIAM JOURNAL ON SCIENTIFIC COMPUTING', 'Smolensky P, 1986, MIT PRESS EBOOKS', 'Lloyd S, 2014, NATURE PHYSICS', 'Thouless D, 1977, PHILOSOPHICAL MAGAZINE', 'Nishimori H, 2001, ', 'Groß D, 2010, PHYSICAL REVIEW LETTERS', 'Decelle A, 2011, PHYSICAL REVIEW E', 'Engel A, 2001, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Dean D, 1996, JOURNAL OF PHYSICS A MATHEMATICAL AND GENERAL', 'Lakemeyer G, 2003, ', 'Decelle A, 2011, PHYSICAL REVIEW LETTERS', 'Gligorov V, 2013, JOURNAL OF INSTRUMENTATION', 'Collett T, 2015, THE ASTROPHYSICAL JOURNAL', 'Minitti M, 2015, PHYSICAL REVIEW LETTERS', 'Kind M, 2013, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Feldmann R, 2006, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Tóth G, 2010, PHYSICAL REVIEW LETTERS', 'Saad D, 1995, PHYSICAL REVIEW. E, STATISTICAL PHYSICS, PLASMAS, FLUIDS, AND RELATED INTERDISCIPLINARY TOPICS', 'Robin A, 2014, ASTRONOMY AND ASTROPHYSICS', 'Hand D, 2015, STATISTICS AND COMPUTING', 'Bonnett C, 2016, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Kabashima Y, 2016, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Ntampaka M, 2015, THE ASTROPHYSICAL JOURNAL', 'Sompolinsky H, 1990, PHYSICAL REVIEW LETTERS', 'Schuch N, 2008, PHYSICAL REVIEW LETTERS', 'Changlani H, 2009, PHYSICAL REVIEW B', 'Györgyi G, 1990, PHYSICAL REVIEW A', 'Mezzacapo F, 2009, NEW JOURNAL OF PHYSICS', 'University&amp;gt; C, 1984, CONTEMPORARY MATHEMATICS - AMERICAN MATHEMATICAL SOCIETY', 'Ishida É, 2015, ASTRONOMY AND COMPUTING', 'Lorenz U, 2010, NEW JOURNAL OF PHYSICS', 'Estrada J, 2007, THE ASTROPHYSICAL JOURNAL', 'Lorenz U, 2010, PHYSICAL REVIEW A', 'Bang J, 2014, NEW JOURNAL OF PHYSICS', 'Sakata A, 2013, EUROPHYSICS LETTERS (EPL)', 'Hintikka J, 1970, ', 'Levi I, 1967, SYNTHESE', 'Gendiar A, 2002, PHYSICAL REVIEW. E, STATISTICAL PHYSICS, PLASMAS, FLUIDS, AND RELATED INTERDISCIPLINARY TOPICS', 'Mehta P, 2014, ARXIV (CORNELL UNIVERSITY)', 'Cranmer K, 2015, ARXIV (CORNELL UNIVERSITY)', 'Bény C, 2013, ARXIV (CORNELL UNIVERSITY)', 'Hochreiter S, 1997, NEURAL COMPUTATION', 'Schmidhuber J, 2014, NEURAL NETWORKS', 'Cybenko G, 1989, MATHEMATICS OF CONTROL SIGNALS AND SYSTEMS', 'Foreman-Mackey D, 2013, PUBLICATIONS OF THE ASTRONOMICAL SOCIETY OF THE PACIFIC', 'White S, 1992, PHYSICAL REVIEW LETTERS', 'Hinton G, 2002, NEURAL COMPUTATION', 'Behler J, 2007, PHYSICAL REVIEW LETTERS', 'Jaeger H, 2004, SCIENCE', 'Bartók A, 2010, PHYSICAL REVIEW LETTERS', 'Beaumont M, 2002, GENETICS', 'Bartók A, 2013, PHYSICAL REVIEW B', 'Rupp M, 2012, PHYSICAL REVIEW LETTERS', 'Reck M, 1994, PHYSICAL REVIEW LETTERS', 'Ramakrishnan R, 2014, SCIENTIFIC DATA', 'Brammer G, 2008, THE ASTROPHYSICAL JOURNAL', 'Verstraete F, 2008, ADVANCES IN PHYSICS', 'Seung H, 1992, ', 'Marjoram P, 2003, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Amit D, 1985, PHYSICAL REVIEW. A, GENERAL PHYSICS', 'Bershady M, 2004, PUBLICATIONS OF THE ASTRONOMICAL SOCIETY OF THE PACIFIC', 'Benitez N, 2000, THE ASTROPHYSICAL JOURNAL', 'Gardner E, 1988, JOURNAL OF PHYSICS A MATHEMATICAL AND GENERAL', 'Johnstone I, 2009, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Anandkumar A, 2014, CALTECHAUTHORS (CALIFORNIA INSTITUTE OF TECHNOLOGY)', 'Snyder J, 2012, PHYSICAL REVIEW LETTERS', 'Krząkała F, 2013, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Shi Y, 2006, PHYSICAL REVIEW A', 'Seung H, 1992, PHYSICAL REVIEW A', 'Hackbusch W, 2009, JOURNAL OF FOURIER ANALYSIS AND APPLICATIONS', 'Cubuk E, 2015, PHYSICAL REVIEW LETTERS', 'Gardner E, 1987, EUROPHYSICS LETTERS (EPL)', 'Sorella S, 1998, PHYSICAL REVIEW LETTERS', 'Carleo G, 2012, SCIENTIFIC REPORTS', 'Forte S, 2002, JOURNAL OF HIGH ENERGY PHYSICS', 'Gardner E, 1989, JOURNAL OF PHYSICS A MATHEMATICAL AND GENERAL', 'Ambs P, 2010, ADVANCES IN OPTICAL TECHNOLOGIES', 'Cameron E, 2012, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Saad D, 1995, PHYSICAL REVIEW LETTERS', 'Marshall P, 2009, THE ASTROPHYSICAL JOURNAL', 'Ben-Nun M, 1997, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Watkin T, 1994, JOURNAL OF PHYSICS A MATHEMATICAL AND GENERAL', 'Shalashilin D, 2011, FARADAY DISCUSSIONS', 'Schwarze H, 1993, JOURNAL OF PHYSICS A MATHEMATICAL AND GENERAL', 'Lu T, 1989, APPLIED OPTICS', 'Lundberg K, 2005, IEEE CONTROL SYSTEMS', 'Barkai N, 1994, PHYSICAL REVIEW. E, STATISTICAL PHYSICS, PLASMAS, FLUIDS, AND RELATED INTERDISCIPLINARY TOPICS', 'Çakmak B, 2014, ', 'Biehl M, 1993, EUROPHYSICS LETTERS (EPL)', 'Minsky M, 1969, ', 'Adachi S, 2015, ARXIV (CORNELL UNIVERSITY)', 'S S, 2005, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Hopfield J, 1982, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Fortunato S, 2009, PHYSICS REPORTS', 'Luxburg U, 2007, STATISTICS AND COMPUTING', 'Dirac P, 1930, MATHEMATICAL PROCEEDINGS OF THE CAMBRIDGE PHILOSOPHICAL SOCIETY', 'Ball R, 2015, JOURNAL OF HIGH ENERGY PHYSICS', 'McClean J, 2016, NEW JOURNAL OF PHYSICS', 'Carleo G, 2017, SCIENCE', 'Hofmann T, 2008, THE ANNALS OF STATISTICS', 'Carrasquilla J, 2017, NATURE PHYSICS', 'Baldi P, 2014, NATURE COMMUNICATIONS', 'Sisson S, 2007, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Marin J, 2011, STATISTICS AND COMPUTING', 'Nishimori H, 2001, ', 'Wang L, 2016, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Brockherde F, 2017, NATURE COMMUNICATIONS', 'Roe B, 2005, NUCLEAR INSTRUMENTS AND METHODS IN PHYSICS RESEARCH SECTION A ACCELERATORS SPECTROMETERS DETECTORS AND ASSOCIATED EQUIPMENT', 'Collister A, 2004, PUBLICATIONS OF THE ASTRONOMICAL SOCIETY OF THE PACIFIC', 'Acar E, 2008, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Zdeborová L, 2016, ADVANCES IN PHYSICS', 'Broecker P, 2017, SCIENTIFIC REPORTS', 'Oliveira L, 2016, JOURNAL OF HIGH ENERGY PHYSICS', 'Krenn M, 2016, PHYSICAL REVIEW LETTERS', 'Baldi P, 2016, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Aurisano A, 2016, JOURNAL OF INSTRUMENTATION', 'Baldi P, 2016, THE EUROPEAN PHYSICAL JOURNAL C', 'Wigley P, 2016, SCIENTIFIC REPORTS', 'Guest D, 2016, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Lookman T, 2015, SPRINGER SERIES IN MATERIALS SCIENCE', 'Tanaka A, 2017, JOURNAL OF THE PHYSICAL SOCIETY OF JAPAN', 'Reddy G, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Riofrío C, 2017, NATURE COMMUNICATIONS', 'Baldassi C, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Baldassi C, 2015, PHYSICAL REVIEW LETTERS', 'Ohtsuki T, 2016, JOURNAL OF THE PHYSICAL SOCIETY OF JAPAN', 'Schoenholz S, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Barnes D, 2016, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Mézard M, 2017, PHYSICAL REVIEW. E', 'Likhomanenko T, 2015, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Ntampaka M, 2016, THE ASTROPHYSICAL JOURNAL', 'Firth A, 2003, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Mavadia S, 2017, NATURE COMMUNICATIONS', 'Kirrander A, 2015, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Stevens J, 2013, JOURNAL OF INSTRUMENTATION', 'Li N, 2016, THE ASTROPHYSICAL JOURNAL', 'Ravanbakhsh S, 2017, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Novikov A, 2016, ARXIV (CORNELL UNIVERSITY)', 'Sutherland D, 2012, ARXIV (CORNELL UNIVERSITY)', 'Flach P, 2015, ', 'Teymur O, 2016, ', 'Biamonte J, 2017, NATURE', 'Bronstein M, 2017, IEEE SIGNAL PROCESSING MAGAZINE', ', 2007, CHOICE REVIEWS ONLINE', 'Germain M, 2015, ', 'Smith J, 2017, CHEMICAL SCIENCE', 'Mézard M, 2009, ', 'Behler J, 2016, THE JOURNAL OF CHEMICAL PHYSICS', 'Nieuwenburg E, 2017, NATURE PHYSICS', 'Gastegger M, 2017, CHEMICAL SCIENCE', 'Wetzel S, 2017, PHYSICAL REVIEW. E', 'Deng D, 2017, PHYSICAL REVIEW X', 'Kull M, 2017, ', 'Paganini M, 2018, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Gao X, 2017, NATURE COMMUNICATIONS', 'Nguyen H, 2017, ADVANCES IN PHYSICS', 'Lanyon B, 2017, NATURE PHYSICS', 'Chen J, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Liu J, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Schawinski K, 2017, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY LETTERS', 'Huang L, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Cai Z, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Koch-Janusz M, 2018, NATURE PHYSICS', 'Torlai G, 2017, PHYSICAL REVIEW LETTERS', 'Lanusse F, 2017, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Arunachalam S, 2017, ACM SIGACT NEWS', 'Schindler F, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Lelarge M, 2018, PROBABILITY THEORY AND RELATED FIELDS', 'Shimmin C, 2017, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Tubiana J, 2017, PHYSICAL REVIEW LETTERS', 'Zhang Y, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Acciarri R, 2017, JOURNAL OF INSTRUMENTATION', 'Varsamopoulos S, 2017, QUANTUM SCIENCE AND TECHNOLOGY', 'Ballard A, 2017, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Coja‐Oghlan A, 2018, ADVANCES IN MATHEMATICS', 'Bradde S, 2017, JOURNAL OF STATISTICAL PHYSICS', 'Liu J, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Ohtsuki T, 2017, JOURNAL OF THE PHYSICAL SOCIETY OF JAPAN', 'Nagai Y, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Barra A, 2018, PHYSICAL REVIEW. E', 'Huang Y, 2021, PHYSICAL REVIEW LETTERS', 'Ilten P, 2017, JOURNAL OF INSTRUMENTATION', 'Miller R, 2016, FARADAY DISCUSSIONS', 'Bellshaw D, 2017, CHEMICAL PHYSICS LETTERS', 'Tramel E, 2018, PHYSICAL REVIEW X', ', 2015, ', 'Shwartz-Ziv R, 2017, ARXIV (CORNELL UNIVERSITY)', 'Law J, 2001, ACM SIGSOFT SOFTWARE ENGINEERING NOTES', 'Shen Y, 2017, NATURE PHOTONICS', 'Zhang L, 2018, PHYSICAL REVIEW LETTERS', 'Faber F, 2017, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Pathak J, 2017, CHAOS AN INTERDISCIPLINARY JOURNAL OF NONLINEAR SCIENCE', 'Becca F, 2017, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Ciliberto C, 2018, PROCEEDINGS OF THE ROYAL SOCIETY A MATHEMATICAL PHYSICAL AND ENGINEERING SCIENCES', 'Mardt A, 2017, NATURE COMMUNICATIONS', 'Wehmeyer C, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Hu W, 2017, PHYSICAL REVIEW. E', 'Nomura Y, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Melnikov A, 2018, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Lubbers N, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Metodiev E, 2017, JOURNAL OF HIGH ENERGY PHYSICS', 'Bukov M, 2018, PHYSICAL REVIEW X', 'Zhang Y, 2017, PHYSICAL REVIEW LETTERS', 'Zhang P, 2018, PHYSICAL REVIEW LETTERS', 'Hezaveh Y, 2017, NATURE', 'Han Z, 2018, PHYSICAL REVIEW X', 'Glasser I, 2018, PHYSICAL REVIEW X', 'Beach M, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Haah J, 2017, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Bereau T, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Venderley J, 2018, PHYSICAL REVIEW LETTERS', 'Schneider E, 2017, PHYSICAL REVIEW LETTERS', 'Advani M, 2020, NEURAL NETWORKS', 'Wang C, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Baireuther P, 2018, QUANTUM', 'Saito H, 2017, JOURNAL OF THE PHYSICAL SOCIETY OF JAPAN', 'Carifio J, 2017, JOURNAL OF HIGH ENERGY PHYSICS', 'Saito H, 2017, JOURNAL OF THE PHYSICAL SOCIETY OF JAPAN', 'Benedetti M, 2017, PHYSICAL REVIEW X', 'Krastanov S, 2017, SCIENTIFIC REPORTS', 'Kaubruegger R, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Martiniani S, 2019, PHYSICAL REVIEW X', 'Clark S, 2018, JOURNAL OF PHYSICS A MATHEMATICAL AND THEORETICAL', 'Rocchetto A, 2018, NPJ QUANTUM INFORMATION', 'Schmitt M, 2018, SCIPOST PHYSICS', 'Arsenault L, 2017, INVERSE PROBLEMS', 'Teng P, 2018, PHYSICAL REVIEW. E', 'Barbier J, 2017, ', 'Cocco S, 2017, PHYSICA A STATISTICAL MECHANICS AND ITS APPLICATIONS', 'Apollinari G, 2015, ARXIV (CORNELL UNIVERSITY)', 'Putzky P, 2017, ARXIV (CORNELL UNIVERSITY)', 'Broecker P, 2017, ARXIV (CORNELL UNIVERSITY)', 'Louppe G, 2017, ARXIV (CORNELL UNIVERSITY)', 'Cristoforetti M, 2017, ARXIV (CORNELL UNIVERSITY)', 'Frate M, 2017, ARXIV (CORNELL UNIVERSITY)', 'Pang L, 2016, ARXIV (CORNELL UNIVERSITY)', 'Izmailov P, 2017, ARXIV (CORNELL UNIVERSITY)', 'Schütt K, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Schuld M, 2019, PHYSICAL REVIEW LETTERS', 'Pathak J, 2018, PHYSICAL REVIEW LETTERS', 'Dunjko V, 2018, REPORTS ON PROGRESS IN PHYSICS', 'Smith J, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Chmiela S, 2018, NATURE COMMUNICATIONS', 'Alet F, 2018, COMPTES RENDUS PHYSIQUE', 'Yao K, 2018, CHEMICAL SCIENCE', 'Deng D, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Paganini M, 2018, PHYSICAL REVIEW LETTERS', 'Deringer V, 2018, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Kamath A, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Fösel T, 2018, PHYSICAL REVIEW X', 'Pang L, 2018, NATURE COMMUNICATIONS', 'Nguyen T, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Alsing J, 2018, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Li S, 2018, PHYSICAL REVIEW LETTERS', 'Carleo G, 2018, NATURE COMMUNICATIONS', 'Torlai G, 2018, PHYSICAL REVIEW LETTERS', 'Komiske P, 2018, JOURNAL OF HIGH ENERGY PHYSICS', 'Chung S, 2018, PHYSICAL REVIEW X', 'Charnock T, 2018, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Kalantre S, 2019, NPJ QUANTUM INFORMATION', 'Hashimoto K, 2018, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Stoudenmire E, 2018, QUANTUM SCIENCE AND TECHNOLOGY', 'Sosso G, 2018, MOLECULAR SIMULATION', 'Czischek S, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Maskara N, 2019, PHYSICAL REVIEW. A/PHYSICAL REVIEW, A', 'Sidky H, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Rodríguez A, 2018, COMPUTATIONAL ASTROPHYSICS AND COSMOLOGY', 'Nagai R, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Shanahan P, 2018, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Nieuwenburg E, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Iakovlev I, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Chen C, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Decelle A, 2017, EUROPHYSICS LETTERS (EPL)', 'Wang C, 2018, FRONTIERS OF PHYSICS', 'Agresti I, 2019, PHYSICAL REVIEW X', 'Anelli A, 2018, PHYSICAL REVIEW MATERIALS', 'Tubiana J, 2019, ELIFE', 'Schmidt E, 2018, COMPUTATIONAL MATERIALS SCIENCE', 'Charnock T, 2018, ARXIV (CORNELL UNIVERSITY)', 'Aaronson S, 2018, SIAM JOURNAL ON COMPUTING', 'Lee J, 2017, ARXIV (CORNELL UNIVERSITY)', 'Torlai G, 2017, ARXIV (CORNELL UNIVERSITY)', 'Kondor R, 2018, ARXIV (CORNELL UNIVERSITY)', 'Tanaka A, 2017, ARXIV (CORNELL UNIVERSITY)', 'Casado M, 2017, ARXIV (CORNELL UNIVERSITY)', 'Regier J, 2018, ARXIV (CORNELL UNIVERSITY)', 'Jain A, 2018, ARXIV (CORNELL UNIVERSITY)', 'Butler K, 2018, NATURE', 'Lin X, 2018, SCIENCE', 'Havlíček V, 2019, NATURE', 'Ambrogio S, 2018, NATURE', 'Schuld M, 2018, QUANTUM SCIENCE AND TECHNOLOGY', 'Radovic A, 2018, NATURE', 'Bartók A, 2018, PHYSICAL REVIEW X', 'Duarte J, 2018, JOURNAL OF INSTRUMENTATION', 'Guest D, 2018, ANNUAL REVIEW OF NUCLEAR AND PARTICLE SCIENCE', 'Paruzzo F, 2018, NATURE COMMUNICATIONS', 'Choo K, 2018, PHYSICAL REVIEW LETTERS', 'Albertsson K, 2018, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Wu D, 2019, PHYSICAL REVIEW LETTERS', 'Reddy G, 2018, NATURE', 'Brehmer J, 2018, PHYSICAL REVIEW LETTERS', 'Brehmer J, 2018, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Gabrié M, 2019, JOURNAL OF STATISTICAL MECHANICS THEORY AND EXPERIMENT', 'Sifain A, 2018, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Huembeli P, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Komiske P, 2018, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Liang X, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Rupp M, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Fournier R, 2020, PHYSICAL REVIEW LETTERS', 'Hsu Y, 2018, PHYSICAL REVIEW LETTERS', 'Engel E, 2018, NATURE COMMUNICATIONS', 'Eickenberg M, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Sun N, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Greitemann J, 2019, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Yoon H, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Bukov M, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Hashimoto K, 2018, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Lu S, 2019, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Huembeli P, 2019, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Guo C, 2018, PHYSICAL REVIEW. E', 'Banchi L, 2018, NEW JOURNAL OF PHYSICS', 'Seif A, 2018, JOURNAL OF PHYSICS B ATOMIC MOLECULAR AND OPTICAL PHYSICS', 'Zhang W, 2019, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Saito H, 2018, JOURNAL OF THE PHYSICAL SOCIETY OF JAPAN', 'Leistedt B, 2019, THE ASTROPHYSICAL JOURNAL', 'Liu Y, 2018, ARXIV (CORNELL UNIVERSITY)', 'Steinbrecher G, 2019, NPJ QUANTUM INFORMATION', 'Papamakarios G, 2018, ARXIV (CORNELL UNIVERSITY)', 'Jónsson B, 2018, ARXIV (CORNELL UNIVERSITY)', 'Song M, 2018, ARXIV (CORNELL UNIVERSITY)', 'Kondor R, 2018, ARXIV (CORNELL UNIVERSITY)', 'Glasser I, 2018, ARXIV (CORNELL UNIVERSITY)', 'Morningstar W, 2018, ARXIV (CORNELL UNIVERSITY)', 'Wang C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Golkar S, 2018, ARXIV (CORNELL UNIVERSITY)', 'LeCun Y, 2015, NATURE', 'Cong I, 2019, NATURE PHYSICS', 'Zhang L, 2019, PHYSICAL REVIEW MATERIALS', 'Carrasquilla J, 2019, NATURE MACHINE INTELLIGENCE', 'Hartmann M, 2019, PHYSICAL REVIEW LETTERS', 'Sharir O, 2020, PHYSICAL REVIEW LETTERS', 'Rem B, 2019, NATURE PHYSICS', 'Nagy A, 2019, PHYSICAL REVIEW LETTERS', 'Vicentini F, 2019, PHYSICAL REVIEW LETTERS', 'Komiske P, 2019, JOURNAL OF HIGH ENERGY PHYSICS', 'Albergo M, 2019, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'He S, 2019, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Levine Y, 2019, PHYSICAL REVIEW LETTERS', 'Barbier J, 2019, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Doggen E, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Yoshioka N, 2019, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Luo D, 2019, PHYSICAL REVIEW LETTERS', 'Zhang Y, 2019, NATURE', 'Torlai G, 2019, PHYSICAL REVIEW LETTERS', 'Gray J, 2018, PHYSICAL REVIEW LETTERS', 'Cheng S, 2019, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Alsing J, 2019, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Salamani D, 2018, ', 'Peel A, 2019, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Morningstar W, 2019, THE ASTROPHYSICAL JOURNAL', 'Liu K, 2019, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Mills K, 2019, CHEMICAL SCIENCE', 'Armitage T, 2019, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY', 'Stokes J, 2019, ENTROPY', 'Kashiwa K, 2019, PROGRESS OF THEORETICAL AND EXPERIMENTAL PHYSICS', 'Borin A, 2020, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Tsaris A, 2018, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Zheng Y, 2019, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Quek Y, 2021, NPJ QUANTUM INFORMATION', 'Cohen T, 2019, ARXIV (CORNELL UNIVERSITY)', ', 2016, ', 'Farrell S, 2018, ARXIV (CORNELL UNIVERSITY)', 'Zhang X, 2019, ARXIV (CORNELL UNIVERSITY)', 'Ntampaka M, 2019, ARXIV (CORNELL UNIVERSITY)', 'Kochkov D, 2018, ARXIV (CORNELL UNIVERSITY)', 'Albertsson K, 2018, ARXIV (CORNELL UNIVERSITY)', 'Xu Q, 2018, ARXIV (CORNELL UNIVERSITY)', 'Cranmer K, 2019, ARXIV (CORNELL UNIVERSITY)', 'Choma N, 2018, ARXIV (CORNELL UNIVERSITY)', 'Bozson A, 2018, ARXIV (CORNELL UNIVERSITY)', ', 2002, THE MIT PRESS EBOOKS', 'Yu B, 2018, FRONTIERS OF INFORMATION TECHNOLOGY &amp; ELECTRONIC ENGINEERING', 'Vidal G, 2007, PHYSICAL REVIEW LETTERS', 'Jaroslav Ř, 2004, LECTURE NOTES IN PHYSICS', 'Noé F, 2019, SCIENCE', 'Han J, 2019, JOURNAL OF COMPUTATIONAL PHYSICS', 'Yang J, 2020, SCIENCE', 'Brehmer J, 2020, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Louppe G, 2017, ORBI (UNIVERSITY OF LIÈGE)', 'Stankus B, 2019, NATURE CHEMISTRY', 'Yong H, 2020, NATURE COMMUNICATIONS', 'Lang D, 2016, ASTROPHYSICS SOURCE CODE LIBRARY', 'Ronhovde P, 2011, THE EUROPEAN PHYSICAL JOURNAL E', 'Rocchetto A, 2019, PUBMED', 'Fabiani G, 2019, SCIPOST PHYSICS', 'Morningstar A, 2018, ARXIV (CORNELL UNIVERSITY)', 'Schoenholz S, 2019, ARXIV (CORNELL UNIVERSITY)', 'Cranmer K, 2016, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Mardt A, 2018, REPEC: RESEARCH PAPERS IN ECONOMICS', ', , PORTSMOUTH RESEARCH PORTAL (UNIVERSITY OF PORTSMOUTH)', 'A. C, 2003, ', 'Gao X, , REPEC: RESEARCH PAPERS IN ECONOMICS', 'Ritzmann U, 2018, ARXIV (CORNELL UNIVERSITY)', 'Zhang Y, , REPEC: RESEARCH PAPERS IN ECONOMICS', 'Justin S, 2013, DSPACE@MIT (MASSACHUSETTS INSTITUTE OF TECHNOLOGY)', 'Aubin B, 2018, HAL (LE CENTRE POUR LA COMMUNICATION SCIENTIFIQUE DIRECTE)', 'Hermans J, 2019, ARXIV (CORNELL UNIVERSITY)', 'Lanusse F, 2019, ARXIV (CORNELL UNIVERSITY)', 'Hofmann T, 2008, ', 'F B, 2017, MPG.PURE (MAX PLANCK SOCIETY)', 'I. G, 2018, MAX PLANCK DIGITAL LIBRARY', 'T. F, 2018, MPG.PURE (MAX PLANCK SOCIETY)', 'Nguyen T, 2018, OPEN MIND', 'Robin A, 2014, SPRINGER LINK (CHIBA INSTITUTE OF TECHNOLOGY)', 'Ntampaka M, 2019, DSPACE@MIT (MASSACHUSETTS INSTITUTE OF TECHNOLOGY)', 'Rocchetto A, 2018, UCL DISCOVERY (UNIVERSITY COLLEGE LONDON)', 'F. M, 2009, MPG.PURE (MAX PLANCK SOCIETY)', 'Sarao M, 2020, HAL (LE CENTRE POUR LA COMMUNICATION SCIENTIFIQUE DIRECTE)', 'vloncar, 2021, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', ', , ANET (UNIVERSITY OF ANTWERP)', 'Komiske P, 2019, DSPACE@MIT (MASSACHUSETTS INSTITUTE OF TECHNOLOGY)', 'Komiske P, 2018, OSTI OAI (U.S. DEPARTMENT OF ENERGY OFFICE OF SCIENTIFIC AND TECHNICAL INFORMATION)', 'Donoho D, 2006, IEEE TRANSACTIONS ON INFORMATION THEORY', ', 1996, COMPUTERS &amp; MATHEMATICS WITH APPLICATIONS', 'Valiant L, 1984, COMMUNICATIONS OF THE ACM', 'Ziegel E, 1989, TECHNOMETRICS', 'Frenkelʹ I, 1934, CLARENDON PRESS EBOOKS', 'Wu Z, 2015, ', 'Dean D, 1996, ', 'Carleo G, 2018, REPEC: RESEARCH PAPERS IN ECONOMICS', 'Rodríguez A, 2018, REPOSITORY FOR PUBLICATIONS AND RESEARCH DATA (ETH ZURICH)', 'Wecker D, 2016, PHYSICAL REVIEW. A/PHYSICAL REVIEW, A', 'L B, 2018, UCL DISCOVERY (UNIVERSITY COLLEGE LONDON)', 'E F, 2002, ', 'M. S, 2018, MAX PLANCK DIGITAL LIBRARY', 'Tiersch M, 2015, SCIENTIFIC REPORTS', ', 2005, IEEE TRANSACTIONS ON INFORMATION THEORY', ', 1992, ', 'Nathan K, 2018, DSPACE@MIT (MASSACHUSETTS INSTITUTE OF TECHNOLOGY)', 'Oliveira L, 2022, OSTI OAI (U.S. DEPARTMENT OF ENERGY OFFICE OF SCIENTIFIC AND TECHNICAL INFORMATION)', ', 2013, PROBABILITY THEORY AND RELATED FIELDS', ', 2018, ', 'Ilten P, 2015, CERN DOCUMENT SERVER (EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', ', 1990, ', ', 2017, ', ', 2008, ADVANCES IN OPTICAL TECHNOLOGIES', 'Mannelli S, 2019, ARXIV (CORNELL UNIVERSITY)', ', 2014, ', 'Kagan M, 2016, OPEN REPOSITORY AND BIBLIOGRAPHY (UNIVERSITY OF LIÈGE)', 'Kondor R, 2018, ARXIV (CORNELL UNIVERSITY)', 'Cohen T, 2018, ARXIV (CORNELL UNIVERSITY)', 'Louppe G, 2020, OPEN REPOSITORY AND BIBLIOGRAPHY (UNIVERSITY OF LIÈGE)', 'Kondor R, 2018, ARXIV (CORNELL UNIVERSITY)', ', 2018, ', 'Levine Y, 2017, ARXIV (CORNELL UNIVERSITY)', 'Frate M, 2017, ARXIV (CORNELL UNIVERSITY)', 'Glasser I, 2018, ARXIV (CORNELL UNIVERSITY)', 'Baydin A, 2018, ARXIV (CORNELL UNIVERSITY)', 'Goldt S, 2019, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -8427,7 +8435,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>3485</v>
+        <v>3489</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -8451,7 +8459,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['Department of Health Care Policy, Harvard Medical School, Boston, and the Department of Medical Ethics and Health Policy, Perelman School of Medicine', 'Department of Health Care Management, Wharton School, University of Pennsylvania, Philadelphia']</t>
+          <t>["From the Department of Emergency Medicine, Harvard Medical School and Brigham and Women's Hospital, and the Department of Health Care Policy, Harvard Medical School, Boston (Z.O.); and the Department of Medical Ethics and Health Policy, Perelman School of Medicine, and the Department of Health Care Management, Wharton School, University of Pennsylvania, Philadelphia (E.J.E.)", 'Department of Health Care Policy, Harvard Medical School, Boston, and the Department of Medical Ethics and Health Policy, Perelman School of Medicine', "From the Department of Emergency Medicine, Harvard Medical School and Brigham and Women's Hospital, and the Department of Health Care Policy, Harvard Medical School, Boston (Z.O.); and the Department of Medical Ethics and Health Policy, Perelman School of Medicine, and the Department of Health Care Management, Wharton School, University of Pennsylvania, Philadelphia (E.J.E.)", 'Department of Health Care Management, Wharton School, University of Pennsylvania, Philadelphia']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
@@ -8487,7 +8495,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>['US']</t>
+          <t>['US', 'TW']</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8598,7 +8606,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>['Papernot N, 2016, ', 'Vitter J, 1985, ACM TRANSACTIONS ON MATHEMATICAL SOFTWARE', 'B. B, 2013, ', 'Sharif M, 2016, ', 'Stallkamp J, 2012, NEURAL NETWORKS', 'Huang L, 2011, ', 'Barreno M, 2006, ', 'Šrndić N, 2014, ', 'Papernot N, 2016, ', 'Xu W, 2016, ', ', 2007, ', 'Rashidi Y, 2015, ', ', 2014, THE MIT PRESS EBOOKS', 'Calders T, 2014, LECTURE NOTES IN COMPUTER SCIENCE', ', 2021, WILEY SERIES IN PROBABILITY AND STATISTICS', 'Tramèr F, 2016, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>['Papernot N, 2016, ', 'Vitter J, 1985, ACM TRANSACTIONS ON MATHEMATICAL SOFTWARE', 'Biggio B, 2013, ', 'Sharif M, 2016, ', 'Stallkamp J, 2012, NEURAL NETWORKS', 'Huang L, 2011, ', 'Barreno M, 2006, ', 'Šrndić N, 2014, ', 'Papernot N, 2016, ', 'Xu W, 2016, ', ', 2007, ', 'Rashidi Y, 2015, ', ', 2014, THE MIT PRESS EBOOKS', 'Calders T, 2014, LECTURE NOTES IN COMPUTER SCIENCE', ', 2021, WILEY SERIES IN PROBABILITY AND STATISTICS', 'Tramèr F, 2016, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -8626,22 +8634,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2157331557</t>
+          <t>https://openalex.org/W1563088657</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>10.3115/v1/d14-1179</t>
+          <t>10.1017/cbo9780511801389</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Learning Phrase Representations using RNN Encoder–Decoder for Statistical Machine Translation</t>
+          <t>An Introduction to Support Vector Machines and Other Kernel-based Learning Methods</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8651,60 +8659,60 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>preprint</t>
+          <t>book</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>24405</v>
-      </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
+        <v>13880</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>CAMBRIDGE UNIVERSITY PRESS EBOOKS</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Cambridge University Press eBooks</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>['Kyunghyun Cho', 'Bart van Merriënboer', 'Çağlar Gülçehre', 'Dzmitry Bahdanau', 'Fethi Bougares', 'Holger Schwenk', 'Yoshua Bengio']</t>
+          <t>['Nello Cristianini', 'John Shawe‐Taylor']</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>['Kyunghyun Cho', 'Bart van Merrienboer', 'Caglar Gulcehre', 'Dzmitry Bahdanau', 'Fethi Bougares', 'Holger Schwenk', 'Yoshua Bengio']</t>
+          <t>['Nello Cristianini', 'John Shawe-Taylor']</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>["Laboratoire d'Informatique de l'Université du Maine", "Laboratoire d'Informatique de l'Université du Maine", "Laboratoire d'Informatique de l'Université du Maine", 'AT&amp;T; Alcatel-Lucent; Ecole Polytechnique de Montreal']</t>
+          <t>['University of Bristol', 'Royal Holloway, University of London', '†Royal Holloway, University of London']</t>
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Kyunghyun Cho, Bart van Merriënboer, Caglar Gulcehre, Dzmitry Bahdanau, Fethi Bougares, Holger Schwenk, Yoshua Bengio. Proceedings of the 2014 Conference on Empirical Methods in Natural Language Processing (EMNLP). 2014.</t>
+          <t>This is the first comprehensive introduction to Support Vector Machines (SVMs), a generation learning system based on recent advances in statistical learning theory. SVMs deliver state-of-the-art performance in real-world applications such as text categorisation, hand-written character recognition, image classification, biosequences analysis, etc., and are now established as one of the standard tools for machine learning and data mining. Students will find the book both stimulating and accessible, while practitioners will be guided smoothly through the material required for a good grasp of the theory and its applications. The concepts are introduced gradually in accessible and self-contained stages, while the presentation is rigorous and thorough. Pointers to relevant literature and web sites containing software ensure that it forms an ideal starting point for further study. Equally, the book and its associated web site will guide practitioners to updated literature, new applications, and on-line software.</t>
         </is>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>1724</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>['Machine translation', 'Computer science', 'Phrase', 'Natural language processing', 'Artificial intelligence', 'Encoder', 'Translation (biology)', 'Statistical learning', 'Speech recognition']</t>
+          <t>['Computer science', 'GRASP', 'Support vector machine', 'Point (geometry)', 'Artificial intelligence', 'Statistical learning theory', 'Presentation (obstetrics)', 'Machine learning', 'Software', 'Kernel (algebra)', 'Data science', 'Software engineering', 'Programming language']</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>['US', 'DE', 'CA']</t>
+          <t>['GB']</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>['Hochreiter S, 1997, NEURAL COMPUTATION', 'Krizhevsky A, 2017, COMMUNICATIONS OF THE ACM', 'Glorot X, 2012, ', 'Koehn P, 2003, ', 'Koehn P, 2005, ', 'Graves A, 2012, STUDIES IN COMPUTATIONAL INTELLIGENCE', 'Dahl G, 2011, IEEE TRANSACTIONS ON AUDIO SPEECH AND LANGUAGE PROCESSING', 'Kalchbrenner N, 2013, ', 'Socher R, 2011, ', 'Pascanu R, 2014, INTERNATIONAL CONFERENCE ON LEARNING REPRESENTATIONS', 'Zou W, 2013, ', 'Moore R, 2010, ', 'Schwenk H, 2006, COMPUTER SPEECH &amp; LANGUAGE', 'Axelrod A, 2011, ', 'Devlin J, 2014, ', 'Bengio Y, 2013, ', 'Marcu D, 2002, ', 'Saxe A, 2014, INTERNATIONAL CONFERENCE ON LEARNING REPRESENTATIONS', 'Auli M, 2013, ', 'Vaswani A, 2013, ', 'Le H, 2012, HAL (LE CENTRE POUR LA COMMUNICATION SCIENTIFIQUE DIRECTE)', 'Schwenk H, 2014, ', 'Mikolov T, 2013, ARXIV (CORNELL UNIVERSITY)', 'Zeiler M, 2012, ARXIV (CORNELL UNIVERSITY)', 'Bastien F, 2012, ARXIV (CORNELL UNIVERSITY)', 'Goodfellow I, 2013, ', 'Schwenk H, 2025, ', 'P S, 2014, ARXIV (CORNELL UNIVERSITY)', 'Maaten L, 2013, ARXIV (CORNELL UNIVERSITY)', 'Gao J, 2013, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -8720,34 +8728,34 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cho K, 2014, </t>
+          <t>Cristianini N, 2000, CAMBRIDGE UNIVERSITY PRESS EBOOKS</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cho K, 2014, </t>
+          <t>Cristianini N, 2000, CAMBRIDGE UNIVERSITY PRESS EBOOKS</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://openalex.org/W1563088657</t>
+          <t>https://openalex.org/W2157331557</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>10.1017/cbo9780511801389</t>
+          <t>10.3115/v1/d14-1179</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>An Introduction to Support Vector Machines and Other Kernel-based Learning Methods</t>
+          <t>Learning Phrase Representations using RNN Encoder–Decoder for Statistical Machine Translation</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8757,60 +8765,60 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>preprint</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>13876</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>CAMBRIDGE UNIVERSITY PRESS EBOOKS</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Cambridge University Press eBooks</t>
-        </is>
-      </c>
+        <v>24415</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>['Nello Cristianini', 'John Shawe‐Taylor']</t>
+          <t>['Kyunghyun Cho', 'Bart van Merriënboer', 'Çağlar Gülçehre', 'Dzmitry Bahdanau', 'Fethi Bougares', 'Holger Schwenk', 'Yoshua Bengio']</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>['Nello Cristianini', 'John Shawe-Taylor']</t>
+          <t>['Kyunghyun Cho', 'Bart van Merrienboer', 'Caglar Gulcehre', 'Dzmitry Bahdanau', 'Fethi Bougares', 'Holger Schwenk', 'Yoshua Bengio']</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['University of Bristol', 'Royal Holloway, University of London', '†Royal Holloway, University of London']</t>
+          <t>["Laboratoire d'Informatique de l'Université du Maine", "Laboratoire d'Informatique de l'Université du Maine", "Laboratoire d'Informatique de l'Université du Maine", 'AT&amp;T; Alcatel-Lucent; Ecole Polytechnique de Montreal']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>This is the first comprehensive introduction to Support Vector Machines (SVMs), a generation learning system based on recent advances in statistical learning theory. SVMs deliver state-of-the-art performance in real-world applications such as text categorisation, hand-written character recognition, image classification, biosequences analysis, etc., and are now established as one of the standard tools for machine learning and data mining. Students will find the book both stimulating and accessible, while practitioners will be guided smoothly through the material required for a good grasp of the theory and its applications. The concepts are introduced gradually in accessible and self-contained stages, while the presentation is rigorous and thorough. Pointers to relevant literature and web sites containing software ensure that it forms an ideal starting point for further study. Equally, the book and its associated web site will guide practitioners to updated literature, new applications, and on-line software.</t>
+          <t>Kyunghyun Cho, Bart van Merriënboer, Caglar Gulcehre, Dzmitry Bahdanau, Fethi Bougares, Holger Schwenk, Yoshua Bengio. Proceedings of the 2014 Conference on Empirical Methods in Natural Language Processing (EMNLP). 2014.</t>
         </is>
       </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1724</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>['Computer science', 'GRASP', 'Support vector machine', 'Point (geometry)', 'Artificial intelligence', 'Statistical learning theory', 'Presentation (obstetrics)', 'Machine learning', 'Software', 'Kernel (algebra)', 'Data science', 'Software engineering', 'Programming language']</t>
+          <t>['Machine translation', 'Computer science', 'Phrase', 'Natural language processing', 'Artificial intelligence', 'Encoder', 'Translation (biology)', 'Statistical learning', 'Speech recognition']</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>['GB']</t>
+          <t>['US', 'DE', 'CA']</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Hochreiter S, 1997, NEURAL COMPUTATION', 'Krizhevsky A, 2017, COMMUNICATIONS OF THE ACM', 'Glorot X, 2012, ', 'Koehn P, 2003, ', 'Koehn P, 2005, ', 'Graves A, 2012, STUDIES IN COMPUTATIONAL INTELLIGENCE', 'Dahl G, 2011, IEEE TRANSACTIONS ON AUDIO SPEECH AND LANGUAGE PROCESSING', 'Kalchbrenner N, 2013, ', 'Socher R, 2011, ', 'Pascanu R, 2014, INTERNATIONAL CONFERENCE ON LEARNING REPRESENTATIONS', 'Zou W, 2013, ', 'Moore R, 2010, ', 'Schwenk H, 2006, COMPUTER SPEECH &amp; LANGUAGE', 'Axelrod A, 2011, ', 'Devlin J, 2014, ', 'Bengio Y, 2013, ', 'Marcu D, 2002, ', 'Saxe A, 2014, INTERNATIONAL CONFERENCE ON LEARNING REPRESENTATIONS', 'Auli M, 2013, ', 'Vaswani A, 2013, ', 'Le H, 2012, HAL (LE CENTRE POUR LA COMMUNICATION SCIENTIFIQUE DIRECTE)', 'Schwenk H, 2014, ', 'Mikolov T, 2013, ARXIV (CORNELL UNIVERSITY)', 'Zeiler M, 2012, ARXIV (CORNELL UNIVERSITY)', 'Bastien F, 2012, ARXIV (CORNELL UNIVERSITY)', 'Goodfellow I, 2013, ', 'Schwenk H, 2025, ', 'P S, 2014, ARXIV (CORNELL UNIVERSITY)', 'Maaten L, 2013, ARXIV (CORNELL UNIVERSITY)', 'Gao J, 2013, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -8826,12 +8834,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>Cristianini N, 2000, CAMBRIDGE UNIVERSITY PRESS EBOOKS</t>
+          <t xml:space="preserve">Cho K, 2014, </t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>Cristianini N, 2000, CAMBRIDGE UNIVERSITY PRESS EBOOKS</t>
+          <t xml:space="preserve">Cho K, 2014, </t>
         </is>
       </c>
     </row>
@@ -8928,7 +8936,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>['Tibshirani R, 1996, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Maaten L, 2008, JOURNAL OF MACHINE LEARNING RESEARCH', 'Zou H, 2005, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Hastie T, 2013, ', 'Ester M, 1996, ', 'Esteva A, 2017, NATURE', 'Kühn M, 2008, JOURNAL OF STATISTICAL SOFTWARE', 'Jain A, 2009, PATTERN RECOGNITION LETTERS', 'Kircher M, 2014, NATURE GENETICS', 'Abadi M, 2016, OPERATING SYSTEMS DESIGN AND IMPLEMENTATION', 'Noble W, 2006, NATURE BIOTECHNOLOGY', 'Alipanahi B, 2015, NATURE BIOTECHNOLOGY', 'Chothia C, 1986, THE EMBO JOURNAL', 'Libbrecht M, 2015, NATURE REVIEWS GENETICS', 'Bengio Y, 2012, LECTURE NOTES IN COMPUTER SCIENCE', 'Qian N, 1988, JOURNAL OF MOLECULAR BIOLOGY', 'Mayr A, 2016, FRONTIERS IN ENVIRONMENTAL SCIENCE', 'Pires D, 2014, NUCLEIC ACIDS RESEARCH', 'Quang D, 2016, NUCLEIC ACIDS RESEARCH', 'Hopf T, 2017, NATURE BIOTECHNOLOGY', 'Ben‐Hur A, 2009, METHODS IN MOLECULAR BIOLOGY', 'Crick F, 1989, NATURE', 'Ben‐Hur A, 2008, PLOS COMPUTATIONAL BIOLOGY', 'Moult J, 2013, PROTEINS STRUCTURE FUNCTION AND BIOINFORMATICS', 'Tarca A, 2007, PLOS COMPUTATIONAL BIOLOGY', 'Zeng H, 2016, BIOINFORMATICS', 'Cheng H, 2014, PLOS COMPUTATIONAL BIOLOGY', 'Nugent T, 2009, BMC BIOINFORMATICS', 'Zhang Y, 2004, JOURNAL OF COMPUTATIONAL CHEMISTRY', 'Wang C, 2016, JOURNAL OF COMPUTATIONAL CHEMISTRY', 'Wei Q, 2013, PLOS ONE', 'Kircher M, 2014, ', 'Bao L, 2005, NUCLEIC ACIDS RESEARCH', 'Soren S, 2007, ANU OPEN RESEARCH (AUSTRALIAN NATIONAL UNIVERSITY)', 'Cozzetto D, 2016, SCIENTIFIC REPORTS', 'Chen L, 2016, BMC BIOINFORMATICS', 'Wang Y, 2016, SCIENTIFIC REPORTS', 'Li Y, 2017, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'List M, 2017, PLOS COMPUTATIONAL BIOLOGY', 'Walsh I, 2015, BRIEFINGS IN BIOINFORMATICS', 'Teodoro M, 2003, JOURNAL OF COMPUTATIONAL BIOLOGY', 'Zhang Z, 2012, BIOINFORMATICS', 'Söding J, 2011, CURRENT OPINION IN STRUCTURAL BIOLOGY', 'Kandoi G, 2015, FRONTIERS IN PHYSIOLOGY', 'deFigueiredo R, 1995, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Haario H, 1998, CHEMOMETRICS AND INTELLIGENT LABORATORY SYSTEMS', 'Pedregosa F, 2012, ARXIV (CORNELL UNIVERSITY)', 'Konečný J, 2016, ARXIV (CORNELL UNIVERSITY)', 'Kelley D, 2016, GENOME RESEARCH', 'Shrikumar A, 2017, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'LeCun Y, 2015, NATURE', 'Steinegger M, 2017, NATURE BIOTECHNOLOGY', 'Ching T, 2018, JOURNAL OF THE ROYAL SOCIETY INTERFACE', 'Dührkop K, 2019, NATURE METHODS', 'Poplin R, 2018, NATURE BIOTECHNOLOGY', 'Poplin R, 2018, NATURE BIOMEDICAL ENGINEERING', 'Zech J, 2018, PLOS MEDICINE', 'Buchan D, 2019, NUCLEIC ACIDS RESEARCH', 'Žitnik M, 2018, BIOINFORMATICS', 'Zou J, 2018, NATURE GENETICS', 'Pandarinath C, 2018, NATURE METHODS', 'Marblestone A, 2016, ARXIV (CORNELL UNIVERSITY)', 'Rappoport N, 2018, NUCLEIC ACIDS RESEARCH', 'Heffernan R, 2017, BIOINFORMATICS', 'Sun T, 2017, BMC BIOINFORMATICS', 'AlQuraishi M, 2019, CELL SYSTEMS', 'Beaulieu‐Jones B, 2019, CIRCULATION CARDIOVASCULAR QUALITY AND OUTCOMES', 'Bzdok D, 2018, NATURE METHODS', 'Nguyen L, 2019, PLOS COMPUTATIONAL BIOLOGY', 'Müller A, 2018, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Gligorijević V, 2018, BIOINFORMATICS', 'Altman N, 2017, NATURE METHODS', 'Avsec Ž, 2019, NATURE BIOTECHNOLOGY', 'Sillitoe I, 2018, NUCLEIC ACIDS RESEARCH', 'AlQuraishi M, 2019, BMC BIOINFORMATICS', 'Chen K, 2019, NATURE METHODS', 'Greener J, 2018, SCIENTIFIC REPORTS', 'Silva J, 2019, PLANT SCIENCE', 'Pagès G, 2019, BIOINFORMATICS', 'Zeng W, 2018, BMC GENOMICS', 'Ingraham J, 2018, INTERNATIONAL CONFERENCE ON LEARNING REPRESENTATIONS', 'Hie B, 2018, SCIENCE', 'Veselkov K, 2019, SCIENTIFIC REPORTS', 'Antczak M, 2019, NATURE COMMUNICATIONS', 'Pérez A, 2018, CURRENT OPINION IN STRUCTURAL BIOLOGY', 'Jumper J, 2018, PLOS COMPUTATIONAL BIOLOGY', 'Paszke A, 2019, ARXIV (CORNELL UNIVERSITY)', 'Abadi M, 2016, ARXIV (CORNELL UNIVERSITY)', 'Gal Y, 2015, ARXIV (CORNELL UNIVERSITY)', 'Fey M, 2019, ARXIV (CORNELL UNIVERSITY)', 'Adebayo J, 2018, ARXIV (CORNELL UNIVERSITY)', 'Pandarinath C, 2017, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Beaulieu‐Jones B, 2017, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Steinegger M, 2019, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Rao R, 2019, PUBMED', 'Zhou N, 2019, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Innes M, 2019, ARXIV (CORNELL UNIVERSITY)', 'Isensee F, 2020, NATURE METHODS', 'Senior A, 2020, NATURE', 'Stokes J, 2020, CELL', 'Geirhos R, 2020, NATURE MACHINE INTELLIGENCE', 'Yang J, 2020, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Zhavoronkov A, 2019, NATURE BIOTECHNOLOGY', 'Tegunov D, 2019, NATURE METHODS', 'Steinegger M, 2019, BMC BIOINFORMATICS', 'Alley E, 2019, NATURE METHODS', 'Moon K, 2019, NATURE BIOTECHNOLOGY', 'Kobak D, 2019, NATURE COMMUNICATIONS', 'Gaínza P, 2019, NATURE METHODS', 'Noé F, 2019, SCIENCE', 'Myszczynska M, 2020, NATURE REVIEWS NEUROLOGY', 'Schmauch B, 2020, NATURE COMMUNICATIONS', 'Zhou N, 2019, GENOME BIOLOGY', 'Das P, 2021, NATURE BIOMEDICAL ENGINEERING', 'Liebal U, 2020, METABOLITES', 'Li W, 2019, FRONTIERS IN GENETICS', 'Fudenberg G, 2020, NATURE METHODS', 'Yuan Y, 2019, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Strokach A, 2020, CELL SYSTEMS', 'Livesey B, 2020, MOLECULAR SYSTEMS BIOLOGY', 'Jones D, 2019, NATURE REVIEWS MOLECULAR CELL BIOLOGY', 'Linder J, 2020, CELL SYSTEMS', 'Kantz E, 2019, ANALYTICAL CHEMISTRY', 'Si D, 2020, SCIENTIFIC REPORTS', 'Driscoll M, 2019, NATURE METHODS', 'Lopez R, 2020, MOLECULAR SYSTEMS BIOLOGY', 'Smith A, 2020, BMC BIOINFORMATICS', 'Gligorijević V, 2021, ', 'Kopp W, 2020, NATURE COMMUNICATIONS', 'Blaom A, 2020, THE JOURNAL OF OPEN SOURCE SOFTWARE', 'Schreiber J, 2020, GENOME BIOLOGY', 'Yao R, 2019, BIOINFORMATICS', 'Schoenholz S, 2019, ARXIV (CORNELL UNIVERSITY)', 'Elnaggar A, 2020, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Hopf T, 2015, ARXIV (CORNELL UNIVERSITY)', 'Yang J, 2019, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Anishchenko I, 2020, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Hiranuma N, 2020, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Gligorijevic V, 2019, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Wang Y, 2020, ARXIV (CORNELL UNIVERSITY)', 'Jumper J, 2021, NATURE', 'Roberts M, 2020, RESEARCH EXPLORER (THE UNIVERSITY OF MANCHESTER)', 'Roberts M, 2021, NATURE MACHINE INTELLIGENCE', 'Gligorijević V, 2021, NATURE COMMUNICATIONS', 'Zhong E, 2021, NATURE METHODS', 'Kryshtafovych A, 2019, PROTEINS STRUCTURE FUNCTION AND BIOINFORMATICS', 'Wang J, 2021, NATURE COMMUNICATIONS', 'Stokes J, 2020, CELL', 'Hiranuma N, 2021, NATURE COMMUNICATIONS', 'Xu J, 2021, NATURE MACHINE INTELLIGENCE', 'Munro D, 2020, BIOINFORMATICS', 'Rappoport N, 2018, NUCLEIC ACIDS RESEARCH']</t>
+          <t>['Tibshirani R, 1996, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Maaten L, 2008, JOURNAL OF MACHINE LEARNING RESEARCH', 'Zou H, 2005, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Hastie T, 2013, ', 'Ester M, 1996, ', 'Esteva A, 2017, NATURE', 'Kühn M, 2008, JOURNAL OF STATISTICAL SOFTWARE', 'Jain A, 2009, PATTERN RECOGNITION LETTERS', 'Kircher M, 2014, NATURE GENETICS', 'Abadi M, 2016, OPERATING SYSTEMS DESIGN AND IMPLEMENTATION', 'Noble W, 2006, NATURE BIOTECHNOLOGY', 'Alipanahi B, 2015, NATURE BIOTECHNOLOGY', 'Chothia C, 1986, THE EMBO JOURNAL', 'Libbrecht M, 2015, NATURE REVIEWS GENETICS', 'Bengio Y, 2012, LECTURE NOTES IN COMPUTER SCIENCE', 'Qian N, 1988, JOURNAL OF MOLECULAR BIOLOGY', 'Mayr A, 2016, FRONTIERS IN ENVIRONMENTAL SCIENCE', 'Pires D, 2014, NUCLEIC ACIDS RESEARCH', 'Quang D, 2016, NUCLEIC ACIDS RESEARCH', 'Hopf T, 2017, NATURE BIOTECHNOLOGY', 'Ben‐Hur A, 2009, METHODS IN MOLECULAR BIOLOGY', 'Crick F, 1989, NATURE', 'Ben‐Hur A, 2008, PLOS COMPUTATIONAL BIOLOGY', 'Moult J, 2013, PROTEINS STRUCTURE FUNCTION AND BIOINFORMATICS', 'Tarca A, 2007, PLOS COMPUTATIONAL BIOLOGY', 'Zeng H, 2016, BIOINFORMATICS', 'Cheng H, 2014, PLOS COMPUTATIONAL BIOLOGY', 'Nugent T, 2009, BMC BIOINFORMATICS', 'Zhang Y, 2004, JOURNAL OF COMPUTATIONAL CHEMISTRY', 'Wang C, 2016, JOURNAL OF COMPUTATIONAL CHEMISTRY', 'Wei Q, 2013, PLOS ONE', 'Kircher M, 2014, ', 'Bao L, 2005, NUCLEIC ACIDS RESEARCH', 'S. S, 2007, ANU OPEN RESEARCH (AUSTRALIAN NATIONAL UNIVERSITY)', 'Cozzetto D, 2016, SCIENTIFIC REPORTS', 'Chen L, 2016, BMC BIOINFORMATICS', 'Wang Y, 2016, SCIENTIFIC REPORTS', 'Li Y, 2017, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'List M, 2017, PLOS COMPUTATIONAL BIOLOGY', 'Walsh I, 2015, BRIEFINGS IN BIOINFORMATICS', 'Teodoro M, 2003, JOURNAL OF COMPUTATIONAL BIOLOGY', 'Zhang Z, 2012, BIOINFORMATICS', 'Söding J, 2011, CURRENT OPINION IN STRUCTURAL BIOLOGY', 'Kandoi G, 2015, FRONTIERS IN PHYSIOLOGY', 'deFigueiredo R, 1995, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Haario H, 1998, CHEMOMETRICS AND INTELLIGENT LABORATORY SYSTEMS', 'Pedregosa F, 2012, ARXIV (CORNELL UNIVERSITY)', 'Konečný J, 2016, ARXIV (CORNELL UNIVERSITY)', 'Kelley D, 2016, GENOME RESEARCH', 'Shrikumar A, 2017, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'LeCun Y, 2015, NATURE', 'Steinegger M, 2017, NATURE BIOTECHNOLOGY', 'Ching T, 2018, JOURNAL OF THE ROYAL SOCIETY INTERFACE', 'Dührkop K, 2019, NATURE METHODS', 'Poplin R, 2018, NATURE BIOTECHNOLOGY', 'Poplin R, 2018, NATURE BIOMEDICAL ENGINEERING', 'Zech J, 2018, PLOS MEDICINE', 'Buchan D, 2019, NUCLEIC ACIDS RESEARCH', 'Žitnik M, 2018, BIOINFORMATICS', 'Zou J, 2018, NATURE GENETICS', 'Pandarinath C, 2018, NATURE METHODS', 'Marblestone A, 2016, ARXIV (CORNELL UNIVERSITY)', 'Rappoport N, 2018, NUCLEIC ACIDS RESEARCH', 'Heffernan R, 2017, BIOINFORMATICS', 'Sun T, 2017, BMC BIOINFORMATICS', 'AlQuraishi M, 2019, CELL SYSTEMS', 'Beaulieu‐Jones B, 2019, CIRCULATION CARDIOVASCULAR QUALITY AND OUTCOMES', 'Bzdok D, 2018, NATURE METHODS', 'Nguyen L, 2019, PLOS COMPUTATIONAL BIOLOGY', 'Müller A, 2018, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Choi E, 2016, PUBMED', 'Gligorijević V, 2018, BIOINFORMATICS', 'Altman N, 2017, NATURE METHODS', 'Avsec Ž, 2019, NATURE BIOTECHNOLOGY', 'Sillitoe I, 2018, NUCLEIC ACIDS RESEARCH', 'AlQuraishi M, 2019, BMC BIOINFORMATICS', 'Chen K, 2019, NATURE METHODS', 'Greener J, 2018, SCIENTIFIC REPORTS', 'Silva J, 2019, PLANT SCIENCE', 'Pagès G, 2019, BIOINFORMATICS', 'Zeng W, 2018, BMC GENOMICS', 'Ingraham J, 2018, INTERNATIONAL CONFERENCE ON LEARNING REPRESENTATIONS', 'Hie B, 2018, SCIENCE', 'Veselkov K, 2019, SCIENTIFIC REPORTS', 'Antczak M, 2019, NATURE COMMUNICATIONS', 'Pérez A, 2018, CURRENT OPINION IN STRUCTURAL BIOLOGY', 'Jumper J, 2018, PLOS COMPUTATIONAL BIOLOGY', 'Paszke A, 2019, ARXIV (CORNELL UNIVERSITY)', 'Abadi M, 2016, ARXIV (CORNELL UNIVERSITY)', 'Gal Y, 2015, ARXIV (CORNELL UNIVERSITY)', 'Fey M, 2019, ARXIV (CORNELL UNIVERSITY)', 'Adebayo J, 2018, ARXIV (CORNELL UNIVERSITY)', 'Pandarinath C, 2017, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Beaulieu‐Jones B, 2017, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Steinegger M, 2019, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Rao R, 2019, PUBMED', 'Zhou N, 2019, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Innes M, 2019, ARXIV (CORNELL UNIVERSITY)', 'Isensee F, 2020, NATURE METHODS', 'Senior A, 2020, NATURE', 'Stokes J, 2020, CELL', 'Geirhos R, 2020, NATURE MACHINE INTELLIGENCE', 'Yang J, 2020, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Zhavoronkov A, 2019, NATURE BIOTECHNOLOGY', 'Tegunov D, 2019, NATURE METHODS', 'Steinegger M, 2019, BMC BIOINFORMATICS', 'Alley E, 2019, NATURE METHODS', 'Moon K, 2019, NATURE BIOTECHNOLOGY', 'Kobak D, 2019, NATURE COMMUNICATIONS', 'Gaínza P, 2019, NATURE METHODS', 'Noé F, 2019, SCIENCE', 'Myszczynska M, 2020, NATURE REVIEWS NEUROLOGY', 'Schmauch B, 2020, NATURE COMMUNICATIONS', 'Zhou N, 2019, GENOME BIOLOGY', 'Das P, 2021, NATURE BIOMEDICAL ENGINEERING', 'Liebal U, 2020, METABOLITES', 'Li W, 2019, FRONTIERS IN GENETICS', 'Fudenberg G, 2020, NATURE METHODS', 'Yuan Y, 2019, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Strokach A, 2020, CELL SYSTEMS', 'Livesey B, 2020, MOLECULAR SYSTEMS BIOLOGY', 'Jones D, 2019, NATURE REVIEWS MOLECULAR CELL BIOLOGY', 'Linder J, 2020, CELL SYSTEMS', 'Kantz E, 2019, ANALYTICAL CHEMISTRY', 'Si D, 2020, SCIENTIFIC REPORTS', 'Driscoll M, 2019, NATURE METHODS', 'Lopez R, 2020, MOLECULAR SYSTEMS BIOLOGY', 'Smith A, 2020, BMC BIOINFORMATICS', 'Gligorijević V, 2021, ', 'Kopp W, 2020, NATURE COMMUNICATIONS', 'Blaom A, 2020, THE JOURNAL OF OPEN SOURCE SOFTWARE', 'Schreiber J, 2020, GENOME BIOLOGY', 'Yao R, 2019, BIOINFORMATICS', 'Schoenholz S, 2019, ARXIV (CORNELL UNIVERSITY)', 'Elnaggar A, 2020, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Hopf T, 2015, ARXIV (CORNELL UNIVERSITY)', 'Yang J, 2019, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Anishchenko I, 2020, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Hiranuma N, 2020, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Gligorijevic V, 2019, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Wang Y, 2020, ARXIV (CORNELL UNIVERSITY)', 'Jumper J, 2021, NATURE', 'Roberts M, 2020, RESEARCH EXPLORER (THE UNIVERSITY OF MANCHESTER)', 'Roberts M, 2021, NATURE MACHINE INTELLIGENCE', 'Gligorijević V, 2021, NATURE COMMUNICATIONS', 'Zhong E, 2021, NATURE METHODS', 'Kryshtafovych A, 2019, PROTEINS STRUCTURE FUNCTION AND BIOINFORMATICS', 'Wang J, 2021, NATURE COMMUNICATIONS', 'Stokes J, 2020, CELL', 'Hiranuma N, 2021, NATURE COMMUNICATIONS', 'Xu J, 2021, NATURE MACHINE INTELLIGENCE', 'Munro D, 2020, BIOINFORMATICS', 'Rappoport N, 2018, NUCLEIC ACIDS RESEARCH']</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -9197,7 +9205,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>2735</v>
+        <v>2740</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -9547,7 +9555,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>3437</v>
+        <v>3441</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -9889,7 +9897,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -10007,7 +10015,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>2472</v>
+        <v>2476</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -10235,7 +10243,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -10504,7 +10512,7 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>['Schuster M, 1997, IEEE TRANSACTIONS ON SIGNAL PROCESSING', 'Koehn P, 2003, ', 'Davide B, 2013, DROPS (SCHLOSS DAGSTUHL – LEIBNIZ CENTER FOR INFORMATICS)', 'Graves A, 2013, ', ', 2000, APPLIED PHYSICS LETTERS', 'Philipp K, 2010, CHOICE REVIEWS ONLINE', 'Kalchbrenner N, 2013, ', 'Pascanu R, 2014, INTERNATIONAL CONFERENCE ON LEARNING REPRESENTATIONS', 'Axelrod A, 2011, ', 'Devlin J, 2014, ', 'Boulanger-Lewandowski N, 2013, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Schwenk H, 2006, ', 'Forcada M, 1997, LECTURE NOTES IN COMPUTER SCIENCE', 'Pouget-Abadie J, 2014, ', 'Zeiler M, 2012, ARXIV (CORNELL UNIVERSITY)', 'Sutskever I, 2014, ARXIV (CORNELL UNIVERSITY)', 'Cho K, 2014, ARXIV (CORNELL UNIVERSITY)', 'Graves A, 2012, ARXIV (CORNELL UNIVERSITY)', 'Cho K, 2014, ARXIV (CORNELL UNIVERSITY)', 'Goodfellow I, 2013, ', 'Schwenk H, 2025, ']</t>
+          <t>['Schuster M, 1997, IEEE TRANSACTIONS ON SIGNAL PROCESSING', 'Koehn P, 2003, ', 'Elena L, 2013, DROPS (SCHLOSS DAGSTUHL – LEIBNIZ CENTER FOR INFORMATICS)', 'Graves A, 2013, ', ', 2000, APPLIED PHYSICS LETTERS', 'Philipp K, 2010, CHOICE REVIEWS ONLINE', 'Kalchbrenner N, 2013, ', 'Pascanu R, 2014, INTERNATIONAL CONFERENCE ON LEARNING REPRESENTATIONS', 'Axelrod A, 2011, ', 'Devlin J, 2014, ', 'Boulanger-Lewandowski N, 2013, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Schwenk H, 2006, ', 'Forcada M, 1997, LECTURE NOTES IN COMPUTER SCIENCE', 'Pouget-Abadie J, 2014, ', 'Zeiler M, 2012, ARXIV (CORNELL UNIVERSITY)', 'Sutskever I, 2014, ARXIV (CORNELL UNIVERSITY)', 'Cho K, 2014, ARXIV (CORNELL UNIVERSITY)', 'Graves A, 2012, ARXIV (CORNELL UNIVERSITY)', 'Cho K, 2014, ARXIV (CORNELL UNIVERSITY)', 'Goodfellow I, 2013, ', 'Schwenk H, 2025, ']</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -10630,22 +10638,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://openalex.org/W1494192115</t>
+          <t>https://openalex.org/W2610886376</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>10.1038/nature14541</t>
+          <t>10.1257/jep.31.2.87</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Probabilistic machine learning and artificial intelligence</t>
+          <t>Machine Learning: An Applied Econometric Approach</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -10655,76 +10663,76 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>1976</v>
+        <v>1882</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>NATURE</t>
+          <t>THE JOURNAL OF ECONOMIC PERSPECTIVES</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>The Journal of Economic Perspectives</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>['Zoubin Ghahramani']</t>
+          <t>['Sendhil Mullainathan', 'Jann Spiess']</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>['Zoubin Ghahramani']</t>
+          <t>['Sendhil Mullainathan', 'Jann Spiess']</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['Department of Engineering, University of Cambridge, Trumpington Street, Cambridge CB2 1PZ, UK', 'Department of Engineering, University of Cambridge, , Trumpington Street, Cambridge CB2 1PZ, UK']</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>Zoubin Ghahramani (corresponding author), Department of Engineering, University of Cambridge, Trumpington Street, Cambridge CB2 1PZ, UK; Department of Engineering, University of Cambridge, , Trumpington Street, Cambridge CB2 1PZ, UK</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
+          <t>['Sendhil Mullainathan is the Robert C. Waggoner Professor of Economics, Harvard University, Cambridge, Massachusetts', 'Jann Spiess is a PhD candidate in Economics, Harvard University, Cambridge, Massachusetts']</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Machines are increasingly doing “intelligent” things. Face recognition algorithms use a large dataset of photos labeled as having a face or not to estimate a function that predicts the presence y of a face from pixels x. This similarity to econometrics raises questions: How do these new empirical tools fit with what we know? As empirical economists, how can we use them? We present a way of thinking about machine learning that gives it its own place in the econometric toolbox. Machine learning not only provides new tools, it solves a different problem. Specifically, machine learning revolves around the problem of prediction, while many economic applications revolve around parameter estimation. So applying machine learning to economics requires finding relevant tasks. Machine learning algorithms are now technically easy to use: you can download convenient packages in R or Python. This also raises the risk that the algorithms are applied naively or their output is misinterpreted. We hope to make them conceptually easier to use by providing a crisper understanding of how these algorithms work, where they excel, and where they can stumble—and thus where they can be most usefully applied.</t>
+        </is>
+      </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>87</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>106</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>['Artificial intelligence', 'Probabilistic logic', 'Computer science', 'Machine learning', 'Field (mathematics)', 'Principal (computer security)', 'Bayesian probability', 'Statistical model', 'Cognitive robotics', 'Robot']</t>
+          <t>['Toolbox', 'Python (programming language)', 'Machine learning', 'Computer science', 'Artificial intelligence', 'Face (sociological concept)', 'Empirical research', 'Mathematics']</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>['GB']</t>
+          <t>['US']</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>['Shannon C, 1948, BELL SYSTEM TECHNICAL JOURNAL', 'Nasrabadi N, 2007, JOURNAL OF ELECTRONIC IMAGING', 'Gelman A, 1995, ', 'Rasmussen C, 2005, THE MIT PRESS EBOOKS', 'Murphy K, 2012, ', 'Jones D, 1998, JOURNAL OF GLOBAL OPTIMIZATION', 'Doucet A, 2001, ', 'Koller D, 2009, ', 'Lunn D, 2000, STATISTICS AND COMPUTING', '1967-2016 M, 2004, KYBERNETES', 'Ferguson T, 1973, THE ANNALS OF STATISTICS', 'Jaynes E, 2003, ', 'Neal R, 1996, LECTURE NOTES IN STATISTICS', 'Jordan M, 1999, MACHINE LEARNING', ', 2018, THE MIT PRESS EBOOKS', 'Wolpert D, 1995, SCIENCE', 'Sammut C, 2010, ', 'Brooks S, 2011, ', 'Schmidt M, 2009, SCIENCE', 'Robbins H, 1952, BULLETIN OF THE AMERICAN MATHEMATICAL SOCIETY', 'Finetti B, 1937, FRENCH DIGITAL MATHEMATICS LIBRARY (NUMDAM)', 'Girolami M, 2011, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Knill D, 1996, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'N. K, 1992, ELSEVIER EBOOKS', 'Marjoram P, 2003, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Kushner H, 1964, JOURNAL OF BASIC ENGINEERING', 'Neal R, 2011, ', 'Skilling J, 1996, ', 'Jefferys W, 1992, AMERICAN SCIENTIST', ', 2006, THE MIT PRESS EBOOKS', 'Gupta S, 1994, ', 'Hennig P, 2012, JOURNAL OF MACHINE LEARNING RESEARCH', 'Milch B, 2007, THE MIT PRESS EBOOKS', 'Mansinghka V, 2014, ARXIV (CORNELL UNIVERSITY)', 'Pfeffer A, 2001, INTERNATIONAL JOINT CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Hjort N, 2010, ', 'Hjort N, 2010, ', 'Pfeffer A, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Steinruecken C, 2015, ', 'Russell S, 1991, THE MIT PRESS EBOOKS', 'Neal R, 1992, ', 'Horn K, 2003, INTERNATIONAL JOURNAL OF APPROXIMATE REASONING', 'Wood F, 2011, COMMUNICATIONS OF THE ACM', 'Hand D, 1986, ADDISON-WESLEY LONGMAN PUBLISHING CO., INC. EBOOKS', 'Wolstenholme D, 1988, KNOWLEDGE-BASED SYSTEMS', 'Freer C, 2014, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Woudhuysen H, 1999, TLS, THE TIMES LITERARY SUPPLEMENT/TIMES LITERARY SUPPLEMENT ON CD-ROM/TLS. TIMES LITERARY SUPPLEMENT', 'Minka T, 2013, ARXIV (CORNELL UNIVERSITY)', 'Sermanet P, 2013, ARXIV (CORNELL UNIVERSITY)', 'Goodman N, 2012, ARXIV (CORNELL UNIVERSITY)', 'Krizhevsky A, 2017, COMMUNICATIONS OF THE ACM', 'Rabiner L, 1989, PROCEEDINGS OF THE IEEE', 'Kumar D, 1995, CHOICE REVIEWS ONLINE', 'Nilsson N, 1996, ARTIFICIAL INTELLIGENCE', 'Hinton G, 2012, IEEE SIGNAL PROCESSING MAGAZINE', 'Thrun S, 2002, COMMUNICATIONS OF THE ACM', 'Teh Y, 2006, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', ', 2007, CHOICE REVIEWS ONLINE', 'Tenenbaum J, 2011, SCIENCE', 'Hoffman M, 2013, JOURNAL OF MACHINE LEARNING RESEARCH', 'Thornton C, 2013, ', 'Deisenroth M, 2011, CAMBRIDGE UNIVERSITY ENGINEERING DEPARTMENT PUBLICATIONS DATABASE', 'Blumer A, 1987, INFORMATION PROCESSING LETTERS', 'Griffiths T, 2006, PSYCHOLOGICAL SCIENCE', 'King R, 2004, NATURE', 'Kemp C, 2006, ', 'Barnard G, 1962, ECONOMETRICA', 'Ziegel E, 1989, TECHNOMETRICS', 'Miller K, 2009, ', 'O’Hagan A, 1991, JOURNAL OF STATISTICAL PLANNING AND INFERENCE', 'Griffiths T, 2011, UWA PROFILES AND RESEARCH REPOSITORY (UNIVERSITY OF WESTERN AUSTRALIA)', 'Denève S, 2007, NEURAL COMPUTATION', 'Lu C, 2015, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Medvedovic M, 2002, BIOINFORMATICS', 'Diaconis P, 1988, ', 'Bishop C, 2013, PHILOSOPHICAL TRANSACTIONS OF THE ROYAL SOCIETY A MATHEMATICAL PHYSICAL AND ENGINEERING SCIENCES', 'Marcus G, 2013, PSYCHOLOGICAL SCIENCE', 'Wingate D, 2011, INTERNATIONAL CONFERENCE ON ARTIFICIAL INTELLIGENCE AND STATISTICS', 'Jordan M, 2013, BERNOULLI', 'Houlsby N, 2012, ', 'Ghahramani Z, 2013, PHILOSOPHICAL TRANSACTIONS OF THE ROYAL SOCIETY A MATHEMATICAL PHYSICAL AND ENGINEERING SCIENCES', 'Fischer B, 2003, JOURNAL OF FUNCTIONAL PROGRAMMING', 'Koller D, 1997, ', 'Rasmussen C, 2009, IEEE/ACM TRANSACTIONS ON COMPUTATIONAL BIOLOGY AND BIOINFORMATICS', 'Goodman N, 2015, PSYCHOLOGICAL SCIENCE', 'Sutskever I, 2014, ARXIV (CORNELL UNIVERSITY)', 'Brochu E, 2010, ARXIV (CORNELL UNIVERSITY)', 'Snoek J, 2012, DIGITAL ACCESS TO SCHOLARSHIP AT HARVARD (DASH) (HARVARD UNIVERSITY)', 'Wood F, 2014, OPEN COLLECTIONS', 'Hernández-Lobato J, 2014, ARXIV (CORNELL UNIVERSITY)', 'Korattikara A, 2013, ARXIV (CORNELL UNIVERSITY)', 'Lloyd J, 2014, ARXIV (CORNELL UNIVERSITY)', 'Adams R, 2009, ARXIV (CORNELL UNIVERSITY)', ', 2004, CHOICE REVIEWS ONLINE', 'Jaynes E, 2003, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Ziegel E, 1989, TECHNOMETRICS', 'Cox R, 2001, JOHNS HOPKINS UNIVERSITY PRESS EBOOKS', 'Oksanen T, 2009, ', 'Hjort N, 2010, CAMBRIDGE UNIVERSITY PRESS EBOOKS', ', 1992, CHOICE REVIEWS ONLINE', ', 2013, ', 'Rasmussen C, 2022, DIRECTORY OF OPEN ACCESS BOOKS (OAPEN FOUNDATION)']</t>
+          <t>['Staiger D, 1997, ECONOMETRICA', 'Dietvorst B, 2014, JOURNAL OF EXPERIMENTAL PSYCHOLOGY GENERAL', 'Antweiler W, 2004, THE JOURNAL OF FINANCE', 'Dawes R, 1989, SCIENCE', 'Hoberg G, 2016, JOURNAL OF POLITICAL ECONOMY', 'Zhao P, 2006, ', 'Jean N, 2016, SCIENCE', 'Varian H, 2014, THE JOURNAL OF ECONOMIC PERSPECTIVES', 'Athey S, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Belloni A, 2013, THE REVIEW OF ECONOMIC STUDIES', 'Bound J, 1995, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Belloni A, 2012, ECONOMETRICA', 'Lee B, 2009, STATISTICS IN MEDICINE', 'Blumenstock J, 2015, SCIENCE', 'Donaldson D, 2016, THE JOURNAL OF ECONOMIC PERSPECTIVES', 'Kleinberg J, 2015, AMERICAN ECONOMIC REVIEW', 'Einav L, 2014, SCIENCE', 'Bekker P, 1994, ECONOMETRICA', 'Angrist J, 1995, JOURNAL OF BUSINESS AND ECONOMIC STATISTICS', 'Lobell D, 2012, FIELD CROPS RESEARCH', 'Angrist J, 1999, JOURNAL OF APPLIED ECONOMETRICS', 'Chalfin A, 2016, AMERICAN ECONOMIC REVIEW', 'Leeb H, 2006, THE ANNALS OF STATISTICS', 'Vaart A, 2006, STATISTICS &amp; DECISIONS', 'Carrasco M, 2012, JOURNAL OF ECONOMETRICS', 'Leeb H, 2007, ECONOMETRIC THEORY', 'Blumenstock J, 2016, SCIENCE', 'Imai K, 2010, POLITICAL ANALYSIS', 'Hansen C, 2014, JOURNAL OF ECONOMETRICS', 'Athey S, 2015, ', 'Chandler D, 2011, AMERICAN ECONOMIC REVIEW', 'McBride L, 2016, THE WORLD BANK ECONOMIC REVIEW', 'Abelson B, 2014, ', 'Bekker P, 1992, REPEC: RESEARCH PAPERS IN ECONOMICS']</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -10740,34 +10748,34 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>Ghahramani Z, 2015, NATURE</t>
+          <t>Mullainathan S, 2017, THE JOURNAL OF ECONOMIC PERSPECTIVES</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>Ghahramani Z, 2015, NATURE</t>
+          <t>Mullainathan S, 2017, THE JOURNAL OF ECONOMIC PERSPECTIVES</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2610886376</t>
+          <t>https://openalex.org/W1494192115</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>10.1257/jep.31.2.87</t>
+          <t>10.1038/nature14541</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Machine Learning: An Applied Econometric Approach</t>
+          <t>Probabilistic machine learning and artificial intelligence</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -10777,76 +10785,76 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1880</v>
+        <v>1978</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>THE JOURNAL OF ECONOMIC PERSPECTIVES</t>
+          <t>NATURE</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>The Journal of Economic Perspectives</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>['Sendhil Mullainathan', 'Jann Spiess']</t>
+          <t>['Zoubin Ghahramani']</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>['Sendhil Mullainathan', 'Jann Spiess']</t>
+          <t>['Zoubin Ghahramani']</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['Sendhil Mullainathan is the Robert C. Waggoner Professor of Economics, Harvard University, Cambridge, Massachusetts', 'Jann Spiess is a PhD candidate in Economics, Harvard University, Cambridge, Massachusetts']</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>Machines are increasingly doing “intelligent” things. Face recognition algorithms use a large dataset of photos labeled as having a face or not to estimate a function that predicts the presence y of a face from pixels x. This similarity to econometrics raises questions: How do these new empirical tools fit with what we know? As empirical economists, how can we use them? We present a way of thinking about machine learning that gives it its own place in the econometric toolbox. Machine learning not only provides new tools, it solves a different problem. Specifically, machine learning revolves around the problem of prediction, while many economic applications revolve around parameter estimation. So applying machine learning to economics requires finding relevant tasks. Machine learning algorithms are now technically easy to use: you can download convenient packages in R or Python. This also raises the risk that the algorithms are applied naively or their output is misinterpreted. We hope to make them conceptually easier to use by providing a crisper understanding of how these algorithms work, where they excel, and where they can stumble—and thus where they can be most usefully applied.</t>
-        </is>
-      </c>
+          <t>['Department of Engineering, University of Cambridge, Trumpington Street, Cambridge CB2 1PZ, UK', 'Department of Engineering, University of Cambridge, , Trumpington Street, Cambridge CB2 1PZ, UK']</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Zoubin Ghahramani (corresponding author), Department of Engineering, University of Cambridge, Trumpington Street, Cambridge CB2 1PZ, UK; Department of Engineering, University of Cambridge, , Trumpington Street, Cambridge CB2 1PZ, UK</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>521</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>452</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>459</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>['Toolbox', 'Python (programming language)', 'Machine learning', 'Computer science', 'Artificial intelligence', 'Face (sociological concept)', 'Empirical research', 'Mathematics']</t>
+          <t>['Artificial intelligence', 'Probabilistic logic', 'Computer science', 'Machine learning', 'Field (mathematics)', 'Principal (computer security)', 'Bayesian probability', 'Statistical model', 'Cognitive robotics', 'Robot']</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>['US']</t>
+          <t>['GB']</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>['Staiger D, 1997, ECONOMETRICA', 'Dietvorst B, 2014, JOURNAL OF EXPERIMENTAL PSYCHOLOGY GENERAL', 'Antweiler W, 2004, THE JOURNAL OF FINANCE', 'Dawes R, 1989, SCIENCE', 'Hoberg G, 2016, JOURNAL OF POLITICAL ECONOMY', 'Zhao P, 2006, ', 'Jean N, 2016, SCIENCE', 'Varian H, 2014, THE JOURNAL OF ECONOMIC PERSPECTIVES', 'Athey S, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Belloni A, 2013, THE REVIEW OF ECONOMIC STUDIES', 'Bound J, 1995, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Belloni A, 2012, ECONOMETRICA', 'Lee B, 2009, STATISTICS IN MEDICINE', 'Blumenstock J, 2015, SCIENCE', 'Donaldson D, 2016, THE JOURNAL OF ECONOMIC PERSPECTIVES', 'Kleinberg J, 2015, AMERICAN ECONOMIC REVIEW', 'Einav L, 2014, SCIENCE', 'Bekker P, 1994, ECONOMETRICA', 'Angrist J, 1995, JOURNAL OF BUSINESS AND ECONOMIC STATISTICS', 'Lobell D, 2012, FIELD CROPS RESEARCH', 'Angrist J, 1999, JOURNAL OF APPLIED ECONOMETRICS', 'Chalfin A, 2016, AMERICAN ECONOMIC REVIEW', 'Leeb H, 2006, THE ANNALS OF STATISTICS', 'Carrasco M, 2012, JOURNAL OF ECONOMETRICS', 'Vaart A, 2006, STATISTICS &amp; DECISIONS', 'Leeb H, 2007, ECONOMETRIC THEORY', 'Blumenstock J, 2016, SCIENCE', 'Imai K, 2010, POLITICAL ANALYSIS', 'Hansen C, 2014, JOURNAL OF ECONOMETRICS', 'Athey S, 2015, ', 'Chandler D, 2011, AMERICAN ECONOMIC REVIEW', 'McBride L, 2016, THE WORLD BANK ECONOMIC REVIEW', 'Abelson B, 2014, ', 'Bekker P, 1992, REPEC: RESEARCH PAPERS IN ECONOMICS']</t>
+          <t>['Shannon C, 1948, BELL SYSTEM TECHNICAL JOURNAL', 'Nasrabadi N, 2007, JOURNAL OF ELECTRONIC IMAGING', 'Gelman A, 1995, ', 'Rasmussen C, 2005, THE MIT PRESS EBOOKS', 'Murphy K, 2012, ', 'Jones D, 1998, JOURNAL OF GLOBAL OPTIMIZATION', 'Doucet A, 2001, ', 'Koller D, 2009, ', 'Lunn D, 2000, STATISTICS AND COMPUTING', '1967-2016 M, 2004, KYBERNETES', 'Ferguson T, 1973, THE ANNALS OF STATISTICS', 'Jaynes E, 2003, ', 'Neal R, 1996, LECTURE NOTES IN STATISTICS', 'Jordan M, 1999, MACHINE LEARNING', ', 2018, THE MIT PRESS EBOOKS', 'Wolpert D, 1995, SCIENCE', 'Sammut C, 2010, ', 'Brooks S, 2011, ', 'Schmidt M, 2009, SCIENCE', 'Robbins H, 1952, BULLETIN OF THE AMERICAN MATHEMATICAL SOCIETY', 'Finetti B, 1937, FRENCH DIGITAL MATHEMATICS LIBRARY (NUMDAM)', 'Girolami M, 2011, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Knill D, 1996, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'N. K, 1992, ELSEVIER EBOOKS', 'Marjoram P, 2003, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Kushner H, 1964, JOURNAL OF BASIC ENGINEERING', 'Neal R, 2011, ', 'Skilling J, 1996, ', 'Jefferys W, 1992, AMERICAN SCIENTIST', ', 2006, THE MIT PRESS EBOOKS', 'Gupta S, 1994, ', 'Hennig P, 2012, JOURNAL OF MACHINE LEARNING RESEARCH', 'Milch B, 2007, THE MIT PRESS EBOOKS', 'Mansinghka V, 2014, ARXIV (CORNELL UNIVERSITY)', 'Pfeffer A, 2001, INTERNATIONAL JOINT CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Hjort N, 2010, ', 'Hjort N, 2010, ', 'Pfeffer A, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Steinruecken C, 2015, ', 'Russell S, 1991, THE MIT PRESS EBOOKS', 'Neal R, 1992, ', 'Horn K, 2003, INTERNATIONAL JOURNAL OF APPROXIMATE REASONING', 'Wood F, 2011, COMMUNICATIONS OF THE ACM', 'Hand D, 1986, ADDISON-WESLEY LONGMAN PUBLISHING CO., INC. EBOOKS', 'Wolstenholme D, 1988, KNOWLEDGE-BASED SYSTEMS', 'Freer C, 2014, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Woudhuysen H, 1999, TLS, THE TIMES LITERARY SUPPLEMENT/TIMES LITERARY SUPPLEMENT ON CD-ROM/TLS. TIMES LITERARY SUPPLEMENT', 'Minka T, 2013, ARXIV (CORNELL UNIVERSITY)', 'Sermanet P, 2013, ARXIV (CORNELL UNIVERSITY)', 'Goodman N, 2012, ARXIV (CORNELL UNIVERSITY)', 'Krizhevsky A, 2017, COMMUNICATIONS OF THE ACM', 'Rabiner L, 1989, PROCEEDINGS OF THE IEEE', 'Kumar D, 1995, CHOICE REVIEWS ONLINE', 'Nilsson N, 1996, ARTIFICIAL INTELLIGENCE', 'Hinton G, 2012, IEEE SIGNAL PROCESSING MAGAZINE', 'Thrun S, 2002, COMMUNICATIONS OF THE ACM', 'Teh Y, 2006, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', ', 2007, CHOICE REVIEWS ONLINE', 'Tenenbaum J, 2011, SCIENCE', 'Hoffman M, 2013, JOURNAL OF MACHINE LEARNING RESEARCH', 'Thornton C, 2013, ', 'Deisenroth M, 2011, CAMBRIDGE UNIVERSITY ENGINEERING DEPARTMENT PUBLICATIONS DATABASE', 'Blumer A, 1987, INFORMATION PROCESSING LETTERS', 'Griffiths T, 2006, PSYCHOLOGICAL SCIENCE', 'King R, 2004, NATURE', 'Kemp C, 2006, ', 'Barnard G, 1962, ECONOMETRICA', 'Ziegel E, 1989, TECHNOMETRICS', 'Miller K, 2009, ', 'O’Hagan A, 1991, JOURNAL OF STATISTICAL PLANNING AND INFERENCE', 'Griffiths T, 2011, UWA PROFILES AND RESEARCH REPOSITORY (UNIVERSITY OF WESTERN AUSTRALIA)', 'Denève S, 2007, NEURAL COMPUTATION', 'Lu C, 2015, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Medvedovic M, 2002, BIOINFORMATICS', 'Diaconis P, 1988, ', 'Bishop C, 2013, PHILOSOPHICAL TRANSACTIONS OF THE ROYAL SOCIETY A MATHEMATICAL PHYSICAL AND ENGINEERING SCIENCES', 'Marcus G, 2013, PSYCHOLOGICAL SCIENCE', 'Wingate D, 2011, INTERNATIONAL CONFERENCE ON ARTIFICIAL INTELLIGENCE AND STATISTICS', 'Jordan M, 2013, BERNOULLI', 'Houlsby N, 2012, ', 'Ghahramani Z, 2013, PHILOSOPHICAL TRANSACTIONS OF THE ROYAL SOCIETY A MATHEMATICAL PHYSICAL AND ENGINEERING SCIENCES', 'Fischer B, 2003, JOURNAL OF FUNCTIONAL PROGRAMMING', 'Koller D, 1997, ', 'Rasmussen C, 2009, IEEE/ACM TRANSACTIONS ON COMPUTATIONAL BIOLOGY AND BIOINFORMATICS', 'Goodman N, 2015, PSYCHOLOGICAL SCIENCE', 'Sutskever I, 2014, ARXIV (CORNELL UNIVERSITY)', 'Brochu E, 2010, ARXIV (CORNELL UNIVERSITY)', 'Snoek J, 2012, DIGITAL ACCESS TO SCHOLARSHIP AT HARVARD (DASH) (HARVARD UNIVERSITY)', 'Wood F, 2014, OPEN COLLECTIONS', 'Hernández-Lobato J, 2014, ARXIV (CORNELL UNIVERSITY)', 'Korattikara A, 2013, ARXIV (CORNELL UNIVERSITY)', 'Lloyd J, 2014, ARXIV (CORNELL UNIVERSITY)', 'Adams R, 2009, ARXIV (CORNELL UNIVERSITY)', ', 2004, CHOICE REVIEWS ONLINE', 'Jaynes E, 2003, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Ziegel E, 1989, TECHNOMETRICS', 'Cox R, 2001, JOHNS HOPKINS UNIVERSITY PRESS EBOOKS', 'Oksanen T, 2009, ', 'Hjort N, 2010, CAMBRIDGE UNIVERSITY PRESS EBOOKS', ', 1992, CHOICE REVIEWS ONLINE', ', 2013, ', 'Rasmussen C, 2022, DIRECTORY OF OPEN ACCESS BOOKS (OAPEN FOUNDATION)']</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -10862,34 +10870,34 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>Mullainathan S, 2017, THE JOURNAL OF ECONOMIC PERSPECTIVES</t>
+          <t>Ghahramani Z, 2015, NATURE</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>Mullainathan S, 2017, THE JOURNAL OF ECONOMIC PERSPECTIVES</t>
+          <t>Ghahramani Z, 2015, NATURE</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2998506103</t>
+          <t>https://openalex.org/W2919115771</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>10.1016/j.ymssp.2019.106587</t>
+          <t>10.1038/nature14539</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Applications of machine learning to machine fault diagnosis: A review and roadmap</t>
+          <t>Deep learning</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -10903,68 +10911,72 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>2687</v>
+        <v>81513</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>MECHANICAL SYSTEMS AND SIGNAL PROCESSING</t>
+          <t>NATURE</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Mechanical Systems and Signal Processing</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>['Yaguo Lei', 'Bin Yang', 'Xinwei Jiang', 'Feng Jia', 'Naipeng Li', 'Asoke K. Nandi']</t>
+          <t>['Yann LeCun', 'Yoshua Bengio', 'Geoffrey E. Hinton']</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>['Yaguo Lei', 'Bin Yang', 'Xinwei Jiang', 'Feng Jia', 'Naipeng Li', 'Asoke K. Nandi']</t>
+          <t>['Yann LeCun', 'Yoshua Bengio', 'Geoffrey Hinton']</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>['Key Laboratory of Education Ministry for Modern Design and Rotor-Bearing System, Xi’an Jiaotong University, Xi’an 710049, China', 'Key Laboratory of Education Ministry for Modern Design and Rotor-Bearing System, Xi’an Jiaotong University, Xi’an 710049, China', 'Key Laboratory of Education Ministry for Modern Design and Rotor-Bearing System, Xi’an Jiaotong University, Xi’an 710049, China', 'Key Laboratory of Education Ministry for Modern Design and Rotor-Bearing System, Xi’an Jiaotong University, Xi’an 710049, China', 'Key Laboratory of Education Ministry for Modern Design and Rotor-Bearing System, Xi’an Jiaotong University, Xi’an 710049, China', 'Department of Electronic and Computer Engineering, Brunel University London, Uxbridge UB8 3PH, United Kingdom']</t>
+          <t>['1] Facebook AI Research, 770 Broadway, New York, New York 10003 USA. [2] New York University, 715 Broadway, New York, New York 10003, USA', 'Facebook AI Research, 770 Broadway, New York, 10003, New York, USA', 'New York University, 715 Broadway, New York, 10003, New York, USA', 'Department of Computer Science and Operations Research Université de Montréal, Pavillon André-Aisenstadt, PO Box 6128 Centre-Ville STN Montréal, Quebec H3C 3J7, Canada', 'Department of Computer Science and Operations Research Université de Montréal, Pavillon André-Aisenstadt, PO Box 6128 Centre-Ville STN, Montréal, H3C 3J7, Quebec, Canada', "1] Google, 1600 Amphitheatre Parkway, Mountain View, California 94043, USA. [2] Department of Computer Science, University of Toronto, 6 King's College Road, Toronto, Ontario M5S 3G4, Canada", 'Google, 1600 Amphitheatre Parkway, Mountain View, 94043, California, USA', "Department of Computer Science, University of Toronto, 6 King's College Road, Toronto, M5S 3G4, Ontario, Canada"]</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Yaguo Lei (corresponding author), Key Laboratory of Education Ministry for Modern Design and Rotor-Bearing System, Xi’an Jiaotong University, Xi’an 710049, China</t>
+          <t>Yann LeCun (corresponding author), 1] Facebook AI Research, 770 Broadway, New York, New York 10003 USA. [2] New York University, 715 Broadway, New York, New York 10003, USA; Facebook AI Research, 770 Broadway, New York, 10003, New York, USA; New York University, 715 Broadway, New York, 10003, New York, USA</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr"/>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>7553</t>
+        </is>
+      </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>106587</t>
+          <t>436</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>106587</t>
+          <t>444</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>['Artificial intelligence', 'Machine learning', 'Computer science', 'Bridge (graph theory)', 'Engineering']</t>
+          <t>['Computer science', 'Deep learning', 'Artificial intelligence', 'Abstraction', 'Representation (politics)', 'Layer (electronics)', 'Object (grammar)', 'Backpropagation', 'Convolutional neural network', 'Feature learning', 'Pattern recognition (psychology)', 'Speech recognition', 'Artificial neural network']</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>['CN', 'GB']</t>
+          <t>['US', 'CA']</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>['Rumelhart D, 1986, NATURE', 'Nair V, 2010, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Koller D, 2009, ', 'Platt J, 1998, THE MIT PRESS EBOOKS', 'Gao Z, 2015, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Kira K, 1992, ELSEVIER EBOOKS', 'Kononenko I, 1994, LECTURE NOTES IN COMPUTER SCIENCE', 'Yin S, 2014, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Yang Y, 2005, JOURNAL OF SOUND AND VIBRATION', 'Chen J, 2015, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Thrun S, 1998, ', 'Hall M, 1998, RESEARCH COMMONS (UNIVERSITY OF WAIKATO)', 'Wang Y, 2015, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Tran V, 2014, EXPERT SYSTEMS WITH APPLICATIONS', 'Pandya D, 2013, EXPERT SYSTEMS WITH APPLICATIONS', 'Kothari S, 1993, ADVANCES IN COMPUTERS', 'Wu J, 2008, EXPERT SYSTEMS WITH APPLICATIONS', 'Li Y, 2015, MEASUREMENT', 'Yang J, 2006, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Lei Y, 2009, EXPERT SYSTEMS WITH APPLICATIONS', 'Zarei J, 2014, MECHATRONICS', 'Gryllias K, 2011, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Yang B, 2004, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Yang B, 2003, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Zhang X, 2015, NEUROCOMPUTING', 'Kang M, 2014, IEEE TRANSACTIONS ON POWER ELECTRONICS', 'Boutros T, 2011, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Keskes H, 2015, IEEE TRANSACTIONS ON INDUSTRIAL INFORMATICS', 'Ziani R, 2014, JOURNAL OF INTELLIGENT MANUFACTURING', 'Boukra T, 2012, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Widodo A, 2009, MECHATRONICS', 'Liu H, 2022, INDUSTRIAL AND ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE AND EXPERT SYSTEMS', 'Zhang K, 2011, NEUROCOMPUTING', 'Hang J, 2015, FUZZY SETS AND SYSTEMS', 'Chen J, 2015, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Kurek J, 2009, NEURAL COMPUTING AND APPLICATIONS', 'Walker R, 2014, MECHANISM AND MACHINE THEORY', 'Li F, 2015, NEUROCOMPUTING', 'Dong S, 2013, MEASUREMENT', 'Geramifard O, 2013, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Zhu K, 2015, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Wang Z, 2013, JOURNAL OF AEROSPACE ENGINEERING', 'Gelgele H, 1998, JOURNAL OF INTELLIGENT MANUFACTURING', 'Arabacı H, 2009, NEURAL COMPUTING AND APPLICATIONS', 'Qiu J, 2015, JOURNAL OF NATURAL GAS SCIENCE AND ENGINEERING', 'Yoon J, 2015, IET SCIENCE MEASUREMENT &amp; TECHNOLOGY', 'Zhong B, 1999, NEURAL COMPUTING AND APPLICATIONS', 'Xiao Z, 2015, MATHEMATICAL PROBLEMS IN ENGINEERING', 'Liu Q, 2003, NEURAL PROCESSING LETTERS', 'Krishnamurthi M, 1992, COMPUTERS &amp; INDUSTRIAL ENGINEERING', 'Samanta B, 2003, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Chiang L, 2003, COMPUTERS &amp; CHEMICAL ENGINEERING', 'Jack L, 2002, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Widodo A, 2008, EXPERT SYSTEMS WITH APPLICATIONS', 'Zhang X, 2013, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Ebrahimi B, 2013, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Shen C, 2013, MEASUREMENT', 'Lei Y, 2009, EXPERT SYSTEMS WITH APPLICATIONS', 'Saïdi L, 2014, ISA TRANSACTIONS', 'Ünal M, 2014, MEASUREMENT', 'Zhu K, 2013, MEASUREMENT', 'Amarnath M, 2012, MEASUREMENT', 'Jiang H, 2014, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Şahin S, 2011, EXPERT SYSTEMS WITH APPLICATIONS', 'He D, 2012, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Keskes H, 2013, ELECTRIC POWER SYSTEMS RESEARCH', 'Su Z, 2015, NEUROCOMPUTING', 'Li X, 2013, MEASUREMENT', 'Moosavi S, 2015, ELECTRIC POWER SYSTEMS RESEARCH', 'Wu S, 2013, ENTROPY', 'Tang X, 2010, KNOWLEDGE-BASED SYSTEMS', 'Yang D, 2002, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Jack L, 2001, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Wuxing L, 2003, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Yuwono M, 2015, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Li H, 2009, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Chen C, 2004, DIGITAL SIGNAL PROCESSING', 'Castejón C, 2009, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Vong C, 2011, EXPERT SYSTEMS WITH APPLICATIONS', 'Hao R, 2011, MEASUREMENT SCIENCE AND TECHNOLOGY', 'Kang M, 2013, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Wu J, 2009, EXPERT SYSTEMS WITH APPLICATIONS', 'He Y, 2013, INFORMATION SCIENCES', 'Wang G, 2007, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Gharavian M, 2013, NEUROCOMPUTING', 'Kuo R, 1995, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Wu J, 2006, EXPERT SYSTEMS WITH APPLICATIONS', 'Cabal‐Yépez E, 2012, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Mohammed A, 2013, MECCANICA', 'Van M, 2015, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Lin T, 2014, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Lu P, 2001, JOURNAL OF ENGINEERING FOR GAS TURBINES AND POWER', 'Varma A, 1999, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Sharkey A, 2000, NEURAL COMPUTING AND APPLICATIONS', 'Guo Q, 2006, DIGITAL SIGNAL PROCESSING', 'Vingerhoeds R, 1995, CONTROL ENGINEERING PRACTICE', 'Hajnayeb A, 2008, INDUSTRIAL LUBRICATION AND TRIBOLOGY', 'Wu H, 2004, AIRCRAFT ENGINEERING AND AEROSPACE TECHNOLOGY', 'Zhang C, 2010, ', 'White M, 1991, MEASUREMENT', 'Schmidhuber J, 2014, NEURAL NETWORKS', 'Bolón‐Canedo V, 2012, KNOWLEDGE AND INFORMATION SYSTEMS', 'Dai X, 2013, IEEE TRANSACTIONS ON INDUSTRIAL INFORMATICS', 'Lei Y, 2013, MEASUREMENT', 'Tamilselvan P, 2013, RELIABILITY ENGINEERING &amp; SYSTEM SAFETY', 'Samanta B, 2003, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Samanta B, 2003, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Lei Y, 2007, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Sugumaran V, 2006, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Abbasion S, 2007, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Yang Y, 2006, MEASUREMENT', 'Safizadeh M, 2013, INFORMATION FUSION', 'Widodo A, 2006, EXPERT SYSTEMS WITH APPLICATIONS', 'Widodo A, 2006, EXPERT SYSTEMS WITH APPLICATIONS', 'Wu S, 2012, ENTROPY', 'Sakthivel N, 2009, EXPERT SYSTEMS WITH APPLICATIONS', 'Jegadeeshwaran R, 2014, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Sheng-fa Y, 2005, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Wang Y, 2013, APPLIED ACOUSTICS', 'Hajnayeb A, 2011, EXPERT SYSTEMS WITH APPLICATIONS', 'Chen F, 2012, MEASUREMENT', 'Saravanan N, 2007, EXPERT SYSTEMS WITH APPLICATIONS', 'Yang D, 2015, MECHANISM AND MACHINE THEORY', 'Yang J, 2001, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Chen F, 2013, MEASUREMENT', 'Sugumaran V, 2007, EXPERT SYSTEMS WITH APPLICATIONS', 'Ebersbach S, 2006, EXPERT SYSTEMS WITH APPLICATIONS', 'Jiang L, 2013, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Wong M, 2005, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Rojas‐Domínguez A, 2005, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Salem S, 2012, ISA TRANSACTIONS', 'WU J, 2007, EXPERT SYSTEMS WITH APPLICATIONS', 'Lu W, 2013, JOURNAL OF SOUND AND VIBRATION', 'Widodo A, 2009, NONDESTRUCTIVE TESTING AND EVALUATION', 'Hernandez-Vargas M, 2014, COMPUTERS &amp; ELECTRICAL ENGINEERING', 'Wu J, 2010, EXPERT SYSTEMS WITH APPLICATIONS', 'Wu J, 2009, EXPERT SYSTEMS WITH APPLICATIONS', 'Kang M, 2014, IEEE TRANSACTIONS ON MAGNETICS', 'Ao H, 2013, JOURNAL OF VIBRATION AND CONTROL', 'Vong C, 2011, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Lei Y, 2009, JOURNAL OF VIBRATION AND ACOUSTICS', 'Barakat M, 2013, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Jiang L, 2012, JOURNAL OF VIBRATION AND CONTROL', 'Jena D, 2013, APPLIED ACOUSTICS', 'Xiao W, 2011, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Ilott P, 1997, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART E JOURNAL OF PROCESS MECHANICAL ENGINEERING', 'Chen X, 2014, APPLIED MATHEMATICS AND COMPUTATION', 'Wu J, 2007, EXPERT SYSTEMS WITH APPLICATIONS', 'Yu J, 2015, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Cortes C, 1995, MACHINE LEARNING', 'Quinlan J, 1992, ', '淳司 柴, 2017, JOURNAL OF JAPAN SOCIETY FOR FUZZY THEORY AND INTELLIGENT INFORMATICS', 'Hinton G, 2006, SCIENCE', 'Cover T, 1967, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Peng H, 2005, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Hinton G, 2002, NEURAL COMPUTATION', 'Tibshirani R, 2004, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Long M, 2013, ', 'Тихонов А, 1995, ', 'Dai W, 2007, ', 'Widodo A, 2007, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Liao S, 2004, EXPERT SYSTEMS WITH APPLICATIONS', 'Gao Z, 2015, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Naimi A, 2014, AMERICAN JOURNAL OF EPIDEMIOLOGY', 'Lei Y, 2010, EXPERT SYSTEMS WITH APPLICATIONS', 'Lei Y, 2009, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Sun W, 2006, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Muruganatham B, 2012, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Ebrahimi B, 2010, IEEE TRANSACTIONS ON POWER ELECTRONICS', 'Yang B, 2008, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Tang B, 2013, RENEWABLE ENERGY', 'Rafiee J, 2008, EXPERT SYSTEMS WITH APPLICATIONS', 'Li Z, 2012, MEASUREMENT', 'Ghate V, 2010, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Li N, 2011, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Jayaswal P, 2010, JOURNAL OF VIBRATION AND CONTROL', 'Yang B, 2005, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Tsoumas I, 2008, IEEE TRANSACTIONS ON ENERGY CONVERSION', 'Cerrada M, 2015, SENSORS', 'Lee H, 2000, IEEE TRANSACTIONS ON POWER DELIVERY', 'Bordoloi D, 2014, MEASUREMENT', 'Xian G, 2009, EXPERT SYSTEMS WITH APPLICATIONS', 'Bacha K, 2012, INTERNATIONAL JOURNAL OF ELECTRICAL POWER &amp; ENERGY SYSTEMS', 'Wang Y, 2011, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Knapp G, 1992, INTERNATIONAL JOURNAL OF PRODUCTION RESEARCH', 'Namdari M, 2014, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Shahriar M, 2013, EURASIP JOURNAL ON IMAGE AND VIDEO PROCESSING', 'Barakat M, 2012, INTERNATIONAL JOURNAL OF MACHINE LEARNING AND CYBERNETICS', 'Becerra J, 2011, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'McCormick A, 1997, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'McCormick A, 1997, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Liu S, 2003, THE INTERNATIONAL JOURNAL OF ADVANCED MANUFACTURING TECHNOLOGY', 'Liu T, 2013, JOURNAL OF VIBRATION AND CONTROL', 'Almeida L, 2014, JOURNAL OF VIBRATION AND CONTROL', 'S V, 2012, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART J JOURNAL OF ENGINEERING TRIBOLOGY', 'Angeli C, 1999, EXPERT SYSTEMS', 'Chen H, 2013, DOAJ (DOAJ: DIRECTORY OF OPEN ACCESS JOURNALS)', 'Shen Y, 2006, ', 'He K, 2016, ', 'Pan S, 2009, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', ', 2013, CHOICE REVIEWS ONLINE', 'Jia F, 2015, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'İnce T, 2016, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Lei Y, 2016, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Rai A, 2016, TRIBOLOGY INTERNATIONAL', 'Lü C, 2016, SIGNAL PROCESSING', 'Lu W, 2016, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Shao H, 2015, MEASUREMENT SCIENCE AND TECHNOLOGY', 'Li C, 2016, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Zheng J, 2016, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Li C, 2015, NEUROCOMPUTING', 'Liu H, 2016, SHOCK AND VIBRATION', 'Long M, 2016, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Yang T, 2016, IEEE TRANSACTIONS ON INSTRUMENTATION AND MEASUREMENT', 'Ayhan B, 2006, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Zhang X, 2015, KNOWLEDGE-BASED SYSTEMS', 'Yin J, 2016, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Sadeghian A, 2009, IEEE TRANSACTIONS ON INSTRUMENTATION AND MEASUREMENT', 'Xie J, 2016, ', 'Zhou H, 2015, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Głowacz A, 2016, APPLIED ACOUSTICS', 'Malik H, 2016, IET RENEWABLE POWER GENERATION', 'Shen F, 2015, ', 'Asr M, 2016, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Goyal D, 2016, ARCHIVES OF COMPUTATIONAL METHODS IN ENGINEERING', 'Li Y, 2016, MECHANISM AND MACHINE THEORY', 'Yang Z, 2016, ENERGIES', 'Liu H, 2016, JOURNAL OF SOUND AND VIBRATION', 'Liu Y, 2015, NEUROCOMPUTING', 'Li Z, 2012, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Waqar T, 2016, MEASUREMENT', 'Abu-Mahfouz I, 2005, INTERNATIONAL JOURNAL OF GENERAL SYSTEMS', 'Kane P, 2016, JOURNAL OF LOW FREQUENCY NOISE, VIBRATION AND ACTIVE CONTROL', 'Chen J, 2016, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Dong S, 2015, JOURNAL OF THE BRAZILIAN SOCIETY OF MECHANICAL SCIENCES AND ENGINEERING', 'Sun J, 2014, TM - TECHNISCHES MESSEN', 'Palácios R, 2016, JOURNAL OF CONTROL AUTOMATION AND ELECTRICAL SYSTEMS', 'An X, 2016, TRANSACTIONS OF THE INSTITUTE OF MEASUREMENT AND CONTROL', 'Dong S, 2015, MEASUREMENT AND CONTROL', 'Khazaee M, 2016, STRUCTURAL HEALTH MONITORING', 'Wong P, 2016, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Lee S, 2009, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Jiang X, 2015, JOURNAL OF VIBROENGINEERING', 'Heidari M, 2016, JOURNAL OF VIBROENGINEERING', 'Liu Z, 2012, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Khazaee M, 2016, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART D JOURNAL OF AUTOMOBILE ENGINEERING', 'Jin X, 2014, JOURNAL OF VIBROENGINEERING', 'Goodfellow I, 2016, MIT PRESS EBOOKS', 'Zhāng W, 2017, SENSORS', 'Zhāng W, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Chen Z, 2017, IEEE TRANSACTIONS ON INSTRUMENTATION AND MEASUREMENT', 'Xia M, 2017, IEEE/ASME TRANSACTIONS ON MECHATRONICS', 'Jing L, 2017, MEASUREMENT', 'Shao H, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Jia F, 2017, NEUROCOMPUTING', 'Ding X, 2017, IEEE TRANSACTIONS ON INSTRUMENTATION AND MEASUREMENT', 'Lü C, 2017, ADVANCED ENGINEERING INFORMATICS', 'Zhang R, 2017, IEEE ACCESS', 'Jing L, 2017, SENSORS', 'Shao H, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Wang Z, 2017, IEEE SENSORS JOURNAL', 'Liu R, 2016, IEEE TRANSACTIONS ON INDUSTRIAL INFORMATICS', 'Sun W, 2017, IEEE TRANSACTIONS ON INDUSTRIAL INFORMATICS', 'Shao H, 2017, ISA TRANSACTIONS', 'Li Y, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Eren L, 2017, MATHEMATICAL PROBLEMS IN ENGINEERING', 'Li S, 2017, SENSORS', 'Janssens O, 2017, IEEE/ASME TRANSACTIONS ON MECHATRONICS', 'Fuan W, 2017, MEASUREMENT SCIENCE AND TECHNOLOGY', 'Gangsar P, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Ahmed H, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Xia M, 2017, IET SCIENCE MEASUREMENT &amp; TECHNOLOGY', 'Sun W, 2017, MATERIALS', 'Li C, 2017, IEEE ACCESS', 'Guo X, 2016, APPLIED SCIENCES', 'He J, 2017, SENSORS', 'Martínez-Morales J, 2016, ELECTRICAL ENGINEERING', 'Gao Z, 2017, NEUROCOMPUTING', 'Xing Z, 2017, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Cheng F, 2016, IEEE TRANSACTIONS ON INDUSTRY APPLICATIONS', 'Qu Y, 2017, APPLIED SCIENCES', 'Merainani B, 2017, JOURNAL OF VIBRATION AND CONTROL', 'Ma J, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Cai C, 2017, CLUSTER COMPUTING', 'Li Z, 2016, JOURNAL OF PROPULSION AND POWER', 'Yao B, 2017, IEEE ACCESS', 'Chen C, 2017, ', 'Islam M, 2017, THE JOURNAL OF THE ACOUSTICAL SOCIETY OF AMERICA', 'He X, 2016, MATHEMATICAL PROBLEMS IN ENGINEERING', 'Wu L, 2017, APPLIED SCIENCES', 'Jiang H, 2017, JOURNAL OF VIBROENGINEERING', 'Yan J, 2016, JOURNAL OF VIBROENGINEERING', 'Xu T, 2017, JOURNAL OF INTELLIGENT &amp; FUZZY SYSTEMS', 'Wang J, 2016, ', 'Heidari M, 2017, JOURNAL OF VIBROENGINEERING', 'Gerdes M, 2016, EKSPLOATACJA I NIEZAWODNOSC - MAINTENANCE AND RELIABILITY', 'Wen L, 2017, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Liu R, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Khan S, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Wen L, 2017, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS SYSTEMS', 'Li Y, 2018, PATTERN RECOGNITION', 'Liu H, 2018, ISA TRANSACTIONS', 'Jia F, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Shao H, 2017, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Cao P, 2018, IEEE ACCESS', 'Shao H, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Sun J, 2017, IEEE TRANSACTIONS ON INSTRUMENTATION AND MEASUREMENT', 'Verstraete D, 2017, SHOCK AND VIBRATION', 'Zhao M, 2017, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Shao H, 2017, KNOWLEDGE-BASED SYSTEMS', 'Ma M, 2018, IEEE TRANSACTIONS ON INDUSTRIAL INFORMATICS', 'Wang S, 2017, KNOWLEDGE-BASED SYSTEMS', 'Guo S, 2018, SENSORS', 'Zhang Y, 2018, JOURNAL OF MANUFACTURING SYSTEMS', 'Duan Z, 2018, THE INTERNATIONAL JOURNAL OF ADVANCED MANUFACTURING TECHNOLOGY', 'Li Y, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Li Y, 2018, JOURNAL OF SOUND AND VIBRATION', 'Islam M, 2018, RELIABILITY ENGINEERING &amp; SYSTEM SAFETY', 'Shao S, 2017, CHINESE JOURNAL OF MECHANICAL ENGINEERING', 'Park S, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Venkateswara H, 2017, IEEE SIGNAL PROCESSING MAGAZINE', 'Berredjem T, 2018, EXPERT SYSTEMS WITH APPLICATIONS', 'Chen Y, 2018, NEUROCOMPUTING', 'Shao H, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Zhang X, 2017, NEUROCOMPUTING', 'Tang S, 2018, NEUROCOMPUTING', 'Zhu X, 2018, IEEE ACCESS', 'Praveenkumar T, 2017, MEASUREMENT', 'Yu D, 2018, INTERNATIONAL JOURNAL OF ELECTRICAL POWER &amp; ENERGY SYSTEMS', 'Sohaib M, 2018, SHOCK AND VIBRATION', 'Gangsar P, 2018, JOURNAL OF DYNAMIC SYSTEMS MEASUREMENT AND CONTROL', 'Huang D, 2018, MICROELECTRONICS RELIABILITY', 'Naha A, 2017, IEEE TRANSACTIONS ON INSTRUMENTATION AND MEASUREMENT', 'Vanraj, 2017, STRUCTURAL HEALTH MONITORING', 'Zgarni S, 2018, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Han D, 2017, ADVANCES IN MECHANICAL ENGINEERING', 'Dong S, 2017, JOURNAL OF LOW FREQUENCY NOISE, VIBRATION AND ACTIVE CONTROL', 'Duong B, 2018, SENSORS', 'Tang T, 2018, JOURNAL OF SOUND AND VIBRATION', 'Wang X, 2017, JOURNAL OF VIBROENGINEERING', 'Yu J, 2018, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Tyagi S, 2017, APPLIED ARTIFICIAL INTELLIGENCE', 'Yuan H, 2017, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Safizadeh M, 2017, INSIGHT - NON-DESTRUCTIVE TESTING AND CONDITION MONITORING', 'Jiang Q, 2017, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Jiang F, 2018, ADVANCES IN MECHANICAL ENGINEERING', 'Zhao R, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Shao S, 2018, IEEE TRANSACTIONS ON INDUSTRIAL INFORMATICS', 'Guo L, 2018, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Jiang G, 2018, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Hoang D, 2018, NEUROCOMPUTING', 'Stetco A, 2018, RENEWABLE ENERGY', 'Eren L, 2018, JOURNAL OF SIGNAL PROCESSING SYSTEMS', 'Li X, 2018, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Zhu Z, 2018, NEUROCOMPUTING', 'Li X, 2018, NEUROCOMPUTING', ', 2017, ELSEVIER EBOOKS', 'Liu G, 2018, MATHEMATICAL PROBLEMS IN ENGINEERING', 'Meng Z, 2018, MEASUREMENT', 'Han T, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Zhao M, 2018, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Shen C, 2018, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Guo Y, 2018, APPLIED ENERGY', 'Zhang B, 2018, IEEE ACCESS', 'Guo D, 2018, NEUROCOMPUTING', 'Li Y, 2018, JOURNAL OF SOUND AND VIBRATION', 'Han Y, 2018, MEASUREMENT', 'Mao W, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Jiao J, 2018, KNOWLEDGE-BASED SYSTEMS', 'Yao Y, 2018, APPLIED SCIENCES', 'Jafarian K, 2018, MEASUREMENT', 'Hasan M, 2018, APPLIED SCIENCES', 'Tong Z, 2018, IEEE ACCESS', 'Zhao X, 2018, NEUROCOMPUTING', 'Appana D, 2018, SOFT COMPUTING', 'Duan L, 2018, JOURNAL OF INTELLIGENT &amp; FUZZY SYSTEMS', 'Jin Y, 2018, IEEE TRANSACTIONS ON INSTRUMENTATION AND MEASUREMENT', 'Xie J, 2018, IEEE ACCESS', 'Wang J, 2018, MEASUREMENT SCIENCE AND TECHNOLOGY', 'Ahmed H, 2018, IEEE ACCESS', 'Singh M, 2018, MEASUREMENT', 'Rapur J, 2018, JOURNAL OF THE BRAZILIAN SOCIETY OF MECHANICAL SCIENCES AND ENGINEERING', 'Zhuang Y, 2018, MEASUREMENT SCIENCE AND TECHNOLOGY', 'Rapur J, 2018, JOURNAL OF NONDESTRUCTIVE EVALUATION', 'Zabihihesari A, 2018, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Yu J, 2018, JOURNAL OF SOUND AND VIBRATION', 'Zheng Y, 2019, SENSORS', 'Saufi M, 2018, MEASUREMENT SCIENCE AND TECHNOLOGY', 'Zhang M, 2018, IEEE TRANSACTIONS ON INSTRUMENTATION AND MEASUREMENT', 'Jiang F, 2018, APPLIED SCIENCES', 'Jiang H, 2018, JOURNAL OF INTELLIGENT &amp; FUZZY SYSTEMS', 'Zhou P, 2018, APPLIED SCIENCES', 'Yu H, 2018, IEEE SIGNAL PROCESSING LETTERS', 'Liu L, 2018, JOURNAL OF SOUND AND VIBRATION', 'Xin Y, 2018, JOURNAL OF VIBROENGINEERING', 'Chen Z, 2018, JOURNAL OF INTELLIGENT &amp; FUZZY SYSTEMS', 'Breiman L, 2001, MACHINE LEARNING', 'LeCun Y, 2015, NATURE', 'Cortes C, 1995, MACHINE LEARNING', 'Gu J, 2017, PATTERN RECOGNITION', 'Yang B, 2019, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Xu Y, 2019, IEEE ACCESS', 'Han T, 2018, KNOWLEDGE-BASED SYSTEMS', 'We Z, 2018, ISA TRANSACTIONS', 'Qiao Z, 2019, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Yang B, 2019, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Peng D, 2018, IEEE ACCESS', 'Zhao D, 2019, COMPUTERS IN INDUSTRY', 'Huang R, 2018, IEEE ACCESS', 'Cao X, 2019, COMPUTERS IN INDUSTRY', 'Islam M, 2019, COMPUTERS IN INDUSTRY', 'Wang X, 2019, IEEE TRANSACTIONS ON INDUSTRIAL INFORMATICS', 'Zheng H, 2019, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Liu X, 2019, SENSORS', 'Xu X, 2019, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Ma S, 2019, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Han Y, 2019, COMPUTERS IN INDUSTRY', 'Li X, 2019, APPLIED SCIENCES', 'Su L, 2019, IEEE TRANSACTIONS ON INDUSTRIAL INFORMATICS', 'Qian W, 2018, IEEE ACCESS', 'Guo S, 2018, SENSORS', 'Suh S, 2019, APPLIED SCIENCES', 'Tong Z, 2018, SHOCK AND VIBRATION', 'Chen H, 2013, SHOCK AND VIBRATION', 'Li J, 2019, SENSORS', 'Gangsar P, 2019, JOURNAL OF THE BRAZILIAN SOCIETY OF MECHANICAL SCIENCES AND ENGINEERING', 'Li Y, 2019, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Tang G, 2018, APPLIED SCIENCES', 'Xie Y, 2018, ', 'Pang B, 2018, ENTROPY', 'Yang B, 2018, 2018 INTERNATIONAL CONFERENCE ON SENSING,DIAGNOSTICS, PROGNOSTICS, AND CONTROL (SDPC)', 'Qian W, 2018, ', 'Chen X, 2019, COMPLEXITY', 'Yu J, 2018, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Jia Y, 2018, SENSORS', 'Zhang X, 2019, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Chunfeng W, 2018, ']</t>
+          <t>['Hochreiter S, 1997, NEURAL COMPUTATION', 'LeCun Y, 1998, PROCEEDINGS OF THE IEEE', 'Rumelhart D, 1986, NATURE', 'Mnih V, 2015, NATURE', 'Cho K, 2014, ', 'Hinton G, 2006, SCIENCE', 'Hinton G, 2006, NEURAL COMPUTATION', 'Hubel D, 1962, THE JOURNAL OF PHYSIOLOGY', 'Bengio Y, 2013, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Hinton G, 2012, IEEE SIGNAL PROCESSING MAGAZINE', 'Bengio Y, 1994, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Felleman D, 1991, CEREBRAL CORTEX', 'Vincent P, 2008, ', 'Bengio Y, 2009, NOW PUBLISHERS, INC. EBOOKS', ', 2018, THE MIT PRESS EBOOKS', 'Goldman‐Rakic P, 1991, CEREBRAL CORTEX', 'Clarke M, 1974, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES A (GENERAL)', 'Lawrence S, 1997, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Werbos P, 1974, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Farabet C, 2012, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Waibel A, 1989, IEEE TRANSACTIONS ON ACOUSTICS SPEECH AND SIGNAL PROCESSING', 'Mohamed A, 2011, IEEE TRANSACTIONS ON AUDIO SPEECH AND LANGUAGE PROCESSING', 'Xiong H, 2014, SCIENCE', 'Ma J, 2015, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Hinton G, 1995, SCIENCE', 'Helmstaedter M, 2013, NATURE', 'Cireşan D, 2012, NEURAL NETWORKS', 'Cadieu C, 2014, PLOS COMPUTATIONAL BIOLOGY', 'Raina R, 2009, ', 'Rogers T, 2004, THE MIT PRESS EBOOKS', 'García C, 2004, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Schwenk H, 2006, COMPUTER SPEECH &amp; LANGUAGE', 'Kavukcuoglu K, 2010, ', 'Leung M, 2014, BIOINFORMATICS', 'Turaga S, 2009, NEURAL COMPUTATION', 'Hadsell R, 2009, JOURNAL OF FIELD ROBOTICS', 'Feng N, 2005, IEEE TRANSACTIONS ON IMAGE PROCESSING', 'Bottou L, 2013, MACHINE LEARNING', 'Boser B, 1991, IEEE JOURNAL OF SOLID-STATE CIRCUITS', 'Farabet C, 2011, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Ciodaro T, 2012, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Neumann B, 2001, K&amp;UUML;NSTLICHE INTELL.', 'Ranzato M, 2013, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Nasr M, 2011, ', 'Xu K, 2015, ARXIV (CORNELL UNIVERSITY)', 'Sermanet P, 2013, ARXIV (CORNELL UNIVERSITY)', 'Dauphin Y, 2014, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -10980,34 +10992,34 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>Lei Y, 2020, MECHANICAL SYSTEMS AND SIGNAL PROCESSING</t>
+          <t>LeCun Y, 2015, NATURE</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>Lei Y, 2020, MECHANICAL SYSTEMS AND SIGNAL PROCESSING</t>
+          <t>LeCun Y, 2015, NATURE</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2919115771</t>
+          <t>https://openalex.org/W2998506103</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>10.1038/nature14539</t>
+          <t>10.1016/j.ymssp.2019.106587</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Deep learning</t>
+          <t>Applications of machine learning to machine fault diagnosis: A review and roadmap</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -11021,72 +11033,68 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>81470</v>
+        <v>2687</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>NATURE</t>
+          <t>MECHANICAL SYSTEMS AND SIGNAL PROCESSING</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Mechanical Systems and Signal Processing</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>['Yann LeCun', 'Yoshua Bengio', 'Geoffrey E. Hinton']</t>
+          <t>['Yaguo Lei', 'Bin Yang', 'Xinwei Jiang', 'Feng Jia', 'Naipeng Li', 'Asoke K. Nandi']</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>['Yann LeCun', 'Yoshua Bengio', 'Geoffrey Hinton']</t>
+          <t>['Yaguo Lei', 'Bin Yang', 'Xinwei Jiang', 'Feng Jia', 'Naipeng Li', 'Asoke K. Nandi']</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1] Facebook AI Research, 770 Broadway, New York, New York 10003 USA. [2] New York University, 715 Broadway, New York, New York 10003, USA', 'Facebook AI Research, 770 Broadway, New York, 10003, New York, USA', 'New York University, 715 Broadway, New York, 10003, New York, USA', 'Department of Computer Science and Operations Research Université de Montréal, Pavillon André-Aisenstadt, PO Box 6128 Centre-Ville STN Montréal, Quebec H3C 3J7, Canada', 'Department of Computer Science and Operations Research Université de Montréal, Pavillon André-Aisenstadt, PO Box 6128 Centre-Ville STN, Montréal, H3C 3J7, Quebec, Canada', "1] Google, 1600 Amphitheatre Parkway, Mountain View, California 94043, USA. [2] Department of Computer Science, University of Toronto, 6 King's College Road, Toronto, Ontario M5S 3G4, Canada", 'Google, 1600 Amphitheatre Parkway, Mountain View, 94043, California, USA', "Department of Computer Science, University of Toronto, 6 King's College Road, Toronto, M5S 3G4, Ontario, Canada"]</t>
+          <t>['Key Laboratory of Education Ministry for Modern Design and Rotor-Bearing System, Xi’an Jiaotong University, Xi’an 710049, China', 'Key Laboratory of Education Ministry for Modern Design and Rotor-Bearing System, Xi’an Jiaotong University, Xi’an 710049, China', 'Key Laboratory of Education Ministry for Modern Design and Rotor-Bearing System, Xi’an Jiaotong University, Xi’an 710049, China', 'Key Laboratory of Education Ministry for Modern Design and Rotor-Bearing System, Xi’an Jiaotong University, Xi’an 710049, China', 'Key Laboratory of Education Ministry for Modern Design and Rotor-Bearing System, Xi’an Jiaotong University, Xi’an 710049, China', 'Department of Electronic and Computer Engineering, Brunel University London, Uxbridge UB8 3PH, United Kingdom']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Yann LeCun (corresponding author), 1] Facebook AI Research, 770 Broadway, New York, New York 10003 USA. [2] New York University, 715 Broadway, New York, New York 10003, USA; Facebook AI Research, 770 Broadway, New York, 10003, New York, USA; New York University, 715 Broadway, New York, 10003, New York, USA</t>
+          <t>Yaguo Lei (corresponding author), Key Laboratory of Education Ministry for Modern Design and Rotor-Bearing System, Xi’an Jiaotong University, Xi’an 710049, China</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>7553</t>
-        </is>
-      </c>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>106587</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>106587</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>['Computer science', 'Deep learning', 'Artificial intelligence', 'Abstraction', 'Representation (politics)', 'Layer (electronics)', 'Object (grammar)', 'Backpropagation', 'Convolutional neural network', 'Feature learning', 'Pattern recognition (psychology)', 'Speech recognition', 'Artificial neural network']</t>
+          <t>['Artificial intelligence', 'Machine learning', 'Computer science', 'Bridge (graph theory)', 'Engineering']</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>['US', 'CA']</t>
+          <t>['CN', 'GB']</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>['Hochreiter S, 1997, NEURAL COMPUTATION', 'LeCun Y, 1998, PROCEEDINGS OF THE IEEE', 'Rumelhart D, 1986, NATURE', 'Mnih V, 2015, NATURE', 'Cho K, 2014, ', 'Hinton G, 2006, SCIENCE', 'Hinton G, 2006, NEURAL COMPUTATION', 'Hubel D, 1962, THE JOURNAL OF PHYSIOLOGY', 'Bengio Y, 2013, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Hinton G, 2012, IEEE SIGNAL PROCESSING MAGAZINE', 'Bengio Y, 1994, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Felleman D, 1991, CEREBRAL CORTEX', 'Vincent P, 2008, ', 'Bengio Y, 2009, NOW PUBLISHERS, INC. EBOOKS', ', 2018, THE MIT PRESS EBOOKS', 'Goldman‐Rakic P, 1991, CEREBRAL CORTEX', 'Clarke M, 1974, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES A (GENERAL)', 'Lawrence S, 1997, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Werbos P, 1974, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Farabet C, 2012, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Waibel A, 1989, IEEE TRANSACTIONS ON ACOUSTICS SPEECH AND SIGNAL PROCESSING', 'Mohamed A, 2011, IEEE TRANSACTIONS ON AUDIO SPEECH AND LANGUAGE PROCESSING', 'Xiong H, 2014, SCIENCE', 'Ma J, 2015, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Hinton G, 1995, SCIENCE', 'Helmstaedter M, 2013, NATURE', 'Cireşan D, 2012, NEURAL NETWORKS', 'Cadieu C, 2014, PLOS COMPUTATIONAL BIOLOGY', 'Raina R, 2009, ', 'Rogers T, 2004, THE MIT PRESS EBOOKS', 'García C, 2004, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Schwenk H, 2006, COMPUTER SPEECH &amp; LANGUAGE', 'Kavukcuoglu K, 2010, ', 'Leung M, 2014, BIOINFORMATICS', 'Turaga S, 2009, NEURAL COMPUTATION', 'Hadsell R, 2009, JOURNAL OF FIELD ROBOTICS', 'Feng N, 2005, IEEE TRANSACTIONS ON IMAGE PROCESSING', 'Bottou L, 2013, MACHINE LEARNING', 'Boser B, 1991, IEEE JOURNAL OF SOLID-STATE CIRCUITS', 'Farabet C, 2011, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Ciodaro T, 2012, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Neumann B, 2001, K&amp;UUML;NSTLICHE INTELL.', 'Ranzato M, 2013, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Nasr M, 2011, ', 'Xu K, 2015, ARXIV (CORNELL UNIVERSITY)', 'Sermanet P, 2013, ARXIV (CORNELL UNIVERSITY)', 'Dauphin Y, 2014, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>['Rumelhart D, 1986, NATURE', 'Nair V, 2010, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Koller D, 2009, ', 'Platt J, 1998, THE MIT PRESS EBOOKS', 'Gao Z, 2015, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Kira K, 1992, ELSEVIER EBOOKS', 'Kononenko I, 1994, LECTURE NOTES IN COMPUTER SCIENCE', 'Yin S, 2014, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Yang Y, 2005, JOURNAL OF SOUND AND VIBRATION', 'Chen J, 2015, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Thrun S, 1998, ', 'Hall M, 1998, RESEARCH COMMONS (UNIVERSITY OF WAIKATO)', 'Wang Y, 2015, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Tran V, 2014, EXPERT SYSTEMS WITH APPLICATIONS', 'Pandya D, 2013, EXPERT SYSTEMS WITH APPLICATIONS', 'Kothari S, 1993, ADVANCES IN COMPUTERS', 'Wu J, 2008, EXPERT SYSTEMS WITH APPLICATIONS', 'Li Y, 2015, MEASUREMENT', 'Yang J, 2006, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Lei Y, 2009, EXPERT SYSTEMS WITH APPLICATIONS', 'Zarei J, 2014, MECHATRONICS', 'Gryllias K, 2011, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Yang B, 2004, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Yang B, 2003, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Zhang X, 2015, NEUROCOMPUTING', 'Kang M, 2014, IEEE TRANSACTIONS ON POWER ELECTRONICS', 'Boutros T, 2011, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Keskes H, 2015, IEEE TRANSACTIONS ON INDUSTRIAL INFORMATICS', 'Ziani R, 2014, JOURNAL OF INTELLIGENT MANUFACTURING', 'Boukra T, 2012, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Widodo A, 2009, MECHATRONICS', 'Liu H, 2022, INDUSTRIAL AND ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE AND EXPERT SYSTEMS', 'Zhang K, 2011, NEUROCOMPUTING', 'Hang J, 2015, FUZZY SETS AND SYSTEMS', 'Chen J, 2015, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Kurek J, 2009, NEURAL COMPUTING AND APPLICATIONS', 'Walker R, 2014, MECHANISM AND MACHINE THEORY', 'Li F, 2015, NEUROCOMPUTING', 'Dong S, 2013, MEASUREMENT', 'Geramifard O, 2013, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Zhu K, 2015, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Wang Z, 2013, JOURNAL OF AEROSPACE ENGINEERING', 'Gelgele H, 1998, JOURNAL OF INTELLIGENT MANUFACTURING', 'Arabacı H, 2009, NEURAL COMPUTING AND APPLICATIONS', 'Qiu J, 2015, JOURNAL OF NATURAL GAS SCIENCE AND ENGINEERING', 'Yoon J, 2015, IET SCIENCE MEASUREMENT &amp; TECHNOLOGY', 'Zhong B, 1999, NEURAL COMPUTING AND APPLICATIONS', 'Xiao Z, 2015, MATHEMATICAL PROBLEMS IN ENGINEERING', 'Liu Q, 2003, NEURAL PROCESSING LETTERS', 'Krishnamurthi M, 1992, COMPUTERS &amp; INDUSTRIAL ENGINEERING', 'Samanta B, 2003, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Chiang L, 2003, COMPUTERS &amp; CHEMICAL ENGINEERING', 'Jack L, 2002, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Widodo A, 2008, EXPERT SYSTEMS WITH APPLICATIONS', 'Zhang X, 2013, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Ebrahimi B, 2013, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Shen C, 2013, MEASUREMENT', 'Lei Y, 2009, EXPERT SYSTEMS WITH APPLICATIONS', 'Saïdi L, 2014, ISA TRANSACTIONS', 'Ünal M, 2014, MEASUREMENT', 'Zhu K, 2013, MEASUREMENT', 'Amarnath M, 2012, MEASUREMENT', 'Jiang H, 2014, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Şahin S, 2011, EXPERT SYSTEMS WITH APPLICATIONS', 'He D, 2012, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Keskes H, 2013, ELECTRIC POWER SYSTEMS RESEARCH', 'Su Z, 2015, NEUROCOMPUTING', 'Li X, 2013, MEASUREMENT', 'Moosavi S, 2015, ELECTRIC POWER SYSTEMS RESEARCH', 'Wu S, 2013, ENTROPY', 'Tang X, 2010, KNOWLEDGE-BASED SYSTEMS', 'Yang D, 2002, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Jack L, 2001, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Wuxing L, 2003, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Yuwono M, 2015, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Li H, 2009, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Chen C, 2004, DIGITAL SIGNAL PROCESSING', 'Castejón C, 2009, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Vong C, 2011, EXPERT SYSTEMS WITH APPLICATIONS', 'Hao R, 2011, MEASUREMENT SCIENCE AND TECHNOLOGY', 'Kang M, 2013, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Wu J, 2009, EXPERT SYSTEMS WITH APPLICATIONS', 'He Y, 2013, INFORMATION SCIENCES', 'Wang G, 2007, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Gharavian M, 2013, NEUROCOMPUTING', 'Kuo R, 1995, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Wu J, 2006, EXPERT SYSTEMS WITH APPLICATIONS', 'Cabal‐Yépez E, 2012, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Mohammed A, 2013, MECCANICA', 'Van M, 2015, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Lin T, 2014, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Lu P, 2001, JOURNAL OF ENGINEERING FOR GAS TURBINES AND POWER', 'Varma A, 1999, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Sharkey A, 2000, NEURAL COMPUTING AND APPLICATIONS', 'Guo Q, 2006, DIGITAL SIGNAL PROCESSING', 'Vingerhoeds R, 1995, CONTROL ENGINEERING PRACTICE', 'Hajnayeb A, 2008, INDUSTRIAL LUBRICATION AND TRIBOLOGY', 'Wu H, 2004, AIRCRAFT ENGINEERING AND AEROSPACE TECHNOLOGY', 'Zhang C, 2010, ', 'White M, 1991, MEASUREMENT', 'Schmidhuber J, 2014, NEURAL NETWORKS', 'Bolón‐Canedo V, 2012, KNOWLEDGE AND INFORMATION SYSTEMS', 'Dai X, 2013, IEEE TRANSACTIONS ON INDUSTRIAL INFORMATICS', 'Lei Y, 2013, MEASUREMENT', 'Tamilselvan P, 2013, RELIABILITY ENGINEERING &amp; SYSTEM SAFETY', 'Samanta B, 2003, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Samanta B, 2003, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Lei Y, 2007, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Sugumaran V, 2006, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Abbasion S, 2007, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Yang Y, 2006, MEASUREMENT', 'Safizadeh M, 2013, INFORMATION FUSION', 'Widodo A, 2006, EXPERT SYSTEMS WITH APPLICATIONS', 'Widodo A, 2006, EXPERT SYSTEMS WITH APPLICATIONS', 'Wu S, 2012, ENTROPY', 'Sakthivel N, 2009, EXPERT SYSTEMS WITH APPLICATIONS', 'Jegadeeshwaran R, 2014, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Sheng-fa Y, 2005, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Wang Y, 2013, APPLIED ACOUSTICS', 'Hajnayeb A, 2011, EXPERT SYSTEMS WITH APPLICATIONS', 'Chen F, 2012, MEASUREMENT', 'Saravanan N, 2007, EXPERT SYSTEMS WITH APPLICATIONS', 'Yang D, 2015, MECHANISM AND MACHINE THEORY', 'Yang J, 2001, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Chen F, 2013, MEASUREMENT', 'Sugumaran V, 2007, EXPERT SYSTEMS WITH APPLICATIONS', 'Ebersbach S, 2006, EXPERT SYSTEMS WITH APPLICATIONS', 'Jiang L, 2013, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Wong M, 2005, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Rojas‐Domínguez A, 2005, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Salem S, 2012, ISA TRANSACTIONS', 'WU J, 2007, EXPERT SYSTEMS WITH APPLICATIONS', 'Lu W, 2013, JOURNAL OF SOUND AND VIBRATION', 'Widodo A, 2009, NONDESTRUCTIVE TESTING AND EVALUATION', 'Hernandez-Vargas M, 2014, COMPUTERS &amp; ELECTRICAL ENGINEERING', 'Wu J, 2010, EXPERT SYSTEMS WITH APPLICATIONS', 'Wu J, 2009, EXPERT SYSTEMS WITH APPLICATIONS', 'Kang M, 2014, IEEE TRANSACTIONS ON MAGNETICS', 'Ao H, 2013, JOURNAL OF VIBRATION AND CONTROL', 'Vong C, 2011, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Lei Y, 2009, JOURNAL OF VIBRATION AND ACOUSTICS', 'Barakat M, 2013, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Jiang L, 2012, JOURNAL OF VIBRATION AND CONTROL', 'Jena D, 2013, APPLIED ACOUSTICS', 'Xiao W, 2011, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Ilott P, 1997, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART E JOURNAL OF PROCESS MECHANICAL ENGINEERING', 'Chen X, 2014, APPLIED MATHEMATICS AND COMPUTATION', 'Wu J, 2007, EXPERT SYSTEMS WITH APPLICATIONS', 'Yu J, 2015, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Cortes C, 1995, MACHINE LEARNING', 'Quinlan J, 1992, ', '淳司 柴, 2017, JOURNAL OF JAPAN SOCIETY FOR FUZZY THEORY AND INTELLIGENT INFORMATICS', 'Hinton G, 2006, SCIENCE', 'Cover T, 1967, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Peng H, 2005, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Hinton G, 2002, NEURAL COMPUTATION', 'Tibshirani R, 2004, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Long M, 2013, ', 'Тихонов А, 1995, ', 'Dai W, 2007, ', 'Widodo A, 2007, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Liao S, 2004, EXPERT SYSTEMS WITH APPLICATIONS', 'Gao Z, 2015, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Naimi A, 2014, AMERICAN JOURNAL OF EPIDEMIOLOGY', 'Lei Y, 2010, EXPERT SYSTEMS WITH APPLICATIONS', 'Lei Y, 2009, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Sun W, 2006, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Muruganatham B, 2012, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Ebrahimi B, 2010, IEEE TRANSACTIONS ON POWER ELECTRONICS', 'Yang B, 2008, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Tang B, 2013, RENEWABLE ENERGY', 'Rafiee J, 2008, EXPERT SYSTEMS WITH APPLICATIONS', 'Li Z, 2012, MEASUREMENT', 'Ghate V, 2010, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Li N, 2011, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Jayaswal P, 2010, JOURNAL OF VIBRATION AND CONTROL', 'Yang B, 2005, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Tsoumas I, 2008, IEEE TRANSACTIONS ON ENERGY CONVERSION', 'Cerrada M, 2015, SENSORS', 'Lee H, 2000, IEEE TRANSACTIONS ON POWER DELIVERY', 'Bordoloi D, 2014, MEASUREMENT', 'Xian G, 2009, EXPERT SYSTEMS WITH APPLICATIONS', 'Bacha K, 2012, INTERNATIONAL JOURNAL OF ELECTRICAL POWER &amp; ENERGY SYSTEMS', 'Wang Y, 2011, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Knapp G, 1992, INTERNATIONAL JOURNAL OF PRODUCTION RESEARCH', 'Namdari M, 2014, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Shahriar M, 2013, EURASIP JOURNAL ON IMAGE AND VIDEO PROCESSING', 'Barakat M, 2012, INTERNATIONAL JOURNAL OF MACHINE LEARNING AND CYBERNETICS', 'Becerra J, 2011, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'McCormick A, 1997, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'McCormick A, 1997, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Liu S, 2003, THE INTERNATIONAL JOURNAL OF ADVANCED MANUFACTURING TECHNOLOGY', 'Liu T, 2013, JOURNAL OF VIBRATION AND CONTROL', 'Almeida L, 2014, JOURNAL OF VIBRATION AND CONTROL', 'S V, 2012, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART J JOURNAL OF ENGINEERING TRIBOLOGY', 'Angeli C, 1999, EXPERT SYSTEMS', 'Chen H, 2013, DOAJ (DOAJ: DIRECTORY OF OPEN ACCESS JOURNALS)', 'Shen Y, 2006, ', 'He K, 2016, ', 'Pan S, 2009, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', ', 2013, CHOICE REVIEWS ONLINE', 'Jia F, 2015, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'İnce T, 2016, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Lei Y, 2016, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Rai A, 2016, TRIBOLOGY INTERNATIONAL', 'Lü C, 2016, SIGNAL PROCESSING', 'Lu W, 2016, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Shao H, 2015, MEASUREMENT SCIENCE AND TECHNOLOGY', 'Li C, 2016, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Zheng J, 2016, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Li C, 2015, NEUROCOMPUTING', 'Liu H, 2016, SHOCK AND VIBRATION', 'Long M, 2016, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Yang T, 2016, IEEE TRANSACTIONS ON INSTRUMENTATION AND MEASUREMENT', 'Ayhan B, 2006, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Zhang X, 2015, KNOWLEDGE-BASED SYSTEMS', 'Yin J, 2016, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Sadeghian A, 2009, IEEE TRANSACTIONS ON INSTRUMENTATION AND MEASUREMENT', 'Xie J, 2016, ', 'Zhou H, 2015, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Głowacz A, 2016, APPLIED ACOUSTICS', 'Malik H, 2016, IET RENEWABLE POWER GENERATION', 'Shen F, 2015, ', 'Asr M, 2016, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Goyal D, 2016, ARCHIVES OF COMPUTATIONAL METHODS IN ENGINEERING', 'Li Y, 2016, MECHANISM AND MACHINE THEORY', 'Yang Z, 2016, ENERGIES', 'Liu H, 2016, JOURNAL OF SOUND AND VIBRATION', 'Liu Y, 2015, NEUROCOMPUTING', 'Li Z, 2012, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Waqar T, 2016, MEASUREMENT', 'Abu-Mahfouz I, 2005, INTERNATIONAL JOURNAL OF GENERAL SYSTEMS', 'Kane P, 2016, JOURNAL OF LOW FREQUENCY NOISE, VIBRATION AND ACTIVE CONTROL', 'Chen J, 2016, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Dong S, 2015, JOURNAL OF THE BRAZILIAN SOCIETY OF MECHANICAL SCIENCES AND ENGINEERING', 'Sun J, 2014, TM - TECHNISCHES MESSEN', 'Palácios R, 2016, JOURNAL OF CONTROL AUTOMATION AND ELECTRICAL SYSTEMS', 'An X, 2016, TRANSACTIONS OF THE INSTITUTE OF MEASUREMENT AND CONTROL', 'Dong S, 2015, MEASUREMENT AND CONTROL', 'Khazaee M, 2016, STRUCTURAL HEALTH MONITORING', 'Wong P, 2016, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Lee S, 2009, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Jiang X, 2015, JOURNAL OF VIBROENGINEERING', 'Heidari M, 2016, JOURNAL OF VIBROENGINEERING', 'Liu Z, 2012, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Khazaee M, 2016, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART D JOURNAL OF AUTOMOBILE ENGINEERING', 'Jin X, 2014, JOURNAL OF VIBROENGINEERING', 'Goodfellow I, 2016, MIT PRESS EBOOKS', 'Zhāng W, 2017, SENSORS', 'Zhāng W, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Chen Z, 2017, IEEE TRANSACTIONS ON INSTRUMENTATION AND MEASUREMENT', 'Xia M, 2017, IEEE/ASME TRANSACTIONS ON MECHATRONICS', 'Jing L, 2017, MEASUREMENT', 'Shao H, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Jia F, 2017, NEUROCOMPUTING', 'Ding X, 2017, IEEE TRANSACTIONS ON INSTRUMENTATION AND MEASUREMENT', 'Lü C, 2017, ADVANCED ENGINEERING INFORMATICS', 'Zhang R, 2017, IEEE ACCESS', 'Jing L, 2017, SENSORS', 'Shao H, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Wang Z, 2017, IEEE SENSORS JOURNAL', 'Liu R, 2016, IEEE TRANSACTIONS ON INDUSTRIAL INFORMATICS', 'Sun W, 2017, IEEE TRANSACTIONS ON INDUSTRIAL INFORMATICS', 'Shao H, 2017, ISA TRANSACTIONS', 'Li Y, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Eren L, 2017, MATHEMATICAL PROBLEMS IN ENGINEERING', 'Li S, 2017, SENSORS', 'Janssens O, 2017, IEEE/ASME TRANSACTIONS ON MECHATRONICS', 'Fuan W, 2017, MEASUREMENT SCIENCE AND TECHNOLOGY', 'Gangsar P, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Ahmed H, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Xia M, 2017, IET SCIENCE MEASUREMENT &amp; TECHNOLOGY', 'Sun W, 2017, MATERIALS', 'Li C, 2017, IEEE ACCESS', 'Guo X, 2016, APPLIED SCIENCES', 'He J, 2017, SENSORS', 'Martínez-Morales J, 2016, ELECTRICAL ENGINEERING', 'Gao Z, 2017, NEUROCOMPUTING', 'Xing Z, 2017, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Cheng F, 2016, IEEE TRANSACTIONS ON INDUSTRY APPLICATIONS', 'Qu Y, 2017, APPLIED SCIENCES', 'Merainani B, 2017, JOURNAL OF VIBRATION AND CONTROL', 'Ma J, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Cai C, 2017, CLUSTER COMPUTING', 'Li Z, 2016, JOURNAL OF PROPULSION AND POWER', 'Yao B, 2017, IEEE ACCESS', 'Chen C, 2017, ', 'Islam M, 2017, THE JOURNAL OF THE ACOUSTICAL SOCIETY OF AMERICA', 'He X, 2016, MATHEMATICAL PROBLEMS IN ENGINEERING', 'Wu L, 2017, APPLIED SCIENCES', 'Jiang H, 2017, JOURNAL OF VIBROENGINEERING', 'Yan J, 2016, JOURNAL OF VIBROENGINEERING', 'Xu T, 2017, JOURNAL OF INTELLIGENT &amp; FUZZY SYSTEMS', 'Wang J, 2016, ', 'Heidari M, 2017, JOURNAL OF VIBROENGINEERING', 'Gerdes M, 2016, EKSPLOATACJA I NIEZAWODNOSC - MAINTENANCE AND RELIABILITY', 'Wen L, 2017, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Liu R, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Khan S, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Wen L, 2017, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS SYSTEMS', 'Li Y, 2018, PATTERN RECOGNITION', 'Liu H, 2018, ISA TRANSACTIONS', 'Jia F, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Shao H, 2017, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Cao P, 2018, IEEE ACCESS', 'Shao H, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Sun J, 2017, IEEE TRANSACTIONS ON INSTRUMENTATION AND MEASUREMENT', 'Verstraete D, 2017, SHOCK AND VIBRATION', 'Zhao M, 2017, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Shao H, 2017, KNOWLEDGE-BASED SYSTEMS', 'Ma M, 2018, IEEE TRANSACTIONS ON INDUSTRIAL INFORMATICS', 'Wang S, 2017, KNOWLEDGE-BASED SYSTEMS', 'Guo S, 2018, SENSORS', 'Zhang Y, 2018, JOURNAL OF MANUFACTURING SYSTEMS', 'Duan Z, 2018, THE INTERNATIONAL JOURNAL OF ADVANCED MANUFACTURING TECHNOLOGY', 'Li Y, 2017, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Li Y, 2018, JOURNAL OF SOUND AND VIBRATION', 'Islam M, 2018, RELIABILITY ENGINEERING &amp; SYSTEM SAFETY', 'Shao S, 2017, CHINESE JOURNAL OF MECHANICAL ENGINEERING', 'Park S, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Venkateswara H, 2017, IEEE SIGNAL PROCESSING MAGAZINE', 'Berredjem T, 2018, EXPERT SYSTEMS WITH APPLICATIONS', 'Chen Y, 2018, NEUROCOMPUTING', 'Shao H, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Zhang X, 2017, NEUROCOMPUTING', 'Tang S, 2018, NEUROCOMPUTING', 'Zhu X, 2018, IEEE ACCESS', 'Praveenkumar T, 2017, MEASUREMENT', 'Yu D, 2018, INTERNATIONAL JOURNAL OF ELECTRICAL POWER &amp; ENERGY SYSTEMS', 'Sohaib M, 2018, SHOCK AND VIBRATION', 'Gangsar P, 2018, JOURNAL OF DYNAMIC SYSTEMS MEASUREMENT AND CONTROL', 'Huang D, 2018, MICROELECTRONICS RELIABILITY', 'Naha A, 2017, IEEE TRANSACTIONS ON INSTRUMENTATION AND MEASUREMENT', 'Vanraj, 2017, STRUCTURAL HEALTH MONITORING', 'Zgarni S, 2018, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Han D, 2017, ADVANCES IN MECHANICAL ENGINEERING', 'Dong S, 2017, JOURNAL OF LOW FREQUENCY NOISE, VIBRATION AND ACTIVE CONTROL', 'Duong B, 2018, SENSORS', 'Tang T, 2018, JOURNAL OF SOUND AND VIBRATION', 'Wang X, 2017, JOURNAL OF VIBROENGINEERING', 'Yu J, 2018, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Tyagi S, 2017, APPLIED ARTIFICIAL INTELLIGENCE', 'Yuan H, 2017, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Safizadeh M, 2017, INSIGHT - NON-DESTRUCTIVE TESTING AND CONDITION MONITORING', 'Jiang Q, 2017, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Jiang F, 2018, ADVANCES IN MECHANICAL ENGINEERING', 'Zhao R, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Shao S, 2018, IEEE TRANSACTIONS ON INDUSTRIAL INFORMATICS', 'Guo L, 2018, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Jiang G, 2018, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Hoang D, 2018, NEUROCOMPUTING', 'Stetco A, 2018, RENEWABLE ENERGY', 'Eren L, 2018, JOURNAL OF SIGNAL PROCESSING SYSTEMS', 'Li X, 2018, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Zhu Z, 2018, NEUROCOMPUTING', 'Li X, 2018, NEUROCOMPUTING', ', 2017, ELSEVIER EBOOKS', 'Liu G, 2018, MATHEMATICAL PROBLEMS IN ENGINEERING', 'Meng Z, 2018, MEASUREMENT', 'Han T, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Zhao M, 2018, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Shen C, 2018, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Guo Y, 2018, APPLIED ENERGY', 'Zhang B, 2018, IEEE ACCESS', 'Guo D, 2018, NEUROCOMPUTING', 'Li Y, 2018, JOURNAL OF SOUND AND VIBRATION', 'Han Y, 2018, MEASUREMENT', 'Mao W, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Jiao J, 2018, KNOWLEDGE-BASED SYSTEMS', 'Yao Y, 2018, APPLIED SCIENCES', 'Jafarian K, 2018, MEASUREMENT', 'Hasan M, 2018, APPLIED SCIENCES', 'Tong Z, 2018, IEEE ACCESS', 'Zhao X, 2018, NEUROCOMPUTING', 'Appana D, 2018, SOFT COMPUTING', 'Duan L, 2018, JOURNAL OF INTELLIGENT &amp; FUZZY SYSTEMS', 'Jin Y, 2018, IEEE TRANSACTIONS ON INSTRUMENTATION AND MEASUREMENT', 'Xie J, 2018, IEEE ACCESS', 'Wang J, 2018, MEASUREMENT SCIENCE AND TECHNOLOGY', 'Ahmed H, 2018, IEEE ACCESS', 'Singh M, 2018, MEASUREMENT', 'Rapur J, 2018, JOURNAL OF THE BRAZILIAN SOCIETY OF MECHANICAL SCIENCES AND ENGINEERING', 'Zhuang Y, 2018, MEASUREMENT SCIENCE AND TECHNOLOGY', 'Rapur J, 2018, JOURNAL OF NONDESTRUCTIVE EVALUATION', 'Zabihihesari A, 2018, PROCEEDINGS OF THE INSTITUTION OF MECHANICAL ENGINEERS PART C JOURNAL OF MECHANICAL ENGINEERING SCIENCE', 'Yu J, 2018, JOURNAL OF SOUND AND VIBRATION', 'Zheng Y, 2019, SENSORS', 'Saufi M, 2018, MEASUREMENT SCIENCE AND TECHNOLOGY', 'Zhang M, 2018, IEEE TRANSACTIONS ON INSTRUMENTATION AND MEASUREMENT', 'Jiang F, 2018, APPLIED SCIENCES', 'Jiang H, 2018, JOURNAL OF INTELLIGENT &amp; FUZZY SYSTEMS', 'Zhou P, 2018, APPLIED SCIENCES', 'Yu H, 2018, IEEE SIGNAL PROCESSING LETTERS', 'Liu L, 2018, JOURNAL OF SOUND AND VIBRATION', 'Xin Y, 2018, JOURNAL OF VIBROENGINEERING', 'Chen Z, 2018, JOURNAL OF INTELLIGENT &amp; FUZZY SYSTEMS', 'Breiman L, 2001, MACHINE LEARNING', 'LeCun Y, 2015, NATURE', 'Cortes C, 1995, MACHINE LEARNING', 'Gu J, 2017, PATTERN RECOGNITION', 'Yang B, 2019, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Xu Y, 2019, IEEE ACCESS', 'Han T, 2018, KNOWLEDGE-BASED SYSTEMS', 'We Z, 2018, ISA TRANSACTIONS', 'Qiao Z, 2019, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Yang B, 2019, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Peng D, 2018, IEEE ACCESS', 'Zhao D, 2019, COMPUTERS IN INDUSTRY', 'Huang R, 2018, IEEE ACCESS', 'Cao X, 2019, COMPUTERS IN INDUSTRY', 'Islam M, 2019, COMPUTERS IN INDUSTRY', 'Wang X, 2019, IEEE TRANSACTIONS ON INDUSTRIAL INFORMATICS', 'Zheng H, 2019, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Liu X, 2019, SENSORS', 'Xu X, 2019, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Ma S, 2019, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Han Y, 2019, COMPUTERS IN INDUSTRY', 'Li X, 2019, APPLIED SCIENCES', 'Su L, 2019, IEEE TRANSACTIONS ON INDUSTRIAL INFORMATICS', 'Qian W, 2018, IEEE ACCESS', 'Guo S, 2018, SENSORS', 'Suh S, 2019, APPLIED SCIENCES', 'Tong Z, 2018, SHOCK AND VIBRATION', 'Chen H, 2013, SHOCK AND VIBRATION', 'Li J, 2019, SENSORS', 'Gangsar P, 2019, JOURNAL OF THE BRAZILIAN SOCIETY OF MECHANICAL SCIENCES AND ENGINEERING', 'Li Y, 2019, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Tang G, 2018, APPLIED SCIENCES', 'Xie Y, 2018, ', 'Pang B, 2018, ENTROPY', 'Yang B, 2018, 2018 INTERNATIONAL CONFERENCE ON SENSING,DIAGNOSTICS, PROGNOSTICS, AND CONTROL (SDPC)', 'Qian W, 2018, ', 'Chen X, 2019, COMPLEXITY', 'Yu J, 2018, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Jia Y, 2018, SENSORS', 'Zhang X, 2019, JOURNAL OF MECHANICAL SCIENCE AND TECHNOLOGY', 'Chunfeng W, 2018, ']</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -11102,12 +11110,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>LeCun Y, 2015, NATURE</t>
+          <t>Lei Y, 2020, MECHANICAL SYSTEMS AND SIGNAL PROCESSING</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>LeCun Y, 2015, NATURE</t>
+          <t>Lei Y, 2020, MECHANICAL SYSTEMS AND SIGNAL PROCESSING</t>
         </is>
       </c>
     </row>
@@ -11232,22 +11240,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2342408547</t>
+          <t>https://openalex.org/W2910705748</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>10.1109/comst.2015.2494502</t>
+          <t>10.1073/pnas.1900654116</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>A Survey of Data Mining and Machine Learning Methods for Cyber Security Intrusion Detection</t>
+          <t>Definitions, methods, and applications in interpretable machine learning</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -11261,62 +11269,66 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>3064</v>
+        <v>2070</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>IEEE COMMUNICATIONS SURVEYS &amp; TUTORIALS</t>
+          <t>PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>IEEE Communications Surveys &amp; Tutorials</t>
+          <t>Proceedings of the National Academy of Sciences</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>['Anna L. Buczak', 'Erhan Guven']</t>
+          <t>['William J. Murdoch', 'Chandan Singh', 'Karl Kumbier', 'Reza Abbasi-Asl', 'Bin Yu']</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>['Anna L. Buczak', 'Erhan Guven']</t>
+          <t>['W. James Murdoch', 'Chandan Singh', 'Karl Kumbier', 'Reza Abbasi-Asl', 'Bin Yu']</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['The Johns Hopkins University Applied Physics Laboratory, Laurel, MD, USA', 'The Johns Hopkins University Applied Physics Laboratory, Laurel, MD, USA']</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr"/>
+          <t>['Statistics Department, University of California, Berkeley, CA 94720;', 'Electrical Engineering and Computer Science Department, University of California, Berkeley, CA 94720;', 'Statistics Department, University of California, Berkeley, CA 94720;', 'Allen Institute for Brain Science, Seattle, WA 98109', 'Department of Neurology, University of California, San Francisco, CA 94158;', 'Electrical Engineering and Computer Science Department, University of California, Berkeley, CA 94720;', 'Department of Neurology, University of California, San Francisco, CA 94158; and', 'Electrical Engineering and Computer Science Department, University of California, Berkeley, CA 94720;', 'Statistics Department, University of California, Berkeley, CA 94720;']</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Bin Yu (corresponding author), Electrical Engineering and Computer Science Department, University of California, Berkeley, CA 94720;; Statistics Department, University of California, Berkeley, CA 94720;</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>This survey paper describes a focused literature survey of machine learning (ML) and data mining (DM) methods for cyber analytics in support of intrusion detection. Short tutorial descriptions of each ML/DM method are provided. Based on the number of citations or the relevance of an emerging method, papers representing each method were identified, read, and summarized. Because data are so important in ML/DM approaches, some well-known cyber data sets used in ML/DM are described. The complexity of ML/DM algorithms is addressed, discussion of challenges for using ML/DM for cyber security is presented, and some recommendations on when to use a given method are provided.</t>
+          <t>Machine-learning models have demonstrated great success in learning complex patterns that enable them to make predictions about unobserved data. In addition to using models for prediction, the ability to interpret what a model has learned is receiving an increasing amount of attention. However, this increased focus has led to considerable confusion about the notion of interpretability. In particular, it is unclear how the wide array of proposed interpretation methods are related and what common concepts can be used to evaluate them. We aim to address these concerns by defining interpretability in the context of machine learning and introducing the predictive, descriptive, relevant (PDR) framework for discussing interpretations. The PDR framework provides 3 overarching desiderata for evaluation: predictive accuracy, descriptive accuracy, and relevancy, with relevancy judged relative to a human audience. Moreover, to help manage the deluge of interpretation methods, we introduce a categorization of existing techniques into model-based and post hoc categories, with subgroups including sparsity, modularity, and simulatability. To demonstrate how practitioners can use the PDR framework to evaluate and understand interpretations, we provide numerous real-world examples. These examples highlight the often underappreciated role played by human audiences in discussions of interpretability. Finally, based on our framework, we discuss limitations of existing methods and directions for future work. We hope that this work will provide a common vocabulary that will make it easier for both practitioners and researchers to discuss and choose from the full range of interpretation methods.</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>116</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>22071</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>22080</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>['Computer science', 'Intrusion detection system', 'Data mining', 'Relevance (law)', 'Analytics', 'Intrusion', 'Data science', 'Machine learning']</t>
+          <t>['Interpretability', 'Computer science', 'Artificial intelligence', 'Categorization', 'Machine learning', 'Context (archaeology)', 'Interpretation (philosophy)', 'Modularity (biology)', 'Vocabulary', 'Data science', 'Focus (optics)']</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
@@ -11326,7 +11338,7 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>['Dempster A, 1977, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Witten I, 2011, ELSEVIER EBOOKS', 'Ester M, 1996, ', 'Koza J, 1992, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Rosenblatt F, 1958, PSYCHOLOGICAL REVIEW', 'Sarle W, 1990, TECHNOMETRICS', 'Salzberg S, 1994, ', 'Jain A, 1996, COMPUTER', 'Jensen F, 2007, INFORMATION SCIENCE AND STATISTICS', 'Cohen W, 1995, ELSEVIER EBOOKS', 'Goldberg D, 1988, MACHINE LEARNING', 'Beyer H, 2002, NATURAL COMPUTING', 'Agrawal R, 1996, KNOWLEDGE DISCOVERY AND DATA MINING', 'Fayyad U, 1996, COMMUNICATIONS OF THE ACM', 'Huang G, 2011, INTERNATIONAL JOURNAL OF MACHINE LEARNING AND CYBERNETICS', 'Heckerman D, 2008, STUDIES IN COMPUTATIONAL INTELLIGENCE', 'Bhuyan M, 2013, IEEE COMMUNICATIONS SURVEYS &amp; TUTORIALS', 'Lee W, 2003, ', 'Moiseev S, 1981, PHYSICA D NONLINEAR PHENOMENA', 'Baum L, 1967, BULLETIN OF THE AMERICAN MATHEMATICAL SOCIETY', 'Lippmann R, 2002, ', 'Lippmann R, 2000, COMPUTER NETWORKS', 'Zhang Y, 2003, WIRELESS NETWORKS', 'Kuok C, 1998, ACM SIGMOD RECORD', 'Bilge L, 2011, ', 'Amiri F, 2011, JOURNAL OF NETWORK AND COMPUTER APPLICATIONS', 'Shon T, 2007, INFORMATION SCIENCES', 'Lyon G, 2009, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Cannady J, 1998, NSUWORKS (NOVA SOUTHEASTERN UNIVERSITY)', 'Li Y, 2011, EXPERT SYSTEMS WITH APPLICATIONS', 'Leung K, 2005, ', 'Livadas C, 2006, ', 'Lippmann R, 2000, COMPUTER NETWORKS', 'Kruegel C, 2003, LECTURE NOTES IN COMPUTER SCIENCE', 'Ahsan K, 2002, ', 'Sequeira K, 2002, ', 'Oliveto P, 2007, INTERNATIONAL JOURNAL OF AUTOMATION AND COMPUTING', 'Hu W, 2003, INTERNATIONAL CONFERENCE ON MACHINE LEARNING AND APPLICATIONS', 'Hu Y, 2004, ', 'Ariu D, 2011, COMPUTERS &amp; SECURITY', 'Joshi S, 2005, ', 'Wagner C, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Jemili F, 2007, ', 'Årnes A, 2006, LECTURE NOTES IN COMPUTER SCIENCE', 'Blowers M, 2013, ADVANCES IN INFORMATION SECURITY', 'Brahmi H, 2012, LECTURE NOTES IN COMPUTER SCIENCE', 'Graczyk M, 2009, LECTURE NOTES IN COMPUTER SCIENCE', 'Apiletti D, 2008, COMPUTER NETWORKS', 'Hendry G, 2008, PROCEEDINGS OF SPIE, THE INTERNATIONAL SOCIETY FOR OPTICAL ENGINEERING/PROCEEDINGS OF SPIE', 'Li Z, 2007, ', 'Breiman L, 2001, MACHINE LEARNING', 'Kennedy J, 2002, ', 'Watts D, 1998, NATURE', 'Vapnik V, 1995, ', 'Quinlan J, 1992, ', 'Hornik K, 1989, NEURAL NETWORKS', 'Dean J, 2008, COMMUNICATIONS OF THE ACM', 'Hall M, 2009, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Burges C, 1998, DATA MINING AND KNOWLEDGE DISCOVERY', 'Quinlan J, 1986, MACHINE LEARNING', 'Agrawal R, 1993, ', 'Friedman J, 1991, THE ANNALS OF STATISTICS', 'Dorigo M, 1997, IEEE TRANSACTIONS ON EVOLUTIONARY COMPUTATION', 'Freund Y, 1996, ', 'Flury B, 1989, JOURNAL OF STATISTICAL PLANNING AND INFERENCE', 'Forney G, 1973, PROCEEDINGS OF THE IEEE', 'Agrawal R, 2002, ', 'Tavallaee M, 2009, ', 'Polikar R, 2006, IEEE CIRCUITS AND SYSTEMS MAGAZINE', 'Caruana R, 2006, ', 'García‐Teodoro P, 2008, COMPUTERS &amp; SECURITY', 'Thu T, 2008, IEEE COMMUNICATIONS SURVEYS &amp; TUTORIALS', 'Wu S, 2009, APPLIED SOFT COMPUTING', 'Holland P, 1971, COMPARATIVE GROUP STUDIES', 'Zhang J, 2008, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS PART C (APPLICATIONS AND REVIEWS)', 'Amor N, 2004, ', 'Sperotto A, 2010, IEEE COMMUNICATIONS SURVEYS &amp; TUTORIALS', 'Mukkamala S, 2004, JOURNAL OF NETWORK AND COMPUTER APPLICATIONS', 'Kruegel C, 2004, ', 'Bilge L, 2014, ACM TRANSACTIONS ON INFORMATION AND SYSTEM SECURITY', 'Li W, 2004, NSUWORKS (NOVA SOUTHEASTERN UNIVERSITY)', 'Bilge L, 2012, ', 'Tajbakhsh A, 2008, APPLIED SOFT COMPUTING', 'Panda M, 2007, ', 'Fan W, 2004, KNOWLEDGE AND INFORMATION SYSTEMS', 'Bivens A, 2002, ', 'Guazzelli A, 2009, THE R JOURNAL', 'Lu W, 2004, COMPUTATIONAL INTELLIGENCE', 'Luo J, 2000, INTERNATIONAL JOURNAL OF INTELLIGENT SYSTEMS', 'Abraham A, 2007, ', 'Hansen J, 2006, DECISION SUPPORT SYSTEMS', 'Gharibian F, 2007, ', 'Morel B, 2011, ', 'Benferhat S, 2008, ', 'Khan M, 2011, INTERNATIONAL JOURNAL OF COMPUTER APPLICATIONS', 'Mukkamala S, 2004, ', 'Long P, 2007, ', 'Han H, 2003, ', 'Hussain O, 2007, ', 'Zadeh L, 1965, INFORMATION AND CONTROL', 'Zadeh L, 1996, ', 'Quinlan J, 1986, MACHINE LEARNING', 'HornikK., 1989, NEURAL NETWORKS', 'Chiang L, 2001, ADVANCED TEXTBOOKS IN CONTROL AND SIGNAL PROCESSING', 'Jensen F, 2001, ', 'Farmer J, 1986, PHYSICA D NONLINEAR PHENOMENA', 'Rahbar, 2008, IEEE COMMUNICATIONS SURVEYS &amp; TUTORIALS', 'Ye N, 2013, ', 'Michalski R, 1983, MACHINE LEARNING', 'Michalski R, 1983, MACHINE LEARNING', 'Beyer H, 2007, SCHOLARPEDIA', 'Hu Z, 2008, ', 'Jolliffe I, 2005, ENCYCLOPEDIA OF STATISTICS IN BEHAVIORAL SCIENCE']</t>
+          <t>['Tibshirani R, 1996, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Dalal N, 2005, ', 'Gordon A, 1984, BIOMETRICS', 'Wickham H, 2009, ', 'Zeiler M, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Ribeiro M, 2016, ', 'Ginestet C, 2011, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES A (STATISTICS IN SOCIETY)', 'Burnham K, 2004, SOCIOLOGICAL METHODS &amp; RESEARCH', 'McKinney W, 2010, PROCEEDINGS OF THE PYTHON IN SCIENCE CONFERENCES', 'Bell A, 1995, NEURAL COMPUTATION', 'Goodall C, 1988, TECHNOMETRICS', 'Koller D, 2009, ', 'Hotelling H, 1936, BIOMETRIKA', 'boyd d, 2012, INFORMATION COMMUNICATION &amp; SOCIETY', 'Pati Y, 2002, ', 'Breiman L, 2001, STATISTICAL SCIENCE', 'Pérez F, 2007, COMPUTING IN SCIENCE &amp; ENGINEERING', 'Akaike H, 1987, SPRINGER SERIES IN STATISTICS', 'Ruppert D, 1987, TECHNOMETRICS', 'Olshausen B, 1997, VISION RESEARCH', 'Hastie T, 1986, STATISTICAL SCIENCE', 'Dwork C, 2012, ', 'Strobl C, 2008, BMC BIOINFORMATICS', 'Altmann A, 2010, BIOINFORMATICS', 'Box G, 1976, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Caruana R, 2015, ', 'Keil F, 2005, ANNUAL REVIEW OF PSYCHOLOGY', 'Hastie T, 1995, STATISTICAL METHODS IN MEDICAL RESEARCH', 'Friedman J, 2008, THE ANNALS OF APPLIED STATISTICS', 'Olden J, 2004, ECOLOGICAL MODELLING', 'Huang C, 2006, EXPERT SYSTEMS WITH APPLICATIONS', 'Letham B, 2015, THE ANNALS OF APPLIED STATISTICS', 'Lombrozo T, 2006, TRENDS IN COGNITIVE SCIENCES', 'Schulz S, 2005, ', 'Craven M, 1995, NEURAL INFORMATION PROCESSING SYSTEMS', 'Roe A, 2012, NEURON', 'Zaidan O, 2007, ', 'Freedman D, 1989, MATHEMATICAL SOCIAL SCIENCES', 'Amaratunga D, 2008, BIOINFORMATICS', 'Hooker G, 2007, JOURNAL OF COMPUTATIONAL AND GRAPHICAL STATISTICS', 'Wu S, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Lim C, 2015, JOURNAL OF COMPUTATIONAL AND GRAPHICAL STATISTICS', 'Caruana R, 1999, PUBMED', 'Brennan T, 2013, CRIMINOLOGY &amp; PUBLIC POLICY', 'Shi T, 2008, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Springenberg J, 2014, ARXIV (CORNELL UNIVERSITY)', 'Karpathy A, 2015, ARXIV (CORNELL UNIVERSITY)', 'Baehrens D, 2009, ARXIV.ORG', 'Wei D, 2015, ARXIV (CORNELL UNIVERSITY)', 'Barter R, 2015, ARXIV (CORNELL UNIVERSITY)', 'Breiman L, 2001, MACHINE LEARNING', 'Flach P, 2015, ', 'Litjens G, 2017, MEDICAL IMAGE ANALYSIS', 'Teymur O, 2016, ', 'Charles-Maxime G, 2024, DAGSTUHL RESEARCH ONLINE PUBLICATION SERVER', 'Rudin C, 2019, NATURE MACHINE INTELLIGENCE', 'Ribeiro M, 2016, ', 'Guidotti R, 2019, ISTI OPEN PORTAL', 'Kluyver T, 2016, IOS PRESS EBOOKS', 'Goodman B, 2017, AI MAGAZINE', 'Jennison C, 1987, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES A (GENERAL)', 'Angermueller C, 2016, MOLECULAR SYSTEMS BIOLOGY', 'Datta A, 2016, ', 'Chakraborty S, 2017, ', 'Ancona M, 2018, REPOSITORY FOR PUBLICATIONS AND RESEARCH DATA (ETH ZURICH)', 'Strobelt H, 2017, IEEE TRANSACTIONS ON VISUALIZATION AND COMPUTER GRAPHICS', 'Kim J, 2017, ', 'Basu S, 2018, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Zhang Q, 2018, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Guidotti R, 2018, ACM COMPUTING SURVEYS', 'Vu M, 2018, JOURNAL OF NEUROSCIENCE', 'Rudin C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Gilpin L, 2018, ARXIV (CORNELL UNIVERSITY)', 'Doshi‐Velez F, 2017, ARXIV (CORNELL UNIVERSITY)', 'Selvaraju R, 2016, ARXIV (CORNELL UNIVERSITY)', 'Strobelt H, 2016, REPEC: RESEARCH PAPERS IN ECONOMICS', 'Abbasi-Asl R, 2017, ARXIV (CORNELL UNIVERSITY)', 'Pimentel H, 2018, QUANTITATIVE BIOLOGY', 'Lundberg S, 2017, ARXIV (CORNELL UNIVERSITY)', 'Sundararajan M, 2017, ARXIV (CORNELL UNIVERSITY)', 'Hardt M, 2016, ARXIV (CORNELL UNIVERSITY)', 'Koh P, 2017, ARXIV (CORNELL UNIVERSITY)', 'Adebayo J, 2018, ARXIV (CORNELL UNIVERSITY)', 'Shrikumar A, 2016, ARXIV (CORNELL UNIVERSITY)', 'Lundberg S, 2018, ARXIV (CORNELL UNIVERSITY)', 'Zintgraf L, 2017, ARXIV (CORNELL UNIVERSITY)', 'Papernot N, 2018, ARXIV (CORNELL UNIVERSITY)', 'Frosst N, 2017, ARXIV (CORNELL UNIVERSITY)', 'Murdoch W, 2018, ARXIV (CORNELL UNIVERSITY)', 'Dabkowski P, 2017, ARXIV (CORNELL UNIVERSITY)', 'Singh C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Murdoch W, 2017, ARXIV (CORNELL UNIVERSITY)', 'Nie W, 2018, ARXIV (CORNELL UNIVERSITY)', 'Kim J, 2017, ARXIV (CORNELL UNIVERSITY)', 'Abbasi-Asl R, 2018, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Zhang Q, 2017, ARXIV (CORNELL UNIVERSITY)', 'Kumbier K, 2018, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Tsang M, 2018, ARXIV (CORNELL UNIVERSITY)', 'Kumbier K, 2018, ARXIV (CORNELL UNIVERSITY)', 'Devlin S, 2019, ARXIV (CORNELL UNIVERSITY)', 'Wickham H, 2016, USE R!', 'Ryzin J, 1986, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', ', 1996, COMPUTERS &amp; MATHEMATICS WITH APPLICATIONS', 'Jolliffe I, 1986, SPRINGER SERIES IN STATISTICS', 'Hotelling H, 1936, BIOMETRIKA', 'Olah C, 2017, DISTILL', 'A. R, 2016, MAX PLANCK DIGITAL LIBRARY', 'Box G, 1976, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Freedman D, 1991, SOCIOLOGICAL METHODOLOGY', 'Bell A, 1999, THE MIT PRESS EBOOKS', 'Yu B, 2013, BERNOULLI', 'Murdoch W, 2018, ARXIV (CORNELL UNIVERSITY)', 'Singh C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Olden J, 2004, ECOLOGICAL MODELLING', ', 1993, ', 'Wickham H, 2016, ', 'Varoquaux G, 2010, PROCEEDINGS OF THE PYTHON IN SCIENCE CONFERENCES']</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -11342,34 +11354,34 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>Buczak A, 2015, IEEE COMMUNICATIONS SURVEYS &amp; TUTORIALS</t>
+          <t>Murdoch W, 2019, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>Buczak A, 2015, IEEE COMMUNICATIONS SURVEYS &amp; TUTORIALS</t>
+          <t>Murdoch W, 2019, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2910705748</t>
+          <t>https://openalex.org/W2342408547</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>10.1073/pnas.1900654116</t>
+          <t>10.1109/comst.2015.2494502</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Definitions, methods, and applications in interpretable machine learning</t>
+          <t>A Survey of Data Mining and Machine Learning Methods for Cyber Security Intrusion Detection</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -11383,66 +11395,62 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>2066</v>
+        <v>3068</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES</t>
+          <t>IEEE COMMUNICATIONS SURVEYS &amp; TUTORIALS</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Proceedings of the National Academy of Sciences</t>
+          <t>IEEE Communications Surveys &amp; Tutorials</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>['William J. Murdoch', 'Chandan Singh', 'Karl Kumbier', 'Reza Abbasi-Asl', 'Bin Yu']</t>
+          <t>['Anna L. Buczak', 'Erhan Guven']</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>['W. James Murdoch', 'Chandan Singh', 'Karl Kumbier', 'Reza Abbasi-Asl', 'Bin Yu']</t>
+          <t>['Anna L. Buczak', 'Erhan Guven']</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>['Statistics Department, University of California, Berkeley, CA 94720;', 'Electrical Engineering and Computer Science Department, University of California, Berkeley, CA 94720;', 'Statistics Department, University of California, Berkeley, CA 94720;', 'Allen Institute for Brain Science, Seattle, WA 98109', 'Department of Neurology, University of California, San Francisco, CA 94158;', 'Electrical Engineering and Computer Science Department, University of California, Berkeley, CA 94720;', 'Department of Neurology, University of California, San Francisco, CA 94158; and', 'Electrical Engineering and Computer Science Department, University of California, Berkeley, CA 94720;', 'Statistics Department, University of California, Berkeley, CA 94720;']</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>Bin Yu (corresponding author), Electrical Engineering and Computer Science Department, University of California, Berkeley, CA 94720;; Statistics Department, University of California, Berkeley, CA 94720;</t>
-        </is>
-      </c>
+          <t>['The Johns Hopkins University Applied Physics Laboratory, Laurel, MD, USA', 'The Johns Hopkins University Applied Physics Laboratory, Laurel, MD, USA']</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Machine-learning models have demonstrated great success in learning complex patterns that enable them to make predictions about unobserved data. In addition to using models for prediction, the ability to interpret what a model has learned is receiving an increasing amount of attention. However, this increased focus has led to considerable confusion about the notion of interpretability. In particular, it is unclear how the wide array of proposed interpretation methods are related and what common concepts can be used to evaluate them. We aim to address these concerns by defining interpretability in the context of machine learning and introducing the predictive, descriptive, relevant (PDR) framework for discussing interpretations. The PDR framework provides 3 overarching desiderata for evaluation: predictive accuracy, descriptive accuracy, and relevancy, with relevancy judged relative to a human audience. Moreover, to help manage the deluge of interpretation methods, we introduce a categorization of existing techniques into model-based and post hoc categories, with subgroups including sparsity, modularity, and simulatability. To demonstrate how practitioners can use the PDR framework to evaluate and understand interpretations, we provide numerous real-world examples. These examples highlight the often underappreciated role played by human audiences in discussions of interpretability. Finally, based on our framework, we discuss limitations of existing methods and directions for future work. We hope that this work will provide a common vocabulary that will make it easier for both practitioners and researchers to discuss and choose from the full range of interpretation methods.</t>
+          <t>This survey paper describes a focused literature survey of machine learning (ML) and data mining (DM) methods for cyber analytics in support of intrusion detection. Short tutorial descriptions of each ML/DM method are provided. Based on the number of citations or the relevance of an emerging method, papers representing each method were identified, read, and summarized. Because data are so important in ML/DM approaches, some well-known cyber data sets used in ML/DM are described. The complexity of ML/DM algorithms is addressed, discussion of challenges for using ML/DM for cyber security is presented, and some recommendations on when to use a given method are provided.</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>22071</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>22080</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>['Interpretability', 'Computer science', 'Artificial intelligence', 'Categorization', 'Machine learning', 'Context (archaeology)', 'Interpretation (philosophy)', 'Modularity (biology)', 'Vocabulary', 'Data science', 'Focus (optics)']</t>
+          <t>['Computer science', 'Intrusion detection system', 'Data mining', 'Relevance (law)', 'Analytics', 'Intrusion', 'Data science', 'Machine learning']</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
@@ -11452,7 +11460,7 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>['Tibshirani R, 1996, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Dalal N, 2005, ', 'Gordon A, 1984, BIOMETRICS', 'Wickham H, 2009, ', 'Zeiler M, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Ribeiro M, 2016, ', 'Ginestet C, 2011, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES A (STATISTICS IN SOCIETY)', 'Burnham K, 2004, SOCIOLOGICAL METHODS &amp; RESEARCH', 'McKinney W, 2010, PROCEEDINGS OF THE PYTHON IN SCIENCE CONFERENCES', 'Bell A, 1995, NEURAL COMPUTATION', 'Goodall C, 1988, TECHNOMETRICS', 'Koller D, 2009, ', 'Hotelling H, 1936, BIOMETRIKA', 'boyd d, 2012, INFORMATION COMMUNICATION &amp; SOCIETY', 'Pati Y, 2002, ', 'Breiman L, 2001, STATISTICAL SCIENCE', 'Pérez F, 2007, COMPUTING IN SCIENCE &amp; ENGINEERING', 'Akaike H, 1987, SPRINGER SERIES IN STATISTICS', 'Ruppert D, 1987, TECHNOMETRICS', 'Olshausen B, 1997, VISION RESEARCH', 'Hastie T, 1986, STATISTICAL SCIENCE', 'Dwork C, 2012, ', 'Strobl C, 2008, BMC BIOINFORMATICS', 'Altmann A, 2010, BIOINFORMATICS', 'Box G, 1976, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Caruana R, 2015, ', 'Keil F, 2005, ANNUAL REVIEW OF PSYCHOLOGY', 'Hastie T, 1995, STATISTICAL METHODS IN MEDICAL RESEARCH', 'Friedman J, 2008, THE ANNALS OF APPLIED STATISTICS', 'Olden J, 2004, ECOLOGICAL MODELLING', 'Huang C, 2006, EXPERT SYSTEMS WITH APPLICATIONS', 'Letham B, 2015, THE ANNALS OF APPLIED STATISTICS', 'Lombrozo T, 2006, TRENDS IN COGNITIVE SCIENCES', 'Schulz S, 2005, ', 'Craven M, 1995, NEURAL INFORMATION PROCESSING SYSTEMS', 'Roe A, 2012, NEURON', 'Zaidan O, 2007, ', 'Freedman D, 1989, MATHEMATICAL SOCIAL SCIENCES', 'Amaratunga D, 2008, BIOINFORMATICS', 'Hooker G, 2007, JOURNAL OF COMPUTATIONAL AND GRAPHICAL STATISTICS', 'Wu S, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Lim C, 2015, JOURNAL OF COMPUTATIONAL AND GRAPHICAL STATISTICS', 'Caruana R, 1999, PUBMED', 'Brennan T, 2013, CRIMINOLOGY &amp; PUBLIC POLICY', 'Shi T, 2008, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Springenberg J, 2014, ARXIV (CORNELL UNIVERSITY)', 'Karpathy A, 2015, ARXIV (CORNELL UNIVERSITY)', 'Baehrens D, 2009, ARXIV.ORG', 'Wei D, 2015, ARXIV (CORNELL UNIVERSITY)', 'Barter R, 2015, ARXIV (CORNELL UNIVERSITY)', 'Breiman L, 2001, MACHINE LEARNING', 'Flach P, 2015, ', 'Litjens G, 2017, MEDICAL IMAGE ANALYSIS', 'Teymur O, 2016, ', 'Charles-Maxime G, 2024, DAGSTUHL RESEARCH ONLINE PUBLICATION SERVER', 'Rudin C, 2019, NATURE MACHINE INTELLIGENCE', 'Ribeiro M, 2016, ', 'Guidotti R, 2019, ISTI OPEN PORTAL', 'Kluyver T, 2016, IOS PRESS EBOOKS', 'Goodman B, 2017, AI MAGAZINE', 'Jennison C, 1987, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES A (GENERAL)', 'Angermueller C, 2016, MOLECULAR SYSTEMS BIOLOGY', 'Datta A, 2016, ', 'Chakraborty S, 2017, ', 'Ancona M, 2018, REPOSITORY FOR PUBLICATIONS AND RESEARCH DATA (ETH ZURICH)', 'Strobelt H, 2017, IEEE TRANSACTIONS ON VISUALIZATION AND COMPUTER GRAPHICS', 'Kim J, 2017, ', 'Basu S, 2018, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Zhang Q, 2018, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Guidotti R, 2018, ACM COMPUTING SURVEYS', 'Vu M, 2018, JOURNAL OF NEUROSCIENCE', 'Rudin C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Gilpin L, 2018, ARXIV (CORNELL UNIVERSITY)', 'Doshi‐Velez F, 2017, ARXIV (CORNELL UNIVERSITY)', 'Selvaraju R, 2016, ARXIV (CORNELL UNIVERSITY)', 'Strobelt H, 2016, REPEC: RESEARCH PAPERS IN ECONOMICS', 'Abbasi-Asl R, 2017, ARXIV (CORNELL UNIVERSITY)', 'Pimentel H, 2018, QUANTITATIVE BIOLOGY', 'Lundberg S, 2017, ARXIV (CORNELL UNIVERSITY)', 'Sundararajan M, 2017, ARXIV (CORNELL UNIVERSITY)', 'Hardt M, 2016, ARXIV (CORNELL UNIVERSITY)', 'Koh P, 2017, ARXIV (CORNELL UNIVERSITY)', 'Adebayo J, 2018, ARXIV (CORNELL UNIVERSITY)', 'Shrikumar A, 2016, ARXIV (CORNELL UNIVERSITY)', 'Lundberg S, 2018, ARXIV (CORNELL UNIVERSITY)', 'Zintgraf L, 2017, ARXIV (CORNELL UNIVERSITY)', 'Papernot N, 2018, ARXIV (CORNELL UNIVERSITY)', 'Frosst N, 2017, ARXIV (CORNELL UNIVERSITY)', 'Murdoch W, 2018, ARXIV (CORNELL UNIVERSITY)', 'Dabkowski P, 2017, ARXIV (CORNELL UNIVERSITY)', 'Singh C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Murdoch W, 2017, ARXIV (CORNELL UNIVERSITY)', 'Nie W, 2018, ARXIV (CORNELL UNIVERSITY)', 'Kim J, 2017, ARXIV (CORNELL UNIVERSITY)', 'Abbasi-Asl R, 2018, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Zhang Q, 2017, ARXIV (CORNELL UNIVERSITY)', 'Kumbier K, 2018, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Tsang M, 2018, ARXIV (CORNELL UNIVERSITY)', 'Kumbier K, 2018, ARXIV (CORNELL UNIVERSITY)', 'Devlin S, 2019, ARXIV (CORNELL UNIVERSITY)', 'Wickham H, 2016, USE R!', 'Ryzin J, 1986, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', ', 1996, COMPUTERS &amp; MATHEMATICS WITH APPLICATIONS', 'Jolliffe I, 1986, SPRINGER SERIES IN STATISTICS', 'Hotelling H, 1936, BIOMETRIKA', 'Olah C, 2017, DISTILL', 'A. R, 2016, MAX PLANCK DIGITAL LIBRARY', 'Box G, 1976, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Freedman D, 1991, SOCIOLOGICAL METHODOLOGY', 'Bell A, 1999, THE MIT PRESS EBOOKS', 'Yu B, 2013, BERNOULLI', 'Murdoch W, 2018, ARXIV (CORNELL UNIVERSITY)', 'Singh C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Olden J, 2004, ECOLOGICAL MODELLING', ', 1993, ', 'Wickham H, 2016, ', 'Varoquaux G, 2010, PROCEEDINGS OF THE PYTHON IN SCIENCE CONFERENCES']</t>
+          <t>['Dempster A, 1977, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Witten I, 2011, ELSEVIER EBOOKS', 'Ester M, 1996, ', 'Koza J, 1992, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Rosenblatt F, 1958, PSYCHOLOGICAL REVIEW', 'Sarle W, 1990, TECHNOMETRICS', 'Salzberg S, 1994, ', 'Jain A, 1996, COMPUTER', 'Jensen F, 2007, INFORMATION SCIENCE AND STATISTICS', 'Cohen W, 1995, ELSEVIER EBOOKS', 'Goldberg D, 1988, MACHINE LEARNING', 'Beyer H, 2002, NATURAL COMPUTING', 'Agrawal R, 1996, KNOWLEDGE DISCOVERY AND DATA MINING', 'Fayyad U, 1996, COMMUNICATIONS OF THE ACM', 'Huang G, 2011, INTERNATIONAL JOURNAL OF MACHINE LEARNING AND CYBERNETICS', 'Heckerman D, 2008, STUDIES IN COMPUTATIONAL INTELLIGENCE', 'Bhuyan M, 2013, IEEE COMMUNICATIONS SURVEYS &amp; TUTORIALS', 'Lee W, 2003, ', 'Moiseev S, 1981, PHYSICA D NONLINEAR PHENOMENA', 'Baum L, 1967, BULLETIN OF THE AMERICAN MATHEMATICAL SOCIETY', 'Lippmann R, 2002, ', 'Lippmann R, 2000, COMPUTER NETWORKS', 'Zhang Y, 2003, WIRELESS NETWORKS', 'Kuok C, 1998, ACM SIGMOD RECORD', 'Bilge L, 2011, ', 'Amiri F, 2011, JOURNAL OF NETWORK AND COMPUTER APPLICATIONS', 'Shon T, 2007, INFORMATION SCIENCES', 'Lyon G, 2009, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Cannady J, 1998, NSUWORKS (NOVA SOUTHEASTERN UNIVERSITY)', 'Li Y, 2011, EXPERT SYSTEMS WITH APPLICATIONS', 'Leung K, 2005, ', 'Livadas C, 2006, ', 'Lippmann R, 2000, COMPUTER NETWORKS', 'Kruegel C, 2003, LECTURE NOTES IN COMPUTER SCIENCE', 'Ahsan K, 2002, ', 'Sequeira K, 2002, ', 'Oliveto P, 2007, INTERNATIONAL JOURNAL OF AUTOMATION AND COMPUTING', 'Hu W, 2003, INTERNATIONAL CONFERENCE ON MACHINE LEARNING AND APPLICATIONS', 'Hu Y, 2004, ', 'Ariu D, 2011, COMPUTERS &amp; SECURITY', 'Joshi S, 2005, ', 'Wagner C, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Jemili F, 2007, ', 'Årnes A, 2006, LECTURE NOTES IN COMPUTER SCIENCE', 'Blowers M, 2013, ADVANCES IN INFORMATION SECURITY', 'Brahmi H, 2012, LECTURE NOTES IN COMPUTER SCIENCE', 'Graczyk M, 2009, LECTURE NOTES IN COMPUTER SCIENCE', 'Apiletti D, 2008, COMPUTER NETWORKS', 'Hendry G, 2008, PROCEEDINGS OF SPIE, THE INTERNATIONAL SOCIETY FOR OPTICAL ENGINEERING/PROCEEDINGS OF SPIE', 'Li Z, 2007, ', 'Breiman L, 2001, MACHINE LEARNING', 'Kennedy J, 2002, ', 'Watts D, 1998, NATURE', 'Vapnik V, 1995, ', 'Quinlan J, 1992, ', 'Hornik K, 1989, NEURAL NETWORKS', 'Dean J, 2008, COMMUNICATIONS OF THE ACM', 'Hall M, 2009, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Burges C, 1998, DATA MINING AND KNOWLEDGE DISCOVERY', 'Quinlan J, 1986, MACHINE LEARNING', 'Agrawal R, 1993, ', 'Friedman J, 1991, THE ANNALS OF STATISTICS', 'Dorigo M, 1997, IEEE TRANSACTIONS ON EVOLUTIONARY COMPUTATION', 'Freund Y, 1996, ', 'Flury B, 1989, JOURNAL OF STATISTICAL PLANNING AND INFERENCE', 'Forney G, 1973, PROCEEDINGS OF THE IEEE', 'Agrawal R, 2002, ', 'Tavallaee M, 2009, ', 'Polikar R, 2006, IEEE CIRCUITS AND SYSTEMS MAGAZINE', 'Caruana R, 2006, ', 'García‐Teodoro P, 2008, COMPUTERS &amp; SECURITY', 'Thu T, 2008, IEEE COMMUNICATIONS SURVEYS &amp; TUTORIALS', 'Wu S, 2009, APPLIED SOFT COMPUTING', 'Holland P, 1971, COMPARATIVE GROUP STUDIES', 'Zhang J, 2008, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS PART C (APPLICATIONS AND REVIEWS)', 'Amor N, 2004, ', 'Sperotto A, 2010, IEEE COMMUNICATIONS SURVEYS &amp; TUTORIALS', 'Mukkamala S, 2004, JOURNAL OF NETWORK AND COMPUTER APPLICATIONS', 'Kruegel C, 2004, ', 'Bilge L, 2014, ACM TRANSACTIONS ON INFORMATION AND SYSTEM SECURITY', 'Li W, 2004, NSUWORKS (NOVA SOUTHEASTERN UNIVERSITY)', 'Bilge L, 2012, ', 'Tajbakhsh A, 2008, APPLIED SOFT COMPUTING', 'Panda M, 2007, ', 'Fan W, 2004, KNOWLEDGE AND INFORMATION SYSTEMS', 'Bivens A, 2002, ', 'Guazzelli A, 2009, THE R JOURNAL', 'Lu W, 2004, COMPUTATIONAL INTELLIGENCE', 'Luo J, 2000, INTERNATIONAL JOURNAL OF INTELLIGENT SYSTEMS', 'Abraham A, 2007, ', 'Hansen J, 2006, DECISION SUPPORT SYSTEMS', 'Gharibian F, 2007, ', 'Morel B, 2011, ', 'Benferhat S, 2008, ', 'Khan M, 2011, INTERNATIONAL JOURNAL OF COMPUTER APPLICATIONS', 'Mukkamala S, 2004, ', 'Long P, 2007, ', 'Han H, 2003, ', 'Hussain O, 2007, ', 'Zadeh L, 1965, INFORMATION AND CONTROL', 'Zadeh L, 1996, ', 'Quinlan J, 1986, MACHINE LEARNING', 'HornikK., 1989, NEURAL NETWORKS', 'Chiang L, 2001, ADVANCED TEXTBOOKS IN CONTROL AND SIGNAL PROCESSING', 'Jensen F, 2001, ', 'Farmer J, 1986, PHYSICA D NONLINEAR PHENOMENA', 'Rahbar, 2008, IEEE COMMUNICATIONS SURVEYS &amp; TUTORIALS', 'Ye N, 2013, ', 'Michalski R, 1983, MACHINE LEARNING', 'Michalski R, 1983, MACHINE LEARNING', 'Beyer H, 2007, SCHOLARPEDIA', 'Hu Z, 2008, ', 'Jolliffe I, 2005, ENCYCLOPEDIA OF STATISTICS IN BEHAVIORAL SCIENCE']</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -11468,12 +11476,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>Murdoch W, 2019, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES</t>
+          <t>Buczak A, 2015, IEEE COMMUNICATIONS SURVEYS &amp; TUTORIALS</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>Murdoch W, 2019, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES</t>
+          <t>Buczak A, 2015, IEEE COMMUNICATIONS SURVEYS &amp; TUTORIALS</t>
         </is>
       </c>
     </row>
@@ -11505,7 +11513,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -11611,7 +11619,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>2392</v>
+        <v>2394</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -11668,7 +11676,7 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>['Friedman J, 2001, THE ANNALS OF STATISTICS', 'He K, 2015, ', 'Zeiler M, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Bednorz J, 1986, THE EUROPEAN PHYSICAL JOURNAL B', 'Murphy K, 2012, ', 'Jones D, 1998, JOURNAL OF GLOBAL OPTIMIZATION', 'Jensen F, 1998, ', 'Bach S, 2015, PLOS ONE', 'Strobl C, 2007, BMC BIOINFORMATICS', 'Devroye L, 1996, STOCHASTIC MODELLING AND APPLIED PROBABILITY', 'Martin R, 2004, ', 'Gori M, 2006, PROCEEDINGS. 2005 IEEE INTERNATIONAL JOINT CONFERENCE ON NEURAL NETWORKS, 2005.', 'Thompson A, 2014, JOURNAL OF COMPUTATIONAL PHYSICS', 'Vert J, 2004, THE MIT PRESS EBOOKS', 'Jong M, 2015, SCIENTIFIC DATA', 'Braams B, 2009, INTERNATIONAL REVIEWS IN PHYSICAL CHEMISTRY', ', 2005, CHOICE REVIEWS ONLINE', 'Kaner R, 2005, SCIENCE', 'Drucker H, 1997, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Guzella T, 2009, EXPERT SYSTEMS WITH APPLICATIONS', ', 2008, CHOICE REVIEWS ONLINE', 'Seko A, 2015, PHYSICAL REVIEW LETTERS', 'Maddox J, 1988, NATURE', 'Chan P, 1998, ', 'Faber F, 2016, PHYSICAL REVIEW LETTERS', 'Kolen J, 2009, ', 'Lee J, 2016, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Ghasemi S, 2015, PHYSICAL REVIEW B', 'Isayev O, 2014, CHEMISTRY OF MATERIALS', 'Ramakrishnan R, 2015, THE JOURNAL OF CHEMICAL PHYSICS', 'Vellido A, 2012, ', 'Gaultois M, 2016, APL MATERIALS', 'Seko A, 2015, PHYSICAL REVIEW B', 'Pettifor D, 1988, MATERIALS SCIENCE AND TECHNOLOGY', 'Seko A, 2014, PHYSICAL REVIEW B', 'Sumpter B, 1992, CHEMICAL PHYSICS LETTERS', 'Yoon B, 2013, IEEE TRANSACTIONS ON SIGNAL PROCESSING', 'Zakutayev A, 2014, CHEMISTRY OF MATERIALS', 'Broderick S, 2011, JOURNAL OF THE AMERICAN CERAMIC SOCIETY', 'Devroye L, 1996, STOCHASTIC MODELLING AND APPLIED PROBABILITY', 'Siddorn M, 2015, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Wang Y, 2015, SIAM JOURNAL ON SCIENTIFIC COMPUTING', 'Liu S, 2010, LECTURE NOTES IN COMPUTER SCIENCE', 'Meremianin A, 2006, JOURNAL OF PHYSICS A MATHEMATICAL AND GENERAL', 'Owolabi T, 2014, JOURNALS &amp; BOOKS HOSTING (INTERNATIONAL KNOWLEDGE SHARING PLATFORM)', 'Johnson D, 2013, ELSEVIER EBOOKS', 'Lindström D, 2015, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Bruna J, 2013, ARXIV (CORNELL UNIVERSITY)', 'Weyl H, , ', 'Baldi P, 1998, ', 'Perdew J, 1996, PHYSICAL REVIEW LETTERS', 'Freund Y, 1997, JOURNAL OF COMPUTER AND SYSTEM SCIENCES', 'McCulloch W, 1943, BULLETIN OF MATHEMATICAL BIOLOGY', 'Jain A, 2013, APL MATERIALS', 'Hill R, 1952, PROCEEDINGS OF THE PHYSICAL SOCIETY SECTION A', 'Tran F, 2009, PHYSICAL REVIEW LETTERS', 'Ong S, 2012, COMPUTATIONAL MATERIALS SCIENCE', 'Schmidt M, 2009, SCIENCE', 'Wang Y, 2012, COMPUTER PHYSICS COMMUNICATIONS', 'Saal J, 2013, JOM', 'Behler J, 2011, THE JOURNAL OF CHEMICAL PHYSICS', 'Kitchin J, 2004, PHYSICAL REVIEW LETTERS', 'Loader C, 1999, STATISCTICS AND COMPUTING/STATISTICS AND COMPUTING', 'Martoňák R, 2003, PHYSICAL REVIEW LETTERS', 'Leininger T, 1997, CHEMICAL PHYSICS LETTERS', 'Kohn W, 1965, PHYSICAL REVIEW LETTERS', 'Pickard C, 2006, PHYSICAL REVIEW LETTERS', 'Tsuneyuki S, 1988, PHYSICAL REVIEW LETTERS', 'Hautier G, 2010, CHEMISTRY OF MATERIALS', 'Fischer C, 2006, NATURE MATERIALS', 'Koskinen P, 2009, COMPUTATIONAL MATERIALS SCIENCE', 'Lüders M, 2005, PHYSICAL REVIEW B', 'Éliashberg G, 1960, JOURNAL OF EXPERIMENTAL AND THEORETICAL PHYSICS', 'Matthias B, 1955, PHYSICAL REVIEW', 'Szlachta W, 2014, PHYSICAL REVIEW B', 'Cśanyi G, 2004, PHYSICAL REVIEW LETTERS', 'Schön J, 1996, ANGEWANDTE CHEMIE INTERNATIONAL EDITION IN ENGLISH', 'Baskes M, 1997, MATERIALS CHEMISTRY AND PHYSICS', 'Pannetier J, 1990, NATURE', 'Becker C, 2013, CURRENT OPINION IN SOLID STATE AND MATERIALS SCIENCE', 'Sosso G, 2012, PHYSICAL REVIEW B', 'Harper P, 1955, PROCEEDINGS OF THE PHYSICAL SOCIETY SECTION A', 'Johnson S, 2007, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Bajorath J, 2009, DRUG DISCOVERY TODAY', 'Kuz’min V, 2008, JOURNAL OF COMPUTER-AIDED MOLECULAR DESIGN', 'Ruggiu F, 2010, MOLECULAR INFORMATICS', 'Pettifor D, 1986, JOURNAL OF PHYSICS C SOLID STATE PHYSICS', 'Lam P, 1987, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Schneider G, 2008, TRENDS IN BIOTECHNOLOGY', 'Owolabi T, 2014, JOURNAL OF SUPERCONDUCTIVITY AND NOVEL MAGNETISM', 'Moussa J, 2012, PHYSICAL REVIEW LETTERS', 'Xu B, 2013, SCIENTIFIC REPORTS', 'Sanville E, 2008, JOURNAL OF PHYSICS CONDENSED MATTER', 'Kadantsev E, 2004, PHYSICAL REVIEW A', 'Abdellahi M, 2014, CERAMICS INTERNATIONAL', 'Villars P, 1988, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Sinkov N, 2010, TALANTA', 'Matos C, 2007, ANALYTICAL CHEMISTRY', 'Cohen M, 1988, MATERIALS SCIENCE AND ENGINEERING A', 'Doll K, 2008, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Hochreiter S, 1997, NEURAL COMPUTATION', 'MacKerell A, 1998, THE JOURNAL OF PHYSICAL CHEMISTRY B', 'Rosenblatt F, 1958, PSYCHOLOGICAL REVIEW', 'Geurts P, 2006, MACHINE LEARNING', 'Daw M, 1984, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Stillinger F, 1985, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Behler J, 2007, PHYSICAL REVIEW LETTERS', 'Goldschmidt V, 1926, DIE NATURWISSENSCHAFTEN', 'Ackley D, 1985, COGNITIVE SCIENCE', 'Bartók A, 2013, PHYSICAL REVIEW B', 'Oganov A, 2006, THE JOURNAL OF CHEMICAL PHYSICS', 'Porezag D, 1995, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Werner P, 1985, JOURNAL OF APPLIED CRYSTALLOGRAPHY', 'Tersoff J, 1986, PHYSICAL REVIEW LETTERS', 'Cohen M, 1985, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Waag W, 2014, JOURNAL OF POWER SOURCES', 'Woodley S, 2008, NATURE MATERIALS', 'Maggiora G, 2006, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Snyder J, 2012, PHYSICAL REVIEW LETTERS', 'Li Z, 2015, PHYSICAL REVIEW LETTERS', 'Montavon G, 2013, NEW JOURNAL OF PHYSICS', 'Sanders M, 1984, JOURNAL OF THE CHEMICAL SOCIETY CHEMICAL COMMUNICATIONS', 'Blank T, 1995, THE JOURNAL OF CHEMICAL PHYSICS', 'Schütt K, 2014, PHYSICAL REVIEW B', 'Koinuma H, 2004, NATURE MATERIALS', 'Dalsin J, 2005, MATERIALS TODAY', 'Khaliullin R, 2011, NATURE MATERIALS', 'Olson G, 2000, SCIENCE', 'Handley C, 2010, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Marques M, 2005, PHYSICAL REVIEW B', 'Yan J, 2014, ENERGY &amp; ENVIRONMENTAL SCIENCE', 'Pettifor D, 1984, SOLID STATE COMMUNICATIONS', 'Seifert G, 2012, WILEY INTERDISCIPLINARY REVIEWS COMPUTATIONAL MOLECULAR SCIENCE', 'Tozer D, 1996, THE JOURNAL OF CHEMICAL PHYSICS', 'Dey P, 2013, COMPUTATIONAL MATERIALS SCIENCE', 'Snyder J, 2013, THE JOURNAL OF CHEMICAL PHYSICS', 'Shoemaker D, 2014, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Zhang X, 2012, ADVANCED FUNCTIONAL MATERIALS', 'Eshet H, 2010, PHYSICAL REVIEW B', 'Gilman J, 2001, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Kuz’min V, 2005, JOURNAL OF MOLECULAR MODELING', 'Gu T, 2005, SOLID STATE SCIENCES', 'Walsh A, 2015, NATURE CHEMISTRY', 'Suram S, 2015, ACS COMBINATORIAL SCIENCE', 'Tatlıer M, 2010, NEURAL COMPUTING AND APPLICATIONS', 'Plaut D, 1987, COMPUTER SPEECH &amp; LANGUAGE', 'Rabe K, 1992, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Freeman C, 1992, JOURNAL OF THE CHEMICAL SOCIETY CHEMICAL COMMUNICATIONS', 'Morita T, 1957, JOURNAL OF THE PHYSICAL SOCIETY OF JAPAN', 'Becke A, 1988, PHYSICAL REVIEW. A, GENERAL PHYSICS', 'Srivastava N, 2014, ', '淳司 柴, 2017, JOURNAL OF JAPAN SOCIETY FOR FUZZY THEORY AND INTELLIGENT INFORMATICS', 'Hinton G, 2006, SCIENCE', 'Hasan M, 2010, REVIEWS OF MODERN PHYSICS', 'Heyd J, 2003, THE JOURNAL OF CHEMICAL PHYSICS', 'Boser B, 1992, ', 'Murnaghan F, 1944, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Birch F, 1947, PHYSICAL REVIEW', 'Golbraikh A, 2002, JOURNAL OF MOLECULAR GRAPHICS AND MODELLING', 'Geman S, 1992, NEURAL COMPUTATION', 'Schapire R, 1990, MACHINE LEARNING', 'Stanley K, 2002, EVOLUTIONARY COMPUTATION', 'Moore J, 2010, NATURE', 'Bartók A, 2010, PHYSICAL REVIEW LETTERS', 'Wang Y, 2010, PHYSICAL REVIEW B', 'Liu A, 1989, SCIENCE', 'Cahill D, 1992, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Rupp M, 2012, PHYSICAL REVIEW LETTERS', 'Forrester A, 2009, PROGRESS IN AEROSPACE SCIENCES', 'Tropsha A, 2003, QSAR &amp; COMBINATORIAL SCIENCE', 'Ramakrishnan R, 2014, SCIENTIFIC DATA', 'Daw M, 1993, MATERIALS SCIENCE REPORTS', 'Beest B, 1990, PHYSICAL REVIEW LETTERS', 'Picard R, 1984, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Nguyen A, 2013, APPLIED ENERGY', 'Gražulis S, 2011, NUCLEIC ACIDS RESEARCH', 'Chapelle O, 2011, ', 'Goedecker S, 2004, THE JOURNAL OF CHEMICAL PHYSICS', 'Huang C, 2006, EXPERT SYSTEMS WITH APPLICATIONS', 'Santosa F, 1986, SIAM JOURNAL ON SCIENTIFIC AND STATISTICAL COMPUTING', 'Foulkes W, 1989, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Potyrailo R, 2011, ACS COMBINATORIAL SCIENCE', 'Artrith N, 2011, PHYSICAL REVIEW B', 'Blatov V, 2004, CRYSTALLOGRAPHY REVIEWS', 'Seko A, 2014, PHYSICAL REVIEW B', 'Oganov A, 2009, THE JOURNAL OF CHEMICAL PHYSICS', 'Paszkowicz W, 2013, MATERIALS AND MANUFACTURING PROCESSES', 'Pukrittayakamee A, 2009, THE JOURNAL OF CHEMICAL PHYSICS', 'Park W, 2012, ADVANCED FUNCTIONAL MATERIALS', 'Kramer G, 1991, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Bush T, 1995, JOURNAL OF MATERIALS CHEMISTRY', 'Eijck B, 2000, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE', 'Villars P, 2003, JOURNAL OF ALLOYS AND COMPOUNDS', 'Gale J, 1998, THE JOURNAL OF PHYSICAL CHEMISTRY B', 'Witkoskie J, 2004, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Gottwald D, 2005, THE JOURNAL OF CHEMICAL PHYSICS', 'Sastre G, 2003, CHEMISTRY OF MATERIALS', 'Chen Z, 2005, ANALYTICAL CHEMISTRY', 'Agatonović-Kuštrin S, 2000, JOURNAL OF PHARMACEUTICAL AND BIOMEDICAL ANALYSIS', 'He K, 2016, ', 'Krizhevsky A, 2017, COMMUNICATIONS OF THE ACM', 'LeCun Y, 1998, PROCEEDINGS OF THE IEEE', 'Tibshirani R, 1996, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Zou H, 2005, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Wang J, 2004, JOURNAL OF COMPUTATIONAL CHEMISTRY', 'Quinlan J, 1986, MACHINE LEARNING', 'Bengio Y, 2013, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'LeCun Y, 1989, NEURAL COMPUTATION', 'Snyder G, 2008, NATURE MATERIALS', 'Tropp J, 2007, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Scarselli F, 2008, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Candès E, 2006, COMMUNICATIONS ON PURE AND APPLIED MATHEMATICS', 'Duin A, 2001, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Glorot X, 2012, ', 'Pati Y, 2002, ', 'Cordero B, 2008, DALTON TRANSACTIONS', 'LeCun Y, 1989, NEURAL INFORMATION PROCESSING SYSTEMS', 'Browne C, 2012, IEEE TRANSACTIONS ON COMPUTATIONAL INTELLIGENCE AND AI IN GAMES', 'Fan J, 2008, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Quinlan J, 1987, INTERNATIONAL JOURNAL OF MAN-MACHINE STUDIES', 'Curtarolo S, 2013, NATURE MATERIALS', 'Ruddigkeit L, 2012, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Glass C, 2006, COMPUTER PHYSICS COMMUNICATIONS', 'Pickard C, 2011, JOURNAL OF PHYSICS CONDENSED MATTER', 'Pazzani M, 1997, MACHINE LEARNING', 'Vítek V, 1968, PHILOSOPHICAL MAGAZINE', 'Morgenstern D, 1962, ECONOMETRICA', 'Ghiringhelli L, 2015, PHYSICAL REVIEW LETTERS', 'Blum L, 2009, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Evgeniou T, 2005, ', 'Alexander J, 1928, TRANSACTIONS OF THE AMERICAN MATHEMATICAL SOCIETY', 'Hachmann J, 2011, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Shan S, 2009, STRUCTURAL AND MULTIDISCIPLINARY OPTIMIZATION', 'Faber F, 2015, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Frazier P, 2009, INFORMS JOURNAL ON COMPUTING', 'Murray C, 1993, MOLECULAR PHYSICS', 'Álvarez M, 2012, FOUNDATIONS AND TRENDS® IN MACHINE LEARNING', 'Rajan K, 2015, ANNUAL REVIEW OF MATERIALS RESEARCH', 'Emmerich M, 2011, ', 'Swamidass S, 2005, COMPUTER APPLICATIONS IN THE BIOSCIENCES', 'Gorai P, 2015, COMPUTATIONAL MATERIALS SCIENCE', 'Wagner T, 2010, ', 'Pilania G, 2015, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE CRYSTAL ENGINEERING AND MATERIALS', 'Vita A, 1997, MRS PROCEEDINGS', 'Klintenberg M, 2012, COMPUTATIONAL MATERIALS SCIENCE', 'Obeidat S, 2011, ', 'Clevert D, 2015, ARXIV (CORNELL UNIVERSITY)', 'Duvenaud D, 2015, ARXIV (CORNELL UNIVERSITY)', 'Jain P, 2014, ARXIV (CORNELL UNIVERSITY)', 'Kohn W, 1965, PHYSICAL REVIEW', 'Wilkinson M, 2016, SCIENTIFIC DATA', 'Silver D, 2016, NATURE', 'Pearson K, 1901, THE LONDON EDINBURGH AND DUBLIN PHILOSOPHICAL MAGAZINE AND JOURNAL OF SCIENCE', 'Groom C, 2016, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE CRYSTAL ENGINEERING AND MATERIALS', 'Weiss K, 2016, JOURNAL OF BIG DATA', 'Kirklin S, 2015, NPJ COMPUTATIONAL MATERIALS', 'Carleo G, 2017, SCIENCE', 'Raccuglia P, 2016, NATURE', 'Kearnes S, 2016, JOURNAL OF COMPUTER-AIDED MOLECULAR DESIGN', 'Ward L, 2016, NPJ COMPUTATIONAL MATERIALS', 'Carrasquilla J, 2017, NATURE PHYSICS', 'Montavon G, 2016, PATTERN RECOGNITION', 'De S, 2016, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Xue D, 2016, NATURE COMMUNICATIONS', 'Isayev O, 2017, NATURE COMMUNICATIONS', 'Reilly A, 2016, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE CRYSTAL ENGINEERING AND MATERIALS', 'Artrith N, 2016, COMPUTATIONAL MATERIALS SCIENCE', 'Ma X, 2015, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Mannodi‐Kanakkithodi A, 2016, SCIENTIFIC REPORTS', ', 2010, ', 'Kalinin S, 2015, NATURE MATERIALS', 'Artrith N, 2012, PHYSICAL REVIEW B', 'Ueno T, 2016, MATERIALS DISCOVERY', 'Chern S, 1946, ANNALS OF MATHEMATICS', 'Carlucci L, 2014, CHEMICAL REVIEWS', 'Setyawan W, 2011, ACS COMBINATORIAL SCIENCE', 'Kim C, 2016, CHEMISTRY OF MATERIALS', 'Balachandran P, 2016, SCIENTIFIC REPORTS', 'Ward L, 2016, CURRENT OPINION IN SOLID STATE AND MATERIALS SCIENCE', 'Kim C, 2016, THE JOURNAL OF PHYSICAL CHEMISTRY C', 'Park W, 2014, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Powell W, 2012, WILEY SERIES IN PROBABILITY AND STATISTICS', 'Shandiz M, 2016, COMPUTATIONAL MATERIALS SCIENCE', 'Butler K, 2016, CHEMICAL SOCIETY REVIEWS', 'Oliynyk A, 2016, CHEMISTRY OF MATERIALS', 'Puchala B, 2016, JOM', 'Glawe H, 2016, NEW JOURNAL OF PHYSICS', 'Boes J, 2016, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Norman M, 2016, REPORTS ON PROGRESS IN PHYSICS', 'Kiyohara S, 2016, JAPANESE JOURNAL OF APPLIED PHYSICS', 'Pilania G, 2015, PHYSICAL REVIEW B', 'Rouet‐Leduc B, 2016, SCIENTIFIC REPORTS', 'Balachandran P, 2016, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Meredig B, 2014, CHEMISTRY OF MATERIALS', 'Ziatdinov M, 2016, NANOTECHNOLOGY', 'Mitsui T, 1998, JOURNAL OF CHEMICAL SOFTWARE', 'Defferrard M, 2016, ARXIV (CORNELL UNIVERSITY)', 'Lipton Z, 2016, ARXIV (CORNELL UNIVERSITY)', 'Zhang L, 2018, PHYSICAL REVIEW LETTERS', 'Schütt K, 2017, NATURE COMMUNICATIONS', 'Behler J, 2016, THE JOURNAL OF CHEMICAL PHYSICS', 'Liu Y, 2017, JOURNAL OF MATERIOMICS', 'Behler J, 2017, ANGEWANDTE CHEMIE INTERNATIONAL EDITION', 'Deringer V, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Brockherde F, 2017, NATURE COMMUNICATIONS', 'Shi S, 2016, CHINESE PHYSICS B', 'Ward L, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Oliynyk A, 2016, CHEMISTRY OF MATERIALS', 'Paganini M, 2018, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Ma J, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Artrith N, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Schmidt J, 2017, CHEMISTRY OF MATERIALS', 'Pilania G, 2016, COMPUTATIONAL MATERIALS SCIENCE', 'Seko A, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Green M, 2017, APPLIED PHYSICS REVIEWS', 'Dragoni D, 2018, PHYSICAL REVIEW MATERIALS', 'Sanvito S, 2017, SCIENCE ADVANCES', 'Zhang Y, 2017, PHYSICAL REVIEW LETTERS', 'Zhang P, 2018, PHYSICAL REVIEW LETTERS', 'Jong M, 2016, SCIENTIFIC REPORTS', 'Han J, 2018, COMMUNICATIONS IN COMPUTATIONAL PHYSICS', 'Schawinski K, 2017, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY LETTERS', 'Park W, 2017, IUCRJ', 'Glielmo A, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Evans J, 2017, CHEMISTRY OF MATERIALS', 'Ling J, 2017, INTEGRATING MATERIALS AND MANUFACTURING INNOVATION', 'Zhu Q, 2018, NATURE COMMUNICATIONS', 'Chen C, 2017, PHYSICAL REVIEW MATERIALS', 'Sánchez-Lengeling B, 2017, CHEMRXIV', 'Xue D, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Legrain F, 2017, CHEMISTRY OF MATERIALS', 'Ghiringhelli L, 2017, NEW JOURNAL OF PHYSICS', 'DeCost B, 2016, JOM', 'Faraji S, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Rosenbrock C, 2017, NPJ COMPUTATIONAL MATERIALS', 'Zhan T, 2017, SCIENTIFIC REPORTS', 'Pankajakshan P, 2017, CHEMISTRY OF MATERIALS', 'Kiyohara S, 2016, SCIENCE ADVANCES', 'Hajinazar S, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Furmanchuk A, 2016, RSC ADVANCES', 'Kumar D, 2017, ', 'Kruglov I, 2017, SCIENTIFIC REPORTS', 'Dieb S, 2017, SCIENCE AND TECHNOLOGY OF ADVANCED MATERIALS', 'Dehghannasiri R, 2017, COMPUTATIONAL MATERIALS SCIENCE', 'Kikuchi S, 2017, PHYSICA B CONDENSED MATTER', 'Liu R, 2016, ', 'Okamoto Y, 2017, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Wang B, 2016, ', 'Hastie T, 2009, SPRINGER SERIES IN STATISTICS', 'Xie T, 2018, PHYSICAL REVIEW LETTERS', 'Schütt K, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Bartel C, 2019, SCIENCE ADVANCES', 'Ward L, 2018, COMPUTATIONAL MATERIALS SCIENCE', 'Zhang Y, 2018, NPJ COMPUTATIONAL MATERIALS', 'Yao K, 2018, CHEMICAL SCIENCE', 'Zhuo Y, 2018, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Stanev V, 2018, NPJ COMPUTATIONAL MATERIALS', 'Ziletti A, 2018, NATURE COMMUNICATIONS', 'Correa-Baena J, 2018, JOULE', 'Deng D, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Li W, 2018, COMPUTATIONAL MATERIALS SCIENCE', 'Kamath A, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Ye W, 2018, NATURE COMMUNICATIONS', 'Wang J, 2017, NATURE MATERIALS', 'Deringer V, 2018, PHYSICAL REVIEW LETTERS', 'Graser J, 2018, CHEMISTRY OF MATERIALS', 'Wood M, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Rowe P, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Zakutayev A, 2018, SCIENTIFIC DATA', 'Jacobs R, 2018, ADVANCED ENERGY MATERIALS', 'Ren Z, 2018, ', 'Toyao T, 2018, THE JOURNAL OF PHYSICAL CHEMISTRY C', 'Beach M, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Yamashita T, 2018, PHYSICAL REVIEW MATERIALS', 'Gopakumar A, 2018, SCIENTIFIC REPORTS', 'Artrith N, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Glielmo A, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Jacobsen T, 2018, PHYSICAL REVIEW LETTERS', 'Pham T, 2017, SCIENCE AND TECHNOLOGY OF ADVANCED MATERIALS', 'Furmanchuk A, 2017, JOURNAL OF COMPUTATIONAL CHEMISTRY', 'Oliynyk A, 2017, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Sosso G, 2018, MOLECULAR SIMULATION', 'Kobayashi R, 2017, PHYSICAL REVIEW MATERIALS', 'Sun N, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Zhai X, 2018, COMPUTATIONAL MATERIALS SCIENCE', 'Schmitz G, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Liu Y, 2017, COMPUTATIONAL MATERIALS SCIENCE', 'Weston L, 2018, PHYSICAL REVIEW MATERIALS', 'Nagai R, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Dieb S, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Liu Q, 2017, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Schmidt J, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Pham T, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Yuan F, 2017, SCIENTIFIC REPORTS', 'Dieb S, 2018, ', 'Pilania G, 2018, JOURNAL OF MATERIALS SCIENCE', 'Ghahramani A, 2018, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Breiman L, 2001, MACHINE LEARNING', 'LeCun Y, 2015, NATURE', 'Paszke A, 2017, ', 'Butler K, 2018, NATURE', 'Chen C, 2019, CHEMISTRY OF MATERIALS', 'Haastrup S, 2018, 2D MATERIALS', 'Ouyang R, 2018, PHYSICAL REVIEW MATERIALS', 'Lu S, 2018, NATURE COMMUNICATIONS', 'Schütt K, 2018, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Rajan A, 2018, CHEMISTRY OF MATERIALS', 'Ryan K, 2018, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Tehrani A, 2018, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Dimiduk D, 2018, INTEGRATING MATERIALS AND MANUFACTURING INNOVATION', 'Sendek A, 2018, CHEMISTRY OF MATERIALS', 'Wei H, 2018, INTERNATIONAL JOURNAL OF HEAT AND MASS TRANSFER', 'Balachandran P, 2018, NATURE COMMUNICATIONS', 'Jäger M, 2018, NPJ COMPUTATIONAL MATERIALS', 'Meredig B, 2018, MOLECULAR SYSTEMS DESIGN &amp; ENGINEERING', 'Rajan K, 2005, STATISTICAL ANALYSIS AND DATA MINING THE ASA DATA SCIENCE JOURNAL', 'Balachandran P, 2018, PHYSICAL REVIEW MATERIALS', 'Cassar D, 2018, ACTA MATERIALIA', 'Oftelie L, 2018, NPJ COMPUTATIONAL MATERIALS', "Jes\\'us C, 2014, ARXIV (CORNELL UNIVERSITY)", 'Yamawaki M, 2018, SCIENCE ADVANCES', 'Li X, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Σολωμού Α, 2018, MATERIALS &amp; DESIGN', 'Jalem R, 2018, SCIENTIFIC REPORTS', 'Kim K, 2018, PHYSICAL REVIEW MATERIALS', 'Kauwe S, 2018, INTEGRATING MATERIALS AND MANUFACTURING INNOVATION', 'Zheng X, 2018, CHEMICAL SCIENCE', 'Yeo B, 2019, SCIENTIFIC REPORTS', 'Xie T, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Li X, 2018, ', 'Ward L, 2018, MRS BULLETIN', 'Wu Y, 2018, ACS APPLIED NANO MATERIALS', 'Dam H, 2018, JOURNAL OF THE PHYSICAL SOCIETY OF JAPAN', 'Balachandran P, 2018, SPRINGER SERIES IN MATERIALS SCIENCE', 'Zhang B, 2018, CHINESE PHYSICS B', 'Kiyohara S, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Liu Z, 2019, ARXIV (CORNELL UNIVERSITY)', 'Ioffe S, 2024, ARXIV (CORNELL UNIVERSITY)', 'Gilmer J, 2017, ARXIV (CORNELL UNIVERSITY)', 'Sutton C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Ledig C, 2017, ', 'Sun J, 2015, PHYSICAL REVIEW LETTERS', 'Yu F, 2019, SPRINGER BRIEFS IN ELECTRICAL AND COMPUTER ENGINEERING', 'Himanen L, 2019, COMPUTER PHYSICS COMMUNICATIONS', 'F B, 2017, MPG.PURE (MAX PLANCK SOCIETY)', 'Montavon G, 2013, MPG.PURE (MAX PLANCK SOCIETY)', 'Carrete J, 2014, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'R. O, 2018, MPG.PURE (MAX PLANCK SOCIETY)', 'Li X, 2018, SCIENTIFIC REPORTS', 'Ye W, 2018, ', 'A. Z, 2018, MPG.PURE (MAX PLANCK SOCIETY)', 'Liu Z, 2020, JOURNAL OF THE OPTICAL SOCIETY OF AMERICA A', 'L. G, 2017, MAX PLANCK DIGITAL LIBRARY', 'Smith J, 2018, CHEMRXIV', 'A.V. M, 2006, MPG.PURE (MAX PLANCK SOCIETY)', 'Gaultois M, 2015, ARXIV (CORNELL UNIVERSITY)', 'Nouira A, 2018, ARXIV (CORNELL UNIVERSITY)', 'Eldar Y, 2012, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Webb G, 2017, ', 'Snyder G, 2010, CO-PUBLISHED WITH MACMILLAN PUBLISHERS LTD, UK EBOOKS', 'Paszkowicz W, 2009, MATERIALS AND MANUFACTURING PROCESSES', 'Newnham R, 2004, OXFORD UNIVERSITY PRESS EBOOKS', 'Sánchez-Lengeling B, 2017, CHEMRXIV', 'Lookman T, 2018, SPRINGER SERIES IN MATERIALS SCIENCE', 'Obeidat S, 2011, SPECTROSCOPY AN INTERNATIONAL JOURNAL', 'Sparks T, 2018, CHEMRXIV', 'Rasmussen C, 2022, DIRECTORY OF OPEN ACCESS BOOKS (OAPEN FOUNDATION)', 'Wager S, 2013, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>['Friedman J, 2001, THE ANNALS OF STATISTICS', 'He K, 2015, ', 'Zeiler M, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Bednorz J, 1986, THE EUROPEAN PHYSICAL JOURNAL B', 'Murphy K, 2012, ', 'Jones D, 1998, JOURNAL OF GLOBAL OPTIMIZATION', 'Jensen F, 1998, ', 'Bach S, 2015, PLOS ONE', 'Strobl C, 2007, BMC BIOINFORMATICS', 'Devroye L, 1996, STOCHASTIC MODELLING AND APPLIED PROBABILITY', 'Martin R, 2004, ', 'Gori M, 2006, PROCEEDINGS. 2005 IEEE INTERNATIONAL JOINT CONFERENCE ON NEURAL NETWORKS, 2005.', 'Thompson A, 2014, JOURNAL OF COMPUTATIONAL PHYSICS', 'Vert J, 2004, THE MIT PRESS EBOOKS', 'Jong M, 2015, SCIENTIFIC DATA', 'Braams B, 2009, INTERNATIONAL REVIEWS IN PHYSICAL CHEMISTRY', ', 2005, CHOICE REVIEWS ONLINE', 'Kaner R, 2005, SCIENCE', 'Drucker H, 1997, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Guzella T, 2009, EXPERT SYSTEMS WITH APPLICATIONS', ', 2008, CHOICE REVIEWS ONLINE', 'Seko A, 2015, PHYSICAL REVIEW LETTERS', 'Maddox J, 1988, NATURE', 'Chan P, 1998, ', 'Faber F, 2016, PHYSICAL REVIEW LETTERS', 'Kolen J, 2009, ', 'Lee J, 2016, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Ghasemi S, 2015, PHYSICAL REVIEW B', 'Isayev O, 2014, CHEMISTRY OF MATERIALS', 'Ramakrishnan R, 2015, THE JOURNAL OF CHEMICAL PHYSICS', 'Vellido A, 2012, ', 'Gaultois M, 2016, APL MATERIALS', 'Seko A, 2015, PHYSICAL REVIEW B', 'Pettifor D, 1988, MATERIALS SCIENCE AND TECHNOLOGY', 'Seko A, 2014, PHYSICAL REVIEW B', 'Sumpter B, 1992, CHEMICAL PHYSICS LETTERS', 'Yoon B, 2013, IEEE TRANSACTIONS ON SIGNAL PROCESSING', 'Zakutayev A, 2014, CHEMISTRY OF MATERIALS', 'Broderick S, 2011, JOURNAL OF THE AMERICAN CERAMIC SOCIETY', 'Devroye L, 1996, STOCHASTIC MODELLING AND APPLIED PROBABILITY', 'Siddorn M, 2015, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Wang Y, 2015, SIAM JOURNAL ON SCIENTIFIC COMPUTING', 'Liu S, 2010, LECTURE NOTES IN COMPUTER SCIENCE', 'Meremianin A, 2006, JOURNAL OF PHYSICS A MATHEMATICAL AND GENERAL', 'Owolabi T, 2014, JOURNALS &amp; BOOKS HOSTING (INTERNATIONAL KNOWLEDGE SHARING PLATFORM)', 'Johnson D, 2013, ELSEVIER EBOOKS', 'Lindström D, 2015, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Bruna J, 2013, ARXIV (CORNELL UNIVERSITY)', 'Weyl H, , ', 'Baldi P, 1998, ', 'Perdew J, 1996, PHYSICAL REVIEW LETTERS', 'Freund Y, 1997, JOURNAL OF COMPUTER AND SYSTEM SCIENCES', 'McCulloch W, 1943, BULLETIN OF MATHEMATICAL BIOLOGY', 'Jain A, 2013, APL MATERIALS', 'Hill R, 1952, PROCEEDINGS OF THE PHYSICAL SOCIETY SECTION A', 'Tran F, 2009, PHYSICAL REVIEW LETTERS', 'Ong S, 2012, COMPUTATIONAL MATERIALS SCIENCE', 'Schmidt M, 2009, SCIENCE', 'Wang Y, 2012, COMPUTER PHYSICS COMMUNICATIONS', 'Saal J, 2013, JOM', 'Behler J, 2011, THE JOURNAL OF CHEMICAL PHYSICS', 'Kitchin J, 2004, PHYSICAL REVIEW LETTERS', 'Loader C, 1999, STATISCTICS AND COMPUTING/STATISTICS AND COMPUTING', 'Martoňák R, 2003, PHYSICAL REVIEW LETTERS', 'Leininger T, 1997, CHEMICAL PHYSICS LETTERS', 'Kohn W, 1965, PHYSICAL REVIEW LETTERS', 'Pickard C, 2006, PHYSICAL REVIEW LETTERS', 'Tsuneyuki S, 1988, PHYSICAL REVIEW LETTERS', 'Hautier G, 2010, CHEMISTRY OF MATERIALS', 'Fischer C, 2006, NATURE MATERIALS', 'Koskinen P, 2009, COMPUTATIONAL MATERIALS SCIENCE', 'Lüders M, 2005, PHYSICAL REVIEW B', 'Éliashberg G, 1960, JOURNAL OF EXPERIMENTAL AND THEORETICAL PHYSICS', 'Matthias B, 1955, PHYSICAL REVIEW', 'Szlachta W, 2014, PHYSICAL REVIEW B', 'Cśanyi G, 2004, PHYSICAL REVIEW LETTERS', 'Schön J, 1996, ANGEWANDTE CHEMIE INTERNATIONAL EDITION IN ENGLISH', 'Baskes M, 1997, MATERIALS CHEMISTRY AND PHYSICS', 'Pannetier J, 1990, NATURE', 'Becker C, 2013, CURRENT OPINION IN SOLID STATE AND MATERIALS SCIENCE', 'Sosso G, 2012, PHYSICAL REVIEW B', 'Harper P, 1955, PROCEEDINGS OF THE PHYSICAL SOCIETY SECTION A', 'Johnson S, 2007, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Bajorath J, 2009, DRUG DISCOVERY TODAY', 'Kuz’min V, 2008, JOURNAL OF COMPUTER-AIDED MOLECULAR DESIGN', 'Ruggiu F, 2010, MOLECULAR INFORMATICS', 'Pettifor D, 1986, JOURNAL OF PHYSICS C SOLID STATE PHYSICS', 'Lam P, 1987, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Schneider G, 2008, TRENDS IN BIOTECHNOLOGY', 'Owolabi T, 2014, JOURNAL OF SUPERCONDUCTIVITY AND NOVEL MAGNETISM', 'Moussa J, 2012, PHYSICAL REVIEW LETTERS', 'Xu B, 2013, SCIENTIFIC REPORTS', 'Sanville E, 2008, JOURNAL OF PHYSICS CONDENSED MATTER', 'Kadantsev E, 2004, PHYSICAL REVIEW A', 'Abdellahi M, 2014, CERAMICS INTERNATIONAL', 'Villars P, 1988, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Sinkov N, 2010, TALANTA', 'Matos C, 2007, ANALYTICAL CHEMISTRY', 'Cohen M, 1988, MATERIALS SCIENCE AND ENGINEERING A', 'Doll K, 2008, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Hochreiter S, 1997, NEURAL COMPUTATION', 'MacKerell A, 1998, THE JOURNAL OF PHYSICAL CHEMISTRY B', 'Rosenblatt F, 1958, PSYCHOLOGICAL REVIEW', 'Geurts P, 2006, MACHINE LEARNING', 'Daw M, 1984, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Stillinger F, 1985, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Behler J, 2007, PHYSICAL REVIEW LETTERS', 'Goldschmidt V, 1926, DIE NATURWISSENSCHAFTEN', 'Ackley D, 1985, COGNITIVE SCIENCE', 'Bartók A, 2013, PHYSICAL REVIEW B', 'Oganov A, 2006, THE JOURNAL OF CHEMICAL PHYSICS', 'Porezag D, 1995, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Werner P, 1985, JOURNAL OF APPLIED CRYSTALLOGRAPHY', 'Tersoff J, 1986, PHYSICAL REVIEW LETTERS', 'Cohen M, 1985, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Waag W, 2014, JOURNAL OF POWER SOURCES', 'Woodley S, 2008, NATURE MATERIALS', 'Maggiora G, 2006, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Snyder J, 2012, PHYSICAL REVIEW LETTERS', 'Li Z, 2015, PHYSICAL REVIEW LETTERS', 'Montavon G, 2013, NEW JOURNAL OF PHYSICS', 'Sanders M, 1984, JOURNAL OF THE CHEMICAL SOCIETY CHEMICAL COMMUNICATIONS', 'Blank T, 1995, THE JOURNAL OF CHEMICAL PHYSICS', 'Schütt K, 2014, PHYSICAL REVIEW B', 'Koinuma H, 2004, NATURE MATERIALS', 'Dalsin J, 2005, MATERIALS TODAY', 'Khaliullin R, 2011, NATURE MATERIALS', 'Olson G, 2000, SCIENCE', 'Handley C, 2010, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Marques M, 2005, PHYSICAL REVIEW B', 'Yan J, 2014, ENERGY &amp; ENVIRONMENTAL SCIENCE', 'Pettifor D, 1984, SOLID STATE COMMUNICATIONS', 'Seifert G, 2012, WILEY INTERDISCIPLINARY REVIEWS COMPUTATIONAL MOLECULAR SCIENCE', 'Tozer D, 1996, THE JOURNAL OF CHEMICAL PHYSICS', 'Dey P, 2013, COMPUTATIONAL MATERIALS SCIENCE', 'Snyder J, 2013, THE JOURNAL OF CHEMICAL PHYSICS', 'Shoemaker D, 2014, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Zhang X, 2012, ADVANCED FUNCTIONAL MATERIALS', 'Eshet H, 2010, PHYSICAL REVIEW B', 'Gilman J, 2001, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Kuz’min V, 2005, JOURNAL OF MOLECULAR MODELING', 'Gu T, 2005, SOLID STATE SCIENCES', 'Walsh A, 2015, NATURE CHEMISTRY', 'Suram S, 2015, ACS COMBINATORIAL SCIENCE', 'Tatlıer M, 2010, NEURAL COMPUTING AND APPLICATIONS', 'Plaut D, 1987, COMPUTER SPEECH &amp; LANGUAGE', 'Rabe K, 1992, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Freeman C, 1992, JOURNAL OF THE CHEMICAL SOCIETY CHEMICAL COMMUNICATIONS', 'Morita T, 1957, JOURNAL OF THE PHYSICAL SOCIETY OF JAPAN', 'Becke A, 1988, PHYSICAL REVIEW. A, GENERAL PHYSICS', 'Srivastava N, 2014, ', '淳司 柴, 2017, JOURNAL OF JAPAN SOCIETY FOR FUZZY THEORY AND INTELLIGENT INFORMATICS', 'Hinton G, 2006, SCIENCE', 'Hasan M, 2010, REVIEWS OF MODERN PHYSICS', 'Heyd J, 2003, THE JOURNAL OF CHEMICAL PHYSICS', 'Boser B, 1992, ', 'Murnaghan F, 1944, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Birch F, 1947, PHYSICAL REVIEW', 'Golbraikh A, 2002, JOURNAL OF MOLECULAR GRAPHICS AND MODELLING', 'Geman S, 1992, NEURAL COMPUTATION', 'Schapire R, 1990, MACHINE LEARNING', 'Stanley K, 2002, EVOLUTIONARY COMPUTATION', 'Moore J, 2010, NATURE', 'Bartók A, 2010, PHYSICAL REVIEW LETTERS', 'Wang Y, 2010, PHYSICAL REVIEW B', 'Liu A, 1989, SCIENCE', 'Cahill D, 1992, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Rupp M, 2012, PHYSICAL REVIEW LETTERS', 'Forrester A, 2009, PROGRESS IN AEROSPACE SCIENCES', 'Tropsha A, 2003, QSAR &amp; COMBINATORIAL SCIENCE', 'Ramakrishnan R, 2014, SCIENTIFIC DATA', 'Daw M, 1993, MATERIALS SCIENCE REPORTS', 'Beest B, 1990, PHYSICAL REVIEW LETTERS', 'Picard R, 1984, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Nguyen A, 2013, APPLIED ENERGY', 'Gražulis S, 2011, NUCLEIC ACIDS RESEARCH', 'Chapelle O, 2011, ', 'Goedecker S, 2004, THE JOURNAL OF CHEMICAL PHYSICS', 'Huang C, 2006, EXPERT SYSTEMS WITH APPLICATIONS', 'Santosa F, 1986, SIAM JOURNAL ON SCIENTIFIC AND STATISTICAL COMPUTING', 'Foulkes W, 1989, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Potyrailo R, 2011, ACS COMBINATORIAL SCIENCE', 'Artrith N, 2011, PHYSICAL REVIEW B', 'Blatov V, 2004, CRYSTALLOGRAPHY REVIEWS', 'Seko A, 2014, PHYSICAL REVIEW B', 'Oganov A, 2009, THE JOURNAL OF CHEMICAL PHYSICS', 'Paszkowicz W, 2013, MATERIALS AND MANUFACTURING PROCESSES', 'Pukrittayakamee A, 2009, THE JOURNAL OF CHEMICAL PHYSICS', 'Park W, 2012, ADVANCED FUNCTIONAL MATERIALS', 'Kramer G, 1991, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Bush T, 1995, JOURNAL OF MATERIALS CHEMISTRY', 'Eijck B, 2000, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE', 'Villars P, 2003, JOURNAL OF ALLOYS AND COMPOUNDS', 'Gale J, 1998, THE JOURNAL OF PHYSICAL CHEMISTRY B', 'Witkoskie J, 2004, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Gottwald D, 2005, THE JOURNAL OF CHEMICAL PHYSICS', 'Sastre G, 2003, CHEMISTRY OF MATERIALS', 'Chen Z, 2005, ANALYTICAL CHEMISTRY', 'Agatonović-Kuštrin S, 2000, JOURNAL OF PHARMACEUTICAL AND BIOMEDICAL ANALYSIS', 'He K, 2016, ', 'Krizhevsky A, 2017, COMMUNICATIONS OF THE ACM', 'LeCun Y, 1998, PROCEEDINGS OF THE IEEE', 'Tibshirani R, 1996, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Zou H, 2005, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Wang J, 2004, JOURNAL OF COMPUTATIONAL CHEMISTRY', 'Quinlan J, 1986, MACHINE LEARNING', 'Bengio Y, 2013, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'LeCun Y, 1989, NEURAL COMPUTATION', 'Snyder G, 2008, NATURE MATERIALS', 'Tropp J, 2007, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Scarselli F, 2008, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Candès E, 2006, COMMUNICATIONS ON PURE AND APPLIED MATHEMATICS', 'Duin A, 2001, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Glorot X, 2012, ', 'Pati Y, 2002, ', 'Cordero B, 2008, DALTON TRANSACTIONS', 'LeCun Y, 1989, NEURAL INFORMATION PROCESSING SYSTEMS', 'Browne C, 2012, IEEE TRANSACTIONS ON COMPUTATIONAL INTELLIGENCE AND AI IN GAMES', 'Fan J, 2008, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Quinlan J, 1987, INTERNATIONAL JOURNAL OF MAN-MACHINE STUDIES', 'Curtarolo S, 2013, NATURE MATERIALS', 'Ruddigkeit L, 2012, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Glass C, 2006, COMPUTER PHYSICS COMMUNICATIONS', 'Pickard C, 2011, JOURNAL OF PHYSICS CONDENSED MATTER', 'Pazzani M, 1997, MACHINE LEARNING', 'Vítek V, 1968, PHILOSOPHICAL MAGAZINE', 'Morgenstern D, 1962, ECONOMETRICA', 'Blum L, 2009, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Ghiringhelli L, 2015, PHYSICAL REVIEW LETTERS', 'Evgeniou T, 2005, ', 'Alexander J, 1928, TRANSACTIONS OF THE AMERICAN MATHEMATICAL SOCIETY', 'Hachmann J, 2011, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Shan S, 2009, STRUCTURAL AND MULTIDISCIPLINARY OPTIMIZATION', 'Faber F, 2015, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Frazier P, 2009, INFORMS JOURNAL ON COMPUTING', 'Murray C, 1993, MOLECULAR PHYSICS', 'Álvarez M, 2012, FOUNDATIONS AND TRENDS® IN MACHINE LEARNING', 'Rajan K, 2015, ANNUAL REVIEW OF MATERIALS RESEARCH', 'Emmerich M, 2011, ', 'Swamidass S, 2005, COMPUTER APPLICATIONS IN THE BIOSCIENCES', 'Gorai P, 2015, COMPUTATIONAL MATERIALS SCIENCE', 'Wagner T, 2010, ', 'Pilania G, 2015, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE CRYSTAL ENGINEERING AND MATERIALS', 'Vita A, 1997, MRS PROCEEDINGS', 'Klintenberg M, 2012, COMPUTATIONAL MATERIALS SCIENCE', 'Obeidat S, 2011, ', 'Clevert D, 2015, ARXIV (CORNELL UNIVERSITY)', 'Duvenaud D, 2015, ARXIV (CORNELL UNIVERSITY)', 'Jain P, 2014, ARXIV (CORNELL UNIVERSITY)', 'Kohn W, 1965, PHYSICAL REVIEW', 'Wilkinson M, 2016, SCIENTIFIC DATA', 'Silver D, 2016, NATURE', 'Pearson K, 1901, THE LONDON EDINBURGH AND DUBLIN PHILOSOPHICAL MAGAZINE AND JOURNAL OF SCIENCE', 'Groom C, 2016, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE CRYSTAL ENGINEERING AND MATERIALS', 'Weiss K, 2016, JOURNAL OF BIG DATA', 'Kirklin S, 2015, NPJ COMPUTATIONAL MATERIALS', 'Carleo G, 2017, SCIENCE', 'Raccuglia P, 2016, NATURE', 'Kearnes S, 2016, JOURNAL OF COMPUTER-AIDED MOLECULAR DESIGN', 'Ward L, 2016, NPJ COMPUTATIONAL MATERIALS', 'Carrasquilla J, 2017, NATURE PHYSICS', 'Montavon G, 2016, PATTERN RECOGNITION', 'De S, 2016, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Xue D, 2016, NATURE COMMUNICATIONS', 'Isayev O, 2017, NATURE COMMUNICATIONS', 'Reilly A, 2016, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE CRYSTAL ENGINEERING AND MATERIALS', 'Artrith N, 2016, COMPUTATIONAL MATERIALS SCIENCE', 'Ma X, 2015, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Mannodi‐Kanakkithodi A, 2016, SCIENTIFIC REPORTS', ', 2010, ', 'Kalinin S, 2015, NATURE MATERIALS', 'Artrith N, 2012, PHYSICAL REVIEW B', 'Ueno T, 2016, MATERIALS DISCOVERY', 'Chern S, 1946, ANNALS OF MATHEMATICS', 'Carlucci L, 2014, CHEMICAL REVIEWS', 'Setyawan W, 2011, ACS COMBINATORIAL SCIENCE', 'Kim C, 2016, CHEMISTRY OF MATERIALS', 'Balachandran P, 2016, SCIENTIFIC REPORTS', 'Ward L, 2016, CURRENT OPINION IN SOLID STATE AND MATERIALS SCIENCE', 'Kim C, 2016, THE JOURNAL OF PHYSICAL CHEMISTRY C', 'Park W, 2014, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Powell W, 2012, WILEY SERIES IN PROBABILITY AND STATISTICS', 'Shandiz M, 2016, COMPUTATIONAL MATERIALS SCIENCE', 'Butler K, 2016, CHEMICAL SOCIETY REVIEWS', 'Oliynyk A, 2016, CHEMISTRY OF MATERIALS', 'Puchala B, 2016, JOM', 'Glawe H, 2016, NEW JOURNAL OF PHYSICS', 'Boes J, 2016, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Norman M, 2016, REPORTS ON PROGRESS IN PHYSICS', 'Kiyohara S, 2016, JAPANESE JOURNAL OF APPLIED PHYSICS', 'Pilania G, 2015, PHYSICAL REVIEW B', 'Rouet‐Leduc B, 2016, SCIENTIFIC REPORTS', 'Balachandran P, 2016, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Meredig B, 2014, CHEMISTRY OF MATERIALS', 'Ziatdinov M, 2016, NANOTECHNOLOGY', 'Mitsui T, 1998, JOURNAL OF CHEMICAL SOFTWARE', 'Defferrard M, 2016, ARXIV (CORNELL UNIVERSITY)', 'Lipton Z, 2016, ARXIV (CORNELL UNIVERSITY)', 'Zhang L, 2018, PHYSICAL REVIEW LETTERS', 'Schütt K, 2017, NATURE COMMUNICATIONS', 'Behler J, 2016, THE JOURNAL OF CHEMICAL PHYSICS', 'Liu Y, 2017, JOURNAL OF MATERIOMICS', 'Behler J, 2017, ANGEWANDTE CHEMIE INTERNATIONAL EDITION', 'Deringer V, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Brockherde F, 2017, NATURE COMMUNICATIONS', 'Shi S, 2016, CHINESE PHYSICS B', 'Ward L, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Oliynyk A, 2016, CHEMISTRY OF MATERIALS', 'Paganini M, 2018, PHYSICAL REVIEW. D/PHYSICAL REVIEW. D.', 'Ma J, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Artrith N, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Schmidt J, 2017, CHEMISTRY OF MATERIALS', 'Pilania G, 2016, COMPUTATIONAL MATERIALS SCIENCE', 'Seko A, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Green M, 2017, APPLIED PHYSICS REVIEWS', 'Dragoni D, 2018, PHYSICAL REVIEW MATERIALS', 'Sanvito S, 2017, SCIENCE ADVANCES', 'Zhang Y, 2017, PHYSICAL REVIEW LETTERS', 'Zhang P, 2018, PHYSICAL REVIEW LETTERS', 'Jong M, 2016, SCIENTIFIC REPORTS', 'Han J, 2018, COMMUNICATIONS IN COMPUTATIONAL PHYSICS', 'Schawinski K, 2017, MONTHLY NOTICES OF THE ROYAL ASTRONOMICAL SOCIETY LETTERS', 'Park W, 2017, IUCRJ', 'Glielmo A, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Evans J, 2017, CHEMISTRY OF MATERIALS', 'Ling J, 2017, INTEGRATING MATERIALS AND MANUFACTURING INNOVATION', 'Zhu Q, 2018, NATURE COMMUNICATIONS', 'Chen C, 2017, PHYSICAL REVIEW MATERIALS', 'Sánchez-Lengeling B, 2017, CHEMRXIV', 'Xue D, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Legrain F, 2017, CHEMISTRY OF MATERIALS', 'Ghiringhelli L, 2017, NEW JOURNAL OF PHYSICS', 'DeCost B, 2016, JOM', 'Faraji S, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Rosenbrock C, 2017, NPJ COMPUTATIONAL MATERIALS', 'Zhan T, 2017, SCIENTIFIC REPORTS', 'Pankajakshan P, 2017, CHEMISTRY OF MATERIALS', 'Kiyohara S, 2016, SCIENCE ADVANCES', 'Hajinazar S, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Furmanchuk A, 2016, RSC ADVANCES', 'Kumar D, 2017, ', 'Kruglov I, 2017, SCIENTIFIC REPORTS', 'Dieb S, 2017, SCIENCE AND TECHNOLOGY OF ADVANCED MATERIALS', 'Dehghannasiri R, 2017, COMPUTATIONAL MATERIALS SCIENCE', 'Kikuchi S, 2017, PHYSICA B CONDENSED MATTER', 'Liu R, 2016, ', 'Okamoto Y, 2017, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Wang B, 2016, ', 'Hastie T, 2009, SPRINGER SERIES IN STATISTICS', 'Xie T, 2018, PHYSICAL REVIEW LETTERS', 'Schütt K, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Bartel C, 2019, SCIENCE ADVANCES', 'Ward L, 2018, COMPUTATIONAL MATERIALS SCIENCE', 'Zhang Y, 2018, NPJ COMPUTATIONAL MATERIALS', 'Yao K, 2018, CHEMICAL SCIENCE', 'Zhuo Y, 2018, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Stanev V, 2018, NPJ COMPUTATIONAL MATERIALS', 'Ziletti A, 2018, NATURE COMMUNICATIONS', 'Correa-Baena J, 2018, JOULE', 'Deng D, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Li W, 2018, COMPUTATIONAL MATERIALS SCIENCE', 'Kamath A, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Ye W, 2018, NATURE COMMUNICATIONS', 'Wang J, 2017, NATURE MATERIALS', 'Deringer V, 2018, PHYSICAL REVIEW LETTERS', 'Graser J, 2018, CHEMISTRY OF MATERIALS', 'Rowe P, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Wood M, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Zakutayev A, 2018, SCIENTIFIC DATA', 'Ren Z, 2018, ', 'Jacobs R, 2018, ADVANCED ENERGY MATERIALS', 'Toyao T, 2018, THE JOURNAL OF PHYSICAL CHEMISTRY C', 'Beach M, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Yamashita T, 2018, PHYSICAL REVIEW MATERIALS', 'Gopakumar A, 2018, SCIENTIFIC REPORTS', 'Artrith N, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Glielmo A, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Pham T, 2017, SCIENCE AND TECHNOLOGY OF ADVANCED MATERIALS', 'Jacobsen T, 2018, PHYSICAL REVIEW LETTERS', 'Furmanchuk A, 2017, JOURNAL OF COMPUTATIONAL CHEMISTRY', 'Oliynyk A, 2017, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Sosso G, 2018, MOLECULAR SIMULATION', 'Kobayashi R, 2017, PHYSICAL REVIEW MATERIALS', 'Sun N, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Zhai X, 2018, COMPUTATIONAL MATERIALS SCIENCE', 'Schmitz G, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Liu Y, 2017, COMPUTATIONAL MATERIALS SCIENCE', 'Weston L, 2018, PHYSICAL REVIEW MATERIALS', 'Nagai R, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Dieb S, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Liu Q, 2017, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Schmidt J, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Pham T, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Yuan F, 2017, SCIENTIFIC REPORTS', 'Dieb S, 2018, ', 'Pilania G, 2018, JOURNAL OF MATERIALS SCIENCE', 'Ghahramani A, 2018, BIORXIV (COLD SPRING HARBOR LABORATORY)', 'Breiman L, 2001, MACHINE LEARNING', 'LeCun Y, 2015, NATURE', 'Paszke A, 2017, ', 'Butler K, 2018, NATURE', 'Chen C, 2019, CHEMISTRY OF MATERIALS', 'Haastrup S, 2018, 2D MATERIALS', 'Ouyang R, 2018, PHYSICAL REVIEW MATERIALS', 'Lu S, 2018, NATURE COMMUNICATIONS', 'Schütt K, 2018, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Rajan A, 2018, CHEMISTRY OF MATERIALS', 'Ryan K, 2018, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Tehrani A, 2018, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Dimiduk D, 2018, INTEGRATING MATERIALS AND MANUFACTURING INNOVATION', 'Sendek A, 2018, CHEMISTRY OF MATERIALS', 'Wei H, 2018, INTERNATIONAL JOURNAL OF HEAT AND MASS TRANSFER', 'Balachandran P, 2018, NATURE COMMUNICATIONS', 'Jäger M, 2018, NPJ COMPUTATIONAL MATERIALS', 'Meredig B, 2018, MOLECULAR SYSTEMS DESIGN &amp; ENGINEERING', 'Rajan K, 2005, STATISTICAL ANALYSIS AND DATA MINING THE ASA DATA SCIENCE JOURNAL', 'Balachandran P, 2018, PHYSICAL REVIEW MATERIALS', 'Cassar D, 2018, ACTA MATERIALIA', 'Oftelie L, 2018, NPJ COMPUTATIONAL MATERIALS', "Jes\\'us C, 2014, ARXIV (CORNELL UNIVERSITY)", 'Yamawaki M, 2018, SCIENCE ADVANCES', 'Li X, 2018, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Σολωμού Α, 2018, MATERIALS &amp; DESIGN', 'Jalem R, 2018, SCIENTIFIC REPORTS', 'Kim K, 2018, PHYSICAL REVIEW MATERIALS', 'Kauwe S, 2018, INTEGRATING MATERIALS AND MANUFACTURING INNOVATION', 'Zheng X, 2018, CHEMICAL SCIENCE', 'Yeo B, 2019, SCIENTIFIC REPORTS', 'Li X, 2018, ', 'Xie T, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Ward L, 2018, MRS BULLETIN', 'Wu Y, 2018, ACS APPLIED NANO MATERIALS', 'Dam H, 2018, JOURNAL OF THE PHYSICAL SOCIETY OF JAPAN', 'Balachandran P, 2018, SPRINGER SERIES IN MATERIALS SCIENCE', 'Zhang B, 2018, CHINESE PHYSICS B', 'Kiyohara S, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Liu Z, 2019, ARXIV (CORNELL UNIVERSITY)', 'Ioffe S, 2024, ARXIV (CORNELL UNIVERSITY)', 'Gilmer J, 2017, ARXIV (CORNELL UNIVERSITY)', 'Sutton C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Ledig C, 2017, ', 'Sun J, 2015, PHYSICAL REVIEW LETTERS', 'Yu F, 2019, SPRINGER BRIEFS IN ELECTRICAL AND COMPUTER ENGINEERING', 'Himanen L, 2019, COMPUTER PHYSICS COMMUNICATIONS', 'F B, 2017, MPG.PURE (MAX PLANCK SOCIETY)', 'Montavon G, 2013, MPG.PURE (MAX PLANCK SOCIETY)', 'Carrete J, 2014, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'R. O, 2018, MPG.PURE (MAX PLANCK SOCIETY)', 'Li X, 2018, SCIENTIFIC REPORTS', 'Ye W, 2018, ', 'A. Z, 2018, MPG.PURE (MAX PLANCK SOCIETY)', 'Liu Z, 2020, JOURNAL OF THE OPTICAL SOCIETY OF AMERICA A', 'L. G, 2017, MAX PLANCK DIGITAL LIBRARY', 'Smith J, 2018, CHEMRXIV', 'A.V. M, 2006, MPG.PURE (MAX PLANCK SOCIETY)', 'Gaultois M, 2015, ARXIV (CORNELL UNIVERSITY)', 'Nouira A, 2018, ARXIV (CORNELL UNIVERSITY)', 'Eldar Y, 2012, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Webb G, 2017, ', 'Snyder G, 2010, CO-PUBLISHED WITH MACMILLAN PUBLISHERS LTD, UK EBOOKS', 'Paszkowicz W, 2009, MATERIALS AND MANUFACTURING PROCESSES', 'Newnham R, 2004, OXFORD UNIVERSITY PRESS EBOOKS', 'Sánchez-Lengeling B, 2017, CHEMRXIV', 'Lookman T, 2018, SPRINGER SERIES IN MATERIALS SCIENCE', 'Obeidat S, 2011, SPECTROSCOPY AN INTERNATIONAL JOURNAL', 'Sparks T, 2018, CHEMRXIV', 'Rasmussen C, 2022, DIRECTORY OF OPEN ACCESS BOOKS (OAPEN FOUNDATION)', 'Wager S, 2013, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -11725,7 +11733,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -11839,7 +11847,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -11916,18 +11924,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://openalex.org/W398859631</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>https://openalex.org/W3123436326</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>10.1111/ectj.12097</t>
+        </is>
+      </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>International Conference on Machine Learning (ICML)-2005</t>
+          <t>Double/debiased machine learning for treatment and structural parameters</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -11941,39 +11953,39 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>2486</v>
+        <v>2454</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>人工知能学会誌 = JOURNAL OF JAPANESE SOCIETY FOR ARTIFICIAL INTELLIGENCE</t>
+          <t>ECONOMETRICS JOURNAL</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>人工知能学会誌 = Journal of Japanese Society for Artificial Intelligence</t>
+          <t>Econometrics Journal</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>['宏治 津田']</t>
+          <t>['Victor Chernozhukov', 'Denis Chetverikov', 'Mert Demirer', 'Esther Duflo', 'Christian Hansen', 'Whitney K. Newey', 'James M. Robins']</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>['宏治 津田']</t>
+          <t>['Victor Chernozhukov', 'Denis Chetverikov', 'Mert Demirer', 'Esther Duflo', 'Christian Hansen', 'Whitney Newey', 'James Robins']</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">宏治 津田 (corresponding author), </t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
+          <t>['Massachusetts Institute of Technology, 50 Memorial Drive, Cambridge, MA 02139, USA', 'University of California Los Angeles, 315 Portola Plaza, Los Angeles, CA 90095, USA', 'Massachusetts Institute of Technology, 50 Memorial Drive, Cambridge, MA 02139, USA', 'Massachusetts Institute of Technology, 50 Memorial Drive, Cambridge, MA 02139, USA', 'University of Chicago, 5807 S. Woodlawn Ave., Chicago, IL 60637, USA', 'Massachusetts Institute of Technology, 50 Memorial Drive, Cambridge, MA 02139, USA', 'Harvard University, 677 Huntington Avenue, Boston, MA 02115, USA']</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>We revisit the classic semi‐parametric problem of inference on a low‐dimensional parameter θ0 in the presence of high‐dimensional nuisance parameters η0. We depart from the classical setting by allowing for η0 to be so high‐dimensional that the traditional assumptions (e.g. Donsker properties) that limit complexity of the parameter space for this object break down. To estimate η0, we consider the use of statistical or machine learning (ML) methods, which are particularly well suited to estimation in modern, very high‐dimensional cases. ML methods perform well by employing regularization to reduce variance and trading off regularization bias with overfitting in practice. However, both regularization bias and overfitting in estimating η0 cause a heavy bias in estimators of θ0 that are obtained by naively plugging ML estimators of η0 into estimating equations for θ0. This bias results in the naive estimator failing to be N−1/2 consistent, where N is the sample size. We show that the impact of regularization bias and overfitting on estimation of the parameter of interest θ0 can be removed by using two simple, yet critical, ingredients: (1) using Neyman‐orthogonal moments/scores that have reduced sensitivity with respect to nuisance parameters to estimate θ0; (2) making use of cross‐fitting, which provides an efficient form of data‐splitting. We call the resulting set of methods double or debiased ML (DML). We verify that DML delivers point estimators that concentrate in an N−1/2‐neighbourhood of the true parameter values and are approximately unbiased and normally distributed, which allows construction of valid confidence statements. The generic statistical theory of DML is elementary and simultaneously relies on only weak theoretical requirements, which will admit the use of a broad array of modern ML methods for estimating the nuisance parameters, such as random forests, lasso, ridge, deep neural nets, boosted trees, and various hybrids and ensembles of these methods. We illustrate the general theory by applying it to provide theoretical properties of the following: DML applied to learn the main regression parameter in a partially linear regression model; DML applied to learn the coefficient on an endogenous variable in a partially linear instrumental variables model; DML applied to learn the average treatment effect and the average treatment effect on the treated under unconfoundedness; DML applied to learn the local average treatment effect in an instrumental variables setting. In addition to these theoretical applications, we also illustrate the use of DML in three empirical examples.</t>
+        </is>
+      </c>
       <c r="O102" t="inlineStr">
         <is>
           <t>21</t>
@@ -11981,28 +11993,32 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>C68</t>
+        </is>
+      </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>['Computer science', 'Geography', 'Artificial intelligence', 'Political science']</t>
+          <t>['Overfitting', 'Estimator', 'Nuisance parameter', 'Regularization (linguistics)', 'Mathematics', 'Statistics', 'Algorithm', 'Artificial intelligence', 'Applied mathematics', 'Computer science', 'Artificial neural network']</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['US']</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Rosenbaum P, 1983, BIOMETRIKA', 'Hansen L, 1982, ECONOMETRICA', 'Imbens G, 1994, ECONOMETRICA', 'Vaart A, 1998, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Abadie A, 2005, ECONOMETRICA', 'Bickel P, 2009, THE ANNALS OF STATISTICS', 'Robinson P, 1988, ECONOMETRICA', 'Belloni A, 2013, THE REVIEW OF ECONOMIC STUDIES', 'Schick A, 1994, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Zhang C, 2013, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Hahn J, 1998, ECONOMETRICA', 'Belloni A, 2012, ECONOMETRICA', 'Robins J, 1995, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Laan M, 2006, THE INTERNATIONAL JOURNAL OF BIOSTATISTICS', 'Geer S, 2014, THE ANNALS OF STATISTICS', 'Chamberlain G, 1987, JOURNAL OF ECONOMETRICS', 'Newey W, 1994, ECONOMETRICA', 'Dasgupta A, 2008, SPRINGER TEXTS IN STATISTICS', 'Bickel P, 1982, THE ANNALS OF STATISTICS', 'Newey W, 1990, JOURNAL OF APPLIED ECONOMETRICS', 'Imai K, 2013, THE ANNALS OF APPLIED STATISTICS', 'Chen X, 2003, ECONOMETRICA', 'Angrist J, 1995, JOURNAL OF BUSINESS AND ECONOMIC STATISTICS', 'Farrell M, 2015, JOURNAL OF ECONOMETRICS', 'Chamberlain G, 1992, ECONOMETRICA', 'Severini T, 1992, THE ANNALS OF STATISTICS', 'Andrews D, 1994, ECONOMETRICA', 'Bartoo J, 1967, THE ANNALS OF MATHEMATICAL STATISTICS', 'Fan J, 2011, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Frölich M, 2006, JOURNAL OF ECONOMETRICS', 'Chernozhukov V, 2015, AMERICAN ECONOMIC REVIEW', 'Schick A, 1986, THE ANNALS OF STATISTICS', 'Chernozhukov V, 2004, THE REVIEW OF ECONOMICS AND STATISTICS', 'Vaart A, 1991, THE ANNALS OF STATISTICS', 'Belloni A, 2014, BIOMETRIKA', 'Chen X, 1999, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Zheng W, 2011, SPRINGER SERIES IN STATISTICS', 'Robins J, 2008, INSTITUTE OF MATHEMATICAL STATISTICS EBOOKS', 'Newey W, 2004, ECONOMETRICA', 'Levit B, 1976, THEORY OF PROBABILITY AND ITS APPLICATIONS', 'Ai C, 2012, JOURNAL OF ECONOMETRICS', 'Hubbard A, 2016, THE INTERNATIONAL JOURNAL OF BIOSTATISTICS', 'Linton O, 1996, ECONOMETRIC THEORY', 'Bera A, 2010, ECONOMETRIC THEORY', 'Wooldridge J, 1991, JOURNAL OF ECONOMETRICS', 'Bilias Y, 2000, JOURNAL OF APPLIED ECONOMETRICS', 'Javanmard A, 2013, ARXIV (CORNELL UNIVERSITY)', 'Gautier É, 2011, ARXIV (CORNELL UNIVERSITY)', 'Belloni A, 2011, SSRN ELECTRONIC JOURNAL', 'Newey W, 1998, DSPACE@MIT (MASSACHUSETTS INSTITUTE OF TECHNOLOGY)', 'Acemoğlu D, 2001, AMERICAN ECONOMIC REVIEW', 'Hirano K, 2003, ECONOMETRICA', 'Laan M, 2007, STATISTICAL APPLICATIONS IN GENETICS AND MOLECULAR BIOLOGY', 'Bühlmann P, 2011, SPRINGER SERIES IN STATISTICS', 'Ибрагимов И, 1981, ', 'Laan M, 2011, SPRINGER SERIES IN STATISTICS', 'Rogers G, 1968, TECHNOMETRICS', 'Belloni A, 2011, BIOMETRIKA', 'Belloni A, 2013, BERNOULLI', 'Belloni A, 2010, THE ANNALS OF STATISTICS', 'Belloni A, 2017, ECONOMETRICA', 'Poterba J, 1995, JOURNAL OF PUBLIC ECONOMICS', 'Chernozhukov V, 2014, THE ANNALS OF STATISTICS', 'Andrews D, 1994, HANDBOOK OF ECONOMETRICS', 'Belloni A, 2016, JOURNAL OF BUSINESS AND ECONOMIC STATISTICS', 'Chernozhukov V, 2015, ANNUAL REVIEW OF ECONOMICS', 'Belloni A, 2014, THE ANNALS OF STATISTICS', 'J. R, 2008, ', 'Robins J, 2017, THE ANNALS OF STATISTICS', 'Belloni A, 2013, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Luedtke A, 2016, THE INTERNATIONAL JOURNAL OF BIOSTATISTICS', 'Jm R, 2013, PUBMED', 'Laan v, 2015, ', 'Walter R, 1959, AMERICAN MATHEMATICAL MONTHLY', ', 1995, CHOICE REVIEWS ONLINE', 'Toth B, 2016, COLLECTION OF BIOSTATISTICS RESEARCH ARCHIVE', 'Bickel P, 1988, UC BERKELEY', 'Zheng W, 2018, THE INTERNATIONAL JOURNAL OF BIOSTATISTICS', 'Feder P, 1980, TECHNOMETRICS', 'Wager S, 2015, ARXIV (CORNELL UNIVERSITY)', 'Chernozhukov V, 2017, ', 'Ichimura H, 2015, ', 'Luo Y, 2016, ARXIV (CORNELL UNIVERSITY)', 'Athey S, 2016, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -12018,34 +12034,30 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>津田 宏, 2006, 人工知能学会誌 = JOURNAL OF JAPANESE SOCIETY FOR ARTIFICIAL INTELLIGENCE</t>
+          <t>Chernozhukov V, 2017, ECONOMETRICS JOURNAL</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>津田 宏, 2006, 人工知能学会誌 = JOURNAL OF JAPANESE SOCIETY FOR ARTIFICIAL INTELLIGENCE</t>
+          <t>Chernozhukov V, 2017, ECONOMETRICS JOURNAL</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3123436326</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>10.1111/ectj.12097</t>
-        </is>
-      </c>
+          <t>https://openalex.org/W398859631</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Double/debiased machine learning for treatment and structural parameters</t>
+          <t>International Conference on Machine Learning (ICML)-2005</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -12059,39 +12071,39 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>2452</v>
+        <v>2486</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>ECONOMETRICS JOURNAL</t>
+          <t>人工知能学会誌 = JOURNAL OF JAPANESE SOCIETY FOR ARTIFICIAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Econometrics Journal</t>
+          <t>人工知能学会誌 = Journal of Japanese Society for Artificial Intelligence</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>['Victor Chernozhukov', 'Denis Chetverikov', 'Mert Demirer', 'Esther Duflo', 'Christian Hansen', 'Whitney K. Newey', 'James M. Robins']</t>
+          <t>['宏治 津田']</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>['Victor Chernozhukov', 'Denis Chetverikov', 'Mert Demirer', 'Esther Duflo', 'Christian Hansen', 'Whitney Newey', 'James Robins']</t>
+          <t>['宏治 津田']</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['Massachusetts Institute of Technology, 50 Memorial Drive, Cambridge, MA 02139, USA', 'University of California Los Angeles, 315 Portola Plaza, Los Angeles, CA 90095, USA', 'Massachusetts Institute of Technology, 50 Memorial Drive, Cambridge, MA 02139, USA', 'Massachusetts Institute of Technology, 50 Memorial Drive, Cambridge, MA 02139, USA', 'University of Chicago, 5807 S. Woodlawn Ave., Chicago, IL 60637, USA', 'Massachusetts Institute of Technology, 50 Memorial Drive, Cambridge, MA 02139, USA', 'Harvard University, 677 Huntington Avenue, Boston, MA 02115, USA']</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>We revisit the classic semi‐parametric problem of inference on a low‐dimensional parameter θ0 in the presence of high‐dimensional nuisance parameters η0. We depart from the classical setting by allowing for η0 to be so high‐dimensional that the traditional assumptions (e.g. Donsker properties) that limit complexity of the parameter space for this object break down. To estimate η0, we consider the use of statistical or machine learning (ML) methods, which are particularly well suited to estimation in modern, very high‐dimensional cases. ML methods perform well by employing regularization to reduce variance and trading off regularization bias with overfitting in practice. However, both regularization bias and overfitting in estimating η0 cause a heavy bias in estimators of θ0 that are obtained by naively plugging ML estimators of η0 into estimating equations for θ0. This bias results in the naive estimator failing to be N−1/2 consistent, where N is the sample size. We show that the impact of regularization bias and overfitting on estimation of the parameter of interest θ0 can be removed by using two simple, yet critical, ingredients: (1) using Neyman‐orthogonal moments/scores that have reduced sensitivity with respect to nuisance parameters to estimate θ0; (2) making use of cross‐fitting, which provides an efficient form of data‐splitting. We call the resulting set of methods double or debiased ML (DML). We verify that DML delivers point estimators that concentrate in an N−1/2‐neighbourhood of the true parameter values and are approximately unbiased and normally distributed, which allows construction of valid confidence statements. The generic statistical theory of DML is elementary and simultaneously relies on only weak theoretical requirements, which will admit the use of a broad array of modern ML methods for estimating the nuisance parameters, such as random forests, lasso, ridge, deep neural nets, boosted trees, and various hybrids and ensembles of these methods. We illustrate the general theory by applying it to provide theoretical properties of the following: DML applied to learn the main regression parameter in a partially linear regression model; DML applied to learn the coefficient on an endogenous variable in a partially linear instrumental variables model; DML applied to learn the average treatment effect and the average treatment effect on the treated under unconfoundedness; DML applied to learn the local average treatment effect in an instrumental variables setting. In addition to these theoretical applications, we also illustrate the use of DML in three empirical examples.</t>
-        </is>
-      </c>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宏治 津田 (corresponding author), </t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
           <t>21</t>
@@ -12099,32 +12111,28 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr">
-        <is>
-          <t>C68</t>
-        </is>
-      </c>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
-          <t>['Overfitting', 'Estimator', 'Nuisance parameter', 'Regularization (linguistics)', 'Mathematics', 'Statistics', 'Algorithm', 'Artificial intelligence', 'Applied mathematics', 'Computer science', 'Artificial neural network']</t>
+          <t>['Computer science', 'Geography', 'Artificial intelligence', 'Political science']</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>['US']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>['Rosenbaum P, 1983, BIOMETRIKA', 'Hansen L, 1982, ECONOMETRICA', 'Imbens G, 1994, ECONOMETRICA', 'Vaart A, 1998, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Abadie A, 2005, ECONOMETRICA', 'Bickel P, 2009, THE ANNALS OF STATISTICS', 'Robinson P, 1988, ECONOMETRICA', 'Belloni A, 2013, THE REVIEW OF ECONOMIC STUDIES', 'Schick A, 1994, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Zhang C, 2013, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Hahn J, 1998, ECONOMETRICA', 'Belloni A, 2012, ECONOMETRICA', 'Robins J, 1995, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Laan M, 2006, THE INTERNATIONAL JOURNAL OF BIOSTATISTICS', 'Geer S, 2014, THE ANNALS OF STATISTICS', 'Chamberlain G, 1987, JOURNAL OF ECONOMETRICS', 'Newey W, 1994, ECONOMETRICA', 'Dasgupta A, 2008, SPRINGER TEXTS IN STATISTICS', 'Bickel P, 1982, THE ANNALS OF STATISTICS', 'Newey W, 1990, JOURNAL OF APPLIED ECONOMETRICS', 'Imai K, 2013, THE ANNALS OF APPLIED STATISTICS', 'Chen X, 2003, ECONOMETRICA', 'Angrist J, 1995, JOURNAL OF BUSINESS AND ECONOMIC STATISTICS', 'Farrell M, 2015, JOURNAL OF ECONOMETRICS', 'Chamberlain G, 1992, ECONOMETRICA', 'Severini T, 1992, THE ANNALS OF STATISTICS', 'Andrews D, 1994, ECONOMETRICA', 'Bartoo J, 1967, THE ANNALS OF MATHEMATICAL STATISTICS', 'Fan J, 2011, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Frölich M, 2006, JOURNAL OF ECONOMETRICS', 'Chernozhukov V, 2015, AMERICAN ECONOMIC REVIEW', 'Schick A, 1986, THE ANNALS OF STATISTICS', 'Chernozhukov V, 2004, THE REVIEW OF ECONOMICS AND STATISTICS', 'Vaart A, 1991, THE ANNALS OF STATISTICS', 'Belloni A, 2014, BIOMETRIKA', 'Chen X, 1999, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Zheng W, 2011, SPRINGER SERIES IN STATISTICS', 'Robins J, 2008, INSTITUTE OF MATHEMATICAL STATISTICS EBOOKS', 'Newey W, 2004, ECONOMETRICA', 'Levit B, 1976, THEORY OF PROBABILITY AND ITS APPLICATIONS', 'Ai C, 2012, JOURNAL OF ECONOMETRICS', 'Hubbard A, 2016, THE INTERNATIONAL JOURNAL OF BIOSTATISTICS', 'Linton O, 1996, ECONOMETRIC THEORY', 'Bera A, 2010, ECONOMETRIC THEORY', 'Wooldridge J, 1991, JOURNAL OF ECONOMETRICS', 'Bilias Y, 2000, JOURNAL OF APPLIED ECONOMETRICS', 'Javanmard A, 2013, ARXIV (CORNELL UNIVERSITY)', 'Gautier É, 2011, ARXIV (CORNELL UNIVERSITY)', 'Belloni A, 2011, SSRN ELECTRONIC JOURNAL', 'Newey W, 1998, DSPACE@MIT (MASSACHUSETTS INSTITUTE OF TECHNOLOGY)', 'Acemoğlu D, 2001, AMERICAN ECONOMIC REVIEW', 'Hirano K, 2003, ECONOMETRICA', 'Laan M, 2007, STATISTICAL APPLICATIONS IN GENETICS AND MOLECULAR BIOLOGY', 'Bühlmann P, 2011, SPRINGER SERIES IN STATISTICS', 'Ибрагимов И, 1981, ', 'Laan M, 2011, SPRINGER SERIES IN STATISTICS', 'Rogers G, 1968, TECHNOMETRICS', 'Belloni A, 2011, BIOMETRIKA', 'Belloni A, 2013, BERNOULLI', 'Belloni A, 2010, THE ANNALS OF STATISTICS', 'Belloni A, 2017, ECONOMETRICA', 'Poterba J, 1995, JOURNAL OF PUBLIC ECONOMICS', 'Chernozhukov V, 2014, THE ANNALS OF STATISTICS', 'Andrews D, 1994, HANDBOOK OF ECONOMETRICS', 'Belloni A, 2016, JOURNAL OF BUSINESS AND ECONOMIC STATISTICS', 'Chernozhukov V, 2015, ANNUAL REVIEW OF ECONOMICS', 'Belloni A, 2014, THE ANNALS OF STATISTICS', 'J. R, 2008, ', 'Robins J, 2017, THE ANNALS OF STATISTICS', 'Belloni A, 2013, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Luedtke A, 2016, THE INTERNATIONAL JOURNAL OF BIOSTATISTICS', 'Jm R, 2013, PUBMED', 'Laan v, 2015, ', 'Walter R, 1959, AMERICAN MATHEMATICAL MONTHLY', ', 1995, CHOICE REVIEWS ONLINE', 'Toth B, 2016, COLLECTION OF BIOSTATISTICS RESEARCH ARCHIVE', 'Bickel P, 1988, UC BERKELEY', 'Zheng W, 2018, THE INTERNATIONAL JOURNAL OF BIOSTATISTICS', 'Feder P, 1980, TECHNOMETRICS', 'Wager S, 2015, ARXIV (CORNELL UNIVERSITY)', 'Chernozhukov V, 2017, ', 'Ichimura H, 2015, ', 'Luo Y, 2016, ARXIV (CORNELL UNIVERSITY)', 'Athey S, 2016, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -12140,12 +12148,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>Chernozhukov V, 2017, ECONOMETRICS JOURNAL</t>
+          <t>津田 宏, 2006, 人工知能学会誌 = JOURNAL OF JAPANESE SOCIETY FOR ARTIFICIAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>Chernozhukov V, 2017, ECONOMETRICS JOURNAL</t>
+          <t>津田 宏, 2006, 人工知能学会誌 = JOURNAL OF JAPANESE SOCIETY FOR ARTIFICIAL INTELLIGENCE</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12189,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -12409,7 +12417,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -12519,7 +12527,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -12608,22 +12616,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2048266589</t>
+          <t>https://openalex.org/W2337082154</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>10.1109/micro.2014.58</t>
+          <t>10.1038/nphys4035</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>DaDianNao: A Machine-Learning Supercomputer</t>
+          <t>Machine learning phases of matter</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -12637,56 +12645,72 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>1506</v>
-      </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
+        <v>1474</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>NATURE PHYSICS</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Nature Physics</t>
+        </is>
+      </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>['Yunji Chen', 'Tao Luo', 'Shaoli Liu', 'Shijin Zhang', 'Liqiang He', 'Jia Wang', 'Ling Li', 'Tianshi Chen', 'Zhiwei Xu', 'Ninghui Sun', 'Olivier Temam']</t>
+          <t>['Juan Carrasquilla', 'Roger G. Melko']</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>['Yunji Chen', 'Tao Luo', 'Shaoli Liu', 'Shijin Zhang', 'Liqiang He', 'Jia Wang', 'Ling Li', 'Tianshi Chen', 'Zhiwei Xu', 'Ninghui Sun', 'Olivier Temam']</t>
+          <t>['Juan Carrasquilla', 'Roger G. Melko']</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['SKL of Computer Architecture, ICT, CAS, China', 'SKL of Computer Architecture, ICT, CAS, China', 'University of CAS, China', 'SKL of Computer Architecture, ICT, CAS, China', 'SKL of Computer Architecture, ICT, CAS, China', 'Inner Mongolia University, China', 'Inria, Scalay, France', 'SKL of Computer Architecture, ICT, CAS, China', 'SKL of Computer Architecture, ICT, CAS, China', 'SKL of Computer Architecture, ICT, CAS, China', 'SKL of Computer Architecture, ICT, CAS, China', 'SKL of Computer Architecture, ICT, CAS, China', 'Inria, Scalay, France']</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>Many companies are deploying services, either for consumers or industry, which are largely based on machine-learning algorithms for sophisticated processing of large amounts of data. The state-of-the-art and most popular such machine-learning algorithms are Convolutional and Deep Neural Networks (CNNs and DNNs), which are known to be both computationally and memory intensive. A number of neural network accelerators have been recently proposed which can offer high computational capacity/area ratio, but which remain hampered by memory accesses. However, unlike the memory wall faced by processors on general-purpose workloads, the CNNs and DNNs memory footprint, while large, is not beyond the capability of the on chip storage of a multi-chip system. This property, combined with the CNN/DNN algorithmic characteristics, can lead to high internal bandwidth and low external communications, which can in turn enable high-degree parallelism at a reasonable area cost. In this article, we introduce a custom multi-chip machine-learning architecture along those lines. We show that, on a subset of the largest known neural network layers, it is possible to achieve a speedup of 450.65x over a GPU, and reduce the energy by 150.31x on average for a 64-chip system. We implement the node down to the place and route at 28nm, containing a combination of custom storage and computational units, with industry-grade interconnects.</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
+          <t>['Perimeter Institute for Theoretical Physics, Waterloo, Ontario N2L 2Y5, Canada', 'Department of Physics and Astronomy, University of Waterloo, Ontario N2L 3G1, Canada', 'Perimeter Institute for Theoretical Physics, Waterloo, Ontario N2L 2Y5, Canada']</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Juan Carrasquilla (corresponding author), Perimeter Institute for Theoretical Physics, Waterloo, Ontario N2L 2Y5, Canada</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>431</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>434</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>['Computer science', 'Supercomputer', 'Memory footprint', 'Convolutional neural network', 'Speedup', 'Parallel computing', 'Artificial neural network', 'Deep learning', 'Memory bandwidth', 'Bandwidth (computing)', 'Auxiliary memory', 'Computer architecture', 'Artificial intelligence', 'Distributed computing', 'Computer engineering', 'Computer hardware', 'Operating system', 'Computer network']</t>
+          <t>['Physics', 'Artificial neural network', 'Locality', 'Artificial intelligence', 'Convolutional neural network', 'Monte Carlo method', 'Statistical physics', 'Coulomb', 'Machine learning', 'Computer science', 'Quantum mechanics']</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>['FR', 'CN']</t>
+          <t>['CA']</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>['Krizhevsky A, 2017, COMMUNICATIONS OF THE ACM', 'Deng J, 2009, 2009 IEEE CONFERENCE ON COMPUTER VISION AND PATTERN RECOGNITION', 'LeCun Y, 1998, PROCEEDINGS OF THE IEEE', 'Cireşan D, 2012, ', 'Bienia C, 2008, ', 'Dally W, 2004, ', 'Deng J, 2009, 2009 IEEE CONFERENCE ON COMPUTER VISION AND PATTERN RECOGNITION', 'Dean J, 2012, ', 'Jarrett K, 2009, ', 'Huang P, 2013, ', 'Le Q, 2013, ', 'Esmaeilzadeh H, 2011, ', 'Chen T, 2014, ', 'Dahl G, 2013, ', 'Cireşan D, 2011, ', ', 2009, ', 'Larochelle H, 2007, ', 'Vanhoucke V, 2011, ', 'Ranzato M, 2012, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Esmaeilzadeh H, 2012, ', 'Coates A, 2013, ', 'Esmaeilzadeh H, 2012, IEEE MICRO', 'Salakhutdinov R, 2012, NEURAL COMPUTATION', 'Ferrucci D, 2012, IBM JOURNAL OF RESEARCH AND DEVELOPMENT', 'Merolla P, 2011, ', 'Hameed R, 2010, ', 'Farabet C, 2011, ', 'Mnih V, 2012, ', 'Hadsell R, 2009, JOURNAL OF FIELD ROBOTICS', 'Schemmel J, 2008, ', 'Khan M, 2008, ', 'Kahng A, 2011, IEEE TRANSACTIONS ON VERY LARGE SCALE INTEGRATION (VLSI) SYSTEMS', 'Qadeer W, 2013, ', 'Hong S, 2013, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Temam O, 2012, ACM SIGARCH COMPUTER ARCHITECTURE NEWS', 'Venkatesh G, 2011, ', 'Chen D, 2011, IEEE MICRO', 'Temam O, 2012, ', 'Matick R, 2005, IBM JOURNAL OF RESEARCH AND DEVELOPMENT', 'Fan K, 2009, ', 'Belhadj B, 2013, ', 'Hashmi A, 2011, ', 'Wang G, 2009, ', 'Majumdar A, 2012, ACM TRANSACTIONS ON ARCHITECTURE AND CODE OPTIMIZATION', 'Hashmi A, 2011, ', 'Huang L, 2011, IEEE TRANSACTIONS ON COMPUTERS', 'Huang K, 2011, ', 'Maeda N, 2012, ', 'Deneroff M, 2008, ', ', 2009, JOURNAL OF FIELD ROBOTICS']</t>
+          <t>['LeCun Y, 1998, PROCEEDINGS OF THE IEEE', 'Bellman R, 1966, SCIENCE', 'Goodfellow I, 2016, MIT PRESS EBOOKS', 'Kitaev A, 2003, ANNALS OF PHYSICS', 'Onsager L, 1944, PHYSICAL REVIEW', 'Kitaev A, 2006, PHYSICAL REVIEW LETTERS', 'Levin M, 2006, PHYSICAL REVIEW LETTERS', 'Kogut J, 1979, REVIEWS OF MODERN PHYSICS', 'Montaño J, 2011, CONFERENCE', 'Ghiringhelli L, 2015, PHYSICAL REVIEW LETTERS', 'Nieuwenburg E, 2017, NATURE PHYSICS', 'Wen X, 2007, ', 'Sandvik A, 2016, ', 'Sandvik A, 2010, AIP CONFERENCE PROCEEDINGS', 'Schoenholz S, 2016, NATURE PHYSICS', 'Kalinin S, 2015, NATURE MATERIALS', 'Kusne A, 2014, SCIENTIFIC REPORTS', 'Castelnovo C, 2007, PHYSICAL REVIEW B', 'Avella A, 2013, ', 'Arsenault L, 2014, PHYSICAL REVIEW B', 'Avella A, 2013, SPRINGER SERIES IN SOLID-STATE SCIENCES', 'Castelnovo C, 2007, PHYSICAL REVIEW B', 'Landon-Cardinal O, 2012, NEW JOURNAL OF PHYSICS', 'Newell G, 1950, PHYSICAL REVIEW', 'Prelovšek P, 2011, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -12702,34 +12726,34 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chen Y, 2014, </t>
+          <t>Carrasquilla J, 2017, NATURE PHYSICS</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chen Y, 2014, </t>
+          <t>Carrasquilla J, 2017, NATURE PHYSICS</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2337082154</t>
+          <t>https://openalex.org/W2048266589</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>10.1038/nphys4035</t>
+          <t>10.1109/micro.2014.58</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Machine learning phases of matter</t>
+          <t>DaDianNao: A Machine-Learning Supercomputer</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -12743,72 +12767,56 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1474</v>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>NATURE PHYSICS</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>Nature Physics</t>
-        </is>
-      </c>
+        <v>1506</v>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
-          <t>['Juan Carrasquilla', 'Roger G. Melko']</t>
+          <t>['Yunji Chen', 'Tao Luo', 'Shaoli Liu', 'Shijin Zhang', 'Liqiang He', 'Jia Wang', 'Ling Li', 'Tianshi Chen', 'Zhiwei Xu', 'Ninghui Sun', 'Olivier Temam']</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>['Juan Carrasquilla', 'Roger G. Melko']</t>
+          <t>['Yunji Chen', 'Tao Luo', 'Shaoli Liu', 'Shijin Zhang', 'Liqiang He', 'Jia Wang', 'Ling Li', 'Tianshi Chen', 'Zhiwei Xu', 'Ninghui Sun', 'Olivier Temam']</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['Perimeter Institute for Theoretical Physics, Waterloo, Ontario N2L 2Y5, Canada', 'Department of Physics and Astronomy, University of Waterloo, Ontario N2L 3G1, Canada', 'Perimeter Institute for Theoretical Physics, Waterloo, Ontario N2L 2Y5, Canada']</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>Juan Carrasquilla (corresponding author), Perimeter Institute for Theoretical Physics, Waterloo, Ontario N2L 2Y5, Canada</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>['SKL of Computer Architecture, ICT, CAS, China', 'SKL of Computer Architecture, ICT, CAS, China', 'University of CAS, China', 'SKL of Computer Architecture, ICT, CAS, China', 'SKL of Computer Architecture, ICT, CAS, China', 'Inner Mongolia University, China', 'Inria, Scalay, France', 'SKL of Computer Architecture, ICT, CAS, China', 'SKL of Computer Architecture, ICT, CAS, China', 'SKL of Computer Architecture, ICT, CAS, China', 'SKL of Computer Architecture, ICT, CAS, China', 'SKL of Computer Architecture, ICT, CAS, China', 'Inria, Scalay, France']</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Many companies are deploying services, either for consumers or industry, which are largely based on machine-learning algorithms for sophisticated processing of large amounts of data. The state-of-the-art and most popular such machine-learning algorithms are Convolutional and Deep Neural Networks (CNNs and DNNs), which are known to be both computationally and memory intensive. A number of neural network accelerators have been recently proposed which can offer high computational capacity/area ratio, but which remain hampered by memory accesses. However, unlike the memory wall faced by processors on general-purpose workloads, the CNNs and DNNs memory footprint, while large, is not beyond the capability of the on chip storage of a multi-chip system. This property, combined with the CNN/DNN algorithmic characteristics, can lead to high internal bandwidth and low external communications, which can in turn enable high-degree parallelism at a reasonable area cost. In this article, we introduce a custom multi-chip machine-learning architecture along those lines. We show that, on a subset of the largest known neural network layers, it is possible to achieve a speedup of 450.65x over a GPU, and reduce the energy by 150.31x on average for a 64-chip system. We implement the node down to the place and route at 28nm, containing a combination of custom storage and computational units, with industry-grade interconnects.</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>609</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>622</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>['Physics', 'Artificial neural network', 'Locality', 'Artificial intelligence', 'Convolutional neural network', 'Monte Carlo method', 'Statistical physics', 'Coulomb', 'Machine learning', 'Computer science', 'Quantum mechanics']</t>
+          <t>['Computer science', 'Supercomputer', 'Memory footprint', 'Convolutional neural network', 'Speedup', 'Parallel computing', 'Artificial neural network', 'Deep learning', 'Memory bandwidth', 'Bandwidth (computing)', 'Auxiliary memory', 'Computer architecture', 'Artificial intelligence', 'Distributed computing', 'Computer engineering', 'Computer hardware', 'Operating system', 'Computer network']</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>['CA']</t>
+          <t>['FR', 'CN']</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>['LeCun Y, 1998, PROCEEDINGS OF THE IEEE', 'Bellman R, 1966, SCIENCE', 'Goodfellow I, 2016, MIT PRESS EBOOKS', 'Kitaev A, 2003, ANNALS OF PHYSICS', 'Onsager L, 1944, PHYSICAL REVIEW', 'Kitaev A, 2006, PHYSICAL REVIEW LETTERS', 'Levin M, 2006, PHYSICAL REVIEW LETTERS', 'Kogut J, 1979, REVIEWS OF MODERN PHYSICS', 'Montaño J, 2011, CONFERENCE', 'Ghiringhelli L, 2015, PHYSICAL REVIEW LETTERS', 'Nieuwenburg E, 2017, NATURE PHYSICS', 'Wen X, 2007, ', 'Sandvik A, 2016, ', 'Sandvik A, 2010, AIP CONFERENCE PROCEEDINGS', 'Schoenholz S, 2016, NATURE PHYSICS', 'Kalinin S, 2015, NATURE MATERIALS', 'Kusne A, 2014, SCIENTIFIC REPORTS', 'Castelnovo C, 2007, PHYSICAL REVIEW B', 'Avella A, 2013, ', 'Arsenault L, 2014, PHYSICAL REVIEW B', 'Avella A, 2013, SPRINGER SERIES IN SOLID-STATE SCIENCES', 'Castelnovo C, 2007, PHYSICAL REVIEW B', 'Landon-Cardinal O, 2012, NEW JOURNAL OF PHYSICS', 'Newell G, 1950, PHYSICAL REVIEW', 'Prelovšek P, 2011, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>['Krizhevsky A, 2017, COMMUNICATIONS OF THE ACM', 'Deng J, 2009, 2009 IEEE CONFERENCE ON COMPUTER VISION AND PATTERN RECOGNITION', 'LeCun Y, 1998, PROCEEDINGS OF THE IEEE', 'Cireşan D, 2012, ', 'Bienia C, 2008, ', 'Dally W, 2004, ', 'Deng J, 2009, 2009 IEEE CONFERENCE ON COMPUTER VISION AND PATTERN RECOGNITION', 'Dean J, 2012, ', 'Jarrett K, 2009, ', 'Huang P, 2013, ', 'Le Q, 2013, ', 'Esmaeilzadeh H, 2011, ', 'Chen T, 2014, ', 'Dahl G, 2013, ', 'Cireşan D, 2011, ', ', 2009, ', 'Larochelle H, 2007, ', 'Vanhoucke V, 2011, ', 'Ranzato M, 2012, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Esmaeilzadeh H, 2012, ', 'Coates A, 2013, ', 'Esmaeilzadeh H, 2012, IEEE MICRO', 'Salakhutdinov R, 2012, NEURAL COMPUTATION', 'Ferrucci D, 2012, IBM JOURNAL OF RESEARCH AND DEVELOPMENT', 'Merolla P, 2011, ', 'Hameed R, 2010, ', 'Farabet C, 2011, ', 'Mnih V, 2012, ', 'Hadsell R, 2009, JOURNAL OF FIELD ROBOTICS', 'Schemmel J, 2008, ', 'Khan M, 2008, ', 'Kahng A, 2011, IEEE TRANSACTIONS ON VERY LARGE SCALE INTEGRATION (VLSI) SYSTEMS', 'Qadeer W, 2013, ', 'Hong S, 2013, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Temam O, 2012, ACM SIGARCH COMPUTER ARCHITECTURE NEWS', 'Venkatesh G, 2011, ', 'Chen D, 2011, IEEE MICRO', 'Temam O, 2012, ', 'Matick R, 2005, IBM JOURNAL OF RESEARCH AND DEVELOPMENT', 'Fan K, 2009, ', 'Belhadj B, 2013, ', 'Hashmi A, 2011, ', 'Wang G, 2009, ', 'Majumdar A, 2012, ACM TRANSACTIONS ON ARCHITECTURE AND CODE OPTIMIZATION', 'Hashmi A, 2011, ', 'Huang L, 2011, IEEE TRANSACTIONS ON COMPUTERS', 'Huang K, 2011, ', 'Maeda N, 2012, ', 'Deneroff M, 2008, ', ', 2009, JOURNAL OF FIELD ROBOTICS']</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -12824,12 +12832,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>Carrasquilla J, 2017, NATURE PHYSICS</t>
+          <t xml:space="preserve">Chen Y, 2014, </t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>Carrasquilla J, 2017, NATURE PHYSICS</t>
+          <t xml:space="preserve">Chen Y, 2014, </t>
         </is>
       </c>
     </row>
@@ -12865,7 +12873,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -12934,7 +12942,7 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>['He K, 2016, ', 'Maaten L, 2008, JOURNAL OF MACHINE LEARNING RESEARCH', 'Friedman J, 2001, THE ANNALS OF STATISTICS', 'Ribeiro M, 2016, ', 'Hartigan J, 1979, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES C (APPLIED STATISTICS)', 'David F, 1977, BIOMETRICS', 'Nickerson R, 1998, REVIEW OF GENERAL PSYCHOLOGY', 'Breiman L, 2001, STATISTICAL SCIENCE', 'Heider F, 1944, THE AMERICAN JOURNAL OF PSYCHOLOGY', 'Goldstein A, 2014, JOURNAL OF COMPUTATIONAL AND GRAPHICAL STATISTICS', 'Herlocker J, 2000, ', 'Kahneman D, 1982, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Montavon G, 2016, PATTERN RECOGNITION', 'Friedman J, 2008, THE ANNALS OF APPLIED STATISTICS', 'Andrews R, 1995, KNOWLEDGE-BASED SYSTEMS', 'Cowan N, 2010, CURRENT DIRECTIONS IN PSYCHOLOGICAL SCIENCE', 'Lakkaraju H, 2016, ', 'Golovin D, 2017, ', 'Freitas A, 2014, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Kim B, 2016, NEURAL INFORMATION PROCESSING SYSTEMS', 'Lou Y, 2012, ', 'Cramer H, 2008, USER MODELING AND USER-ADAPTED INTERACTION', 'Kahng M, 2017, IEEE TRANSACTIONS ON VISUALIZATION AND COMPUTER GRAPHICS', 'Lent M, 2004, ', 'Wu M, 2018, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Wang T, 2017, ', 'Donnelly C, 2010, ASTIN BULLETIN', 'Goodman B, 2016, ARXIV (CORNELL UNIVERSITY)', 'Temizer S, 2010, AIAA GUIDANCE, NAVIGATION, AND CONTROL CONFERENCE', 'Fisher A, 2018, ARXIV (CORNELL UNIVERSITY)', 'Angelino E, 2017, ', 'Weller A, 2017, ARXIV (CORNELL UNIVERSITY)', 'Rudziński F, 2015, APPLIED SOFT COMPUTING', 'Rüping S, 2006, ', 'Keil F, 2004, ', 'Swartout W, 1983, COMPUTER COMPACTS', 'Hinton G, 2015, ARXIV (CORNELL UNIVERSITY)', 'Lundberg S, 2017, ARXIV (CORNELL UNIVERSITY)', 'Doshi‐Velez F, 2017, ARXIV (CORNELL UNIVERSITY)', 'Springenberg J, 2014, ARXIV (CORNELL UNIVERSITY)', 'Smilkov D, 2017, ARXIV (CORNELL UNIVERSITY)', 'Doran D, 2017, ARXIV (CORNELL UNIVERSITY)', 'Frosst N, 2017, ARXIV (CORNELL UNIVERSITY)', 'Polino A, 2018, ARXIV (CORNELL UNIVERSITY)', 'Apley D, 2016, ARXIV (CORNELL UNIVERSITY)', 'Bastani O, 2017, ARXIV (CORNELL UNIVERSITY)', 'Kim B, 2015, ARXIV (CORNELL UNIVERSITY)', 'Murdoch W, 2017, ARXIV (CORNELL UNIVERSITY)', 'Tan S, 2017, ARXIV (CORNELL UNIVERSITY)', 'Selvaraju R, 2017, ', 'Adadi A, 2018, IEEE ACCESS', 'Ribeiro M, 2018, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Holzinger A, 2019, WILEY INTERDISCIPLINARY REVIEWS DATA MINING AND KNOWLEDGE DISCOVERY', 'Wachter S, 2017, INTERNATIONAL DATA PRIVACY LAW', 'Thelisson E, 2018, ', 'Abdul A, 2018, ', 'Gunning D, 2019, ', 'Molnar C, 2020, ', 'Pope P, 2019, ', 'Zhang Q, 2019, ', 'Zhang J, 2018, IEEE TRANSACTIONS ON VISUALIZATION AND COMPUTER GRAPHICS', 'Robnik‐Šikonja M, 2018, HUMAN-COMPUTER INTERACTION SERIES', 'Doshi‐Velez F, 2018, \x98THE \x9cSPRINGER SERIES ON CHALLENGES IN MACHINE LEARNING', 'Rudin C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Staniak M, 2018, LINCOLN (UNIVERSITY OF NEBRASKA)', 'Gilpin L, 2018, ARXIV (CORNELL UNIVERSITY)', 'Rudin C, 2018, INFORMS JOURNAL ON APPLIED ANALYTICS', 'Staniak M, 2019, THE R JOURNAL', 'Stoyanov D, 2018, LECTURE NOTES IN COMPUTER SCIENCE', 'Bibal A, 2016, REPOSITORY OF THE UNIVERSITY OF NAMUR', 'Silva W, 2018, LECTURE NOTES IN COMPUTER SCIENCE', 'Case N, 2018, JOURNAL OF DESIGN AND SCIENCE', 'Palangi H, 2018, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Müller H, 2021, ARTIFICIAL INTELLIGENCE', 'Fahner G, 2018, ', 'Shah N, 2020, INTERNATIONAL JOURNAL OF INNOVATIVE TECHNOLOGY AND EXPLORING ENGINEERING', 'Wagner J, 2019, ', 'Lim B, 2019, ', ', , VIEW', 'Jolliffe I, 2014, WILEY STATSREF: STATISTICS REFERENCE ONLINE', 'Kim B, 2017, ARXIV (CORNELL UNIVERSITY)', 'Kim B, 2017, ARXIV (CORNELL UNIVERSITY)', 'Sundararajan M, 2017, ARXIV (CORNELL UNIVERSITY)', 'Hardt M, 2016, ARXIV (CORNELL UNIVERSITY)', 'Wu M, 2017, ARXIV (CORNELL UNIVERSITY)', 'Kindermans P, 2017, ARXIV (CORNELL UNIVERSITY)', 'Dash S, 2018, ARXIV (CORNELL UNIVERSITY)', 'Lage I, 2018, ARXIV (CORNELL UNIVERSITY)', 'Honegger M, 2018, ARXIV (CORNELL UNIVERSITY)', 'Kirsch A, 2017, HAL (LE CENTRE POUR LA COMMUNICATION SCIENTIFIQUE DIRECTE)', 'Varshney K, 2018, ARXIV (CORNELL UNIVERSITY)', 'Jolliffe I, 2011, INTERNATIONAL ENCYCLOPEDIA OF STATISTICAL SCIENCE', 'Lipton P, 1990, ROYAL INSTITUTE OF PHILOSOPHY SUPPLEMENT', 'Hossain M, 2021, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Yang H, 2016, ']</t>
+          <t>['He K, 2016, ', 'Maaten L, 2008, JOURNAL OF MACHINE LEARNING RESEARCH', 'Friedman J, 2001, THE ANNALS OF STATISTICS', 'Ribeiro M, 2016, ', 'Hartigan J, 1979, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES C (APPLIED STATISTICS)', 'David F, 1977, BIOMETRICS', 'Nickerson R, 1998, REVIEW OF GENERAL PSYCHOLOGY', 'Breiman L, 2001, STATISTICAL SCIENCE', 'Heider F, 1944, THE AMERICAN JOURNAL OF PSYCHOLOGY', 'Goldstein A, 2014, JOURNAL OF COMPUTATIONAL AND GRAPHICAL STATISTICS', 'Herlocker J, 2000, ', 'Kahneman D, 1982, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Montavon G, 2016, PATTERN RECOGNITION', 'Friedman J, 2008, THE ANNALS OF APPLIED STATISTICS', 'Andrews R, 1995, KNOWLEDGE-BASED SYSTEMS', 'Cowan N, 2010, CURRENT DIRECTIONS IN PSYCHOLOGICAL SCIENCE', 'Lakkaraju H, 2016, ', 'Golovin D, 2017, ', 'Freitas A, 2014, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Kim B, 2016, NEURAL INFORMATION PROCESSING SYSTEMS', 'Lou Y, 2012, ', 'Cramer H, 2008, USER MODELING AND USER-ADAPTED INTERACTION', 'Kahng M, 2017, IEEE TRANSACTIONS ON VISUALIZATION AND COMPUTER GRAPHICS', 'Lent M, 2004, ', 'Wu M, 2018, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Wang T, 2017, ', 'Donnelly C, 2010, ASTIN BULLETIN', 'Goodman B, 2016, ARXIV (CORNELL UNIVERSITY)', 'Temizer S, 2010, AIAA GUIDANCE, NAVIGATION, AND CONTROL CONFERENCE', 'Fisher A, 2018, ARXIV (CORNELL UNIVERSITY)', 'Angelino E, 2017, ', 'Weller A, 2017, ARXIV (CORNELL UNIVERSITY)', 'Rudziński F, 2015, APPLIED SOFT COMPUTING', 'Rüping S, 2006, ', 'Melle W, 2005, ', 'Keil F, 2004, ', 'Swartout W, 1983, COMPUTER COMPACTS', 'Hinton G, 2015, ARXIV (CORNELL UNIVERSITY)', 'Lundberg S, 2017, ARXIV (CORNELL UNIVERSITY)', 'Doshi‐Velez F, 2017, ARXIV (CORNELL UNIVERSITY)', 'Springenberg J, 2014, ARXIV (CORNELL UNIVERSITY)', 'Smilkov D, 2017, ARXIV (CORNELL UNIVERSITY)', 'Doran D, 2017, ARXIV (CORNELL UNIVERSITY)', 'Frosst N, 2017, ARXIV (CORNELL UNIVERSITY)', 'Polino A, 2018, ARXIV (CORNELL UNIVERSITY)', 'Apley D, 2016, ARXIV (CORNELL UNIVERSITY)', 'Bastani O, 2017, ARXIV (CORNELL UNIVERSITY)', 'Kim B, 2015, ARXIV (CORNELL UNIVERSITY)', 'Murdoch W, 2017, ARXIV (CORNELL UNIVERSITY)', 'Tan S, 2017, ARXIV (CORNELL UNIVERSITY)', 'Selvaraju R, 2017, ', 'Adadi A, 2018, IEEE ACCESS', 'Ribeiro M, 2018, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Holzinger A, 2019, WILEY INTERDISCIPLINARY REVIEWS DATA MINING AND KNOWLEDGE DISCOVERY', 'Wachter S, 2017, INTERNATIONAL DATA PRIVACY LAW', 'Thelisson E, 2018, ', 'Abdul A, 2018, ', 'Gunning D, 2019, ', 'Pope P, 2019, ', 'Molnar C, 2020, ', 'Zhang Q, 2019, ', 'Zhang J, 2018, IEEE TRANSACTIONS ON VISUALIZATION AND COMPUTER GRAPHICS', 'Robnik‐Šikonja M, 2018, HUMAN-COMPUTER INTERACTION SERIES', 'Doshi‐Velez F, 2018, \x98THE \x9cSPRINGER SERIES ON CHALLENGES IN MACHINE LEARNING', 'Rudin C, 2018, ARXIV (CORNELL UNIVERSITY)', 'Staniak M, 2018, LINCOLN (UNIVERSITY OF NEBRASKA)', 'Gilpin L, 2018, ARXIV (CORNELL UNIVERSITY)', 'Rudin C, 2018, INFORMS JOURNAL ON APPLIED ANALYTICS', 'Staniak M, 2019, THE R JOURNAL', 'Stoyanov D, 2018, LECTURE NOTES IN COMPUTER SCIENCE', 'Bibal A, 2016, REPOSITORY OF THE UNIVERSITY OF NAMUR', 'Silva W, 2018, LECTURE NOTES IN COMPUTER SCIENCE', 'Case N, 2018, JOURNAL OF DESIGN AND SCIENCE', 'Palangi H, 2018, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Müller H, 2021, ARTIFICIAL INTELLIGENCE', 'Fahner G, 2018, ', 'Shah N, 2020, INTERNATIONAL JOURNAL OF INNOVATIVE TECHNOLOGY AND EXPLORING ENGINEERING', 'Wagner J, 2019, ', 'Lim B, 2019, ', ', , VIEW', 'Jolliffe I, 2014, WILEY STATSREF: STATISTICS REFERENCE ONLINE', 'Kim B, 2017, ARXIV (CORNELL UNIVERSITY)', 'Kim B, 2017, ARXIV (CORNELL UNIVERSITY)', 'Sundararajan M, 2017, ARXIV (CORNELL UNIVERSITY)', 'Hardt M, 2016, ARXIV (CORNELL UNIVERSITY)', 'Wu M, 2017, ARXIV (CORNELL UNIVERSITY)', 'Kindermans P, 2017, ARXIV (CORNELL UNIVERSITY)', 'Dash S, 2018, ARXIV (CORNELL UNIVERSITY)', 'Lage I, 2018, ARXIV (CORNELL UNIVERSITY)', 'Honegger M, 2018, ARXIV (CORNELL UNIVERSITY)', 'Kirsch A, 2017, HAL (LE CENTRE POUR LA COMMUNICATION SCIENTIFIQUE DIRECTE)', 'Varshney K, 2018, ARXIV (CORNELL UNIVERSITY)', 'Jolliffe I, 2011, INTERNATIONAL ENCYCLOPEDIA OF STATISTICAL SCIENCE', 'Lipton P, 1990, ROYAL INSTITUTE OF PHILOSOPHY SUPPLEMENT', 'Hossain M, 2021, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Yang H, 2016, ']</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -12991,7 +12999,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -13084,22 +13092,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2798701005</t>
+          <t>https://openalex.org/W2601810315</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>10.1126/science.aat8084</t>
+          <t>10.1093/bioinformatics/btx180</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>All-optical machine learning using diffractive deep neural networks</t>
+          <t>Trainable Weka Segmentation: a machine learning tool for microscopy pixel classification</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -13113,76 +13121,76 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>2422</v>
+        <v>2478</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>SCIENCE</t>
+          <t>BIOINFORMATICS</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Bioinformatics</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>['Xing Lin', 'Yair Rivenson', 'Nezih Tolga Yardimci', 'Muhammed Veli', 'Yi Luo', 'Mona Jarrahi', 'Aydogan Özcan']</t>
+          <t>['Ignacio Arganda‐Carreras', 'Verena Kaynig', 'Curtis Rueden', 'Kevin W. Eliceiri', 'Johannes Schindelin', 'Albert Cardona', 'H. Sebastian Seung']</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>['Xing Lin', 'Yair Rivenson', 'Nezih T. Yardimci', 'Muhammed Veli', 'Yi Luo', 'Mona Jarrahi', 'Aydogan Ozcan']</t>
+          <t>['Ignacio Arganda-Carreras', 'Verena Kaynig', 'Curtis Rueden', 'Kevin W Eliceiri', 'Johannes Schindelin', 'Albert Cardona', 'H Sebastian Seung']</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['California NanoSystems Institute (CNSI), University of California, Los Angeles, CA 90095, USA', 'Department of Bioengineering, University of California, Los Angeles, CA 90095, USA', 'Department of Electrical and Computer Engineering, University of California, Los Angeles, CA 90095, USA', 'California NanoSystems Institute (CNSI), University of California, Los Angeles, CA 90095, USA', 'Department of Bioengineering, University of California, Los Angeles, CA 90095, USA', 'Department of Electrical and Computer Engineering, University of California, Los Angeles, CA 90095, USA', 'California NanoSystems Institute (CNSI), University of California, Los Angeles, CA 90095, USA', 'Department of Electrical and Computer Engineering, University of California, Los Angeles, CA 90095, USA', 'California NanoSystems Institute (CNSI), University of California, Los Angeles, CA 90095, USA', 'Department of Bioengineering, University of California, Los Angeles, CA 90095, USA', 'Department of Electrical and Computer Engineering, University of California, Los Angeles, CA 90095, USA', 'California NanoSystems Institute (CNSI), University of California, Los Angeles, CA 90095, USA', 'Department of Bioengineering, University of California, Los Angeles, CA 90095, USA', 'Department of Electrical and Computer Engineering, University of California, Los Angeles, CA 90095, USA', 'California NanoSystems Institute (CNSI), University of California, Los Angeles, CA 90095, USA', 'Department of Electrical and Computer Engineering, University of California, Los Angeles, CA 90095, USA', 'California NanoSystems Institute (CNSI), University of California, Los Angeles, CA 90095, USA', 'Department of Bioengineering, University of California, Los Angeles, CA 90095, USA', 'Department of Electrical and Computer Engineering, University of California, Los Angeles, CA 90095, USA', 'Department of Surgery, David Geffen School of Medicine, University of California, Los Angeles, CA 90095, USA']</t>
+          <t>['Computer Science and Artificial Intelligence Department, Basque Country University, San Sebastian, Spain', 'Donostia International Physics Center, San Sebastian, Spain', 'Ikerbasque, Basque Foundation for Science, Bilbao, Spain', 'Harvard John A. Paulson School of Engineering and Applied Sciences, Harvard University, Cambridge, MA, USA', 'Laboratory for Optical and Computational Instrumentation, University of Wisconsin, Madison, WI, USA', 'Laboratory for Optical and Computational Instrumentation, University of Wisconsin, Madison, WI, USA', 'Laboratory for Optical and Computational Instrumentation, University of Wisconsin, Madison, WI, USA', 'Howard Hughes Medical Institute, Janelia Research Campus, Ashburn, VA, USA', 'Neuroscience Institute and Computer Science Department, Princeton University, NJ, USA']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Aydogan Ozcan (corresponding author), California NanoSystems Institute (CNSI), University of California, Los Angeles, CA 90095, USA; Department of Bioengineering, University of California, Los Angeles, CA 90095, USA; Department of Electrical and Computer Engineering, University of California, Los Angeles, CA 90095, USA; Department of Surgery, David Geffen School of Medicine, University of California, Los Angeles, CA 90095, USA</t>
+          <t>Ignacio Arganda-Carreras (corresponding author), Computer Science and Artificial Intelligence Department, Basque Country University, San Sebastian, Spain; Donostia International Physics Center, San Sebastian, Spain; Ikerbasque, Basque Foundation for Science, Bilbao, Spain</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>All-optical deep learning Deep learning uses multilayered artificial neural networks to learn digitally from large datasets. It then performs advanced identification and classification tasks. To date, these multilayered neural networks have been implemented on a computer. Lin et al. demonstrate all-optical machine learning that uses passive optical components that can be patterned and fabricated with 3D-printing. Their hardware approach comprises stacked layers of diffractive optical elements analogous to an artificial neural network that can be trained to execute complex functions at the speed of light. Science , this issue p. 1004</t>
+          <t>SUMMARY: State-of-the-art light and electron microscopes are capable of acquiring large image datasets, but quantitatively evaluating the data often involves manually annotating structures of interest. This process is time-consuming and often a major bottleneck in the evaluation pipeline. To overcome this problem, we have introduced the Trainable Weka Segmentation (TWS), a machine learning tool that leverages a limited number of manual annotations in order to train a classifier and segment the remaining data automatically. In addition, TWS can provide unsupervised segmentation learning schemes (clustering) and can be customized to employ user-designed image features or classifiers. AVAILABILITY AND IMPLEMENTATION: TWS is distributed as open-source software as part of the Fiji image processing distribution of ImageJ at http://imagej.net/Trainable_Weka_Segmentation . CONTACT: ignacio.arganda@ehu.eus. SUPPLEMENTARY INFORMATION: Supplementary data are available at Bioinformatics online.</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>33</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>['Computer science', 'Deep learning', 'Artificial intelligence', 'Artificial neural network', 'Feature (linguistics)', 'Lithography', 'Deep neural networks', 'Pattern recognition (psychology)', 'Computer architecture', 'Computer vision', 'Materials science', 'Optoelectronics']</t>
+          <t>['Computer science', 'Segmentation', 'Artificial intelligence', 'Pipeline (software)', 'Bottleneck', 'Cluster analysis', 'Classifier (UML)', 'Software', 'Pixel', 'Pattern recognition (psychology)', 'Image segmentation', 'Process (computing)', 'Machine learning', 'Data mining']</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>['US']</t>
+          <t>['ES', 'US']</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>['LeCun Y, 2015, NATURE', 'LeCun Y, 1998, PROCEEDINGS OF THE IEEE', 'Wang Z, 2004, IEEE TRANSACTIONS ON IMAGE PROCESSING', 'Srivastava N, 2014, ', 'Cho K, 2014, ', 'Silver D, 2016, NATURE', 'Litjens G, 2017, MEDICAL IMAGE ANALYSIS', 'Graves A, 2013, ', 'Yu N, 2014, NATURE MATERIALS', 'Sutton P, 1996, QUANTUM AND SEMICLASSICAL OPTICS JOURNAL OF THE EUROPEAN OPTICAL SOCIETY PART B', 'Cireşan D, 2012, ', 'Khorasaninejad M, 2016, SCIENCE', 'Shen Y, 2017, NATURE PHOTONICS', 'Kildishev A, 2013, SCIENCE', 'Chen Y, 2014, IEEE JOURNAL OF SELECTED TOPICS IN APPLIED EARTH OBSERVATIONS AND REMOTE SENSING', 'Jin K, 2017, IEEE TRANSACTIONS ON IMAGE PROCESSING', 'Grischkowsky D, 1990, JOURNAL OF THE OPTICAL SOCIETY OF AMERICA B', 'Kazhdan M, 2013, ACM TRANSACTIONS ON GRAPHICS', 'Hammernik K, 2017, MAGNETIC RESONANCE IN MEDICINE', 'Ranzato M, 2007, THE MIT PRESS EBOOKS', 'Rivenson Y, 2017, LIGHT SCIENCE &amp; APPLICATIONS', 'Brunner D, 2013, NATURE COMMUNICATIONS', 'Sinha A, 2017, OPTICA', 'Rivenson Y, 2017, OPTICA', 'Greenbaum A, 2012, NATURE METHODS', 'Kamilov U, 2015, OPTICA', 'Özcan A, 2016, ANNUAL REVIEW OF BIOMEDICAL ENGINEERING', 'Greenbaum A, 2014, SCIENCE TRANSLATIONAL MEDICINE', 'Psaltis D, 1990, NATURE', 'Riedhammer K, 2012, INTERNATIONAL CONFERENCE ON ACOUSTICS, SPEECH, AND SIGNAL PROCESSING', 'Reinert B, 2013, ACM TRANSACTIONS ON GRAPHICS', 'Shen Y, 2017, ', 'Marini A, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Rivenson Y, 2018, ACS PHOTONICS', 'Greenbaum A, 2013, SCIENTIFIC REPORTS', 'Emons M, 2012, OPTICAL MATERIALS EXPRESS', 'Bianchi V, 2017, NATURE COMMUNICATIONS', 'Shastri B, 2018, ', 'Hermans M, 2015, NATURE COMMUNICATIONS', 'Xiao Y, 2018, ACS PHOTONICS', 'Yin X, 2012, OPTICS EXPRESS', 'Wagner K, 2017, ', ', 1993, ', 'Cignoni P, 2008, ISTI OPEN PORTAL']</t>
+          <t>['Schindelin J, 2012, NATURE METHODS', 'Hall M, 2009, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Kamentsky L, 2011, BIOINFORMATICS', 'Marée R, 2016, BIOINFORMATICS', 'Dietz C, 2016, ADVANCES IN ANATOMY, EMBRYOLOGY AND CELL BIOLOGY', 'Vos W, 2016, ADVANCES IN ANATOMY, EMBRYOLOGY AND CELL BIOLOGY']</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -13198,12 +13206,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>Lin X, 2018, SCIENCE</t>
+          <t>Arganda‐Carreras I, 2017, BIOINFORMATICS</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>Lin X, 2018, SCIENCE</t>
+          <t>Arganda‐Carreras I, 2017, BIOINFORMATICS</t>
         </is>
       </c>
     </row>
@@ -13312,22 +13320,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2162651021</t>
+          <t>https://openalex.org/W2798701005</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>10.7551/mitpress/9780262170055.001.0001</t>
+          <t>10.1126/science.aat8084</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dataset Shift in Machine Learning</t>
+          <t>All-optical machine learning using diffractive deep neural networks</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -13337,60 +13345,80 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>1516</v>
+        <v>2423</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>THE MIT PRESS EBOOKS</t>
+          <t>SCIENCE</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>The MIT Press eBooks</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Xing Lin', 'Yair Rivenson', 'Nezih Tolga Yardimci', 'Muhammed Veli', 'Yi Luo', 'Mona Jarrahi', 'Aydogan Özcan']</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Xing Lin', 'Yair Rivenson', 'Nezih T. Yardimci', 'Muhammed Veli', 'Yi Luo', 'Mona Jarrahi', 'Aydogan Ozcan']</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr"/>
+          <t>['California NanoSystems Institute (CNSI), University of California, Los Angeles, CA 90095, USA', 'Department of Bioengineering, University of California, Los Angeles, CA 90095, USA', 'Department of Electrical and Computer Engineering, University of California, Los Angeles, CA 90095, USA', 'California NanoSystems Institute (CNSI), University of California, Los Angeles, CA 90095, USA', 'Department of Bioengineering, University of California, Los Angeles, CA 90095, USA', 'Department of Electrical and Computer Engineering, University of California, Los Angeles, CA 90095, USA', 'California NanoSystems Institute (CNSI), University of California, Los Angeles, CA 90095, USA', 'Department of Electrical and Computer Engineering, University of California, Los Angeles, CA 90095, USA', 'California NanoSystems Institute (CNSI), University of California, Los Angeles, CA 90095, USA', 'Department of Bioengineering, University of California, Los Angeles, CA 90095, USA', 'Department of Electrical and Computer Engineering, University of California, Los Angeles, CA 90095, USA', 'California NanoSystems Institute (CNSI), University of California, Los Angeles, CA 90095, USA', 'Department of Bioengineering, University of California, Los Angeles, CA 90095, USA', 'Department of Electrical and Computer Engineering, University of California, Los Angeles, CA 90095, USA', 'California NanoSystems Institute (CNSI), University of California, Los Angeles, CA 90095, USA', 'Department of Electrical and Computer Engineering, University of California, Los Angeles, CA 90095, USA', 'California NanoSystems Institute (CNSI), University of California, Los Angeles, CA 90095, USA', 'Department of Bioengineering, University of California, Los Angeles, CA 90095, USA', 'Department of Electrical and Computer Engineering, University of California, Los Angeles, CA 90095, USA', 'Department of Surgery, David Geffen School of Medicine, University of California, Los Angeles, CA 90095, USA']</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Aydogan Ozcan (corresponding author), California NanoSystems Institute (CNSI), University of California, Los Angeles, CA 90095, USA; Department of Bioengineering, University of California, Los Angeles, CA 90095, USA; Department of Electrical and Computer Engineering, University of California, Los Angeles, CA 90095, USA; Department of Surgery, David Geffen School of Medicine, University of California, Los Angeles, CA 90095, USA</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>An overview of recent efforts in the machine learning community to deal with dataset and covariate shift, which occurs when test and training inputs and outputs have different distributions. Dataset shift is a common problem in predictive modeling that occurs when the joint distribution of inputs and outputs differs between training and test stages. Covariate shift, a particular case of dataset shift, occurs when only the input distribution changes. Dataset shift is present in most practical applications, for reasons ranging from the bias introduced by experimental design to the irreproducibility of the testing conditions at training time. (An example is -email spam filtering, which may fail to recognize spam that differs in form from the spam the automatic filter has been built on.) Despite this, and despite the attention given to the apparently similar problems of semi-supervised learning and active learning, dataset shift has received relatively little attention in the machine learning community until recently. This volume offers an overview of current efforts to deal with dataset and covariate shift. The chapters offer a mathematical and philosophical introduction to the problem, place dataset shift in relationship to transfer learning, transduction, local learning, active learning, and semi-supervised learning, provide theoretical views of dataset and covariate shift (including decision theoretic and Bayesian perspectives), and present algorithms for covariate shift. Contributors Shai Ben-David, Steffen Bickel, Karsten Borgwardt, Michael Brückner, David Corfield, Amir Globerson, Arthur Gretton, Lars Kai Hansen, Matthias Hein, Jiayuan Huang, Choon Hui Teo, Takafumi Kanamori, Klaus-Robert Müller, Sam Roweis, Neil Rubens, Tobias Scheffer, Marcel Schmittfull, Bernhard Schölkopf Hidetoshi Shimodaira, Alex Smola, Amos Storkey, Masashi Sugiyama</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="inlineStr"/>
+          <t>All-optical deep learning Deep learning uses multilayered artificial neural networks to learn digitally from large datasets. It then performs advanced identification and classification tasks. To date, these multilayered neural networks have been implemented on a computer. Lin et al. demonstrate all-optical machine learning that uses passive optical components that can be patterned and fabricated with 3D-printing. Their hardware approach comprises stacked layers of diffractive optical elements analogous to an artificial neural network that can be trained to execute complex functions at the speed of light. Science , this issue p. 1004</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>6406</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>['Artificial intelligence', 'Machine learning', 'Covariate', 'Computer science', 'Bayesian probability', 'Paradigm shift', 'Filter (signal processing)']</t>
+          <t>['Computer science', 'Deep learning', 'Artificial intelligence', 'Artificial neural network', 'Feature (linguistics)', 'Lithography', 'Deep neural networks', 'Pattern recognition (psychology)', 'Computer architecture', 'Computer vision', 'Materials science', 'Optoelectronics']</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['US']</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>['Gordon A, 1984, BIOMETRICS', 'Rissanen J, 1978, AUTOMATICA', 'Platt J, 1998, THE MIT PRESS EBOOKS', 'Madden E, 1955, PHILOSOPHY AND PHENOMENOLOGICAL RESEARCH', 'Ruppert D, 1987, TECHNOMETRICS', 'Devroye L, 1996, STOCHASTIC MODELLING AND APPLIED PROBABILITY', 'Japkowicz N, 2002, INTELLIGENT DATA ANALYSIS', 'Heckman J, 1974, ECONOMETRICA', 'Elkan C, 2001, ', 'Dhanasekaran S, 2001, NATURE', 'Амари Ш, 1985, LECTURE NOTES IN STATISTICS', 'Shimodaira H, 2000, JOURNAL OF STATISTICAL PLANNING AND INFERENCE', 'Manski C, 1977, ECONOMETRICA', 'Akbani R, 2004, LECTURE NOTES IN COMPUTER SCIENCE', 'Vella F, 1998, THE JOURNAL OF HUMAN RESOURCES', 'Kimeldorf G, 1970, THE ANNALS OF MATHEMATICAL STATISTICS', 'Welsh J, 2001, PUBMED', 'Wells P, 2001, PHYSIOLOGICAL MEASUREMENT', 'Zadrozny B, 2004, ', 'Sugiyama M, 2007, ', 'Veropoulos K, 1999, ', 'LeCun Y, 1995, ', 'Manski C, 1989, THE JOURNAL OF HUMAN RESOURCES', 'Lee L, 1982, THE REVIEW OF ECONOMIC STUDIES', 'Zadrozny B, 2001, ', 'Ben-David S, 2003, LECTURE NOTES IN COMPUTER SCIENCE', 'Gilad-Bachrach R, 2004, ', 'Abe N, 1998, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Lowd D, 2005, CONFERENCE ON EMAIL AND ANTI-SPAM', 'Warnat P, 2005, BMC BIOINFORMATICS', 'Teo C, 2007, ', 'Wittel G, 2004, ', 'Dai Y, 2005, MATHEMATICAL PROGRAMMING', 'Gibbs M, 1997, ', 'Cohen S, 2005, EDINBURGH RESEARCH EXPLORER (UNIVERSITY OF EDINBURGH)', 'Steinwart I, 2002, JOURNAL OF COMPLEXITY', 'Basu A, 1994, ANNALS OF THE INSTITUTE OF STATISTICAL MATHEMATICS', 'Haussler D, 1997, THE ANNALS OF STATISTICS', 'Field C, 1994, INTERNATIONAL STATISTICAL REVIEW', 'Bonilla E, 2007, EDINBURGH RESEARCH EXPLORER (UNIVERSITY OF EDINBURGH)', 'Hein M, 2006, LECTURE NOTES IN COMPUTER SCIENCE', 'Shimodaira H, 2007, JOURNAL OF STATISTICAL PLANNING AND INFERENCE', 'Horowitz J, 2005, JOURNAL OF ECONOMETRICS', 'Sugiyama M, 2006, LECTURE NOTES IN COMPUTER SCIENCE', 'Kanamori T, 2003, JOURNAL OF STATISTICAL PLANNING AND INFERENCE', 'Lawrence N, 2005, LECTURE NOTES IN COMPUTER SCIENCE', 'Sugiyama M, 2005, LECTURE NOTES IN COMPUTER SCIENCE', 'Smith A, 2004, ', 'Warmuth M, 2003, MPG.PURE (MAX PLANCK SOCIETY)', 'Sugiyama M, 2003, ', 'Chawla N, 2002, JOURNAL OF ARTIFICIAL INTELLIGENCE RESEARCH', 'Heckman J, 1979, ECONOMETRICA', 'Wu Y, 1999, TECHNOMETRICS', 'Stone M, 1974, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Schölkopf B, 2001, NEURAL COMPUTATION', 'Jacobs R, 1991, NEURAL COMPUTATION', 'Zhu X, 2003, ', 'Ben-David S, 2007, THE MIT PRESS EBOOKS', 'Tsochantaridis I, 2005, MPG.PURE (MAX PLANCK SOCIETY)', 'Gretton A, 2007, THE MIT PRESS EBOOKS', 'Huang J, 2007, THE MIT PRESS EBOOKS', 'Shalev‐Shwartz S, 2010, MATHEMATICAL PROGRAMMING', 'Taskar B, 2003, ', 'Mackay D, 1992, NEURAL COMPUTATION', 'Weston J, 2000, ', 'Williams C, 1998, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Gruvberger S, 2001, PUBMED', 'Sugiyama M, 2007, ', 'Nedić A, 2001, SIAM JOURNAL ON OPTIMIZATION', 'Fine S, 2002, ', 'Xue Y, 2007, ', 'Zhu X, 2003, ', 'Pfeffermann D, 1998, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Fukumizu K, 2007, ', 'Lindsay B, 1994, THE ANNALS OF STATISTICS', 'Rasmussen C, 2001, ', 'Batu T, 2002, ', 'Watanabe S, 2001, NEURAL COMPUTATION', 'Tresp V, 2000, ', 'Mendelson S, 2003, LECTURE NOTES IN COMPUTER SCIENCE', 'Kim S, 2005, ', 'Sugiyama M, 2006, JOURNAL OF MACHINE LEARNING RESEARCH', 'Bousquet O, 2003, ', 'Teo C, 2007, ', 'Fukumizu K, 2000, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Sugiyama M, 2001, NEURAL COMPUTATION', 'Wiens D, 2000, JOURNAL OF STATISTICAL PLANNING AND INFERENCE', 'Graepel T, 2003, ', 'Bach F, 2007, THE MIT PRESS EBOOKS', 'Rosset S, 2004, ', 'Kanamori T, 2007, NEUROCOMPUTING', 'Sugiyama M, 2000, NEURAL COMPUTATION', 'Sugiyama M, 2004, NEURAL COMPUTATION', 'He T, 2006, IEEE TRANSACTIONS ON SIGNAL PROCESSING', 'Hansen L, 1999, ', 'Krupka E, 2005, ', 'Osuna E, 1997, DSPACE@MIT (MASSACHUSETTS INSTITUTE OF TECHNOLOGY)', 'Sung H, 2004, RICE DIGITAL SCHOLARSHIP ARCHIVE (RICE UNIVERSITY)', 'Sugiyama M, 2007, IEICE TRANSACTIONS ON FUNDAMENTALS OF ELECTRONICS COMMUNICATIONS AND COMPUTER SCIENCES', 'Lu Z, 2010, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES A (STATISTICS IN SOCIETY)', 'Yang Y, 1997, ', 'Hoeffding W, 1963, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Dehnad K, 1987, TECHNOMETRICS', 'Zhou D, 2003, MPG.PURE (MAX PLANCK SOCIETY)', 'Abe S, 2001, ', 'Rosenbaum P, 1983, BIOMETRIKA', ', 2000, CHOICE REVIEWS ONLINE', 'Schölkopf B, 2000, NEURAL COMPUTATION', 'Singh D, 2002, CANCER CELL', 'Herzberg A, 1972, BIOMETRIKA', 'Lunceford J, 2004, STATISTICS IN MEDICINE', 'Blitzer J, 2006, ', 'Drucker H, 1999, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'McDiarmid C, 1989, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'West M, 2001, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Dudley R, 2002, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Heckman J, 1990, AMERICAN ECONOMIC REVIEW', 'Dalvi N, 2004, ', 'Ziegel E, 1994, TECHNOMETRICS', 'Baxter J, 2000, ', 'Green P, 1984, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Skinner C, 1992, BIOMETRICS', 'Dubin J, 1989, SOCIOLOGICAL METHODS &amp; RESEARCH', 'Smola A, 2005, ', 'Mackay D, 1992, ', 'Bush R, 1956, THE AMERICAN JOURNAL OF PSYCHOLOGY', 'Dudı́k M, 2005, ', 'R.Black T, 2002, ', 'Jordan M, 2005, ', 'Chawla N, 2005, ', 'Sugiyama M, 2005, STATISTICS &amp; DECISIONS', 'Storkey A, 2007, THE MIT PRESS EBOOKS', 'Corfield D, 2003, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Schmidt M, 2002, ', 'KIFER D, 2004, ELSEVIER EBOOKS', 'Windham M, 1995, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Bickel S, 2007, THE MIT PRESS EBOOKS', 'Winship C, 1992, ANNUAL REVIEW OF SOCIOLOGY', 'Chapelle O, 2007, THE MIT PRESS EBOOKS', 'Bickel S, 2006, ', 'Sollich P, 1999, ', 'Sugiyama M, 2002, NEURAL NETWORKS', 'Leskovec J, 2003, ', 'Fukumizu K, 1995, ', 'Lawrence N, 2006, THE MIT PRESS EBOOKS', 'Rasmussen C, 2022, DIRECTORY OF OPEN ACCESS BOOKS (OAPEN FOUNDATION)', 'Bishop C, 1995, ', 'Grimshaw S, 1995, TECHNOMETRICS', 'Cohn D, 1996, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>['LeCun Y, 2015, NATURE', 'LeCun Y, 1998, PROCEEDINGS OF THE IEEE', 'Wang Z, 2004, IEEE TRANSACTIONS ON IMAGE PROCESSING', 'Srivastava N, 2014, ', 'Cho K, 2014, ', 'Silver D, 2016, NATURE', 'Litjens G, 2017, MEDICAL IMAGE ANALYSIS', 'Graves A, 2013, ', 'Yu N, 2014, NATURE MATERIALS', 'Sutton P, 1996, QUANTUM AND SEMICLASSICAL OPTICS JOURNAL OF THE EUROPEAN OPTICAL SOCIETY PART B', 'Cireşan D, 2012, ', 'Khorasaninejad M, 2016, SCIENCE', 'Shen Y, 2017, NATURE PHOTONICS', 'Kildishev A, 2013, SCIENCE', 'Chen Y, 2014, IEEE JOURNAL OF SELECTED TOPICS IN APPLIED EARTH OBSERVATIONS AND REMOTE SENSING', 'Jin K, 2017, IEEE TRANSACTIONS ON IMAGE PROCESSING', 'Grischkowsky D, 1990, JOURNAL OF THE OPTICAL SOCIETY OF AMERICA B', 'Kazhdan M, 2013, ACM TRANSACTIONS ON GRAPHICS', 'Hammernik K, 2017, MAGNETIC RESONANCE IN MEDICINE', 'Ranzato M, 2007, THE MIT PRESS EBOOKS', 'Rivenson Y, 2017, LIGHT SCIENCE &amp; APPLICATIONS', 'Brunner D, 2013, NATURE COMMUNICATIONS', 'Sinha A, 2017, OPTICA', 'Rivenson Y, 2017, OPTICA', 'Greenbaum A, 2012, NATURE METHODS', 'Kamilov U, 2015, OPTICA', 'Özcan A, 2016, ANNUAL REVIEW OF BIOMEDICAL ENGINEERING', 'Greenbaum A, 2014, SCIENCE TRANSLATIONAL MEDICINE', 'Psaltis D, 1990, NATURE', 'Riedhammer K, 2012, INTERNATIONAL CONFERENCE ON ACOUSTICS, SPEECH, AND SIGNAL PROCESSING', 'Reinert B, 2013, ACM TRANSACTIONS ON GRAPHICS', 'Shen Y, 2017, ', 'Marini A, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Rivenson Y, 2018, ACS PHOTONICS', 'Greenbaum A, 2013, SCIENTIFIC REPORTS', 'Emons M, 2012, OPTICAL MATERIALS EXPRESS', 'Bianchi V, 2017, NATURE COMMUNICATIONS', 'Shastri B, 2018, ', 'Hermans M, 2015, NATURE COMMUNICATIONS', 'Xiao Y, 2018, ACS PHOTONICS', 'Yin X, 2012, OPTICS EXPRESS', 'Wagner K, 2017, ', ', 1993, ', 'Cignoni P, 2008, ISTI OPEN PORTAL']</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -13406,34 +13434,34 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>NA, 2008, THE MIT PRESS EBOOKS</t>
+          <t>Lin X, 2018, SCIENCE</t>
         </is>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>NA, 2008, THE MIT PRESS EBOOKS</t>
+          <t>Lin X, 2018, SCIENCE</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2601810315</t>
+          <t>https://openalex.org/W2162651021</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>10.1093/bioinformatics/btx180</t>
+          <t>10.7551/mitpress/9780262170055.001.0001</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Trainable Weka Segmentation: a machine learning tool for microscopy pixel classification</t>
+          <t>Dataset Shift in Machine Learning</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -13443,80 +13471,60 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>book</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>2476</v>
+        <v>1516</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>BIOINFORMATICS</t>
+          <t>THE MIT PRESS EBOOKS</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Bioinformatics</t>
+          <t>The MIT Press eBooks</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>['Ignacio Arganda‐Carreras', 'Verena Kaynig', 'Curtis Rueden', 'Kevin W. Eliceiri', 'Johannes Schindelin', 'Albert Cardona', 'H. Sebastian Seung']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>['Ignacio Arganda-Carreras', 'Verena Kaynig', 'Curtis Rueden', 'Kevin W Eliceiri', 'Johannes Schindelin', 'Albert Cardona', 'H Sebastian Seung']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['Computer Science and Artificial Intelligence Department, Basque Country University, San Sebastian, Spain', 'Donostia International Physics Center, San Sebastian, Spain', 'Ikerbasque, Basque Foundation for Science, Bilbao, Spain', 'Harvard John A. Paulson School of Engineering and Applied Sciences, Harvard University, Cambridge, MA, USA', 'Laboratory for Optical and Computational Instrumentation, University of Wisconsin, Madison, WI, USA', 'Laboratory for Optical and Computational Instrumentation, University of Wisconsin, Madison, WI, USA', 'Laboratory for Optical and Computational Instrumentation, University of Wisconsin, Madison, WI, USA', 'Howard Hughes Medical Institute, Janelia Research Campus, Ashburn, VA, USA', 'Neuroscience Institute and Computer Science Department, Princeton University, NJ, USA']</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>Ignacio Arganda-Carreras (corresponding author), Computer Science and Artificial Intelligence Department, Basque Country University, San Sebastian, Spain; Donostia International Physics Center, San Sebastian, Spain; Ikerbasque, Basque Foundation for Science, Bilbao, Spain</t>
-        </is>
-      </c>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
-          <t>SUMMARY: State-of-the-art light and electron microscopes are capable of acquiring large image datasets, but quantitatively evaluating the data often involves manually annotating structures of interest. This process is time-consuming and often a major bottleneck in the evaluation pipeline. To overcome this problem, we have introduced the Trainable Weka Segmentation (TWS), a machine learning tool that leverages a limited number of manual annotations in order to train a classifier and segment the remaining data automatically. In addition, TWS can provide unsupervised segmentation learning schemes (clustering) and can be customized to employ user-designed image features or classifiers. AVAILABILITY AND IMPLEMENTATION: TWS is distributed as open-source software as part of the Fiji image processing distribution of ImageJ at http://imagej.net/Trainable_Weka_Segmentation . CONTACT: ignacio.arganda@ehu.eus. SUPPLEMENTARY INFORMATION: Supplementary data are available at Bioinformatics online.</t>
-        </is>
-      </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>2424</t>
-        </is>
-      </c>
-      <c r="R115" t="inlineStr">
-        <is>
-          <t>2426</t>
-        </is>
-      </c>
+          <t>An overview of recent efforts in the machine learning community to deal with dataset and covariate shift, which occurs when test and training inputs and outputs have different distributions. Dataset shift is a common problem in predictive modeling that occurs when the joint distribution of inputs and outputs differs between training and test stages. Covariate shift, a particular case of dataset shift, occurs when only the input distribution changes. Dataset shift is present in most practical applications, for reasons ranging from the bias introduced by experimental design to the irreproducibility of the testing conditions at training time. (An example is -email spam filtering, which may fail to recognize spam that differs in form from the spam the automatic filter has been built on.) Despite this, and despite the attention given to the apparently similar problems of semi-supervised learning and active learning, dataset shift has received relatively little attention in the machine learning community until recently. This volume offers an overview of current efforts to deal with dataset and covariate shift. The chapters offer a mathematical and philosophical introduction to the problem, place dataset shift in relationship to transfer learning, transduction, local learning, active learning, and semi-supervised learning, provide theoretical views of dataset and covariate shift (including decision theoretic and Bayesian perspectives), and present algorithms for covariate shift. Contributors Shai Ben-David, Steffen Bickel, Karsten Borgwardt, Michael Brückner, David Corfield, Amir Globerson, Arthur Gretton, Lars Kai Hansen, Matthias Hein, Jiayuan Huang, Choon Hui Teo, Takafumi Kanamori, Klaus-Robert Müller, Sam Roweis, Neil Rubens, Tobias Scheffer, Marcel Schmittfull, Bernhard Schölkopf Hidetoshi Shimodaira, Alex Smola, Amos Storkey, Masashi Sugiyama</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
-          <t>['Computer science', 'Segmentation', 'Artificial intelligence', 'Pipeline (software)', 'Bottleneck', 'Cluster analysis', 'Classifier (UML)', 'Software', 'Pixel', 'Pattern recognition (psychology)', 'Image segmentation', 'Process (computing)', 'Machine learning', 'Data mining']</t>
+          <t>['Artificial intelligence', 'Machine learning', 'Covariate', 'Computer science', 'Bayesian probability', 'Paradigm shift', 'Filter (signal processing)']</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>['ES', 'US']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>['Schindelin J, 2012, NATURE METHODS', 'Hall M, 2009, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Kamentsky L, 2011, BIOINFORMATICS', 'Marée R, 2016, BIOINFORMATICS', 'Dietz C, 2016, ADVANCES IN ANATOMY, EMBRYOLOGY AND CELL BIOLOGY', 'Vos W, 2016, ADVANCES IN ANATOMY, EMBRYOLOGY AND CELL BIOLOGY']</t>
+          <t>['Gordon A, 1984, BIOMETRICS', 'Rissanen J, 1978, AUTOMATICA', 'Platt J, 1998, THE MIT PRESS EBOOKS', 'Madden E, 1955, PHILOSOPHY AND PHENOMENOLOGICAL RESEARCH', 'Ruppert D, 1987, TECHNOMETRICS', 'Devroye L, 1996, STOCHASTIC MODELLING AND APPLIED PROBABILITY', 'Japkowicz N, 2002, INTELLIGENT DATA ANALYSIS', 'Heckman J, 1974, ECONOMETRICA', 'Elkan C, 2001, ', 'Dhanasekaran S, 2001, NATURE', 'Амари Ш, 1985, LECTURE NOTES IN STATISTICS', 'Shimodaira H, 2000, JOURNAL OF STATISTICAL PLANNING AND INFERENCE', 'Manski C, 1977, ECONOMETRICA', 'Akbani R, 2004, LECTURE NOTES IN COMPUTER SCIENCE', 'Vella F, 1998, THE JOURNAL OF HUMAN RESOURCES', 'Kimeldorf G, 1970, THE ANNALS OF MATHEMATICAL STATISTICS', 'Welsh J, 2001, PUBMED', 'Wells P, 2001, PHYSIOLOGICAL MEASUREMENT', 'Zadrozny B, 2004, ', 'Sugiyama M, 2007, ', 'Veropoulos K, 1999, ', 'LeCun Y, 1995, ', 'Manski C, 1989, THE JOURNAL OF HUMAN RESOURCES', 'Lee L, 1982, THE REVIEW OF ECONOMIC STUDIES', 'Zadrozny B, 2001, ', 'Ben-David S, 2003, LECTURE NOTES IN COMPUTER SCIENCE', 'Gilad-Bachrach R, 2004, ', 'Abe N, 1998, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Lowd D, 2005, CONFERENCE ON EMAIL AND ANTI-SPAM', 'Warnat P, 2005, BMC BIOINFORMATICS', 'Teo C, 2007, ', 'Wittel G, 2004, ', 'Dai Y, 2005, MATHEMATICAL PROGRAMMING', 'Gibbs M, 1997, ', 'Cohen S, 2005, EDINBURGH RESEARCH EXPLORER (UNIVERSITY OF EDINBURGH)', 'Steinwart I, 2002, JOURNAL OF COMPLEXITY', 'Basu A, 1994, ANNALS OF THE INSTITUTE OF STATISTICAL MATHEMATICS', 'Haussler D, 1997, THE ANNALS OF STATISTICS', 'Field C, 1994, INTERNATIONAL STATISTICAL REVIEW', 'Bonilla E, 2007, EDINBURGH RESEARCH EXPLORER (UNIVERSITY OF EDINBURGH)', 'Hein M, 2006, LECTURE NOTES IN COMPUTER SCIENCE', 'Shimodaira H, 2007, JOURNAL OF STATISTICAL PLANNING AND INFERENCE', 'Horowitz J, 2005, JOURNAL OF ECONOMETRICS', 'Sugiyama M, 2006, LECTURE NOTES IN COMPUTER SCIENCE', 'Kanamori T, 2003, JOURNAL OF STATISTICAL PLANNING AND INFERENCE', 'Lawrence N, 2005, LECTURE NOTES IN COMPUTER SCIENCE', 'Sugiyama M, 2005, LECTURE NOTES IN COMPUTER SCIENCE', 'Smith A, 2004, ', 'Warmuth M, 2003, MPG.PURE (MAX PLANCK SOCIETY)', 'Sugiyama M, 2003, ', 'Chawla N, 2002, JOURNAL OF ARTIFICIAL INTELLIGENCE RESEARCH', 'Heckman J, 1979, ECONOMETRICA', 'Wu Y, 1999, TECHNOMETRICS', 'Stone M, 1974, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Schölkopf B, 2001, NEURAL COMPUTATION', 'Jacobs R, 1991, NEURAL COMPUTATION', 'Zhu X, 2003, ', 'Ben-David S, 2007, THE MIT PRESS EBOOKS', 'Tsochantaridis I, 2005, MPG.PURE (MAX PLANCK SOCIETY)', 'Gretton A, 2007, THE MIT PRESS EBOOKS', 'Huang J, 2007, THE MIT PRESS EBOOKS', 'Shalev‐Shwartz S, 2010, MATHEMATICAL PROGRAMMING', 'Taskar B, 2003, ', 'Mackay D, 1992, NEURAL COMPUTATION', 'Weston J, 2000, ', 'Williams C, 1998, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Gruvberger S, 2001, PUBMED', 'Sugiyama M, 2007, ', 'Nedić A, 2001, SIAM JOURNAL ON OPTIMIZATION', 'Fine S, 2002, ', 'Xue Y, 2007, ', 'Zhu X, 2003, ', 'Pfeffermann D, 1998, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Fukumizu K, 2007, ', 'Lindsay B, 1994, THE ANNALS OF STATISTICS', 'Rasmussen C, 2001, ', 'Batu T, 2002, ', 'Watanabe S, 2001, NEURAL COMPUTATION', 'Tresp V, 2000, ', 'Mendelson S, 2003, LECTURE NOTES IN COMPUTER SCIENCE', 'Kim S, 2005, ', 'Sugiyama M, 2006, JOURNAL OF MACHINE LEARNING RESEARCH', 'Bousquet O, 2003, ', 'Teo C, 2007, ', 'Fukumizu K, 2000, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Sugiyama M, 2001, NEURAL COMPUTATION', 'Wiens D, 2000, JOURNAL OF STATISTICAL PLANNING AND INFERENCE', 'Graepel T, 2003, ', 'Bach F, 2007, THE MIT PRESS EBOOKS', 'Rosset S, 2004, ', 'Kanamori T, 2007, NEUROCOMPUTING', 'Sugiyama M, 2000, NEURAL COMPUTATION', 'Sugiyama M, 2004, NEURAL COMPUTATION', 'He T, 2006, IEEE TRANSACTIONS ON SIGNAL PROCESSING', 'Hansen L, 1999, ', 'Krupka E, 2005, ', 'Osuna E, 1997, DSPACE@MIT (MASSACHUSETTS INSTITUTE OF TECHNOLOGY)', 'Sung H, 2004, RICE DIGITAL SCHOLARSHIP ARCHIVE (RICE UNIVERSITY)', 'Sugiyama M, 2007, IEICE TRANSACTIONS ON FUNDAMENTALS OF ELECTRONICS COMMUNICATIONS AND COMPUTER SCIENCES', 'Lu Z, 2010, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES A (STATISTICS IN SOCIETY)', 'Yang Y, 1997, ', 'Hoeffding W, 1963, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Dehnad K, 1987, TECHNOMETRICS', 'Zhou D, 2003, MPG.PURE (MAX PLANCK SOCIETY)', 'Abe S, 2001, ', 'Rosenbaum P, 1983, BIOMETRIKA', ', 2000, CHOICE REVIEWS ONLINE', 'Schölkopf B, 2000, NEURAL COMPUTATION', 'Singh D, 2002, CANCER CELL', 'Herzberg A, 1972, BIOMETRIKA', 'Lunceford J, 2004, STATISTICS IN MEDICINE', 'Blitzer J, 2006, ', 'Drucker H, 1999, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'McDiarmid C, 1989, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'West M, 2001, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Dudley R, 2002, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Heckman J, 1990, AMERICAN ECONOMIC REVIEW', 'Dalvi N, 2004, ', 'Ziegel E, 1994, TECHNOMETRICS', 'Baxter J, 2000, ', 'Green P, 1984, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Skinner C, 1992, BIOMETRICS', 'Dubin J, 1989, SOCIOLOGICAL METHODS &amp; RESEARCH', 'Smola A, 2005, ', 'Mackay D, 1992, ', 'Bush R, 1956, THE AMERICAN JOURNAL OF PSYCHOLOGY', 'Dudı́k M, 2005, ', 'R.Black T, 2002, ', 'Jordan M, 2005, ', 'Chawla N, 2005, ', 'Sugiyama M, 2005, STATISTICS &amp; DECISIONS', 'Storkey A, 2007, THE MIT PRESS EBOOKS', 'Corfield D, 2003, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Schmidt M, 2002, ', 'KIFER D, 2004, ELSEVIER EBOOKS', 'Windham M, 1995, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Bickel S, 2007, THE MIT PRESS EBOOKS', 'Winship C, 1992, ANNUAL REVIEW OF SOCIOLOGY', 'Chapelle O, 2007, THE MIT PRESS EBOOKS', 'Bickel S, 2006, ', 'Sollich P, 1999, ', 'Sugiyama M, 2002, NEURAL NETWORKS', 'Leskovec J, 2003, ', 'Fukumizu K, 1995, ', 'Lawrence N, 2006, THE MIT PRESS EBOOKS', 'Rasmussen C, 2022, DIRECTORY OF OPEN ACCESS BOOKS (OAPEN FOUNDATION)', 'Bishop C, 1995, ', 'Grimshaw S, 1995, TECHNOMETRICS', 'Cohn D, 1996, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
@@ -13532,12 +13540,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>Arganda‐Carreras I, 2017, BIOINFORMATICS</t>
+          <t>NA, 2008, THE MIT PRESS EBOOKS</t>
         </is>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>Arganda‐Carreras I, 2017, BIOINFORMATICS</t>
+          <t>NA, 2008, THE MIT PRESS EBOOKS</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13581,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
@@ -13610,7 +13618,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>['Vapnik V, 1995, ', '1959- B, 1994, CHOICE REVIEWS ONLINE', 'Ho T, 1998, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Ripley B, 1996, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Neal R, 1996, LECTURE NOTES IN STATISTICS', 'Mackay D, 1992, NEURAL COMPUTATION', 'Møller M, 1993, NEURAL NETWORKS', 'Krogh A, 1994, ', 'Krogh A, 1991, ', 'Liu Y, 1999, NEURAL NETWORKS', 'Wang S, 2009, ', 'Minku L, 2009, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Brown G, 2005, ', 'Islam M, 2003, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Gestel T, 2002, NEURAL COMPUTATION', 'Liu Y, 1999, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS PART B (CYBERNETICS)', 'Chandra A, 2006, JOURNAL OF MATHEMATICAL MODELLING AND ALGORITHMS', 'Chen H, 2009, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Jin Y, 2004, ', 'Wang S, 2009, ', 'Chen H, 2012, ']</t>
+          <t>['Vapnik V, 1995, ', '1959- B, 1994, CHOICE REVIEWS ONLINE', 'Ho T, 1998, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Ripley B, 1996, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Mackay D, 1992, NEURAL COMPUTATION', 'Neal R, 1996, LECTURE NOTES IN STATISTICS', 'Møller M, 1993, NEURAL NETWORKS', 'Krogh A, 1994, ', 'Krogh A, 1991, ', 'Liu Y, 1999, NEURAL NETWORKS', 'Wang S, 2009, ', 'Minku L, 2009, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Brown G, 2005, ', 'Islam M, 2003, IEEE TRANSACTIONS ON NEURAL NETWORKS', 'Gestel T, 2002, NEURAL COMPUTATION', 'Liu Y, 1999, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS PART B (CYBERNETICS)', 'Chandra A, 2006, JOURNAL OF MATHEMATICAL MODELLING AND ALGORITHMS', 'Chen H, 2009, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Jin Y, 2004, ', 'Wang S, 2009, ', 'Chen H, 2012, ']</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -13667,7 +13675,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -13794,7 +13802,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -14014,7 +14022,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -14142,17 +14150,17 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
-          <t>['Hofmann, T.', 'Schölkopf, B.', 'Smola, A.']</t>
+          <t>['Thomas Hofmann', 'Bernhard Schölkopf', 'Alexander J. Smola']</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>['Hofmann, T.', 'Schölkopf, B.', 'Smola, A.']</t>
+          <t>['Thomas Hofmann', 'Bernhard Schölkopf', 'Alexander J. Smola']</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>['Department Empirical Inference, Max Planck Institute for Biological Cybernetics, Max Planck Society', 'Max Planck Institute for Biological Cybernetics, Max Planck Society', 'Darmstadt University of Technology, Max Planck Institute for Biological Cybernetics and National ICT Australia', 'Department Empirical Inference, Max Planck Institute for Biological Cybernetics, Max Planck Society', 'Max Planck Institute for Biological Cybernetics, Max Planck Society', 'DARMSTADT UNIVERSITY OF TECHNOLOGY DEPARTMENT OF COMPUTER SCIENCE DARMSTADT GERMANY', 'Darmstadt University of Technology, Max Planck Institute for Biological Cybernetics and National ICT Australia', 'MAX PLANCK INSTITUTE FOR BIOLOGICAL CYBERNETICS TÜBINGEN GERMANY']</t>
+          <t>['Darmstadt University of Technology, Max Planck Institute for Biological Cybernetics and National ICT Australia', 'DARMSTADT UNIVERSITY OF TECHNOLOGY DEPARTMENT OF COMPUTER SCIENCE DARMSTADT GERMANY', 'MAX PLANCK INSTITUTE FOR BIOLOGICAL CYBERNETICS TÜBINGEN GERMANY', 'Darmstadt University of Technology, Max Planck Institute for Biological Cybernetics and National ICT Australia']</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -14234,7 +14242,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>2144</v>
+        <v>2147</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -14327,22 +14335,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2701059868</t>
+          <t>https://openalex.org/W2792946961</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>10.1109/sp.2017.12</t>
+          <t>10.1103/physrevlett.122.040504</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SecureML: A System for Scalable Privacy-Preserving Machine Learning</t>
+          <t>Quantum Machine Learning in Feature Hilbert Spaces</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -14356,56 +14364,72 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1846</v>
-      </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+        <v>1649</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>PHYSICAL REVIEW LETTERS</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Physical Review Letters</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>['Payman Mohassel', 'Yupeng Zhang']</t>
+          <t>['Maria Schuld', 'Nathan Killoran']</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>['Payman Mohassel', 'Yupeng Zhang']</t>
+          <t>['Maria Schuld', 'Nathan Killoran']</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['Visa Research', 'University of Maryland']</t>
+          <t>['Xanadu, 372 Richmond Street West, Toronto M5V 2L7, Canada', 'Xanadu, 372 Richmond Street West, Toronto M5V 2L7, Canada']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Machine learning is widely used in practice to produce predictive models for applications such as image processing, speech and text recognition. These models are more accurate when trained on large amount of data collected from different sources. However, the massive data collection raises privacy concerns. In this paper, we present new and efficient protocols for privacy preserving machine learning for linear regression, logistic regression and neural network training using the stochastic gradient descent method. Our protocols fall in the two-server model where data owners distribute their private data among two non-colluding servers who train various models on the joint data using secure two-party computation (2PC). We develop new techniques to support secure arithmetic operations on shared decimal numbers, and propose MPC-friendly alternatives to non-linear functions such as sigmoid and softmax that are superior to prior work. We implement our system in C++. Our experiments validate that our protocols are several orders of magnitude faster than the state of the art implementations for privacy preserving linear and logistic regressions, and scale to millions of data samples with thousands of features. We also implement the first privacy preserving system for training neural networks.</t>
-        </is>
-      </c>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
+          <t>A basic idea of quantum computing is surprisingly similar to that of kernel methods in machine learning, namely, to efficiently perform computations in an intractably large Hilbert space. In this Letter we explore some theoretical foundations of this link and show how it opens up a new avenue for the design of quantum machine learning algorithms. We interpret the process of encoding inputs in a quantum state as a nonlinear feature map that maps data to quantum Hilbert space. A quantum computer can now analyze the input data in this feature space. Based on this link, we discuss two approaches for building a quantum model for classification. In the first approach, the quantum device estimates inner products of quantum states to compute a classically intractable kernel. The kernel can be fed into any classical kernel method such as a support vector machine. In the second approach, we use a variational quantum circuit as a linear model that classifies data explicitly in Hilbert space. We illustrate these ideas with a feature map based on squeezing in a continuous-variable system, and visualize the working principle with two-dimensional minibenchmark datasets.</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>040504</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>040504</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>['Computer science', 'Softmax function', 'Scalability', 'Server', 'Machine learning', 'Artificial neural network', 'Information privacy', 'Artificial intelligence', 'Stochastic gradient descent', 'MNIST database', 'Implementation', 'Data mining', 'Computer security', 'Computer network', 'Database']</t>
+          <t>['Hilbert space', 'Kernel (algebra)', 'Computer science', 'Quantum computer', 'Reproducing kernel Hilbert space', 'Quantum machine learning', 'Quantum state', 'Feature vector', 'Kernel method', 'Feature (linguistics)', 'Quantum algorithm', 'Quantum information', 'POVM', 'Support vector machine', 'Quantum process', 'Algorithm', 'Quantum', 'Theoretical computer science', 'Artificial intelligence', 'Quantum operation', 'Open quantum system', 'Mathematics', 'Quantum mechanics', 'Physics', 'Quantum dynamics', 'Pure mathematics']</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>['GB', 'US']</t>
+          <t>['CA']</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>['Lu Z, 2010, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES A (STATISTICS IN SOCIETY)', 'Paillier P, 2007, LECTURE NOTES IN COMPUTER SCIENCE', 'Abadi M, 2016, ', 'Canetti R, 2001, ', 'Yao A, 1982, ', 'Shokri R, 2015, ', 'Agrawal R, 2000, ', 'Dowlin N, 2016, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Lindell Y, 2000, LECTURE NOTES IN COMPUTER SCIENCE', 'Demmler D, 2015, ', 'Malkhi D, 2004, ', 'Kolesnikov V, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Ishai Y, 2003, LECTURE NOTES IN COMPUTER SCIENCE', 'Peikert C, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Lindell Y, 2008, JOURNAL OF CRYPTOLOGY', 'Guyon I, 2004, EPRINTS SOTON (UNIVERSITY OF SOUTHAMPTON)', 'Bellare M, 2012, ', 'Song S, 2013, ', 'Chaudhuri K, 2008, ', 'Nikolaenko V, 2013, ', 'Jagannathan G, 2005, ', 'Du W, 2004, ', 'Asharov G, 2013, ', 'Bellare M, 2013, ', 'Nikolaenko V, 2013, ', 'Damgård I, 2008, INTERNATIONAL JOURNAL OF APPLIED CRYPTOGRAPHY', 'Bunn P, 2007, ', 'Livni R, 2014, ', 'Yu H, 2006, LECTURE NOTES IN COMPUTER SCIENCE', 'Aono Y, 2016, ', 'Vaidya J, 2007, KNOWLEDGE AND INFORMATION SYSTEMS', 'Sanil A, 2004, ', 'Nayak K, 2015, ', 'Du W, 2005, ', 'Slavković A, 2007, ', 'Wu S, 2013, 人工知能学会全国大会論文集', 'Kamara S, 2011, IACR CRYPTOLOGY EPRINT ARCHIVE', 'Gascón A, 2016, IACR CRYPTOLOGY EPRINT ARCHIVE', 'Gilad-Bachrach R, 2016, ', 'Wang X, 2016, IACR CRYPTOLOGY EPRINT ARCHIVE']</t>
+          <t>['Preskill J, 2018, QUANTUM', 'Aronszajn N, 1950, TRANSACTIONS OF THE AMERICAN MATHEMATICAL SOCIETY', 'Williams C, 2003, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Braunstein S, 2005, REVIEWS OF MODERN PHYSICS', 'Weedbrook C, 2012, REVIEWS OF MODERN PHYSICS', 'McClean J, 2016, NEW JOURNAL OF PHYSICS', 'Mercer J, 1909, PHILOSOPHICAL TRANSACTIONS OF THE ROYAL SOCIETY OF LONDON SERIES A CONTAINING PAPERS OF A MATHEMATICAL OR PHYSICAL CHARACTER', 'Rebentrost P, 2014, PHYSICAL REVIEW LETTERS', 'Berlinet A, 2004, ', 'Hofmann T, 2008, THE ANNALS OF STATISTICS', 'Gottesman D, 2001, PHYSICAL REVIEW A', 'Hofmann T, 2008, ', 'Barnett S, 2002, ', 'Klauder J, 1985, WORLD SCIENTIFIC EBOOKS', 'Wiebe N, 2012, PHYSICAL REVIEW LETTERS', 'Bremner M, 2016, PHYSICAL REVIEW LETTERS', 'L. B, 2003, ', 'Schuld M, 2016, PHYSICAL REVIEW. A/PHYSICAL REVIEW, A', 'Wan K, 2017, NPJ QUANTUM INFORMATION', ', 2006, ', 'Schuld M, 2017, EUROPHYSICS LETTERS (EPL)', 'Madrid R, 2005, EUROPEAN JOURNAL OF PHYSICS', 'Bartlett S, 2002, PHYSICAL REVIEW A', 'Amin M, 2015, PHYSICAL REVIEW A', ', 2005, ', 'Benedetti M, 2017, PHYSICAL REVIEW X', 'Low G, 2014, PHYSICAL REVIEW A', 'O’Gorman B, 2015, THE EUROPEAN PHYSICAL JOURNAL SPECIAL TOPICS', 'Douce T, 2017, PHYSICAL REVIEW LETTERS', 'Kivinen J, 2002, LECTURE NOTES IN COMPUTER SCIENCE', 'Flamini F, 2017, SCIENTIFIC REPORTS', 'Wittek P, 2017, SCIENTIFIC REPORTS', 'Wang S, 2015, JOURNAL OF MATHEMATICS RESEARCH', 'Langford J, 2012, ARXIV (CORNELL UNIVERSITY)', 'Chatterjee R, 2017, QUANTUM INFORMATION AND COMPUTATION']</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
@@ -14421,34 +14445,34 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mohassel P, 2017, </t>
+          <t>Schuld M, 2019, PHYSICAL REVIEW LETTERS</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mohassel P, 2017, </t>
+          <t>Schuld M, 2019, PHYSICAL REVIEW LETTERS</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2792946961</t>
+          <t>https://openalex.org/W2701059868</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>10.1103/physrevlett.122.040504</t>
+          <t>10.1109/sp.2017.12</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Quantum Machine Learning in Feature Hilbert Spaces</t>
+          <t>SecureML: A System for Scalable Privacy-Preserving Machine Learning</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -14462,72 +14486,56 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1643</v>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>PHYSICAL REVIEW LETTERS</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>Physical Review Letters</t>
-        </is>
-      </c>
+        <v>1847</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
-          <t>['Maria Schuld', 'Nathan Killoran']</t>
+          <t>['Payman Mohassel', 'Yupeng Zhang']</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>['Maria Schuld', 'Nathan Killoran']</t>
+          <t>['Payman Mohassel', 'Yupeng Zhang']</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['Xanadu, 372 Richmond Street West, Toronto M5V 2L7, Canada', 'Xanadu, 372 Richmond Street West, Toronto M5V 2L7, Canada']</t>
+          <t>['Visa Research', 'University of Maryland']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
-          <t>A basic idea of quantum computing is surprisingly similar to that of kernel methods in machine learning, namely, to efficiently perform computations in an intractably large Hilbert space. In this Letter we explore some theoretical foundations of this link and show how it opens up a new avenue for the design of quantum machine learning algorithms. We interpret the process of encoding inputs in a quantum state as a nonlinear feature map that maps data to quantum Hilbert space. A quantum computer can now analyze the input data in this feature space. Based on this link, we discuss two approaches for building a quantum model for classification. In the first approach, the quantum device estimates inner products of quantum states to compute a classically intractable kernel. The kernel can be fed into any classical kernel method such as a support vector machine. In the second approach, we use a variational quantum circuit as a linear model that classifies data explicitly in Hilbert space. We illustrate these ideas with a feature map based on squeezing in a continuous-variable system, and visualize the working principle with two-dimensional minibenchmark datasets.</t>
-        </is>
-      </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Machine learning is widely used in practice to produce predictive models for applications such as image processing, speech and text recognition. These models are more accurate when trained on large amount of data collected from different sources. However, the massive data collection raises privacy concerns. In this paper, we present new and efficient protocols for privacy preserving machine learning for linear regression, logistic regression and neural network training using the stochastic gradient descent method. Our protocols fall in the two-server model where data owners distribute their private data among two non-colluding servers who train various models on the joint data using secure two-party computation (2PC). We develop new techniques to support secure arithmetic operations on shared decimal numbers, and propose MPC-friendly alternatives to non-linear functions such as sigmoid and softmax that are superior to prior work. We implement our system in C++. Our experiments validate that our protocols are several orders of magnitude faster than the state of the art implementations for privacy preserving linear and logistic regressions, and scale to millions of data samples with thousands of features. We also implement the first privacy preserving system for training neural networks.</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>040504</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>040504</t>
+          <t>38</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>['Hilbert space', 'Kernel (algebra)', 'Computer science', 'Quantum computer', 'Reproducing kernel Hilbert space', 'Quantum machine learning', 'Quantum state', 'Feature vector', 'Kernel method', 'Feature (linguistics)', 'Quantum algorithm', 'Quantum information', 'POVM', 'Support vector machine', 'Quantum process', 'Algorithm', 'Quantum', 'Theoretical computer science', 'Artificial intelligence', 'Quantum operation', 'Open quantum system', 'Mathematics', 'Quantum mechanics', 'Physics', 'Quantum dynamics', 'Pure mathematics']</t>
+          <t>['Computer science', 'Softmax function', 'Scalability', 'Server', 'Machine learning', 'Artificial neural network', 'Information privacy', 'Artificial intelligence', 'Stochastic gradient descent', 'MNIST database', 'Implementation', 'Data mining', 'Computer security', 'Computer network', 'Database']</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>['CA']</t>
+          <t>['GB', 'US']</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>['Preskill J, 2018, QUANTUM', 'Aronszajn N, 1950, TRANSACTIONS OF THE AMERICAN MATHEMATICAL SOCIETY', 'Williams C, 2003, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Braunstein S, 2005, REVIEWS OF MODERN PHYSICS', 'Weedbrook C, 2012, REVIEWS OF MODERN PHYSICS', 'McClean J, 2016, NEW JOURNAL OF PHYSICS', 'Mercer J, 1909, PHILOSOPHICAL TRANSACTIONS OF THE ROYAL SOCIETY OF LONDON SERIES A CONTAINING PAPERS OF A MATHEMATICAL OR PHYSICAL CHARACTER', 'Rebentrost P, 2014, PHYSICAL REVIEW LETTERS', 'Berlinet A, 2004, ', 'Hofmann T, 2008, THE ANNALS OF STATISTICS', 'Gottesman D, 2001, PHYSICAL REVIEW A', 'T. H, 2008, ', 'Barnett S, 2002, ', 'Klauder J, 1985, WORLD SCIENTIFIC EBOOKS', 'Wiebe N, 2012, PHYSICAL REVIEW LETTERS', 'Bremner M, 2016, PHYSICAL REVIEW LETTERS', 'L. B, 2003, ', 'Schuld M, 2016, PHYSICAL REVIEW. A/PHYSICAL REVIEW, A', 'Wan K, 2017, NPJ QUANTUM INFORMATION', ', 2006, ', 'Schuld M, 2017, EUROPHYSICS LETTERS (EPL)', 'Madrid R, 2005, EUROPEAN JOURNAL OF PHYSICS', 'Bartlett S, 2002, PHYSICAL REVIEW A', 'Amin M, 2015, PHYSICAL REVIEW A', ', 2005, ', 'Benedetti M, 2017, PHYSICAL REVIEW X', 'Low G, 2014, PHYSICAL REVIEW A', 'O’Gorman B, 2015, THE EUROPEAN PHYSICAL JOURNAL SPECIAL TOPICS', 'Douce T, 2017, PHYSICAL REVIEW LETTERS', 'Kivinen J, 2002, LECTURE NOTES IN COMPUTER SCIENCE', 'Flamini F, 2017, SCIENTIFIC REPORTS', 'Wittek P, 2017, SCIENTIFIC REPORTS', 'Wang S, 2015, JOURNAL OF MATHEMATICS RESEARCH', 'Langford J, 2012, ARXIV (CORNELL UNIVERSITY)', 'Chatterjee R, 2017, QUANTUM INFORMATION AND COMPUTATION']</t>
+          <t>['Lu Z, 2010, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES A (STATISTICS IN SOCIETY)', 'Paillier P, 2007, LECTURE NOTES IN COMPUTER SCIENCE', 'Abadi M, 2016, ', 'Canetti R, 2001, ', 'Yao A, 1982, ', 'Shokri R, 2015, ', 'Agrawal R, 2000, ', 'Dowlin N, 2016, INTERNATIONAL CONFERENCE ON MACHINE LEARNING', 'Lindell Y, 2000, LECTURE NOTES IN COMPUTER SCIENCE', 'Demmler D, 2015, ', 'Malkhi D, 2004, ', 'Kolesnikov V, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Ishai Y, 2003, LECTURE NOTES IN COMPUTER SCIENCE', 'Peikert C, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Lindell Y, 2008, JOURNAL OF CRYPTOLOGY', 'Guyon I, 2004, EPRINTS SOTON (UNIVERSITY OF SOUTHAMPTON)', 'Bellare M, 2012, ', 'Song S, 2013, ', 'Chaudhuri K, 2008, ', 'Nikolaenko V, 2013, ', 'Jagannathan G, 2005, ', 'Du W, 2004, ', 'Asharov G, 2013, ', 'Bellare M, 2013, ', 'Nikolaenko V, 2013, ', 'Damgård I, 2008, INTERNATIONAL JOURNAL OF APPLIED CRYPTOGRAPHY', 'Bunn P, 2007, ', 'Livni R, 2014, ', 'Yu H, 2006, LECTURE NOTES IN COMPUTER SCIENCE', 'Aono Y, 2016, ', 'Vaidya J, 2007, KNOWLEDGE AND INFORMATION SYSTEMS', 'Sanil A, 2004, ', 'Nayak K, 2015, ', 'Du W, 2005, ', 'Slavković A, 2007, ', 'Wu S, 2013, 人工知能学会全国大会論文集', 'Kamara S, 2011, IACR CRYPTOLOGY EPRINT ARCHIVE', 'Gascón A, 2016, IACR CRYPTOLOGY EPRINT ARCHIVE', 'Gilad-Bachrach R, 2016, ', 'Wang X, 2016, IACR CRYPTOLOGY EPRINT ARCHIVE']</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
@@ -14543,12 +14551,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>Schuld M, 2019, PHYSICAL REVIEW LETTERS</t>
+          <t xml:space="preserve">Mohassel P, 2017, </t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>Schuld M, 2019, PHYSICAL REVIEW LETTERS</t>
+          <t xml:space="preserve">Mohassel P, 2017, </t>
         </is>
       </c>
     </row>
@@ -15138,7 +15146,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -15366,7 +15374,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -15492,7 +15500,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -15732,7 +15740,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -15854,7 +15862,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -15919,7 +15927,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>['Barabási A, 1999, SCIENCE', 'Murphy K, 2012, ', 'Wolpert D, 1992, NEURAL NETWORKS', 'Koller D, 2009, ', 'Davis J, 2006, ', 'Bottou L, 2010, ', 'Auer S, 2007, LECTURE NOTES IN COMPUTER SCIENCE', 'Koren Y, 2008, ', 'McGuinness D, 2004, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Rahm E, 2001, THE VLDB JOURNAL', 'Lü L, 2010, PHYSICA A STATISTICAL MECHANICS AND ITS APPLICATIONS', 'Richardson M, 2006, MACHINE LEARNING', 'Hong W, 2014, ARXIV (CORNELL UNIVERSITY)', 'Carlson J, 2010, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Nickel M, 2011, ', ', 2007, THE MIT PRESS EBOOKS', 'Quinlan J, 1990, MACHINE LEARNING', 'Halford G, 1998, BEHAVIORAL AND BRAIN SCIENCES', 'Riedel S, 2013, SCHOLARWORKS@UMASSAMHERST (UNIVERSITY OF MASSACHUSETTS AMHERST)', 'Lao N, 2018, FIGSHARE', 'Sun Y, 2012, SYNTHESIS LECTURES ON DATA MINING AND KNOWLEDGE DISCOVERY', 'Nakashole N, 2012, MPG.PURE (MAX PLANCK SOCIETY)', 'Halpin H, 2010, LECTURE NOTES IN COMPUTER SCIENCE', 'Li X, 2012, PROCEEDINGS OF THE VLDB ENDOWMENT', 'Poon H, 2006, ', 'Suh B, 2009, ', 'Dong X, 2014, PROCEEDINGS OF THE VLDB ENDOWMENT', 'Franz T, 2009, LECTURE NOTES IN COMPUTER SCIENCE', 'Orbanz P, 2014, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Dong X, 2015, PROCEEDINGS OF THE VLDB ENDOWMENT', 'Kimmig A, 2012, LIRIAS (KU LEUVEN)', 'Jensen D, 2002, ', 'Kolda T, 2006, ', 'Rettinger A, 2012, DATA MINING AND KNOWLEDGE DISCOVERY', 'Lösch U, 2012, LECTURE NOTES IN COMPUTER SCIENCE', 'Nickel M, 2013, LECTURE NOTES IN COMPUTER SCIENCE', 'Culotta A, 2005, ', 'Miettinen P, 2011, ', 'Angeli G, 2013, ', 'Ji H, 2013, KNOWLEDGE AND INFORMATION SYSTEMS', 'Krompaß D, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Pujara J, 2015, AI MAGAZINE', 'Hong L, 2015, ', 'd’Amato C, 2006, CINECA IRIS INSTITUTIONAL RESEARCH INFORMATION SYSTEM (UNIVERSITY OF BARI ALDO MORO)', 'Mikolov T, 2013, ARXIV (CORNELL UNIVERSITY)', 'Sowa J, 2000, CERN DOCUMENT SERVER (EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Hogan A, 2010, ARROW@DIT (DUBLIN INSTITUTE OF TECHNOLOGY)', 'Bach S, 2015, ARXIV (CORNELL UNIVERSITY)', 'Nickel M, 2013, ARXIV (CORNELL UNIVERSITY)', 'Nickel M, 2013, ELECTRONIC THESES OF LMU MUNICH (LUDWIG-MAXIMILIANS-UNIVERSITÄT MÜNCHEN)', 'Brin S, 1998, COMPUTER NETWORKS AND ISDN SYSTEMS', 'Miller G, 1995, COMMUNICATIONS OF THE ACM', 'Koren Y, 2009, COMPUTER', 'Fortunato S, 2009, PHYSICS REPORTS', 'Kolda T, 2009, SIAM REVIEW', 'Bordes A, 2015, ', 'Bollacker K, 2008, ', 'Bizer C, 2009, INTERNATIONAL JOURNAL ON SEMANTIC WEB AND INFORMATION SYSTEMS', 'Newman M, 2001, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Suchanek F, 2007, ', 'Katz L, 1953, PSYCHOMETRIKA', 'Vrandečić D, 2014, COMMUNICATIONS OF THE ACM', 'Holland P, 1983, SOCIAL NETWORKS', 'Hoff P, 2002, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Lenat D, 1995, COMMUNICATIONS OF THE ACM', 'Socher R, 2013, ', 'Dong X, 2014, ', 'Muggleton S, 1995, NEW GENERATION COMPUTING', 'Rendle S, 2012, ACM TRANSACTIONS ON INTELLIGENT SYSTEMS AND TECHNOLOGY', 'Hoffart J, 2012, ARTIFICIAL INTELLIGENCE', 'Getoor L, 2005, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Smolensky P, 1990, ARTIFICIAL INTELLIGENCE', 'Leicht E, 2006, PHYSICAL REVIEW E', 'Newcombe H, 1959, SCIENCE', 'Rendle S, 2010, ', 'Lao N, 2010, MACHINE LEARNING', 'Liu W, 2010, EUROPHYSICS LETTERS (EPL)', 'Kemp C, 2006, ', 'Minsky M, 1997, THE MIT PRESS EBOOKS', 'Džeroski S, 2006, ', 'Galárraga L, 2015, THE VLDB JOURNAL', 'Taskar B, 2003, ', 'Nickel M, 2012, ', 'Neville J, 2007, THE MIT PRESS EBOOKS', 'Kok S, 2007, ', 'Sutskever I, 2009, DSPACE@MIT (MASSACHUSETTS INSTITUTE OF TECHNOLOGY)', 'Nakashole N, 2011, ', 'Chang K, 2014, ', 'Wang D, 2008, PROCEEDINGS OF THE VLDB ENDOWMENT', 'Anderson C, 1992, SOCIAL NETWORKS', 'Ruttenberg A, 2009, BRIEFINGS IN BIOINFORMATICS', 'Drumond L, 2012, ', 'Zhang C, 2013, ', 'Whang S, 2012, ', 'Fan J, 2010, ', 'Erdös D, 2013, ', 'Jenatton R, 2012, HAL (LE CENTRE POUR LA COMMUNICATION SCIENTIFIQUE DIRECTE)', 'Xu Z, 2012, ARXIV (CORNELL UNIVERSITY)', 'James G, 2013, SPRINGER TEXTS IN STATISTICS', 'Minsky M, 1988, ELSEVIER EBOOKS', 'Bodenreider O, 2003, NUCLEIC ACIDS RESEARCH', 'Adamic L, 2003, SOCIAL NETWORKS', 'Bleiholder J, 2009, ACM COMPUTING SURVEYS', 'Ferrucci D, 2010, AI MAGAZINE', 'Fader A, 2011, ', 'Platt J, 2000, THE MIT PRESS EBOOKS', 'Toutanova K, 2015, ', 'Muggleton S, 1991, NEW GENERATION COMPUTING', 'Bordes A, 2011, ', 'Lee N, 2024, ENCYCLOPEDIA OF COMPUTER GRAPHICS AND GAMES', 'Belleau F, 2008, JOURNAL OF BIOMEDICAL INFORMATICS', 'Schmitz M, 2012, ', 'Davis R, 1993, ', 'Quinlan J, 1990, MACHINE LEARNING', 'Galárraga L, 2013, ', 'Etzioni O, 2011, ', 'Barnden J, 1998, ', 'Singla P, 2006, PROCEEDINGS', 'Raedt L, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Suciu D, 2008, ACM SIGACT NEWS', 'Tejada S, 2001, INFORMATION SYSTEMS', 'West R, 2014, ', 'Globerson A, 2007, ', 'Kolda T, 2006, ', 'Lehmann J, 2009, ', 'Sun Y, 2012, SYNTHESIS LECTURES ON DATA MINING AND KNOWLEDGE DISCOVERY', 'Weikum G, 2010, ', 'Xu Z, 2006, ', 'Rendle S, 2013, PROCEEDINGS OF THE VLDB ENDOWMENT', 'Niu F, 2012, INTERNATIONAL JOURNAL ON SEMANTIC WEB AND INFORMATION SYSTEMS', 'Nickel M, 2014, ', 'Tresp V, 2009, ', 'Tibshirani R, 2007, ', 'LehmannJens, 2009, JOURNAL OF MACHINE LEARNING RESEARCH', 'Biega J, 2013, ', 'Jiang S, 2012, ', 'Huang Y, 2014, SEMANTIC WEB', 'Jiang X, 2012, ', 'Krompaß D, 2014, ', 'Lisi F, 2010, THEORY AND PRACTICE OF LOGIC PROGRAMMING', 'Krompaß D, 2014, ', 'Minervini P, 2014, ', 'Hoff P, 2007, ARXIV.ORG', 'Li X, 2015, ARXIV (CORNELL UNIVERSITY)', 'Liben‐Nowell D, 2007, JOURNAL OF THE AMERICAN SOCIETY FOR INFORMATION SCIENCE AND TECHNOLOGY', 'Klyne G, 2004, ', 'Ooi V, 2019, EDINBURGH UNIVERSITY PRESS EBOOKS', 'Minsky M, 1979, ', ', 2004, ELSEVIER EBOOKS', 'Bottou L, 2011, CHAPMAN &amp; HALL/CRC SERIES IN COMPUTER SCIENCE &amp; DATA ANALYSIS/SERIES IN COMPUTER SCIENCE AND DATA ANALYSIS', ', 2001, ', 'M. G, 2008, COGNITIVE TECHNOLOGIES', 'Suciu D, 2011, SYNTHESIS LECTURES ON DATA MANAGEMENT', 'Suciu D, 2011, SYNTHESIS LECTURES ON DATA MANAGEMENT', 'Smolensky P, 1991, THE MIT PRESS EBOOKS', 'Dězeroski S, 2001, SPRINGER EBOOKS', 'Newman M, 2011, PRINCETON UNIVERSITY PRESS EBOOKS', 'Hoff P, 2001, ', 'Sowa J, 2005, ENCYCLOPEDIA OF COGNITIVE SCIENCE', 'Kenny J, 2005, ']</t>
+          <t>['Barabási A, 1999, SCIENCE', 'Murphy K, 2012, ', 'Wolpert D, 1992, NEURAL NETWORKS', 'Koller D, 2009, ', 'Davis J, 2006, ', 'Bottou L, 2010, ', 'Auer S, 2007, LECTURE NOTES IN COMPUTER SCIENCE', 'Koren Y, 2008, ', 'McGuinness D, 2004, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Rahm E, 2001, THE VLDB JOURNAL', 'Lü L, 2010, PHYSICA A STATISTICAL MECHANICS AND ITS APPLICATIONS', 'Richardson M, 2006, MACHINE LEARNING', 'Bishan Y, 2014, ARXIV (CORNELL UNIVERSITY)', 'Carlson J, 2010, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Nickel M, 2011, ', ', 2007, THE MIT PRESS EBOOKS', 'Quinlan J, 1990, MACHINE LEARNING', 'Halford G, 1998, BEHAVIORAL AND BRAIN SCIENCES', 'Riedel S, 2013, SCHOLARWORKS@UMASSAMHERST (UNIVERSITY OF MASSACHUSETTS AMHERST)', 'Lao N, 2018, FIGSHARE', 'Sun Y, 2012, SYNTHESIS LECTURES ON DATA MINING AND KNOWLEDGE DISCOVERY', 'Nakashole N, 2012, MPG.PURE (MAX PLANCK SOCIETY)', 'Halpin H, 2010, LECTURE NOTES IN COMPUTER SCIENCE', 'Li X, 2012, PROCEEDINGS OF THE VLDB ENDOWMENT', 'Poon H, 2006, ', 'Suh B, 2009, ', 'Dong X, 2014, PROCEEDINGS OF THE VLDB ENDOWMENT', 'Franz T, 2009, LECTURE NOTES IN COMPUTER SCIENCE', 'Orbanz P, 2014, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Dong X, 2015, PROCEEDINGS OF THE VLDB ENDOWMENT', 'Kimmig A, 2012, LIRIAS (KU LEUVEN)', 'Jensen D, 2002, ', 'Kolda T, 2006, ', 'Rettinger A, 2012, DATA MINING AND KNOWLEDGE DISCOVERY', 'Lösch U, 2012, LECTURE NOTES IN COMPUTER SCIENCE', 'Nickel M, 2013, LECTURE NOTES IN COMPUTER SCIENCE', 'Culotta A, 2005, ', 'Miettinen P, 2011, ', 'Angeli G, 2013, ', 'Ji H, 2013, KNOWLEDGE AND INFORMATION SYSTEMS', 'Krompaß D, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Pujara J, 2015, AI MAGAZINE', 'Hong L, 2015, ', 'd’Amato C, 2006, CINECA IRIS INSTITUTIONAL RESEARCH INFORMATION SYSTEM (UNIVERSITY OF BARI ALDO MORO)', 'Mikolov T, 2013, ARXIV (CORNELL UNIVERSITY)', 'Sowa J, 2000, CERN DOCUMENT SERVER (EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Hogan A, 2010, ARROW@DIT (DUBLIN INSTITUTE OF TECHNOLOGY)', 'Bach S, 2015, ARXIV (CORNELL UNIVERSITY)', 'Nickel M, 2013, ARXIV (CORNELL UNIVERSITY)', 'Nickel M, 2013, ELECTRONIC THESES OF LMU MUNICH (LUDWIG-MAXIMILIANS-UNIVERSITÄT MÜNCHEN)', 'Brin S, 1998, COMPUTER NETWORKS AND ISDN SYSTEMS', 'Miller G, 1995, COMMUNICATIONS OF THE ACM', 'Koren Y, 2009, COMPUTER', 'Fortunato S, 2009, PHYSICS REPORTS', 'Kolda T, 2009, SIAM REVIEW', 'Bordes A, 2015, ', 'Bollacker K, 2008, ', 'Bizer C, 2009, INTERNATIONAL JOURNAL ON SEMANTIC WEB AND INFORMATION SYSTEMS', 'Newman M, 2001, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Suchanek F, 2007, ', 'Katz L, 1953, PSYCHOMETRIKA', 'Vrandečić D, 2014, COMMUNICATIONS OF THE ACM', 'Holland P, 1983, SOCIAL NETWORKS', 'Hoff P, 2002, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Lenat D, 1995, COMMUNICATIONS OF THE ACM', 'Socher R, 2013, ', 'Dong X, 2014, ', 'Muggleton S, 1995, NEW GENERATION COMPUTING', 'Rendle S, 2012, ACM TRANSACTIONS ON INTELLIGENT SYSTEMS AND TECHNOLOGY', 'Hoffart J, 2012, ARTIFICIAL INTELLIGENCE', 'Getoor L, 2005, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Smolensky P, 1990, ARTIFICIAL INTELLIGENCE', 'Leicht E, 2006, PHYSICAL REVIEW E', 'Newcombe H, 1959, SCIENCE', 'Rendle S, 2010, ', 'Lao N, 2010, MACHINE LEARNING', 'Liu W, 2010, EUROPHYSICS LETTERS (EPL)', 'Kemp C, 2006, ', 'Minsky M, 1997, THE MIT PRESS EBOOKS', 'Džeroski S, 2006, ', 'Galárraga L, 2015, THE VLDB JOURNAL', 'Taskar B, 2003, ', 'Nickel M, 2012, ', 'Neville J, 2007, THE MIT PRESS EBOOKS', 'Kok S, 2007, ', 'Sutskever I, 2009, DSPACE@MIT (MASSACHUSETTS INSTITUTE OF TECHNOLOGY)', 'Nakashole N, 2011, ', 'Chang K, 2014, ', 'Wang D, 2008, PROCEEDINGS OF THE VLDB ENDOWMENT', 'Anderson C, 1992, SOCIAL NETWORKS', 'Ruttenberg A, 2009, BRIEFINGS IN BIOINFORMATICS', 'Drumond L, 2012, ', 'Zhang C, 2013, ', 'Whang S, 2012, ', 'Fan J, 2010, ', 'Erdös D, 2013, ', 'Jenatton R, 2012, HAL (LE CENTRE POUR LA COMMUNICATION SCIENTIFIQUE DIRECTE)', 'Xu Z, 2012, ARXIV (CORNELL UNIVERSITY)', 'James G, 2013, SPRINGER TEXTS IN STATISTICS', 'Minsky M, 1988, ELSEVIER EBOOKS', 'Bodenreider O, 2003, NUCLEIC ACIDS RESEARCH', 'Adamic L, 2003, SOCIAL NETWORKS', 'Bleiholder J, 2009, ACM COMPUTING SURVEYS', 'Ferrucci D, 2010, AI MAGAZINE', 'Fader A, 2011, ', 'Platt J, 2000, THE MIT PRESS EBOOKS', 'Toutanova K, 2015, ', 'Muggleton S, 1991, NEW GENERATION COMPUTING', 'Bordes A, 2011, ', 'Lee N, 2024, ENCYCLOPEDIA OF COMPUTER GRAPHICS AND GAMES', 'Belleau F, 2008, JOURNAL OF BIOMEDICAL INFORMATICS', 'Schmitz M, 2012, ', 'Davis R, 1993, ', 'Quinlan J, 1990, MACHINE LEARNING', 'Galárraga L, 2013, ', 'Etzioni O, 2011, ', 'Barnden J, 1998, ', 'Singla P, 2006, PROCEEDINGS', 'Raedt L, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Suciu D, 2008, ACM SIGACT NEWS', 'Tejada S, 2001, INFORMATION SYSTEMS', 'West R, 2014, ', 'Globerson A, 2007, ', 'Kolda T, 2006, ', 'Lehmann J, 2009, ', 'Sun Y, 2012, SYNTHESIS LECTURES ON DATA MINING AND KNOWLEDGE DISCOVERY', 'Weikum G, 2010, ', 'Xu Z, 2006, ', 'Rendle S, 2013, PROCEEDINGS OF THE VLDB ENDOWMENT', 'Niu F, 2012, INTERNATIONAL JOURNAL ON SEMANTIC WEB AND INFORMATION SYSTEMS', 'Nickel M, 2014, ', 'Tresp V, 2009, ', 'Tibshirani R, 2007, ', 'LehmannJens, 2009, JOURNAL OF MACHINE LEARNING RESEARCH', 'Biega J, 2013, ', 'Jiang S, 2012, ', 'Huang Y, 2014, SEMANTIC WEB', 'Jiang X, 2012, ', 'Krompaß D, 2014, ', 'Lisi F, 2010, THEORY AND PRACTICE OF LOGIC PROGRAMMING', 'Krompaß D, 2014, ', 'Minervini P, 2014, ', 'Hoff P, 2007, ARXIV.ORG', 'Li X, 2015, ARXIV (CORNELL UNIVERSITY)', 'Liben‐Nowell D, 2007, JOURNAL OF THE AMERICAN SOCIETY FOR INFORMATION SCIENCE AND TECHNOLOGY', 'Klyne G, 2004, ', 'Ooi V, 2019, EDINBURGH UNIVERSITY PRESS EBOOKS', 'Minsky M, 1979, ', ', 2004, ELSEVIER EBOOKS', 'Bottou L, 2011, CHAPMAN &amp; HALL/CRC SERIES IN COMPUTER SCIENCE &amp; DATA ANALYSIS/SERIES IN COMPUTER SCIENCE AND DATA ANALYSIS', ', 2001, ', 'De R, 2008, COGNITIVE TECHNOLOGIES', 'Suciu D, 2011, SYNTHESIS LECTURES ON DATA MANAGEMENT', 'Suciu D, 2011, SYNTHESIS LECTURES ON DATA MANAGEMENT', 'Smolensky P, 1991, THE MIT PRESS EBOOKS', 'Dězeroski S, 2001, SPRINGER EBOOKS', 'Newman M, 2011, PRINCETON UNIVERSITY PRESS EBOOKS', 'Hoff P, 2001, ', 'Sowa J, 2005, ENCYCLOPEDIA OF COGNITIVE SCIENCE', 'Kenny J, 2005, ']</t>
         </is>
       </c>
       <c r="V136" t="inlineStr">
@@ -16098,7 +16106,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>48363</v>
+        <v>48425</v>
       </c>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
@@ -16175,17 +16183,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2284729062</t>
+          <t>https://openalex.org/W2963784900</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>10.1177/1745691617693393</t>
+          <t>10.1038/s41524-017-0056-5</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Choosing Prediction Over Explanation in Psychology: Lessons From Machine Learning</t>
+          <t>Machine learning in materials informatics: recent applications and prospects</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16200,80 +16208,72 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>1995</v>
+        <v>1760</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>PERSPECTIVES ON PSYCHOLOGICAL SCIENCE</t>
+          <t>NPJ COMPUTATIONAL MATERIALS</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Perspectives on Psychological Science</t>
+          <t>npj Computational Materials</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>['Tal Yarkoni', 'Jacob Westfall']</t>
+          <t>['Rampi Ramprasad', 'Rohit Batra', 'Ghanshyam Pilania', 'Arun Mannodi‐Kanakkithodi', 'Chiho Kim']</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>['Tal Yarkoni', 'Jacob Westfall']</t>
+          <t>['Rampi Ramprasad', 'Rohit Batra', 'Ghanshyam Pilania', 'Arun Mannodi-Kanakkithodi', 'Chiho Kim']</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>['University of Texas at Austin', 'University of Texas at Austin']</t>
+          <t>['Department of Materials Science &amp; Engineering and Institute of Materials Science, University of Connecticut, 97 North Eagleville Rd., Unit 3136, Storrs, CT, 06269-3136, USA', 'Department of Materials Science &amp; Engineering and Institute of Materials Science, University of Connecticut, 97 North Eagleville Rd., Unit 3136, Storrs, CT, 06269-3136, USA', 'Fritz-Haber-Institut der Max-Planck-Gesellschaft, Faradayweg 4-6, 14195, Berlin, Germany', 'Materials Science and Technology Division, Los Alamos National Laboratory, Los Alamos, NM, 87545, USA', 'Center for Nanoscale Materials, Lamont National Laboratory, 9700 S. Cass Ave., Lemont, IL, 60439, USA', 'Department of Materials Science &amp; Engineering and Institute of Materials Science, University of Connecticut, 97 North Eagleville Rd., Unit 3136, Storrs, CT, 06269-3136, USA', 'Department of Materials Science &amp; Engineering and Institute of Materials Science, University of Connecticut, 97 North Eagleville Rd., Unit 3136, Storrs, CT, 06269-3136, USA']</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Tal Yarkoni (corresponding author), University of Texas at Austin</t>
+          <t>Rampi Ramprasad (corresponding author), Department of Materials Science &amp; Engineering and Institute of Materials Science, University of Connecticut, 97 North Eagleville Rd., Unit 3136, Storrs, CT, 06269-3136, USA</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Psychology has historically been concerned, first and foremost, with explaining the causal mechanisms that give rise to behavior. Randomized, tightly controlled experiments are enshrined as the gold standard of psychological research, and there are endless investigations of the various mediating and moderating variables that govern various behaviors. We argue that psychology's near-total focus on explaining the causes of behavior has led much of the field to be populated by research programs that provide intricate theories of psychological mechanism but that have little (or unknown) ability to predict future behaviors with any appreciable accuracy. We propose that principles and techniques from the field of machine learning can help psychology become a more predictive science. We review some of the fundamental concepts and tools of machine learning and point out examples where these concepts have been used to conduct interesting and important psychological research that focuses on predictive research questions. We suggest that an increased focus on prediction, rather than explanation, can ultimately lead us to greater understanding of behavior.</t>
+          <t>Abstract Propelled partly by the Materials Genome Initiative, and partly by the algorithmic developments and the resounding successes of data-driven efforts in other domains, informatics strategies are beginning to take shape within materials science. These approaches lead to surrogate machine learning models that enable rapid predictions based purely on past data rather than by direct experimentation or by computations/simulations in which fundamental equations are explicitly solved. Data-centric informatics methods are becoming useful to determine material properties that are hard to measure or compute using traditional methods—due to the cost, time or effort involved—but for which reliable data either already exists or can be generated for at least a subset of the critical cases. Predictions are typically interpolative, involving fingerprinting a material numerically first, and then following a mapping (established via a learning algorithm) between the fingerprint and the property of interest. Fingerprints, also referred to as “descriptors”, may be of many types and scales, as dictated by the application domain and needs. Predictions may also be extrapolative—extending into new materials spaces—provided prediction uncertainties are properly taken into account. This article attempts to provide an overview of some of the recent successful data-driven “materials informatics” strategies undertaken in the last decade, with particular emphasis on the fingerprint or descriptor choices. The review also identifies some challenges the community is facing and those that should be overcome in the near future.</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="R139" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>['Psychology', 'Field (mathematics)', 'Psychological research', 'Mechanism (biology)', 'Focus (optics)', 'Psychological science', 'Cognitive psychology', 'Basic science', 'Experimental psychology', 'Contrast (vision)', 'Point (geometry)', 'Cognitive science', 'Epistemology', 'Social psychology', 'Artificial intelligence', 'Cognition', 'Computer science']</t>
+          <t>['Computer science', 'Informatics', 'Data science', 'Domain (mathematical analysis)', 'Fingerprint (computing)', 'Property (philosophy)', 'Artificial intelligence', 'Machine learning', 'Materials informatics', 'Computation', 'Data mining', 'Management science', 'Health informatics', 'Engineering informatics', 'Algorithm', 'Mathematics', 'Engineering']</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>['US']</t>
+          <t>['US', 'DE']</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>['Cohen J, 1992, PSYCHOLOGICAL BULLETIN', 'Friedman J, 2001, THE ANNALS OF STATISTICS', 'Hastie T, 2001, SPRINGER SERIES IN STATISTICS', 'Schmidhuber J, 2014, NEURAL NETWORKS', 'Zeiler M, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Gelman A, 2006, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'C. P, 2001, TECHNOMETRICS', 'Ekman P, 1992, COGNITION &amp; EMOTION', 'Aarts A, 2015, SCIENCE', 'Essen D, 2013, NEUROIMAGE', 'Biswal B, 2010, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Brysbaert M, 2009, BEHAVIOR RESEARCH METHODS', 'Bond R, 2012, NATURE', 'Dawes R, 1979, AMERICAN PSYCHOLOGIST', 'Vrieze S, 2012, PSYCHOLOGICAL METHODS', 'Pennebaker J, 1999, JOURNAL OF PERSONALITY AND SOCIAL PSYCHOLOGY', 'Shao J, 1993, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Ebstein R, 1996, NATURE GENETICS', 'Browne M, 2000, JOURNAL OF MATHEMATICAL PSYCHOLOGY', 'Klein R, 2014, SOCIAL PSYCHOLOGY', 'Ripke S, 2012, MOLECULAR PSYCHIATRY', 'Brewer J, 1998, SCIENCE', 'Meehl P, 1990, PSYCHOLOGICAL REPORTS', 'Du S, 2014, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Wainer H, 1976, PSYCHOLOGICAL BULLETIN', 'Gosling S, 2011, CYBERPSYCHOLOGY BEHAVIOR AND SOCIAL NETWORKING', 'Yarkoni T, 2010, JOURNAL OF RESEARCH IN PERSONALITY', 'Baayen R, 2011, PSYCHOLOGICAL REVIEW', 'Yarkoni T, 2009, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE', 'Whelan R, 2014, NATURE', 'McNeish D, 2015, MULTIVARIATE BEHAVIORAL RESEARCH', 'Fast L, 2008, JOURNAL OF PERSONALITY AND SOCIAL PSYCHOLOGY', 'Browne M, 2002, PSYCHOLOGICAL METHODS', 'Fleet D, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Munafò M, 2011, TRENDS IN COGNITIVE SCIENCES', 'Horn J, 2013, BRAIN IMAGING AND BEHAVIOR', 'Gelman A, 2009, AMERICAN SCIENTIST', 'Kurtz A, 1948, PERSONNEL PSYCHOLOGY', 'Wu S, 2007, THE CANADIAN JOURNAL OF CHEMICAL ENGINEERING', 'Mosier C, 1951, EDUCATIONAL AND PSYCHOLOGICAL MEASUREMENT', 'Hagerty M, 1991, PSYCHOMETRIKA', 'Strube M, 2006, BEHAVIOR RESEARCH METHODS', 'Davis‐Stober C, 2013, BEHAVIOR RESEARCH METHODS', 'Shear B, 2013, EDUCATIONAL AND PSYCHOLOGICAL MEASUREMENT', 'Jonas K, 2015, COMPREHENSIVE RESULTS IN SOCIAL PSYCHOLOGY', 'Yarkoni T, 2015, PEERJ', 'Wherry R, 1975, PERSONNEL PSYCHOLOGY', 'Schmitt N, 1977, PSYCHOLOGICAL BULLETIN', 'Wherry R, 1951, EDUCATIONAL AND PSYCHOLOGICAL MEASUREMENT', ', 2017, ANNUAL REVIEW OF PSYCHOLOGY', 'Deng J, 2009, 2009 IEEE CONFERENCE ON COMPUTER VISION AND PATTERN RECOGNITION', 'Tibshirani R, 1996, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Cohen P, 2014, PSYCHOLOGY PRESS EBOOKS', 'Wolpert D, 1997, IEEE TRANSACTIONS ON EVOLUTIONARY COMPUTATION', 'Burnham K, 2004, SOCIOLOGICAL METHODS &amp; RESEARCH', 'Simmons J, 2011, PSYCHOLOGICAL SCIENCE', 'Lesch K, 1996, SCIENCE', 'Breiman L, 2001, STATISTICAL SCIENCE', 'Tibshirani R, 2011, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Domingos P, 2012, COMMUNICATIONS OF THE ACM', 'Kosiński M, 2013, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Balota D, 2007, BEHAVIOR RESEARCH METHODS', 'Poropat A, 2009, PSYCHOLOGICAL BULLETIN', 'John L, 2012, PSYCHOLOGICAL SCIENCE', 'Wood A, 2014, NATURE GENETICS', 'Varma S, 2006, BMC BIOINFORMATICS', 'Cawley G, 2010, ', 'Cohen J, 1962, JOURNAL OF ABNORMAL &amp; SOCIAL PSYCHOLOGY', 'Rentfrow P, 2003, JOURNAL OF PERSONALITY AND SOCIAL PSYCHOLOGY', 'Dwan K, 2008, PLOS ONE', 'Ioannidis J, 2008, EPIDEMIOLOGY', 'Breiman L, 2001, ', 'Back M, 2010, PSYCHOLOGICAL SCIENCE', 'Wagenmakers E, 2012, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE', 'Krstajić D, 2014, JOURNAL OF CHEMINFORMATICS', 'New B, 2004, BEHAVIOR RESEARCH METHODS, INSTRUMENTS, &amp; COMPUTERS', 'Westfall J, 2014, JOURNAL OF EXPERIMENTAL PSYCHOLOGY GENERAL', 'Bakker M, 2012, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE', 'Sedlmeier P, 1989, PSYCHOLOGICAL BULLETIN', 'Nosek B, 2014, SOCIAL PSYCHOLOGY', 'Yarkoni T, 2008, PSYCHONOMIC BULLETIN &amp; REVIEW', 'Miller G, 2012, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE', 'Ferguson C, 2012, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE', 'Ioannidis J, 2012, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE', 'Westfall J, 2016, PLOS ONE', 'Judd C, 2016, ANNUAL REVIEW OF PSYCHOLOGY', 'Vazire S, 2004, JOURNAL OF PERSONALITY AND SOCIAL PSYCHOLOGY', 'Rowe M, 2008, DEVELOPMENTAL SCIENCE', 'Perry C, 2010, COGNITIVE PSYCHOLOGY', 'Holbert R, 2002, HUMAN COMMUNICATION RESEARCH', 'Apté C, 1997, FUTURE GENERATION COMPUTER SYSTEMS', 'Vitaro F, 1999, ADDICTION', 'Greenwald A, 2012, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE', 'Yap M, 2011, JOURNAL OF EXPERIMENTAL PSYCHOLOGY HUMAN PERCEPTION &amp; PERFORMANCE', 'Bunea F, 2010, NEUROIMAGE', 'Rissman J, 2010, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Rawlings D, 1997, PSYCHOLOGY OF MUSIC', 'Xu K, 2014, JOURNAL OF OPEN PSYCHOLOGY DATA', 'Yarkoni T, 2012, CURRENT DIRECTIONS IN PSYCHOLOGICAL SCIENCE', 'Bentley R, 2014, BEHAVIORAL AND BRAIN SCIENCES', 'Breiman L, 2001, MACHINE LEARNING', 'LeCun Y, 2015, NATURE', 'Hastie T, 2009, SPRINGER SERIES IN STATISTICS', 'Pinheiro J, 2000, STATISCTICS AND COMPUTING/STATISTICS AND COMPUTING', 'Cohen J, 1992, PSYCHOLOGICAL BULLETIN', 'Wood S, 2006, ', 'Cohen ⁄, 2013, ', 'Shmueli G, 2010, STATISTICAL SCIENCE', 'Nosek B, 2012, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE', 'Ebersole C, 2016, JOURNAL OF EXPERIMENTAL SOCIAL PSYCHOLOGY', 'Pennebaker J, 1999, JOURNAL OF PERSONALITY AND SOCIAL PSYCHOLOGY', 'Smıth D, 2016, MOLECULAR PSYCHIATRY', 'Browne M, 2002, PSYCHOLOGICAL METHODS', 'Loftus E, 1996, ', 'Ebersole C, 2016, ', 'Smıth D, 2016, MOLECULAR PSYCHIATRY']</t>
+          <t>['Jordan M, 2015, SCIENCE', 'Behler J, 2007, PHYSICAL REVIEW LETTERS', 'Feynman R, 1939, PHYSICAL REVIEW', 'Bartók A, 2010, PHYSICAL REVIEW LETTERS', 'Schmidt M, 2009, SCIENCE', 'Bartók A, 2013, PHYSICAL REVIEW B', 'Sánchez J, 1984, PHYSICA A STATISTICAL MECHANICS AND ITS APPLICATIONS', ', 1991, CHOICE REVIEWS ONLINE', 'Ercolessi F, 1994, EUROPHYSICS LETTERS (EPL)', 'Thompson A, 2014, JOURNAL OF COMPUTATIONAL PHYSICS', 'Forrester A, 2007, PROCEEDINGS OF THE ROYAL SOCIETY A MATHEMATICAL PHYSICAL AND ENGINEERING SCIENCES', 'Walle A, 2002, JOURNAL OF PHASE EQUILIBRIA AND DIFFUSION', 'Pilania G, 2013, SCIENTIFIC REPORTS', 'Snyder J, 2012, PHYSICAL REVIEW LETTERS', 'Li Z, 2015, PHYSICAL REVIEW LETTERS', 'Bartók A, 2015, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Hautier G, 2010, CHEMISTRY OF MATERIALS', 'Fontaine D, 1994, SOLID STATE PHYSICS', ', 2008, CHOICE REVIEWS ONLINE', 'Seko A, 2015, PHYSICAL REVIEW LETTERS', 'Behler J, 2014, JOURNAL OF PHYSICS CONDENSED MATTER', 'Faber F, 2016, PHYSICAL REVIEW LETTERS', 'Rupp M, 2015, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Laks D, 1992, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Lee J, 2016, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Szlachta W, 2014, PHYSICAL REVIEW B', 'Fernández M, 2014, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Behler J, 2008, PHYSICAL REVIEW LETTERS', 'Nelson L, 2013, PHYSICAL REVIEW B', 'Gupta A, 2015, ACTA MATERIALIA', 'Petch N, 1986, ACTA METALLURGICA', 'Aryal S, 2014, PHYSICA STATUS SOLIDI (B)', 'Ryzhov I, 2012, OPERATIONS RESEARCH', 'Huan T, 2015, PHYSICAL REVIEW B', 'Dey P, 2013, COMPUTATIONAL MATERIALS SCIENCE', 'Seko A, 2009, PHYSICAL REVIEW B', 'Snyder J, 2013, THE JOURNAL OF CHEMICAL PHYSICS', 'Lorenzini R, 2013, POLYMER', 'Theodoridis S, 2015, MACHINE LEARNING', 'Zunger A, 1994, NATO ASI SERIES. SERIES B : PHYSICS', 'Hume-Rothery W, 1947, ', 'Chatterjee S, 2007, MATERIALS SCIENCE AND TECHNOLOGY', 'Dudiy S, 2006, PHYSICAL REVIEW LETTERS', 'Mueller T, 2010, PHYSICAL REVIEW B', 'Cockayne E, 2010, PHYSICAL REVIEW B', 'Kalidindi S, 2012, ISRN MATERIALS SCIENCE', 'Adamson G, 1974, NATURE', 'Sanders J, 2015, ACS CENTRAL SCIENCE', 'Adamson G, 1974, JOURNAL OF CHEMICAL DOCUMENTATION', 'Powell W, 2011, WILEY ENCYCLOPEDIA OF OPERATIONS RESEARCH AND MANAGEMENT SCIENCE', 'Hall E, 1951, PROCEEDINGS OF THE PHYSICAL SOCIETY SECTION B', 'Rupp M, 2012, PHYSICAL REVIEW LETTERS', 'Ward L, 2016, NPJ COMPUTATIONAL MATERIALS', 'Ghiringhelli L, 2015, PHYSICAL REVIEW LETTERS', 'De S, 2016, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Xue D, 2016, NATURE COMMUNICATIONS', 'Meredig B, 2014, PHYSICAL REVIEW B', 'Micchelli C, 2004, NEURAL COMPUTATION', 'Mannodi‐Kanakkithodi A, 2016, SCIENTIFIC REPORTS', 'Botu V, 2014, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Oliynyk A, 2016, CHEMISTRY OF MATERIALS', 'Huan T, 2016, PROGRESS IN MATERIALS SCIENCE', 'Álvarez M, 2012, FOUNDATIONS AND TRENDS® IN MACHINE LEARNING', 'Panchal J, 2012, COMPUTER-AIDED DESIGN', 'Sharma V, 2014, NATURE COMMUNICATIONS', 'Hong W, 2015, THE JOURNAL OF PHYSICAL CHEMISTRY C', 'Seko A, 2014, PHYSICAL REVIEW B', 'Kusne A, 2014, SCIENTIFIC REPORTS', 'Emery A, 2016, CHEMISTRY OF MATERIALS', 'Kim C, 2016, CHEMISTRY OF MATERIALS', 'Li Z, 2016, CATALYSIS TODAY', 'Ward L, 2016, CURRENT OPINION IN SOLID STATE AND MATERIALS SCIENCE', 'Huan T, 2016, SCIENTIFIC DATA', 'Pilania G, 2016, FRONTIERS IN MATERIALS', 'Kim C, 2016, THE JOURNAL OF PHYSICAL CHEMISTRY C', 'Botu V, 2015, PHYSICAL REVIEW B', 'Mannodi‐Kanakkithodi A, 2016, ADVANCED MATERIALS', 'Lookman T, 2015, SPRINGER SERIES IN MATERIALS SCIENCE', 'Perdikaris P, 2015, PROCEEDINGS OF THE ROYAL SOCIETY A MATHEMATICAL PHYSICAL AND ENGINEERING SCIENCES', 'Powell W, 2012, WILEY SERIES IN PROBABILITY AND STATISTICS', 'Deml A, 2016, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Hattrick‐Simpers J, 2016, APL MATERIALS', 'Ashton M, 2016, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Kusne A, 2015, NANOTECHNOLOGY', 'Pilania G, 2015, PHYSICAL REVIEW B', 'Liu C, 2012, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Kalidindi S, 2016, MRS BULLETIN', 'Brough D, 2016, CURRENT OPINION IN SOLID STATE AND MATERIALS SCIENCE', 'Pilania G, 2017, CHEMISTRY OF MATERIALS', 'Kalidindi S, 2015, NANOTECHNOLOGY', 'Bunn J, 2016, JOM', 'Bialon A, 2016, CHEMISTRY OF MATERIALS', 'Srinivasan S, 2004, UNIVERSITY PRESS EBOOKS', 'Snyder J, 2015, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Fancher C, 2016, SCIENTIFIC REPORTS', 'Bianchini F, 2016, MODELLING AND SIMULATION IN MATERIALS SCIENCE AND ENGINEERING', 'Felsenstein J, 2008, SPRINGER SERIES IN STATISTICS', 'Mueller T, 2016, REVIEWS IN COMPUTATIONAL CHEMISTRY', 'Chmiela S, 2017, SCIENCE ADVANCES', 'Ercolessi F, 1994, ', 'Krevelen D, 2009, ELSEVIER EBOOKS', 'Deringer V, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Botu V, 2016, THE JOURNAL OF PHYSICAL CHEMISTRY C', 'Pilania G, 2016, COMPUTATIONAL MATERIALS SCIENCE', 'Green M, 2017, APPLIED PHYSICS REVIEWS', 'Jong M, 2016, SCIENTIFIC REPORTS', 'Glielmo A, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Xue D, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Legrain F, 2017, CHEMISTRY OF MATERIALS', 'Medasani B, 2016, NPJ COMPUTATIONAL MATERIALS', 'Ghiringhelli L, 2017, NEW JOURNAL OF PHYSICS', 'Lookman T, 2016, CURRENT OPINION IN SOLID STATE AND MATERIALS SCIENCE', 'Goldsmith B, 2017, NEW JOURNAL OF PHYSICS', 'Brough D, 2017, INTEGRATING MATERIALS AND MANUFACTURING INNOVATION', 'Theodoridis S, 2015, MACHINE LEARNING', 'L. G, 2017, MAX PLANCK DIGITAL LIBRARY', 'Mannodi‐Kanakkithodi A, 2017, CHEMISTRY OF MATERIALS', 'Jindal S, 2017, THE JOURNAL OF CHEMICAL PHYSICS', 'Botu V, 2017, COMPUTATIONAL MATERIALS SCIENCE', 'Brough D, 2017, INTEGRATING MATERIALS AND MANUFACTURING INNOVATION', 'Treich G, 2017, IEEE TRANSACTIONS ON DIELECTRICS AND ELECTRICAL INSULATION', 'J.W.C., 1961, JOURNAL OF THE LESS COMMON METALS', 'Gopnik A, 2017, SCIENTIFIC AMERICAN']</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
@@ -16289,29 +16289,29 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>Yarkoni T, 2017, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE</t>
+          <t>Ramprasad R, 2017, NPJ COMPUTATIONAL MATERIALS</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>Yarkoni T, 2017, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE</t>
+          <t>Ramprasad R, 2017, NPJ COMPUTATIONAL MATERIALS</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2963784900</t>
+          <t>https://openalex.org/W2284729062</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>10.1038/s41524-017-0056-5</t>
+          <t>10.1177/1745691617693393</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Machine learning in materials informatics: recent applications and prospects</t>
+          <t>Choosing Prediction Over Explanation in Psychology: Lessons From Machine Learning</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -16326,72 +16326,80 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>1759</v>
+        <v>1997</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>NPJ COMPUTATIONAL MATERIALS</t>
+          <t>PERSPECTIVES ON PSYCHOLOGICAL SCIENCE</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>npj Computational Materials</t>
+          <t>Perspectives on Psychological Science</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>['Rampi Ramprasad', 'Rohit Batra', 'Ghanshyam Pilania', 'Arun Mannodi‐Kanakkithodi', 'Chiho Kim']</t>
+          <t>['Tal Yarkoni', 'Jacob Westfall']</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>['Rampi Ramprasad', 'Rohit Batra', 'Ghanshyam Pilania', 'Arun Mannodi-Kanakkithodi', 'Chiho Kim']</t>
+          <t>['Tal Yarkoni', 'Jacob Westfall']</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>['Department of Materials Science &amp; Engineering and Institute of Materials Science, University of Connecticut, 97 North Eagleville Rd., Unit 3136, Storrs, CT, 06269-3136, USA', 'Department of Materials Science &amp; Engineering and Institute of Materials Science, University of Connecticut, 97 North Eagleville Rd., Unit 3136, Storrs, CT, 06269-3136, USA', 'Fritz-Haber-Institut der Max-Planck-Gesellschaft, Faradayweg 4-6, 14195, Berlin, Germany', 'Materials Science and Technology Division, Los Alamos National Laboratory, Los Alamos, NM, 87545, USA', 'Center for Nanoscale Materials, Lamont National Laboratory, 9700 S. Cass Ave., Lemont, IL, 60439, USA', 'Department of Materials Science &amp; Engineering and Institute of Materials Science, University of Connecticut, 97 North Eagleville Rd., Unit 3136, Storrs, CT, 06269-3136, USA', 'Department of Materials Science &amp; Engineering and Institute of Materials Science, University of Connecticut, 97 North Eagleville Rd., Unit 3136, Storrs, CT, 06269-3136, USA']</t>
+          <t>['University of Texas at Austin', 'University of Texas at Austin']</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Rampi Ramprasad (corresponding author), Department of Materials Science &amp; Engineering and Institute of Materials Science, University of Connecticut, 97 North Eagleville Rd., Unit 3136, Storrs, CT, 06269-3136, USA</t>
+          <t>Tal Yarkoni (corresponding author), University of Texas at Austin</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>Abstract Propelled partly by the Materials Genome Initiative, and partly by the algorithmic developments and the resounding successes of data-driven efforts in other domains, informatics strategies are beginning to take shape within materials science. These approaches lead to surrogate machine learning models that enable rapid predictions based purely on past data rather than by direct experimentation or by computations/simulations in which fundamental equations are explicitly solved. Data-centric informatics methods are becoming useful to determine material properties that are hard to measure or compute using traditional methods—due to the cost, time or effort involved—but for which reliable data either already exists or can be generated for at least a subset of the critical cases. Predictions are typically interpolative, involving fingerprinting a material numerically first, and then following a mapping (established via a learning algorithm) between the fingerprint and the property of interest. Fingerprints, also referred to as “descriptors”, may be of many types and scales, as dictated by the application domain and needs. Predictions may also be extrapolative—extending into new materials spaces—provided prediction uncertainties are properly taken into account. This article attempts to provide an overview of some of the recent successful data-driven “materials informatics” strategies undertaken in the last decade, with particular emphasis on the fingerprint or descriptor choices. The review also identifies some challenges the community is facing and those that should be overcome in the near future.</t>
+          <t>Psychology has historically been concerned, first and foremost, with explaining the causal mechanisms that give rise to behavior. Randomized, tightly controlled experiments are enshrined as the gold standard of psychological research, and there are endless investigations of the various mediating and moderating variables that govern various behaviors. We argue that psychology's near-total focus on explaining the causes of behavior has led much of the field to be populated by research programs that provide intricate theories of psychological mechanism but that have little (or unknown) ability to predict future behaviors with any appreciable accuracy. We propose that principles and techniques from the field of machine learning can help psychology become a more predictive science. We review some of the fundamental concepts and tools of machine learning and point out examples where these concepts have been used to conduct interesting and important psychological research that focuses on predictive research questions. We suggest that an increased focus on prediction, rather than explanation, can ultimately lead us to greater understanding of behavior.</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q140" t="inlineStr"/>
-      <c r="R140" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>1122</t>
+        </is>
+      </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>['Computer science', 'Informatics', 'Data science', 'Domain (mathematical analysis)', 'Fingerprint (computing)', 'Property (philosophy)', 'Artificial intelligence', 'Machine learning', 'Materials informatics', 'Computation', 'Data mining', 'Management science', 'Health informatics', 'Engineering informatics', 'Algorithm', 'Mathematics', 'Engineering']</t>
+          <t>['Psychology', 'Field (mathematics)', 'Psychological research', 'Mechanism (biology)', 'Focus (optics)', 'Psychological science', 'Cognitive psychology', 'Basic science', 'Experimental psychology', 'Contrast (vision)', 'Point (geometry)', 'Cognitive science', 'Epistemology', 'Social psychology', 'Artificial intelligence', 'Cognition', 'Computer science']</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>['US', 'DE']</t>
+          <t>['US']</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>['Jordan M, 2015, SCIENCE', 'Behler J, 2007, PHYSICAL REVIEW LETTERS', 'Feynman R, 1939, PHYSICAL REVIEW', 'Bartók A, 2010, PHYSICAL REVIEW LETTERS', 'Schmidt M, 2009, SCIENCE', 'Bartók A, 2013, PHYSICAL REVIEW B', 'Sánchez J, 1984, PHYSICA A STATISTICAL MECHANICS AND ITS APPLICATIONS', ', 1991, CHOICE REVIEWS ONLINE', 'Ercolessi F, 1994, EUROPHYSICS LETTERS (EPL)', 'Thompson A, 2014, JOURNAL OF COMPUTATIONAL PHYSICS', 'Forrester A, 2007, PROCEEDINGS OF THE ROYAL SOCIETY A MATHEMATICAL PHYSICAL AND ENGINEERING SCIENCES', 'Walle A, 2002, JOURNAL OF PHASE EQUILIBRIA AND DIFFUSION', 'Pilania G, 2013, SCIENTIFIC REPORTS', 'Snyder J, 2012, PHYSICAL REVIEW LETTERS', 'Li Z, 2015, PHYSICAL REVIEW LETTERS', 'Bartók A, 2015, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Hautier G, 2010, CHEMISTRY OF MATERIALS', 'Fontaine D, 1994, SOLID STATE PHYSICS', ', 2008, CHOICE REVIEWS ONLINE', 'Seko A, 2015, PHYSICAL REVIEW LETTERS', 'Behler J, 2014, JOURNAL OF PHYSICS CONDENSED MATTER', 'Faber F, 2016, PHYSICAL REVIEW LETTERS', 'Rupp M, 2015, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Laks D, 1992, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Lee J, 2016, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Szlachta W, 2014, PHYSICAL REVIEW B', 'Fernández M, 2014, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Behler J, 2008, PHYSICAL REVIEW LETTERS', 'Nelson L, 2013, PHYSICAL REVIEW B', 'Gupta A, 2015, ACTA MATERIALIA', 'Petch N, 1986, ACTA METALLURGICA', 'Aryal S, 2014, PHYSICA STATUS SOLIDI (B)', 'Ryzhov I, 2012, OPERATIONS RESEARCH', 'Huan T, 2015, PHYSICAL REVIEW B', 'Dey P, 2013, COMPUTATIONAL MATERIALS SCIENCE', 'Seko A, 2009, PHYSICAL REVIEW B', 'Snyder J, 2013, THE JOURNAL OF CHEMICAL PHYSICS', 'Lorenzini R, 2013, POLYMER', 'Theodoridis S, 2015, MACHINE LEARNING', 'Zunger A, 1994, NATO ASI SERIES. SERIES B : PHYSICS', 'Hume-Rothery W, 1947, ', 'Chatterjee S, 2007, MATERIALS SCIENCE AND TECHNOLOGY', 'Dudiy S, 2006, PHYSICAL REVIEW LETTERS', 'Mueller T, 2010, PHYSICAL REVIEW B', 'Cockayne E, 2010, PHYSICAL REVIEW B', 'Kalidindi S, 2012, ISRN MATERIALS SCIENCE', 'Adamson G, 1974, NATURE', 'Sanders J, 2015, ACS CENTRAL SCIENCE', 'Adamson G, 1974, JOURNAL OF CHEMICAL DOCUMENTATION', 'Powell W, 2011, WILEY ENCYCLOPEDIA OF OPERATIONS RESEARCH AND MANAGEMENT SCIENCE', 'Hall E, 1951, PROCEEDINGS OF THE PHYSICAL SOCIETY SECTION B', 'Rupp M, 2012, PHYSICAL REVIEW LETTERS', 'Ward L, 2016, NPJ COMPUTATIONAL MATERIALS', 'Ghiringhelli L, 2015, PHYSICAL REVIEW LETTERS', 'De S, 2016, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Xue D, 2016, NATURE COMMUNICATIONS', 'Meredig B, 2014, PHYSICAL REVIEW B', 'Micchelli C, 2004, NEURAL COMPUTATION', 'Mannodi‐Kanakkithodi A, 2016, SCIENTIFIC REPORTS', 'Botu V, 2014, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Oliynyk A, 2016, CHEMISTRY OF MATERIALS', 'Huan T, 2016, PROGRESS IN MATERIALS SCIENCE', 'Álvarez M, 2012, FOUNDATIONS AND TRENDS® IN MACHINE LEARNING', 'Panchal J, 2012, COMPUTER-AIDED DESIGN', 'Sharma V, 2014, NATURE COMMUNICATIONS', 'Hong W, 2015, THE JOURNAL OF PHYSICAL CHEMISTRY C', 'Seko A, 2014, PHYSICAL REVIEW B', 'Kusne A, 2014, SCIENTIFIC REPORTS', 'Emery A, 2016, CHEMISTRY OF MATERIALS', 'Kim C, 2016, CHEMISTRY OF MATERIALS', 'Li Z, 2016, CATALYSIS TODAY', 'Ward L, 2016, CURRENT OPINION IN SOLID STATE AND MATERIALS SCIENCE', 'Huan T, 2016, SCIENTIFIC DATA', 'Pilania G, 2016, FRONTIERS IN MATERIALS', 'Kim C, 2016, THE JOURNAL OF PHYSICAL CHEMISTRY C', 'Botu V, 2015, PHYSICAL REVIEW B', 'Mannodi‐Kanakkithodi A, 2016, ADVANCED MATERIALS', 'Lookman T, 2015, SPRINGER SERIES IN MATERIALS SCIENCE', 'Perdikaris P, 2015, PROCEEDINGS OF THE ROYAL SOCIETY A MATHEMATICAL PHYSICAL AND ENGINEERING SCIENCES', 'Powell W, 2012, WILEY SERIES IN PROBABILITY AND STATISTICS', 'Deml A, 2016, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Hattrick‐Simpers J, 2016, APL MATERIALS', 'Ashton M, 2016, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Kusne A, 2015, NANOTECHNOLOGY', 'Pilania G, 2015, PHYSICAL REVIEW B', 'Liu C, 2012, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Kalidindi S, 2016, MRS BULLETIN', 'Brough D, 2016, CURRENT OPINION IN SOLID STATE AND MATERIALS SCIENCE', 'Pilania G, 2017, CHEMISTRY OF MATERIALS', 'Kalidindi S, 2015, NANOTECHNOLOGY', 'Bunn J, 2016, JOM', 'Bialon A, 2016, CHEMISTRY OF MATERIALS', 'Srinivasan S, 2004, UNIVERSITY PRESS EBOOKS', 'Snyder J, 2015, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Fancher C, 2016, SCIENTIFIC REPORTS', 'Bianchini F, 2016, MODELLING AND SIMULATION IN MATERIALS SCIENCE AND ENGINEERING', 'Felsenstein J, 2008, SPRINGER SERIES IN STATISTICS', 'Mueller T, 2016, REVIEWS IN COMPUTATIONAL CHEMISTRY', 'Chmiela S, 2017, SCIENCE ADVANCES', 'Ercolessi F, 1994, ', 'Krevelen D, 2009, ELSEVIER EBOOKS', 'Deringer V, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Botu V, 2016, THE JOURNAL OF PHYSICAL CHEMISTRY C', 'Pilania G, 2016, COMPUTATIONAL MATERIALS SCIENCE', 'Green M, 2017, APPLIED PHYSICS REVIEWS', 'Jong M, 2016, SCIENTIFIC REPORTS', 'Glielmo A, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Xue D, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Legrain F, 2017, CHEMISTRY OF MATERIALS', 'Medasani B, 2016, NPJ COMPUTATIONAL MATERIALS', 'Ghiringhelli L, 2017, NEW JOURNAL OF PHYSICS', 'Lookman T, 2016, CURRENT OPINION IN SOLID STATE AND MATERIALS SCIENCE', 'Goldsmith B, 2017, NEW JOURNAL OF PHYSICS', 'Brough D, 2017, INTEGRATING MATERIALS AND MANUFACTURING INNOVATION', 'Theodoridis S, 2015, MACHINE LEARNING', 'L. G, 2017, MAX PLANCK DIGITAL LIBRARY', 'Mannodi‐Kanakkithodi A, 2017, CHEMISTRY OF MATERIALS', 'Jindal S, 2017, THE JOURNAL OF CHEMICAL PHYSICS', 'Botu V, 2017, COMPUTATIONAL MATERIALS SCIENCE', 'Brough D, 2017, INTEGRATING MATERIALS AND MANUFACTURING INNOVATION', 'Treich G, 2017, IEEE TRANSACTIONS ON DIELECTRICS AND ELECTRICAL INSULATION', 'J.W.C., 1961, JOURNAL OF THE LESS COMMON METALS', 'Gopnik A, 2017, SCIENTIFIC AMERICAN']</t>
+          <t>['Cohen J, 1992, PSYCHOLOGICAL BULLETIN', 'Friedman J, 2001, THE ANNALS OF STATISTICS', 'Hastie T, 2001, SPRINGER SERIES IN STATISTICS', 'Schmidhuber J, 2014, NEURAL NETWORKS', 'Zeiler M, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Gelman A, 2006, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'C. P, 2001, TECHNOMETRICS', 'Ekman P, 1992, COGNITION &amp; EMOTION', 'Aarts A, 2015, SCIENCE', 'Essen D, 2013, NEUROIMAGE', 'Biswal B, 2010, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Brysbaert M, 2009, BEHAVIOR RESEARCH METHODS', 'Bond R, 2012, NATURE', 'Dawes R, 1979, AMERICAN PSYCHOLOGIST', 'Vrieze S, 2012, PSYCHOLOGICAL METHODS', 'Pennebaker J, 1999, JOURNAL OF PERSONALITY AND SOCIAL PSYCHOLOGY', 'Shao J, 1993, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Ebstein R, 1996, NATURE GENETICS', 'Browne M, 2000, JOURNAL OF MATHEMATICAL PSYCHOLOGY', 'Klein R, 2014, SOCIAL PSYCHOLOGY', 'Ripke S, 2012, MOLECULAR PSYCHIATRY', 'Brewer J, 1998, SCIENCE', 'Meehl P, 1990, PSYCHOLOGICAL REPORTS', 'Du S, 2014, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Wainer H, 1976, PSYCHOLOGICAL BULLETIN', 'Gosling S, 2011, CYBERPSYCHOLOGY BEHAVIOR AND SOCIAL NETWORKING', 'Yarkoni T, 2010, JOURNAL OF RESEARCH IN PERSONALITY', 'Baayen R, 2011, PSYCHOLOGICAL REVIEW', 'Yarkoni T, 2009, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE', 'Whelan R, 2014, NATURE', 'McNeish D, 2015, MULTIVARIATE BEHAVIORAL RESEARCH', 'Fast L, 2008, JOURNAL OF PERSONALITY AND SOCIAL PSYCHOLOGY', 'Browne M, 2002, PSYCHOLOGICAL METHODS', 'Fleet D, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Munafò M, 2011, TRENDS IN COGNITIVE SCIENCES', 'Horn J, 2013, BRAIN IMAGING AND BEHAVIOR', 'Gelman A, 2009, AMERICAN SCIENTIST', 'Kurtz A, 1948, PERSONNEL PSYCHOLOGY', 'Wu S, 2007, THE CANADIAN JOURNAL OF CHEMICAL ENGINEERING', 'Mosier C, 1951, EDUCATIONAL AND PSYCHOLOGICAL MEASUREMENT', 'Hagerty M, 1991, PSYCHOMETRIKA', 'Strube M, 2006, BEHAVIOR RESEARCH METHODS', 'Davis‐Stober C, 2013, BEHAVIOR RESEARCH METHODS', 'Shear B, 2013, EDUCATIONAL AND PSYCHOLOGICAL MEASUREMENT', 'Jonas K, 2015, COMPREHENSIVE RESULTS IN SOCIAL PSYCHOLOGY', 'Yarkoni T, 2015, PEERJ', 'Wherry R, 1975, PERSONNEL PSYCHOLOGY', 'Schmitt N, 1977, PSYCHOLOGICAL BULLETIN', 'Wherry R, 1951, EDUCATIONAL AND PSYCHOLOGICAL MEASUREMENT', ', 2017, ANNUAL REVIEW OF PSYCHOLOGY', 'Deng J, 2009, 2009 IEEE CONFERENCE ON COMPUTER VISION AND PATTERN RECOGNITION', 'Tibshirani R, 1996, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Cohen P, 2014, PSYCHOLOGY PRESS EBOOKS', 'Wolpert D, 1997, IEEE TRANSACTIONS ON EVOLUTIONARY COMPUTATION', 'Burnham K, 2004, SOCIOLOGICAL METHODS &amp; RESEARCH', 'Simmons J, 2011, PSYCHOLOGICAL SCIENCE', 'Lesch K, 1996, SCIENCE', 'Breiman L, 2001, STATISTICAL SCIENCE', 'Tibshirani R, 2011, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Domingos P, 2012, COMMUNICATIONS OF THE ACM', 'Kosiński M, 2013, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Balota D, 2007, BEHAVIOR RESEARCH METHODS', 'Poropat A, 2009, PSYCHOLOGICAL BULLETIN', 'John L, 2012, PSYCHOLOGICAL SCIENCE', 'Wood A, 2014, NATURE GENETICS', 'Varma S, 2006, BMC BIOINFORMATICS', 'Cawley G, 2010, ', 'Cohen J, 1962, JOURNAL OF ABNORMAL &amp; SOCIAL PSYCHOLOGY', 'Rentfrow P, 2003, JOURNAL OF PERSONALITY AND SOCIAL PSYCHOLOGY', 'Dwan K, 2008, PLOS ONE', 'Ioannidis J, 2008, EPIDEMIOLOGY', 'Breiman L, 2001, ', 'Back M, 2010, PSYCHOLOGICAL SCIENCE', 'Wagenmakers E, 2012, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE', 'Krstajić D, 2014, JOURNAL OF CHEMINFORMATICS', 'New B, 2004, BEHAVIOR RESEARCH METHODS, INSTRUMENTS, &amp; COMPUTERS', 'Westfall J, 2014, JOURNAL OF EXPERIMENTAL PSYCHOLOGY GENERAL', 'Bakker M, 2012, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE', 'Sedlmeier P, 1989, PSYCHOLOGICAL BULLETIN', 'Nosek B, 2014, SOCIAL PSYCHOLOGY', 'Yarkoni T, 2008, PSYCHONOMIC BULLETIN &amp; REVIEW', 'Miller G, 2012, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE', 'Ferguson C, 2012, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE', 'Ioannidis J, 2012, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE', 'Westfall J, 2016, PLOS ONE', 'Judd C, 2016, ANNUAL REVIEW OF PSYCHOLOGY', 'Vazire S, 2004, JOURNAL OF PERSONALITY AND SOCIAL PSYCHOLOGY', 'Rowe M, 2008, DEVELOPMENTAL SCIENCE', 'Perry C, 2010, COGNITIVE PSYCHOLOGY', 'Holbert R, 2002, HUMAN COMMUNICATION RESEARCH', 'Apté C, 1997, FUTURE GENERATION COMPUTER SYSTEMS', 'Vitaro F, 1999, ADDICTION', 'Greenwald A, 2012, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE', 'Yap M, 2011, JOURNAL OF EXPERIMENTAL PSYCHOLOGY HUMAN PERCEPTION &amp; PERFORMANCE', 'Bunea F, 2010, NEUROIMAGE', 'Rissman J, 2010, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Rawlings D, 1997, PSYCHOLOGY OF MUSIC', 'Xu K, 2014, JOURNAL OF OPEN PSYCHOLOGY DATA', 'Yarkoni T, 2012, CURRENT DIRECTIONS IN PSYCHOLOGICAL SCIENCE', 'Bentley R, 2014, BEHAVIORAL AND BRAIN SCIENCES', 'Breiman L, 2001, MACHINE LEARNING', 'LeCun Y, 2015, NATURE', 'Hastie T, 2009, SPRINGER SERIES IN STATISTICS', 'Pinheiro J, 2000, STATISCTICS AND COMPUTING/STATISTICS AND COMPUTING', 'Cohen J, 1992, PSYCHOLOGICAL BULLETIN', 'Wood S, 2006, ', 'Cohen ⁄, 2013, ', 'Shmueli G, 2010, STATISTICAL SCIENCE', 'Nosek B, 2012, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE', 'Ebersole C, 2016, JOURNAL OF EXPERIMENTAL SOCIAL PSYCHOLOGY', 'Pennebaker J, 1999, JOURNAL OF PERSONALITY AND SOCIAL PSYCHOLOGY', 'Smıth D, 2016, MOLECULAR PSYCHIATRY', 'Browne M, 2002, PSYCHOLOGICAL METHODS', 'Loftus E, 1996, ', 'Ebersole C, 2016, ', 'Smıth D, 2016, MOLECULAR PSYCHIATRY']</t>
         </is>
       </c>
       <c r="V140" t="inlineStr">
@@ -16407,12 +16415,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>Ramprasad R, 2017, NPJ COMPUTATIONAL MATERIALS</t>
+          <t>Yarkoni T, 2017, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>Ramprasad R, 2017, NPJ COMPUTATIONAL MATERIALS</t>
+          <t>Yarkoni T, 2017, PERSPECTIVES ON PSYCHOLOGICAL SCIENCE</t>
         </is>
       </c>
     </row>
@@ -16448,7 +16456,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>125719</v>
+        <v>125821</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -16570,7 +16578,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
@@ -16891,22 +16899,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2041616772</t>
+          <t>https://openalex.org/W2540093921</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>10.1007/978-3-642-42051-1_16</t>
+          <t>10.7551/mitpress/8291.003.0006</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Challenges in Representation Learning: A Report on Three Machine Learning Contests</t>
+          <t>Foundations of Machine Learning</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -16920,60 +16928,64 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>1531</v>
+        <v>1088</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>LECTURE NOTES IN COMPUTER SCIENCE</t>
+          <t>THE MIT PRESS EBOOKS</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
+          <t>The MIT Press eBooks</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>['Ian Goodfellow', 'Dumitru Erhan', 'Pierre Carrier', 'Aaron Courville', 'Mehdi Mirza', 'Ben Hamner', 'Will Cukierski', 'Yichuan Tang', 'David S. Thaler', 'Dong‐Hyun Lee', 'Yingbo Zhou', 'Chetan Ramaiah', 'Fangxiang Feng', 'Ruifan Li', 'Xiaojie Wang', 'Dimitris Athanasakis', 'John Shawe‐Taylor', 'Maxim Milakov', 'John Park', 'Radu Tudor Ionescu', 'Marius Popescu', 'Cristian Grozea', 'James Bergstra', 'Jingjing Xie', 'Łukasz Romaszko', 'Bing Xu', 'Chuang Zhang', 'Yoshua Bengio']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>['Ian J. Goodfellow', 'Dumitru Erhan', 'Pierre Luc Carrier', 'Aaron Courville', 'Mehdi Mirza', 'Ben Hamner', 'Will Cukierski', 'Yichuan Tang', 'David Thaler', 'Dong-Hyun Lee', 'Yingbo Zhou', 'Chetan Ramaiah', 'Fangxiang Feng', 'Ruifan Li', 'Xiaojie Wang', 'Dimitris Athanasakis', 'John Shawe-Taylor', 'Maxim Milakov', 'John Park', 'Radu Ionescu', 'Marius Popescu', 'Cristian Grozea', 'James Bergstra', 'Jingjing Xie', 'Lukasz Romaszko', 'Bing Xu', 'Zhang Chuang', 'Yoshua Bengio']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Google, Venice, USA', 'Google†#TAB#', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Foundations of Machine LearningSoon we will embark on a theoretical study of AdaBoost in order to understand its properties, particularly its ability as a learning algorithm to generalize, that is, to make accurate predictions on data not seen during training.Before this will be possible, however, it will be necessary to take a step back to outline our approach to the more general problem of machine learning, including some fundamental general-purpose tools that will be invaluable in our analysis of AdaBoost.We study the basic problem of inferring from a set of training examples a classification rule whose predictions are highly accurate on freshly observed test data.On first encounter, it may seem questionable whether this kind of learning should even be possible.After all, why should there be any connection between the training and test examples, and why should it be possible to generalize from a relatively small number of training examples to a potentially vast universe of test examples?Although such objections have indeed often been the subject of philosophical debate, in this chapter we will identify an idealized but realistic model of the inference problem in which this kind of learning can be proved to be entirely feasible when certain conditions are satisfied.In particular, we will see that if we can find a simple rule that fits the training data well, and if the training set is not too small, then this rule will in fact generalize well, providing accurate predictions on previously unseen test examples.This is the basis of the approach presented in this chapter, and we will often use the general analysis on which it is founded to guide us in understanding how, why, and when learning is possible.We also outline in this chapter a mathematical framework for studying machine learning, one in which a precise formulation of the boosting problem can be clearly and naturally expressed.Note that, unlike the rest of the book, this chapter omits nearly all of the proofs of the main results since these have largely all appeared in various texts and articles.</t>
+        </is>
+      </c>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>52</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>['Computer science', 'Representation (politics)', 'Artificial intelligence', 'Feature learning', 'Machine learning', 'Learning to learn', 'Data science', 'Mathematics education', 'Psychology']</t>
+          <t>['Computer science', 'Artificial intelligence']</t>
         </is>
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>['CA', 'US']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>['Breiman L, 2001, MACHINE LEARNING', 'Cortes C, 1995, MACHINE LEARNING', 'Lowe D, 1999, ', 'Bengio Y, 2013, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Vincent P, 2008, ', 'Bradski G, 2000, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Ahn L, 2004, ', 'Grandvalet Y, 2004, ', 'Goodfellow I, 2013, ', 'Bengio Y, 2012, ', 'Ngiam J, 2011, NEURAL INFORMATION PROCESSING SYSTEMS', 'Ionescu R, 2014, ', 'Guyon I, 2011, ', 'Netzer Y, 2024, ', 'Tang Y, 2013, ARXIV (CORNELL UNIVERSITY)', 'Goodfellow I, 2013, ARXIV (CORNELL UNIVERSITY)', 'Goodfellow I, 2012, ARXIV (CORNELL UNIVERSITY)', 'Feng F, 2013, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
@@ -16989,34 +17001,34 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>Goodfellow I, 2013, LECTURE NOTES IN COMPUTER SCIENCE</t>
+          <t>NA, 2012, THE MIT PRESS EBOOKS</t>
         </is>
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>Goodfellow I, 2013, LECTURE NOTES IN COMPUTER SCIENCE</t>
+          <t>NA, 2012, THE MIT PRESS EBOOKS</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2540093921</t>
+          <t>https://openalex.org/W2041616772</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>10.7551/mitpress/8291.003.0006</t>
+          <t>10.1007/978-3-642-42051-1_16</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Foundations of Machine Learning</t>
+          <t>Challenges in Representation Learning: A Report on Three Machine Learning Contests</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -17030,64 +17042,60 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>1088</v>
+        <v>1531</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>THE MIT PRESS EBOOKS</t>
+          <t>LECTURE NOTES IN COMPUTER SCIENCE</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>The MIT Press eBooks</t>
+          <t>Lecture notes in computer science</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Ian Goodfellow', 'Dumitru Erhan', 'Pierre Carrier', 'Aaron Courville', 'Mehdi Mirza', 'Ben Hamner', 'Will Cukierski', 'Yichuan Tang', 'David S. Thaler', 'Dong‐Hyun Lee', 'Yingbo Zhou', 'Chetan Ramaiah', 'Fangxiang Feng', 'Ruifan Li', 'Xiaojie Wang', 'Dimitris Athanasakis', 'John Shawe‐Taylor', 'Maxim Milakov', 'John Park', 'Radu Tudor Ionescu', 'Marius Popescu', 'Cristian Grozea', 'James Bergstra', 'Jingjing Xie', 'Łukasz Romaszko', 'Bing Xu', 'Chuang Zhang', 'Yoshua Bengio']</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Ian J. Goodfellow', 'Dumitru Erhan', 'Pierre Luc Carrier', 'Aaron Courville', 'Mehdi Mirza', 'Ben Hamner', 'Will Cukierski', 'Yichuan Tang', 'David Thaler', 'Dong-Hyun Lee', 'Yingbo Zhou', 'Chetan Ramaiah', 'Fangxiang Feng', 'Ruifan Li', 'Xiaojie Wang', 'Dimitris Athanasakis', 'John Shawe-Taylor', 'Maxim Milakov', 'John Park', 'Radu Ionescu', 'Marius Popescu', 'Cristian Grozea', 'James Bergstra', 'Jingjing Xie', 'Lukasz Romaszko', 'Bing Xu', 'Zhang Chuang', 'Yoshua Bengio']</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Google, Venice, USA', 'Google†#TAB#', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL', 'Université de Montréal, Montréal, Canada', 'UNIVERSITE DE MONTREAL']</t>
         </is>
       </c>
       <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>Foundations of Machine LearningSoon we will embark on a theoretical study of AdaBoost in order to understand its properties, particularly its ability as a learning algorithm to generalize, that is, to make accurate predictions on data not seen during training.Before this will be possible, however, it will be necessary to take a step back to outline our approach to the more general problem of machine learning, including some fundamental general-purpose tools that will be invaluable in our analysis of AdaBoost.We study the basic problem of inferring from a set of training examples a classification rule whose predictions are highly accurate on freshly observed test data.On first encounter, it may seem questionable whether this kind of learning should even be possible.After all, why should there be any connection between the training and test examples, and why should it be possible to generalize from a relatively small number of training examples to a potentially vast universe of test examples?Although such objections have indeed often been the subject of philosophical debate, in this chapter we will identify an idealized but realistic model of the inference problem in which this kind of learning can be proved to be entirely feasible when certain conditions are satisfied.In particular, we will see that if we can find a simple rule that fits the training data well, and if the training set is not too small, then this rule will in fact generalize well, providing accurate predictions on previously unseen test examples.This is the basis of the approach presented in this chapter, and we will often use the general analysis on which it is founded to guide us in understanding how, why, and when learning is possible.We also outline in this chapter a mathematical framework for studying machine learning, one in which a precise formulation of the boosting problem can be clearly and naturally expressed.Note that, unlike the rest of the book, this chapter omits nearly all of the proofs of the main results since these have largely all appeared in various texts and articles.</t>
-        </is>
-      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>117</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>124</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>['Computer science', 'Artificial intelligence']</t>
+          <t>['Computer science', 'Representation (politics)', 'Artificial intelligence', 'Feature learning', 'Machine learning', 'Learning to learn', 'Data science', 'Mathematics education', 'Psychology']</t>
         </is>
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CA', 'US']</t>
         </is>
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Breiman L, 2001, MACHINE LEARNING', 'Cortes C, 1995, MACHINE LEARNING', 'Lowe D, 1999, ', 'Bengio Y, 2013, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Vincent P, 2008, ', 'Bradski G, 2000, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Ahn L, 2004, ', 'Grandvalet Y, 2004, ', 'Goodfellow I, 2013, ', 'Bengio Y, 2012, ', 'Ngiam J, 2011, NEURAL INFORMATION PROCESSING SYSTEMS', 'Ionescu R, 2014, ', 'Guyon I, 2011, ', 'Netzer Y, 2024, ', 'Tang Y, 2013, ARXIV (CORNELL UNIVERSITY)', 'Goodfellow I, 2013, ARXIV (CORNELL UNIVERSITY)', 'Goodfellow I, 2012, ARXIV (CORNELL UNIVERSITY)', 'Feng F, 2013, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V146" t="inlineStr">
@@ -17103,34 +17111,34 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>NA, 2012, THE MIT PRESS EBOOKS</t>
+          <t>Goodfellow I, 2013, LECTURE NOTES IN COMPUTER SCIENCE</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>NA, 2012, THE MIT PRESS EBOOKS</t>
+          <t>Goodfellow I, 2013, LECTURE NOTES IN COMPUTER SCIENCE</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2347129741</t>
+          <t>https://openalex.org/W2995098893</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>10.1038/nature17439</t>
+          <t>10.1186/s12911-019-1004-8</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Machine-learning-assisted materials discovery using failed experiments</t>
+          <t>Comparing different supervised machine learning algorithms for disease prediction</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -17144,72 +17152,76 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>1709</v>
+        <v>1628</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>NATURE</t>
+          <t>BMC MEDICAL INFORMATICS AND DECISION MAKING</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>BMC Medical Informatics and Decision Making</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>['Paul Raccuglia', 'Katherine C. Elbert', 'Philip Adler', 'Casey Falk', 'Malia B. Wenny', 'Aurelio Mollo', 'Mat\xadthias Zeller', 'Sorelle A. Friedler', 'Joshua Schrier', 'Alexander J. Norquist']</t>
+          <t>['Shahadat Uddin', 'Arif Khan', 'Md Ekramul Hossain', 'Mohammad Ali Moni']</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>['Paul Raccuglia', 'Katherine C. Elbert', 'Philip D. F. Adler', 'Casey Falk', 'Malia B. Wenny', 'Aurelio Mollo', 'Matthias Zeller', 'Sorelle A. Friedler', 'Joshua Schrier', 'Alexander J. Norquist']</t>
+          <t>['Shahadat Uddin', 'Arif Khan', 'Md Ekramul Hossain', 'Mohammad Ali Moni']</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>['Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA', 'Department of Chemistry, Purdue University, 560 Oval Drive, West Lafayette, Indiana 47907-2084, USA', 'Department of Chemistry, Purdue University, 560 Oval Drive, West Lafayette, 47907-2084, Indiana, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA']</t>
+          <t>['Complex Systems Research Group, Faculty of Engineering, The University of Sydney, Room 524, SIT Building (J12), Darlington, NSW, 2008, Australia. shahadat.uddin@sydney.edu.au', 'Complex Systems Research Group, Faculty of Engineering, The University of Sydney, Room 524, SIT Building (J12), Darlington, NSW, 2008, Australia', 'Complex Systems Research Group, Faculty of Engineering, The University of Sydney, Room 524, SIT Building (J12), Darlington, NSW, 2008, Australia', 'Health Market Quality Research Stream, Capital Markets CRC, Level 3, 55 Harrington Street, Sydney, NSW, Australia', 'Complex Systems Research Group, Faculty of Engineering, The University of Sydney, Room 524, SIT Building (J12), Darlington, NSW, 2008, Australia', 'Faculty of Medicine and Health, School of Medical Sciences, The University of Sydney, Camperdown, NSW, 2006, Australia']</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Alexander J. Norquist (corresponding author), Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA; Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
+          <t>Shahadat Uddin (corresponding author), Complex Systems Research Group, Faculty of Engineering, The University of Sydney, Room 524, SIT Building (J12), Darlington, NSW, 2008, Australia. shahadat.uddin@sydney.edu.au; Complex Systems Research Group, Faculty of Engineering, The University of Sydney, Room 524, SIT Building (J12), Darlington, NSW, 2008, Australia</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>BACKGROUND: Supervised machine learning algorithms have been a dominant method in the data mining field. Disease prediction using health data has recently shown a potential application area for these methods. This study ai7ms to identify the key trends among different types of supervised machine learning algorithms, and their performance and usage for disease risk prediction. METHODS: In this study, extensive research efforts were made to identify those studies that applied more than one supervised machine learning algorithm on single disease prediction. Two databases (i.e., Scopus and PubMed) were searched for different types of search items. Thus, we selected 48 articles in total for the comparison among variants supervised machine learning algorithms for disease prediction. RESULTS: We found that the Support Vector Machine (SVM) algorithm is applied most frequently (in 29 studies) followed by the Naïve Bayes algorithm (in 23 studies). However, the Random Forest (RF) algorithm showed superior accuracy comparatively. Of the 17 studies where it was applied, RF showed the highest accuracy in 9 of them, i.e., 53%. This was followed by SVM which topped in 41% of the studies it was considered. CONCLUSION: This study provides a wide overview of the relative performance of different variants of supervised machine learning algorithms for disease prediction. This important information of relative performance can be used to aid researchers in the selection of an appropriate supervised machine learning algorithm for their studies.</t>
+        </is>
+      </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>281</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>281</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>['Computer science', 'Data science', 'Artificial intelligence']</t>
+          <t>['Health informatics', 'Computer science', 'Machine learning', 'Artificial intelligence', 'Algorithm', 'Public health', 'Medicine', 'Nursing']</t>
         </is>
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>['US']</t>
+          <t>['AU']</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>['Chang C, 2011, ACM TRANSACTIONS ON INTELLIGENT SYSTEMS AND TECHNOLOGY', 'Cortes C, 1995, MACHINE LEARNING', 'Hastie T, 2001, SPRINGER SERIES IN STATISTICS', 'Hall M, 2009, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Allen F, 2002, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE', 'Joachims T, 1998, LECTURE NOTES IN COMPUTER SCIENCE', 'Zhou H, 2012, CHEMICAL REVIEWS', 'Stranks S, 2015, NATURE NANOTECHNOLOGY', 'Cheetham A, 1999, ANGEWANDTE CHEMIE INTERNATIONAL EDITION', 'Cundy C, 2003, CHEMICAL REVIEWS', 'Férey G, 2001, CHEMISTRY OF MATERIALS', 'Li Y, 2014, CHEMICAL REVIEWS', 'Hautier G, 2010, CHEMISTRY OF MATERIALS', 'Leach A, 2007, ', 'Gaultois M, 2013, CHEMISTRY OF MATERIALS', 'Colón Y, 2014, CHEMICAL SOCIETY REVIEWS', 'Riniker S, 2013, JOURNAL OF CHEMINFORMATICS', 'Sokolov A, 2011, NATURE COMMUNICATIONS', 'Üstün B, 2005, CHEMOMETRICS AND INTELLIGENT LABORATORY SYSTEMS', 'Fernández M, 2014, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Kalidindi S, 2015, ANNUAL REVIEW OF MATERIALS RESEARCH', 'Hachmann J, 2013, ENERGY &amp; ENVIRONMENTAL SCIENCE', 'Hastie T, 2008, SPRINGER SERIES IN STATISTICS', 'Rao C, 2006, CHEMICAL SOCIETY REVIEWS', 'Barakat N, 2008, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Beran G, 2014, ANGEWANDTE CHEMIE INTERNATIONAL EDITION', 'Haushalter R, 1992, CHEMISTRY OF MATERIALS', 'Férey G, 1995, JOURNAL OF FLUORINE CHEMISTRY', 'Rao C, 2000, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Wicker J, 2014, CRYSTENGCOMM', 'Martin R, 2013, THE JOURNAL OF PHYSICAL CHEMISTRY C', 'Thakur T, 2014, ANNUAL REVIEW OF PHYSICAL CHEMISTRY', 'Thangavelu S, 2015, CRYSTAL GROWTH &amp; DESIGN', 'Zhao J, 2014, CHINESE SCIENCE BULLETIN', 'Groom C, 2014, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE CRYSTAL ENGINEERING AND MATERIALS', 'Yang S, 2009, THE JOURNAL OF PHYSICAL CHEMISTRY C', 'Olshansky J, 2014, INORGANIC CHEMISTRY']</t>
+          <t>['Moher D, 2009, BMJ', 'Moher D, 2009, ANNALS OF INTERNAL MEDICINE', 'W H, 1990, CHOICE REVIEWS ONLINE', 'Rumelhart D, 1986, NATURE', 'Fawcett T, 2005, PATTERN RECOGNITION LETTERS', 'McCulloch W, 1943, BULLETIN OF MATHEMATICAL BIOLOGY', 'Cover T, 1967, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Quinlan J, 1986, MACHINE LEARNING', 'Demšar J, 2006, ', 'Sebastiani F, 2002, ACM COMPUTING SURVEYS', 'Falagas M, 2007, THE FASEB JOURNAL', 'Michalski R, 2013, ', 'Rish I, 2001, ', 'Levy O, 2015, TRANSACTIONS OF THE ASSOCIATION FOR COMPUTATIONAL LINGUISTICS', 'Delen D, 2004, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Sahami M, 1998, ', 'Cruz J, 2007, PUBMED', 'Palaniappan S, 2008, ', 'Aleskerov E, 2002, ', 'Chen H, 2012, EXPERT SYSTEMS WITH APPLICATIONS', 'Sinclair C, 2003, ', 'Long N, 2015, EXPERT SYSTEMS WITH APPLICATIONS', 'Culler S, 1998, MEDICAL CARE', 'Ayer T, 2009, RADIOGRAPHICS', 'Lundin J, 1999, ONCOLOGY', 'Farran B, 2013, BMJ OPEN', 'Davis D, 2009, DATA MINING AND KNOWLEDGE DISCOVERY', 'Zupan B, 2000, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Mani S, 2012, PUBMED', 'Kim J, 2015, HEALTHCARE INFORMATICS RESEARCH', 'Kim E, 2003, DECISION SUPPORT SYSTEMS', 'Eski̇dere Ö, 2011, EXPERT SYSTEMS WITH APPLICATIONS', 'Tapak L, 2013, HEALTHCARE INFORMATICS RESEARCH', 'Mahadevan S, 1998, ', 'Thenmozhi K, 2014, ', 'Bahadur S, 2013, IOSR JOURNAL OF AGRICULTURE AND VETERINARY SCIENCE', 'Cai L, 2015, PLOS ONE', 'Tang Z, 2013, PLOS ONE', 'Yao D, 2013, JOURNAL OF COMPUTERS', 'Uddin S, 2011, JOURNAL FOR HEALTHCARE QUALITY', 'Panicker N, 2016, INTERNATIONAL JOURNAL OF TELEMEDICINE AND APPLICATIONS', 'Lee P, 2007, OPHTHALMOLOGY', 'Yang J, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Aneja S, 2014, ', 'Yiannakoulias N, 2009, CHRONIC DISEASES AND INJURIES IN CANADA', 'Fisher E, 1990, INTERNATIONAL JOURNAL OF TECHNOLOGY ASSESSMENT IN HEALTH CARE', 'Toshniwal D, 2015, LECTURE NOTES IN COMPUTER SCIENCE', 'Chen C, 2012, ', 'Pedregosa F, 2012, ARXIV (CORNELL UNIVERSITY)', 'McCormick T, 2011, SSRN ELECTRONIC JOURNAL', 'Breiman L, 2001, MACHINE LEARNING', 'Moher D, 2009, PUBMED', 'Hosmer D, 2013, WILEY SERIES IN PROBABILITY AND STATISTICS', 'Touretzky D, 1989, ', 'Kavakiotis I, 2017, COMPUTATIONAL AND STRUCTURAL BIOTECHNOLOGY JOURNAL', 'Chen M, 2017, IEEE ACCESS', 'Lindley D, 1958, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Sisodia D, 2018, PROCEDIA COMPUTER SCIENCE', 'Charlton P, 2014, ', 'Lynch C, 2017, INTERNATIONAL JOURNAL OF MEDICAL INFORMATICS', 'LG A, 2013, JOURNAL OF HEALTH &amp; MEDICAL INFORMATICS', 'Anbarasi M, 2010, ', 'Hung C, 2017, ', 'Bhatla N, 2012, ', 'Jin B, 2018, IEEE ACCESS', 'Khateeb N, 2017, ', 'Hussain L, 2017, CANCER BIOMARKERS', 'Taslimitehrani V, 2016, JOURNAL OF BIOMEDICAL INFORMATICS', 'Alonso D, 2018, JOURNAL OF NUCLEAR CARDIOLOGY', 'Mansoor H, 2017, HEART &amp; LUNG', 'Behroozi M, 2016, INTERNATIONAL JOURNAL OF TELEMEDICINE AND APPLICATIONS', 'Mustaqeem A, 2017, ', 'Malik S, 2016, SPRINGERPLUS', 'Ani R, 2016, ', 'Juhola M, 2018, SCIENTIFIC REPORTS', 'Mohaimenul I, 2018, STUDIES IN HEALTH TECHNOLOGY AND INFORMATICS', 'Lu P, 2018, JOURNAL OF HEALTHCARE ENGINEERING', 'Atlas L, 1990, PROCEEDINGS OF THE IEEE', 'Marikani T, 2017, INTERNATIONAL JOURNAL OF COMPUTER APPLICATIONS', 'Borah M, 2018, INTERNATIONAL JOURNAL OF MACHINE LEARNING AND COMPUTING', 'Forssen H, 2017, STUDIES IN HEALTH TECHNOLOGY AND INFORMATICS', 'Puyalnithi T, 2016, INDIAN JOURNAL OF SCIENCE AND TECHNOLOGY', 'Zaret B, 1994, JOURNAL OF NUCLEAR CARDIOLOGY']</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
@@ -17225,34 +17237,34 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>Raccuglia P, 2016, NATURE</t>
+          <t>Uddin S, 2019, BMC MEDICAL INFORMATICS AND DECISION MAKING</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>Raccuglia P, 2016, NATURE</t>
+          <t>Uddin S, 2019, BMC MEDICAL INFORMATICS AND DECISION MAKING</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2995098893</t>
+          <t>https://openalex.org/W2347129741</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>10.1186/s12911-019-1004-8</t>
+          <t>10.1038/nature17439</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Comparing different supervised machine learning algorithms for disease prediction</t>
+          <t>Machine-learning-assisted materials discovery using failed experiments</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -17266,76 +17278,72 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1628</v>
+        <v>1710</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>BMC MEDICAL INFORMATICS AND DECISION MAKING</t>
+          <t>NATURE</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>BMC Medical Informatics and Decision Making</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>['Shahadat Uddin', 'Arif Khan', 'Md Ekramul Hossain', 'Mohammad Ali Moni']</t>
+          <t>['Paul Raccuglia', 'Katherine C. Elbert', 'Philip Adler', 'Casey Falk', 'Malia B. Wenny', 'Aurelio Mollo', 'Mat\xadthias Zeller', 'Sorelle A. Friedler', 'Joshua Schrier', 'Alexander J. Norquist']</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>['Shahadat Uddin', 'Arif Khan', 'Md Ekramul Hossain', 'Mohammad Ali Moni']</t>
+          <t>['Paul Raccuglia', 'Katherine C. Elbert', 'Philip D. F. Adler', 'Casey Falk', 'Malia B. Wenny', 'Aurelio Mollo', 'Matthias Zeller', 'Sorelle A. Friedler', 'Joshua Schrier', 'Alexander J. Norquist']</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['Complex Systems Research Group, Faculty of Engineering, The University of Sydney, Room 524, SIT Building (J12), Darlington, NSW, 2008, Australia. shahadat.uddin@sydney.edu.au', 'Complex Systems Research Group, Faculty of Engineering, The University of Sydney, Room 524, SIT Building (J12), Darlington, NSW, 2008, Australia', 'Complex Systems Research Group, Faculty of Engineering, The University of Sydney, Room 524, SIT Building (J12), Darlington, NSW, 2008, Australia', 'Health Market Quality Research Stream, Capital Markets CRC, Level 3, 55 Harrington Street, Sydney, NSW, Australia', 'Complex Systems Research Group, Faculty of Engineering, The University of Sydney, Room 524, SIT Building (J12), Darlington, NSW, 2008, Australia', 'Faculty of Medicine and Health, School of Medical Sciences, The University of Sydney, Camperdown, NSW, 2006, Australia']</t>
+          <t>['Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA', 'Department of Chemistry, Purdue University, 560 Oval Drive, West Lafayette, Indiana 47907-2084, USA', 'Department of Chemistry, Purdue University, 560 Oval Drive, West Lafayette, 47907-2084, Indiana, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA', 'Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Shahadat Uddin (corresponding author), Complex Systems Research Group, Faculty of Engineering, The University of Sydney, Room 524, SIT Building (J12), Darlington, NSW, 2008, Australia. shahadat.uddin@sydney.edu.au; Complex Systems Research Group, Faculty of Engineering, The University of Sydney, Room 524, SIT Building (J12), Darlington, NSW, 2008, Australia</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>BACKGROUND: Supervised machine learning algorithms have been a dominant method in the data mining field. Disease prediction using health data has recently shown a potential application area for these methods. This study ai7ms to identify the key trends among different types of supervised machine learning algorithms, and their performance and usage for disease risk prediction. METHODS: In this study, extensive research efforts were made to identify those studies that applied more than one supervised machine learning algorithm on single disease prediction. Two databases (i.e., Scopus and PubMed) were searched for different types of search items. Thus, we selected 48 articles in total for the comparison among variants supervised machine learning algorithms for disease prediction. RESULTS: We found that the Support Vector Machine (SVM) algorithm is applied most frequently (in 29 studies) followed by the Naïve Bayes algorithm (in 23 studies). However, the Random Forest (RF) algorithm showed superior accuracy comparatively. Of the 17 studies where it was applied, RF showed the highest accuracy in 9 of them, i.e., 53%. This was followed by SVM which topped in 41% of the studies it was considered. CONCLUSION: This study provides a wide overview of the relative performance of different variants of supervised machine learning algorithms for disease prediction. This important information of relative performance can be used to aid researchers in the selection of an appropriate supervised machine learning algorithm for their studies.</t>
-        </is>
-      </c>
+          <t>Alexander J. Norquist (corresponding author), Haverford College, 370 Lancaster Avenue, Haverford, Pennsylvania 19041, USA; Haverford College, 370 Lancaster Avenue, Haverford, 19041, Pennsylvania, USA</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>533</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>73</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>76</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>['Health informatics', 'Computer science', 'Machine learning', 'Artificial intelligence', 'Algorithm', 'Public health', 'Medicine', 'Nursing']</t>
+          <t>['Computer science', 'Data science', 'Artificial intelligence']</t>
         </is>
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>['AU']</t>
+          <t>['US']</t>
         </is>
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>['Moher D, 2009, BMJ', 'Moher D, 2009, ANNALS OF INTERNAL MEDICINE', 'W H, 1990, CHOICE REVIEWS ONLINE', 'Rumelhart D, 1986, NATURE', 'Fawcett T, 2005, PATTERN RECOGNITION LETTERS', 'McCulloch W, 1943, BULLETIN OF MATHEMATICAL BIOLOGY', 'Cover T, 1967, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Quinlan J, 1986, MACHINE LEARNING', 'Demšar J, 2006, ', 'Sebastiani F, 2002, ACM COMPUTING SURVEYS', 'Falagas M, 2007, THE FASEB JOURNAL', 'Michalski R, 2013, ', 'Rish I, 2001, ', 'Levy O, 2015, TRANSACTIONS OF THE ASSOCIATION FOR COMPUTATIONAL LINGUISTICS', 'Delen D, 2004, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Sahami M, 1998, ', 'Cruz J, 2007, PUBMED', 'Palaniappan S, 2008, ', 'Aleskerov E, 2002, ', 'Chen H, 2012, EXPERT SYSTEMS WITH APPLICATIONS', 'Sinclair C, 2003, ', 'Long N, 2015, EXPERT SYSTEMS WITH APPLICATIONS', 'Culler S, 1998, MEDICAL CARE', 'Ayer T, 2009, RADIOGRAPHICS', 'Lundin J, 1999, ONCOLOGY', 'Farran B, 2013, BMJ OPEN', 'Davis D, 2009, DATA MINING AND KNOWLEDGE DISCOVERY', 'Zupan B, 2000, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Mani S, 2012, PUBMED', 'Kim J, 2015, HEALTHCARE INFORMATICS RESEARCH', 'Kim E, 2003, DECISION SUPPORT SYSTEMS', 'Eski̇dere Ö, 2011, EXPERT SYSTEMS WITH APPLICATIONS', 'Tapak L, 2013, HEALTHCARE INFORMATICS RESEARCH', 'Mahadevan S, 1998, ', 'Thenmozhi K, 2014, ', 'Bahadur S, 2013, IOSR JOURNAL OF AGRICULTURE AND VETERINARY SCIENCE', 'Cai L, 2015, PLOS ONE', 'Tang Z, 2013, PLOS ONE', 'Yao D, 2013, JOURNAL OF COMPUTERS', 'Uddin S, 2011, JOURNAL FOR HEALTHCARE QUALITY', 'Panicker N, 2016, INTERNATIONAL JOURNAL OF TELEMEDICINE AND APPLICATIONS', 'Lee P, 2007, OPHTHALMOLOGY', 'Yang J, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Aneja S, 2014, ', 'Yiannakoulias N, 2009, CHRONIC DISEASES AND INJURIES IN CANADA', 'Fisher E, 1990, INTERNATIONAL JOURNAL OF TECHNOLOGY ASSESSMENT IN HEALTH CARE', 'Toshniwal D, 2015, LECTURE NOTES IN COMPUTER SCIENCE', 'Chen C, 2012, ', 'Pedregosa F, 2012, ARXIV (CORNELL UNIVERSITY)', 'McCormick T, 2011, SSRN ELECTRONIC JOURNAL', 'Breiman L, 2001, MACHINE LEARNING', 'Moher D, 2009, PUBMED', 'Hosmer D, 2013, WILEY SERIES IN PROBABILITY AND STATISTICS', 'Kavakiotis I, 2017, COMPUTATIONAL AND STRUCTURAL BIOTECHNOLOGY JOURNAL', 'Touretzky D, 1989, ', 'Chen M, 2017, IEEE ACCESS', 'Lindley D, 1958, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Sisodia D, 2018, PROCEDIA COMPUTER SCIENCE', 'Charlton P, 2014, ', 'Lynch C, 2017, INTERNATIONAL JOURNAL OF MEDICAL INFORMATICS', 'LG A, 2013, JOURNAL OF HEALTH &amp; MEDICAL INFORMATICS', 'Anbarasi M, 2010, ', 'Hung C, 2017, ', 'Bhatla N, 2012, ', 'Jin B, 2018, IEEE ACCESS', 'Khateeb N, 2017, ', 'Hussain L, 2017, CANCER BIOMARKERS', 'Taslimitehrani V, 2016, JOURNAL OF BIOMEDICAL INFORMATICS', 'Alonso D, 2018, JOURNAL OF NUCLEAR CARDIOLOGY', 'Mansoor H, 2017, HEART &amp; LUNG', 'Behroozi M, 2016, INTERNATIONAL JOURNAL OF TELEMEDICINE AND APPLICATIONS', 'Mustaqeem A, 2017, ', 'Malik S, 2016, SPRINGERPLUS', 'Ani R, 2016, ', 'Juhola M, 2018, SCIENTIFIC REPORTS', 'Mohaimenul I, 2018, STUDIES IN HEALTH TECHNOLOGY AND INFORMATICS', 'Lu P, 2018, JOURNAL OF HEALTHCARE ENGINEERING', 'Atlas L, 1990, PROCEEDINGS OF THE IEEE', 'Marikani T, 2017, INTERNATIONAL JOURNAL OF COMPUTER APPLICATIONS', 'Borah M, 2018, INTERNATIONAL JOURNAL OF MACHINE LEARNING AND COMPUTING', 'Forssen H, 2017, STUDIES IN HEALTH TECHNOLOGY AND INFORMATICS', 'Puyalnithi T, 2016, INDIAN JOURNAL OF SCIENCE AND TECHNOLOGY', 'Zaret B, 1994, JOURNAL OF NUCLEAR CARDIOLOGY']</t>
+          <t>['Chang C, 2011, ACM TRANSACTIONS ON INTELLIGENT SYSTEMS AND TECHNOLOGY', 'Cortes C, 1995, MACHINE LEARNING', 'Hastie T, 2001, SPRINGER SERIES IN STATISTICS', 'Hall M, 2009, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Allen F, 2002, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE', 'Joachims T, 1998, LECTURE NOTES IN COMPUTER SCIENCE', 'Zhou H, 2012, CHEMICAL REVIEWS', 'Stranks S, 2015, NATURE NANOTECHNOLOGY', 'Cheetham A, 1999, ANGEWANDTE CHEMIE INTERNATIONAL EDITION', 'Cundy C, 2003, CHEMICAL REVIEWS', 'Férey G, 2001, CHEMISTRY OF MATERIALS', 'Li Y, 2014, CHEMICAL REVIEWS', 'Hautier G, 2010, CHEMISTRY OF MATERIALS', 'Leach A, 2007, ', 'Gaultois M, 2013, CHEMISTRY OF MATERIALS', 'Colón Y, 2014, CHEMICAL SOCIETY REVIEWS', 'Riniker S, 2013, JOURNAL OF CHEMINFORMATICS', 'Sokolov A, 2011, NATURE COMMUNICATIONS', 'Üstün B, 2005, CHEMOMETRICS AND INTELLIGENT LABORATORY SYSTEMS', 'Fernández M, 2014, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Kalidindi S, 2015, ANNUAL REVIEW OF MATERIALS RESEARCH', 'Hachmann J, 2013, ENERGY &amp; ENVIRONMENTAL SCIENCE', 'Hastie T, 2008, SPRINGER SERIES IN STATISTICS', 'Rao C, 2006, CHEMICAL SOCIETY REVIEWS', 'Barakat N, 2008, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Beran G, 2014, ANGEWANDTE CHEMIE INTERNATIONAL EDITION', 'Haushalter R, 1992, CHEMISTRY OF MATERIALS', 'Férey G, 1995, JOURNAL OF FLUORINE CHEMISTRY', 'Rao C, 2000, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Wicker J, 2014, CRYSTENGCOMM', 'Martin R, 2013, THE JOURNAL OF PHYSICAL CHEMISTRY C', 'Thakur T, 2014, ANNUAL REVIEW OF PHYSICAL CHEMISTRY', 'Thangavelu S, 2015, CRYSTAL GROWTH &amp; DESIGN', 'Zhao J, 2014, CHINESE SCIENCE BULLETIN', 'Groom C, 2014, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE CRYSTAL ENGINEERING AND MATERIALS', 'Yang S, 2009, THE JOURNAL OF PHYSICAL CHEMISTRY C', 'Olshansky J, 2014, INORGANIC CHEMISTRY']</t>
         </is>
       </c>
       <c r="V148" t="inlineStr">
@@ -17351,12 +17359,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>Uddin S, 2019, BMC MEDICAL INFORMATICS AND DECISION MAKING</t>
+          <t>Raccuglia P, 2016, NATURE</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>Uddin S, 2019, BMC MEDICAL INFORMATICS AND DECISION MAKING</t>
+          <t>Raccuglia P, 2016, NATURE</t>
         </is>
       </c>
     </row>
@@ -17392,7 +17400,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -17485,22 +17493,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2186615578</t>
+          <t>https://openalex.org/W2981679558</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>10.48550/arxiv.1512.01274</t>
+          <t>10.1371/journal.pone.0224365</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MXNet: A Flexible and Efficient Machine Learning Library for Heterogeneous Distributed Systems</t>
+          <t>Machine learning algorithm validation with a limited sample size</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -17510,60 +17518,80 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>preprint</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>1922</v>
+        <v>1687</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>ARXIV (CORNELL UNIVERSITY)</t>
+          <t>PLOS ONE</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>arXiv (Cornell University)</t>
+          <t>PLoS ONE</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>['Tianqi Chen', 'Mu Li', 'Yutian Li', 'Min Lin', 'Naiyan Wang', 'Minjie Wang', 'Tianjun Xiao', 'Bing Xu', 'Chiyuan Zhang', 'Zheng Zhang']</t>
+          <t>['Andrius Vabalas', 'Emma Gowen', 'Ellen Poliakoff', 'Alexander J. Casson']</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>['Chen, Tianqi', 'Li, Mu', 'Li, Yutian', 'Lin, Min', 'Wang, Naiyan', 'Wang, Minjie', 'Xiao, Tianjun', 'Xu, Bing', 'Zhang, Chiyuan', 'Zhang, Zheng']</t>
+          <t>['Andrius Vabalas', 'Emma Gowen', 'Ellen Poliakoff', 'Alexander J. Casson']</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['Carnegie Mellon University']</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr"/>
+          <t>['Materials, Devices and Systems Division, School of Electrical and Electronic Engineering, The University of Manchester, Manchester, England, United Kingdom', 'School of Biological Sciences, The University of Manchester, Manchester, England, United Kingdom', 'School of Biological Sciences, The University of Manchester, Manchester, England, United Kingdom', 'Materials, Devices and Systems Division, School of Electrical and Electronic Engineering, The University of Manchester, Manchester, England, United Kingdom']</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Andrius Vabalas (corresponding author), Materials, Devices and Systems Division, School of Electrical and Electronic Engineering, The University of Manchester, Manchester, England, United Kingdom</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>MXNet is a multi-language machine learning (ML) library to ease the development of ML algorithms, especially for deep neural networks. Embedded in the host language, it blends declarative symbolic expression with imperative tensor computation. It offers auto differentiation to derive gradients. MXNet is computation and memory efficient and runs on various heterogeneous systems, ranging from mobile devices to distributed GPU clusters. This paper describes both the API design and the system implementation of MXNet, and explains how embedding of both symbolic expression and tensor operation is handled in a unified fashion. Our preliminary experiments reveal promising results on large scale deep neural network applications using multiple GPU machines.</t>
-        </is>
-      </c>
-      <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr"/>
-      <c r="R150" t="inlineStr"/>
+          <t>Advances in neuroimaging, genomic, motion tracking, eye-tracking and many other technology-based data collection methods have led to a torrent of high dimensional datasets, which commonly have a small number of samples because of the intrinsic high cost of data collection involving human participants. High dimensional data with a small number of samples is of critical importance for identifying biomarkers and conducting feasibility and pilot work, however it can lead to biased machine learning (ML) performance estimates. Our review of studies which have applied ML to predict autistic from non-autistic individuals showed that small sample size is associated with higher reported classification accuracy. Thus, we have investigated whether this bias could be caused by the use of validation methods which do not sufficiently control overfitting. Our simulations show that K-fold Cross-Validation (CV) produces strongly biased performance estimates with small sample sizes, and the bias is still evident with sample size of 1000. Nested CV and train/test split approaches produce robust and unbiased performance estimates regardless of sample size. We also show that feature selection if performed on pooled training and testing data is contributing to bias considerably more than parameter tuning. In addition, the contribution to bias by data dimensionality, hyper-parameter space and number of CV folds was explored, and validation methods were compared with discriminable data. The results suggest how to design robust testing methodologies when working with small datasets and how to interpret the results of other studies based on what validation method was used.</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>e0224365</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>e0224365</t>
+        </is>
+      </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>['Computer science', 'Distributed computing', 'Artificial intelligence']</t>
+          <t>['Overfitting', 'Sample size determination', 'Computer science', 'Artificial intelligence', 'Cross-validation', 'Data collection', 'Machine learning', 'Selection bias', 'Sample (material)', 'Statistics', 'Feature selection', 'Data mining', 'Pattern recognition (psychology)', 'Mathematics', 'Artificial neural network']</t>
         </is>
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>['US']</t>
+          <t>['GB']</t>
         </is>
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>['Russakovsky O, 2015, INTERNATIONAL JOURNAL OF COMPUTER VISION', 'Jia Y, 2014, ', 'Dean J, 2012, ', 'Collobert R, 2011, INFOSCIENCE (ECOLE POLYTECHNIQUE FÉDÉRALE DE LAUSANNE)', 'Li M, 2014, OPERATING SYSTEMS DESIGN AND IMPLEMENTATION', 'Li M, 2014, NEURAL INFORMATION PROCESSING SYSTEMS', 'Ioffe S, 2024, ARXIV (CORNELL UNIVERSITY)', 'Bastien F, 2012, ARXIV (CORNELL UNIVERSITY)', 'Lin M, 2014, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>['Chang C, 2011, ACM TRANSACTIONS ON INTELLIGENT SYSTEMS AND TECHNOLOGY', 'Sudlow C, 2015, PLOS MEDICINE', 'Boser B, 1992, ', 'Stone M, 1974, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Ferrari V, 2008, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Guyon I, 2002, MACHINE LEARNING', 'Saeys Y, 2007, BIOINFORMATICS', 'Libbrecht M, 2015, NATURE REVIEWS GENETICS', 'Varma S, 2006, BMC BIOINFORMATICS', 'Cawley G, 2010, ', 'Raudys Š, 1991, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Krstajić D, 2014, JOURNAL OF CHEMINFORMATICS', 'Hira Z, 2015, ADVANCES IN BIOINFORMATICS', 'Arbabshirani M, 2016, NEUROIMAGE', 'Varoquaux G, 2016, NEUROIMAGE', 'Bolón‐Canedo V, 2014, INFORMATION SCIENCES', 'Combrisson E, 2015, JOURNAL OF NEUROSCIENCE METHODS', 'Jain A, 1982, HANDBOOK OF STATISTICS', 'Figueroa R, 2012, BMC MEDICAL INFORMATICS AND DECISION MAKING', 'Beleites C, 2012, ANALYTICA CHIMICA ACTA', 'Hua J, 2004, COMPUTER APPLICATIONS IN THE BIOSCIENCES', 'Devos O, 2008, CHEMOMETRICS AND INTELLIGENT LABORATORY SYSTEMS', 'Mukherjee S, 2003, JOURNAL OF COMPUTATIONAL BIOLOGY', 'Hyde K, 2019, REVIEW JOURNAL OF AUTISM AND DEVELOPMENTAL DISORDERS', 'Bone D, 2014, JOURNAL OF AUTISM AND DEVELOPMENTAL DISORDERS', 'Kassraian P, 2016, FRONTIERS IN PSYCHIATRY', 'Dernoncourt D, 2013, COMPUTATIONAL STATISTICS &amp; DATA ANALYSIS', 'Devadoss F, 2014, JOURNAL OF CHEMINFORMATICS', 'Kanal L, 1971, PATTERN RECOGNITION', 'Pedregosa F, 2012, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V150" t="inlineStr">
@@ -17579,34 +17607,34 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>Chen T, 2015, ARXIV (CORNELL UNIVERSITY)</t>
+          <t>Vabalas A, 2019, PLOS ONE</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>Chen T, 2015, ARXIV (CORNELL UNIVERSITY)</t>
+          <t>Vabalas A, 2019, PLOS ONE</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2981679558</t>
+          <t>https://openalex.org/W2186615578</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>10.1371/journal.pone.0224365</t>
+          <t>10.48550/arxiv.1512.01274</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Machine learning algorithm validation with a limited sample size</t>
+          <t>MXNet: A Flexible and Efficient Machine Learning Library for Heterogeneous Distributed Systems</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -17616,80 +17644,60 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>preprint</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>1687</v>
+        <v>1922</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>PLOS ONE</t>
+          <t>ARXIV (CORNELL UNIVERSITY)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>PLoS ONE</t>
+          <t>arXiv (Cornell University)</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>['Andrius Vabalas', 'Emma Gowen', 'Ellen Poliakoff', 'Alexander J. Casson']</t>
+          <t>['Tianqi Chen', 'Mu Li', 'Yutian Li', 'Min Lin', 'Naiyan Wang', 'Minjie Wang', 'Tianjun Xiao', 'Bing Xu', 'Chiyuan Zhang', 'Zheng Zhang']</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>['Andrius Vabalas', 'Emma Gowen', 'Ellen Poliakoff', 'Alexander J. Casson']</t>
+          <t>['Chen, Tianqi', 'Li, Mu', 'Li, Yutian', 'Lin, Min', 'Wang, Naiyan', 'Wang, Minjie', 'Xiao, Tianjun', 'Xu, Bing', 'Zhang, Chiyuan', 'Zhang, Zheng']</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['Materials, Devices and Systems Division, School of Electrical and Electronic Engineering, The University of Manchester, Manchester, England, United Kingdom', 'School of Biological Sciences, The University of Manchester, Manchester, England, United Kingdom', 'School of Biological Sciences, The University of Manchester, Manchester, England, United Kingdom', 'Materials, Devices and Systems Division, School of Electrical and Electronic Engineering, The University of Manchester, Manchester, England, United Kingdom']</t>
-        </is>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>Andrius Vabalas (corresponding author), Materials, Devices and Systems Division, School of Electrical and Electronic Engineering, The University of Manchester, Manchester, England, United Kingdom</t>
-        </is>
-      </c>
+          <t>['Carnegie Mellon University']</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
-          <t>Advances in neuroimaging, genomic, motion tracking, eye-tracking and many other technology-based data collection methods have led to a torrent of high dimensional datasets, which commonly have a small number of samples because of the intrinsic high cost of data collection involving human participants. High dimensional data with a small number of samples is of critical importance for identifying biomarkers and conducting feasibility and pilot work, however it can lead to biased machine learning (ML) performance estimates. Our review of studies which have applied ML to predict autistic from non-autistic individuals showed that small sample size is associated with higher reported classification accuracy. Thus, we have investigated whether this bias could be caused by the use of validation methods which do not sufficiently control overfitting. Our simulations show that K-fold Cross-Validation (CV) produces strongly biased performance estimates with small sample sizes, and the bias is still evident with sample size of 1000. Nested CV and train/test split approaches produce robust and unbiased performance estimates regardless of sample size. We also show that feature selection if performed on pooled training and testing data is contributing to bias considerably more than parameter tuning. In addition, the contribution to bias by data dimensionality, hyper-parameter space and number of CV folds was explored, and validation methods were compared with discriminable data. The results suggest how to design robust testing methodologies when working with small datasets and how to interpret the results of other studies based on what validation method was used.</t>
-        </is>
-      </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>e0224365</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr">
-        <is>
-          <t>e0224365</t>
-        </is>
-      </c>
+          <t>MXNet is a multi-language machine learning (ML) library to ease the development of ML algorithms, especially for deep neural networks. Embedded in the host language, it blends declarative symbolic expression with imperative tensor computation. It offers auto differentiation to derive gradients. MXNet is computation and memory efficient and runs on various heterogeneous systems, ranging from mobile devices to distributed GPU clusters. This paper describes both the API design and the system implementation of MXNet, and explains how embedding of both symbolic expression and tensor operation is handled in a unified fashion. Our preliminary experiments reveal promising results on large scale deep neural network applications using multiple GPU machines.</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
-          <t>['Overfitting', 'Sample size determination', 'Computer science', 'Artificial intelligence', 'Cross-validation', 'Data collection', 'Machine learning', 'Selection bias', 'Sample (material)', 'Statistics', 'Feature selection', 'Data mining', 'Pattern recognition (psychology)', 'Mathematics', 'Artificial neural network']</t>
+          <t>['Computer science', 'Distributed computing', 'Artificial intelligence']</t>
         </is>
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>['GB']</t>
+          <t>['US']</t>
         </is>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>['Chang C, 2011, ACM TRANSACTIONS ON INTELLIGENT SYSTEMS AND TECHNOLOGY', 'Sudlow C, 2015, PLOS MEDICINE', 'Boser B, 1992, ', 'Stone M, 1974, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Ferrari V, 2008, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Guyon I, 2002, MACHINE LEARNING', 'Saeys Y, 2007, BIOINFORMATICS', 'Libbrecht M, 2015, NATURE REVIEWS GENETICS', 'Varma S, 2006, BMC BIOINFORMATICS', 'Cawley G, 2010, ', 'Raudys Š, 1991, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Krstajić D, 2014, JOURNAL OF CHEMINFORMATICS', 'Hira Z, 2015, ADVANCES IN BIOINFORMATICS', 'Arbabshirani M, 2016, NEUROIMAGE', 'Varoquaux G, 2016, NEUROIMAGE', 'Bolón‐Canedo V, 2014, INFORMATION SCIENCES', 'Combrisson E, 2015, JOURNAL OF NEUROSCIENCE METHODS', 'Jain A, 1982, HANDBOOK OF STATISTICS', 'Figueroa R, 2012, BMC MEDICAL INFORMATICS AND DECISION MAKING', 'Beleites C, 2012, ANALYTICA CHIMICA ACTA', 'Hua J, 2004, COMPUTER APPLICATIONS IN THE BIOSCIENCES', 'Devos O, 2008, CHEMOMETRICS AND INTELLIGENT LABORATORY SYSTEMS', 'Mukherjee S, 2003, JOURNAL OF COMPUTATIONAL BIOLOGY', 'Hyde K, 2019, REVIEW JOURNAL OF AUTISM AND DEVELOPMENTAL DISORDERS', 'Bone D, 2014, JOURNAL OF AUTISM AND DEVELOPMENTAL DISORDERS', 'Kassraian P, 2016, FRONTIERS IN PSYCHIATRY', 'Dernoncourt D, 2013, COMPUTATIONAL STATISTICS &amp; DATA ANALYSIS', 'Devadoss F, 2014, JOURNAL OF CHEMINFORMATICS', 'Kanal L, 1971, PATTERN RECOGNITION', 'Pedregosa F, 2012, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>['Russakovsky O, 2015, INTERNATIONAL JOURNAL OF COMPUTER VISION', 'Jia Y, 2014, ', 'Dean J, 2012, ', 'Collobert R, 2011, INFOSCIENCE (ECOLE POLYTECHNIQUE FÉDÉRALE DE LAUSANNE)', 'Li M, 2014, OPERATING SYSTEMS DESIGN AND IMPLEMENTATION', 'Li M, 2014, NEURAL INFORMATION PROCESSING SYSTEMS', 'Ioffe S, 2024, ARXIV (CORNELL UNIVERSITY)', 'Bastien F, 2012, ARXIV (CORNELL UNIVERSITY)', 'Lin M, 2014, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
@@ -17705,12 +17713,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>Vabalas A, 2019, PLOS ONE</t>
+          <t>Chen T, 2015, ARXIV (CORNELL UNIVERSITY)</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>Vabalas A, 2019, PLOS ONE</t>
+          <t>Chen T, 2015, ARXIV (CORNELL UNIVERSITY)</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17754,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -17827,22 +17835,18 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2513506629</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>10.1126/science.aaf7894</t>
-        </is>
-      </c>
+          <t>https://openalex.org/W2182361439</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Combining satellite imagery and machine learning to predict poverty</t>
+          <t>Efficient and robust automated machine learning</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -17856,76 +17860,68 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1641</v>
+        <v>1259</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>SCIENCE</t>
+          <t>NEURAL INFORMATION PROCESSING SYSTEMS</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Neural Information Processing Systems</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>['Neal Jean', 'Marshall Burke', 'Sang Michael Xie', 'W. Matthew Davis', 'David B. Lobell', 'Stefano Ermon']</t>
+          <t>['Matthias Feurer', 'Aaron Klein', 'Katharina Eggensperger', 'Jost Tobias Springenberg', 'Manuel Blum', 'Frank Hutter']</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>['Neal Jean', 'Marshall Burke', 'Michael Xie', 'W. Matthew Davis', 'David B. Lobell', 'Stefano Ermon']</t>
+          <t>['Matthias Feurer', 'Aaron Klein', 'Katharina Eggensperger', 'Jost Tobias Springenberg', 'Manuel Blum', 'Frank Hutter']</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['Department of Computer Science, Stanford University, Stanford, CA, USA', 'Department of Electrical Engineering, Stanford University, Stanford, CA, USA', 'Center on Food Security and the Environment, Stanford University, Stanford, CA, USA', 'Department of Earth System Science, Stanford University, Stanford, CA, USA', 'National Bureau of Economic Research, Boston, MA, USA', 'Department of Computer Science, Stanford University, Stanford, CA, USA', 'Center on Food Security and the Environment, Stanford University, Stanford, CA, USA', 'Center on Food Security and the Environment, Stanford University, Stanford, CA, USA', 'Department of Earth System Science, Stanford University, Stanford, CA, USA', 'Department of Computer Science, Stanford University, Stanford, CA, USA']</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>Marshall Burke (corresponding author), Center on Food Security and the Environment, Stanford University, Stanford, CA, USA; Department of Earth System Science, Stanford University, Stanford, CA, USA; National Bureau of Economic Research, Boston, MA, USA</t>
-        </is>
-      </c>
+          <t>['Department of Computer Science , University of Freiburg , Germany', 'Department of Computer Science , University of Freiburg , Germany', 'Department of Computer Science , University of Freiburg , Germany', 'Department of Computer Science , University of Freiburg , Germany', 'Department of Computer Science , University of Freiburg , Germany', 'Department of Computer Science , University of Freiburg , Germany']</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
-          <t>Reliable data on economic livelihoods remain scarce in the developing world, hampering efforts to study these outcomes and to design policies that improve them. Here we demonstrate an accurate, inexpensive, and scalable method for estimating consumption expenditure and asset wealth from high-resolution satellite imagery. Using survey and satellite data from five African countries--Nigeria, Tanzania, Uganda, Malawi, and Rwanda--we show how a convolutional neural network can be trained to identify image features that can explain up to 75% of the variation in local-level economic outcomes. Our method, which requires only publicly available data, could transform efforts to track and target poverty in developing countries. It also demonstrates how powerful machine learning techniques can be applied in a setting with limited training data, suggesting broad potential application across many scientific domains.</t>
+          <t>The success of machine learning in a broad range of applications has led to an ever-growing demand for machine learning systems that can be used off the shelf by non-experts. To be effective in practice, such systems need to automatically choose a good algorithm and feature preprocessing steps for a new dataset at hand, and also set their respective hyperparameters. Recent work has started to tackle this automated machine learning (AutoML) problem with the help of efficient Bayesian optimization methods. Building on this, we introduce a robust new AutoML system based on scikit-learn (using 15 classifiers, 14 feature preprocessing methods, and 4 data preprocessing methods, giving rise to a structured hypothesis space with 110 hyperparameters). This system, which we dub AUTO-SKLEARN, improves on existing AutoML methods by automatically taking into account past performance on similar datasets, and by constructing ensembles from the models evaluated during the optimization. Our system won the first phase of the ongoing ChaLearn AutoML challenge, and our comprehensive analysis on over 100 diverse datasets shows that it substantially outperforms the previous state of the art in AutoML. We also demonstrate the performance gains due to each of our contributions and derive insights into the effectiveness of the individual components of AUTO-SKLEARN.</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>6301</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>['Proxy (statistics)', 'Poverty', 'Satellite imagery', 'Satellite', 'Daytime', 'Consumption (sociology)', 'Perspective (graphical)', 'Computer science', 'Remote sensing', 'Meteorology', 'Artificial intelligence', 'Machine learning', 'Geography', 'Economic growth', 'Economics', 'Geology', 'Sociology', 'Atmospheric sciences', 'Engineering']</t>
+          <t>['Hyperparameter', 'Machine learning', 'Artificial intelligence', 'Computer science', 'Preprocessor', 'Bayesian optimization', 'Feature (linguistics)', 'Set (abstract data type)', 'Bayesian probability']</t>
         </is>
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>['US']</t>
+          <t>['DE']</t>
         </is>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>['LeCun Y, 2015, NATURE', 'Krizhevsky A, 2017, COMMUNICATIONS OF THE ACM', 'Russakovsky O, 2015, INTERNATIONAL JOURNAL OF COMPUTER VISION', 'Pan S, 2009, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Filmer D, 2001, DEMOGRAPHY', 'Razavian A, 2014, ', 'Chatfield K, 2014, ', 'Filmer D, 2001, DEMOGRAPHY', 'Chen X, 2011, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Sahn D, 2003, REVIEW OF INCOME AND WEALTH', 'Blumenstock J, 2015, SCIENCE', 'Mnih V, 2010, LECTURE NOTES IN COMPUTER SCIENCE', 'Michalopoulos S, 2013, THE QUARTERLY JOURNAL OF ECONOMICS', 'Balk D, 2006, ADVANCES IN PARASITOLOGY/ADVANCES IN PARASITOLOGY', 'Xie S, 2016, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Pinkovskiy M, 2016, THE QUARTERLY JOURNAL OF ECONOMICS', 'Devarajan S, 2013, REVIEW OF INCOME AND WEALTH', 'Sandefur J, 2015, THE JOURNAL OF DEVELOPMENT STUDIES', 'Jerven M, 2013, VERFASSUNG IN RECHT UND ÜBERSEE', 'Hand E, 2015, SCIENCE', 'Hong L, 2016, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE']</t>
+          <t>['Breiman L, 2001, MACHINE LEARNING', 'Hall M, 2009, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Wolpert D, 1992, NEURAL NETWORKS', 'Bergstra J, 2011, ', 'Hutter F, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Fulkerson B, 1995, TECHNOMETRICS', 'Thornton C, 2013, ', 'Vanschoren J, 2014, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Caruana R, 2004, ', 'Hamerly G, 2003, ', 'Brazdil P, 2009, ', 'Feurer M, 2015, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Pfahringer B, 2000, ', 'Komer B, 2014, PROCEEDINGS OF THE PYTHON IN SCIENCE CONFERENCES', 'Bardenet R, 2013, HAL (LE CENTRE POUR LA COMMUNICATION SCIENTIFIQUE DIRECTE)', 'Guyon I, 2010, ', 'Reif M, 2012, MACHINE LEARNING', 'Yogatama D, 2014, INTERNATIONAL CONFERENCE ON ARTIFICIAL INTELLIGENCE AND STATISTICS', 'Gomes T, 2011, NEUROCOMPUTING', 'Guyon I, 2015, ', 'Caruana R, 2006, PROCEEDINGS', 'Lacoste A, 2014, ', 'Pedregosa F, 2012, ARXIV (CORNELL UNIVERSITY)', 'Snoek J, 2012, ARXIV (CORNELL UNIVERSITY)', 'Brochu E, 2010, ARXIV (CORNELL UNIVERSITY)', 'Kalousis A, 2002, ARCHIVE OUVERTE UNIGE (UNIVERSITY OF GENEVA)']</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
@@ -17941,30 +17937,34 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>Jean N, 2016, SCIENCE</t>
+          <t>Feurer M, 2015, NEURAL INFORMATION PROCESSING SYSTEMS</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>Jean N, 2016, SCIENCE</t>
+          <t>Feurer M, 2015, NEURAL INFORMATION PROCESSING SYSTEMS</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2182361439</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr"/>
+          <t>https://openalex.org/W1549998098</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>10.1201/b17476</t>
+        </is>
+      </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Efficient and robust automated machine learning</t>
+          <t>Machine Learning: An Algorithmic Perspective</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -17974,72 +17974,56 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>book</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>1259</v>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>NEURAL INFORMATION PROCESSING SYSTEMS</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Neural Information Processing Systems</t>
-        </is>
-      </c>
+        <v>1082</v>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
-          <t>['Matthias Feurer', 'Aaron Klein', 'Katharina Eggensperger', 'Jost Tobias Springenberg', 'Manuel Blum', 'Frank Hutter']</t>
+          <t>['Stephen Marsland']</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>['Matthias Feurer', 'Aaron Klein', 'Katharina Eggensperger', 'Jost Tobias Springenberg', 'Manuel Blum', 'Frank Hutter']</t>
+          <t>['Stephen Marsland']</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['Department of Computer Science , University of Freiburg , Germany', 'Department of Computer Science , University of Freiburg , Germany', 'Department of Computer Science , University of Freiburg , Germany', 'Department of Computer Science , University of Freiburg , Germany', 'Department of Computer Science , University of Freiburg , Germany', 'Department of Computer Science , University of Freiburg , Germany']</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen Marsland (corresponding author), </t>
+        </is>
+      </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>The success of machine learning in a broad range of applications has led to an ever-growing demand for machine learning systems that can be used off the shelf by non-experts. To be effective in practice, such systems need to automatically choose a good algorithm and feature preprocessing steps for a new dataset at hand, and also set their respective hyperparameters. Recent work has started to tackle this automated machine learning (AutoML) problem with the help of efficient Bayesian optimization methods. Building on this, we introduce a robust new AutoML system based on scikit-learn (using 15 classifiers, 14 feature preprocessing methods, and 4 data preprocessing methods, giving rise to a structured hypothesis space with 110 hyperparameters). This system, which we dub AUTO-SKLEARN, improves on existing AutoML methods by automatically taking into account past performance on similar datasets, and by constructing ensembles from the models evaluated during the optimization. Our system won the first phase of the ongoing ChaLearn AutoML challenge, and our comprehensive analysis on over 100 diverse datasets shows that it substantially outperforms the previous state of the art in AutoML. We also demonstrate the performance gains due to each of our contributions and derive insights into the effectiveness of the individual components of AUTO-SKLEARN.</t>
-        </is>
-      </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>Traditional books on machine learning can be divided into two groups - those aimed at advanced undergraduates or early postgraduates with reasonable mathematical knowledge and those that are primers on how to code algorithms. The field is ready for a text that not only demonstrates how to use the algorithms that make up machine learning methods, but also provides the background needed to understand how and why these algorithms work. Machine Learning: An Algorithmic Perspective is that text.Theory Backed up by Practical ExamplesThe book covers neural networks, graphical models, reinforcement le</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>2755</t>
-        </is>
-      </c>
-      <c r="R154" t="inlineStr">
-        <is>
-          <t>2763</t>
-        </is>
-      </c>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>['Hyperparameter', 'Machine learning', 'Artificial intelligence', 'Computer science', 'Preprocessor', 'Bayesian optimization', 'Feature (linguistics)', 'Set (abstract data type)', 'Bayesian probability']</t>
+          <t>['Python (programming language)', 'Computer science', 'Implementation', 'Perspective (graphical)', 'Artificial intelligence', 'Reinforcement learning', 'Dimensionality reduction', 'Theoretical computer science', 'Machine learning', 'Programming language']</t>
         </is>
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>['DE']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>['Breiman L, 2001, MACHINE LEARNING', 'Hall M, 2009, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Wolpert D, 1992, NEURAL NETWORKS', 'Bergstra J, 2011, ', 'Hutter F, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Fulkerson B, 1995, TECHNOMETRICS', 'Thornton C, 2013, ', 'Vanschoren J, 2014, ACM SIGKDD EXPLORATIONS NEWSLETTER', 'Caruana R, 2004, ', 'Hamerly G, 2003, ', 'Brazdil P, 2009, ', 'Feurer M, 2015, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Pfahringer B, 2000, ', 'Komer B, 2014, PROCEEDINGS OF THE PYTHON IN SCIENCE CONFERENCES', 'Bardenet R, 2013, HAL (LE CENTRE POUR LA COMMUNICATION SCIENTIFIQUE DIRECTE)', 'Guyon I, 2010, ', 'Reif M, 2012, MACHINE LEARNING', 'Yogatama D, 2014, INTERNATIONAL CONFERENCE ON ARTIFICIAL INTELLIGENCE AND STATISTICS', 'Gomes T, 2011, NEUROCOMPUTING', 'Guyon I, 2015, ', 'Caruana R, 2006, PROCEEDINGS', 'Lacoste A, 2014, ', 'Pedregosa F, 2012, ARXIV (CORNELL UNIVERSITY)', 'Snoek J, 2012, ARXIV (CORNELL UNIVERSITY)', 'Brochu E, 2010, ARXIV (CORNELL UNIVERSITY)', 'Kalousis A, 2002, ARCHIVE OUVERTE UNIGE (UNIVERSITY OF GENEVA)']</t>
+          <t>['Seel N, 2012, ', 'Hastie T, 2013, ', 'Naur P, 1991, RESEARCH AT THE UNIVERSITY OF COPENHAGEN (UNIVERSITY OF COPENHAGEN)', 'Naur P, 1995, STUDIES IN COGNITIVE SYSTEMS']</t>
         </is>
       </c>
       <c r="V154" t="inlineStr">
@@ -18055,34 +18039,34 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>Feurer M, 2015, NEURAL INFORMATION PROCESSING SYSTEMS</t>
+          <t xml:space="preserve">Marsland S, 2009, </t>
         </is>
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>Feurer M, 2015, NEURAL INFORMATION PROCESSING SYSTEMS</t>
+          <t xml:space="preserve">Marsland S, 2009, </t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2990168612</t>
+          <t>https://openalex.org/W2513506629</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>10.1007/978-3-319-20010-1</t>
+          <t>10.1126/science.aaf7894</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>An Introduction to Machine Learning</t>
+          <t>Combining satellite imagery and machine learning to predict poverty</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -18092,42 +18076,70 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>1019</v>
-      </c>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
+        <v>1642</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>SCIENCE</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>['Miroslav Kubát']</t>
+          <t>['Neal Jean', 'Marshall Burke', 'Sang Michael Xie', 'W. Matthew Davis', 'David B. Lobell', 'Stefano Ermon']</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>['Miroslav Kubat']</t>
+          <t>['Neal Jean', 'Marshall Burke', 'Michael Xie', 'W. Matthew Davis', 'David B. Lobell', 'Stefano Ermon']</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>['Department of Electrical and Computer Engineering, University of Miami, Coral Gables, USA']</t>
+          <t>['Department of Computer Science, Stanford University, Stanford, CA, USA', 'Department of Electrical Engineering, Stanford University, Stanford, CA, USA', 'Center on Food Security and the Environment, Stanford University, Stanford, CA, USA', 'Department of Earth System Science, Stanford University, Stanford, CA, USA', 'National Bureau of Economic Research, Boston, MA, USA', 'Department of Computer Science, Stanford University, Stanford, CA, USA', 'Center on Food Security and the Environment, Stanford University, Stanford, CA, USA', 'Center on Food Security and the Environment, Stanford University, Stanford, CA, USA', 'Department of Earth System Science, Stanford University, Stanford, CA, USA', 'Department of Computer Science, Stanford University, Stanford, CA, USA']</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Miroslav Kubat (corresponding author), Department of Electrical and Computer Engineering, University of Miami, Coral Gables, USA</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr"/>
-      <c r="R155" t="inlineStr"/>
+          <t>Marshall Burke (corresponding author), Center on Food Security and the Environment, Stanford University, Stanford, CA, USA; Department of Earth System Science, Stanford University, Stanford, CA, USA; National Bureau of Economic Research, Boston, MA, USA</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Reliable data on economic livelihoods remain scarce in the developing world, hampering efforts to study these outcomes and to design policies that improve them. Here we demonstrate an accurate, inexpensive, and scalable method for estimating consumption expenditure and asset wealth from high-resolution satellite imagery. Using survey and satellite data from five African countries--Nigeria, Tanzania, Uganda, Malawi, and Rwanda--we show how a convolutional neural network can be trained to identify image features that can explain up to 75% of the variation in local-level economic outcomes. Our method, which requires only publicly available data, could transform efforts to track and target poverty in developing countries. It also demonstrates how powerful machine learning techniques can be applied in a setting with limited training data, suggesting broad potential application across many scientific domains.</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>6301</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>794</t>
+        </is>
+      </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>['Advice (programming)', 'Computer science', 'Simple (philosophy)', 'Artificial intelligence', 'Mathematics education', 'Human–computer interaction', 'Machine learning', 'Psychology', 'Programming language', 'Epistemology']</t>
+          <t>['Proxy (statistics)', 'Poverty', 'Satellite imagery', 'Satellite', 'Daytime', 'Consumption (sociology)', 'Perspective (graphical)', 'Computer science', 'Remote sensing', 'Meteorology', 'Artificial intelligence', 'Machine learning', 'Geography', 'Economic growth', 'Economics', 'Geology', 'Sociology', 'Atmospheric sciences', 'Engineering']</t>
         </is>
       </c>
       <c r="T155" t="inlineStr">
@@ -18137,7 +18149,7 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['LeCun Y, 2015, NATURE', 'Krizhevsky A, 2017, COMMUNICATIONS OF THE ACM', 'Russakovsky O, 2015, INTERNATIONAL JOURNAL OF COMPUTER VISION', 'Pan S, 2009, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Filmer D, 2001, DEMOGRAPHY', 'Razavian A, 2014, ', 'Chatfield K, 2014, ', 'Filmer D, 2001, DEMOGRAPHY', 'Chen X, 2011, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Sahn D, 2003, REVIEW OF INCOME AND WEALTH', 'Blumenstock J, 2015, SCIENCE', 'Mnih V, 2010, LECTURE NOTES IN COMPUTER SCIENCE', 'Michalopoulos S, 2013, THE QUARTERLY JOURNAL OF ECONOMICS', 'Balk D, 2006, ADVANCES IN PARASITOLOGY/ADVANCES IN PARASITOLOGY', 'Xie S, 2016, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Pinkovskiy M, 2016, THE QUARTERLY JOURNAL OF ECONOMICS', 'Devarajan S, 2013, REVIEW OF INCOME AND WEALTH', 'Sandefur J, 2015, THE JOURNAL OF DEVELOPMENT STUDIES', 'Jerven M, 2013, VERFASSUNG IN RECHT UND ÜBERSEE', 'Hand E, 2015, SCIENCE', 'Hong L, 2016, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE']</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
@@ -18153,34 +18165,34 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kubát M, 2015, </t>
+          <t>Jean N, 2016, SCIENCE</t>
         </is>
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kubát M, 2015, </t>
+          <t>Jean N, 2016, SCIENCE</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://openalex.org/W1549998098</t>
+          <t>https://openalex.org/W2990168612</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>10.1201/b17476</t>
+          <t>10.1007/978-3-319-20010-1</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Machine Learning: An Algorithmic Perspective</t>
+          <t>An Introduction to Machine Learning</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -18194,52 +18206,48 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>1082</v>
+        <v>1019</v>
       </c>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>['Stephen Marsland']</t>
+          <t>['Miroslav Kubát']</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>['Stephen Marsland']</t>
+          <t>['Miroslav Kubat']</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Department of Electrical and Computer Engineering, University of Miami, Coral Gables, USA']</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stephen Marsland (corresponding author), </t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>Traditional books on machine learning can be divided into two groups - those aimed at advanced undergraduates or early postgraduates with reasonable mathematical knowledge and those that are primers on how to code algorithms. The field is ready for a text that not only demonstrates how to use the algorithms that make up machine learning methods, but also provides the background needed to understand how and why these algorithms work. Machine Learning: An Algorithmic Perspective is that text.Theory Backed up by Practical ExamplesThe book covers neural networks, graphical models, reinforcement le</t>
-        </is>
-      </c>
+          <t>Miroslav Kubat (corresponding author), Department of Electrical and Computer Engineering, University of Miami, Coral Gables, USA</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr">
         <is>
-          <t>['Python (programming language)', 'Computer science', 'Implementation', 'Perspective (graphical)', 'Artificial intelligence', 'Reinforcement learning', 'Dimensionality reduction', 'Theoretical computer science', 'Machine learning', 'Programming language']</t>
+          <t>['Advice (programming)', 'Computer science', 'Simple (philosophy)', 'Artificial intelligence', 'Mathematics education', 'Human–computer interaction', 'Machine learning', 'Psychology', 'Programming language', 'Epistemology']</t>
         </is>
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['US']</t>
         </is>
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>['Seel N, 2012, ', 'Hastie T, 2013, ', 'Naur P, 1991, RESEARCH AT THE UNIVERSITY OF COPENHAGEN (UNIVERSITY OF COPENHAGEN)', 'Naur P, 1995, STUDIES IN COGNITIVE SYSTEMS']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="V156" t="inlineStr">
@@ -18255,12 +18263,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marsland S, 2009, </t>
+          <t xml:space="preserve">Kubát M, 2015, </t>
         </is>
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marsland S, 2009, </t>
+          <t xml:space="preserve">Kubát M, 2015, </t>
         </is>
       </c>
     </row>
@@ -18422,7 +18430,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -18540,7 +18548,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -18633,22 +18641,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2109722477</t>
+          <t>https://openalex.org/W4299828299</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>10.7551/mitpress/7503.003.0040</t>
+          <t>10.48550/arxiv.1207.4676</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Map-Reduce for Machine Learning on Multicore</t>
+          <t>Proceedings of the 29th International Conference on Machine Learning (ICML-12)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -18658,58 +18666,50 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>book-chapter</t>
+          <t>preprint</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>1253</v>
+        <v>1618</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>THE MIT PRESS EBOOKS</t>
+          <t>ARXIV (CORNELL UNIVERSITY)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>The MIT Press eBooks</t>
+          <t>arXiv (Cornell University)</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>['Cheng-Tao Chu', 'Sang Kyun Kim', 'Yi-An Lin', 'Yuanyuan Yu', 'Gary Bradski', 'Andrew Y. Ng', 'Kunle Olukotun']</t>
+          <t>['John Langford', 'Joëlle Pineau']</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>['Cheng-Tao Chu', 'Sang Kyun Kim', 'Yi-An Lin', 'YuanYuan Yu', 'Gary Bradski', 'Andrew Y. Ng', 'Kunle Olukotun']</t>
+          <t>['Langford, John', 'Pineau, Joelle']</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>['CS. Department, Stanford University, Stanford CA#TAB#', 'CS. Department, Stanford University, Stanford CA#TAB#', 'CS. Department, Stanford University, Stanford CA#TAB#', 'CS. Department, Stanford University, Stanford CA#TAB#', 'CS. Department, Stanford University, Stanford CA and Rexee Inc.#TAB#', 'CS. Department, Stanford University, Stanford CA#TAB#', 'CS. Department, Stanford University, Stanford CA#TAB#']</t>
+          <t>['Editors', 'Editors']</t>
         </is>
       </c>
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr">
         <is>
-          <t>We are at the beginning of the multicore era. Computers will have increasingly many cores (processors), but there is still no good programming framework for these architectures, and thus no simple and unified way for machine learning to take advantage of the potential speed up. In this paper, we develop a broadly applicable parallel programming method, one that is easily applied to many different learning algorithms. Our work is in distinct contrast to the tradition in machine learning of designing (often ingenious) ways to speed up a single algorithm at a time. Specifically, we show that algorithms that fit the Statistical Query model [15] can be written in a certain summation form, which allows them to be easily parallelized on multicore computers. We adapt Google's map-reduce [7] paradigm to demonstrate this parallel speed up technique on a variety of learning algorithms including locally weighted linear regression (LWLR), k-means, logistic regression (LR), naive Bayes (NB), SVM, ICA, PCA, gaussian discriminant analysis (GDA), EM, and backpropagation (NN). Our experimental results show basically linear speedup with an increasing number of processors.</t>
+          <t>This is an index to the papers that appear in the Proceedings of the 29th International Conference on Machine Learning (ICML-12). The conference was held in Edinburgh, Scotland, June 27th - July 3rd, 2012.</t>
         </is>
       </c>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="R160" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
       <c r="S160" t="inlineStr">
         <is>
-          <t>['Computer science', 'Speedup', 'Machine learning', 'Artificial intelligence', 'Multi-core processor', 'Support vector machine', 'Parallel computing', 'Algorithm']</t>
+          <t>['Library science', 'Geography', 'Forestry', 'Computer science']</t>
         </is>
       </c>
       <c r="T160" t="inlineStr">
@@ -18719,7 +18719,7 @@
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t>['Wold S, 1987, CHEMOMETRICS AND INTELLIGENT LABORATORY SYSTEMS', 'Bell A, 1995, NEURAL COMPUTATION', 'Hartigan J, 1975, ', 'Cleveland W, 1988, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Platt J, 1998, THE MIT PRESS EBOOKS', 'Valiant L, 1984, ', 'Moon T, 1996, IEEE SIGNAL PROCESSING MAGAZINE', 'Dayalan M, 2018, INTERNATIONAL JOURNAL OF RESEARCH AND ENGINEERING', 'Vapnik V, 2006, INFORMATION SCIENCE AND STATISTICS', 'Lewis D, 1998, LECTURE NOTES IN COMPUTER SCIENCE', 'Kearns M, 1994, THE MIT PRESS EBOOKS', 'Pregibon D, 1981, THE ANNALS OF STATISTICS', 'Langley P, 1992, ', 'Hastie T, 1996, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Chapelle O, 2007, NEURAL COMPUTATION', 'Moore G, 1975, INTERNATIONAL ELECTRON DEVICES MEETING', 'Kearns M, 1998, JOURNAL OF THE ACM', 'Sutter H, 2005, QUEUE', 'Graf H, 2004, ', 'Frank D, 2002, IBM JOURNAL OF RESEARCH AND DEVELOPMENT', 'Csanky L, 1976, SIAM JOURNAL ON COMPUTING', 'Gelsinger P, 2002, ', 'Jin R, 2004, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Caragea D, 2004, INTERNATIONAL JOURNAL OF HYBRID INTELLIGENT SYSTEMS', 'Jin R, 2002, SIAM INTERNATIONAL CONFERENCE ON DATA MINING', 'Welsch R, 1977, NATIONAL BUREAU OF ECONOMIC RESEARCH']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="V160" t="inlineStr">
@@ -18735,30 +18735,34 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>Chu C, 2007, THE MIT PRESS EBOOKS</t>
+          <t>Langford J, 2012, ARXIV (CORNELL UNIVERSITY)</t>
         </is>
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>Chu C, 2007, THE MIT PRESS EBOOKS</t>
+          <t>Langford J, 2012, ARXIV (CORNELL UNIVERSITY)</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://openalex.org/W1569512666</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr"/>
+          <t>https://openalex.org/W2547447472</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>10.1063/1.4966192</t>
+        </is>
+      </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Neural Networks And Learning Machines</t>
+          <t>Perspective: Machine learning potentials for atomistic simulations</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -18768,52 +18772,80 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>6573</v>
-      </c>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
+        <v>1490</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>THE JOURNAL OF CHEMICAL PHYSICS</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>The Journal of Chemical Physics</t>
+        </is>
+      </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>['S. Haykin']</t>
+          <t>['Jörg Behler']</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>['S. Haykin']</t>
+          <t>['Jörg Behler']</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Lehrstuhl für Theoretische Chemie, Ruhr-Universität Bochum , D-44780 Bochum, Germany']</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">S. Haykin (corresponding author), </t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr"/>
-      <c r="R161" t="inlineStr"/>
+          <t>Jörg Behler (corresponding author), Lehrstuhl für Theoretische Chemie, Ruhr-Universität Bochum , D-44780 Bochum, Germany</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Nowadays, computer simulations have become a standard tool in essentially all fields of chemistry, condensed matter physics, and materials science. In order to keep up with state-of-the-art experiments and the ever growing complexity of the investigated problems, there is a constantly increasing need for simulations of more realistic, i.e., larger, model systems with improved accuracy. In many cases, the availability of sufficiently efficient interatomic potentials providing reliable energies and forces has become a serious bottleneck for performing these simulations. To address this problem, currently a paradigm change is taking place in the development of interatomic potentials. Since the early days of computer simulations simplified potentials have been derived using physical approximations whenever the direct application of electronic structure methods has been too demanding. Recent advances in machine learning (ML) now offer an alternative approach for the representation of potential-energy surfaces by fitting large data sets from electronic structure calculations. In this perspective, the central ideas underlying these ML potentials, solved problems and remaining challenges are reviewed along with a discussion of their current applicability and limitations.</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>170901</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>170901</t>
+        </is>
+      </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>['Artificial neural network', 'Computer science', 'Artificial intelligence', 'Cognitive science', 'Machine learning', 'Psychology']</t>
+          <t>['Bottleneck', 'Representation (politics)', 'Computer science', 'Perspective (graphical)', 'Interatomic potential', 'Statistical physics', 'Electronic structure', 'Computational science', 'Theoretical computer science', 'Artificial intelligence', 'Molecular dynamics', 'Physics', 'Quantum mechanics']</t>
         </is>
       </c>
       <c r="T161" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['DE']</t>
         </is>
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['McCulloch W, 1943, BULLETIN OF MATHEMATICAL BIOLOGY', 'Cybenko G, 1989, MATHEMATICS OF CONTROL SIGNALS AND SYSTEMS', 'Allen F, 2002, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE', 'Hornik K, 1991, NEURAL NETWORKS', 'Behler J, 2007, PHYSICAL REVIEW LETTERS', 'Steinhardt P, 1983, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Bartók A, 2010, PHYSICAL REVIEW LETTERS', 'Tersoff J, 1990, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Bartók A, 2013, PHYSICAL REVIEW B', 'Rupp M, 2012, PHYSICAL REVIEW LETTERS', 'Behler J, 2011, THE JOURNAL OF CHEMICAL PHYSICS', ', 2000, ', 'Thompson A, 2014, JOURNAL OF COMPUTATIONAL PHYSICS', 'Kohn W, 1996, PHYSICAL REVIEW LETTERS', 'Braams B, 2009, INTERNATIONAL REVIEWS IN PHYSICAL CHEMISTRY', 'Behler J, 2015, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Pilania G, 2013, SCIENTIFIC REPORTS', 'Hansen K, 2015, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Behler J, 2011, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Li Z, 2015, PHYSICAL REVIEW LETTERS', 'Bartók A, 2015, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Gasteiger J, 1993, ANGEWANDTE CHEMIE INTERNATIONAL EDITION IN ENGLISH', 'Blank T, 1995, THE JOURNAL OF CHEMICAL PHYSICS', 'Behler J, 2014, JOURNAL OF PHYSICS CONDENSED MATTER', 'Artrith N, 2011, PHYSICAL REVIEW B', 'Lorenz S, 2004, CHEMICAL PHYSICS LETTERS', 'Rupp M, 2015, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Bernstein F, 1978, ARCHIVES OF BIOCHEMISTRY AND BIOPHYSICS', 'Khaliullin R, 2011, NATURE MATERIALS', 'Handley C, 2010, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Ghasemi S, 2015, PHYSICAL REVIEW B', 'Manzhos S, 2006, THE JOURNAL OF CHEMICAL PHYSICS', 'Rupp M, 2015, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Balabin R, 2011, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Manzhos S, 2005, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Geiger P, 2013, THE JOURNAL OF CHEMICAL PHYSICS', 'Agrafiotis D, 2002, JOURNAL OF CHEMICAL INFORMATION AND COMPUTER SCIENCES', 'Behler J, 2007, THE JOURNAL OF CHEMICAL PHYSICS', 'Handley C, 2009, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Jose K, 2012, THE JOURNAL OF CHEMICAL PHYSICS', 'Sosso G, 2012, PHYSICAL REVIEW B', 'Gassner H, 1998, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Valle M, 2010, ACTA CRYSTALLOGRAPHICA SECTION A FOUNDATIONS OF CRYSTALLOGRAPHY', 'Handley C, 2014, THE EUROPEAN PHYSICAL JOURNAL B', 'Ishida T, 1999, CHEMICAL PHYSICS LETTERS', 'Houlding S, 2007, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Keil M, 2004, JOURNAL OF COMPUTATIONAL CHEMISTRY', 'Hobday S, 1999, MODELLING AND SIMULATION IN MATERIALS SCIENCE AND ENGINEERING', 'Laio A, 2007, LECTURE NOTES IN PHYSICS', 'Thomsen J, 1989, JOURNAL OF MAGNETIC RESONANCE (1969)', 'Born M, 1927, ANNALEN DER PHYSIK', 'Tersoff J, 1989, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Marx D, 2009, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Ghiringhelli L, 2015, PHYSICAL REVIEW LETTERS', 'De S, 2016, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Morawietz T, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', "Jain A, 2016, JOURNAL OF MATERIALS RESEARCH/PRATT'S GUIDE TO VENTURE CAPITAL SOURCES", 'Ward L, 2016, CURRENT OPINION IN SOLID STATE AND MATERIALS SCIENCE', 'Natarajan S, 2016, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Artrith N, 2014, NANO LETTERS', 'Elias J, 2016, ACS CATALYSIS', 'Zhu L, 2016, THE JOURNAL OF CHEMICAL PHYSICS', 'J. B, 2007, MAX PLANCK INSTITUTE FOR PLASMA PHYSICS', 'Sumpter B, 1994, ANNUAL REVIEW OF PHYSICAL CHEMISTRY', 'Hellström M, 2016, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS']</t>
         </is>
       </c>
       <c r="V161" t="inlineStr">
@@ -18829,34 +18861,34 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haykin S, 2010, </t>
+          <t>Behler J, 2016, THE JOURNAL OF CHEMICAL PHYSICS</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haykin S, 2010, </t>
+          <t>Behler J, 2016, THE JOURNAL OF CHEMICAL PHYSICS</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://openalex.org/W4299828299</t>
+          <t>https://openalex.org/W2109722477</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>10.48550/arxiv.1207.4676</t>
+          <t>10.7551/mitpress/7503.003.0040</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Proceedings of the 29th International Conference on Machine Learning (ICML-12)</t>
+          <t>Map-Reduce for Machine Learning on Multicore</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -18866,50 +18898,58 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>preprint</t>
+          <t>book-chapter</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>1618</v>
+        <v>1253</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>ARXIV (CORNELL UNIVERSITY)</t>
+          <t>THE MIT PRESS EBOOKS</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>arXiv (Cornell University)</t>
+          <t>The MIT Press eBooks</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>['John Langford', 'Joëlle Pineau']</t>
+          <t>['Cheng-Tao Chu', 'Sang Kyun Kim', 'Yi-An Lin', 'Yuanyuan Yu', 'Gary Bradski', 'Andrew Y. Ng', 'Kunle Olukotun']</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>['Langford, John', 'Pineau, Joelle']</t>
+          <t>['Cheng-Tao Chu', 'Sang Kyun Kim', 'Yi-An Lin', 'YuanYuan Yu', 'Gary Bradski', 'Andrew Y. Ng', 'Kunle Olukotun']</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>['Editors', 'Editors']</t>
+          <t>['CS. Department, Stanford University, Stanford CA#TAB#', 'CS. Department, Stanford University, Stanford CA#TAB#', 'CS. Department, Stanford University, Stanford CA#TAB#', 'CS. Department, Stanford University, Stanford CA#TAB#', 'CS. Department, Stanford University, Stanford CA and Rexee Inc.#TAB#', 'CS. Department, Stanford University, Stanford CA#TAB#', 'CS. Department, Stanford University, Stanford CA#TAB#']</t>
         </is>
       </c>
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
-          <t>This is an index to the papers that appear in the Proceedings of the 29th International Conference on Machine Learning (ICML-12). The conference was held in Edinburgh, Scotland, June 27th - July 3rd, 2012.</t>
+          <t>We are at the beginning of the multicore era. Computers will have increasingly many cores (processors), but there is still no good programming framework for these architectures, and thus no simple and unified way for machine learning to take advantage of the potential speed up. In this paper, we develop a broadly applicable parallel programming method, one that is easily applied to many different learning algorithms. Our work is in distinct contrast to the tradition in machine learning of designing (often ingenious) ways to speed up a single algorithm at a time. Specifically, we show that algorithms that fit the Statistical Query model [15] can be written in a certain summation form, which allows them to be easily parallelized on multicore computers. We adapt Google's map-reduce [7] paradigm to demonstrate this parallel speed up technique on a variety of learning algorithms including locally weighted linear regression (LWLR), k-means, logistic regression (LR), naive Bayes (NB), SVM, ICA, PCA, gaussian discriminant analysis (GDA), EM, and backpropagation (NN). Our experimental results show basically linear speedup with an increasing number of processors.</t>
         </is>
       </c>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr"/>
-      <c r="R162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>['Library science', 'Geography', 'Forestry', 'Computer science']</t>
+          <t>['Computer science', 'Speedup', 'Machine learning', 'Artificial intelligence', 'Multi-core processor', 'Support vector machine', 'Parallel computing', 'Algorithm']</t>
         </is>
       </c>
       <c r="T162" t="inlineStr">
@@ -18919,7 +18959,7 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Wold S, 1987, CHEMOMETRICS AND INTELLIGENT LABORATORY SYSTEMS', 'Bell A, 1995, NEURAL COMPUTATION', 'Hartigan J, 1975, ', 'Cleveland W, 1988, JOURNAL OF THE AMERICAN STATISTICAL ASSOCIATION', 'Platt J, 1998, THE MIT PRESS EBOOKS', 'Valiant L, 1984, ', 'Moon T, 1996, IEEE SIGNAL PROCESSING MAGAZINE', 'Dayalan M, 2018, INTERNATIONAL JOURNAL OF RESEARCH AND ENGINEERING', 'Vapnik V, 2006, INFORMATION SCIENCE AND STATISTICS', 'Lewis D, 1998, LECTURE NOTES IN COMPUTER SCIENCE', 'Kearns M, 1994, THE MIT PRESS EBOOKS', 'Pregibon D, 1981, THE ANNALS OF STATISTICS', 'Langley P, 1992, ', 'Hastie T, 1996, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Chapelle O, 2007, NEURAL COMPUTATION', 'Moore G, 1975, INTERNATIONAL ELECTRON DEVICES MEETING', 'Kearns M, 1998, JOURNAL OF THE ACM', 'Sutter H, 2005, QUEUE', 'Graf H, 2004, ', 'Frank D, 2002, IBM JOURNAL OF RESEARCH AND DEVELOPMENT', 'Csanky L, 1976, SIAM JOURNAL ON COMPUTING', 'Gelsinger P, 2002, ', 'Jin R, 2004, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Caragea D, 2004, INTERNATIONAL JOURNAL OF HYBRID INTELLIGENT SYSTEMS', 'Jin R, 2002, SIAM INTERNATIONAL CONFERENCE ON DATA MINING', 'Welsch R, 1977, NATIONAL BUREAU OF ECONOMIC RESEARCH']</t>
         </is>
       </c>
       <c r="V162" t="inlineStr">
@@ -18935,34 +18975,30 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>Langford J, 2012, ARXIV (CORNELL UNIVERSITY)</t>
+          <t>Chu C, 2007, THE MIT PRESS EBOOKS</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>Langford J, 2012, ARXIV (CORNELL UNIVERSITY)</t>
+          <t>Chu C, 2007, THE MIT PRESS EBOOKS</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2547447472</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>10.1063/1.4966192</t>
-        </is>
-      </c>
+          <t>https://openalex.org/W1569512666</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Perspective: Machine learning potentials for atomistic simulations</t>
+          <t>Neural Networks And Learning Machines</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -18972,80 +19008,52 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>book</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1488</v>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>THE JOURNAL OF CHEMICAL PHYSICS</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>The Journal of Chemical Physics</t>
-        </is>
-      </c>
+        <v>6573</v>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>['Jörg Behler']</t>
+          <t>['S. Haykin']</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>['Jörg Behler']</t>
+          <t>['S. Haykin']</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['Lehrstuhl für Theoretische Chemie, Ruhr-Universität Bochum , D-44780 Bochum, Germany']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Jörg Behler (corresponding author), Lehrstuhl für Theoretische Chemie, Ruhr-Universität Bochum , D-44780 Bochum, Germany</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>Nowadays, computer simulations have become a standard tool in essentially all fields of chemistry, condensed matter physics, and materials science. In order to keep up with state-of-the-art experiments and the ever growing complexity of the investigated problems, there is a constantly increasing need for simulations of more realistic, i.e., larger, model systems with improved accuracy. In many cases, the availability of sufficiently efficient interatomic potentials providing reliable energies and forces has become a serious bottleneck for performing these simulations. To address this problem, currently a paradigm change is taking place in the development of interatomic potentials. Since the early days of computer simulations simplified potentials have been derived using physical approximations whenever the direct application of electronic structure methods has been too demanding. Recent advances in machine learning (ML) now offer an alternative approach for the representation of potential-energy surfaces by fitting large data sets from electronic structure calculations. In this perspective, the central ideas underlying these ML potentials, solved problems and remaining challenges are reviewed along with a discussion of their current applicability and limitations.</t>
-        </is>
-      </c>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="P163" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>170901</t>
-        </is>
-      </c>
-      <c r="R163" t="inlineStr">
-        <is>
-          <t>170901</t>
-        </is>
-      </c>
+          <t xml:space="preserve">S. Haykin (corresponding author), </t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr">
         <is>
-          <t>['Bottleneck', 'Representation (politics)', 'Computer science', 'Perspective (graphical)', 'Interatomic potential', 'Statistical physics', 'Electronic structure', 'Computational science', 'Theoretical computer science', 'Artificial intelligence', 'Molecular dynamics', 'Physics', 'Quantum mechanics']</t>
+          <t>['Artificial neural network', 'Computer science', 'Artificial intelligence', 'Cognitive science', 'Machine learning', 'Psychology']</t>
         </is>
       </c>
       <c r="T163" t="inlineStr">
         <is>
-          <t>['DE']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>['McCulloch W, 1943, BULLETIN OF MATHEMATICAL BIOLOGY', 'Cybenko G, 1989, MATHEMATICS OF CONTROL SIGNALS AND SYSTEMS', 'Allen F, 2002, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE', 'Hornik K, 1991, NEURAL NETWORKS', 'Behler J, 2007, PHYSICAL REVIEW LETTERS', 'Steinhardt P, 1983, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Bartók A, 2010, PHYSICAL REVIEW LETTERS', 'Tersoff J, 1990, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Bartók A, 2013, PHYSICAL REVIEW B', 'Rupp M, 2012, PHYSICAL REVIEW LETTERS', 'Behler J, 2011, THE JOURNAL OF CHEMICAL PHYSICS', ', 2000, ', 'Thompson A, 2014, JOURNAL OF COMPUTATIONAL PHYSICS', 'Kohn W, 1996, PHYSICAL REVIEW LETTERS', 'Braams B, 2009, INTERNATIONAL REVIEWS IN PHYSICAL CHEMISTRY', 'Behler J, 2015, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Pilania G, 2013, SCIENTIFIC REPORTS', 'Hansen K, 2015, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Behler J, 2011, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Li Z, 2015, PHYSICAL REVIEW LETTERS', 'Bartók A, 2015, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Gasteiger J, 1993, ANGEWANDTE CHEMIE INTERNATIONAL EDITION IN ENGLISH', 'Blank T, 1995, THE JOURNAL OF CHEMICAL PHYSICS', 'Behler J, 2014, JOURNAL OF PHYSICS CONDENSED MATTER', 'Lorenz S, 2004, CHEMICAL PHYSICS LETTERS', 'Artrith N, 2011, PHYSICAL REVIEW B', 'Rupp M, 2015, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Bernstein F, 1978, ARCHIVES OF BIOCHEMISTRY AND BIOPHYSICS', 'Khaliullin R, 2011, NATURE MATERIALS', 'Handley C, 2010, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Ghasemi S, 2015, PHYSICAL REVIEW B', 'Manzhos S, 2006, THE JOURNAL OF CHEMICAL PHYSICS', 'Rupp M, 2015, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Balabin R, 2011, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Manzhos S, 2005, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Geiger P, 2013, THE JOURNAL OF CHEMICAL PHYSICS', 'Agrafiotis D, 2002, JOURNAL OF CHEMICAL INFORMATION AND COMPUTER SCIENCES', 'Behler J, 2007, THE JOURNAL OF CHEMICAL PHYSICS', 'Handley C, 2009, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Jose K, 2012, THE JOURNAL OF CHEMICAL PHYSICS', 'Sosso G, 2012, PHYSICAL REVIEW B', 'Gassner H, 1998, THE JOURNAL OF PHYSICAL CHEMISTRY A', 'Valle M, 2010, ACTA CRYSTALLOGRAPHICA SECTION A FOUNDATIONS OF CRYSTALLOGRAPHY', 'Handley C, 2014, THE EUROPEAN PHYSICAL JOURNAL B', 'Ishida T, 1999, CHEMICAL PHYSICS LETTERS', 'Houlding S, 2007, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Keil M, 2004, JOURNAL OF COMPUTATIONAL CHEMISTRY', 'Hobday S, 1999, MODELLING AND SIMULATION IN MATERIALS SCIENCE AND ENGINEERING', 'Laio A, 2007, LECTURE NOTES IN PHYSICS', 'Thomsen J, 1989, JOURNAL OF MAGNETIC RESONANCE (1969)', 'Born M, 1927, ANNALEN DER PHYSIK', 'Tersoff J, 1989, PHYSICAL REVIEW. B, CONDENSED MATTER', 'Marx D, 2009, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Ghiringhelli L, 2015, PHYSICAL REVIEW LETTERS', 'De S, 2016, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Morawietz T, 2016, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', "Jain A, 2016, JOURNAL OF MATERIALS RESEARCH/PRATT'S GUIDE TO VENTURE CAPITAL SOURCES", 'Ward L, 2016, CURRENT OPINION IN SOLID STATE AND MATERIALS SCIENCE', 'Natarajan S, 2016, PHYSICAL CHEMISTRY CHEMICAL PHYSICS', 'Artrith N, 2014, NANO LETTERS', 'Elias J, 2016, ACS CATALYSIS', 'Zhu L, 2016, THE JOURNAL OF CHEMICAL PHYSICS', 'J. B, 2007, MAX PLANCK INSTITUTE FOR PLASMA PHYSICS', 'Sumpter B, 1994, ANNUAL REVIEW OF PHYSICAL CHEMISTRY', 'Hellström M, 2016, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="V163" t="inlineStr">
@@ -19061,12 +19069,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>Behler J, 2016, THE JOURNAL OF CHEMICAL PHYSICS</t>
+          <t xml:space="preserve">Haykin S, 2010, </t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>Behler J, 2016, THE JOURNAL OF CHEMICAL PHYSICS</t>
+          <t xml:space="preserve">Haykin S, 2010, </t>
         </is>
       </c>
     </row>
@@ -19220,7 +19228,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -19313,22 +19321,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3014596384</t>
+          <t>https://openalex.org/W2883583109</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>10.1007/s10994-021-05946-3</t>
+          <t>10.1126/science.aat2663</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Aleatoric and epistemic uncertainty in machine learning: an introduction to concepts and methods</t>
+          <t>Inverse molecular design using machine learning: Generative models for matter engineering</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -19338,76 +19346,80 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>1471</v>
+        <v>2057</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>MACHINE LEARNING</t>
+          <t>SCIENCE</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>['Eyke Hüllermeier', 'Willem Waegeman']</t>
+          <t>['Benjamín Sánchez-Lengeling', 'Alán Aspuru‐Guzik']</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>['Eyke Hüllermeier', 'Willem Waegeman']</t>
+          <t>['Benjamin Sanchez-Lengeling', 'Alán Aspuru-Guzik']</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['Heinz Nixdorf Institute and Department of Computer Science, Paderborn University, Paderborn, Germany', 'Department of Mathematical Modelling, Statistics and Bioinformatics, Ghent University, Ghent, Belgium']</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr"/>
+          <t>['Department of Chemistry and Chemical Biology, Harvard University, 12 Oxford Street, Cambridge, MA 02138, USA', 'Canadian Institute for Advanced Research (CIFAR) Senior Fellow, Toronto, Ontario M5S 1M1, Canada', 'Department of Chemistry and Department of Computer Science, University of Toronto, Toronto, Ontario M5S 3H6, Canada', 'Vector Institute for Artificial Intelligence, Toronto, Ontario M5S 1M1, Canada']</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Alán Aspuru-Guzik (corresponding author), Canadian Institute for Advanced Research (CIFAR) Senior Fellow, Toronto, Ontario M5S 1M1, Canada; Department of Chemistry and Department of Computer Science, University of Toronto, Toronto, Ontario M5S 3H6, Canada; Vector Institute for Artificial Intelligence, Toronto, Ontario M5S 1M1, Canada</t>
+        </is>
+      </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>Abstract The notion of uncertainty is of major importance in machine learning and constitutes a key element of machine learning methodology. In line with the statistical tradition, uncertainty has long been perceived as almost synonymous with standard probability and probabilistic predictions. Yet, due to the steadily increasing relevance of machine learning for practical applications and related issues such as safety requirements, new problems and challenges have recently been identified by machine learning scholars, and these problems may call for new methodological developments. In particular, this includes the importance of distinguishing between (at least) two different types of uncertainty, often referred to as aleatoric and epistemic . In this paper, we provide an introduction to the topic of uncertainty in machine learning as well as an overview of attempts so far at handling uncertainty in general and formalizing this distinction in particular.</t>
+          <t>The discovery of new materials can bring enormous societal and technological progress. In this context, exploring completely the large space of potential materials is computationally intractable. Here, we review methods for achieving inverse design, which aims to discover tailored materials from the starting point of a particular desired functionality. Recent advances from the rapidly growing field of artificial intelligence, mostly from the subfield of machine learning, have resulted in a fertile exchange of ideas, where approaches to inverse molecular design are being proposed and employed at a rapid pace. Among these, deep generative models have been applied to numerous classes of materials: rational design of prospective drugs, synthetic routes to organic compounds, and optimization of photovoltaics and redox flow batteries, as well as a variety of other solid-state materials.</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>361</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>360</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>365</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>['Probabilistic logic', 'Relevance (law)', 'Algorithmic learning theory', 'Key (lock)', 'Computational learning theory', 'Element (criminal law)']</t>
+          <t>['Generative grammar', 'Context (archaeology)', 'Computer science', 'Variety (cybernetics)', 'Pace', 'Artificial intelligence', 'Generative Design', 'Biochemical engineering', 'Machine learning', 'Engineering', 'Biology']</t>
         </is>
       </c>
       <c r="T166" t="inlineStr">
         <is>
-          <t>['DE', 'BE']</t>
+          <t>['US', 'CA']</t>
         </is>
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t>['Jordan M, 1999, MACHINE LEARNING', 'Tax D, 2003, MACHINE LEARNING', 'Mackay D, 1992, NEURAL COMPUTATION', 'Kiureghian A, 2008, STRUCTURAL SAFETY', 'Jeffreys H, 1946, PROCEEDINGS OF THE ROYAL SOCIETY OF LONDON A MATHEMATICAL AND PHYSICAL SCIENCES', 'Smets P, 1994, ARTIFICIAL INTELLIGENCE', 'Hartley R, 1928, BELL SYSTEM TECHNICAL JOURNAL', 'Wolpert D, 1996, NEURAL COMPUTATION', 'Seeger M, 2004, INTERNATIONAL JOURNAL OF NEURAL SYSTEMS', 'Endres D, 2003, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Bernardo J, 1979, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Zadrozny B, 2002, ', 'Graves A, 2011, ', 'Chow C, 1970, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Zadrozny B, 2001, ', 'Khan S, 2014, THE KNOWLEDGE ENGINEERING REVIEW', 'Dubois D, 2006, COMPUTATIONAL STATISTICS &amp; DATA ANALYSIS', 'Nguyen H, 1978, JOURNAL OF MATHEMATICAL ANALYSIS AND APPLICATIONS', 'Shilkret N, 1971, INDAGATIONES MATHEMATICAE (PROCEEDINGS)', 'Mitchell T, 1977, INTERNATIONAL JOINT CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Hora S, 1996, RELIABILITY ENGINEERING &amp; SYSTEM SAFETY', 'Denker J, 1990, ', 'Hellman M, 1970, IEEE TRANSACTIONS ON SYSTEMS SCIENCE AND CYBERNETICS', 'Herbei R, 2006, CANADIAN JOURNAL OF STATISTICS', 'Papadopoulos H, 2008, INTECH EBOOKS', 'Bernard J, 2004, INTERNATIONAL JOURNAL OF APPROXIMATE REASONING', 'Balasubramanian V, 2014, ', 'Gama J, 2012, PROGRESS IN ARTIFICIAL INTELLIGENCE', 'Senge R, 2013, INFORMATION SCIENCES', 'Yang F, 2009, BMC BIOINFORMATICS', 'Destercke S, 2008, INTERNATIONAL JOURNAL OF APPROXIMATE REASONING', 'Denœux T, 2013, INTERNATIONAL JOURNAL OF APPROXIMATE REASONING', 'Hühn J, 2008, IEEE TRANSACTIONS ON FUZZY SYSTEMS', 'Kruse R, 1991, ARTIFICIAL INTELLIGENCE', 'Dubois D, 1997, JOURNAL OF MATHEMATICAL ANALYSIS AND APPLICATIONS', 'Zaffalon M, 2002, JOURNAL OF STATISTICAL PLANNING AND INFERENCE', 'Dubois D, 1996, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS - PART A SYSTEMS AND HUMANS', 'Wasserman L, 1990, CANADIAN JOURNAL OF STATISTICS', 'Kruppa J, 2014, BIOMETRICAL JOURNAL', 'Hüllermeier E, 2008, FUZZY SETS AND SYSTEMS', 'Zaffalon M, 2012, INTERNATIONAL JOURNAL OF APPROXIMATE REASONING', 'Corani G, 2008, ', 'Coz J, 2009, JOURNAL OF MACHINE LEARNING RESEARCH', 'Lambrou A, 2010, IEEE TRANSACTIONS ON INFORMATION TECHNOLOGY IN BIOMEDICINE', 'Bi W, 2015, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Dubois D, 2006, INTERNATIONAL JOURNAL OF APPROXIMATE REASONING', 'Klir G, 1987, FUZZY SETS AND SYSTEMS', 'Gammerman A, 2002, THEORETICAL COMPUTER SCIENCE', 'Corani G, 2009, ', 'Gal Y, 2015, ARXIV (CORNELL UNIVERSITY)', 'Breiman L, 2001, MACHINE LEARNING', 'Shafer G, 1976, PRINCETON UNIVERSITY PRESS EBOOKS', 'Liu F, 2008, ', 'Walley P, 1991, ', 'Pukelsheim F, 2006, SOCIETY FOR INDUSTRIAL AND APPLIED MATHEMATICS EBOOKS', 'Frieden B, 2004, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Yager R, 1983, INTERNATIONAL JOURNAL OF GENERAL SYSTEMS', 'Cozman F, 2000, ARTIFICIAL INTELLIGENCE', 'Csiszár I, 2008, ENTROPY', 'Sato M, 2018, ', 'Kull M, 2017, BRISTOL RESEARCH (UNIVERSITY OF BRISTOL)', 'Blum M, 2013, THE EUROPEAN SYMPOSIUM ON ARTIFICIAL NEURAL NETWORKS', 'Abellán J, 2006, INTERNATIONAL JOURNAL OF GENERAL SYSTEMS', 'Barber R, 2020, INFORMATION AND INFERENCE A JOURNAL OF THE IMA', 'Freitas A, 2007, IGI GLOBAL EBOOKS', 'Sourati J, 2017, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Flach P, 2017, ENCYCLOPEDIA OF MACHINE LEARNING AND DATA MINING', 'Nguyen V, 2018, ', 'Varshney K, 2017, BIG DATA', 'Kull M, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Oh S, 2017, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'ABELLAN J, 2000, INTERNATIONAL JOURNAL OF UNCERTAINTY FUZZINESS AND KNOWLEDGE-BASED SYSTEMS', 'Yang G, 2016, IEEE TRANSACTIONS ON CYBERNETICS', 'Perelló-Nieto M, 2016, ', 'Yang G, 2016, SOFT COMPUTING', 'Linusson H, 2018, LECTURE NOTES IN COMPUTER SCIENCE', 'Lassiter D, 2019, PHILOSOPHICAL STUDIES', 'Klir G, 1994, JOHN WILEY &amp; SONS, INC. EBOOKS', 'Linusson H, 2016, LECTURE NOTES IN COMPUTER SCIENCE', 'Johansson U, 2018, KTH PUBLICATION DATABASE DIVA (KTH ROYAL INSTITUTE OF TECHNOLOGY)', 'Tan M, 2019, ARXIV (CORNELL UNIVERSITY)', 'Hendrycks D, 2016, ARXIV (CORNELL UNIVERSITY)', 'Lee K, 2018, ARXIV (CORNELL UNIVERSITY)', 'Lakshminarayanan B, 2016, ARXIV (CORNELL UNIVERSITY)', 'Liang S, 2017, ARXIV (CORNELL UNIVERSITY)', 'Şensoy M, 2018, ARXIV (CORNELL UNIVERSITY)', 'Papernot N, 2018, ARXIV (CORNELL UNIVERSITY)', 'Malinin A, 2018, ARXIV (CORNELL UNIVERSITY)', 'DeVries T, 2018, ARXIV (CORNELL UNIVERSITY)', 'Depeweg S, 2017, ARXIV (CORNELL UNIVERSITY)', 'Gneiting T, 2005, ', 'Feng J, 2019, ARXIV (CORNELL UNIVERSITY)', 'Ramaswamy H, 2015, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>['Hochreiter S, 1997, NEURAL COMPUTATION', 'Silver D, 2016, NATURE', 'Jordan M, 2015, SCIENCE', 'Rogers D, 2010, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Newman D, 2016, JOURNAL OF NATURAL PRODUCTS', 'Shahriari B, 2015, PROCEEDINGS OF THE IEEE', 'Scharber M, 2006, ADVANCED MATERIALS', 'Gómez-Bombarelli R, 2018, ACS CENTRAL SCIENCE', 'Bartók A, 2013, PHYSICAL REVIEW B', 'Rupp M, 2012, PHYSICAL REVIEW LETTERS', 'Raccuglia P, 2016, NATURE', 'Kearnes S, 2016, JOURNAL OF COMPUTER-AIDED MOLECULAR DESIGN', 'Behler J, 2011, THE JOURNAL OF CHEMICAL PHYSICS', 'Huskinson B, 2014, NATURE', 'Schütt K, 2017, NATURE COMMUNICATIONS', 'Weininger D, 1989, JOURNAL OF CHEMICAL INFORMATION AND COMPUTER SCIENCES', 'Gómez‐Bombarelli R, 2016, NATURE MATERIALS', 'Jain A, 2011, COMPUTATIONAL MATERIALS SCIENCE', 'Schneider G, 2005, NATURE REVIEWS DRUG DISCOVERY', 'Hansen K, 2015, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Reymond J, 2015, ACCOUNTS OF CHEMICAL RESEARCH', 'Hoelder S, 2012, MOLECULAR ONCOLOGY', 'Lin K, 2016, NATURE ENERGY', 'Ley S, 2015, ANGEWANDTE CHEMIE INTERNATIONAL EDITION', 'Wei J, 2016, ACS CENTRAL SCIENCE', 'Nikolaev P, 2016, NPJ COMPUTATIONAL MATERIALS', 'Cheng L, 2014, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Virshup A, 2013, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Pyzer‐Knapp E, 2015, ANNUAL REVIEW OF MATERIALS RESEARCH', 'Broach J, 1996, NATURE', 'Carnero A, 2006, CLINICAL &amp; TRANSLATIONAL ONCOLOGY', 'Robbins D, 2011, SCIENCE', 'Hachmann J, 2013, ENERGY &amp; ENVIRONMENTAL SCIENCE', 'Petousis I, 2017, SCIENTIFIC DATA', 'Qu X, 2015, COMPUTATIONAL MATERIALS SCIENCE', 'Kanal I, 2013, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Yan Q, 2017, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Ikebata H, 2017, JOURNAL OF COMPUTER-AIDED MOLECULAR DESIGN', 'Wang M, 2006, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Lilienfeld O, 2013, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Rupakheti C, 2015, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Hirn M, 2017, MULTISCALE MODELING AND SIMULATION', 'Supady A, 2015, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Xiao D, 2011, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Kühn C, 1996, THE JOURNAL OF PHYSICAL CHEMISTRY', 'Olah C, 2016, DISTILL', 'Weymuth T, 2014, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Meredig B, 2014, CHEMISTRY OF MATERIALS', 'Qian C, 2014, SMALL', 'Mnih V, 2013, ARXIV (CORNELL UNIVERSITY)', 'Yu L, 2017, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Gómez‐Bombarelli R, 2018, CAMBRIDGE UNIVERSITY ENGINEERING DEPARTMENT PUBLICATIONS DATABASE', 'Segler M, 2018, NATURE', 'Olivecrona M, 2017, JOURNAL OF CHEMINFORMATICS', 'Popova M, 2018, SCIENCE ADVANCES', 'Kadurin A, 2017, MOLECULAR PHARMACEUTICS', 'Zhou Z, 2017, ACS CENTRAL SCIENCE', 'Zunger A, 2018, NATURE REVIEWS CHEMISTRY', 'Kirkpatrick P, 2004, NATURE', 'Yang X, 2017, SCIENCE AND TECHNOLOGY OF ADVANCED MATERIALS', 'Maine E, 2006, RESEARCH POLICY', 'Lopez S, 2017, JOULE', 'Kitson P, 2018, SCIENCE', 'Roch L, 2018, SCIENCE ROBOTICS', 'Sánchez-Lengeling B, 2017, CHEMRXIV', 'Bouchacourt D, 2018, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Aspuru‐Guzik A, 2018, ACS CENTRAL SCIENCE', 'Mullard A, 2017, NATURE', 'Jørgensen P, 2018, MOLECULAR INFORMATICS', 'Yoshikawa N, 2018, CHEMISTRY LETTERS', 'A. S, 2015, MAX PLANCK DIGITAL LIBRARY', 'Sánchez-Lengeling B, 2017, CHEMRXIV', 'Aspuru‐Guzik A, 2018, DIGITAL ACCESS TO SCHOLARSHIP AT HARVARD (DASH) (HARVARD UNIVERSITY)', 'Saxena S, 2021, INTECHOPEN EBOOKS', 'Weymuth T, 2014, CHEMINFORM']</t>
         </is>
       </c>
       <c r="V166" t="inlineStr">
@@ -19423,34 +19435,34 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>Hüllermeier E, 2021, MACHINE LEARNING</t>
+          <t>Sánchez-Lengeling B, 2018, SCIENCE</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>Hüllermeier E, 2021, MACHINE LEARNING</t>
+          <t>Sánchez-Lengeling B, 2018, SCIENCE</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2883583109</t>
+          <t>https://openalex.org/W3014596384</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>10.1126/science.aat2663</t>
+          <t>10.1007/s10994-021-05946-3</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Inverse molecular design using machine learning: Generative models for matter engineering</t>
+          <t>Aleatoric and epistemic uncertainty in machine learning: an introduction to concepts and methods</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -19460,80 +19472,80 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>2054</v>
+        <v>1473</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>SCIENCE</t>
+          <t>MACHINE LEARNING</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>['Benjamín Sánchez-Lengeling', 'Alán Aspuru‐Guzik']</t>
+          <t>['Eyke Hüllermeier', 'Willem Waegeman']</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>['Benjamin Sanchez-Lengeling', 'Alán Aspuru-Guzik']</t>
+          <t>['Eyke Hüllermeier', 'Willem Waegeman']</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>['Department of Chemistry and Chemical Biology, Harvard University, 12 Oxford Street, Cambridge, MA 02138, USA', 'Canadian Institute for Advanced Research (CIFAR) Senior Fellow, Toronto, Ontario M5S 1M1, Canada', 'Department of Chemistry and Department of Computer Science, University of Toronto, Toronto, Ontario M5S 3H6, Canada', 'Vector Institute for Artificial Intelligence, Toronto, Ontario M5S 1M1, Canada']</t>
+          <t>['Heinz Nixdorf Institute and Department of Computer Science, Paderborn University, Paderborn, Germany', 'Department of Mathematical Modelling, Statistics and Bioinformatics, Ghent University, Ghent, Belgium']</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Alán Aspuru-Guzik (corresponding author), Canadian Institute for Advanced Research (CIFAR) Senior Fellow, Toronto, Ontario M5S 1M1, Canada; Department of Chemistry and Department of Computer Science, University of Toronto, Toronto, Ontario M5S 3H6, Canada; Vector Institute for Artificial Intelligence, Toronto, Ontario M5S 1M1, Canada</t>
+          <t>Eyke Hüllermeier (corresponding author), Heinz Nixdorf Institute and Department of Computer Science, Paderborn University, Paderborn, Germany</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>The discovery of new materials can bring enormous societal and technological progress. In this context, exploring completely the large space of potential materials is computationally intractable. Here, we review methods for achieving inverse design, which aims to discover tailored materials from the starting point of a particular desired functionality. Recent advances from the rapidly growing field of artificial intelligence, mostly from the subfield of machine learning, have resulted in a fertile exchange of ideas, where approaches to inverse molecular design are being proposed and employed at a rapid pace. Among these, deep generative models have been applied to numerous classes of materials: rational design of prospective drugs, synthetic routes to organic compounds, and optimization of photovoltaics and redox flow batteries, as well as a variety of other solid-state materials.</t>
+          <t>Abstract The notion of uncertainty is of major importance in machine learning and constitutes a key element of machine learning methodology. In line with the statistical tradition, uncertainty has long been perceived as almost synonymous with standard probability and probabilistic predictions. Yet, due to the steadily increasing relevance of machine learning for practical applications and related issues such as safety requirements, new problems and challenges have recently been identified by machine learning scholars, and these problems may call for new methodological developments. In particular, this includes the importance of distinguishing between (at least) two different types of uncertainty, often referred to as aleatoric and epistemic . In this paper, we provide an introduction to the topic of uncertainty in machine learning as well as an overview of attempts so far at handling uncertainty in general and formalizing this distinction in particular.</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>110</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>457</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>506</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>['Generative grammar', 'Context (archaeology)', 'Computer science', 'Variety (cybernetics)', 'Pace', 'Artificial intelligence', 'Generative Design', 'Biochemical engineering', 'Machine learning', 'Engineering', 'Biology']</t>
+          <t>['Probabilistic logic', 'Relevance (law)', 'Algorithmic learning theory', 'Key (lock)', 'Computational learning theory', 'Element (criminal law)']</t>
         </is>
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>['US', 'CA']</t>
+          <t>['DE', 'BE']</t>
         </is>
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>['Hochreiter S, 1997, NEURAL COMPUTATION', 'Silver D, 2016, NATURE', 'Jordan M, 2015, SCIENCE', 'Rogers D, 2010, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Newman D, 2016, JOURNAL OF NATURAL PRODUCTS', 'Shahriari B, 2015, PROCEEDINGS OF THE IEEE', 'Scharber M, 2006, ADVANCED MATERIALS', 'Gómez-Bombarelli R, 2018, ACS CENTRAL SCIENCE', 'Bartók A, 2013, PHYSICAL REVIEW B', 'Rupp M, 2012, PHYSICAL REVIEW LETTERS', 'Raccuglia P, 2016, NATURE', 'Kearnes S, 2016, JOURNAL OF COMPUTER-AIDED MOLECULAR DESIGN', 'Behler J, 2011, THE JOURNAL OF CHEMICAL PHYSICS', 'Huskinson B, 2014, NATURE', 'Schütt K, 2017, NATURE COMMUNICATIONS', 'Weininger D, 1989, JOURNAL OF CHEMICAL INFORMATION AND COMPUTER SCIENCES', 'Gómez‐Bombarelli R, 2016, NATURE MATERIALS', 'Jain A, 2011, COMPUTATIONAL MATERIALS SCIENCE', 'Schneider G, 2005, NATURE REVIEWS DRUG DISCOVERY', 'Hansen K, 2015, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Reymond J, 2015, ACCOUNTS OF CHEMICAL RESEARCH', 'Hoelder S, 2012, MOLECULAR ONCOLOGY', 'Lin K, 2016, NATURE ENERGY', 'Ley S, 2015, ANGEWANDTE CHEMIE INTERNATIONAL EDITION', 'Wei J, 2016, ACS CENTRAL SCIENCE', 'Nikolaev P, 2016, NPJ COMPUTATIONAL MATERIALS', 'Cheng L, 2014, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Virshup A, 2013, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Pyzer‐Knapp E, 2015, ANNUAL REVIEW OF MATERIALS RESEARCH', 'Broach J, 1996, NATURE', 'Carnero A, 2006, CLINICAL &amp; TRANSLATIONAL ONCOLOGY', 'Robbins D, 2011, SCIENCE', 'Hachmann J, 2013, ENERGY &amp; ENVIRONMENTAL SCIENCE', 'Petousis I, 2017, SCIENTIFIC DATA', 'Qu X, 2015, COMPUTATIONAL MATERIALS SCIENCE', 'Kanal I, 2013, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Yan Q, 2017, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Ikebata H, 2017, JOURNAL OF COMPUTER-AIDED MOLECULAR DESIGN', 'Wang M, 2006, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Lilienfeld O, 2013, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Rupakheti C, 2015, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Hirn M, 2017, MULTISCALE MODELING AND SIMULATION', 'Supady A, 2015, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Xiao D, 2011, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Kühn C, 1996, THE JOURNAL OF PHYSICAL CHEMISTRY', 'Olah C, 2016, DISTILL', 'Weymuth T, 2014, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Meredig B, 2014, CHEMISTRY OF MATERIALS', 'Qian C, 2014, SMALL', 'Mnih V, 2013, ARXIV (CORNELL UNIVERSITY)', 'Yu L, 2017, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Gómez‐Bombarelli R, 2018, CAMBRIDGE UNIVERSITY ENGINEERING DEPARTMENT PUBLICATIONS DATABASE', 'Segler M, 2018, NATURE', 'Olivecrona M, 2017, JOURNAL OF CHEMINFORMATICS', 'Popova M, 2018, SCIENCE ADVANCES', 'Kadurin A, 2017, MOLECULAR PHARMACEUTICS', 'Zhou Z, 2017, ACS CENTRAL SCIENCE', 'Zunger A, 2018, NATURE REVIEWS CHEMISTRY', 'Kirkpatrick P, 2004, NATURE', 'Yang X, 2017, SCIENCE AND TECHNOLOGY OF ADVANCED MATERIALS', 'Maine E, 2006, RESEARCH POLICY', 'Lopez S, 2017, JOULE', 'Kitson P, 2018, SCIENCE', 'Roch L, 2018, SCIENCE ROBOTICS', 'Sánchez-Lengeling B, 2017, CHEMRXIV', 'Bouchacourt D, 2018, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Aspuru‐Guzik A, 2018, ACS CENTRAL SCIENCE', 'Mullard A, 2017, NATURE', 'Jørgensen P, 2018, MOLECULAR INFORMATICS', 'Yoshikawa N, 2018, CHEMISTRY LETTERS', 'A. S, 2015, MAX PLANCK DIGITAL LIBRARY', 'Sánchez-Lengeling B, 2017, CHEMRXIV', 'Aspuru‐Guzik A, 2018, DIGITAL ACCESS TO SCHOLARSHIP AT HARVARD (DASH) (HARVARD UNIVERSITY)', 'Saxena S, 2021, INTECHOPEN EBOOKS', 'Weymuth T, 2014, CHEMINFORM']</t>
+          <t>['Jordan M, 1999, MACHINE LEARNING', 'Tax D, 2003, MACHINE LEARNING', 'Mackay D, 1992, NEURAL COMPUTATION', 'Kiureghian A, 2008, STRUCTURAL SAFETY', 'Jeffreys H, 1946, PROCEEDINGS OF THE ROYAL SOCIETY OF LONDON A MATHEMATICAL AND PHYSICAL SCIENCES', 'Smets P, 1994, ARTIFICIAL INTELLIGENCE', 'Hartley R, 1928, BELL SYSTEM TECHNICAL JOURNAL', 'Wolpert D, 1996, NEURAL COMPUTATION', 'Seeger M, 2004, INTERNATIONAL JOURNAL OF NEURAL SYSTEMS', 'Endres D, 2003, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Bernardo J, 1979, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Zadrozny B, 2002, ', 'Graves A, 2011, ', 'Chow C, 1970, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Zadrozny B, 2001, ', 'Khan S, 2014, THE KNOWLEDGE ENGINEERING REVIEW', 'Dubois D, 2006, COMPUTATIONAL STATISTICS &amp; DATA ANALYSIS', 'Nguyen H, 1978, JOURNAL OF MATHEMATICAL ANALYSIS AND APPLICATIONS', 'Shilkret N, 1971, INDAGATIONES MATHEMATICAE (PROCEEDINGS)', 'Mitchell T, 1977, INTERNATIONAL JOINT CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'Hora S, 1996, RELIABILITY ENGINEERING &amp; SYSTEM SAFETY', 'Denker J, 1990, ', 'Hellman M, 1970, IEEE TRANSACTIONS ON SYSTEMS SCIENCE AND CYBERNETICS', 'Herbei R, 2006, CANADIAN JOURNAL OF STATISTICS', 'Papadopoulos H, 2008, INTECH EBOOKS', 'Bernard J, 2004, INTERNATIONAL JOURNAL OF APPROXIMATE REASONING', 'Balasubramanian V, 2014, ', 'Gama J, 2012, PROGRESS IN ARTIFICIAL INTELLIGENCE', 'Senge R, 2013, INFORMATION SCIENCES', 'Yang F, 2009, BMC BIOINFORMATICS', 'Destercke S, 2008, INTERNATIONAL JOURNAL OF APPROXIMATE REASONING', 'Denœux T, 2013, INTERNATIONAL JOURNAL OF APPROXIMATE REASONING', 'Hühn J, 2008, IEEE TRANSACTIONS ON FUZZY SYSTEMS', 'Kruse R, 1991, ARTIFICIAL INTELLIGENCE', 'Dubois D, 1997, JOURNAL OF MATHEMATICAL ANALYSIS AND APPLICATIONS', 'Zaffalon M, 2002, JOURNAL OF STATISTICAL PLANNING AND INFERENCE', 'Dubois D, 1996, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS - PART A SYSTEMS AND HUMANS', 'Wasserman L, 1990, CANADIAN JOURNAL OF STATISTICS', 'Kruppa J, 2014, BIOMETRICAL JOURNAL', 'Hüllermeier E, 2008, FUZZY SETS AND SYSTEMS', 'Zaffalon M, 2012, INTERNATIONAL JOURNAL OF APPROXIMATE REASONING', 'Corani G, 2008, ', 'Coz J, 2009, JOURNAL OF MACHINE LEARNING RESEARCH', 'Lambrou A, 2010, IEEE TRANSACTIONS ON INFORMATION TECHNOLOGY IN BIOMEDICINE', 'Bi W, 2015, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Dubois D, 2006, INTERNATIONAL JOURNAL OF APPROXIMATE REASONING', 'Klir G, 1987, FUZZY SETS AND SYSTEMS', 'Gammerman A, 2002, THEORETICAL COMPUTER SCIENCE', 'Corani G, 2009, ', 'Gal Y, 2015, ARXIV (CORNELL UNIVERSITY)', 'Breiman L, 2001, MACHINE LEARNING', 'Shafer G, 1976, PRINCETON UNIVERSITY PRESS EBOOKS', 'Liu F, 2008, ', 'Walley P, 1991, ', 'Pukelsheim F, 2006, SOCIETY FOR INDUSTRIAL AND APPLIED MATHEMATICS EBOOKS', 'Frieden B, 2004, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Yager R, 1983, INTERNATIONAL JOURNAL OF GENERAL SYSTEMS', 'Cozman F, 2000, ARTIFICIAL INTELLIGENCE', 'Csiszár I, 2008, ENTROPY', 'Sato M, 2018, ', 'Kull M, 2017, BRISTOL RESEARCH (UNIVERSITY OF BRISTOL)', 'Blum M, 2013, THE EUROPEAN SYMPOSIUM ON ARTIFICIAL NEURAL NETWORKS', 'Abellán J, 2006, INTERNATIONAL JOURNAL OF GENERAL SYSTEMS', 'Barber R, 2020, INFORMATION AND INFERENCE A JOURNAL OF THE IMA', 'Freitas A, 2007, IGI GLOBAL EBOOKS', 'Sourati J, 2017, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Flach P, 2017, ENCYCLOPEDIA OF MACHINE LEARNING AND DATA MINING', 'Nguyen V, 2018, ', 'Varshney K, 2017, BIG DATA', 'Yang G, 2016, IEEE TRANSACTIONS ON CYBERNETICS', 'Kull M, 2014, LECTURE NOTES IN COMPUTER SCIENCE', 'Oh S, 2017, PROCEEDINGS OF THE AAAI CONFERENCE ON ARTIFICIAL INTELLIGENCE', 'ABELLAN J, 2000, INTERNATIONAL JOURNAL OF UNCERTAINTY FUZZINESS AND KNOWLEDGE-BASED SYSTEMS', 'Perelló-Nieto M, 2016, ', 'Yang G, 2016, SOFT COMPUTING', 'Linusson H, 2018, LECTURE NOTES IN COMPUTER SCIENCE', 'Lassiter D, 2019, PHILOSOPHICAL STUDIES', 'Klir G, 1994, JOHN WILEY &amp; SONS, INC. EBOOKS', 'Linusson H, 2016, LECTURE NOTES IN COMPUTER SCIENCE', 'Johansson U, 2018, KTH PUBLICATION DATABASE DIVA (KTH ROYAL INSTITUTE OF TECHNOLOGY)', 'Tan M, 2019, ARXIV (CORNELL UNIVERSITY)', 'Hendrycks D, 2016, ARXIV (CORNELL UNIVERSITY)', 'Lee K, 2018, ARXIV (CORNELL UNIVERSITY)', 'Lakshminarayanan B, 2016, ARXIV (CORNELL UNIVERSITY)', 'Liang S, 2017, ARXIV (CORNELL UNIVERSITY)', 'Şensoy M, 2018, ARXIV (CORNELL UNIVERSITY)', 'Papernot N, 2018, ARXIV (CORNELL UNIVERSITY)', 'Malinin A, 2018, ARXIV (CORNELL UNIVERSITY)', 'DeVries T, 2018, ARXIV (CORNELL UNIVERSITY)', 'Depeweg S, 2017, ARXIV (CORNELL UNIVERSITY)', 'Gneiting T, 2005, ', 'Feng J, 2019, ARXIV (CORNELL UNIVERSITY)', 'Ramaswamy H, 2015, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V167" t="inlineStr">
@@ -19549,12 +19561,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>Sánchez-Lengeling B, 2018, SCIENCE</t>
+          <t>Hüllermeier E, 2021, MACHINE LEARNING</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>Sánchez-Lengeling B, 2018, SCIENCE</t>
+          <t>Hüllermeier E, 2021, MACHINE LEARNING</t>
         </is>
       </c>
     </row>
@@ -19667,22 +19679,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://openalex.org/W4402843978</t>
+          <t>https://openalex.org/W3148181069</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>10.58248/pn633</t>
+          <t>10.38094/jastt20165</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Interpretable machine learning</t>
+          <t>Classification Based on Decision Tree Algorithm for Machine Learning</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -19692,56 +19704,76 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G169" t="n">
-        <v>987</v>
-      </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
+        <v>1820</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>JOURNAL OF APPLIED SCIENCE AND TECHNOLOGY TRENDS</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Journal of Applied Science and Technology Trends</t>
+        </is>
+      </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>['Parliamentary Office of Science and Technology', 'Lorna Christie']</t>
+          <t>['Bahzad Charbuty', 'Adnan Mohsin Abdulazeez']</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>['Parliamentary Office of Science and Technology', 'Lorna Christie']</t>
+          <t>['Bahzad Charbuty', 'Adnan Abdulazeez']</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parliamentary Office of Science and Technology (corresponding author), </t>
-        </is>
-      </c>
+          <t>['IT Department, Technical College of Informatics Akre, Duhok Polytechnic University, Duhok, Kurdistan Region, Iraq', 'Duhok Polytechnic University, Duhok, Kurdistan Region, Iraq']</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr">
         <is>
-          <t>Machine learning (ML, a type of artificial intelligence) is increasingly being used to support decision making in a variety of applications including recruitment and clinical diagnoses. While ML has many advantages, there are concerns that in some cases it may not be possible to explain completely how its outputs have been produced. This POSTnote gives an overview of ML and its role in decision-making. It examines the challenges of understanding how a complex ML system has reached its output, and some of the technical approaches to making ML easier to interpret. It also gives a brief overview of some of the proposed tools for making ML systems more accountable.</t>
-        </is>
-      </c>
-      <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
-      <c r="R169" t="inlineStr"/>
+          <t>Decision tree classifiers are regarded to be a standout of the most well-known methods to data classification representation of classifiers. Different researchers from various fields and backgrounds have considered the problem of extending a decision tree from available data, such as machine study, pattern recognition, and statistics. In various fields such as medical disease analysis, text classification, user smartphone classification, images, and many more the employment of Decision tree classifiers has been proposed in many ways. This paper provides a detailed approach to the decision trees. Furthermore, paper specifics, such as algorithms/approaches used, datasets, and outcomes achieved, are evaluated and outlined comprehensively. In addition, all of the approaches analyzed were discussed to illustrate the themes of the authors and identify the most accurate classifiers. As a result, the uses of different types of datasets are discussed and their findings are analyzed.</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>['Artificial intelligence', 'Computer science', 'Machine learning']</t>
+          <t>['Decision tree', 'Computer science', 'Machine learning', 'Artificial intelligence', 'ID3 algorithm', 'Decision tree learning', 'Incremental decision tree', 'Representation (politics)', 'Tree (set theory)', 'Statistical classification', 'Data mining', 'Pattern recognition (psychology)', 'Mathematics']</t>
         </is>
       </c>
       <c r="T169" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['IQ']</t>
         </is>
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Kotsiantis S, 2007, ', 'Carleo G, 2019, REVIEWS OF MODERN PHYSICS', 'Libbrecht M, 2015, NATURE REVIEWS GENETICS', 'Kotsiantis S, 2006, ARTIFICIAL INTELLIGENCE REVIEW', 'Palo V, 2015, ', 'Lim T, 2000, MACHINE LEARNING', 'Song Y, 2015, PUBMED', 'Tso K, 2007, ENERGY', 'Zou Q, 2018, FRONTIERS IN GENETICS', 'Rokach L, 2005, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS PART C (APPLICATIONS AND REVIEWS)', 'Janikow C, 1998, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS PART B (CYBERNETICS)', 'Loh W, 2014, INTERNATIONAL STATISTICAL REVIEW', 'Raileanu L, 2004, ANNALS OF MATHEMATICS AND ARTIFICIAL INTELLIGENCE', 'Swain P, 1977, IEEE TRANSACTIONS ON GEOSCIENCE ELECTRONICS', 'Mántaras R, 1991, MACHINE LEARNING', 'Eesa A, 2014, EXPERT SYSTEMS WITH APPLICATIONS', 'Brodley C, 1995, MACHINE LEARNING', 'Barros R, 2011, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS PART C (APPLICATIONS AND REVIEWS)', 'Zhao Y, 2007, ADVANCES IN SPACE RESEARCH', 'Stein G, 2005, ', 'Liang J, 2019, IEEE TRANSACTIONS ON DEPENDABLE AND SECURE COMPUTING', 'Zeebaree D, 2018, ', 'Pérez‐Ortiz M, 2016, ENERGIES', 'Shang C, 2013, KNOWLEDGE-BASED SYSTEMS', 'Zeebaree D, 2019, ', 'Maszczyk T, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Linty N, 2018, IEEE TRANSACTIONS ON AEROSPACE AND ELECTRONIC SYSTEMS', 'Damanik I, 2019, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Suresh A, 2019, SOFT COMPUTING', 'Feng C, 2017, ', 'Taneja S, 2014, ', 'Gavankar S, 2017, ', 'Wang J, 2005, LECTURE NOTES IN COMPUTER SCIENCE', 'Kumar R, 2012, ', 'Bengio Y, 2010, COMPUTATIONAL INTELLIGENCE', 'Kuang W, 2019, IEEE TRANSACTIONS ON CIRCUITS AND SYSTEMS FOR VIDEO TECHNOLOGY', 'Ahmed N, 2018, ', 'Anuradha, 2014, ', 'Nagra A, 2019, CONNECTION SCIENCE', 'Patil D, 2006, ', 'Zhang Y, 2019, ', 'Shamim A, 2010, ', 'Cheushev V, 2002, ', 'Hussain D, 2018, JOURNAL OF X-RAY SCIENCE AND TECHNOLOGY', 'Hassan O, 2018, ', 'Ahmim A, 2019, ', 'Eesa A, 2017, SCIENCE JOURNAL OF UNIVERSITY OF ZAKHO', 'Liu Y, 2013, ', 'Maulud D, 2020, JOURNAL OF APPLIED SCIENCE AND TECHNOLOGY TRENDS', 'Zebari R, 2020, JOURNAL OF APPLIED SCIENCE AND TECHNOLOGY TRENDS', 'Ling Q, 2023, APPLIED AND COMPUTATIONAL ENGINEERING', 'Brodley C, 1995, MACHINE LEARNING', 'Priyanka N, 2020, INTERNATIONAL JOURNAL OF INFORMATION AND DECISION SCIENCES', ', 2017, INTERNATIONAL JOURNAL OF MODERN TRENDS IN ENGINEERING &amp; RESEARCH', 'Hillel T, 2020, JOURNAL OF CHOICE MODELLING', 'Pahwa K, 2019, ', 'Li M, 2019, ENTROPY', 'Yang F, 2019, ', 'Omar A, 2019, ', 'Assegie T, 2019, INTERNATIONAL JOURNAL OF POWER ELECTRONICS AND DRIVE SYSTEMS/INTERNATIONAL JOURNAL OF ELECTRICAL AND COMPUTER ENGINEERING', 'Nandhini S, 2020, 2020 INTERNATIONAL CONFERENCE ON EMERGING TRENDS IN INFORMATION TECHNOLOGY AND ENGINEERING (IC-ETITE)', 'Sulaiman M, 2020, INTERNATIONAL JOURNAL OF SUSTAINABLE CONSTRUCTION ENGINEERING AND TECHNOLOGY (UNIVERSITI TUN HUSSEIN ONN MALAYSIA)', 'Pathan S, 2019, JOURNAL OF APPLIED BIOMEDICINE', 'Kumar D, 2020, INTERNATIONAL JOURNAL OF INFORMATION AND DECISION SCIENCES', 'Patil S, 2019, 2019 3RD INTERNATIONAL CONFERENCE ON TRENDS IN ELECTRONICS AND INFORMATICS (ICOEI)', 'Sathiyanarayanan P, 2019, 2019 IEEE INTERNATIONAL CONFERENCE ON SYSTEM, COMPUTATION, AUTOMATION AND NETWORKING (ICSCAN)', 'Dash S, 2020, SMART INNOVATION, SYSTEMS AND TECHNOLOGIES', 'Arowolo M, 2020, ', 'Mrva J, 2019, ', 'Jiao S, 2020, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Taloba A, 2019, ', 'Ramadhan I, 2020, ', 'Felice F, 2019, JOURNAL OF CANCER RESEARCH AND CLINICAL ONCOLOGY', 'Issa A, 2011, ENGINEERING AND TECHNOLOGY JOURNAL', 'Chen X, 2019, 2019 3RD INTERNATIONAL CONFERENCE ON ELECTRONIC INFORMATION TECHNOLOGY AND COMPUTER ENGINEERING (EITCE)', 'Vishwakarma A, 2024, ', 'M�ntaras R, 1991, MACHINE LEARNING', 'Batitis V, 2020, ', 'Goyal P, 2020, ']</t>
         </is>
       </c>
       <c r="V169" t="inlineStr">
@@ -19757,12 +19789,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Technology P, 2020, </t>
+          <t>Charbuty B, 2021, JOURNAL OF APPLIED SCIENCE AND TECHNOLOGY TRENDS</t>
         </is>
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Technology P, 2020, </t>
+          <t>Charbuty B, 2021, JOURNAL OF APPLIED SCIENCE AND TECHNOLOGY TRENDS</t>
         </is>
       </c>
     </row>
@@ -19863,7 +19895,7 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>['Witten I, 2011, ELSEVIER EBOOKS', 'Agrawal R, 1994, VERY LARGE DATA BASES', 'Després J, 2006, NATURE', 'Robnik‐Šikonja M, 2003, MACHINE LEARNING', 'Krentz A, 2005, DRUGS', 'Laing S, 2003, DIABETOLOGIA', 'Tapp R, 2003, DIABETES CARE', 'Roychowdhury S, 2014, IEEE JOURNAL OF BIOMEDICAL AND HEALTH INFORMATICS', 'Giancardo L, 2011, MEDICAL IMAGE ANALYSIS', 'Özçift A, 2011, COMPUTER METHODS AND PROGRAMS IN BIOMEDICINE', 'Georga E, 2012, IEEE JOURNAL OF BIOMEDICAL AND HEALTH INFORMATICS', 'Wright A, 2014, JOURNAL OF BIOMEDICAL INFORMATICS', 'Chikh M, 2011, JOURNAL OF MEDICAL SYSTEMS', 'Choi S, 2014, COMPUTATIONAL AND MATHEMATICAL METHODS IN MEDICINE', 'Huang G, 2015, BMC BIOINFORMATICS', 'El–Sappagh S, 2015, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Mani S, 2012, PUBMED', 'Anderson A, 2015, JOURNAL OF BIOMEDICAL INFORMATICS', 'Herrero P, 2014, IEEE JOURNAL OF BIOMEDICAL AND HEALTH INFORMATICS', 'Tapak L, 2013, HEALTHCARE INFORMATICS RESEARCH', 'Georga E, 2013, DIABETES TECHNOLOGY &amp; THERAPEUTICS', 'Worachartcheewan A, 2015, THE SCIENTIFIC WORLD JOURNAL', 'Jin H, 2015, PREVENTING CHRONIC DISEASE', 'Simon G, 2014, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Cai L, 2015, PLOS ONE', 'Jelinek H, 2006, AUSTRALIAN JOURNAL OF PRIMARY HEALTH', 'Yusuf N, 2015, BMC BIOINFORMATICS', 'Török Z, 2015, JOURNAL OF DIABETES RESEARCH', 'Pinhas‐Hamiel O, 2013, INTERNATIONAL JOURNAL OF EATING DISORDERS', 'Ibrahim S, 2015, MEDICAL &amp; BIOLOGICAL ENGINEERING &amp; COMPUTING', 'Jonnagaddala J, 2015, BIOMED RESEARCH INTERNATIONAL', 'Lagani V, 2015, JOURNAL OF DIABETES AND ITS COMPLICATIONS', 'Nantasenamat C, 2015, DRUG DESIGN DEVELOPMENT AND THERAPY', 'Chen L, 2012, INTELLIGENT DATA ANALYSIS', 'Huang J, 2013, TALANTA', 'Shankaracharya N, 2012, THE REVIEW OF DIABETIC STUDIES', 'Halevas E, 2015, JOURNAL OF INORGANIC BIOCHEMISTRY', 'Simon G, 2013, PUBMED', 'Bradley P, 2013, BIG DATA', 'Gregori D, 2009, JOURNAL OF MEDICAL SYSTEMS', 'Tsave O, 2015, JOURNAL OF INORGANIC BIOCHEMISTRY', 'Nimmagadda S, 2014, INTERNATIONAL JOURNAL OF ENVIRONMENTAL RESEARCH AND PUBLIC HEALTH', 'Deja R, 2015, BIOMEDICAL ENGINEERING ONLINE', 'Schrom J, 2013, PUBMED', 'Lee J, 2013, COMPUTERS IN BIOLOGY AND MEDICINE', 'Pakhomov S, 2011, PUBMED CENTRAL', 'Quellec G, 2013, ', 'Karahoca A, 2012, EXPERT SYSTEMS WITH APPLICATIONS', 'Yarimizu M, 2015, ADVANCES IN BIOINFORMATICS', 'Kavakiotis I, 2013, ', 'Han J, 2012, CHOICE REVIEWS ONLINE', 'Kumar D, 1995, CHOICE REVIEWS ONLINE', 'Cover T, 1967, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Fan J, 2008, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Marx V, 2013, NATURE', 'Monte S, 2008, JOURNAL OF DIABETES SCIENCE AND TECHNOLOGY', 'Cade W, 2008, PHYSICAL THERAPY', 'Cryer P, 2003, PUBMED', 'Kaprio J, 1992, DIABETOLOGIA', 'Meng X, 2012, THE KAOHSIUNG JOURNAL OF MEDICAL SCIENCES', 'Malley J, 2011, METHODS OF INFORMATION IN MEDICINE', 'Sudharsan B, 2014, JOURNAL OF DIABETES SCIENCE AND TECHNOLOGY', 'Mattmann C, 2013, NATURE', 'Ganji M, 2011, EXPERT SYSTEMS WITH APPLICATIONS', 'Han L, 2014, IEEE JOURNAL OF BIOMEDICAL AND HEALTH INFORMATICS', 'Nguyen C, 2013, DIABETES', 'Lee B, 2015, IEEE JOURNAL OF BIOMEDICAL AND HEALTH INFORMATICS', 'Çalişir D, 2011, EXPERT SYSTEMS WITH APPLICATIONS', 'Zhang B, 2013, IEEE TRANSACTIONS ON BIOMEDICAL ENGINEERING', 'Robertson G, 2011, JOURNAL OF ELECTRICAL AND COMPUTER ENGINEERING', 'Beloufa F, 2013, COMPUTER METHODS AND PROGRAMS IN BIOMEDICINE', 'Aslam M, 2013, EXPERT SYSTEMS WITH APPLICATIONS', 'Habibi S, 2015, GLOBAL JOURNAL OF HEALTH SCIENCE', 'Cox M, 2009, CLINICAL DIABETES', 'Oh E, 2013, BMC MEDICAL INFORMATICS AND DECISION MAKING', 'Leung R, 2013, BMC NEPHROLOGY', 'Lagani V, 2015, JOURNAL OF DIABETES AND ITS COMPLICATIONS', 'Anjos S, 2004, MOLECULAR GENETICS AND METABOLISM', 'Georga E, 2015, MEDICAL &amp; BIOLOGICAL ENGINEERING &amp; COMPUTING', 'Ramezankhani A, 2014, MEDICAL DECISION MAKING', 'Lee B, 2013, IEEE JOURNAL OF BIOMEDICAL AND HEALTH INFORMATICS', 'Stranieri A, 2013, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Pires R, 2013, IEEE TRANSACTIONS ON BIOMEDICAL ENGINEERING', 'Török Z, 2013, BMC OPHTHALMOLOGY', 'Lopes M, 2014, GENOMICS', 'Lee W, 2012, ASIAN JOURNAL OF SURGERY', 'Wang K, 2015, JOURNAL OF BIOMEDICAL INFORMATICS', 'Ramezankhani A, 2015, INTERNATIONAL JOURNAL OF ENDOCRINOLOGY AND METABOLISM', 'Park S, 2011, BMC SYSTEMS BIOLOGY', 'Abawajy J, 2013, COMPUTERS IN BIOLOGY AND MEDICINE', 'Caveney E, 2011, JOURNAL OF DIABETES SCIENCE AND TECHNOLOGY', 'Li B, 2013, CURRENT DIABETES REPORTS', 'Marling C, 2013, JOURNAL OF DIABETES SCIENCE AND TECHNOLOGY', 'Lee J, 2011, OSONG PUBLIC HEALTH AND RESEARCH PERSPECTIVES', 'Jensen M, 2014, JOURNAL OF DIABETES SCIENCE AND TECHNOLOGY', 'Bujac S, 2014, DIABETES THERAPY', 'Namayanja J, 2012, JOURNAL OF MEDICAL SYSTEMS', 'Renard L, 2011, BMC MEDICAL INFORMATICS AND DECISION MAKING', 'Narasimhan K, 2014, CNS &amp; NEUROLOGICAL DISORDERS - DRUG TARGETS', 'Ozery-Flato M, 2013, DIABETOLOGY &amp; METABOLIC SYNDROME', 'Breiman L, 2001, MACHINE LEARNING', 'Agrawal R, 1993, ', 'Association A, 2010, DIABETES CARE', 'GuyonIsabelle, 2003, JOURNAL OF MACHINE LEARNING RESEARCH', 'Fayyad U, 1996, ', 'Zeevi D, 2015, CELL', 'Blundell J, 2017, PUBMED', 'Association A, 2008, DIABETES CARE', ', 2019, SERIES IN MACHINE PERCEPTION AND ARTIFICIAL INTELLIGENCE', 'Cryer P, 2003, DIABETES CARE', 'Thomas N, 2016, JAYPEE BROTHERS MEDICAL PUBLISHERS (P) LTD. EBOOKS', 'Bocca J, 1994, ', 'Razavian N, 2015, BIG DATA', 'Bagherzadeh‐Khiabani F, 2015, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Agarwal V, 2016, JOURNAL OF THE AMERICAN MEDICAL INFORMATICS ASSOCIATION', 'Batal I, 2012, ', 'Allalou A, 2016, DIABETES', 'Farran B, 2013, BMJ OPEN', 'Bashir S, 2015, JOURNAL OF BIOMEDICAL INFORMATICS', 'Rau H, 2015, COMPUTER METHODS AND PROGRAMS IN BIOMEDICINE', 'Anderson J, 2015, JOURNAL OF DIABETES SCIENCE AND TECHNOLOGY', 'Malik S, 2016, SPRINGERPLUS', 'Oh W, 2016, BIG DATA', 'Collins A, 1988, ELSEVIER EBOOKS', 'Dubrava S, 2016, PAIN MEDICINE', 'Ogunyemi O, 2015, PUBMED', 'Belciug S, 2014, JOURNAL OF BIOMEDICAL INFORMATICS', 'Jin J, 2015, JOURNAL OF DIABETES RESEARCH', 'Lee Y, 2012, OBESITY RESEARCH &amp; CLINICAL PRACTICE', 'Tsave O, 2016, JOURNAL OF INORGANIC BIOCHEMISTRY', 'Jelinek H, 2016, COMPUTERS IN BIOLOGY AND MEDICINE', 'Ibrahim Z, 2013, WILEY EBOOKS', 'Sideris C, 2016, COMPUTERS IN BIOLOGY AND MEDICINE', 'Patra J, 2010, JOURNAL OF COMPUTATIONAL CHEMISTRY', 'Fong S, 2013, BIOMED RESEARCH INTERNATIONAL', 'Haifeng L, 2013, STUDIES IN HEALTH TECHNOLOGY AND INFORMATICS', 'Sacchi L, 2015, ', 'Prentašić P, 2014, ', 'Worachartcheewan A, 2013, PUBMED', 'Worachartcheewan A, 2013, PUBMED', 'Zhao L, 2016, GENETIC EPIDEMIOLOGY', 'Krishnamoorthy S, 2015, PLOS ONE', 'Hoyt R, 2016, PUBMED', 'Anderson A, 2015, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>['Witten I, 2011, ELSEVIER EBOOKS', 'Agrawal R, 1994, VERY LARGE DATA BASES', 'Després J, 2006, NATURE', 'Robnik‐Šikonja M, 2003, MACHINE LEARNING', 'Krentz A, 2005, DRUGS', 'Laing S, 2003, DIABETOLOGIA', 'Tapp R, 2003, DIABETES CARE', 'Roychowdhury S, 2014, IEEE JOURNAL OF BIOMEDICAL AND HEALTH INFORMATICS', 'Giancardo L, 2011, MEDICAL IMAGE ANALYSIS', 'Özçift A, 2011, COMPUTER METHODS AND PROGRAMS IN BIOMEDICINE', 'Georga E, 2012, IEEE JOURNAL OF BIOMEDICAL AND HEALTH INFORMATICS', 'Wright A, 2014, JOURNAL OF BIOMEDICAL INFORMATICS', 'Chikh M, 2011, JOURNAL OF MEDICAL SYSTEMS', 'Choi S, 2014, COMPUTATIONAL AND MATHEMATICAL METHODS IN MEDICINE', 'Huang G, 2015, BMC BIOINFORMATICS', 'El–Sappagh S, 2015, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Mani S, 2012, PUBMED', 'Anderson A, 2015, JOURNAL OF BIOMEDICAL INFORMATICS', 'Herrero P, 2014, IEEE JOURNAL OF BIOMEDICAL AND HEALTH INFORMATICS', 'Tapak L, 2013, HEALTHCARE INFORMATICS RESEARCH', 'Georga E, 2013, DIABETES TECHNOLOGY &amp; THERAPEUTICS', 'Worachartcheewan A, 2015, THE SCIENTIFIC WORLD JOURNAL', 'Jin H, 2015, PREVENTING CHRONIC DISEASE', 'Simon G, 2014, IEEE TRANSACTIONS ON KNOWLEDGE AND DATA ENGINEERING', 'Cai L, 2015, PLOS ONE', 'Jelinek H, 2006, AUSTRALIAN JOURNAL OF PRIMARY HEALTH', 'Yusuf N, 2015, BMC BIOINFORMATICS', 'Török Z, 2015, JOURNAL OF DIABETES RESEARCH', 'Pinhas‐Hamiel O, 2013, INTERNATIONAL JOURNAL OF EATING DISORDERS', 'Ibrahim S, 2015, MEDICAL &amp; BIOLOGICAL ENGINEERING &amp; COMPUTING', 'Jonnagaddala J, 2015, BIOMED RESEARCH INTERNATIONAL', 'Lagani V, 2015, JOURNAL OF DIABETES AND ITS COMPLICATIONS', 'Nantasenamat C, 2015, DRUG DESIGN DEVELOPMENT AND THERAPY', 'Chen L, 2012, INTELLIGENT DATA ANALYSIS', 'Huang J, 2013, TALANTA', 'Shankaracharya N, 2012, THE REVIEW OF DIABETIC STUDIES', 'Halevas E, 2015, JOURNAL OF INORGANIC BIOCHEMISTRY', 'Simon G, 2013, PUBMED', 'Bradley P, 2013, BIG DATA', 'Gregori D, 2009, JOURNAL OF MEDICAL SYSTEMS', 'Tsave O, 2015, JOURNAL OF INORGANIC BIOCHEMISTRY', 'Nimmagadda S, 2014, INTERNATIONAL JOURNAL OF ENVIRONMENTAL RESEARCH AND PUBLIC HEALTH', 'Deja R, 2015, BIOMEDICAL ENGINEERING ONLINE', 'Schrom J, 2013, PUBMED', 'Lee J, 2013, COMPUTERS IN BIOLOGY AND MEDICINE', 'Pakhomov S, 2011, PUBMED', 'Quellec G, 2013, ', 'Karahoca A, 2012, EXPERT SYSTEMS WITH APPLICATIONS', 'Yarimizu M, 2015, ADVANCES IN BIOINFORMATICS', 'Kavakiotis I, 2013, ', 'Han J, 2012, CHOICE REVIEWS ONLINE', 'Kumar D, 1995, CHOICE REVIEWS ONLINE', 'Cover T, 1967, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Fan J, 2008, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES B (STATISTICAL METHODOLOGY)', 'Marx V, 2013, NATURE', 'Monte S, 2008, JOURNAL OF DIABETES SCIENCE AND TECHNOLOGY', 'Cade W, 2008, PHYSICAL THERAPY', 'Cryer P, 2003, PUBMED', 'Kaprio J, 1992, DIABETOLOGIA', 'Meng X, 2012, THE KAOHSIUNG JOURNAL OF MEDICAL SCIENCES', 'Malley J, 2011, METHODS OF INFORMATION IN MEDICINE', 'Sudharsan B, 2014, JOURNAL OF DIABETES SCIENCE AND TECHNOLOGY', 'Mattmann C, 2013, NATURE', 'Ganji M, 2011, EXPERT SYSTEMS WITH APPLICATIONS', 'Nguyen C, 2013, DIABETES', 'Han L, 2014, IEEE JOURNAL OF BIOMEDICAL AND HEALTH INFORMATICS', 'Lee B, 2015, IEEE JOURNAL OF BIOMEDICAL AND HEALTH INFORMATICS', 'Çalişir D, 2011, EXPERT SYSTEMS WITH APPLICATIONS', 'Zhang B, 2013, IEEE TRANSACTIONS ON BIOMEDICAL ENGINEERING', 'Robertson G, 2011, JOURNAL OF ELECTRICAL AND COMPUTER ENGINEERING', 'Beloufa F, 2013, COMPUTER METHODS AND PROGRAMS IN BIOMEDICINE', 'Aslam M, 2013, EXPERT SYSTEMS WITH APPLICATIONS', 'Habibi S, 2015, GLOBAL JOURNAL OF HEALTH SCIENCE', 'Cox M, 2009, CLINICAL DIABETES', 'Oh E, 2013, BMC MEDICAL INFORMATICS AND DECISION MAKING', 'Leung R, 2013, BMC NEPHROLOGY', 'Lagani V, 2015, JOURNAL OF DIABETES AND ITS COMPLICATIONS', 'Anjos S, 2004, MOLECULAR GENETICS AND METABOLISM', 'Georga E, 2015, MEDICAL &amp; BIOLOGICAL ENGINEERING &amp; COMPUTING', 'Ramezankhani A, 2014, MEDICAL DECISION MAKING', 'Lee B, 2013, IEEE JOURNAL OF BIOMEDICAL AND HEALTH INFORMATICS', 'Stranieri A, 2013, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Pires R, 2013, IEEE TRANSACTIONS ON BIOMEDICAL ENGINEERING', 'Török Z, 2013, BMC OPHTHALMOLOGY', 'Lopes M, 2014, GENOMICS', 'Lee W, 2012, ASIAN JOURNAL OF SURGERY', 'Wang K, 2015, JOURNAL OF BIOMEDICAL INFORMATICS', 'Ramezankhani A, 2015, INTERNATIONAL JOURNAL OF ENDOCRINOLOGY AND METABOLISM', 'Park S, 2011, BMC SYSTEMS BIOLOGY', 'Abawajy J, 2013, COMPUTERS IN BIOLOGY AND MEDICINE', 'Caveney E, 2011, JOURNAL OF DIABETES SCIENCE AND TECHNOLOGY', 'Li B, 2013, CURRENT DIABETES REPORTS', 'Marling C, 2013, JOURNAL OF DIABETES SCIENCE AND TECHNOLOGY', 'Lee J, 2011, OSONG PUBLIC HEALTH AND RESEARCH PERSPECTIVES', 'Jensen M, 2014, JOURNAL OF DIABETES SCIENCE AND TECHNOLOGY', 'Bujac S, 2014, DIABETES THERAPY', 'Namayanja J, 2012, JOURNAL OF MEDICAL SYSTEMS', 'Renard L, 2011, BMC MEDICAL INFORMATICS AND DECISION MAKING', 'Narasimhan K, 2014, CNS &amp; NEUROLOGICAL DISORDERS - DRUG TARGETS', 'Ozery-Flato M, 2013, DIABETOLOGY &amp; METABOLIC SYNDROME', 'Breiman L, 2001, MACHINE LEARNING', 'Agrawal R, 1993, ', 'Association A, 2010, DIABETES CARE', 'GuyonIsabelle, 2003, JOURNAL OF MACHINE LEARNING RESEARCH', 'Fayyad U, 1996, ', 'Zeevi D, 2015, CELL', 'Blundell J, 2017, PUBMED', 'Association A, 2008, DIABETES CARE', ', 2019, SERIES IN MACHINE PERCEPTION AND ARTIFICIAL INTELLIGENCE', 'Cryer P, 2003, DIABETES CARE', 'Thomas N, 2016, JAYPEE BROTHERS MEDICAL PUBLISHERS (P) LTD. EBOOKS', 'Bocca J, 1994, ', 'Razavian N, 2015, BIG DATA', 'Bagherzadeh‐Khiabani F, 2015, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Agarwal V, 2016, JOURNAL OF THE AMERICAN MEDICAL INFORMATICS ASSOCIATION', 'Batal I, 2012, ', 'Allalou A, 2016, DIABETES', 'Farran B, 2013, BMJ OPEN', 'Bashir S, 2015, JOURNAL OF BIOMEDICAL INFORMATICS', 'Rau H, 2015, COMPUTER METHODS AND PROGRAMS IN BIOMEDICINE', 'Anderson J, 2015, JOURNAL OF DIABETES SCIENCE AND TECHNOLOGY', 'Malik S, 2016, SPRINGERPLUS', 'Oh W, 2016, BIG DATA', 'Collins A, 1988, ELSEVIER EBOOKS', 'Dubrava S, 2016, PAIN MEDICINE', 'Ogunyemi O, 2015, PUBMED', 'Belciug S, 2014, JOURNAL OF BIOMEDICAL INFORMATICS', 'Jin J, 2015, JOURNAL OF DIABETES RESEARCH', 'Lee Y, 2012, OBESITY RESEARCH &amp; CLINICAL PRACTICE', 'Tsave O, 2016, JOURNAL OF INORGANIC BIOCHEMISTRY', 'Jelinek H, 2016, COMPUTERS IN BIOLOGY AND MEDICINE', 'Ibrahim Z, 2013, WILEY EBOOKS', 'Sideris C, 2016, COMPUTERS IN BIOLOGY AND MEDICINE', 'Patra J, 2010, JOURNAL OF COMPUTATIONAL CHEMISTRY', 'Fong S, 2013, BIOMED RESEARCH INTERNATIONAL', 'Haifeng L, 2013, STUDIES IN HEALTH TECHNOLOGY AND INFORMATICS', 'Sacchi L, 2015, ', 'Prentašić P, 2014, ', 'Worachartcheewan A, 2013, PUBMED', 'Worachartcheewan A, 2013, PUBMED', 'Zhao L, 2016, GENETIC EPIDEMIOLOGY', 'Krishnamoorthy S, 2015, PLOS ONE', 'Hoyt R, 2016, PUBMED', 'Anderson A, 2015, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V170" t="inlineStr">
@@ -19891,22 +19923,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3148181069</t>
+          <t>https://openalex.org/W4402843978</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>10.38094/jastt20165</t>
+          <t>10.58248/pn633</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Classification Based on Decision Tree Algorithm for Machine Learning</t>
+          <t>Interpretable machine learning</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -19916,76 +19948,56 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>report</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>1819</v>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>JOURNAL OF APPLIED SCIENCE AND TECHNOLOGY TRENDS</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Journal of Applied Science and Technology Trends</t>
-        </is>
-      </c>
+        <v>987</v>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
-          <t>['Bahzad Charbuty', 'Adnan Mohsin Abdulazeez']</t>
+          <t>['Parliamentary Office of Science and Technology', 'Lorna Christie']</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>['Bahzad Charbuty', 'Adnan Abdulazeez']</t>
+          <t>['Parliamentary Office of Science and Technology', 'Lorna Christie']</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>['IT Department, Technical College of Informatics Akre, Duhok Polytechnic University, Duhok, Kurdistan Region, Iraq', 'Duhok Polytechnic University, Duhok, Kurdistan Region, Iraq']</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parliamentary Office of Science and Technology (corresponding author), </t>
+        </is>
+      </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>Decision tree classifiers are regarded to be a standout of the most well-known methods to data classification representation of classifiers. Different researchers from various fields and backgrounds have considered the problem of extending a decision tree from available data, such as machine study, pattern recognition, and statistics. In various fields such as medical disease analysis, text classification, user smartphone classification, images, and many more the employment of Decision tree classifiers has been proposed in many ways. This paper provides a detailed approach to the decision trees. Furthermore, paper specifics, such as algorithms/approaches used, datasets, and outcomes achieved, are evaluated and outlined comprehensively. In addition, all of the approaches analyzed were discussed to illustrate the themes of the authors and identify the most accurate classifiers. As a result, the uses of different types of datasets are discussed and their findings are analyzed.</t>
-        </is>
-      </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>Machine learning (ML, a type of artificial intelligence) is increasingly being used to support decision making in a variety of applications including recruitment and clinical diagnoses. While ML has many advantages, there are concerns that in some cases it may not be possible to explain completely how its outputs have been produced. This POSTnote gives an overview of ML and its role in decision-making. It examines the challenges of understanding how a complex ML system has reached its output, and some of the technical approaches to making ML easier to interpret. It also gives a brief overview of some of the proposed tools for making ML systems more accountable.</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr">
         <is>
-          <t>['Decision tree', 'Computer science', 'Machine learning', 'Artificial intelligence', 'ID3 algorithm', 'Decision tree learning', 'Incremental decision tree', 'Representation (politics)', 'Tree (set theory)', 'Statistical classification', 'Data mining', 'Pattern recognition (psychology)', 'Mathematics']</t>
+          <t>['Artificial intelligence', 'Computer science', 'Machine learning']</t>
         </is>
       </c>
       <c r="T171" t="inlineStr">
         <is>
-          <t>['IQ']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>['Kotsiantis S, 2007, ', 'Carleo G, 2019, REVIEWS OF MODERN PHYSICS', 'Libbrecht M, 2015, NATURE REVIEWS GENETICS', 'Kotsiantis S, 2006, ARTIFICIAL INTELLIGENCE REVIEW', 'Palo V, 2015, ', 'Lim T, 2000, MACHINE LEARNING', 'Song Y, 2015, PUBMED', 'Tso K, 2007, ENERGY', 'Zou Q, 2018, FRONTIERS IN GENETICS', 'Rokach L, 2005, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS PART C (APPLICATIONS AND REVIEWS)', 'Janikow C, 1998, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS PART B (CYBERNETICS)', 'Loh W, 2014, INTERNATIONAL STATISTICAL REVIEW', 'Raileanu L, 2004, ANNALS OF MATHEMATICS AND ARTIFICIAL INTELLIGENCE', 'Swain P, 1977, IEEE TRANSACTIONS ON GEOSCIENCE ELECTRONICS', 'Mántaras R, 1991, MACHINE LEARNING', 'Eesa A, 2014, EXPERT SYSTEMS WITH APPLICATIONS', 'Brodley C, 1995, MACHINE LEARNING', 'Barros R, 2011, IEEE TRANSACTIONS ON SYSTEMS MAN AND CYBERNETICS PART C (APPLICATIONS AND REVIEWS)', 'Zhao Y, 2007, ADVANCES IN SPACE RESEARCH', 'Stein G, 2005, ', 'Liang J, 2019, IEEE TRANSACTIONS ON DEPENDABLE AND SECURE COMPUTING', 'Zeebaree D, 2018, ', 'Pérez‐Ortiz M, 2016, ENERGIES', 'Shang C, 2013, KNOWLEDGE-BASED SYSTEMS', 'Zeebaree D, 2019, ', 'Maszczyk T, 2008, LECTURE NOTES IN COMPUTER SCIENCE', 'Linty N, 2018, IEEE TRANSACTIONS ON AEROSPACE AND ELECTRONIC SYSTEMS', 'Damanik I, 2019, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Suresh A, 2019, SOFT COMPUTING', 'Feng C, 2017, ', 'Taneja S, 2014, ', 'Gavankar S, 2017, ', 'Wang J, 2005, LECTURE NOTES IN COMPUTER SCIENCE', 'Kumar R, 2012, ', 'Bengio Y, 2010, COMPUTATIONAL INTELLIGENCE', 'Kuang W, 2019, IEEE TRANSACTIONS ON CIRCUITS AND SYSTEMS FOR VIDEO TECHNOLOGY', 'Ahmed N, 2018, ', 'Anuradha, 2014, ', 'Nagra A, 2019, CONNECTION SCIENCE', 'Patil D, 2006, ', 'Zhang Y, 2019, ', 'Shamim A, 2010, ', 'Cheushev V, 2002, ', 'Hussain D, 2018, JOURNAL OF X-RAY SCIENCE AND TECHNOLOGY', 'Hassan O, 2018, ', 'Ahmim A, 2019, ', 'Eesa A, 2017, SCIENCE JOURNAL OF UNIVERSITY OF ZAKHO', 'Liu Y, 2013, ', 'Maulud D, 2020, JOURNAL OF APPLIED SCIENCE AND TECHNOLOGY TRENDS', 'Zebari R, 2020, JOURNAL OF APPLIED SCIENCE AND TECHNOLOGY TRENDS', 'Ling Q, 2023, APPLIED AND COMPUTATIONAL ENGINEERING', 'Brodley C, 1995, MACHINE LEARNING', 'Priyanka N, 2020, INTERNATIONAL JOURNAL OF INFORMATION AND DECISION SCIENCES', ', 2017, INTERNATIONAL JOURNAL OF MODERN TRENDS IN ENGINEERING &amp; RESEARCH', 'Hillel T, 2020, JOURNAL OF CHOICE MODELLING', 'Pahwa K, 2019, ', 'Li M, 2019, ENTROPY', 'Yang F, 2019, ', 'Omar A, 2019, ', 'Assegie T, 2019, INTERNATIONAL JOURNAL OF POWER ELECTRONICS AND DRIVE SYSTEMS/INTERNATIONAL JOURNAL OF ELECTRICAL AND COMPUTER ENGINEERING', 'Nandhini S, 2020, 2020 INTERNATIONAL CONFERENCE ON EMERGING TRENDS IN INFORMATION TECHNOLOGY AND ENGINEERING (IC-ETITE)', 'Sulaiman M, 2020, INTERNATIONAL JOURNAL OF SUSTAINABLE CONSTRUCTION ENGINEERING AND TECHNOLOGY (UNIVERSITI TUN HUSSEIN ONN MALAYSIA)', 'Pathan S, 2019, JOURNAL OF APPLIED BIOMEDICINE', 'Kumar D, 2020, INTERNATIONAL JOURNAL OF INFORMATION AND DECISION SCIENCES', 'Patil S, 2019, 2019 3RD INTERNATIONAL CONFERENCE ON TRENDS IN ELECTRONICS AND INFORMATICS (ICOEI)', 'Sathiyanarayanan P, 2019, 2019 IEEE INTERNATIONAL CONFERENCE ON SYSTEM, COMPUTATION, AUTOMATION AND NETWORKING (ICSCAN)', 'Dash S, 2020, SMART INNOVATION, SYSTEMS AND TECHNOLOGIES', 'Arowolo M, 2020, ', 'Mrva J, 2019, ', 'Jiao S, 2020, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Taloba A, 2019, ', 'Ramadhan I, 2020, ', 'Felice F, 2019, JOURNAL OF CANCER RESEARCH AND CLINICAL ONCOLOGY', 'Issa A, 2011, ENGINEERING AND TECHNOLOGY JOURNAL', 'Chen X, 2019, 2019 3RD INTERNATIONAL CONFERENCE ON ELECTRONIC INFORMATION TECHNOLOGY AND COMPUTER ENGINEERING (EITCE)', 'Vishwakarma A, 2024, ', 'M�ntaras R, 1991, MACHINE LEARNING', 'Batitis V, 2020, ', 'Goyal P, 2020, ']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="V171" t="inlineStr">
@@ -20001,12 +20013,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>Charbuty B, 2021, JOURNAL OF APPLIED SCIENCE AND TECHNOLOGY TRENDS</t>
+          <t xml:space="preserve">Technology P, 2020, </t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>Charbuty B, 2021, JOURNAL OF APPLIED SCIENCE AND TECHNOLOGY TRENDS</t>
+          <t xml:space="preserve">Technology P, 2020, </t>
         </is>
       </c>
     </row>
@@ -20061,7 +20073,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>['Olvi, Mangasarian']</t>
+          <t>['Sra, Suvrit 1976-']</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -20071,7 +20083,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Olvi, Mangasarian (corresponding author), Dept. Empirical Inference, Max Planck Institute for Intelligent Systems, Max Planck Society</t>
+          <t>Sra, Suvrit 1976- (corresponding author), Dept. Empirical Inference, Max Planck Institute for Intelligent Systems, Max Planck Society</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -20123,22 +20135,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://openalex.org/W4206070770</t>
+          <t>https://openalex.org/W2138178898</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>10.1108/k.2010.06739hae.001</t>
+          <t>10.1147/rd.441.0206</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Introduction to Machine Learning</t>
+          <t>Some studies in machine learning using the game of checkers</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -20152,26 +20164,26 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>1198</v>
+        <v>1443</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>KYBERNETES</t>
+          <t>IBM JOURNAL OF RESEARCH AND DEVELOPMENT</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Kybernetes</t>
+          <t>IBM Journal of Research and Development</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>['Introduzione Al Corso', 'Roberto Basili', 'Wm&amp;amp;amp;r Motivazioni']</t>
+          <t>['Arthur L. Samuel']</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>['Introduzione Al Corso', 'Roberto Basili', 'Wm&amp;amp;amp;r Motivazioni']</t>
+          <t>['A. L. Samuel']</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -20179,23 +20191,39 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A. L. Samuel (corresponding author), </t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Two machine-learning procedures have been investigated in some detail using the game of checkers. Enough work has been done to verify the fact that a computer can be programmed so that it will learn to play a better game of checkers than can be played by the person who wrote the program. Furthermore, it can learn to do this in a remarkably short period of time (8 or 10 hours of machine-playing time) when given only the rules of the game, a sense of direction, and a redundant and incomplete list of parameters which are thought to have something to do with the game, but whose correct signs and relative weights are unknown and unspecified. The principles of machine learning verified by these experiments are, of course, applicable to many other situations.</t>
+        </is>
+      </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Q173" t="inlineStr"/>
-      <c r="R173" t="inlineStr"/>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>['Cybernetics', 'Computer science', 'Artificial intelligence']</t>
+          <t>['Computer science', 'Artificial intelligence', 'Machine learning']</t>
         </is>
       </c>
       <c r="T173" t="inlineStr">
@@ -20205,7 +20233,7 @@
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Rosenblatt F, 1958, PSYCHOLOGICAL REVIEW', 'Shannon, 1950, THE PHILOSOPHICAL MAGAZINE A JOURNAL OF THEORETICAL EXPERIMENTAL AND APPLIED PHYSICS', 'Newell A, 1958, IBM JOURNAL OF RESEARCH AND DEVELOPMENT', 'Rochester N, 1956, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Strachey C, 1952, ', 'Bernstein A, 1958, SCIENTIFIC AMERICAN', 'Kister J, 1957, JOURNAL OF THE ACM', 'McCulloch W, 1949, ']</t>
         </is>
       </c>
       <c r="V173" t="inlineStr">
@@ -20221,34 +20249,34 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>Corso I, 2010, KYBERNETES</t>
+          <t>Samuel A, 2000, IBM JOURNAL OF RESEARCH AND DEVELOPMENT</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>Corso I, 2010, KYBERNETES</t>
+          <t>Samuel A, 2000, IBM JOURNAL OF RESEARCH AND DEVELOPMENT</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2138178898</t>
+          <t>https://openalex.org/W4206070770</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>10.1147/rd.441.0206</t>
+          <t>10.1108/k.2010.06739hae.001</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Some studies in machine learning using the game of checkers</t>
+          <t>Introduction to Machine Learning</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -20262,26 +20290,26 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>1443</v>
+        <v>1198</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>IBM JOURNAL OF RESEARCH AND DEVELOPMENT</t>
+          <t>KYBERNETES</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>IBM Journal of Research and Development</t>
+          <t>Kybernetes</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>['Arthur L. Samuel']</t>
+          <t>['Bernhard Schölkopf']</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>['A. L. Samuel']</t>
+          <t>['Bernhard Schölkopf']</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -20291,37 +20319,25 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">A. L. Samuel (corresponding author), </t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>Two machine-learning procedures have been investigated in some detail using the game of checkers. Enough work has been done to verify the fact that a computer can be programmed so that it will learn to play a better game of checkers than can be played by the person who wrote the program. Furthermore, it can learn to do this in a remarkably short period of time (8 or 10 hours of machine-playing time) when given only the rules of the game, a sense of direction, and a redundant and incomplete list of parameters which are thought to have something to do with the game, but whose correct signs and relative weights are unknown and unspecified. The principles of machine learning verified by these experiments are, of course, applicable to many other situations.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Bernhard Schölkopf (corresponding author), </t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>39</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr">
         <is>
-          <t>['Computer science', 'Artificial intelligence', 'Machine learning']</t>
+          <t>['Cybernetics', 'Computer science', 'Artificial intelligence']</t>
         </is>
       </c>
       <c r="T174" t="inlineStr">
@@ -20331,7 +20347,7 @@
       </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>['Rosenblatt F, 1958, PSYCHOLOGICAL REVIEW', 'Shannon, 1950, THE PHILOSOPHICAL MAGAZINE A JOURNAL OF THEORETICAL EXPERIMENTAL AND APPLIED PHYSICS', 'Newell A, 1958, IBM JOURNAL OF RESEARCH AND DEVELOPMENT', 'Rochester N, 1956, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Strachey C, 1952, ', 'Bernstein A, 1958, SCIENTIFIC AMERICAN', 'Kister J, 1957, JOURNAL OF THE ACM', 'McCulloch W, 1949, ']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="V174" t="inlineStr">
@@ -20347,12 +20363,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>Samuel A, 2000, IBM JOURNAL OF RESEARCH AND DEVELOPMENT</t>
+          <t>Schölkopf B, 2010, KYBERNETES</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>Samuel A, 2000, IBM JOURNAL OF RESEARCH AND DEVELOPMENT</t>
+          <t>Schölkopf B, 2010, KYBERNETES</t>
         </is>
       </c>
     </row>
@@ -20388,7 +20404,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -20514,7 +20530,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>1692</v>
+        <v>1695</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -20607,22 +20623,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2342603028</t>
+          <t>https://openalex.org/W2972418846</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>10.21037/atm.2016.03.37</t>
+          <t>10.1002/inf2.12028</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Introduction to machine learning: k-nearest neighbors</t>
+          <t>Machine learning in materials science</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -20636,66 +20652,66 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>1255</v>
+        <v>1001</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>ANNALS OF TRANSLATIONAL MEDICINE</t>
+          <t>INFOMAT</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Annals of Translational Medicine</t>
+          <t>InfoMat</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>['Zhongheng Zhang']</t>
+          <t>['Jing Wei', 'Xuan Chu', 'Xiangyu Sun', 'Kun Xu', 'Hui‐Xiong Deng', 'Ji-Gen Chen', 'Zhongming Wei', 'Ming Lei']</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>['Zhongheng Zhang']</t>
+          <t>['Jing Wei', 'Xuan Chu', 'Xiang‐Yu Sun', 'Kun Xu', 'Hui‐Xiong Deng', 'Jigen Chen', 'Zhongming Wei', 'Ming Lei']</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>['Department of Critical Care Medicine, Jinhua Municipal Central Hospital, Jinhua Hospital of Zhejiang University, Jinhua 321000, China', 'Municipal Central Hospital. He graduated from School of Medicine, Zhejiang University in 2009', 'Department of Critical Care Medicine, Jinhua Municipal Central Hospital, Jinhua Hospital of Zhejiang University', '351#, Mingyue Road, Jinhua 321000, China']</t>
+          <t>['State Key Laboratory of Information Photonics and Optical Communications Beijing University of Posts and Telecommunications  Beijing China', 'State Key Laboratory of Information Photonics and Optical Communications, Beijing University of Posts and Telecommunications, Beijing, China', 'State Key Laboratory of Information Photonics and Optical Communications Beijing University of Posts and Telecommunications  Beijing China', 'State Key Laboratory of Information Photonics and Optical Communications, Beijing University of Posts and Telecommunications, Beijing, China', 'State Key Laboratory of Information Photonics and Optical Communications Beijing University of Posts and Telecommunications  Beijing China', 'State Key Laboratory of Information Photonics and Optical Communications, Beijing University of Posts and Telecommunications, Beijing, China', 'State Key Laboratory of Information Photonics and Optical Communications Beijing University of Posts and Telecommunications  Beijing China', 'State Key Laboratory of Information Photonics and Optical Communications, Beijing University of Posts and Telecommunications, Beijing, China', 'State Key Laboratory of Superlattices and Microstructures, Institute of Semiconductors, Chinese Academy of Sciences, Center of Materials Science and Optoelectronics Engineering University of Chinese Academy of Sciences  Beijing China', 'State Key Laboratory of Superlattices and Microstructures, Institute of Semiconductors, Chinese Academy of Sciences, Center of Materials Science and Optoelectronics Engineering, University of Chinese Academy of Sciences, Beijing, China', 'Zhejiang Provincial Key Laboratory for Cutting Tools Taizhou University  Taizhou China', 'Zhejiang Provincial Key Laboratory for Cutting Tools, Taizhou University, Taizhou, China', 'Beijing Academy of Quantum Information Sciences  Beijing China', 'State Key Laboratory of Superlattices and Microstructures, Institute of Semiconductors, Chinese Academy of Sciences, Center of Materials Science and Optoelectronics Engineering University of Chinese Academy of Sciences  Beijing China', 'Beijing Academy of Quantum Information Sciences, Beijing, China', 'State Key Laboratory of Superlattices and Microstructures, Institute of Semiconductors, Chinese Academy of Sciences, Center of Materials Science and Optoelectronics Engineering, University of Chinese Academy of Sciences, Beijing, China', 'State Key Laboratory of Information Photonics and Optical Communications Beijing University of Posts and Telecommunications  Beijing China', 'State Key Laboratory of Information Photonics and Optical Communications, Beijing University of Posts and Telecommunications, Beijing, China']</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Zhongheng Zhang (corresponding author), Department of Critical Care Medicine, Jinhua Municipal Central Hospital, Jinhua Hospital of Zhejiang University, Jinhua 321000, China; Municipal Central Hospital. He graduated from School of Medicine, Zhejiang University in 2009; Department of Critical Care Medicine, Jinhua Municipal Central Hospital, Jinhua Hospital of Zhejiang University; 351#, Mingyue Road, Jinhua 321000, China</t>
+          <t>Ming Lei (corresponding author), State Key Laboratory of Information Photonics and Optical Communications Beijing University of Posts and Telecommunications  Beijing China; State Key Laboratory of Information Photonics and Optical Communications, Beijing University of Posts and Telecommunications, Beijing, China</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>Machine learning techniques have been widely used in many scientific fields, but its use in medical literature is limited partly because of technical difficulties. k-nearest neighbors (kNN) is a simple method of machine learning. The article introduces some basic ideas underlying the kNN algorithm, and then focuses on how to perform kNN modeling with R. The dataset should be prepared before running the knn() function in R. After prediction of outcome with kNN algorithm, the diagnostic performance of the model should be checked. Average accuracy is the mostly widely used statistic to reflect the kNN algorithm. Factors such as k value, distance calculation and choice of appropriate predictors all have significant impact on the model performance.</t>
+          <t>Abstract Traditional methods of discovering new materials, such as the empirical trial and error method and the density functional theory (DFT)‐based method, are unable to keep pace with the development of materials science today due to their long development cycles, low efficiency, and high costs. Accordingly, due to its low computational cost and short development cycle, machine learning is coupled with powerful data processing and high prediction performance and is being widely used in material detection, material analysis, and material design. In this article, we discuss the basic operational procedures in analyzing material properties via machine learning, summarize recent applications of machine learning algorithms to several mature fields in materials science, and discuss the improvements that are required for wide‐ranging application.</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>338</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>358</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>['k-nearest neighbors algorithm', 'Computer science', 'Statistic', 'Artificial intelligence', 'Machine learning', 'Simple (philosophy)', 'Value (mathematics)', 'Function (biology)', 'Data mining', 'Statistics', 'Mathematics']</t>
+          <t>['Pace', 'Computer science', 'Machine learning', 'Artificial intelligence', 'Development (topology)', 'Ranging', 'Industrial engineering', 'Engineering', 'Mathematics']</t>
         </is>
       </c>
       <c r="T177" t="inlineStr">
@@ -20705,7 +20721,7 @@
       </c>
       <c r="U177" t="inlineStr">
         <is>
-          <t>['Weinberger K, 2009, JOURNAL OF MACHINE LEARNING RESEARCH', 'Linden A, 2006, JOURNAL OF EVALUATION IN CLINICAL PRACTICE', 'Cost S, 1993, MACHINE LEARNING', 'James D, 1996, TECHNOMETRICS', 'Short R, 1981, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Zhang Z, 2014, PUBMED', 'Hernández-Torruco J, 2015, ', 'Thompson J, 2001, STATISTICS IN MEDICINE', ', 2023, IEEE TRANSACTIONS ON INFORMATION THEORY']</t>
+          <t>['Szegedy C, 2015, ', 'Jain A, 2013, APL MATERIALS', 'Allen F, 2002, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE', 'Rogers D, 2010, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Waser R, 2009, ADVANCED MATERIALS', 'Arlot S, 2010, STATISTICS SURVEYS', 'Farabet C, 2012, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Bartók A, 2013, PHYSICAL REVIEW B', 'Saal J, 2013, JOM', 'Rupp M, 2012, PHYSICAL REVIEW LETTERS', 'Brown M, 2000, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Kononenko I, 2001, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Xiong H, 2014, SCIENCE', 'Ma J, 2015, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Curtarolo S, 2012, COMPUTATIONAL MATERIALS SCIENCE', 'Helmstaedter M, 2013, NATURE', 'Ruoff R, 1993, THE JOURNAL OF PHYSICAL CHEMISTRY', 'Cambria E, 2014, IEEE COMPUTATIONAL INTELLIGENCE MAGAZINE', 'Cully A, 2015, NATURE', 'Hand D, 2001, INTERNATIONAL STATISTICAL REVIEW', 'Pilania G, 2013, SCIENTIFIC REPORTS', 'Hansen K, 2015, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Hansen K, 2013, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Tsai C, 2014, IEEE COMMUNICATIONS SURVEYS &amp; TUTORIALS', 'Hautier G, 2010, CHEMISTRY OF MATERIALS', 'Schütt K, 2014, PHYSICAL REVIEW B', 'Seko A, 2014, PHYSICAL REVIEW B', 'Kalidindi S, 2015, ANNUAL REVIEW OF MATERIALS RESEARCH', 'Hachmann J, 2013, ENERGY &amp; ENVIRONMENTAL SCIENCE', 'Nantasenamat C, 2010, EXPERT OPINION ON DRUG DISCOVERY', 'Epa V, 2012, NANO LETTERS', 'Feng N, 2013, INFORMATION SCIENCES', 'Dey P, 2013, COMPUTATIONAL MATERIALS SCIENCE', 'Butcher J, 2013, COMPUTER-AIDED CIVIL AND INFRASTRUCTURE ENGINEERING', 'Ciodaro T, 2012, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Maghsoudi M, 2014, SPECTROCHIMICA ACTA PART A MOLECULAR AND BIOMOLECULAR SPECTROSCOPY', 'Mántaras R, 1998, DATA &amp; KNOWLEDGE ENGINEERING', 'Sadowski Ł, 2012, ARCHIVES OF CIVIL AND MECHANICAL ENGINEERING', 'Cho K, 2002, JOURNAL OF MOLECULAR STRUCTURE', 'Amato F, 2012, TALANTA', 'Zhao G, 2013, ', 'Postolache O, 2010, COMPUTER STANDARDS &amp; INTERFACES', 'Yang L, 2013, PHYSICAL REVIEW B', 'Akbarpour H, 2013, COMPUTATIONAL MATERIALS SCIENCE', 'Castelli I, 2014, MODELLING AND SIMULATION IN MATERIALS SCIENCE AND ENGINEERING', 'Prabhu D, 1993, REVIEW OF PROGRESS IN QUANTITATIVE NONDESTRUCTIVE EVALUATION', 'Pyrgiotakis G, 2011, JOURNAL OF RAMAN SPECTROSCOPY', 'Bardsley W, 1986, BIOMETRIKA', 'Cifarelli C, 2006, OPTIMIZATION METHODS &amp; SOFTWARE', 'Barton T, 2002, ', 'Burges C, 1998, DATA MINING AND KNOWLEDGE DISCOVERY', 'Silver D, 2016, NATURE', 'Hinton G, 2012, IEEE SIGNAL PROCESSING MAGAZINE', 'Joachims T, 1998, LECTURE NOTES IN COMPUTER SCIENCE', 'Shin H, 2016, IEEE TRANSACTIONS ON MEDICAL IMAGING', 'Gómez-Bombarelli R, 2018, ACS CENTRAL SCIENCE', 'Wu Z, 2017, CHEMICAL SCIENCE', 'Kirklin S, 2015, NPJ COMPUTATIONAL MATERIALS', 'Smith J, 2017, CHEMICAL SCIENCE', 'Raccuglia P, 2016, NATURE', 'Kearnes S, 2016, JOURNAL OF COMPUTER-AIDED MOLECULAR DESIGN', 'Ward L, 2016, NPJ COMPUTATIONAL MATERIALS', 'Schütt K, 2017, NATURE COMMUNICATIONS', 'Agrawal A, 2016, APL MATERIALS', 'Janssens O, 2016, JOURNAL OF SOUND AND VIBRATION', 'Li L, 2016, SENSORS', 'Meredig B, 2014, PHYSICAL REVIEW B', 'Zhao R, 2017, SENSORS', 'Hachmann J, 2011, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Jing L, 2017, MEASUREMENT', 'Ulissi Z, 2017, NATURE COMMUNICATIONS', 'Zhang P, 1993, THE ANNALS OF STATISTICS', 'Lal T, 2004, IEEE TRANSACTIONS ON BIOMEDICAL ENGINEERING', 'Oh E, 2016, NATURE NANOTECHNOLOGY', 'Leung M, 2014, BIOINFORMATICS', 'Gibert X, 2016, IEEE TRANSACTIONS ON INTELLIGENT TRANSPORTATION SYSTEMS', 'Ward L, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Oliynyk A, 2016, CHEMISTRY OF MATERIALS', 'Warmuth M, 2003, JOURNAL OF CHEMICAL INFORMATION AND COMPUTER SCIENCES', 'Liu H, 2017, PHYSICS OF LIFE REVIEWS', 'Agrawal A, 2014, INTEGRATING MATERIALS AND MANUFACTURING INNOVATION', 'Lima A, 2016, EXPERT OPINION ON DRUG DISCOVERY', 'Zhao R, 2016, ', 'Meng M, 2017, NEUROCOMPUTING', 'Legrain F, 2017, THE JOURNAL OF PHYSICAL CHEMISTRY B', 'Saad Y, 2012, PHYSICAL REVIEW B', 'Giben X, 2015, ', 'Pankajakshan P, 2017, CHEMISTRY OF MATERIALS', 'Hirn M, 2017, MULTISCALE MODELING AND SIMULATION', 'Serra J, 2007, COMBINATORIAL CHEMISTRY &amp; HIGH THROUGHPUT SCREENING', 'Dong J, 2017, JOURNAL OF CHEMINFORMATICS', 'Garcia‐Molina G, 2003, EURASIP JOURNAL ON ADVANCES IN SIGNAL PROCESSING', 'Liu J, 2015, SIGNAL PROCESSING', 'Uruchurtu J, 2012, RECENT PATENTS ON CORROSION SCIENCE', 'Field A, 1921, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Duvenaud D, 2015, ARXIV (CORNELL UNIVERSITY)', 'Wallach I, 2015, ARXIV (CORNELL UNIVERSITY)', 'Goh G, 2017, ARXIV (CORNELL UNIVERSITY)', 'LeCun Y, 2015, NATURE', 'Cortes C, 1995, MACHINE LEARNING', 'Quinlan J, 1986, MACHINE LEARNING', 'Silver D, 2017, NATURE', 'Butler K, 2018, NATURE', 'Arlot S, 2009, ', 'Deng L, 2014, FOUNDATIONS AND TRENDS® IN SIGNAL PROCESSING', 'Zhao R, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Schütt K, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Sánchez-Lengeling B, 2018, SCIENCE', 'Gómez‐Bombarelli R, 2018, CAMBRIDGE UNIVERSITY ENGINEERING DEPARTMENT PUBLICATIONS DATABASE', 'Cha Y, 2017, COMPUTER-AIDED CIVIL AND INFRASTRUCTURE ENGINEERING', 'Zhang A, 2017, COMPUTER-AIDED CIVIL AND INFRASTRUCTURE ENGINEERING', 'Lu S, 2018, NATURE COMMUNICATIONS', 'Faber F, 2017, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Lin Y, 2017, COMPUTER-AIDED CIVIL AND INFRASTRUCTURE ENGINEERING', ', 1998, MACHINE LEARNING', 'Wainberg M, 2018, NATURE BIOTECHNOLOGY', 'Feinberg E, 2018, ACS CENTRAL SCIENCE', 'Jia F, 2017, NEUROCOMPUTING', 'Jha D, 2018, SCIENTIFIC REPORTS', 'Kim E, 2017, CHEMISTRY OF MATERIALS', 'Zhou Z, 2017, ACS CENTRAL SCIENCE', 'Carrete J, 2014, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Atha D, 2017, STRUCTURAL HEALTH MONITORING', 'Cecen A, 2017, ACTA MATERIALIA', 'Elton D, 2018, SCIENTIFIC REPORTS', 'Wei J, 2018, ADVANCED MATERIALS', 'Jang K, 2019, STRUCTURAL HEALTH MONITORING', 'Nash W, 2018, NPJ MATERIALS DEGRADATION', 'Zhu Q, 2018, NATURE COMMUNICATIONS', 'Kim K, 2018, NPJ COMPUTATIONAL MATERIALS', 'Wang X, 2017, ', 'Hou W, 2018, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Wang M, 2019, SMALL METHODS', 'Sun B, 2017, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Burman P, 1989, BIOMETRIKA', 'Widener\ufeff\ufeff\ufeff A, 2013, CHEMICAL &amp; ENGINEERING NEWS', 'Liu L, 2018, ', 'Huang B, 2017, ARXIV (CORNELL UNIVERSITY)', 'Wu W, 2018, ZHONGGUO KEXUE. WULIXUE LIXUE TIANWENXUE', 'Sutskever I, 2014, ARXIV (CORNELL UNIVERSITY)', 'Gilmer J, 2017, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V177" t="inlineStr">
@@ -20721,34 +20737,34 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>Zhang Z, 2016, ANNALS OF TRANSLATIONAL MEDICINE</t>
+          <t>Wei J, 2019, INFOMAT</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>Zhang Z, 2016, ANNALS OF TRANSLATIONAL MEDICINE</t>
+          <t>Wei J, 2019, INFOMAT</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2972418846</t>
+          <t>https://openalex.org/W2342603028</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>10.1002/inf2.12028</t>
+          <t>10.21037/atm.2016.03.37</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Machine learning in materials science</t>
+          <t>Introduction to machine learning: k-nearest neighbors</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -20762,66 +20778,66 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>1000</v>
+        <v>1255</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>INFOMAT</t>
+          <t>ANNALS OF TRANSLATIONAL MEDICINE</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>InfoMat</t>
+          <t>Annals of Translational Medicine</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>['Jing Wei', 'Xuan Chu', 'Xiangyu Sun', 'Kun Xu', 'Hui‐Xiong Deng', 'Ji-Gen Chen', 'Zhongming Wei', 'Ming Lei']</t>
+          <t>['Zhongheng Zhang']</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>['Jing Wei', 'Xuan Chu', 'Xiang‐Yu Sun', 'Kun Xu', 'Hui‐Xiong Deng', 'Jigen Chen', 'Zhongming Wei', 'Ming Lei']</t>
+          <t>['Zhongheng Zhang']</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>['State Key Laboratory of Information Photonics and Optical Communications Beijing University of Posts and Telecommunications  Beijing China', 'State Key Laboratory of Information Photonics and Optical Communications, Beijing University of Posts and Telecommunications, Beijing, China', 'State Key Laboratory of Information Photonics and Optical Communications Beijing University of Posts and Telecommunications  Beijing China', 'State Key Laboratory of Information Photonics and Optical Communications, Beijing University of Posts and Telecommunications, Beijing, China', 'State Key Laboratory of Information Photonics and Optical Communications Beijing University of Posts and Telecommunications  Beijing China', 'State Key Laboratory of Information Photonics and Optical Communications, Beijing University of Posts and Telecommunications, Beijing, China', 'State Key Laboratory of Information Photonics and Optical Communications Beijing University of Posts and Telecommunications  Beijing China', 'State Key Laboratory of Information Photonics and Optical Communications, Beijing University of Posts and Telecommunications, Beijing, China', 'State Key Laboratory of Superlattices and Microstructures, Institute of Semiconductors, Chinese Academy of Sciences, Center of Materials Science and Optoelectronics Engineering University of Chinese Academy of Sciences  Beijing China', 'State Key Laboratory of Superlattices and Microstructures, Institute of Semiconductors, Chinese Academy of Sciences, Center of Materials Science and Optoelectronics Engineering, University of Chinese Academy of Sciences, Beijing, China', 'Zhejiang Provincial Key Laboratory for Cutting Tools Taizhou University  Taizhou China', 'Zhejiang Provincial Key Laboratory for Cutting Tools, Taizhou University, Taizhou, China', 'Beijing Academy of Quantum Information Sciences  Beijing China', 'State Key Laboratory of Superlattices and Microstructures, Institute of Semiconductors, Chinese Academy of Sciences, Center of Materials Science and Optoelectronics Engineering University of Chinese Academy of Sciences  Beijing China', 'Beijing Academy of Quantum Information Sciences, Beijing, China', 'State Key Laboratory of Superlattices and Microstructures, Institute of Semiconductors, Chinese Academy of Sciences, Center of Materials Science and Optoelectronics Engineering, University of Chinese Academy of Sciences, Beijing, China', 'State Key Laboratory of Information Photonics and Optical Communications Beijing University of Posts and Telecommunications  Beijing China', 'State Key Laboratory of Information Photonics and Optical Communications, Beijing University of Posts and Telecommunications, Beijing, China']</t>
+          <t>['Department of Critical Care Medicine, Jinhua Municipal Central Hospital, Jinhua Hospital of Zhejiang University, Jinhua 321000, China', 'Municipal Central Hospital. He graduated from School of Medicine, Zhejiang University in 2009', 'Department of Critical Care Medicine, Jinhua Municipal Central Hospital, Jinhua Hospital of Zhejiang University', '351#, Mingyue Road, Jinhua 321000, China']</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Ming Lei (corresponding author), State Key Laboratory of Information Photonics and Optical Communications Beijing University of Posts and Telecommunications  Beijing China; State Key Laboratory of Information Photonics and Optical Communications, Beijing University of Posts and Telecommunications, Beijing, China</t>
+          <t>Zhongheng Zhang (corresponding author), Department of Critical Care Medicine, Jinhua Municipal Central Hospital, Jinhua Hospital of Zhejiang University, Jinhua 321000, China; Municipal Central Hospital. He graduated from School of Medicine, Zhejiang University in 2009; Department of Critical Care Medicine, Jinhua Municipal Central Hospital, Jinhua Hospital of Zhejiang University; 351#, Mingyue Road, Jinhua 321000, China</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>Abstract Traditional methods of discovering new materials, such as the empirical trial and error method and the density functional theory (DFT)‐based method, are unable to keep pace with the development of materials science today due to their long development cycles, low efficiency, and high costs. Accordingly, due to its low computational cost and short development cycle, machine learning is coupled with powerful data processing and high prediction performance and is being widely used in material detection, material analysis, and material design. In this article, we discuss the basic operational procedures in analyzing material properties via machine learning, summarize recent applications of machine learning algorithms to several mature fields in materials science, and discuss the improvements that are required for wide‐ranging application.</t>
+          <t>Machine learning techniques have been widely used in many scientific fields, but its use in medical literature is limited partly because of technical difficulties. k-nearest neighbors (kNN) is a simple method of machine learning. The article introduces some basic ideas underlying the kNN algorithm, and then focuses on how to perform kNN modeling with R. The dataset should be prepared before running the knn() function in R. After prediction of outcome with kNN algorithm, the diagnostic performance of the model should be checked. Average accuracy is the mostly widely used statistic to reflect the kNN algorithm. Factors such as k value, distance calculation and choice of appropriate predictors all have significant impact on the model performance.</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>218</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>['Pace', 'Computer science', 'Machine learning', 'Artificial intelligence', 'Development (topology)', 'Ranging', 'Industrial engineering', 'Engineering', 'Mathematics']</t>
+          <t>['k-nearest neighbors algorithm', 'Computer science', 'Statistic', 'Artificial intelligence', 'Machine learning', 'Simple (philosophy)', 'Value (mathematics)', 'Function (biology)', 'Data mining', 'Statistics', 'Mathematics']</t>
         </is>
       </c>
       <c r="T178" t="inlineStr">
@@ -20831,7 +20847,7 @@
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>['Szegedy C, 2015, ', 'Jain A, 2013, APL MATERIALS', 'Allen F, 2002, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE', 'Rogers D, 2010, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Waser R, 2009, ADVANCED MATERIALS', 'Arlot S, 2010, STATISTICS SURVEYS', 'Farabet C, 2012, IEEE TRANSACTIONS ON PATTERN ANALYSIS AND MACHINE INTELLIGENCE', 'Bartók A, 2013, PHYSICAL REVIEW B', 'Saal J, 2013, JOM', 'Rupp M, 2012, PHYSICAL REVIEW LETTERS', 'Brown M, 2000, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Kononenko I, 2001, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Xiong H, 2014, SCIENCE', 'Ma J, 2015, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Curtarolo S, 2012, COMPUTATIONAL MATERIALS SCIENCE', 'Helmstaedter M, 2013, NATURE', 'Ruoff R, 1993, THE JOURNAL OF PHYSICAL CHEMISTRY', 'Cambria E, 2014, IEEE COMPUTATIONAL INTELLIGENCE MAGAZINE', 'Cully A, 2015, NATURE', 'Hand D, 2001, INTERNATIONAL STATISTICAL REVIEW', 'Pilania G, 2013, SCIENTIFIC REPORTS', 'Hansen K, 2015, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Hansen K, 2013, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Tsai C, 2014, IEEE COMMUNICATIONS SURVEYS &amp; TUTORIALS', 'Hautier G, 2010, CHEMISTRY OF MATERIALS', 'Schütt K, 2014, PHYSICAL REVIEW B', 'Seko A, 2014, PHYSICAL REVIEW B', 'Kalidindi S, 2015, ANNUAL REVIEW OF MATERIALS RESEARCH', 'Hachmann J, 2013, ENERGY &amp; ENVIRONMENTAL SCIENCE', 'Nantasenamat C, 2010, EXPERT OPINION ON DRUG DISCOVERY', 'Epa V, 2012, NANO LETTERS', 'Feng N, 2013, INFORMATION SCIENCES', 'Dey P, 2013, COMPUTATIONAL MATERIALS SCIENCE', 'Butcher J, 2013, COMPUTER-AIDED CIVIL AND INFRASTRUCTURE ENGINEERING', 'Ciodaro T, 2012, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Maghsoudi M, 2014, SPECTROCHIMICA ACTA PART A MOLECULAR AND BIOMOLECULAR SPECTROSCOPY', 'Mántaras R, 1998, DATA &amp; KNOWLEDGE ENGINEERING', 'Sadowski Ł, 2012, ARCHIVES OF CIVIL AND MECHANICAL ENGINEERING', 'Cho K, 2002, JOURNAL OF MOLECULAR STRUCTURE', 'Amato F, 2012, TALANTA', 'Zhao G, 2013, ', 'Postolache O, 2010, COMPUTER STANDARDS &amp; INTERFACES', 'Yang L, 2013, PHYSICAL REVIEW B', 'Akbarpour H, 2013, COMPUTATIONAL MATERIALS SCIENCE', 'Castelli I, 2014, MODELLING AND SIMULATION IN MATERIALS SCIENCE AND ENGINEERING', 'Prabhu D, 1993, REVIEW OF PROGRESS IN QUANTITATIVE NONDESTRUCTIVE EVALUATION', 'Pyrgiotakis G, 2011, JOURNAL OF RAMAN SPECTROSCOPY', 'Bardsley W, 1986, BIOMETRIKA', 'Cifarelli C, 2006, OPTIMIZATION METHODS &amp; SOFTWARE', 'Barton T, 2002, ', 'Burges C, 1998, DATA MINING AND KNOWLEDGE DISCOVERY', 'Silver D, 2016, NATURE', 'Hinton G, 2012, IEEE SIGNAL PROCESSING MAGAZINE', 'Joachims T, 1998, LECTURE NOTES IN COMPUTER SCIENCE', 'Shin H, 2016, IEEE TRANSACTIONS ON MEDICAL IMAGING', 'Gómez-Bombarelli R, 2018, ACS CENTRAL SCIENCE', 'Wu Z, 2017, CHEMICAL SCIENCE', 'Kirklin S, 2015, NPJ COMPUTATIONAL MATERIALS', 'Smith J, 2017, CHEMICAL SCIENCE', 'Raccuglia P, 2016, NATURE', 'Kearnes S, 2016, JOURNAL OF COMPUTER-AIDED MOLECULAR DESIGN', 'Ward L, 2016, NPJ COMPUTATIONAL MATERIALS', 'Schütt K, 2017, NATURE COMMUNICATIONS', 'Agrawal A, 2016, APL MATERIALS', 'Janssens O, 2016, JOURNAL OF SOUND AND VIBRATION', 'Li L, 2016, SENSORS', 'Meredig B, 2014, PHYSICAL REVIEW B', 'Zhao R, 2017, SENSORS', 'Hachmann J, 2011, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Jing L, 2017, MEASUREMENT', 'Ulissi Z, 2017, NATURE COMMUNICATIONS', 'Zhang P, 1993, THE ANNALS OF STATISTICS', 'Lal T, 2004, IEEE TRANSACTIONS ON BIOMEDICAL ENGINEERING', 'Oh E, 2016, NATURE NANOTECHNOLOGY', 'Leung M, 2014, BIOINFORMATICS', 'Gibert X, 2016, IEEE TRANSACTIONS ON INTELLIGENT TRANSPORTATION SYSTEMS', 'Ward L, 2017, PHYSICAL REVIEW. B./PHYSICAL REVIEW. B', 'Oliynyk A, 2016, CHEMISTRY OF MATERIALS', 'Warmuth M, 2003, JOURNAL OF CHEMICAL INFORMATION AND COMPUTER SCIENCES', 'Liu H, 2017, PHYSICS OF LIFE REVIEWS', 'Agrawal A, 2014, INTEGRATING MATERIALS AND MANUFACTURING INNOVATION', 'Lima A, 2016, EXPERT OPINION ON DRUG DISCOVERY', 'Zhao R, 2016, ', 'Meng M, 2017, NEUROCOMPUTING', 'Legrain F, 2017, THE JOURNAL OF PHYSICAL CHEMISTRY B', 'Saad Y, 2012, PHYSICAL REVIEW B', 'Giben X, 2015, ', 'Pankajakshan P, 2017, CHEMISTRY OF MATERIALS', 'Hirn M, 2017, MULTISCALE MODELING AND SIMULATION', 'Serra J, 2007, COMBINATORIAL CHEMISTRY &amp; HIGH THROUGHPUT SCREENING', 'Dong J, 2017, JOURNAL OF CHEMINFORMATICS', 'Garcia‐Molina G, 2003, EURASIP JOURNAL ON ADVANCES IN SIGNAL PROCESSING', 'Liu J, 2015, SIGNAL PROCESSING', 'Uruchurtu J, 2012, RECENT PATENTS ON CORROSION SCIENCE', 'Field A, 1921, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Duvenaud D, 2015, ARXIV (CORNELL UNIVERSITY)', 'Wallach I, 2015, ARXIV (CORNELL UNIVERSITY)', 'Goh G, 2017, ARXIV (CORNELL UNIVERSITY)', 'LeCun Y, 2015, NATURE', 'Cortes C, 1995, MACHINE LEARNING', 'Quinlan J, 1986, MACHINE LEARNING', 'Silver D, 2017, NATURE', 'Butler K, 2018, NATURE', 'Arlot S, 2009, ', 'Deng L, 2014, FOUNDATIONS AND TRENDS® IN SIGNAL PROCESSING', 'Zhao R, 2018, MECHANICAL SYSTEMS AND SIGNAL PROCESSING', 'Schütt K, 2018, THE JOURNAL OF CHEMICAL PHYSICS', 'Sánchez-Lengeling B, 2018, SCIENCE', 'Gómez‐Bombarelli R, 2018, CAMBRIDGE UNIVERSITY ENGINEERING DEPARTMENT PUBLICATIONS DATABASE', 'Cha Y, 2017, COMPUTER-AIDED CIVIL AND INFRASTRUCTURE ENGINEERING', 'Zhang A, 2017, COMPUTER-AIDED CIVIL AND INFRASTRUCTURE ENGINEERING', 'Lu S, 2018, NATURE COMMUNICATIONS', 'Faber F, 2017, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Lin Y, 2017, COMPUTER-AIDED CIVIL AND INFRASTRUCTURE ENGINEERING', ', 1998, MACHINE LEARNING', 'Wainberg M, 2018, NATURE BIOTECHNOLOGY', 'Feinberg E, 2018, ACS CENTRAL SCIENCE', 'Jia F, 2017, NEUROCOMPUTING', 'Jha D, 2018, SCIENTIFIC REPORTS', 'Kim E, 2017, CHEMISTRY OF MATERIALS', 'Zhou Z, 2017, ACS CENTRAL SCIENCE', 'Carrete J, 2014, ZENODO (CERN EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Atha D, 2017, STRUCTURAL HEALTH MONITORING', 'Cecen A, 2017, ACTA MATERIALIA', 'Elton D, 2018, SCIENTIFIC REPORTS', 'Wei J, 2018, ADVANCED MATERIALS', 'Jang K, 2019, STRUCTURAL HEALTH MONITORING', 'Nash W, 2018, NPJ MATERIALS DEGRADATION', 'Zhu Q, 2018, NATURE COMMUNICATIONS', 'Kim K, 2018, NPJ COMPUTATIONAL MATERIALS', 'Wang X, 2017, ', 'Hou W, 2018, JOURNAL OF PHYSICS CONFERENCE SERIES', 'Wang M, 2019, SMALL METHODS', 'Sun B, 2017, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Burman P, 1989, BIOMETRIKA', 'Widener\ufeff\ufeff\ufeff A, 2013, CHEMICAL &amp; ENGINEERING NEWS', 'Liu L, 2018, ', 'Huang B, 2017, ARXIV (CORNELL UNIVERSITY)', 'Wu W, 2018, ZHONGGUO KEXUE. WULIXUE LIXUE TIANWENXUE', 'Sutskever I, 2014, ARXIV (CORNELL UNIVERSITY)', 'Gilmer J, 2017, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>['Weinberger K, 2009, JOURNAL OF MACHINE LEARNING RESEARCH', 'Linden A, 2006, JOURNAL OF EVALUATION IN CLINICAL PRACTICE', 'Cost S, 1993, MACHINE LEARNING', 'James D, 1996, TECHNOMETRICS', 'Short R, 1981, IEEE TRANSACTIONS ON INFORMATION THEORY', 'Zhang Z, 2014, PUBMED', 'Hernández-Torruco J, 2015, ', 'Thompson J, 2001, STATISTICS IN MEDICINE', ', 2023, IEEE TRANSACTIONS ON INFORMATION THEORY']</t>
         </is>
       </c>
       <c r="V178" t="inlineStr">
@@ -20847,12 +20863,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>Wei J, 2019, INFOMAT</t>
+          <t>Zhang Z, 2016, ANNALS OF TRANSLATIONAL MEDICINE</t>
         </is>
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>Wei J, 2019, INFOMAT</t>
+          <t>Zhang Z, 2016, ANNALS OF TRANSLATIONAL MEDICINE</t>
         </is>
       </c>
     </row>
@@ -21087,22 +21103,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2943491685</t>
+          <t>https://openalex.org/W2742835787</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>10.1016/s1470-2045(19)30149-4</t>
+          <t>10.1016/j.jmat.2017.08.002</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Big data and machine learning algorithms for health-care delivery</t>
+          <t>Materials discovery and design using machine learning</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -21112,76 +21128,80 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>1422</v>
+        <v>1229</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>THE LANCET ONCOLOGY</t>
+          <t>JOURNAL OF MATERIOMICS</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>The Lancet Oncology</t>
+          <t>Journal of Materiomics</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>['Kee Yuan Ngiam', 'Ing Wei Khor']</t>
+          <t>['Yue Liu', 'Tianlu Zhao', 'Wangwei Ju', 'Siqi Shi']</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>['Kee Yuan Ngiam', 'Ing Wei Khor']</t>
+          <t>['Yue Liu', 'Tianlu Zhao', 'Wangwei Ju', 'Siqi Shi']</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['Department of Surgery, National University of Singapore, Singapore; Division of General Surgery (Thyroid and Endocrine Surgery), University Surgical Cluster, National University Hospital, Singapore; National University Health System Corporate Office, Singapore. Electronic address: kee_yuan_ngiam@nuhs.edu.sg', 'National University Health System Corporate Office, Singapore', 'Department of Surgery, National University of Singapore, Singapore', 'Division of General Surgery (Thyroid and Endocrine Surgery), University Surgical Cluster, National University Hospital, Singapore', 'Department of Medicine, Yong Loo Lin School of Medicine, National University of Singapore, Singapore']</t>
+          <t>['School of Computer Engineering and Science, Shanghai University, Shanghai 200444, China', 'School of Computer Engineering and Science, Shanghai University, Shanghai 200444, China', 'School of Computer Engineering and Science, Shanghai University, Shanghai 200444, China', 'Materials Genome Institute, Shanghai University, Shanghai 200444, China', 'School of Materials Science and Engineering, Shanghai University, Shanghai 200444, China']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Kee Yuan Ngiam (corresponding author), Department of Surgery, National University of Singapore, Singapore; Division of General Surgery (Thyroid and Endocrine Surgery), University Surgical Cluster, National University Hospital, Singapore; National University Health System Corporate Office, Singapore. Electronic address: kee_yuan_ngiam@nuhs.edu.sg; National University Health System Corporate Office, Singapore; Department of Surgery, National University of Singapore, Singapore; Division of General Surgery (Thyroid and Endocrine Surgery), University Surgical Cluster, National University Hospital, Singapore</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr"/>
+          <t>Siqi Shi (corresponding author), Materials Genome Institute, Shanghai University, Shanghai 200444, China; School of Materials Science and Engineering, Shanghai University, Shanghai 200444, China</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>The screening of novel materials with good performance and the modelling of quantitative structure-activity relationships (QSARs), among other issues, are hot topics in the field of materials science. Traditional experiments and computational modelling often consume tremendous time and resources and are limited by their experimental conditions and theoretical foundations. Thus, it is imperative to develop a new method of accelerating the discovery and design process for novel materials. Recently, materials discovery and design using machine learning have been receiving increasing attention and have achieved great improvements in both time efficiency and prediction accuracy. In this review, we first outline the typical mode of and basic procedures for applying machine learning in materials science, and we classify and compare the main algorithms. Then, the current research status is reviewed with regard to applications of machine learning in material property prediction, in new materials discovery and for other purposes. Finally, we discuss problems related to machine learning in materials science, propose possible solutions, and forecast potential directions of future research. By directly combining computational studies with experiments, we hope to provide insight into the parameters that affect the properties of materials, thereby enabling more efficient and target-oriented research on materials discovery and design. Machine learning provides a new means of screening novel materials with good performance, developing quantitative structure-activity relationships (QSARs) and other models, predicting the properties of materials, discovering new materials and performing other materials-relateds studies. • The typical mode of and basic procedures for applying machine learning in materials science are summarized and discussed. • For various points of application, the machine learning methods used for different purposes are comprehensively reviewed. • Existing problems are discussed, possible solutions are proposed and potential directions of future research are suggested.</t>
+        </is>
+      </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>e262</t>
+          <t>159</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>e273</t>
+          <t>177</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>['Machine learning', 'Artificial intelligence', 'Computer science', 'Big data', 'Health care', 'Scalability', 'Flexibility (engineering)', 'Data science', 'Data mining', 'Database']</t>
+          <t>['Materials science', 'Nanotechnology', 'Systems engineering', 'Construction engineering', 'Engineering']</t>
         </is>
       </c>
       <c r="T181" t="inlineStr">
         <is>
-          <t>['SG']</t>
+          <t>['CN']</t>
         </is>
       </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>['LeCun Y, 2015, NATURE', 'Esteva A, 2017, NATURE', 'Topol E, 2018, NATURE MEDICINE', 'Jiang F, 2017, STROKE AND VASCULAR NEUROLOGY', 'Bodenreider O, 2003, NUCLEIC ACIDS RESEARCH', 'Samuel A, 1959, IBM JOURNAL OF RESEARCH AND DEVELOPMENT', 'Concato J, 2000, NEW ENGLAND JOURNAL OF MEDICINE', 'Deo R, 2015, CIRCULATION', 'Greenspan H, 2016, IEEE TRANSACTIONS ON MEDICAL IMAGING', 'Abràmoff M, 2018, NPJ DIGITAL MEDICINE', 'Rajpurkar P, 2018, PLOS MEDICINE', 'Laranjo L, 2018, JOURNAL OF THE AMERICAN MEDICAL INFORMATICS ASSOCIATION', 'Bates D, 2014, HEALTH AFFAIRS', 'Ekeland A, 2010, INTERNATIONAL JOURNAL OF MEDICAL INFORMATICS', 'Mobadersany P, 2018, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Faust O, 2018, COMPUTER METHODS AND PROGRAMS IN BIOMEDICINE', 'Tuckson R, 2017, NEW ENGLAND JOURNAL OF MEDICINE', ', 2005, ', 'Jha S, 2016, JAMA', 'Wainberg M, 2018, NATURE BIOTECHNOLOGY', 'Henry K, 2015, SCIENCE TRANSLATIONAL MEDICINE', 'Nam J, 2018, RADIOLOGY', 'Titano J, 2018, NATURE MEDICINE', 'Grinsven M, 2016, IEEE TRANSACTIONS ON MEDICAL IMAGING', 'Kuo C, 2016, JOURNAL OF VISUAL COMMUNICATION AND IMAGE REPRESENTATION', 'Haendel M, 2018, NEW ENGLAND JOURNAL OF MEDICINE', 'Luxton D, 2014, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Loh E, 2018, BMJ LEADER', 'Lin H, 2018, PLOS MEDICINE', 'Zarrinpar A, 2016, SCIENCE TRANSLATIONAL MEDICINE', 'Pantuck A, 2018, ADVANCED THERAPEUTICS', 'Kantarjian H, 2015, JAMA ONCOLOGY', 'Gawehn E, 2018, EXPERT OPINION ON DRUG DISCOVERY', 'Kowatsch T, 2017, ALEXANDRIA (UNISG) (UNIVERSITY OF ST.GALLEN)', 'Kerlikowske K, 2018, ANNALS OF INTERNAL MEDICINE', 'Wang H, 2018, QUANTITATIVE IMAGING IN MEDICINE AND SURGERY', 'Hainc N, 2017, FRONTIERS IN NEUROLOGY', 'Azizi S, 2017, INTERNATIONAL JOURNAL OF COMPUTER ASSISTED RADIOLOGY AND SURGERY', 'Zheng K, 2017, ', 'Silver D, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Mazzanti M, 2018, CURRENT CARDIOLOGY REPORTS', 'Gelhaus P, 2011, JOURNAL OF EVALUATION IN CLINICAL PRACTICE', 'Voelker R, 2018, JAMA', 'Marcus G, 2018, ARXIV (CORNELL UNIVERSITY)']</t>
+          <t>['Friedman J, 2001, THE ANNALS OF STATISTICS', 'Nasrabadi N, 2007, JOURNAL OF ELECTRONIC IMAGING', 'Jain A, 2013, APL MATERIALS', 'Rosenblatt F, 1958, PSYCHOLOGICAL REVIEW', 'Allen F, 2002, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE', 'Murphy K, 2012, ', 'Alder B, 1959, THE JOURNAL OF CHEMICAL PHYSICS', 'Mitchell T, 1999, COMMUNICATIONS OF THE ACM', 'Snyder J, 2012, PHYSICAL REVIEW LETTERS', 'Hansen K, 2013, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Hautier G, 2010, CHEMISTRY OF MATERIALS', 'Schütt K, 2014, PHYSICAL REVIEW B', 'Fischer C, 2006, NATURE MATERIALS', 'Maddox J, 1988, NATURE', 'Curtarolo S, 2003, PHYSICAL REVIEW LETTERS', 'Hautier G, 2010, INORGANIC CHEMISTRY', 'Klass V, 2014, JOURNAL OF POWER SOURCES', 'Olson G, 2000, SCIENCE', 'Isarankura‐Na‐Ayudhya C, 2009, PUBMED', 'Peck R, 2000, ', 'Topçu İ, 2007, COMPUTATIONAL MATERIALS SCIENCE', 'Hutchinson J, 2009, JOURNAL OF THERMAL ANALYSIS AND CALORIMETRY', 'Fleischer C, 2013, JOURNAL OF POWER ELECTRONICS', 'Javed S, 2006, COMPUTATIONAL MATERIALS SCIENCE', 'Chen B, 2008, COMPUTATIONAL MATERIALS SCIENCE', 'Fang S, 2008, MATERIALS &amp; DESIGN (1980-2015)', 'Zhu Q, 2003, ACTA MATERIALIA', 'Alzghoul A, 2014, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Carrera G, 2008, TETRAHEDRON', 'Liu X, 2009, COMPUTATIONAL MATERIALS SCIENCE', 'Chen X, 2007, INTERNATIONAL JOURNAL OF INTELLIGENT SYSTEMS', 'Yu X, 2008, JOURNAL OF THEORETICAL AND COMPUTATIONAL CHEMISTRY', 'Martínez R, 2014, COMPUTATIONAL MATERIALS SCIENCE', 'Castin N, 2014, COMPUTATIONAL MATERIALS SCIENCE', 'Abbod M, 2002, MATERIALS SCIENCE AND ENGINEERING A', 'Farrusseng D, 2008, COMPUTATIONAL MATERIALS SCIENCE', 'Zhou Z, 2004, JOURNAL OF COMPUTER SCIENCE AND TECHNOLOGY', 'Zhang X, 2007, MATERIALS &amp; DESIGN (1980-2015)', 'Camacho-Zúñiga C, 2003, INDUSTRIAL &amp; ENGINEERING CHEMISTRY RESEARCH', 'Majid A, 2011, COMPUTATIONAL MATERIALS SCIENCE', 'Sivasankaran S, 2009, COMPUTATIONAL MATERIALS SCIENCE', 'Mohn C, 2008, COMPUTATIONAL MATERIALS SCIENCE', 'Pei J, 2012, MACROMOLECULAR THEORY AND SIMULATIONS', 'Han Y, 2010, COMPUTATIONAL MATERIALS SCIENCE', 'Paszkowicz W, 2008, COMPUTATIONAL MATERIALS SCIENCE', 'Hachmann J, 2011, BULLETIN OF THE AMERICAN PHYSICAL SOCIETY', 'Cavaliere P, 2006, COMPUTATIONAL MATERIALS SCIENCE', 'Joze H, 2010, ', '1943- B, 2009, ', 'Vapnik V, 1995, ', 'Cortes C, 1995, MACHINE LEARNING', 'Kumar D, 1995, CHOICE REVIEWS ONLINE', 'De’ath G, 2000, ECOLOGY', 'Chen L, 2002, ANNUAL REVIEW OF MATERIALS RESEARCH', 'Rahman A, 1964, PHYSICAL REVIEW', 'Boettinger W, 2002, ANNUAL REVIEW OF MATERIALS RESEARCH', 'Belsky A, 2002, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE', 'Steinbach I, 2009, MODELLING AND SIMULATION IN MATERIALS SCIENCE AND ENGINEERING', 'Ghiringhelli L, 2015, PHYSICAL REVIEW LETTERS', 'Larrañaga P, 2006, BRIEFINGS IN BIOINFORMATICS', 'Pilania G, 2013, SCIENTIFIC REPORTS', 'Charkhgard M, 2010, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Hachmann J, 2011, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Mylopoulos J, 1999, COMMUNICATIONS OF THE ACM', 'Fernández M, 2014, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Kusne A, 2014, SCIENTIFIC REPORTS', 'Fujimura K, 2013, ADVANCED ENERGY MATERIALS', 'Lilienfeld O, 2015, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Olsson F, 2009, KTH PUBLICATION DATABASE DIVA (KTH ROYAL INSTITUTE OF TECHNOLOGY)', 'Hautier G, 2012, JOURNAL OF MATERIALS SCIENCE', 'Sundararaghavan V, 2004, COMPUTATIONAL MATERIALS SCIENCE', 'Altun F, 2007, COMPUTATIONAL MATERIALS SCIENCE', 'Wu S, 2013, RELIABILITY ENGINEERING &amp; SYSTEM SAFETY', 'Fang S, 2008, COMPUTATIONAL MATERIALS SCIENCE', 'Scott D, 2007, JOURNAL OF THE EUROPEAN CERAMIC SOCIETY', 'Gajewski J, 2013, COMPUTATIONAL MATERIALS SCIENCE', 'Beran G, 2014, ANGEWANDTE CHEMIE INTERNATIONAL EDITION', 'Guo Z, 2004, COMPUTATIONAL MATERIALS SCIENCE', 'Majid A, 2010, COMPUTATIONAL MATERIALS SCIENCE', 'Salahinejad M, 2012, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Addin O, 2006, MATERIALS &amp; DESIGN (1980-2015)', 'Lee D, 2007, IEEE TRANSACTIONS ON VEHICULAR TECHNOLOGY', 'Rao H, 1996, COMPUTATIONAL MATERIALS SCIENCE', 'Phillips C, 2013, SOFT MATTER', 'Ceder G, 2006, MRS BULLETIN', 'Li C, 2003, JOURNAL OF PHYSICS AND CHEMISTRY OF SOLIDS', 'Raj R, 2008, COMPUTATIONAL MATERIALS SCIENCE', 'Ning X, 2011, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Gharagheizi F, 2012, CHEMICAL ENGINEERING SCIENCE', 'Reich Y, 1995, MATERIALS &amp; DESIGN (1980-2015)', 'Eminağaoğlu M, 2010, ', 'Pei J, 2012, JOURNAL OF THEORETICAL AND COMPUTATIONAL CHEMISTRY', 'Bertinetto\u202c \u202a, 2008, JOURNAL OF MOLECULAR GRAPHICS AND MODELLING', 'Li G, 2009, ', 'Yu K, 2006, TALANTA', 'Vahed A, 2003, ', 'Li C, 1996, JOURNAL OF PHYSICS AND CHEMISTRY OF SOLIDS', 'Liu Y, 2004, IEEE INTERNATIONAL CONFERENCE ON COGNITIVE INFORMATICS', 'Yang L, 2005, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Kohn W, 1965, PHYSICAL REVIEW', 'Cortes C, 1995, MACHINE LEARNING', 'Vapnik V, 2000, ', 'GuyonIsabelle, 2003, JOURNAL OF MACHINE LEARNING RESEARCH', 'Buckland S, 1994, BIOMETRICS', ', 2007, CHOICE REVIEWS ONLINE', 'Kirklin S, 2015, NPJ COMPUTATIONAL MATERIALS', 'Raccuglia P, 2016, NATURE', 'Ward L, 2016, NPJ COMPUTATIONAL MATERIALS', 'Agrawal A, 2016, APL MATERIALS', 'Gómez‐Bombarelli R, 2016, NATURE MATERIALS', 'Meredig B, 2014, PHYSICAL REVIEW B', 'Marriott P, 1995, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES A (STATISTICS IN SOCIETY)', 'Lufaso M, 2001, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE', 'Isayev O, 2017, NATURE COMMUNICATIONS', ', 1998, MACHINE LEARNING', 'Shi S, 2016, CHINESE PHYSICS B', 'Sendek A, 2016, ENERGY &amp; ENVIRONMENTAL SCIENCE', 'Ward C, 2012, 23RD ADVANCED AEROSPACE MATERIALS AND PROCESSES (AEROMAT) CONFERENCE AND EXPOSITION', 'Blaiszik B, 2016, JOM', 'Heumann C, 2016, ', 'Binder K, 1995, TOPICS IN APPLIED PHYSICS', "Jain A, 2016, JOURNAL OF MATERIALS RESEARCH/PRATT'S GUIDE TO VENTURE CAPITAL SOURCES", 'Helma C, 2004, JOURNAL OF CHEMICAL INFORMATION AND COMPUTER SCIENCES', 'Liu R, 2015, SCIENTIFIC REPORTS', 'Hill J, 2016, MRS BULLETIN', 'Ward L, 2016, CURRENT OPINION IN SOLID STATE AND MATERIALS SCIENCE', 'Rajan K, 2005, STATISTICAL ANALYSIS AND DATA MINING THE ASA DATA SCIENCE JOURNAL', 'Bolstad W, 2004, ', 'Häse F, 2016, CHEMICAL SCIENCE', 'Saldana D, 2012, ENERGY &amp; FUELS', 'Puchala B, 2016, JOM', 'Balachandran P, 2015, SCIENTIFIC REPORTS', 'Wang X, 2017, JOURNAL OF MATERIOMICS', 'Liu R, 2015, INTEGRATING MATERIALS AND MANUFACTURING INNOVATION', 'Chen C, 2017, SCIENTIFIC REPORTS', 'Roekeghem A, 2016, PHYSICAL REVIEW X', 'Wu H, 2017, COMPUTATIONAL MATERIALS SCIENCE', 'Kalidindi S, 2016, JOM', 'Sumpter B, 2015, NPJ COMPUTATIONAL MATERIALS', 'Liu R, 2017, INTEGRATING MATERIALS AND MANUFACTURING INNOVATION', 'Chen L, 2015, NPJ COMPUTATIONAL MATERIALS', 'Liu Y, 2004, ', 'Mueller T, 2016, REVIEWS IN COMPUTATIONAL CHEMISTRY']</t>
         </is>
       </c>
       <c r="V181" t="inlineStr">
@@ -21197,34 +21217,34 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>Ngiam K, 2019, THE LANCET ONCOLOGY</t>
+          <t>Liu Y, 2017, JOURNAL OF MATERIOMICS</t>
         </is>
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>Ngiam K, 2019, THE LANCET ONCOLOGY</t>
+          <t>Liu Y, 2017, JOURNAL OF MATERIOMICS</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2742835787</t>
+          <t>https://openalex.org/W2943491685</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>10.1016/j.jmat.2017.08.002</t>
+          <t>10.1016/s1470-2045(19)30149-4</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Materials discovery and design using machine learning</t>
+          <t>Big data and machine learning algorithms for health-care delivery</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -21234,80 +21254,76 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>1227</v>
+        <v>1424</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>JOURNAL OF MATERIOMICS</t>
+          <t>THE LANCET ONCOLOGY</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Journal of Materiomics</t>
+          <t>The Lancet Oncology</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>['Yue Liu', 'Tianlu Zhao', 'Wangwei Ju', 'Siqi Shi']</t>
+          <t>['Kee Yuan Ngiam', 'Ing Wei Khor']</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>['Yue Liu', 'Tianlu Zhao', 'Wangwei Ju', 'Siqi Shi']</t>
+          <t>['Kee Yuan Ngiam', 'Ing Wei Khor']</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['School of Computer Engineering and Science, Shanghai University, Shanghai 200444, China', 'School of Computer Engineering and Science, Shanghai University, Shanghai 200444, China', 'School of Computer Engineering and Science, Shanghai University, Shanghai 200444, China', 'Materials Genome Institute, Shanghai University, Shanghai 200444, China', 'School of Materials Science and Engineering, Shanghai University, Shanghai 200444, China']</t>
+          <t>['Department of Surgery, National University of Singapore, Singapore; Division of General Surgery (Thyroid and Endocrine Surgery), University Surgical Cluster, National University Hospital, Singapore; National University Health System Corporate Office, Singapore. Electronic address: kee_yuan_ngiam@nuhs.edu.sg', 'National University Health System Corporate Office, Singapore', 'Department of Surgery, National University of Singapore, Singapore', 'Division of General Surgery (Thyroid and Endocrine Surgery), University Surgical Cluster, National University Hospital, Singapore', 'Department of Medicine, Yong Loo Lin School of Medicine, National University of Singapore, Singapore']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Siqi Shi (corresponding author), Materials Genome Institute, Shanghai University, Shanghai 200444, China; School of Materials Science and Engineering, Shanghai University, Shanghai 200444, China</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>The screening of novel materials with good performance and the modelling of quantitative structure-activity relationships (QSARs), among other issues, are hot topics in the field of materials science. Traditional experiments and computational modelling often consume tremendous time and resources and are limited by their experimental conditions and theoretical foundations. Thus, it is imperative to develop a new method of accelerating the discovery and design process for novel materials. Recently, materials discovery and design using machine learning have been receiving increasing attention and have achieved great improvements in both time efficiency and prediction accuracy. In this review, we first outline the typical mode of and basic procedures for applying machine learning in materials science, and we classify and compare the main algorithms. Then, the current research status is reviewed with regard to applications of machine learning in material property prediction, in new materials discovery and for other purposes. Finally, we discuss problems related to machine learning in materials science, propose possible solutions, and forecast potential directions of future research. By directly combining computational studies with experiments, we hope to provide insight into the parameters that affect the properties of materials, thereby enabling more efficient and target-oriented research on materials discovery and design. Machine learning provides a new means of screening novel materials with good performance, developing quantitative structure-activity relationships (QSARs) and other models, predicting the properties of materials, discovering new materials and performing other materials-relateds studies. • The typical mode of and basic procedures for applying machine learning in materials science are summarized and discussed. • For various points of application, the machine learning methods used for different purposes are comprehensively reviewed. • Existing problems are discussed, possible solutions are proposed and potential directions of future research are suggested.</t>
-        </is>
-      </c>
+          <t>Kee Yuan Ngiam (corresponding author), Department of Surgery, National University of Singapore, Singapore; Division of General Surgery (Thyroid and Endocrine Surgery), University Surgical Cluster, National University Hospital, Singapore; National University Health System Corporate Office, Singapore. Electronic address: kee_yuan_ngiam@nuhs.edu.sg; National University Health System Corporate Office, Singapore; Department of Surgery, National University of Singapore, Singapore; Division of General Surgery (Thyroid and Endocrine Surgery), University Surgical Cluster, National University Hospital, Singapore</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>e262</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>e273</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>['Materials science', 'Nanotechnology', 'Systems engineering', 'Construction engineering', 'Engineering']</t>
+          <t>['Machine learning', 'Artificial intelligence', 'Computer science', 'Big data', 'Health care', 'Scalability', 'Flexibility (engineering)', 'Data science', 'Data mining', 'Database']</t>
         </is>
       </c>
       <c r="T182" t="inlineStr">
         <is>
-          <t>['CN']</t>
+          <t>['SG']</t>
         </is>
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>['Friedman J, 2001, THE ANNALS OF STATISTICS', 'Nasrabadi N, 2007, JOURNAL OF ELECTRONIC IMAGING', 'Jain A, 2013, APL MATERIALS', 'Rosenblatt F, 1958, PSYCHOLOGICAL REVIEW', 'Allen F, 2002, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE', 'Murphy K, 2012, ', 'Alder B, 1959, THE JOURNAL OF CHEMICAL PHYSICS', 'Mitchell T, 1999, COMMUNICATIONS OF THE ACM', 'Snyder J, 2012, PHYSICAL REVIEW LETTERS', 'Hansen K, 2013, JOURNAL OF CHEMICAL THEORY AND COMPUTATION', 'Hautier G, 2010, CHEMISTRY OF MATERIALS', 'Schütt K, 2014, PHYSICAL REVIEW B', 'Fischer C, 2006, NATURE MATERIALS', 'Maddox J, 1988, NATURE', 'Curtarolo S, 2003, PHYSICAL REVIEW LETTERS', 'Hautier G, 2010, INORGANIC CHEMISTRY', 'Klass V, 2014, JOURNAL OF POWER SOURCES', 'Olson G, 2000, SCIENCE', 'Isarankura‐Na‐Ayudhya C, 2009, PUBMED', 'Peck R, 2000, ', 'Topçu İ, 2007, COMPUTATIONAL MATERIALS SCIENCE', 'Hutchinson J, 2009, JOURNAL OF THERMAL ANALYSIS AND CALORIMETRY', 'Fleischer C, 2013, JOURNAL OF POWER ELECTRONICS', 'Javed S, 2006, COMPUTATIONAL MATERIALS SCIENCE', 'Chen B, 2008, COMPUTATIONAL MATERIALS SCIENCE', 'Fang S, 2008, MATERIALS &amp; DESIGN (1980-2015)', 'Zhu Q, 2003, ACTA MATERIALIA', 'Alzghoul A, 2014, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Carrera G, 2008, TETRAHEDRON', 'Liu X, 2009, COMPUTATIONAL MATERIALS SCIENCE', 'Chen X, 2007, INTERNATIONAL JOURNAL OF INTELLIGENT SYSTEMS', 'Yu X, 2008, JOURNAL OF THEORETICAL AND COMPUTATIONAL CHEMISTRY', 'Martínez R, 2014, COMPUTATIONAL MATERIALS SCIENCE', 'Castin N, 2014, COMPUTATIONAL MATERIALS SCIENCE', 'Abbod M, 2002, MATERIALS SCIENCE AND ENGINEERING A', 'Farrusseng D, 2008, COMPUTATIONAL MATERIALS SCIENCE', 'Zhou Z, 2004, JOURNAL OF COMPUTER SCIENCE AND TECHNOLOGY', 'Zhang X, 2007, MATERIALS &amp; DESIGN (1980-2015)', 'Camacho-Zúñiga C, 2003, INDUSTRIAL &amp; ENGINEERING CHEMISTRY RESEARCH', 'Majid A, 2011, COMPUTATIONAL MATERIALS SCIENCE', 'Sivasankaran S, 2009, COMPUTATIONAL MATERIALS SCIENCE', 'Mohn C, 2008, COMPUTATIONAL MATERIALS SCIENCE', 'Pei J, 2012, MACROMOLECULAR THEORY AND SIMULATIONS', 'Han Y, 2010, COMPUTATIONAL MATERIALS SCIENCE', 'Paszkowicz W, 2008, COMPUTATIONAL MATERIALS SCIENCE', 'Hachmann J, 2011, BULLETIN OF THE AMERICAN PHYSICAL SOCIETY', 'Cavaliere P, 2006, COMPUTATIONAL MATERIALS SCIENCE', 'Joze H, 2010, ', '1943- B, 2009, ', 'Vapnik V, 1995, ', 'Cortes C, 1995, MACHINE LEARNING', 'Kumar D, 1995, CHOICE REVIEWS ONLINE', 'De’ath G, 2000, ECOLOGY', 'Chen L, 2002, ANNUAL REVIEW OF MATERIALS RESEARCH', 'Rahman A, 1964, PHYSICAL REVIEW', 'Boettinger W, 2002, ANNUAL REVIEW OF MATERIALS RESEARCH', 'Belsky A, 2002, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE', 'Steinbach I, 2009, MODELLING AND SIMULATION IN MATERIALS SCIENCE AND ENGINEERING', 'Ghiringhelli L, 2015, PHYSICAL REVIEW LETTERS', 'Larrañaga P, 2006, BRIEFINGS IN BIOINFORMATICS', 'Pilania G, 2013, SCIENTIFIC REPORTS', 'Charkhgard M, 2010, IEEE TRANSACTIONS ON INDUSTRIAL ELECTRONICS', 'Hachmann J, 2011, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Mylopoulos J, 1999, COMMUNICATIONS OF THE ACM', 'Fernández M, 2014, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Kusne A, 2014, SCIENTIFIC REPORTS', 'Fujimura K, 2013, ADVANCED ENERGY MATERIALS', 'Lilienfeld O, 2015, INTERNATIONAL JOURNAL OF QUANTUM CHEMISTRY', 'Olsson F, 2009, KTH PUBLICATION DATABASE DIVA (KTH ROYAL INSTITUTE OF TECHNOLOGY)', 'Hautier G, 2012, JOURNAL OF MATERIALS SCIENCE', 'Sundararaghavan V, 2004, COMPUTATIONAL MATERIALS SCIENCE', 'Altun F, 2007, COMPUTATIONAL MATERIALS SCIENCE', 'Wu S, 2013, RELIABILITY ENGINEERING &amp; SYSTEM SAFETY', 'Fang S, 2008, COMPUTATIONAL MATERIALS SCIENCE', 'Scott D, 2007, JOURNAL OF THE EUROPEAN CERAMIC SOCIETY', 'Gajewski J, 2013, COMPUTATIONAL MATERIALS SCIENCE', 'Beran G, 2014, ANGEWANDTE CHEMIE INTERNATIONAL EDITION', 'Guo Z, 2004, COMPUTATIONAL MATERIALS SCIENCE', 'Majid A, 2010, COMPUTATIONAL MATERIALS SCIENCE', 'Salahinejad M, 2012, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Addin O, 2006, MATERIALS &amp; DESIGN (1980-2015)', 'Lee D, 2007, IEEE TRANSACTIONS ON VEHICULAR TECHNOLOGY', 'Rao H, 1996, COMPUTATIONAL MATERIALS SCIENCE', 'Phillips C, 2013, SOFT MATTER', 'Ceder G, 2006, MRS BULLETIN', 'Li C, 2003, JOURNAL OF PHYSICS AND CHEMISTRY OF SOLIDS', 'Raj R, 2008, COMPUTATIONAL MATERIALS SCIENCE', 'Ning X, 2011, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Gharagheizi F, 2012, CHEMICAL ENGINEERING SCIENCE', 'Reich Y, 1995, MATERIALS &amp; DESIGN (1980-2015)', 'Eminağaoğlu M, 2010, ', 'Pei J, 2012, JOURNAL OF THEORETICAL AND COMPUTATIONAL CHEMISTRY', 'Bertinetto\u202c \u202a, 2008, JOURNAL OF MOLECULAR GRAPHICS AND MODELLING', 'Li G, 2009, ', 'Yu K, 2006, TALANTA', 'Vahed A, 2003, ', 'Li C, 1996, JOURNAL OF PHYSICS AND CHEMISTRY OF SOLIDS', 'Liu Y, 2004, IEEE INTERNATIONAL CONFERENCE ON COGNITIVE INFORMATICS', 'Yang L, 2005, JOURNAL OF CHEMICAL INFORMATION AND MODELING', 'Kohn W, 1965, PHYSICAL REVIEW', 'Cortes C, 1995, MACHINE LEARNING', 'Vapnik V, 2000, ', 'GuyonIsabelle, 2003, JOURNAL OF MACHINE LEARNING RESEARCH', 'Buckland S, 1994, BIOMETRICS', ', 2007, CHOICE REVIEWS ONLINE', 'Kirklin S, 2015, NPJ COMPUTATIONAL MATERIALS', 'Raccuglia P, 2016, NATURE', 'Ward L, 2016, NPJ COMPUTATIONAL MATERIALS', 'Agrawal A, 2016, APL MATERIALS', 'Gómez‐Bombarelli R, 2016, NATURE MATERIALS', 'Meredig B, 2014, PHYSICAL REVIEW B', 'Marriott P, 1995, JOURNAL OF THE ROYAL STATISTICAL SOCIETY SERIES A (STATISTICS IN SOCIETY)', 'Lufaso M, 2001, ACTA CRYSTALLOGRAPHICA SECTION B STRUCTURAL SCIENCE', 'Isayev O, 2017, NATURE COMMUNICATIONS', ', 1998, MACHINE LEARNING', 'Shi S, 2016, CHINESE PHYSICS B', 'Sendek A, 2016, ENERGY &amp; ENVIRONMENTAL SCIENCE', 'Ward C, 2012, 23RD ADVANCED AEROSPACE MATERIALS AND PROCESSES (AEROMAT) CONFERENCE AND EXPOSITION', 'Blaiszik B, 2016, JOM', 'Heumann C, 2016, ', 'Binder K, 1995, TOPICS IN APPLIED PHYSICS', "Jain A, 2016, JOURNAL OF MATERIALS RESEARCH/PRATT'S GUIDE TO VENTURE CAPITAL SOURCES", 'Helma C, 2004, JOURNAL OF CHEMICAL INFORMATION AND COMPUTER SCIENCES', 'Liu R, 2015, SCIENTIFIC REPORTS', 'Hill J, 2016, MRS BULLETIN', 'Ward L, 2016, CURRENT OPINION IN SOLID STATE AND MATERIALS SCIENCE', 'Rajan K, 2005, STATISTICAL ANALYSIS AND DATA MINING THE ASA DATA SCIENCE JOURNAL', 'Bolstad W, 2004, ', 'Häse F, 2016, CHEMICAL SCIENCE', 'Saldana D, 2012, ENERGY &amp; FUELS', 'Puchala B, 2016, JOM', 'Balachandran P, 2015, SCIENTIFIC REPORTS', 'Wang X, 2017, JOURNAL OF MATERIOMICS', 'Liu R, 2015, INTEGRATING MATERIALS AND MANUFACTURING INNOVATION', 'Chen C, 2017, SCIENTIFIC REPORTS', 'Roekeghem A, 2016, PHYSICAL REVIEW X', 'Wu H, 2017, COMPUTATIONAL MATERIALS SCIENCE', 'Kalidindi S, 2016, JOM', 'Sumpter B, 2015, NPJ COMPUTATIONAL MATERIALS', 'Liu R, 2017, INTEGRATING MATERIALS AND MANUFACTURING INNOVATION', 'Chen L, 2015, NPJ COMPUTATIONAL MATERIALS', 'Liu Y, 2004, ', 'Mueller T, 2016, REVIEWS IN COMPUTATIONAL CHEMISTRY']</t>
+          <t>['LeCun Y, 2015, NATURE', 'Esteva A, 2017, NATURE', 'Topol E, 2018, NATURE MEDICINE', 'Jiang F, 2017, STROKE AND VASCULAR NEUROLOGY', 'Samuel A, 1959, IBM JOURNAL OF RESEARCH AND DEVELOPMENT', 'Bodenreider O, 2003, NUCLEIC ACIDS RESEARCH', 'Concato J, 2000, NEW ENGLAND JOURNAL OF MEDICINE', 'Deo R, 2015, CIRCULATION', 'Greenspan H, 2016, IEEE TRANSACTIONS ON MEDICAL IMAGING', 'Abràmoff M, 2018, NPJ DIGITAL MEDICINE', 'Rajpurkar P, 2018, PLOS MEDICINE', 'Laranjo L, 2018, JOURNAL OF THE AMERICAN MEDICAL INFORMATICS ASSOCIATION', 'Bates D, 2014, HEALTH AFFAIRS', 'Ekeland A, 2010, INTERNATIONAL JOURNAL OF MEDICAL INFORMATICS', 'Mobadersany P, 2018, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Faust O, 2018, COMPUTER METHODS AND PROGRAMS IN BIOMEDICINE', 'Tuckson R, 2017, NEW ENGLAND JOURNAL OF MEDICINE', ', 2005, ', 'Jha S, 2016, JAMA', 'Wainberg M, 2018, NATURE BIOTECHNOLOGY', 'Henry K, 2015, SCIENCE TRANSLATIONAL MEDICINE', 'Nam J, 2018, RADIOLOGY', 'Titano J, 2018, NATURE MEDICINE', 'Grinsven M, 2016, IEEE TRANSACTIONS ON MEDICAL IMAGING', 'Kuo C, 2016, JOURNAL OF VISUAL COMMUNICATION AND IMAGE REPRESENTATION', 'Haendel M, 2018, NEW ENGLAND JOURNAL OF MEDICINE', 'Luxton D, 2014, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'Loh E, 2018, BMJ LEADER', 'Lin H, 2018, PLOS MEDICINE', 'Zarrinpar A, 2016, SCIENCE TRANSLATIONAL MEDICINE', 'Pantuck A, 2018, ADVANCED THERAPEUTICS', 'Kantarjian H, 2015, JAMA ONCOLOGY', 'Gawehn E, 2018, EXPERT OPINION ON DRUG DISCOVERY', 'Kowatsch T, 2017, ALEXANDRIA (UNISG) (UNIVERSITY OF ST.GALLEN)', 'Kerlikowske K, 2018, ANNALS OF INTERNAL MEDICINE', 'Wang H, 2018, QUANTITATIVE IMAGING IN MEDICINE AND SURGERY', 'Hainc N, 2017, FRONTIERS IN NEUROLOGY', 'Azizi S, 2017, INTERNATIONAL JOURNAL OF COMPUTER ASSISTED RADIOLOGY AND SURGERY', 'Zheng K, 2017, ', 'Silver D, 2011, LECTURE NOTES IN COMPUTER SCIENCE', 'Mazzanti M, 2018, CURRENT CARDIOLOGY REPORTS', 'Gelhaus P, 2011, JOURNAL OF EVALUATION IN CLINICAL PRACTICE', 'Voelker R, 2018, JAMA', 'Marcus G, 2018, ARXIV (CORNELL UNIVERSITY)']</t>
         </is>
       </c>
       <c r="V182" t="inlineStr">
@@ -21323,12 +21339,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>Liu Y, 2017, JOURNAL OF MATERIOMICS</t>
+          <t>Ngiam K, 2019, THE LANCET ONCOLOGY</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>Liu Y, 2017, JOURNAL OF MATERIOMICS</t>
+          <t>Ngiam K, 2019, THE LANCET ONCOLOGY</t>
         </is>
       </c>
     </row>
@@ -21364,7 +21380,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -21706,7 +21722,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>23111</v>
+        <v>23129</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -21855,7 +21871,11 @@
           <t>['Computer Science Division, University of California, Berkeley, CA, 94720-1776, USA', 'Computer Science Division, University of California, Berkeley, USA 94720-1776#TAB#', 'Computer Science Division, University of California, Berkeley, CA, 94720-1776, USA', 'Computer Science Division, University of California, Berkeley, USA 94720-1776#TAB#', 'Computer Science Division, University of California, Berkeley, CA, 94720-1776, USA', 'Computer Science Division, University of California, Berkeley, USA 94720-1776#TAB#', 'Computer Science Division, University of California, Berkeley, CA, 94720-1776, USA', 'Computer Science Division, University of California, Berkeley, USA 94720-1776#TAB#']</t>
         </is>
       </c>
-      <c r="M187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Marco Barreno (corresponding author), Computer Science Division, University of California, Berkeley, CA, 94720-1776, USA; Computer Science Division, University of California, Berkeley, USA 94720-1776#TAB#</t>
+        </is>
+      </c>
       <c r="N187" t="inlineStr">
         <is>
           <t>Machine learning’s ability to rapidly evolve to changing and complex situations has helped it become a fundamental tool for computer security. That adaptability is also a vulnerability: attackers can exploit machine learning systems. We present a taxonomy identifying and analyzing attacks against machine learning systems. We show how these classes influence the costs for the attacker and defender, and we give a formal structure defining their interaction. We use our framework to survey and analyze the literature of attacks against machine learning systems. We also illustrate our taxonomy by showing how it can guide attacks against SpamBayes, a popular statistical spam filter. Finally, we discuss how our taxonomy suggests new lines of defenses.</t>
@@ -22149,22 +22169,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3025104221</t>
+          <t>https://openalex.org/W4232533539</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>10.1038/s41586-020-2242-8</t>
+          <t>10.1007/978-981-15-1967-3</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Accelerated discovery of CO2 electrocatalysts using active machine learning</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -22174,76 +22194,52 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>book</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>1498</v>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>NATURE</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>Nature</t>
-        </is>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>['Miao Zhong', 'Kevin Tran', 'Yimeng Min', 'Chuanhao Wang', 'Ziyun Wang', 'Cao‐Thang Dinh', 'Phil De Luna', 'Zongqian Yu', 'Armin Sedighian Rasouli', 'Peter Brodersen', 'Song Sun', 'Oleksandr Voznyy', 'Chih‐Shan Tan', 'Mikhail Askerka', 'Fanglin Che', 'Min Liu', 'Ali Seifitokaldani', 'Yuanjie Pang', 'Shen-Chuan Lo', 'Alexander H. Ip', 'Zachary W. Ulissi', 'Edward H. Sargent']</t>
+          <t>['Zhi‐Hua Zhou']</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>['Miao Zhong', 'Kevin Tran', 'Yimeng Min', 'Chuanhao Wang', 'Ziyun Wang', 'Cao-Thang Dinh', 'Phil De Luna', 'Zongqian Yu', 'Armin Sedighian Rasouli', 'Peter Brodersen', 'Song Sun', 'Oleksandr Voznyy', 'Chih-Shan Tan', 'Mikhail Askerka', 'Fanglin Che', 'Min Liu', 'Ali Seifitokaldani', 'Yuanjie Pang', 'Shen-Chuan Lo', 'Alexander Ip', 'Zachary Ulissi', 'Edward H. Sargent']</t>
+          <t>['Zhi-Hua Zhou']</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>['College of Engineering and Applied Sciences, National Laboratory of Solid State Microstructures, Collaborative Innovation Center of Advanced Microstructure, Nanjing University, Nanjing, China', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Chemical Engineering, Carnegie Mellon University, Pittsburgh, PA, USA', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Materials Science Engineering, University of Toronto, Toronto, Ontario, Canada', 'National Research Council of Canada, Ottawa, Ontario, Canada', 'Chemical Engineering, Carnegie Mellon University, Pittsburgh, PA, USA', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Ontario Centre for Characterization of Advanced Materials (OCCAM), University of Toronto, Toronto, Ontario, Canada', 'National Synchrotron Radiation Laboratory, University of Science and Technology of China, Hefei, China', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Industrial Technology Research Institute, Material and Chemical Research Laboratories, Hsinchu, Taiwan', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Chemical Engineering, Carnegie Mellon University, Pittsburgh, PA, USA. zulissi@andrew.cmu.edu', 'Chemical Engineering, Carnegie Mellon University, Pittsburgh, PA, USA', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada. ted.sargent@utoronto.ca', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada']</t>
+          <t>['Nanjing University, Nanjing, China']</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Edward H. Sargent (corresponding author), Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada. ted.sargent@utoronto.ca; Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada</t>
+          <t>Zhi-Hua Zhou (corresponding author), Nanjing University, Nanjing, China</t>
         </is>
       </c>
       <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
-      </c>
-      <c r="P190" t="inlineStr">
-        <is>
-          <t>7807</t>
-        </is>
-      </c>
-      <c r="Q190" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="R190" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr">
         <is>
-          <t>['Faraday efficiency', 'Renewable energy', 'Electrocatalyst', 'Materials science', 'Ethylene glycol', 'Electrochemistry', 'Fossil fuel', 'Ethylene', 'Electrode', 'Nanotechnology', 'Chemical engineering', 'Chemistry', 'Catalysis', 'Electrical engineering', 'Organic chemistry']</t>
+          <t>['Unsupervised learning', 'Computer science', 'Artificial intelligence', 'Semi-supervised learning', 'Machine learning', 'Active learning (machine learning)', 'Reinforcement learning', 'Algorithmic learning theory', 'Supervised learning', 'Error-driven learning', 'Artificial neural network']</t>
         </is>
       </c>
       <c r="T190" t="inlineStr">
         <is>
-          <t>['CA', 'CN', 'US', 'TW']</t>
+          <t>['CN']</t>
         </is>
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>['Jain A, 2013, APL MATERIALS', 'Seh Z, 2017, SCIENCE', 'Nørskov J, 2005, JOURNAL OF THE ELECTROCHEMICAL SOCIETY', 'Peterson A, 2010, ENERGY &amp; ENVIRONMENTAL SCIENCE', 'Luna P, 2019, SCIENCE', 'Lin S, 2015, SCIENCE', 'Dinh C, 2018, SCIENCE', 'Maaten L, 2014, ', 'Kortlever R, 2015, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Liu M, 2016, NATURE', 'Gao S, 2016, NATURE', 'Li C, 2014, NATURE', 'Lu Q, 2014, NATURE COMMUNICATIONS', 'Whipple D, 2010, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Mistry H, 2016, NATURE COMMUNICATIONS', 'Luna P, 2018, NATURE CATALYSIS', 'Tran K, 2018, NATURE CATALYSIS', 'Liu X, 2017, NATURE COMMUNICATIONS', 'Hori Y, 2001, THE JOURNAL OF PHYSICAL CHEMISTRY B', 'Xiao H, 2017, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Schreier M, 2017, NATURE ENERGY', 'Wang L, 2018, ACS CATALYSIS', 'Li Y, 2017, NANO LETTERS', 'Xiao H, 2016, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Lum Y, 2017, THE JOURNAL OF PHYSICAL CHEMISTRY C', 'Li Y, 2016, ACS ENERGY LETTERS', 'Zeng Z, 2017, NATURE ENERGY', 'Jeanty P, 2018, JOURNAL OF CO2 UTILIZATION', 'Larrazábal G, 2017, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Xiao Q, 2017, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Yano H, 2003, JOURNAL OF ELECTROANALYTICAL CHEMISTRY', 'Montoya J, 2017, NPJ COMPUTATIONAL MATERIALS', 'Persson K, 2012, PHYSICAL REVIEW B']</t>
+          <t>['Zhou Z, 2021, MACHINE LEARNING', 'Zhou Z, 2021, MACHINE LEARNING']</t>
         </is>
       </c>
       <c r="V190" t="inlineStr">
@@ -22259,34 +22255,34 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>Zhong M, 2020, NATURE</t>
+          <t xml:space="preserve">Zhou Z, 2021, </t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>Zhong M, 2020, NATURE</t>
+          <t xml:space="preserve">Zhou Z, 2021, </t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://openalex.org/W4232533539</t>
+          <t>https://openalex.org/W3025104221</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>10.1007/978-981-15-1967-3</t>
+          <t>10.1038/s41586-020-2242-8</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Accelerated discovery of CO2 electrocatalysts using active machine learning</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -22296,52 +22292,76 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>765</v>
-      </c>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
+        <v>1498</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>NATURE</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>['Zhi‐Hua Zhou']</t>
+          <t>['Miao Zhong', 'Kevin Tran', 'Yimeng Min', 'Chuanhao Wang', 'Ziyun Wang', 'Cao‐Thang Dinh', 'Phil De Luna', 'Zongqian Yu', 'Armin Sedighian Rasouli', 'Peter Brodersen', 'Song Sun', 'Oleksandr Voznyy', 'Chih‐Shan Tan', 'Mikhail Askerka', 'Fanglin Che', 'Min Liu', 'Ali Seifitokaldani', 'Yuanjie Pang', 'Shen-Chuan Lo', 'Alexander H. Ip', 'Zachary W. Ulissi', 'Edward H. Sargent']</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>['Zhi-Hua Zhou']</t>
+          <t>['Miao Zhong', 'Kevin Tran', 'Yimeng Min', 'Chuanhao Wang', 'Ziyun Wang', 'Cao-Thang Dinh', 'Phil De Luna', 'Zongqian Yu', 'Armin Sedighian Rasouli', 'Peter Brodersen', 'Song Sun', 'Oleksandr Voznyy', 'Chih-Shan Tan', 'Mikhail Askerka', 'Fanglin Che', 'Min Liu', 'Ali Seifitokaldani', 'Yuanjie Pang', 'Shen-Chuan Lo', 'Alexander Ip', 'Zachary Ulissi', 'Edward H. Sargent']</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['Nanjing University, Nanjing, China']</t>
+          <t>['College of Engineering and Applied Sciences, National Laboratory of Solid State Microstructures, Collaborative Innovation Center of Advanced Microstructure, Nanjing University, Nanjing, China', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Chemical Engineering, Carnegie Mellon University, Pittsburgh, PA, USA', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Materials Science Engineering, University of Toronto, Toronto, Ontario, Canada', 'National Research Council of Canada, Ottawa, Ontario, Canada', 'Chemical Engineering, Carnegie Mellon University, Pittsburgh, PA, USA', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Ontario Centre for Characterization of Advanced Materials (OCCAM), University of Toronto, Toronto, Ontario, Canada', 'National Synchrotron Radiation Laboratory, University of Science and Technology of China, Hefei, China', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Industrial Technology Research Institute, Material and Chemical Research Laboratories, Hsinchu, Taiwan', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada', 'Chemical Engineering, Carnegie Mellon University, Pittsburgh, PA, USA. zulissi@andrew.cmu.edu', 'Chemical Engineering, Carnegie Mellon University, Pittsburgh, PA, USA', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada. ted.sargent@utoronto.ca', 'Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Zhi-Hua Zhou (corresponding author), Nanjing University, Nanjing, China</t>
+          <t>Edward H. Sargent (corresponding author), Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada. ted.sargent@utoronto.ca; Department of Electrical and Computer Engineering, University of Toronto, Toronto, Ontario, Canada</t>
         </is>
       </c>
       <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
-      <c r="R191" t="inlineStr"/>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>7807</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>['Unsupervised learning', 'Computer science', 'Artificial intelligence', 'Semi-supervised learning', 'Machine learning', 'Active learning (machine learning)', 'Reinforcement learning', 'Algorithmic learning theory', 'Supervised learning', 'Error-driven learning', 'Artificial neural network']</t>
+          <t>['Faraday efficiency', 'Renewable energy', 'Electrocatalyst', 'Materials science', 'Ethylene glycol', 'Electrochemistry', 'Fossil fuel', 'Ethylene', 'Electrode', 'Nanotechnology', 'Chemical engineering', 'Chemistry', 'Catalysis', 'Electrical engineering', 'Organic chemistry']</t>
         </is>
       </c>
       <c r="T191" t="inlineStr">
         <is>
-          <t>['CN']</t>
+          <t>['CA', 'CN', 'US', 'TW']</t>
         </is>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>['Zhou Z, 2021, MACHINE LEARNING', 'Zhou Z, 2021, MACHINE LEARNING']</t>
+          <t>['Jain A, 2013, APL MATERIALS', 'Seh Z, 2017, SCIENCE', 'Nørskov J, 2005, JOURNAL OF THE ELECTROCHEMICAL SOCIETY', 'Peterson A, 2010, ENERGY &amp; ENVIRONMENTAL SCIENCE', 'Luna P, 2019, SCIENCE', 'Lin S, 2015, SCIENCE', 'Dinh C, 2018, SCIENCE', 'Maaten L, 2014, ', 'Kortlever R, 2015, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Liu M, 2016, NATURE', 'Gao S, 2016, NATURE', 'Li C, 2014, NATURE', 'Lu Q, 2014, NATURE COMMUNICATIONS', 'Whipple D, 2010, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Mistry H, 2016, NATURE COMMUNICATIONS', 'Luna P, 2018, NATURE CATALYSIS', 'Tran K, 2018, NATURE CATALYSIS', 'Liu X, 2017, NATURE COMMUNICATIONS', 'Hori Y, 2001, THE JOURNAL OF PHYSICAL CHEMISTRY B', 'Xiao H, 2017, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Schreier M, 2017, NATURE ENERGY', 'Wang L, 2018, ACS CATALYSIS', 'Li Y, 2017, NANO LETTERS', 'Xiao H, 2016, JOURNAL OF THE AMERICAN CHEMICAL SOCIETY', 'Lum Y, 2017, THE JOURNAL OF PHYSICAL CHEMISTRY C', 'Li Y, 2016, ACS ENERGY LETTERS', 'Zeng Z, 2017, NATURE ENERGY', 'Jeanty P, 2018, JOURNAL OF CO2 UTILIZATION', 'Larrazábal G, 2017, THE JOURNAL OF PHYSICAL CHEMISTRY LETTERS', 'Xiao Q, 2017, PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES', 'Yano H, 2003, JOURNAL OF ELECTROANALYTICAL CHEMISTRY', 'Montoya J, 2017, NPJ COMPUTATIONAL MATERIALS', 'Persson K, 2012, PHYSICAL REVIEW B']</t>
         </is>
       </c>
       <c r="V191" t="inlineStr">
@@ -22357,34 +22377,34 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhou Z, 2021, </t>
+          <t>Zhong M, 2020, NATURE</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhou Z, 2021, </t>
+          <t>Zhong M, 2020, NATURE</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2335322260</t>
+          <t>https://openalex.org/W3118299338</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>10.1016/0022-2496(83)90037-8</t>
+          <t>10.38094/jastt1457</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Machine learning: An artificial intelligence approach</t>
+          <t>A Review on Linear Regression Comprehensive in Machine Learning</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -22394,76 +22414,76 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G192" t="n">
-        <v>1375</v>
+        <v>1210</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>JOURNAL OF MATHEMATICAL PSYCHOLOGY</t>
+          <t>JOURNAL OF APPLIED SCIENCE AND TECHNOLOGY TRENDS</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Journal of Mathematical Psychology</t>
+          <t>Journal of Applied Science and Technology Trends</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>['Earl Hunt']</t>
+          <t>['Dastan Hussen Maulud', 'Adnan Mohsin Abdulazeez']</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>['Earl Hunt']</t>
+          <t>['Dastan Maulud', 'Adnan M. Abdulazeez']</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Earl Hunt (corresponding author), </t>
-        </is>
-      </c>
-      <c r="N192" t="inlineStr"/>
+          <t>['Duhok Polytechnic University,  Duhok, Kurdistan Region, Iraq', 'Presidency of Duhok Polytechnic University, Duhok, Kurdistan Region, Iraq']</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Perhaps one of the most common and comprehensive statistical and machine learning algorithms are linear regression. Linear regression is used to find a linear relationship between one or more predictors. The linear regression has two types: simple regression and multiple regression (MLR). This paper discusses various works by different researchers on linear regression and polynomial regression and compares their performance using the best approach to optimize prediction and precision. Almost all of the articles analyzed in this review is focused on datasets; in order to determine a model's efficiency, it must be correlated with the actual values obtained for the explanatory variables.</t>
+        </is>
+      </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>140</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>['Artificial intelligence', 'Computer science', 'Machine learning']</t>
+          <t>['Proper linear model', 'Linear regression', 'Polynomial regression', 'Regression diagnostic', 'Regression analysis', 'Simple linear regression', 'Linear predictor function', 'Regression', 'Bayesian multivariate linear regression', 'Computer science', 'Linear model', 'Machine learning', 'Local regression', 'Multivariate adaptive regression splines', 'Statistics', 'Artificial intelligence', 'Cross-sectional regression', 'Mathematics']</t>
         </is>
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['IQ']</t>
         </is>
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Murphy K, 2012, ', 'Domingos P, 2012, COMMUNICATIONS OF THE ACM', 'Shalev‐Shwartz S, 2015, ', 'F S, 2013, ', 'Ober P, 2013, JOURNAL OF APPLIED STATISTICS', 'Kılıç S, 2013, JOURNAL OF MOOD DISORDERS', 'Xin Y, 2009, WORLD SCIENTIFIC PUBLISHING CO. PTE. LTD. EBOOKS', 'Montgomery D, 2007, WILEY-INTERSCIENCE EBOOKS', 'Wolberg J, 2005, CERN DOCUMENT SERVER (EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Kavitha S, 2016, ', 'Finlayson G, 2015, IEEE TRANSACTIONS ON IMAGE PROCESSING', 'Acharya M, 2019, ', 'Zeebaree D, 2019, ', 'Xue J, 2011, IEEE TRANSACTIONS ON IMAGE PROCESSING', 'Roopa H, 2019, IEEE ACCESS', 'Sreehari E, 2018, ', 'Kafazi I, 2017, ', 'Niu H, 2018, ', 'Zhang Z, 2019, ', 'Gopalakrishnan T, 2018, ', 'Mohammed N, 2017, ', 'Bakibayev T, 2018, ', 'Yang Y, 2018, ', 'Mohammed N, 2017, ', 'Lim H, 2019, ', 'Roziqin M, 2016, ', 'Akgün B, 2015, ', 'Luminto, 2017, ', 'Feng Q, 2015, ', 'Sarkar M, 2015, ', 'Chi H, 2015, ', 'Dehghan M, 2015, ', 'Chen Y, 2018, ', 'Sabnis N, 2019, ', 'Harimurti R, 2018, 2018 INTERNATIONAL CONFERENCE ON INFORMATION AND COMMUNICATIONS TECHNOLOGY (ICOIACT)', 'Feng X, 2017, ', 'Fujita Y, 2019, IEEE TRANSACTIONS ON MAGNETICS', 'Peng Z, 2018, ', 'Wang D, 2017, ', 'Prasad A, 2015, ', 'Wang X, 2016, ', 'Xiong C, 2019, MATHEMATICAL MODELLING AND ENGINEERING PROBLEMS', 'Kwon S, 2019, ', 'Maeda T, 2015, ', 'Wei D, 2018, ', 'Nnachi G, 2017, ', 'Zhang R, 2016, ', 'Jie H, 2019, ', 'Jackson E, 2018, ', 'Zebari D, 2020, IEEE ACCESS', 'Bargarai F, 2020, INTERNATIONAL JOURNAL OF INTERACTIVE MOBILE TECHNOLOGIES (IJIM)', 'Sulaiman M, 2020, INTERNATIONAL JOURNAL OF SUSTAINABLE CONSTRUCTION ENGINEERING AND TECHNOLOGY (UNIVERSITI TUN HUSSEIN ONN MALAYSIA)', 'Abdulazeez A, 2020, INTERNATIONAL JOURNAL OF INTERACTIVE MOBILE TECHNOLOGIES (IJIM)', 'Wu J, 2019, ', 'Al-Imam A, 2020, MODERN APPLIED SCIENCE', 'Grondin F, 2020, ']</t>
         </is>
       </c>
       <c r="V192" t="inlineStr">
@@ -22479,34 +22499,34 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>Hunt E, 1983, JOURNAL OF MATHEMATICAL PSYCHOLOGY</t>
+          <t>Maulud D, 2020, JOURNAL OF APPLIED SCIENCE AND TECHNOLOGY TRENDS</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>Hunt E, 1983, JOURNAL OF MATHEMATICAL PSYCHOLOGY</t>
+          <t>Maulud D, 2020, JOURNAL OF APPLIED SCIENCE AND TECHNOLOGY TRENDS</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3118299338</t>
+          <t>https://openalex.org/W2335322260</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>10.38094/jastt1457</t>
+          <t>10.1016/0022-2496(83)90037-8</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>A Review on Linear Regression Comprehensive in Machine Learning</t>
+          <t>Machine learning: An artificial intelligence approach</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -22516,76 +22536,76 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>1208</v>
+        <v>1375</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>JOURNAL OF APPLIED SCIENCE AND TECHNOLOGY TRENDS</t>
+          <t>JOURNAL OF MATHEMATICAL PSYCHOLOGY</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Journal of Applied Science and Technology Trends</t>
+          <t>Journal of Mathematical Psychology</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>['Dastan Hussen Maulud', 'Adnan Mohsin Abdulazeez']</t>
+          <t>['Earl Hunt']</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>['Dastan Maulud', 'Adnan M. Abdulazeez']</t>
+          <t>['Earl Hunt']</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['Duhok Polytechnic University,  Duhok, Kurdistan Region, Iraq', 'Presidency of Duhok Polytechnic University, Duhok, Kurdistan Region, Iraq']</t>
-        </is>
-      </c>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>Perhaps one of the most common and comprehensive statistical and machine learning algorithms are linear regression. Linear regression is used to find a linear relationship between one or more predictors. The linear regression has two types: simple regression and multiple regression (MLR). This paper discusses various works by different researchers on linear regression and polynomial regression and compares their performance using the best approach to optimize prediction and precision. Almost all of the articles analyzed in this review is focused on datasets; in order to determine a model's efficiency, it must be correlated with the actual values obtained for the explanatory variables.</t>
-        </is>
-      </c>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Earl Hunt (corresponding author), </t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>456</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>460</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>['Proper linear model', 'Linear regression', 'Polynomial regression', 'Regression diagnostic', 'Regression analysis', 'Simple linear regression', 'Linear predictor function', 'Regression', 'Bayesian multivariate linear regression', 'Computer science', 'Linear model', 'Machine learning', 'Local regression', 'Multivariate adaptive regression splines', 'Statistics', 'Artificial intelligence', 'Cross-sectional regression', 'Mathematics']</t>
+          <t>['Artificial intelligence', 'Computer science', 'Machine learning']</t>
         </is>
       </c>
       <c r="T193" t="inlineStr">
         <is>
-          <t>['IQ']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>['Murphy K, 2012, ', 'Domingos P, 2012, COMMUNICATIONS OF THE ACM', 'Shalev‐Shwartz S, 2015, ', '1938- S, 2013, ', 'Ober P, 2013, JOURNAL OF APPLIED STATISTICS', 'Kılıç S, 2013, JOURNAL OF MOOD DISORDERS', 'Xin Y, 2009, WORLD SCIENTIFIC PUBLISHING CO. PTE. LTD. EBOOKS', 'Montgomery D, 2007, WILEY-INTERSCIENCE EBOOKS', 'Wolberg J, 2005, CERN DOCUMENT SERVER (EUROPEAN ORGANIZATION FOR NUCLEAR RESEARCH)', 'Kavitha S, 2016, ', 'Finlayson G, 2015, IEEE TRANSACTIONS ON IMAGE PROCESSING', 'Acharya M, 2019, ', 'Zeebaree D, 2019, ', 'Xue J, 2011, IEEE TRANSACTIONS ON IMAGE PROCESSING', 'Roopa H, 2019, IEEE ACCESS', 'Sreehari E, 2018, ', 'Kafazi I, 2017, ', 'Niu H, 2018, ', 'Zhang Z, 2019, ', 'Gopalakrishnan T, 2018, ', 'Mohammed N, 2017, ', 'Bakibayev T, 2018, ', 'Yang Y, 2018, ', 'Mohammed N, 2017, ', 'Lim H, 2019, ', 'Roziqin M, 2016, ', 'Akgün B, 2015, ', 'Luminto, 2017, ', 'Feng Q, 2015, ', 'Sarkar M, 2015, ', 'Chi H, 2015, ', 'Dehghan M, 2015, ', 'Chen Y, 2018, ', 'Sabnis N, 2019, ', 'Harimurti R, 2018, 2018 INTERNATIONAL CONFERENCE ON INFORMATION AND COMMUNICATIONS TECHNOLOGY (ICOIACT)', 'Feng X, 2017, ', 'Fujita Y, 2019, IEEE TRANSACTIONS ON MAGNETICS', 'Peng Z, 2018, ', 'Wang D, 2017, ', 'Prasad A, 2015, ', 'Wang X, 2016, ', 'Xiong C, 2019, MATHEMATICAL MODELLING AND ENGINEERING PROBLEMS', 'Kwon S, 2019, ', 'Maeda T, 2015, ', 'Wei D, 2018, ', 'Nnachi G, 2017, ', 'Zhang R, 2016, ', 'Jie H, 2019, ', 'Jackson E, 2018, ', 'Zebari D, 2020, IEEE ACCESS', 'Bargarai F, 2020, INTERNATIONAL JOURNAL OF INTERACTIVE MOBILE TECHNOLOGIES (IJIM)', 'Sulaiman M, 2020, INTERNATIONAL JOURNAL OF SUSTAINABLE CONSTRUCTION ENGINEERING AND TECHNOLOGY (UNIVERSITI TUN HUSSEIN ONN MALAYSIA)', 'Abdulazeez A, 2020, INTERNATIONAL JOURNAL OF INTERACTIVE MOBILE TECHNOLOGIES (IJIM)', 'Wu J, 2019, ', 'Al-Imam A, 2020, MODERN APPLIED SCIENCE', 'Grondin F, 2020, ']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="V193" t="inlineStr">
@@ -22601,12 +22621,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>Maulud D, 2020, JOURNAL OF APPLIED SCIENCE AND TECHNOLOGY TRENDS</t>
+          <t>Hunt E, 1983, JOURNAL OF MATHEMATICAL PSYCHOLOGY</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>Maulud D, 2020, JOURNAL OF APPLIED SCIENCE AND TECHNOLOGY TRENDS</t>
+          <t>Hunt E, 1983, JOURNAL OF MATHEMATICAL PSYCHOLOGY</t>
         </is>
       </c>
     </row>
@@ -23069,22 +23089,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2218047931</t>
+          <t>https://openalex.org/W4394857110</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>10.1016/j.gsf.2015.07.003</t>
+          <t>10.1136/bmj-2023-078378</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Machine learning in geosciences and remote sensing</t>
+          <t>TRIPOD+AI statement: updated guidance for reporting clinical prediction models that use regression or machine learning methods</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -23098,76 +23118,72 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>1099</v>
+        <v>2137</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>GEOSCIENCE FRONTIERS</t>
+          <t>BMJ</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Geoscience Frontiers</t>
+          <t>BMJ</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>['David J. Lary', 'Amir H. Alavi', 'Amir H. Gandomi', 'Annette L. Walker']</t>
+          <t>['Gary S. Collins', 'Karel G.M. Moons', 'Paula Dhiman', 'Richard D Riley', 'Andrew L. Beam', 'Ben Van Calster', 'Marzyeh Ghassemi', 'Xiaoxuan Liu', 'Johannes B. Reitsma', 'Maarten van Smeden', 'Anne‐Laure Boulesteix', 'Jennifer Camaradou', 'Leo Anthony Celi', 'Spiros Denaxas', 'Alastair K. Denniston', 'Ben Glocker', 'Robert Golub', 'Hugh Harvey', 'Georg Heinze', 'Michael M. Hoffman', 'André Pascal Kengne', 'Emily Lam', 'Naomi Lee', 'Elizabeth Loder', 'Lena Maier‐Hein', 'Bilal A. Mateen', 'Melissa D. McCradden', 'Lauren Oakden‐Rayner', 'Johan Ordish', 'Richard Parnell', 'Sherri Rose', 'Karandeep Singh', 'Laure Wynants', 'Patrícia Logullo']</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>['David J. Lary', 'Amir H. Alavi', 'Amir H. Gandomi', 'Annette L. Walker']</t>
+          <t>['Gary S Collins', 'Karel G M Moons', 'Paula Dhiman', 'Richard D Riley', 'Andrew L Beam', 'Ben Van Calster', 'Marzyeh Ghassemi', 'Xiaoxuan Liu', 'Johannes B Reitsma', 'Maarten van Smeden', 'Anne-Laure Boulesteix', 'Jennifer Catherine Camaradou', 'Leo Anthony Celi', 'Spiros Denaxas', 'Alastair K Denniston', 'Ben Glocker', 'Robert M Golub', 'Hugh Harvey', 'Georg Heinze', 'Michael M Hoffman', 'André Pascal Kengne', 'Emily Lam', 'Naomi Lee', 'Elizabeth W Loder', 'Lena Maier-Hein', 'Bilal A Mateen', 'Melissa D McCradden', 'Lauren Oakden-Rayner', 'Johan Ordish', 'Richard Parnell', 'Sherri Rose', 'Karandeep Singh', 'Laure Wynants', 'Patricia Logullo']</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>['Hanson Center for Space Science, University of Texas at Dallas, Richardson, TX 75080, USA', 'Department of Civil and Environmental Engineering, Michigan State University, East Lansing, MI 48824, USA', 'BEACON Center for the Study of Evolution in Action, Michigan State University, East Lansing, MI 48824, USA', 'Aerosol and Radiation Section, Naval Research Laboratory, 7 Grace Hopper Ave., Stop 2, Monterey, CA 93943-5502, USA']</t>
+          <t>['Centre for Statistics in Medicine, UK EQUATOR Centre, Nuffield Department of Orthopaedics, Rheumatology, and Musculoskeletal Sciences, University of Oxford, Oxford OX3 7LD, UK', 'Julius Centre for Health Sciences and Primary Care, University Medical Centre Utrecht, Utrecht University, Utrecht, Netherlands', 'Centre for Statistics in Medicine, UK EQUATOR Centre, Nuffield Department of Orthopaedics, Rheumatology, and Musculoskeletal Sciences, University of Oxford, Oxford OX3 7LD, UK', 'Institute of Applied Health Research, College of Medical and Dental Sciences, University of Birmingham, Birmingham, UK', 'National Institute for Health and Care Research (NIHR) Birmingham Biomedical Research Centre, Birmingham, UK', 'Department of Epidemiology, Harvard T H Chan School of Public Health, Boston, MA, USA', 'Department of Biomedical Data Science, Leiden University Medical Centre, Leiden, Netherlands', 'Department of Development and Regeneration, KU Leuven, Leuven, Belgium', 'Department of Electrical Engineering and Computer Science, Institute for Medical Engineering and Science, Massachusetts Institute of Technology, Cambridge, MA, USA', 'Institute of Inflammation and Ageing, College of Medical and Dental Sciences, University of Birmingham, Birmingham, UK', 'University Hospitals Birmingham NHS Foundation Trust, Birmingham, UK', 'Julius Centre for Health Sciences and Primary Care, University Medical Centre Utrecht, Utrecht University, Utrecht, Netherlands', 'Julius Centre for Health Sciences and Primary Care, University Medical Centre Utrecht, Utrecht University, Utrecht, Netherlands', 'Institute for Medical Information Processing, Biometry and Epidemiology, Faculty of Medicine, Ludwig-Maximilians-University of Munich and Munich Centre of Machine Learning, Germany', 'Department of Medical Information Processing, Biometry and Epidemiology, Ludwig-Maximilians-University of Munich, Munich, Germany', 'Patient representative, Health Data Research UK patient and public involvement and engagement group', 'Patient representative, University of East Anglia, Faculty of Health Sciences, Norwich Research Park, Norwich, UK', 'Beth Israel Deaconess Medical Center, Boston, MA, USA', 'Department of Biostatistics, Harvard T H Chan School of Public Health, Boston, MA, USA', 'Laboratory for Computational Physiology, Massachusetts Institute of Technology, Cambridge, MA, USA', 'British Heart Foundation Data Science Centre, London, UK', 'Institute of Health Informatics, University College London, London, UK', 'Institute of Inflammation and Ageing, College of Medical and Dental Sciences, University of Birmingham, Birmingham, UK', 'National Institute for Health and Care Research (NIHR) Birmingham Biomedical Research Centre, Birmingham, UK', 'Department of Computing, Imperial College London, London, UK', 'Northwestern University Feinberg School of Medicine, Chicago, IL, USA', 'Hardian Health, Haywards Heath, UK', 'Section for Clinical Biometrics, Centre for Medical Data Science, Medical University of Vienna, Vienna, Austria', 'Department of Computer Science, University of Toronto, Toronto, ON, Canada', 'Department of Medical Biophysics, University of Toronto, Toronto, ON, Canada', 'Princess Margaret Cancer Centre, University Health Network, Toronto, ON, Canada', 'Vector Institute for Artificial Intelligence, Toronto, ON, Canada', 'Department of Medicine, University of Cape Town, Cape Town, South Africa', 'Patient representative, Health Data Research UK patient and public involvement and engagement group', 'National Institute for Health and Care Excellence, London, UK', "Department of Neurology, Brigham and Women's Hospital, Harvard Medical School, Boston, MA, USA", 'The BMJ, London, UK', 'Department of Intelligent Medical Systems, German Cancer Research Centre, Heidelberg, Germany', 'Alan Turing Institute, London, UK', 'Institute of Health Informatics, University College London, London, UK', 'Wellcome Trust, London, UK', 'Department of Bioethics, Hospital for Sick Children Toronto, ON, Canada', 'Genetics and Genome Biology, SickKids Research Institute, Toronto, ON, Canada', 'Australian Institute for Machine Learning, University of Adelaide, Adelaide, SA, Australia', 'Medicines and Healthcare products Regulatory Agency, London, UK', 'Patient representative, Health Data Research UK patient and public involvement and engagement group', 'Department of Health Policy and Center for Health Policy, Stanford University, Stanford, CA, USA', 'Australian Institute for Machine Learning, University of Adelaide, Adelaide, SA, Australia', 'Department of Epidemiology, CAPHRI Care and Public Health Research Institute, Maastricht University, Maastricht, Netherlands', 'Department of Health Policy and Center for Health Policy, Stanford University, Stanford, CA, USA', 'Department of Epidemiology, CAPHRI Care and Public Health Research Institute, Maastricht University, Maastricht, Netherlands', 'Centre for Statistics in Medicine, UK EQUATOR Centre, Nuffield Department of Orthopaedics, Rheumatology, and Musculoskeletal Sciences, University of Oxford, Oxford OX3 7LD, UK']</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Amir H. Alavi (corresponding author), Department of Civil and Environmental Engineering, Michigan State University, East Lansing, MI 48824, USA</t>
+          <t>Gary S Collins (corresponding author), Centre for Statistics in Medicine, UK EQUATOR Centre, Nuffield Department of Orthopaedics, Rheumatology, and Musculoskeletal Sciences, University of Oxford, Oxford OX3 7LD, UK</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>Learning incorporates a broad range of complex procedures. Machine learning (ML) is a subdivision of artificial intelligence based on the biological learning process. The ML approach deals with the design of algorithms to learn from machine readable data. ML covers main domains such as data mining, difficult-to-program applications, and software applications. It is a collection of a variety of algorithms (e.g. neural networks, support vector machines, self-organizing map, decision trees, random forests, case-based reasoning, genetic programming, etc.) that can provide multivariate, nonlinear, nonparametric regression or classification. The modeling capabilities of the ML-based methods have resulted in their extensive applications in science and engineering. Herein, the role of ML as an effective approach for solving problems in geosciences and remote sensing will be highlighted. The unique features of some of the ML techniques will be outlined with a specific attention to genetic programming paradigm. Furthermore, nonparametric regression and classification illustrative examples are presented to demonstrate the efficiency of ML for tackling the geosciences and remote sensing problems.</t>
+          <t>The TRIPOD (Transparent Reporting of a multivariable prediction model for Individual Prognosis Or Diagnosis) statement was published in 2015 to provide the minimum reporting recommendations for studies developing or evaluating the performance of a prediction model. Methodological advances in the field of prediction have since included the widespread use of artificial intelligence (AI) powered by machine learning methods to develop prediction models. An update to the TRIPOD statement is thus needed. TRIPOD+AI provides harmonised guidance for reporting prediction model studies, irrespective of whether regression modelling or machine learning methods have been used. The new checklist supersedes the TRIPOD 2015 checklist, which should no longer be used. This article describes the development of TRIPOD+AI and presents the expanded 27 item checklist with more detailed explanation of each reporting recommendation, and the TRIPOD+AI for Abstracts checklist. TRIPOD+AI aims to promote the complete, accurate, and transparent reporting of studies that develop a prediction model or evaluate its performance. Complete reporting will facilitate study appraisal, model evaluation, and model implementation.</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P198" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr"/>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>e078378</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>e078378</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>['Computer science', 'Machine learning', 'Genetic programming', 'Artificial intelligence', 'Process (computing)', 'Artificial neural network', 'Support vector machine', 'Variety (cybernetics)', 'Decision tree', 'Range (aeronautics)', 'Random forest', 'Software', 'Nonparametric statistics', 'Data mining']</t>
+          <t>['Tripod (photography)', 'Checklist', 'Machine learning', 'Computer science', 'Artificial intelligence', 'Engineering', 'Psychology']</t>
         </is>
       </c>
       <c r="T198" t="inlineStr">
         <is>
-          <t>['US']</t>
+          <t>['GB', 'NL', 'US', 'BE', 'DE', 'AT', 'CA', 'ZA', 'AU']</t>
         </is>
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>['Koza J, 1992, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Kohonen T, 1982, BIOLOGICAL CYBERNETICS', 'Prospero J, 2002, REVIEWS OF GEOPHYSICS', 'Ginoux P, 2001, JOURNAL OF GEOPHYSICAL RESEARCH ATMOSPHERES', 'Tegen I, 1996, NATURE', 'Pope C, 2009, CIRCULATION', 'Allen M, 2000, NATURE', 'Lee H, 2011, ATMOSPHERIC CHEMISTRY AND PHYSICS', 'Shahin M, 2001, ', 'Alavi A, 2011, ENGINEERING COMPUTATIONS', 'Yi J, 1996, ENVIRONMENTAL POLLUTION', 'Samui P, 2007, COMPUTERS AND GEOTECHNICS', 'Samui P, 2008, ENVIRONMENTAL GEOLOGY', 'Alavi A, 2010, CONSTRUCTION AND BUILDING MATERIALS', 'Engel‐Cox J, 2004, JOURNAL OF THE AIR &amp; WASTE MANAGEMENT ASSOCIATION', 'Alavi A, 2009, ENGINEERING WITH COMPUTERS', 'Javadi A, 2006, COMPUTERS AND GEOTECHNICS', 'Das S, 2008, ENGINEERING GEOLOGY', 'Azamathulla H, 2011, APPLIED SOFT COMPUTING', 'Boldo E, 2010, ENVIRONMENT INTERNATIONAL', 'Lary D, 2014, GEOSPATIAL HEALTH', 'Garg A, 2014, RAPID PROTOTYPING JOURNAL', 'Garg A, 2014, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Ginoux P, 2003, JOURNAL OF GEOPHYSICAL RESEARCH ATMOSPHERES', 'Chuang M, 2011, ATMOSPHERIC ENVIRONMENT', 'Alavi A, 2011, GEOSCIENCE FRONTIERS', 'Makkeasorn A, 2006, WATER RESOURCES RESEARCH', 'Liu Y, 2012, ENVIRONMENT INTERNATIONAL', 'Zahabiyoun B, 2012, CLEAN - SOIL AIR WATER', 'Azamathulla H, 2011, OCEAN ENGINEERING', 'Makkeasorn A, 2008, JOURNAL OF ENVIRONMENTAL MANAGEMENT', 'Shahin M, 2005, COMPUTERS AND GEOTECHNICS', 'Çabalar A, 2009, COMPUTERS &amp; GEOSCIENCES', 'Ayala A, 2011, AIR QUALITY ATMOSPHERE &amp; HEALTH', 'Karakus M, 2010, COMPUTERS &amp; GEOSCIENCES', 'Liu Y, 2011, ATMOSPHERIC ENVIRONMENT', 'Garg A, 2014, MECCANICA', 'Madadi M, 2014, EARTH SCIENCE INFORMATICS', 'Li W, 2007, INTERNATIONAL JOURNAL OF ROCK MECHANICS AND MINING SCIENCES', 'Zhai S, 2006, JOURNAL OF CHINA UNIVERSITY OF GEOSCIENCES', 'Alavi A, 2011, JOURNAL OF EARTHQUAKE ENGINEERING', 'Samui P, 2010, INTERNATIONAL JOURNAL FOR NUMERICAL AND ANALYTICAL METHODS IN GEOMECHANICS', 'Ravandi E, 2013, INTERNATIONAL JOURNAL OF MINING SCIENCE AND TECHNOLOGY', 'John D, 2010, INTECH EBOOKS', 'Santos J, 2010, ', 'Nikravesh M, 2007, STUDIES IN FUZZINESS AND SOFT COMPUTING', 'Chen L, 2003, INTERNATIONAL JOURNAL OF REMOTE SENSING', 'Lewkowski C, 2010, EGU GENERAL ASSEMBLY CONFERENCE ABSTRACTS', 'Chen L, 2011, HYDROLOGICAL PROCESSES', 'Chuang M, 2012, ATMOSPHERIC ENVIRONMENT', 'Change I, 2014, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Dockery D, 1993, NEW ENGLAND JOURNAL OF MEDICINE', 'Stocker R, 2013, ', 'Pope C, 2006, JOURNAL OF THE AIR &amp; WASTE MANAGEMENT ASSOCIATION', 'Brook R, 2010, CIRCULATION', 'Foody G, 2002, REMOTE SENSING OF ENVIRONMENT', 'Grell G, 2005, ATMOSPHERIC ENVIRONMENT', 'Kohonen T, 1982, BIOLOGICAL CYBERNETICS', 'Schauer J, 1996, ATMOSPHERIC ENVIRONMENT', 'Atkinson P, 1997, INTERNATIONAL JOURNAL OF REMOTE SENSING', 'Hansen J, 1988, JOURNAL OF GEOPHYSICAL RESEARCH ATMOSPHERES', 'Tegen I, 1996, JOURNAL OF GEOPHYSICAL RESEARCH ATMOSPHERES', 'Engel‐Cox J, 2004, ATMOSPHERIC ENVIRONMENT', 'Baykasoğlu A, 2007, EXPERT SYSTEMS WITH APPLICATIONS', 'Detto M, 2006, WATER RESOURCES RESEARCH', 'Liu Y, 2006, REMOTE SENSING OF ENVIRONMENT', 'Schaap M, 2009, ATMOSPHERIC CHEMISTRY AND PHYSICS', 'Gandomi A, 2011, INFORMATION SCIENCES', 'Azamathulla H, 2010, APPLIED SOFT COMPUTING', 'Gandomi A, 2011, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Risacher F, 1991, CHEMICAL GEOLOGY', 'Walker A, 2009, JOURNAL OF GEOPHYSICAL RESEARCH ATMOSPHERES', 'Brown M, 2008, INTERNATIONAL JOURNAL OF REMOTE SENSING', 'Carpenter G, 1997, IEEE TRANSACTIONS ON GEOSCIENCE AND REMOTE SENSING', 'Lary D, 2009, IEEE GEOSCIENCE AND REMOTE SENSING LETTERS', 'Risacher F, 1991, GEOCHIMICA ET COSMOCHIMICA ACTA', 'Beiki M, 2010, INTERNATIONAL JOURNAL OF ROCK MECHANICS AND MINING SCIENCES', 'Özbek A, 2013, JOURNAL OF ROCK MECHANICS AND GEOTECHNICAL ENGINEERING', 'Imperatore P, 2010, INTECH EBOOKS', 'Rajeev K, 2008, JOURNAL OF GEOPHYSICAL RESEARCH ATMOSPHERES', 'Gandomi A, 2013, INTERNATIONAL JOURNAL OF EARTHQUAKE ENGINEERING AND HAZARD MITIGATION (IREHM)', 'Lary D, 2004, ATMOSPHERIC CHEMISTRY AND PHYSICS', 'Rosin P, 2002, ', 'Prospero J, 2003, GEOCHIMICA ET COSMOCHIMICA ACTA SUPPLEMENT', 'Lary D, 2007, GEOPHYSICAL RESEARCH LETTERS', 'Lee H, 2010, EPIDEMIOLOGY', ', 2002, ']</t>
+          <t>['D’Agostino R, 2008, CIRCULATION', 'Moons K, 2015, ANNALS OF INTERNAL MEDICINE', 'Gail M, 1989, JNCI JOURNAL OF THE NATIONAL CANCER INSTITUTE', 'Wynants L, 2020, BMJ', 'Collins G, 2015, ANNALS OF INTERNAL MEDICINE', 'Nashef S, 2012, EUROPEAN JOURNAL OF CARDIO-THORACIC SURGERY', 'Wolff R, 2018, ANNALS OF INTERNAL MEDICINE', 'Riley R, 2020, BMJ', 'Christodoulou E, 2019, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Staniszewska S, 2017, RESEARCH INVOLVEMENT AND ENGAGEMENT', 'Moons K, 2018, ANNALS OF INTERNAL MEDICINE', 'Moher D, 2010, PLOS MEDICINE', 'Steyerberg E, 2008, PLOS MEDICINE', 'Glasziou P, 2014, THE LANCET', 'Mongan J, 2020, RADIOLOGY ARTIFICIAL INTELLIGENCE', 'Kanis J, 2007, OSTEOPOROSIS INTERNATIONAL', 'Riley R, 2018, STATISTICS IN MEDICINE', 'Damen J, 2016, BMJ', 'Smeden M, 2018, STATISTICAL METHODS IN MEDICAL RESEARCH', 'Collins G, 2014, BMC MEDICAL RESEARCH METHODOLOGY', 'Collins G, 2019, THE LANCET', 'Bouwmeester W, 2012, PLOS MEDICINE', 'Liu X, 2020, BMJ', 'Norgeot B, 2020, NATURE MEDICINE', 'Smeden M, 2016, BMC MEDICAL RESEARCH METHODOLOGY', 'Collins G, 2011, BMC MEDICINE', 'Chen I, 2021, ANNUAL REVIEW OF BIOMEDICAL DATA SCIENCE', 'Hernandez‐Boussard T, 2020, JOURNAL OF THE AMERICAN MEDICAL INFORMATICS ASSOCIATION', 'Rivera S, 2020, BMJ', 'Schwendicke F, 2021, JOURNAL OF DENTISTRY', 'Riley R, 2018, STATISTICS IN MEDICINE', 'Ibrahim H, 2021, THE LANCET DIGITAL HEALTH', 'Stevens L, 2020, CIRCULATION CARDIOVASCULAR QUALITY AND OUTCOMES', 'McCradden M, 2020, THE LANCET DIGITAL HEALTH', 'McDermott M, 2021, SCIENCE TRANSLATIONAL MEDICINE', 'Smeden M, 2021, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Sendak M, 2020, NPJ DIGITAL MEDICINE', 'Altman D, 2008, PUBMED', 'Mallett S, 2010, BMC MEDICINE', 'Bellou V, 2019, BMJ', 'Wang W, 2020, PLOS ONE', 'Archer L, 2020, STATISTICS IN MEDICINE', 'Scott I, 2021, BMJ HEALTH &amp; CARE INFORMATICS', 'Snell K, 2021, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Yusuf M, 2020, BMJ OPEN', 'Miles J, 2020, DIAGNOSTIC AND PROGNOSTIC RESEARCH', 'Groot O, 2021, JOURNAL OF ORTHOPAEDIC RESEARCH®', 'Groot O, 2021, ACTA ORTHOPAEDICA', 'Heus P, 2020, ANNALS OF INTERNAL MEDICINE', 'Kadakia K, 2021, NEW ENGLAND JOURNAL OF MEDICINE', 'Staniszewska S, 2017, BMJ', 'Collins G, 2021, BMJ OPEN', 'Gattrell W, 2024, PLOS MEDICINE', 'Collins G, 2024, BMJ', 'Vasey B, 2022, NATURE MEDICINE', 'Hond A, 2022, NPJ DIGITAL MEDICINE', 'Navarro C, 2021, BMJ', 'Riley R, 2021, STATISTICS IN MEDICINE', 'Altman D, 2008, THE LANCET', 'Sounderajah V, 2021, BMJ OPEN', 'Riley R, 2024, BMJ', 'Calster B, 2023, BMC MEDICINE', 'Snell K, 2023, BMJ', 'Riley R, 2024, BMJ', 'Dhiman P, 2022, BMC MEDICAL RESEARCH METHODOLOGY', 'Olczak J, 2021, ACTA ORTHOPAEDICA', 'Cacciamani G, 2023, NATURE MEDICINE', 'Navarro C, 2022, BMC MEDICAL RESEARCH METHODOLOGY', 'Li B, 2022, NPJ DIGITAL MEDICINE', ', 2021, ', 'Dhiman P, 2021, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Riley R, 2021, STATISTICS IN MEDICINE', 'Gichoya J, 2021, BMJ HEALTH &amp; CARE INFORMATICS', 'Navarro C, 2022, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Ganapathi S, 2022, NATURE MEDICINE', 'Wessler B, 2021, CIRCULATION CARDIOVASCULAR QUALITY AND OUTCOMES', 'Debray T, 2023, BMJ', 'Kee O, 2023, CARDIOVASCULAR DIABETOLOGY', 'Kwong J, 2021, EUROPEAN UROLOGY FOCUS', 'Dhiman P, 2022, DIAGNOSTIC AND PROGNOSTIC RESEARCH', 'Navarro C, 2023, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Thibault R, 2023, PLOS BIOLOGY', 'Debray T, 2023, BMJ', 'Dhiman P, 2023, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Araújo A, 2023, ORAL ONCOLOGY', 'Yang Q, 2022, ACTA OBSTETRICIA ET GYNECOLOGICA SCANDINAVICA', 'Sheehy J, 2023, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'McCradden M, 2023, ', 'Finlayson S, 2023, JAMA PEDIATRICS', 'Collins G, 2023, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Song Z, 2022, FRONTIERS IN CARDIOVASCULAR MEDICINE', 'Munguía‐Realpozo P, 2023, AUTOIMMUNITY REVIEWS', 'Dhiman P, 2023, NATURE MACHINE INTELLIGENCE', 'Camaradou J, 2023, ADVANCES IN THERAPY', 'Lans A, 2022, JOURNAL OF EVALUATION IN CLINICAL PRACTICE', 'Rech M, 2023, BRAIN SCIENCES', 'Hawksworth C, 2023, MEDRXIV']</t>
         </is>
       </c>
       <c r="V198" t="inlineStr">
@@ -23183,34 +23199,34 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>Lary D, 2015, GEOSCIENCE FRONTIERS</t>
+          <t>Collins G, 2024, BMJ</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>Lary D, 2015, GEOSCIENCE FRONTIERS</t>
+          <t>Collins G, 2024, BMJ</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://openalex.org/W4394857110</t>
+          <t>https://openalex.org/W2218047931</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>10.1136/bmj-2023-078378</t>
+          <t>10.1016/j.gsf.2015.07.003</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>TRIPOD+AI statement: updated guidance for reporting clinical prediction models that use regression or machine learning methods</t>
+          <t>Machine learning in geosciences and remote sensing</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -23224,72 +23240,76 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>2113</v>
+        <v>1099</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>BMJ</t>
+          <t>GEOSCIENCE FRONTIERS</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>BMJ</t>
+          <t>Geoscience Frontiers</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>['Gary S. Collins', 'Karel G.M. Moons', 'Paula Dhiman', 'Richard D Riley', 'Andrew L. Beam', 'Ben Van Calster', 'Marzyeh Ghassemi', 'Xiaoxuan Liu', 'Johannes B. Reitsma', 'Maarten van Smeden', 'Anne‐Laure Boulesteix', 'Jennifer Camaradou', 'Leo Anthony Celi', 'Spiros Denaxas', 'Alastair K. Denniston', 'Ben Glocker', 'Robert Golub', 'Hugh Harvey', 'Georg Heinze', 'Michael M. Hoffman', 'André Pascal Kengne', 'Emily Lam', 'Naomi Lee', 'Elizabeth Loder', 'Lena Maier‐Hein', 'Bilal A. Mateen', 'Melissa D. McCradden', 'Lauren Oakden‐Rayner', 'Johan Ordish', 'Richard Parnell', 'Sherri Rose', 'Karandeep Singh', 'Laure Wynants', 'Patrícia Logullo']</t>
+          <t>['David J. Lary', 'Amir H. Alavi', 'Amir H. Gandomi', 'Annette L. Walker']</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>['Gary S Collins', 'Karel G M Moons', 'Paula Dhiman', 'Richard D Riley', 'Andrew L Beam', 'Ben Van Calster', 'Marzyeh Ghassemi', 'Xiaoxuan Liu', 'Johannes B Reitsma', 'Maarten van Smeden', 'Anne-Laure Boulesteix', 'Jennifer Catherine Camaradou', 'Leo Anthony Celi', 'Spiros Denaxas', 'Alastair K Denniston', 'Ben Glocker', 'Robert M Golub', 'Hugh Harvey', 'Georg Heinze', 'Michael M Hoffman', 'André Pascal Kengne', 'Emily Lam', 'Naomi Lee', 'Elizabeth W Loder', 'Lena Maier-Hein', 'Bilal A Mateen', 'Melissa D McCradden', 'Lauren Oakden-Rayner', 'Johan Ordish', 'Richard Parnell', 'Sherri Rose', 'Karandeep Singh', 'Laure Wynants', 'Patricia Logullo']</t>
+          <t>['David J. Lary', 'Amir H. Alavi', 'Amir H. Gandomi', 'Annette L. Walker']</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>['Centre for Statistics in Medicine, UK EQUATOR Centre, Nuffield Department of Orthopaedics, Rheumatology, and Musculoskeletal Sciences, University of Oxford, Oxford OX3 7LD, UK', 'Julius Centre for Health Sciences and Primary Care, University Medical Centre Utrecht, Utrecht University, Utrecht, Netherlands', 'Centre for Statistics in Medicine, UK EQUATOR Centre, Nuffield Department of Orthopaedics, Rheumatology, and Musculoskeletal Sciences, University of Oxford, Oxford OX3 7LD, UK', 'Institute of Applied Health Research, College of Medical and Dental Sciences, University of Birmingham, Birmingham, UK', 'National Institute for Health and Care Research (NIHR) Birmingham Biomedical Research Centre, Birmingham, UK', 'Department of Epidemiology, Harvard T H Chan School of Public Health, Boston, MA, USA', 'Department of Biomedical Data Science, Leiden University Medical Centre, Leiden, Netherlands', 'Department of Development and Regeneration, KU Leuven, Leuven, Belgium', 'Department of Electrical Engineering and Computer Science, Institute for Medical Engineering and Science, Massachusetts Institute of Technology, Cambridge, MA, USA', 'Institute of Inflammation and Ageing, College of Medical and Dental Sciences, University of Birmingham, Birmingham, UK', 'University Hospitals Birmingham NHS Foundation Trust, Birmingham, UK', 'Julius Centre for Health Sciences and Primary Care, University Medical Centre Utrecht, Utrecht University, Utrecht, Netherlands', 'Julius Centre for Health Sciences and Primary Care, University Medical Centre Utrecht, Utrecht University, Utrecht, Netherlands', 'Institute for Medical Information Processing, Biometry and Epidemiology, Faculty of Medicine, Ludwig-Maximilians-University of Munich and Munich Centre of Machine Learning, Germany', 'Department of Medical Information Processing, Biometry and Epidemiology, Ludwig-Maximilians-University of Munich, Munich, Germany', 'Patient representative, Health Data Research UK patient and public involvement and engagement group', 'Patient representative, University of East Anglia, Faculty of Health Sciences, Norwich Research Park, Norwich, UK', 'Beth Israel Deaconess Medical Center, Boston, MA, USA', 'Department of Biostatistics, Harvard T H Chan School of Public Health, Boston, MA, USA', 'Laboratory for Computational Physiology, Massachusetts Institute of Technology, Cambridge, MA, USA', 'British Heart Foundation Data Science Centre, London, UK', 'Institute of Health Informatics, University College London, London, UK', 'Institute of Inflammation and Ageing, College of Medical and Dental Sciences, University of Birmingham, Birmingham, UK', 'National Institute for Health and Care Research (NIHR) Birmingham Biomedical Research Centre, Birmingham, UK', 'Department of Computing, Imperial College London, London, UK', 'Northwestern University Feinberg School of Medicine, Chicago, IL, USA', 'Hardian Health, Haywards Heath, UK', 'Section for Clinical Biometrics, Centre for Medical Data Science, Medical University of Vienna, Vienna, Austria', 'Department of Computer Science, University of Toronto, Toronto, ON, Canada', 'Department of Medical Biophysics, University of Toronto, Toronto, ON, Canada', 'Princess Margaret Cancer Centre, University Health Network, Toronto, ON, Canada', 'Vector Institute for Artificial Intelligence, Toronto, ON, Canada', 'Department of Medicine, University of Cape Town, Cape Town, South Africa', 'Patient representative, Health Data Research UK patient and public involvement and engagement group', 'National Institute for Health and Care Excellence, London, UK', "Department of Neurology, Brigham and Women's Hospital, Harvard Medical School, Boston, MA, USA", 'The BMJ, London, UK', 'Department of Intelligent Medical Systems, German Cancer Research Centre, Heidelberg, Germany', 'Alan Turing Institute, London, UK', 'Institute of Health Informatics, University College London, London, UK', 'Wellcome Trust, London, UK', 'Department of Bioethics, Hospital for Sick Children Toronto, ON, Canada', 'Genetics and Genome Biology, SickKids Research Institute, Toronto, ON, Canada', 'Australian Institute for Machine Learning, University of Adelaide, Adelaide, SA, Australia', 'Medicines and Healthcare products Regulatory Agency, London, UK', 'Patient representative, Health Data Research UK patient and public involvement and engagement group', 'Department of Health Policy and Center for Health Policy, Stanford University, Stanford, CA, USA', 'Australian Institute for Machine Learning, University of Adelaide, Adelaide, SA, Australia', 'Department of Epidemiology, CAPHRI Care and Public Health Research Institute, Maastricht University, Maastricht, Netherlands', 'Department of Health Policy and Center for Health Policy, Stanford University, Stanford, CA, USA', 'Department of Epidemiology, CAPHRI Care and Public Health Research Institute, Maastricht University, Maastricht, Netherlands', 'Centre for Statistics in Medicine, UK EQUATOR Centre, Nuffield Department of Orthopaedics, Rheumatology, and Musculoskeletal Sciences, University of Oxford, Oxford OX3 7LD, UK']</t>
+          <t>['Hanson Center for Space Science, University of Texas at Dallas, Richardson, TX 75080, USA', 'Department of Civil and Environmental Engineering, Michigan State University, East Lansing, MI 48824, USA', 'BEACON Center for the Study of Evolution in Action, Michigan State University, East Lansing, MI 48824, USA', 'Aerosol and Radiation Section, Naval Research Laboratory, 7 Grace Hopper Ave., Stop 2, Monterey, CA 93943-5502, USA']</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Gary S Collins (corresponding author), Centre for Statistics in Medicine, UK EQUATOR Centre, Nuffield Department of Orthopaedics, Rheumatology, and Musculoskeletal Sciences, University of Oxford, Oxford OX3 7LD, UK</t>
+          <t>Amir H. Alavi (corresponding author), Department of Civil and Environmental Engineering, Michigan State University, East Lansing, MI 48824, USA</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>The TRIPOD (Transparent Reporting of a multivariable prediction model for Individual Prognosis Or Diagnosis) statement was published in 2015 to provide the minimum reporting recommendations for studies developing or evaluating the performance of a prediction model. Methodological advances in the field of prediction have since included the widespread use of artificial intelligence (AI) powered by machine learning methods to develop prediction models. An update to the TRIPOD statement is thus needed. TRIPOD+AI provides harmonised guidance for reporting prediction model studies, irrespective of whether regression modelling or machine learning methods have been used. The new checklist supersedes the TRIPOD 2015 checklist, which should no longer be used. This article describes the development of TRIPOD+AI and presents the expanded 27 item checklist with more detailed explanation of each reporting recommendation, and the TRIPOD+AI for Abstracts checklist. TRIPOD+AI aims to promote the complete, accurate, and transparent reporting of studies that develop a prediction model or evaluate its performance. Complete reporting will facilitate study appraisal, model evaluation, and model implementation.</t>
+          <t>Learning incorporates a broad range of complex procedures. Machine learning (ML) is a subdivision of artificial intelligence based on the biological learning process. The ML approach deals with the design of algorithms to learn from machine readable data. ML covers main domains such as data mining, difficult-to-program applications, and software applications. It is a collection of a variety of algorithms (e.g. neural networks, support vector machines, self-organizing map, decision trees, random forests, case-based reasoning, genetic programming, etc.) that can provide multivariate, nonlinear, nonparametric regression or classification. The modeling capabilities of the ML-based methods have resulted in their extensive applications in science and engineering. Herein, the role of ML as an effective approach for solving problems in geosciences and remote sensing will be highlighted. The unique features of some of the ML techniques will be outlined with a specific attention to genetic programming paradigm. Furthermore, nonparametric regression and classification illustrative examples are presented to demonstrate the efficiency of ML for tackling the geosciences and remote sensing problems.</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="P199" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>e078378</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>e078378</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>['Tripod (photography)', 'Checklist', 'Machine learning', 'Computer science', 'Artificial intelligence', 'Engineering', 'Psychology']</t>
+          <t>['Computer science', 'Machine learning', 'Genetic programming', 'Artificial intelligence', 'Process (computing)', 'Artificial neural network', 'Support vector machine', 'Variety (cybernetics)', 'Decision tree', 'Range (aeronautics)', 'Random forest', 'Software', 'Nonparametric statistics', 'Data mining']</t>
         </is>
       </c>
       <c r="T199" t="inlineStr">
         <is>
-          <t>['GB', 'NL', 'US', 'BE', 'DE', 'AT', 'CA', 'ZA', 'AU']</t>
+          <t>['US']</t>
         </is>
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>['D’Agostino R, 2008, CIRCULATION', 'Moons K, 2015, ANNALS OF INTERNAL MEDICINE', 'Gail M, 1989, JNCI JOURNAL OF THE NATIONAL CANCER INSTITUTE', 'Wynants L, 2020, BMJ', 'Collins G, 2015, ANNALS OF INTERNAL MEDICINE', 'Nashef S, 2012, EUROPEAN JOURNAL OF CARDIO-THORACIC SURGERY', 'Wolff R, 2018, ANNALS OF INTERNAL MEDICINE', 'Riley R, 2020, BMJ', 'Christodoulou E, 2019, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Staniszewska S, 2017, RESEARCH INVOLVEMENT AND ENGAGEMENT', 'Moons K, 2018, ANNALS OF INTERNAL MEDICINE', 'Moher D, 2010, PLOS MEDICINE', 'Steyerberg E, 2008, PLOS MEDICINE', 'Glasziou P, 2014, THE LANCET', 'Mongan J, 2020, RADIOLOGY ARTIFICIAL INTELLIGENCE', 'Kanis J, 2007, OSTEOPOROSIS INTERNATIONAL', 'Riley R, 2018, STATISTICS IN MEDICINE', 'Damen J, 2016, BMJ', 'Smeden M, 2018, STATISTICAL METHODS IN MEDICAL RESEARCH', 'Collins G, 2014, BMC MEDICAL RESEARCH METHODOLOGY', 'Collins G, 2019, THE LANCET', 'Bouwmeester W, 2012, PLOS MEDICINE', 'Liu X, 2020, BMJ', 'Norgeot B, 2020, NATURE MEDICINE', 'Smeden M, 2016, BMC MEDICAL RESEARCH METHODOLOGY', 'Collins G, 2011, BMC MEDICINE', 'Chen I, 2021, ANNUAL REVIEW OF BIOMEDICAL DATA SCIENCE', 'Hernandez‐Boussard T, 2020, JOURNAL OF THE AMERICAN MEDICAL INFORMATICS ASSOCIATION', 'Rivera S, 2020, BMJ', 'Schwendicke F, 2021, JOURNAL OF DENTISTRY', 'Riley R, 2018, STATISTICS IN MEDICINE', 'Ibrahim H, 2021, THE LANCET DIGITAL HEALTH', 'Stevens L, 2020, CIRCULATION CARDIOVASCULAR QUALITY AND OUTCOMES', 'McCradden M, 2020, THE LANCET DIGITAL HEALTH', 'McDermott M, 2021, SCIENCE TRANSLATIONAL MEDICINE', 'Smeden M, 2021, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Sendak M, 2020, NPJ DIGITAL MEDICINE', 'Altman D, 2008, PUBMED', 'Mallett S, 2010, BMC MEDICINE', 'Bellou V, 2019, BMJ', 'Wang W, 2020, PLOS ONE', 'Archer L, 2020, STATISTICS IN MEDICINE', 'Scott I, 2021, BMJ HEALTH &amp; CARE INFORMATICS', 'Snell K, 2021, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Yusuf M, 2020, BMJ OPEN', 'Miles J, 2020, DIAGNOSTIC AND PROGNOSTIC RESEARCH', 'Groot O, 2021, JOURNAL OF ORTHOPAEDIC RESEARCH®', 'Groot O, 2021, ACTA ORTHOPAEDICA', 'Heus P, 2020, ANNALS OF INTERNAL MEDICINE', 'Kadakia K, 2021, NEW ENGLAND JOURNAL OF MEDICINE', 'Staniszewska S, 2017, BMJ', 'Collins G, 2021, BMJ OPEN', 'Gattrell W, 2024, PLOS MEDICINE', 'Collins G, 2024, BMJ', 'Vasey B, 2022, NATURE MEDICINE', 'Hond A, 2022, NPJ DIGITAL MEDICINE', 'Navarro C, 2021, BMJ', 'Riley R, 2021, STATISTICS IN MEDICINE', 'Altman D, 2008, THE LANCET', 'Sounderajah V, 2021, BMJ OPEN', 'Riley R, 2024, BMJ', 'Calster B, 2023, BMC MEDICINE', 'Snell K, 2023, BMJ', 'Dhiman P, 2022, BMC MEDICAL RESEARCH METHODOLOGY', 'Riley R, 2024, BMJ', 'Olczak J, 2021, ACTA ORTHOPAEDICA', 'Cacciamani G, 2023, NATURE MEDICINE', 'Navarro C, 2022, BMC MEDICAL RESEARCH METHODOLOGY', 'Li B, 2022, NPJ DIGITAL MEDICINE', ', 2021, ', 'Dhiman P, 2021, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Riley R, 2021, STATISTICS IN MEDICINE', 'Gichoya J, 2021, BMJ HEALTH &amp; CARE INFORMATICS', 'Navarro C, 2022, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Ganapathi S, 2022, NATURE MEDICINE', 'Wessler B, 2021, CIRCULATION CARDIOVASCULAR QUALITY AND OUTCOMES', 'Debray T, 2023, BMJ', 'Kee O, 2023, CARDIOVASCULAR DIABETOLOGY', 'Kwong J, 2021, EUROPEAN UROLOGY FOCUS', 'Dhiman P, 2022, DIAGNOSTIC AND PROGNOSTIC RESEARCH', 'Navarro C, 2023, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Thibault R, 2023, PLOS BIOLOGY', 'Debray T, 2023, BMJ', 'Dhiman P, 2023, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Araújo A, 2023, ORAL ONCOLOGY', 'Yang Q, 2022, ACTA OBSTETRICIA ET GYNECOLOGICA SCANDINAVICA', 'Sheehy J, 2023, ARTIFICIAL INTELLIGENCE IN MEDICINE', 'McCradden M, 2023, ', 'Finlayson S, 2023, JAMA PEDIATRICS', 'Collins G, 2023, JOURNAL OF CLINICAL EPIDEMIOLOGY', 'Munguía‐Realpozo P, 2023, AUTOIMMUNITY REVIEWS', 'Dhiman P, 2023, NATURE MACHINE INTELLIGENCE', 'Song Z, 2022, FRONTIERS IN CARDIOVASCULAR MEDICINE', 'Camaradou J, 2023, ADVANCES IN THERAPY', 'Lans A, 2022, JOURNAL OF EVALUATION IN CLINICAL PRACTICE', 'Rech M, 2023, BRAIN SCIENCES', 'Hawksworth C, 2023, MEDRXIV']</t>
+          <t>['Koza J, 1992, MEDICAL ENTOMOLOGY AND ZOOLOGY', 'Kohonen T, 1982, BIOLOGICAL CYBERNETICS', 'Prospero J, 2002, REVIEWS OF GEOPHYSICS', 'Ginoux P, 2001, JOURNAL OF GEOPHYSICAL RESEARCH ATMOSPHERES', 'Tegen I, 1996, NATURE', 'Pope C, 2009, CIRCULATION', 'Allen M, 2000, NATURE', 'Lee H, 2011, ATMOSPHERIC CHEMISTRY AND PHYSICS', 'Shahin M, 2001, ', 'Alavi A, 2011, ENGINEERING COMPUTATIONS', 'Yi J, 1996, ENVIRONMENTAL POLLUTION', 'Samui P, 2007, COMPUTERS AND GEOTECHNICS', 'Samui P, 2008, ENVIRONMENTAL GEOLOGY', 'Alavi A, 2010, CONSTRUCTION AND BUILDING MATERIALS', 'Engel‐Cox J, 2004, JOURNAL OF THE AIR &amp; WASTE MANAGEMENT ASSOCIATION', 'Alavi A, 2009, ENGINEERING WITH COMPUTERS', 'Javadi A, 2006, COMPUTERS AND GEOTECHNICS', 'Das S, 2008, ENGINEERING GEOLOGY', 'Azamathulla H, 2011, APPLIED SOFT COMPUTING', 'Boldo E, 2010, ENVIRONMENT INTERNATIONAL', 'Lary D, 2014, GEOSPATIAL HEALTH', 'Garg A, 2014, RAPID PROTOTYPING JOURNAL', 'Garg A, 2014, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Ginoux P, 2003, JOURNAL OF GEOPHYSICAL RESEARCH ATMOSPHERES', 'Chuang M, 2011, ATMOSPHERIC ENVIRONMENT', 'Alavi A, 2011, GEOSCIENCE FRONTIERS', 'Makkeasorn A, 2006, WATER RESOURCES RESEARCH', 'Liu Y, 2012, ENVIRONMENT INTERNATIONAL', 'Zahabiyoun B, 2012, CLEAN - SOIL AIR WATER', 'Azamathulla H, 2011, OCEAN ENGINEERING', 'Makkeasorn A, 2008, JOURNAL OF ENVIRONMENTAL MANAGEMENT', 'Shahin M, 2005, COMPUTERS AND GEOTECHNICS', 'Çabalar A, 2009, COMPUTERS &amp; GEOSCIENCES', 'Ayala A, 2011, AIR QUALITY ATMOSPHERE &amp; HEALTH', 'Karakus M, 2010, COMPUTERS &amp; GEOSCIENCES', 'Liu Y, 2011, ATMOSPHERIC ENVIRONMENT', 'Garg A, 2014, MECCANICA', 'Madadi M, 2014, EARTH SCIENCE INFORMATICS', 'Li W, 2007, INTERNATIONAL JOURNAL OF ROCK MECHANICS AND MINING SCIENCES', 'Zhai S, 2006, JOURNAL OF CHINA UNIVERSITY OF GEOSCIENCES', 'Alavi A, 2011, JOURNAL OF EARTHQUAKE ENGINEERING', 'Samui P, 2010, INTERNATIONAL JOURNAL FOR NUMERICAL AND ANALYTICAL METHODS IN GEOMECHANICS', 'Ravandi E, 2013, INTERNATIONAL JOURNAL OF MINING SCIENCE AND TECHNOLOGY', 'John D, 2010, INTECH EBOOKS', 'Santos J, 2010, ', 'Nikravesh M, 2007, STUDIES IN FUZZINESS AND SOFT COMPUTING', 'Chen L, 2003, INTERNATIONAL JOURNAL OF REMOTE SENSING', 'Lewkowski C, 2010, EGU GENERAL ASSEMBLY CONFERENCE ABSTRACTS', 'Chen L, 2011, HYDROLOGICAL PROCESSES', 'Chuang M, 2012, ATMOSPHERIC ENVIRONMENT', 'Change I, 2014, CAMBRIDGE UNIVERSITY PRESS EBOOKS', 'Dockery D, 1993, NEW ENGLAND JOURNAL OF MEDICINE', 'Stocker R, 2013, ', 'Pope C, 2006, JOURNAL OF THE AIR &amp; WASTE MANAGEMENT ASSOCIATION', 'Brook R, 2010, CIRCULATION', 'Foody G, 2002, REMOTE SENSING OF ENVIRONMENT', 'Grell G, 2005, ATMOSPHERIC ENVIRONMENT', 'Kohonen T, 1982, BIOLOGICAL CYBERNETICS', 'Schauer J, 1996, ATMOSPHERIC ENVIRONMENT', 'Atkinson P, 1997, INTERNATIONAL JOURNAL OF REMOTE SENSING', 'Hansen J, 1988, JOURNAL OF GEOPHYSICAL RESEARCH ATMOSPHERES', 'Tegen I, 1996, JOURNAL OF GEOPHYSICAL RESEARCH ATMOSPHERES', 'Engel‐Cox J, 2004, ATMOSPHERIC ENVIRONMENT', 'Baykasoğlu A, 2007, EXPERT SYSTEMS WITH APPLICATIONS', 'Detto M, 2006, WATER RESOURCES RESEARCH', 'Liu Y, 2006, REMOTE SENSING OF ENVIRONMENT', 'Schaap M, 2009, ATMOSPHERIC CHEMISTRY AND PHYSICS', 'Gandomi A, 2011, INFORMATION SCIENCES', 'Azamathulla H, 2010, APPLIED SOFT COMPUTING', 'Gandomi A, 2011, ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE', 'Risacher F, 1991, CHEMICAL GEOLOGY', 'Walker A, 2009, JOURNAL OF GEOPHYSICAL RESEARCH ATMOSPHERES', 'Brown M, 2008, INTERNATIONAL JOURNAL OF REMOTE SENSING', 'Carpenter G, 1997, IEEE TRANSACTIONS ON GEOSCIENCE AND REMOTE SENSING', 'Lary D, 2009, IEEE GEOSCIENCE AND REMOTE SENSING LETTERS', 'Risacher F, 1991, GEOCHIMICA ET COSMOCHIMICA ACTA', 'Beiki M, 2010, INTERNATIONAL JOURNAL OF ROCK MECHANICS AND MINING SCIENCES', 'Özbek A, 2013, JOURNAL OF ROCK MECHANICS AND GEOTECHNICAL ENGINEERING', 'Imperatore P, 2010, INTECH EBOOKS', 'Rajeev K, 2008, JOURNAL OF GEOPHYSICAL RESEARCH ATMOSPHERES', 'Gandomi A, 2013, INTERNATIONAL JOURNAL OF EARTHQUAKE ENGINEERING AND HAZARD MITIGATION (IREHM)', 'Lary D, 2004, ATMOSPHERIC CHEMISTRY AND PHYSICS', 'Rosin P, 2002, ', 'Prospero J, 2003, GEOCHIMICA ET COSMOCHIMICA ACTA SUPPLEMENT', 'Lary D, 2007, GEOPHYSICAL RESEARCH LETTERS', 'Lee H, 2010, EPIDEMIOLOGY', ', 2002, ']</t>
         </is>
       </c>
       <c r="V199" t="inlineStr">
@@ -23305,12 +23325,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>Collins G, 2024, BMJ</t>
+          <t>Lary D, 2015, GEOSCIENCE FRONTIERS</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>Collins G, 2024, BMJ</t>
+          <t>Lary D, 2015, GEOSCIENCE FRONTIERS</t>
         </is>
       </c>
     </row>
